--- a/모닛_5개년_사업계획_손익계산서_2026-2030.xlsx
+++ b/모닛_5개년_사업계획_손익계산서_2026-2030.xlsx
@@ -1030,6 +1030,21 @@
 </comments>
 </file>
 
+<file path=xl/comments/comment2.xml><?xml version="1.0" encoding="utf-8"?>
+<comments xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main">
+  <authors>
+    <author>MONIT 사업계획</author>
+  </authors>
+  <commentList>
+    <comment ref="C91" authorId="0" shapeId="0">
+      <text>
+        <t>2026년 09월분 급상여대장(지급일 2026-09-25): 7명 지급합계 39,688,891원 ÷ 7 = 5,669,841원. 대표이사 포함, 기본급·연장·식대·상여 등 지급 항목 합계(공제 전). 연간 상여·성과급은 별도 반영 없음.</t>
+      </text>
+    </comment>
+  </commentList>
+</comments>
+</file>
+
 <file path=xl/drawings/drawing1.xml><?xml version="1.0" encoding="utf-8"?>
 <wsDr xmlns:a="http://schemas.openxmlformats.org/drawingml/2006/main" xmlns:c="http://schemas.openxmlformats.org/drawingml/2006/chart" xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" xmlns="http://schemas.openxmlformats.org/drawingml/2006/spreadsheetDrawing">
   <oneCellAnchor>
@@ -1642,27 +1657,27 @@
       </c>
       <c r="D12" s="13">
         <f>'3_연간손익'!D13/100000</f>
-        <v>-0.700931107344632</v>
+        <v>-2.92328310734463</v>
       </c>
       <c r="E12" s="13">
         <f>'3_연간손익'!E13/100000</f>
-        <v>6.60993944</v>
+        <v>3.26335378</v>
       </c>
       <c r="F12" s="13">
         <f>'3_연간손익'!F13/100000</f>
-        <v>30.8793016290429</v>
+        <v>19.1966269398429</v>
       </c>
       <c r="G12" s="13">
         <f>'3_연간손익'!G13/100000</f>
-        <v>79.3051551401019</v>
+        <v>54.9743045583219</v>
       </c>
       <c r="H12" s="13">
         <f>'3_연간손익'!H13/100000</f>
-        <v>214.119925449323</v>
+        <v>164.668697971292</v>
       </c>
       <c r="I12" s="14">
         <f>IFERROR(('3_연간손익'!H13/'3_연간손익'!C13)^(1/5)-1,"n/a")</f>
-        <v>2.80643221565146</v>
+        <v>2.61167692074088</v>
       </c>
     </row>
     <row r="13">
@@ -1677,23 +1692,23 @@
       </c>
       <c r="D13" s="16">
         <f>'3_연간손익'!D14</f>
-        <v>-0.0584109256120527</v>
+        <v>-0.243606925612053</v>
       </c>
       <c r="E13" s="16">
         <f>'3_연간손익'!E14</f>
-        <v>0.0660859128737737</v>
+        <v>0.0326268819160891</v>
       </c>
       <c r="F13" s="16">
         <f>'3_연간손익'!F14</f>
-        <v>0.0935736413001299</v>
+        <v>0.0581715967874026</v>
       </c>
       <c r="G13" s="16">
         <f>'3_연간손익'!G14</f>
-        <v>0.113293078771574</v>
+        <v>0.0785347207976027</v>
       </c>
       <c r="H13" s="16">
         <f>'3_연간손익'!H14</f>
-        <v>0.137256362467515</v>
+        <v>0.105556857673905</v>
       </c>
     </row>
     <row r="14">
@@ -1708,27 +1723,27 @@
       </c>
       <c r="D14" s="17">
         <f>'3_연간손익'!D21/100000</f>
-        <v>-0.626821427344632</v>
+        <v>-2.84917342734463</v>
       </c>
       <c r="E14" s="17">
         <f>'3_연간손익'!E21/100000</f>
-        <v>6.24193944</v>
+        <v>2.89535378</v>
       </c>
       <c r="F14" s="17">
         <f>'3_연간손익'!F21/100000</f>
-        <v>28.4775097078692</v>
+        <v>17.5766269398429</v>
       </c>
       <c r="G14" s="17">
         <f>'3_연간손익'!G21/100000</f>
-        <v>59.0828210092795</v>
+        <v>42.8983203511415</v>
       </c>
       <c r="H14" s="17">
         <f>'3_연간손익'!H21/100000</f>
-        <v>162.920663490587</v>
+        <v>124.543184417608</v>
       </c>
       <c r="I14" s="14">
         <f>IFERROR(('3_연간손익'!H21/'3_연간손익'!C21)^(1/5)-1,"n/a")</f>
-        <v>4.00892388037824</v>
+        <v>3.74693397338258</v>
       </c>
     </row>
     <row r="15">
@@ -1739,23 +1754,23 @@
       </c>
       <c r="D15" s="17">
         <f>'3_연간손익'!D23/100000</f>
-        <v>-0.520931107344632</v>
+        <v>-2.74328310734463</v>
       </c>
       <c r="E15" s="17">
         <f>'3_연간손익'!E23/100000</f>
-        <v>10.96946944</v>
+        <v>7.62288378</v>
       </c>
       <c r="F15" s="17">
         <f>'3_연간손익'!F23/100000</f>
-        <v>35.7388316290429</v>
+        <v>24.0561569398429</v>
       </c>
       <c r="G15" s="17">
         <f>'3_연간손익'!G23/100000</f>
-        <v>85.0646851401019</v>
+        <v>60.7338345583219</v>
       </c>
       <c r="H15" s="17">
         <f>'3_연간손익'!H23/100000</f>
-        <v>221.079455449323</v>
+        <v>171.628227971292</v>
       </c>
     </row>
     <row r="16">
@@ -7169,123 +7184,123 @@
       </c>
       <c r="C30" s="18">
         <f>'7_비용인력'!C19</f>
-        <v>25200</v>
+        <v>39690</v>
       </c>
       <c r="D30" s="18">
         <f>'7_비용인력'!D19</f>
-        <v>25200</v>
+        <v>39690</v>
       </c>
       <c r="E30" s="18">
         <f>'7_비용인력'!E19</f>
-        <v>25200</v>
+        <v>39690</v>
       </c>
       <c r="F30" s="18">
         <f>'7_비용인력'!F19</f>
-        <v>25200</v>
+        <v>39690</v>
       </c>
       <c r="G30" s="18">
         <f>'7_비용인력'!G19</f>
-        <v>25200</v>
+        <v>39690</v>
       </c>
       <c r="H30" s="18">
         <f>'7_비용인력'!H19</f>
-        <v>25200</v>
+        <v>39690</v>
       </c>
       <c r="I30" s="18">
         <f>'7_비용인력'!I19</f>
-        <v>25200</v>
+        <v>39690</v>
       </c>
       <c r="J30" s="18">
         <f>'7_비용인력'!J19</f>
-        <v>25200</v>
+        <v>39690</v>
       </c>
       <c r="K30" s="18">
         <f>'7_비용인력'!K19</f>
-        <v>25200</v>
+        <v>39690</v>
       </c>
       <c r="L30" s="18">
         <f>'7_비용인력'!L19</f>
-        <v>28800</v>
+        <v>45360</v>
       </c>
       <c r="M30" s="18">
         <f>'7_비용인력'!M19</f>
-        <v>28800</v>
+        <v>45360</v>
       </c>
       <c r="N30" s="18">
         <f>'7_비용인력'!N19</f>
-        <v>32400</v>
+        <v>51030</v>
       </c>
       <c r="O30" s="35">
         <f>'7_비용인력'!O19</f>
-        <v>316800</v>
+        <v>498960</v>
       </c>
       <c r="P30" s="18">
         <f>'7_비용인력'!P19</f>
-        <v>46000</v>
+        <v>60669</v>
       </c>
       <c r="Q30" s="18">
         <f>'7_비용인력'!Q19</f>
-        <v>50600</v>
+        <v>66735.9</v>
       </c>
       <c r="R30" s="18">
         <f>'7_비용인력'!R19</f>
-        <v>55200</v>
+        <v>72802.8</v>
       </c>
       <c r="S30" s="18">
         <f>'7_비용인력'!S19</f>
-        <v>59800</v>
+        <v>78869.7</v>
       </c>
       <c r="T30" s="18">
         <f>'7_비용인력'!T19</f>
-        <v>64400</v>
+        <v>84936.6</v>
       </c>
       <c r="U30" s="18">
         <f>'7_비용인력'!U19</f>
-        <v>69000</v>
+        <v>91003.5</v>
       </c>
       <c r="V30" s="18">
         <f>'7_비용인력'!V19</f>
-        <v>73600</v>
+        <v>97070.4</v>
       </c>
       <c r="W30" s="18">
         <f>'7_비용인력'!W19</f>
-        <v>78200</v>
+        <v>103137.3</v>
       </c>
       <c r="X30" s="18">
         <f>'7_비용인력'!X19</f>
-        <v>82800</v>
+        <v>109204.2</v>
       </c>
       <c r="Y30" s="18">
         <f>'7_비용인력'!Y19</f>
-        <v>87400</v>
+        <v>115271.1</v>
       </c>
       <c r="Z30" s="18">
         <f>'7_비용인력'!Z19</f>
-        <v>92000</v>
+        <v>121338</v>
       </c>
       <c r="AA30" s="18">
         <f>'7_비용인력'!AA19</f>
-        <v>101200</v>
+        <v>133471.8</v>
       </c>
       <c r="AB30" s="35">
         <f>'7_비용인력'!AB19</f>
-        <v>860200</v>
+        <v>1134510.3</v>
       </c>
       <c r="AC30" s="24">
         <f>'7_비용인력'!AC19</f>
-        <v>3210000</v>
+        <v>4167596.286</v>
       </c>
       <c r="AD30" s="24">
         <f>'7_비용인력'!AD19</f>
-        <v>6966000</v>
+        <v>8960332.0149</v>
       </c>
       <c r="AE30" s="24">
         <f>'7_비용인력'!AE19</f>
-        <v>13338000</v>
+        <v>17391379.301478</v>
       </c>
       <c r="AF30" s="36">
         <f>'7_비용인력'!AF19</f>
-        <v>24691000</v>
+        <v>32152777.902378</v>
       </c>
     </row>
     <row r="31">
@@ -7296,123 +7311,123 @@
       </c>
       <c r="C31" s="18">
         <f>'7_비용인력'!C20</f>
-        <v>5544</v>
+        <v>8731.8</v>
       </c>
       <c r="D31" s="18">
         <f>'7_비용인력'!D20</f>
-        <v>5544</v>
+        <v>8731.8</v>
       </c>
       <c r="E31" s="18">
         <f>'7_비용인력'!E20</f>
-        <v>5544</v>
+        <v>8731.8</v>
       </c>
       <c r="F31" s="18">
         <f>'7_비용인력'!F20</f>
-        <v>5544</v>
+        <v>8731.8</v>
       </c>
       <c r="G31" s="18">
         <f>'7_비용인력'!G20</f>
-        <v>5544</v>
+        <v>8731.8</v>
       </c>
       <c r="H31" s="18">
         <f>'7_비용인력'!H20</f>
-        <v>5544</v>
+        <v>8731.8</v>
       </c>
       <c r="I31" s="18">
         <f>'7_비용인력'!I20</f>
-        <v>5544</v>
+        <v>8731.8</v>
       </c>
       <c r="J31" s="18">
         <f>'7_비용인력'!J20</f>
-        <v>5544</v>
+        <v>8731.8</v>
       </c>
       <c r="K31" s="18">
         <f>'7_비용인력'!K20</f>
-        <v>5544</v>
+        <v>8731.8</v>
       </c>
       <c r="L31" s="18">
         <f>'7_비용인력'!L20</f>
-        <v>6336</v>
+        <v>9979.2</v>
       </c>
       <c r="M31" s="18">
         <f>'7_비용인력'!M20</f>
-        <v>6336</v>
+        <v>9979.2</v>
       </c>
       <c r="N31" s="18">
         <f>'7_비용인력'!N20</f>
-        <v>7128</v>
+        <v>11226.6</v>
       </c>
       <c r="O31" s="35">
         <f>'7_비용인력'!O20</f>
-        <v>69696</v>
+        <v>109771.2</v>
       </c>
       <c r="P31" s="18">
         <f>'7_비용인력'!P20</f>
-        <v>10120</v>
+        <v>13347.18</v>
       </c>
       <c r="Q31" s="18">
         <f>'7_비용인력'!Q20</f>
-        <v>11132</v>
+        <v>14681.898</v>
       </c>
       <c r="R31" s="18">
         <f>'7_비용인력'!R20</f>
-        <v>12144</v>
+        <v>16016.616</v>
       </c>
       <c r="S31" s="18">
         <f>'7_비용인력'!S20</f>
-        <v>13156</v>
+        <v>17351.334</v>
       </c>
       <c r="T31" s="18">
         <f>'7_비용인력'!T20</f>
-        <v>14168</v>
+        <v>18686.052</v>
       </c>
       <c r="U31" s="18">
         <f>'7_비용인력'!U20</f>
-        <v>15180</v>
+        <v>20020.77</v>
       </c>
       <c r="V31" s="18">
         <f>'7_비용인력'!V20</f>
-        <v>16192</v>
+        <v>21355.488</v>
       </c>
       <c r="W31" s="18">
         <f>'7_비용인력'!W20</f>
-        <v>17204</v>
+        <v>22690.206</v>
       </c>
       <c r="X31" s="18">
         <f>'7_비용인력'!X20</f>
-        <v>18216</v>
+        <v>24024.924</v>
       </c>
       <c r="Y31" s="18">
         <f>'7_비용인력'!Y20</f>
-        <v>19228</v>
+        <v>25359.642</v>
       </c>
       <c r="Z31" s="18">
         <f>'7_비용인력'!Z20</f>
-        <v>20240</v>
+        <v>26694.36</v>
       </c>
       <c r="AA31" s="18">
         <f>'7_비용인력'!AA20</f>
-        <v>22264</v>
+        <v>29363.796</v>
       </c>
       <c r="AB31" s="35">
         <f>'7_비용인력'!AB20</f>
-        <v>189244</v>
+        <v>249592.266</v>
       </c>
       <c r="AC31" s="24">
         <f>'7_비용인력'!AC20</f>
-        <v>706200</v>
+        <v>916871.18292</v>
       </c>
       <c r="AD31" s="24">
         <f>'7_비용인력'!AD20</f>
-        <v>1532520</v>
+        <v>1971273.043278</v>
       </c>
       <c r="AE31" s="24">
         <f>'7_비용인력'!AE20</f>
-        <v>2934360</v>
+        <v>3826103.44632516</v>
       </c>
       <c r="AF31" s="36">
         <f>'7_비용인력'!AF20</f>
-        <v>5432020</v>
+        <v>7073611.13852316</v>
       </c>
     </row>
     <row r="32">
@@ -8566,123 +8581,123 @@
       </c>
       <c r="C41" s="26">
         <f>SUM(C30:C40)</f>
-        <v>48067.6909461035</v>
+        <v>65745.4909461035</v>
       </c>
       <c r="D41" s="26">
         <f>SUM(D30:D40)</f>
-        <v>48264.301115595</v>
+        <v>65942.101115595</v>
       </c>
       <c r="E41" s="26">
         <f>SUM(E30:E40)</f>
-        <v>48460.9112850865</v>
+        <v>66138.7112850865</v>
       </c>
       <c r="F41" s="26">
         <f>SUM(F30:F40)</f>
-        <v>48657.5214545781</v>
+        <v>66335.3214545781</v>
       </c>
       <c r="G41" s="26">
         <f>SUM(G30:G40)</f>
-        <v>48854.1316240696</v>
+        <v>66531.9316240696</v>
       </c>
       <c r="H41" s="26">
         <f>SUM(H30:H40)</f>
-        <v>49050.7417935611</v>
+        <v>66728.5417935611</v>
       </c>
       <c r="I41" s="26">
         <f>SUM(I30:I40)</f>
-        <v>51232.2408519415</v>
+        <v>68910.0408519415</v>
       </c>
       <c r="J41" s="26">
         <f>SUM(J30:J40)</f>
-        <v>52253.7399103219</v>
+        <v>69931.5399103219</v>
       </c>
       <c r="K41" s="26">
         <f>SUM(K30:K40)</f>
-        <v>53275.2389687024</v>
+        <v>70953.0389687024</v>
       </c>
       <c r="L41" s="26">
         <f>SUM(L30:L40)</f>
-        <v>59225.7750641198</v>
+        <v>79428.9750641198</v>
       </c>
       <c r="M41" s="26">
         <f>SUM(M30:M40)</f>
-        <v>61705.3511595373</v>
+        <v>81908.5511595373</v>
       </c>
       <c r="N41" s="26">
         <f>SUM(N30:N40)</f>
-        <v>70648.3558263833</v>
+        <v>93376.9558263833</v>
       </c>
       <c r="O41" s="27">
         <f>SUM(O30:O40)</f>
-        <v>639696</v>
+        <v>861931.2</v>
       </c>
       <c r="P41" s="26">
         <f>SUM(P30:P40)</f>
-        <v>162350.338714017</v>
+        <v>180246.518714017</v>
       </c>
       <c r="Q41" s="26">
         <f>SUM(Q30:Q40)</f>
-        <v>184602.998737913</v>
+        <v>204288.796737913</v>
       </c>
       <c r="R41" s="26">
         <f>SUM(R30:R40)</f>
-        <v>206855.65876181</v>
+        <v>228331.07476181</v>
       </c>
       <c r="S41" s="26">
         <f>SUM(S30:S40)</f>
-        <v>228854.081497571</v>
+        <v>252119.115497571</v>
       </c>
       <c r="T41" s="26">
         <f>SUM(T30:T40)</f>
-        <v>250852.504233332</v>
+        <v>275907.156233332</v>
       </c>
       <c r="U41" s="26">
         <f>SUM(U30:U40)</f>
-        <v>281850.926969093</v>
+        <v>308695.196969093</v>
       </c>
       <c r="V41" s="26">
         <f>SUM(V30:V40)</f>
-        <v>302782.683038187</v>
+        <v>331416.571038187</v>
       </c>
       <c r="W41" s="26">
         <f>SUM(W30:W40)</f>
-        <v>322155.61557787</v>
+        <v>352579.12157787</v>
       </c>
       <c r="X41" s="26">
         <f>SUM(X30:X40)</f>
-        <v>332528.548117552</v>
+        <v>364741.672117552</v>
       </c>
       <c r="Y41" s="26">
         <f>SUM(Y30:Y40)</f>
-        <v>338140.548117552</v>
+        <v>372143.290117552</v>
       </c>
       <c r="Z41" s="26">
         <f>SUM(Z30:Z40)</f>
-        <v>343752.548117552</v>
+        <v>379544.908117552</v>
       </c>
       <c r="AA41" s="26">
         <f>SUM(AA30:AA40)</f>
-        <v>354976.548117552</v>
+        <v>394348.144117552</v>
       </c>
       <c r="AB41" s="27">
         <f>SUM(AB30:AB40)</f>
-        <v>3309703</v>
+        <v>3644361.566</v>
       </c>
       <c r="AC41" s="28">
         <f>SUM(AC30:AC40)</f>
-        <v>9986153</v>
+        <v>11154420.46892</v>
       </c>
       <c r="AD41" s="28">
         <f>SUM(AD30:AD40)</f>
-        <v>19994473</v>
+        <v>22427558.058178</v>
       </c>
       <c r="AE41" s="28">
         <f>SUM(AE30:AE40)</f>
-        <v>42300313</v>
+        <v>47245435.7478032</v>
       </c>
       <c r="AF41" s="26">
         <f>SUM(AF30:AF40)</f>
-        <v>76230338</v>
+        <v>85333707.0409012</v>
       </c>
     </row>
     <row r="42">
@@ -8693,123 +8708,123 @@
       </c>
       <c r="C42" s="37">
         <f>C26-C41</f>
-        <v>-15976.5802476011</v>
+        <v>-33654.3802476011</v>
       </c>
       <c r="D42" s="37">
         <f>D26-D41</f>
-        <v>-15364.3768577706</v>
+        <v>-33042.1768577706</v>
       </c>
       <c r="E42" s="37">
         <f>E26-E41</f>
-        <v>-14752.1734679401</v>
+        <v>-32429.9734679401</v>
       </c>
       <c r="F42" s="37">
         <f>F26-F41</f>
-        <v>-14139.9700781096</v>
+        <v>-31817.7700781096</v>
       </c>
       <c r="G42" s="37">
         <f>G26-G41</f>
-        <v>-13527.7666882791</v>
+        <v>-31205.5666882791</v>
       </c>
       <c r="H42" s="37">
         <f>H26-H41</f>
-        <v>-12915.5632984486</v>
+        <v>-30593.3632984486</v>
       </c>
       <c r="I42" s="37">
         <f>I26-I41</f>
-        <v>-6544.82657528472</v>
+        <v>-24222.6265752847</v>
       </c>
       <c r="J42" s="37">
         <f>J26-J41</f>
-        <v>-3364.08985212089</v>
+        <v>-21041.8898521209</v>
       </c>
       <c r="K42" s="37">
         <f>K26-K41</f>
-        <v>-183.353128957046</v>
+        <v>-17861.1531289571</v>
       </c>
       <c r="L42" s="37">
         <f>L26-L41</f>
-        <v>454.920631243826</v>
+        <v>-19748.2793687562</v>
       </c>
       <c r="M42" s="37">
         <f>M26-M41</f>
-        <v>8268.95839144471</v>
+        <v>-11934.2416085553</v>
       </c>
       <c r="N42" s="37">
         <f>N26-N41</f>
-        <v>17951.7104373599</v>
+        <v>-4776.88956264011</v>
       </c>
       <c r="O42" s="38">
         <f>O26-O41</f>
-        <v>-70093.1107344632</v>
+        <v>-292328.310734463</v>
       </c>
       <c r="P42" s="37">
         <f>P26-P41</f>
-        <v>-48430.9953446328</v>
+        <v>-66327.1753446328</v>
       </c>
       <c r="Q42" s="37">
         <f>Q26-Q41</f>
-        <v>-26907.4427723496</v>
+        <v>-46593.2407723496</v>
       </c>
       <c r="R42" s="37">
         <f>R26-R41</f>
-        <v>-5383.8902000665</v>
+        <v>-26859.3062000665</v>
       </c>
       <c r="S42" s="37">
         <f>S26-S41</f>
-        <v>15721.6962705218</v>
+        <v>-7543.33772947823</v>
       </c>
       <c r="T42" s="37">
         <f>T26-T41</f>
-        <v>36827.28274111</v>
+        <v>11772.63074111</v>
       </c>
       <c r="U42" s="37">
         <f>U26-U41</f>
-        <v>76382.8692116982</v>
+        <v>49538.5992116982</v>
       </c>
       <c r="V42" s="37">
         <f>V26-V41</f>
-        <v>95734.8556822865</v>
+        <v>67100.9676822865</v>
       </c>
       <c r="W42" s="37">
         <f>W26-W41</f>
-        <v>112563.665682287</v>
+        <v>82140.1596822866</v>
       </c>
       <c r="X42" s="37">
         <f>X26-X41</f>
-        <v>110942.475682286</v>
+        <v>78729.3516822865</v>
       </c>
       <c r="Y42" s="37">
         <f>Y26-Y41</f>
-        <v>105330.475682286</v>
+        <v>71327.7336822865</v>
       </c>
       <c r="Z42" s="37">
         <f>Z26-Z41</f>
-        <v>99718.4756822865</v>
+        <v>63926.1156822864</v>
       </c>
       <c r="AA42" s="37">
         <f>AA26-AA41</f>
-        <v>88494.4756822865</v>
+        <v>49122.8796822865</v>
       </c>
       <c r="AB42" s="38">
         <f>AB26-AB41</f>
-        <v>660993.944</v>
+        <v>326335.378</v>
       </c>
       <c r="AC42" s="39">
         <f>AC26-AC41</f>
-        <v>3087930.16290429</v>
+        <v>1919662.69398429</v>
       </c>
       <c r="AD42" s="39">
         <f>AD26-AD41</f>
-        <v>7930515.51401019</v>
+        <v>5497430.45583219</v>
       </c>
       <c r="AE42" s="39">
         <f>AE26-AE41</f>
-        <v>21411992.5449323</v>
+        <v>16466869.7971292</v>
       </c>
       <c r="AF42" s="37">
         <f>AF26-AF41</f>
-        <v>33021339.0551124</v>
+        <v>23917970.0142112</v>
       </c>
     </row>
     <row r="43">
@@ -8820,123 +8835,123 @@
       </c>
       <c r="C43" s="14">
         <f>IFERROR(C42/C14,0)</f>
-        <v>-0.236880945513925</v>
+        <v>-0.498985470619341</v>
       </c>
       <c r="D43" s="14">
         <f>IFERROR(D42/D14,0)</f>
-        <v>-0.222219551337776</v>
+        <v>-0.477898829515085</v>
       </c>
       <c r="E43" s="14">
         <f>IFERROR(E42/E14,0)</f>
-        <v>-0.208259778268134</v>
+        <v>-0.457821289747737</v>
       </c>
       <c r="F43" s="14">
         <f>IFERROR(F42/F14,0)</f>
-        <v>-0.194952439108384</v>
+        <v>-0.43868210819768</v>
       </c>
       <c r="G43" s="14">
         <f>IFERROR(G42/G14,0)</f>
-        <v>-0.182252839370495</v>
+        <v>-0.420417003349996</v>
       </c>
       <c r="H43" s="14">
         <f>IFERROR(H42/H14,0)</f>
-        <v>-0.170120275777294</v>
+        <v>-0.402967434019094</v>
       </c>
       <c r="I43" s="14">
         <f>IFERROR(I42/I14,0)</f>
-        <v>-0.0690920314691576</v>
+        <v>-0.255711967055814</v>
       </c>
       <c r="J43" s="14">
         <f>IFERROR(J42/J14,0)</f>
-        <v>-0.0324931618636163</v>
+        <v>-0.203239973644075</v>
       </c>
       <c r="K43" s="14">
         <f>IFERROR(K42/K14,0)</f>
-        <v>-0.00163215201640456</v>
+        <v>-0.15899438019172</v>
       </c>
       <c r="L43" s="14">
         <f>IFERROR(L42/L14,0)</f>
-        <v>0.00361697099457423</v>
+        <v>-0.157014100403056</v>
       </c>
       <c r="M43" s="14">
         <f>IFERROR(M42/M14,0)</f>
-        <v>0.0561942375221244</v>
+        <v>-0.0811027914097904</v>
       </c>
       <c r="N43" s="14">
         <f>IFERROR(N42/N14,0)</f>
-        <v>0.0963165651599776</v>
+        <v>-0.0256295129329029</v>
       </c>
       <c r="O43" s="30">
         <f>IFERROR(O42/O14,0)</f>
-        <v>-0.0584109256120527</v>
+        <v>-0.243606925612053</v>
       </c>
       <c r="P43" s="14">
         <f>IFERROR(P42/P14,0)</f>
-        <v>-0.169335505042919</v>
+        <v>-0.231908216115124</v>
       </c>
       <c r="Q43" s="14">
         <f>IFERROR(Q42/Q14,0)</f>
-        <v>-0.0677865161698741</v>
+        <v>-0.117379919591144</v>
       </c>
       <c r="R43" s="14">
         <f>IFERROR(R42/R14,0)</f>
-        <v>-0.0106006794733265</v>
+        <v>-0.0528849744928527</v>
       </c>
       <c r="S43" s="14">
         <f>IFERROR(S42/S14,0)</f>
-        <v>0.0254757313923249</v>
+        <v>-0.0122233658818419</v>
       </c>
       <c r="T43" s="14">
         <f>IFERROR(T42/T14,0)</f>
-        <v>0.0507006376162704</v>
+        <v>0.0162075461605775</v>
       </c>
       <c r="U43" s="14">
         <f>IFERROR(U42/U14,0)</f>
-        <v>0.0852858536126479</v>
+        <v>0.0553126867862862</v>
       </c>
       <c r="V43" s="14">
         <f>IFERROR(V42/V14,0)</f>
-        <v>0.0959515357613975</v>
+        <v>0.0672528396716701</v>
       </c>
       <c r="W43" s="14">
         <f>IFERROR(W42/W14,0)</f>
-        <v>0.103318581960321</v>
+        <v>0.0753938206341094</v>
       </c>
       <c r="X43" s="14">
         <f>IFERROR(X42/X14,0)</f>
-        <v>0.0989479218800416</v>
+        <v>0.0702175221169055</v>
       </c>
       <c r="Y43" s="14">
         <f>IFERROR(Y42/Y14,0)</f>
-        <v>0.0939426636669381</v>
+        <v>0.0636161305836278</v>
       </c>
       <c r="Z43" s="14">
         <f>IFERROR(Z42/Z14,0)</f>
-        <v>0.0889374054538347</v>
+        <v>0.0570147390503501</v>
       </c>
       <c r="AA43" s="14">
         <f>IFERROR(AA42/AA14,0)</f>
-        <v>0.0789268890276278</v>
+        <v>0.0438119559837948</v>
       </c>
       <c r="AB43" s="30">
         <f>IFERROR(AB42/AB14,0)</f>
-        <v>0.0660859128737737</v>
+        <v>0.0326268819160891</v>
       </c>
       <c r="AC43" s="31">
         <f>IFERROR(AC42/AC14,0)</f>
-        <v>0.0935736413001299</v>
+        <v>0.0581715967874026</v>
       </c>
       <c r="AD43" s="31">
         <f>IFERROR(AD42/AD14,0)</f>
-        <v>0.113293078771574</v>
+        <v>0.0785347207976027</v>
       </c>
       <c r="AE43" s="31">
         <f>IFERROR(AE42/AE14,0)</f>
-        <v>0.137256362467515</v>
+        <v>0.105556857673905</v>
       </c>
       <c r="AF43" s="14">
         <f>IFERROR(AF42/AF14,0)</f>
-        <v>0.122209806614015</v>
+        <v>0.0885188358097193</v>
       </c>
     </row>
     <row r="44"/>
@@ -9463,123 +9478,123 @@
       </c>
       <c r="C50" s="26">
         <f>C42+C46-C48</f>
-        <v>-15358.9995809344</v>
+        <v>-33036.7995809344</v>
       </c>
       <c r="D50" s="26">
         <f>D42+D46-D48</f>
-        <v>-14746.7961911039</v>
+        <v>-32424.5961911039</v>
       </c>
       <c r="E50" s="26">
         <f>E42+E46-E48</f>
-        <v>-14134.5928012734</v>
+        <v>-31812.3928012734</v>
       </c>
       <c r="F50" s="26">
         <f>F42+F46-F48</f>
-        <v>-13522.3894114429</v>
+        <v>-31200.1894114429</v>
       </c>
       <c r="G50" s="26">
         <f>G42+G46-G48</f>
-        <v>-12910.1860216124</v>
+        <v>-30587.9860216124</v>
       </c>
       <c r="H50" s="26">
         <f>H42+H46-H48</f>
-        <v>-12297.9826317819</v>
+        <v>-29975.7826317819</v>
       </c>
       <c r="I50" s="26">
         <f>I42+I46-I48</f>
-        <v>-5927.24590861806</v>
+        <v>-23605.045908618</v>
       </c>
       <c r="J50" s="26">
         <f>J42+J46-J48</f>
-        <v>-2746.50918545423</v>
+        <v>-20424.3091854542</v>
       </c>
       <c r="K50" s="26">
         <f>K42+K46-K48</f>
-        <v>434.227537709621</v>
+        <v>-17243.5724622904</v>
       </c>
       <c r="L50" s="26">
         <f>L42+L46-L48</f>
-        <v>1072.50129791049</v>
+        <v>-19130.6987020895</v>
       </c>
       <c r="M50" s="26">
         <f>M42+M46-M48</f>
-        <v>8886.53905811138</v>
+        <v>-11316.6609418886</v>
       </c>
       <c r="N50" s="26">
         <f>N42+N46-N48</f>
-        <v>18569.2911040266</v>
+        <v>-4159.30889597344</v>
       </c>
       <c r="O50" s="27">
         <f>O42+O46-O48</f>
-        <v>-62682.1427344632</v>
+        <v>-284917.342734463</v>
       </c>
       <c r="P50" s="26">
         <f>P42+P46-P48</f>
-        <v>-51497.6620112995</v>
+        <v>-69393.8420112995</v>
       </c>
       <c r="Q50" s="26">
         <f>Q42+Q46-Q48</f>
-        <v>-29974.1094390163</v>
+        <v>-49659.9074390163</v>
       </c>
       <c r="R50" s="26">
         <f>R42+R46-R48</f>
-        <v>-8450.55686673316</v>
+        <v>-29925.9728667332</v>
       </c>
       <c r="S50" s="26">
         <f>S42+S46-S48</f>
-        <v>12655.0296038551</v>
+        <v>-10610.0043961449</v>
       </c>
       <c r="T50" s="26">
         <f>T42+T46-T48</f>
-        <v>33760.6160744433</v>
+        <v>8705.96407444329</v>
       </c>
       <c r="U50" s="26">
         <f>U42+U46-U48</f>
-        <v>73316.2025450316</v>
+        <v>46471.9325450316</v>
       </c>
       <c r="V50" s="26">
         <f>V42+V46-V48</f>
-        <v>92668.1890156198</v>
+        <v>64034.3010156198</v>
       </c>
       <c r="W50" s="26">
         <f>W42+W46-W48</f>
-        <v>109496.99901562</v>
+        <v>79073.4930156199</v>
       </c>
       <c r="X50" s="26">
         <f>X42+X46-X48</f>
-        <v>107875.80901562</v>
+        <v>75662.6850156198</v>
       </c>
       <c r="Y50" s="26">
         <f>Y42+Y46-Y48</f>
-        <v>102263.80901562</v>
+        <v>68261.0670156198</v>
       </c>
       <c r="Z50" s="26">
         <f>Z42+Z46-Z48</f>
-        <v>96651.8090156198</v>
+        <v>60859.4490156198</v>
       </c>
       <c r="AA50" s="26">
         <f>AA42+AA46-AA48</f>
-        <v>85427.8090156198</v>
+        <v>46056.2130156198</v>
       </c>
       <c r="AB50" s="27">
         <f>AB42+AB46-AB48</f>
-        <v>624193.944</v>
+        <v>289535.378</v>
       </c>
       <c r="AC50" s="28">
         <f>AC42+AC46-AC48</f>
-        <v>2925930.16290429</v>
+        <v>1757662.69398429</v>
       </c>
       <c r="AD50" s="28">
         <f>AD42+AD46-AD48</f>
-        <v>7546515.51401019</v>
+        <v>5113430.45583219</v>
       </c>
       <c r="AE50" s="28">
         <f>AE42+AE46-AE48</f>
-        <v>20883992.5449323</v>
+        <v>15938869.7971292</v>
       </c>
       <c r="AF50" s="26">
         <f>AF42+AF46-AF48</f>
-        <v>31917950.0231124</v>
+        <v>22814580.9822112</v>
       </c>
     </row>
     <row r="51">
@@ -9699,19 +9714,19 @@
       </c>
       <c r="AC51" s="24">
         <f>'7_비용인력'!AC49</f>
-        <v>78179.1921173607</v>
+        <v>0</v>
       </c>
       <c r="AD51" s="24">
         <f>'7_비용인력'!AD49</f>
-        <v>1638233.41308224</v>
+        <v>823598.420718043</v>
       </c>
       <c r="AE51" s="24">
         <f>'7_비용인력'!AE49</f>
-        <v>4591926.19587363</v>
+        <v>3484551.35536842</v>
       </c>
       <c r="AF51" s="25">
         <f>O51+AB51+AC51+AD51+AE51</f>
-        <v>6308338.80107323</v>
+        <v>4308149.77608646</v>
       </c>
     </row>
     <row r="52">
@@ -9722,123 +9737,123 @@
       </c>
       <c r="C52" s="37">
         <f>C50-C51</f>
-        <v>-15358.9995809344</v>
+        <v>-33036.7995809344</v>
       </c>
       <c r="D52" s="37">
         <f>D50-D51</f>
-        <v>-14746.7961911039</v>
+        <v>-32424.5961911039</v>
       </c>
       <c r="E52" s="37">
         <f>E50-E51</f>
-        <v>-14134.5928012734</v>
+        <v>-31812.3928012734</v>
       </c>
       <c r="F52" s="37">
         <f>F50-F51</f>
-        <v>-13522.3894114429</v>
+        <v>-31200.1894114429</v>
       </c>
       <c r="G52" s="37">
         <f>G50-G51</f>
-        <v>-12910.1860216124</v>
+        <v>-30587.9860216124</v>
       </c>
       <c r="H52" s="37">
         <f>H50-H51</f>
-        <v>-12297.9826317819</v>
+        <v>-29975.7826317819</v>
       </c>
       <c r="I52" s="37">
         <f>I50-I51</f>
-        <v>-5927.24590861806</v>
+        <v>-23605.045908618</v>
       </c>
       <c r="J52" s="37">
         <f>J50-J51</f>
-        <v>-2746.50918545423</v>
+        <v>-20424.3091854542</v>
       </c>
       <c r="K52" s="37">
         <f>K50-K51</f>
-        <v>434.227537709621</v>
+        <v>-17243.5724622904</v>
       </c>
       <c r="L52" s="37">
         <f>L50-L51</f>
-        <v>1072.50129791049</v>
+        <v>-19130.6987020895</v>
       </c>
       <c r="M52" s="37">
         <f>M50-M51</f>
-        <v>8886.53905811138</v>
+        <v>-11316.6609418886</v>
       </c>
       <c r="N52" s="37">
         <f>N50-N51</f>
-        <v>18569.2911040266</v>
+        <v>-4159.30889597344</v>
       </c>
       <c r="O52" s="38">
         <f>O50-O51</f>
-        <v>-62682.1427344632</v>
+        <v>-284917.342734463</v>
       </c>
       <c r="P52" s="37">
         <f>P50-P51</f>
-        <v>-51497.6620112995</v>
+        <v>-69393.8420112995</v>
       </c>
       <c r="Q52" s="37">
         <f>Q50-Q51</f>
-        <v>-29974.1094390163</v>
+        <v>-49659.9074390163</v>
       </c>
       <c r="R52" s="37">
         <f>R50-R51</f>
-        <v>-8450.55686673316</v>
+        <v>-29925.9728667332</v>
       </c>
       <c r="S52" s="37">
         <f>S50-S51</f>
-        <v>12655.0296038551</v>
+        <v>-10610.0043961449</v>
       </c>
       <c r="T52" s="37">
         <f>T50-T51</f>
-        <v>33760.6160744433</v>
+        <v>8705.96407444329</v>
       </c>
       <c r="U52" s="37">
         <f>U50-U51</f>
-        <v>73316.2025450316</v>
+        <v>46471.9325450316</v>
       </c>
       <c r="V52" s="37">
         <f>V50-V51</f>
-        <v>92668.1890156198</v>
+        <v>64034.3010156198</v>
       </c>
       <c r="W52" s="37">
         <f>W50-W51</f>
-        <v>109496.99901562</v>
+        <v>79073.4930156199</v>
       </c>
       <c r="X52" s="37">
         <f>X50-X51</f>
-        <v>107875.80901562</v>
+        <v>75662.6850156198</v>
       </c>
       <c r="Y52" s="37">
         <f>Y50-Y51</f>
-        <v>102263.80901562</v>
+        <v>68261.0670156198</v>
       </c>
       <c r="Z52" s="37">
         <f>Z50-Z51</f>
-        <v>96651.8090156198</v>
+        <v>60859.4490156198</v>
       </c>
       <c r="AA52" s="37">
         <f>AA50-AA51</f>
-        <v>85427.8090156198</v>
+        <v>46056.2130156198</v>
       </c>
       <c r="AB52" s="38">
         <f>AB50-AB51</f>
-        <v>624193.944</v>
+        <v>289535.378</v>
       </c>
       <c r="AC52" s="39">
         <f>AC50-AC51</f>
-        <v>2847750.97078692</v>
+        <v>1757662.69398429</v>
       </c>
       <c r="AD52" s="39">
         <f>AD50-AD51</f>
-        <v>5908282.10092795</v>
+        <v>4289832.03511415</v>
       </c>
       <c r="AE52" s="39">
         <f>AE50-AE51</f>
-        <v>16292066.3490587</v>
+        <v>12454318.4417608</v>
       </c>
       <c r="AF52" s="37">
         <f>AF50-AF51</f>
-        <v>25609611.2220391</v>
+        <v>18506431.2061247</v>
       </c>
     </row>
     <row r="53">
@@ -9849,123 +9864,123 @@
       </c>
       <c r="C53" s="14">
         <f>IFERROR(C52/C14,0)</f>
-        <v>-0.227724224239165</v>
+        <v>-0.489828749344581</v>
       </c>
       <c r="D53" s="14">
         <f>IFERROR(D52/D14,0)</f>
-        <v>-0.213287298508262</v>
+        <v>-0.468966576685571</v>
       </c>
       <c r="E53" s="14">
         <f>IFERROR(E52/E14,0)</f>
-        <v>-0.199541251945067</v>
+        <v>-0.44910276342467</v>
       </c>
       <c r="F53" s="14">
         <f>IFERROR(F52/F14,0)</f>
-        <v>-0.186437650417336</v>
+        <v>-0.430167319506631</v>
       </c>
       <c r="G53" s="14">
         <f>IFERROR(G52/G14,0)</f>
-        <v>-0.173932483717271</v>
+        <v>-0.412096647696772</v>
       </c>
       <c r="H53" s="14">
         <f>IFERROR(H52/H14,0)</f>
-        <v>-0.161985671741814</v>
+        <v>-0.394832829983614</v>
       </c>
       <c r="I53" s="14">
         <f>IFERROR(I52/I14,0)</f>
-        <v>-0.062572393039438</v>
+        <v>-0.249192328626095</v>
       </c>
       <c r="J53" s="14">
         <f>IFERROR(J52/J14,0)</f>
-        <v>-0.0265280570513329</v>
+        <v>-0.197274868831791</v>
       </c>
       <c r="K53" s="14">
         <f>IFERROR(K52/K14,0)</f>
-        <v>0.0038653572768708</v>
+        <v>-0.153496870898445</v>
       </c>
       <c r="L53" s="14">
         <f>IFERROR(L52/L14,0)</f>
-        <v>0.00852721512229309</v>
+        <v>-0.152103856275337</v>
       </c>
       <c r="M53" s="14">
         <f>IFERROR(M52/M14,0)</f>
-        <v>0.0603911959573784</v>
+        <v>-0.0769058329745364</v>
       </c>
       <c r="N53" s="14">
         <f>IFERROR(N52/N14,0)</f>
-        <v>0.0996300794198082</v>
+        <v>-0.0223159986730722</v>
       </c>
       <c r="O53" s="30">
         <f>IFERROR(O52/O14,0)</f>
-        <v>-0.052235118945386</v>
+        <v>-0.237431118945386</v>
       </c>
       <c r="P53" s="14">
         <f>IFERROR(P52/P14,0)</f>
-        <v>-0.180057885309998</v>
+        <v>-0.242630596382203</v>
       </c>
       <c r="Q53" s="14">
         <f>IFERROR(Q52/Q14,0)</f>
-        <v>-0.0755122094416715</v>
+        <v>-0.125105612862942</v>
       </c>
       <c r="R53" s="14">
         <f>IFERROR(R52/R14,0)</f>
-        <v>-0.0166388320315764</v>
+        <v>-0.0589231270511026</v>
       </c>
       <c r="S53" s="14">
         <f>IFERROR(S52/S14,0)</f>
-        <v>0.0205064472307754</v>
+        <v>-0.0171926500433915</v>
       </c>
       <c r="T53" s="14">
         <f>IFERROR(T52/T14,0)</f>
-        <v>0.0464787145260013</v>
+        <v>0.0119856230703084</v>
       </c>
       <c r="U53" s="14">
         <f>IFERROR(U52/U14,0)</f>
-        <v>0.0818617444228341</v>
+        <v>0.0518885775964724</v>
       </c>
       <c r="V53" s="14">
         <f>IFERROR(V52/V14,0)</f>
-        <v>0.0928779281997851</v>
+        <v>0.0641792321100576</v>
       </c>
       <c r="W53" s="14">
         <f>IFERROR(W52/W14,0)</f>
-        <v>0.100503786889243</v>
+        <v>0.0725790255630313</v>
       </c>
       <c r="X53" s="14">
         <f>IFERROR(X52/X14,0)</f>
-        <v>0.0962128081023894</v>
+        <v>0.0674824083392533</v>
       </c>
       <c r="Y53" s="14">
         <f>IFERROR(Y52/Y14,0)</f>
-        <v>0.091207549889286</v>
+        <v>0.0608810168059757</v>
       </c>
       <c r="Z53" s="14">
         <f>IFERROR(Z52/Z14,0)</f>
-        <v>0.0862022916761825</v>
+        <v>0.054279625272698</v>
       </c>
       <c r="AA53" s="14">
         <f>IFERROR(AA52/AA14,0)</f>
-        <v>0.0761917752499756</v>
+        <v>0.0410768422061427</v>
       </c>
       <c r="AB53" s="30">
         <f>IFERROR(AB52/AB14,0)</f>
-        <v>0.0624066634406581</v>
+        <v>0.0289476324829735</v>
       </c>
       <c r="AC53" s="31">
         <f>IFERROR(AC52/AC14,0)</f>
-        <v>0.0862954839632401</v>
+        <v>0.0532625058783117</v>
       </c>
       <c r="AD53" s="31">
         <f>IFERROR(AD52/AD14,0)</f>
-        <v>0.0844040300132564</v>
+        <v>0.061283314787345</v>
       </c>
       <c r="AE53" s="31">
         <f>IFERROR(AE52/AE14,0)</f>
-        <v>0.104436322750376</v>
+        <v>0.0798353746266715</v>
       </c>
       <c r="AF53" s="14">
         <f>IFERROR(AF52/AF14,0)</f>
-        <v>0.0947794887930496</v>
+        <v>0.0684910861743484</v>
       </c>
     </row>
     <row r="54"/>
@@ -9984,123 +9999,123 @@
       </c>
       <c r="C56" s="43">
         <f>C42+C38</f>
-        <v>-14476.5802476011</v>
+        <v>-32154.3802476011</v>
       </c>
       <c r="D56" s="43">
         <f>D42+D38</f>
-        <v>-13864.3768577706</v>
+        <v>-31542.1768577706</v>
       </c>
       <c r="E56" s="43">
         <f>E42+E38</f>
-        <v>-13252.1734679401</v>
+        <v>-30929.9734679401</v>
       </c>
       <c r="F56" s="43">
         <f>F42+F38</f>
-        <v>-12639.9700781096</v>
+        <v>-30317.7700781096</v>
       </c>
       <c r="G56" s="43">
         <f>G42+G38</f>
-        <v>-12027.7666882791</v>
+        <v>-29705.5666882791</v>
       </c>
       <c r="H56" s="43">
         <f>H42+H38</f>
-        <v>-11415.5632984486</v>
+        <v>-29093.3632984486</v>
       </c>
       <c r="I56" s="43">
         <f>I42+I38</f>
-        <v>-5044.82657528472</v>
+        <v>-22722.6265752847</v>
       </c>
       <c r="J56" s="43">
         <f>J42+J38</f>
-        <v>-1864.08985212089</v>
+        <v>-19541.8898521209</v>
       </c>
       <c r="K56" s="43">
         <f>K42+K38</f>
-        <v>1316.64687104295</v>
+        <v>-16361.1531289571</v>
       </c>
       <c r="L56" s="43">
         <f>L42+L38</f>
-        <v>1954.92063124383</v>
+        <v>-18248.2793687562</v>
       </c>
       <c r="M56" s="43">
         <f>M42+M38</f>
-        <v>9768.95839144471</v>
+        <v>-10434.2416085553</v>
       </c>
       <c r="N56" s="43">
         <f>N42+N38</f>
-        <v>19451.7104373599</v>
+        <v>-3276.88956264011</v>
       </c>
       <c r="O56" s="44">
         <f>O42+O38</f>
-        <v>-52093.1107344632</v>
+        <v>-274328.310734463</v>
       </c>
       <c r="P56" s="43">
         <f>P42+P38</f>
-        <v>-12101.5786779661</v>
+        <v>-29997.7586779661</v>
       </c>
       <c r="Q56" s="43">
         <f>Q42+Q38</f>
-        <v>9421.97389431706</v>
+        <v>-10263.824105683</v>
       </c>
       <c r="R56" s="43">
         <f>R42+R38</f>
-        <v>30945.5264666002</v>
+        <v>9470.11046660017</v>
       </c>
       <c r="S56" s="43">
         <f>S42+S38</f>
-        <v>52051.1129371885</v>
+        <v>28786.0789371884</v>
       </c>
       <c r="T56" s="43">
         <f>T42+T38</f>
-        <v>73156.6994077766</v>
+        <v>48102.0474077766</v>
       </c>
       <c r="U56" s="43">
         <f>U42+U38</f>
-        <v>112712.285878365</v>
+        <v>85868.0158783649</v>
       </c>
       <c r="V56" s="43">
         <f>V42+V38</f>
-        <v>132064.272348953</v>
+        <v>103430.384348953</v>
       </c>
       <c r="W56" s="43">
         <f>W42+W38</f>
-        <v>148893.082348953</v>
+        <v>118469.576348953</v>
       </c>
       <c r="X56" s="43">
         <f>X42+X38</f>
-        <v>147271.892348953</v>
+        <v>115058.768348953</v>
       </c>
       <c r="Y56" s="43">
         <f>Y42+Y38</f>
-        <v>141659.892348953</v>
+        <v>107657.150348953</v>
       </c>
       <c r="Z56" s="43">
         <f>Z42+Z38</f>
-        <v>136047.892348953</v>
+        <v>100255.532348953</v>
       </c>
       <c r="AA56" s="43">
         <f>AA42+AA38</f>
-        <v>124823.892348953</v>
+        <v>85452.2963489531</v>
       </c>
       <c r="AB56" s="44">
         <f>AB42+AB38</f>
-        <v>1096946.944</v>
+        <v>762288.378</v>
       </c>
       <c r="AC56" s="45">
         <f>AC42+AC38</f>
-        <v>3573883.16290429</v>
+        <v>2405615.69398429</v>
       </c>
       <c r="AD56" s="45">
         <f>AD42+AD38</f>
-        <v>8506468.51401019</v>
+        <v>6073383.45583219</v>
       </c>
       <c r="AE56" s="45">
         <f>AE42+AE38</f>
-        <v>22107945.5449323</v>
+        <v>17162822.7971292</v>
       </c>
       <c r="AF56" s="43">
         <f>AF42+AF38</f>
-        <v>35233151.0551124</v>
+        <v>26129782.0142112</v>
       </c>
     </row>
     <row r="57">
@@ -10111,123 +10126,123 @@
       </c>
       <c r="C57" s="14">
         <f>IFERROR(C56/C14,0)</f>
-        <v>-0.214640803207862</v>
+        <v>-0.476745328313278</v>
       </c>
       <c r="D57" s="14">
         <f>IFERROR(D56/D14,0)</f>
-        <v>-0.200524605288722</v>
+        <v>-0.456203883466032</v>
       </c>
       <c r="E57" s="14">
         <f>IFERROR(E56/E14,0)</f>
-        <v>-0.18708393810593</v>
+        <v>-0.436645449585533</v>
       </c>
       <c r="F57" s="14">
         <f>IFERROR(F56/F14,0)</f>
-        <v>-0.174271443530091</v>
+        <v>-0.418001112619387</v>
       </c>
       <c r="G57" s="14">
         <f>IFERROR(G56/G14,0)</f>
-        <v>-0.162044089075252</v>
+        <v>-0.400208253054753</v>
       </c>
       <c r="H57" s="14">
         <f>IFERROR(H56/H14,0)</f>
-        <v>-0.150362685049788</v>
+        <v>-0.383209843291588</v>
       </c>
       <c r="I57" s="14">
         <f>IFERROR(I56/I14,0)</f>
-        <v>-0.0532569217055001</v>
+        <v>-0.239876857292157</v>
       </c>
       <c r="J57" s="14">
         <f>IFERROR(J56/J14,0)</f>
-        <v>-0.0180049213772047</v>
+        <v>-0.188751733157663</v>
       </c>
       <c r="K57" s="14">
         <f>IFERROR(K56/K14,0)</f>
-        <v>0.011720377272476</v>
+        <v>-0.145641850902839</v>
       </c>
       <c r="L57" s="14">
         <f>IFERROR(L56/L14,0)</f>
-        <v>0.0155431315580714</v>
+        <v>-0.145087939839559</v>
       </c>
       <c r="M57" s="14">
         <f>IFERROR(M56/M14,0)</f>
-        <v>0.0663879466077084</v>
+        <v>-0.0709090823242063</v>
       </c>
       <c r="N57" s="14">
         <f>IFERROR(N56/N14,0)</f>
-        <v>0.104364536312592</v>
+        <v>-0.0175815417802881</v>
       </c>
       <c r="O57" s="30">
         <f>IFERROR(O56/O14,0)</f>
-        <v>-0.0434109256120527</v>
+        <v>-0.228606925612053</v>
       </c>
       <c r="P57" s="14">
         <f>IFERROR(P56/P14,0)</f>
-        <v>-0.0423123027447157</v>
+        <v>-0.10488501381692</v>
       </c>
       <c r="Q57" s="14">
         <f>IFERROR(Q56/Q14,0)</f>
-        <v>0.0237362870616442</v>
+        <v>-0.025857116359626</v>
       </c>
       <c r="R57" s="14">
         <f>IFERROR(R56/R14,0)</f>
-        <v>0.0609305901523993</v>
+        <v>0.0186462951328731</v>
       </c>
       <c r="S57" s="14">
         <f>IFERROR(S56/S14,0)</f>
-        <v>0.0843445992749338</v>
+        <v>0.046645502000767</v>
       </c>
       <c r="T57" s="14">
         <f>IFERROR(T56/T14,0)</f>
-        <v>0.100715856012252</v>
+        <v>0.0662227645565587</v>
       </c>
       <c r="U57" s="14">
         <f>IFERROR(U56/U14,0)</f>
-        <v>0.125849730613379</v>
+        <v>0.0958765637870169</v>
       </c>
       <c r="V57" s="14">
         <f>IFERROR(V56/V14,0)</f>
-        <v>0.13236317807954</v>
+        <v>0.103664481989812</v>
       </c>
       <c r="W57" s="14">
         <f>IFERROR(W56/W14,0)</f>
-        <v>0.136664189450041</v>
+        <v>0.10873942812383</v>
       </c>
       <c r="X57" s="14">
         <f>IFERROR(X56/X14,0)</f>
-        <v>0.131349581029737</v>
+        <v>0.102619181266601</v>
       </c>
       <c r="Y57" s="14">
         <f>IFERROR(Y56/Y14,0)</f>
-        <v>0.126344322816633</v>
+        <v>0.0960177897333232</v>
       </c>
       <c r="Z57" s="14">
         <f>IFERROR(Z56/Z14,0)</f>
-        <v>0.12133906460353</v>
+        <v>0.0894163982000455</v>
       </c>
       <c r="AA57" s="14">
         <f>IFERROR(AA56/AA14,0)</f>
-        <v>0.111328548177323</v>
+        <v>0.0762136151334902</v>
       </c>
       <c r="AB57" s="30">
         <f>IFERROR(AB56/AB14,0)</f>
-        <v>0.109672321246466</v>
+        <v>0.0762132902887811</v>
       </c>
       <c r="AC57" s="31">
         <f>IFERROR(AC56/AC14,0)</f>
-        <v>0.108299489784978</v>
+        <v>0.0728974452722511</v>
       </c>
       <c r="AD57" s="31">
         <f>IFERROR(AD56/AD14,0)</f>
-        <v>0.121520978771574</v>
+        <v>0.0867626207976027</v>
       </c>
       <c r="AE57" s="31">
         <f>IFERROR(AE56/AE14,0)</f>
-        <v>0.141717599647002</v>
+        <v>0.110018094853392</v>
       </c>
       <c r="AF57" s="14">
         <f>IFERROR(AF56/AF14,0)</f>
-        <v>0.130395577528254</v>
+        <v>0.0967046067239581</v>
       </c>
     </row>
     <row r="58">
@@ -10925,23 +10940,23 @@
       </c>
       <c r="D12" s="18">
         <f>'2_손익계산서'!O41</f>
-        <v>639696</v>
+        <v>861931.2</v>
       </c>
       <c r="E12" s="18">
         <f>'2_손익계산서'!AB41</f>
-        <v>3309703</v>
+        <v>3644361.566</v>
       </c>
       <c r="F12" s="18">
         <f>'2_손익계산서'!AC41</f>
-        <v>9986153</v>
+        <v>11154420.46892</v>
       </c>
       <c r="G12" s="18">
         <f>'2_손익계산서'!AD41</f>
-        <v>19994473</v>
+        <v>22427558.058178</v>
       </c>
       <c r="H12" s="18">
         <f>'2_손익계산서'!AE41</f>
-        <v>42300313</v>
+        <v>47245435.7478032</v>
       </c>
     </row>
     <row r="13">
@@ -10960,27 +10975,27 @@
       </c>
       <c r="D13" s="37">
         <f>D10-D12</f>
-        <v>-70093.1107344632</v>
+        <v>-292328.310734463</v>
       </c>
       <c r="E13" s="37">
         <f>E10-E12</f>
-        <v>660993.944</v>
+        <v>326335.378</v>
       </c>
       <c r="F13" s="37">
         <f>F10-F12</f>
-        <v>3087930.16290429</v>
+        <v>1919662.69398429</v>
       </c>
       <c r="G13" s="37">
         <f>G10-G12</f>
-        <v>7930515.51401019</v>
+        <v>5497430.45583219</v>
       </c>
       <c r="H13" s="37">
         <f>H10-H12</f>
-        <v>21411992.5449323</v>
+        <v>16466869.7971292</v>
       </c>
       <c r="I13" s="14">
         <f>IFERROR((H13/C13)^(1/5)-1,"n/a")</f>
-        <v>2.80643221565146</v>
+        <v>2.61167692074088</v>
       </c>
     </row>
     <row r="14">
@@ -10999,23 +11014,23 @@
       </c>
       <c r="D14" s="14">
         <f>IFERROR(D13/D7,0)</f>
-        <v>-0.0584109256120527</v>
+        <v>-0.243606925612053</v>
       </c>
       <c r="E14" s="14">
         <f>IFERROR(E13/E7,0)</f>
-        <v>0.0660859128737737</v>
+        <v>0.0326268819160891</v>
       </c>
       <c r="F14" s="14">
         <f>IFERROR(F13/F7,0)</f>
-        <v>0.0935736413001299</v>
+        <v>0.0581715967874026</v>
       </c>
       <c r="G14" s="14">
         <f>IFERROR(G13/G7,0)</f>
-        <v>0.113293078771574</v>
+        <v>0.0785347207976027</v>
       </c>
       <c r="H14" s="14">
         <f>IFERROR(H13/H7,0)</f>
-        <v>0.137256362467515</v>
+        <v>0.105556857673905</v>
       </c>
     </row>
     <row r="15">
@@ -11166,23 +11181,23 @@
       </c>
       <c r="D19" s="25">
         <f>D13+D15-D17</f>
-        <v>-62682.1427344632</v>
+        <v>-284917.342734463</v>
       </c>
       <c r="E19" s="25">
         <f>E13+E15-E17</f>
-        <v>624193.944</v>
+        <v>289535.378</v>
       </c>
       <c r="F19" s="25">
         <f>F13+F15-F17</f>
-        <v>2925930.16290429</v>
+        <v>1757662.69398429</v>
       </c>
       <c r="G19" s="25">
         <f>G13+G15-G17</f>
-        <v>7546515.51401019</v>
+        <v>5113430.45583219</v>
       </c>
       <c r="H19" s="25">
         <f>H13+H15-H17</f>
-        <v>20883992.5449323</v>
+        <v>15938869.7971292</v>
       </c>
     </row>
     <row r="20">
@@ -11207,15 +11222,15 @@
       </c>
       <c r="F20" s="18">
         <f>'2_손익계산서'!AC51</f>
-        <v>78179.1921173607</v>
+        <v>0</v>
       </c>
       <c r="G20" s="18">
         <f>'2_손익계산서'!AD51</f>
-        <v>1638233.41308224</v>
+        <v>823598.420718043</v>
       </c>
       <c r="H20" s="18">
         <f>'2_손익계산서'!AE51</f>
-        <v>4591926.19587363</v>
+        <v>3484551.35536842</v>
       </c>
     </row>
     <row r="21">
@@ -11234,27 +11249,27 @@
       </c>
       <c r="D21" s="37">
         <f>D19-D20</f>
-        <v>-62682.1427344632</v>
+        <v>-284917.342734463</v>
       </c>
       <c r="E21" s="37">
         <f>E19-E20</f>
-        <v>624193.944</v>
+        <v>289535.378</v>
       </c>
       <c r="F21" s="37">
         <f>F19-F20</f>
-        <v>2847750.97078692</v>
+        <v>1757662.69398429</v>
       </c>
       <c r="G21" s="37">
         <f>G19-G20</f>
-        <v>5908282.10092795</v>
+        <v>4289832.03511415</v>
       </c>
       <c r="H21" s="37">
         <f>H19-H20</f>
-        <v>16292066.3490587</v>
+        <v>12454318.4417608</v>
       </c>
       <c r="I21" s="14">
         <f>IFERROR((H21/C21)^(1/5)-1,"n/a")</f>
-        <v>4.00892388037824</v>
+        <v>3.74693397338258</v>
       </c>
     </row>
     <row r="22">
@@ -11273,23 +11288,23 @@
       </c>
       <c r="D22" s="14">
         <f>IFERROR(D21/D7,0)</f>
-        <v>-0.052235118945386</v>
+        <v>-0.237431118945386</v>
       </c>
       <c r="E22" s="14">
         <f>IFERROR(E21/E7,0)</f>
-        <v>0.0624066634406581</v>
+        <v>0.0289476324829735</v>
       </c>
       <c r="F22" s="14">
         <f>IFERROR(F21/F7,0)</f>
-        <v>0.0862954839632401</v>
+        <v>0.0532625058783117</v>
       </c>
       <c r="G22" s="14">
         <f>IFERROR(G21/G7,0)</f>
-        <v>0.0844040300132564</v>
+        <v>0.061283314787345</v>
       </c>
       <c r="H22" s="14">
         <f>IFERROR(H21/H7,0)</f>
-        <v>0.104436322750376</v>
+        <v>0.0798353746266715</v>
       </c>
     </row>
     <row r="23">
@@ -11300,23 +11315,23 @@
       </c>
       <c r="D23" s="18">
         <f>'2_손익계산서'!O56</f>
-        <v>-52093.1107344632</v>
+        <v>-274328.310734463</v>
       </c>
       <c r="E23" s="18">
         <f>'2_손익계산서'!AB56</f>
-        <v>1096946.944</v>
+        <v>762288.378</v>
       </c>
       <c r="F23" s="18">
         <f>'2_손익계산서'!AC56</f>
-        <v>3573883.16290429</v>
+        <v>2405615.69398429</v>
       </c>
       <c r="G23" s="18">
         <f>'2_손익계산서'!AD56</f>
-        <v>8506468.51401019</v>
+        <v>6073383.45583219</v>
       </c>
       <c r="H23" s="18">
         <f>'2_손익계산서'!AE56</f>
-        <v>22107945.5449323</v>
+        <v>17162822.7971292</v>
       </c>
     </row>
     <row r="24">
@@ -31694,119 +31709,119 @@
       </c>
       <c r="C16" s="18">
         <f>'8_가정'!$C$91</f>
-        <v>3600</v>
+        <v>5670</v>
       </c>
       <c r="D16" s="18">
         <f>'8_가정'!$C$91</f>
-        <v>3600</v>
+        <v>5670</v>
       </c>
       <c r="E16" s="18">
         <f>'8_가정'!$C$91</f>
-        <v>3600</v>
+        <v>5670</v>
       </c>
       <c r="F16" s="18">
         <f>'8_가정'!$C$91</f>
-        <v>3600</v>
+        <v>5670</v>
       </c>
       <c r="G16" s="18">
         <f>'8_가정'!$C$91</f>
-        <v>3600</v>
+        <v>5670</v>
       </c>
       <c r="H16" s="18">
         <f>'8_가정'!$C$91</f>
-        <v>3600</v>
+        <v>5670</v>
       </c>
       <c r="I16" s="18">
         <f>'8_가정'!$C$91</f>
-        <v>3600</v>
+        <v>5670</v>
       </c>
       <c r="J16" s="18">
         <f>'8_가정'!$C$91</f>
-        <v>3600</v>
+        <v>5670</v>
       </c>
       <c r="K16" s="18">
         <f>'8_가정'!$C$91</f>
-        <v>3600</v>
+        <v>5670</v>
       </c>
       <c r="L16" s="18">
         <f>'8_가정'!$C$91</f>
-        <v>3600</v>
+        <v>5670</v>
       </c>
       <c r="M16" s="18">
         <f>'8_가정'!$C$91</f>
-        <v>3600</v>
+        <v>5670</v>
       </c>
       <c r="N16" s="18">
         <f>'8_가정'!$C$91</f>
-        <v>3600</v>
+        <v>5670</v>
       </c>
       <c r="O16" s="48">
         <f>'8_가정'!$C$91</f>
-        <v>3600</v>
+        <v>5670</v>
       </c>
       <c r="P16" s="18">
         <f>'8_가정'!$D$91</f>
-        <v>4600</v>
+        <v>6066.9</v>
       </c>
       <c r="Q16" s="18">
         <f>'8_가정'!$D$91</f>
-        <v>4600</v>
+        <v>6066.9</v>
       </c>
       <c r="R16" s="18">
         <f>'8_가정'!$D$91</f>
-        <v>4600</v>
+        <v>6066.9</v>
       </c>
       <c r="S16" s="18">
         <f>'8_가정'!$D$91</f>
-        <v>4600</v>
+        <v>6066.9</v>
       </c>
       <c r="T16" s="18">
         <f>'8_가정'!$D$91</f>
-        <v>4600</v>
+        <v>6066.9</v>
       </c>
       <c r="U16" s="18">
         <f>'8_가정'!$D$91</f>
-        <v>4600</v>
+        <v>6066.9</v>
       </c>
       <c r="V16" s="18">
         <f>'8_가정'!$D$91</f>
-        <v>4600</v>
+        <v>6066.9</v>
       </c>
       <c r="W16" s="18">
         <f>'8_가정'!$D$91</f>
-        <v>4600</v>
+        <v>6066.9</v>
       </c>
       <c r="X16" s="18">
         <f>'8_가정'!$D$91</f>
-        <v>4600</v>
+        <v>6066.9</v>
       </c>
       <c r="Y16" s="18">
         <f>'8_가정'!$D$91</f>
-        <v>4600</v>
+        <v>6066.9</v>
       </c>
       <c r="Z16" s="18">
         <f>'8_가정'!$D$91</f>
-        <v>4600</v>
+        <v>6066.9</v>
       </c>
       <c r="AA16" s="18">
         <f>'8_가정'!$D$91</f>
-        <v>4600</v>
+        <v>6066.9</v>
       </c>
       <c r="AB16" s="48">
         <f>'8_가정'!$D$91</f>
-        <v>4600</v>
+        <v>6066.9</v>
       </c>
       <c r="AC16" s="24">
         <f>'8_가정'!$E$91</f>
-        <v>5000</v>
+        <v>6491.583</v>
       </c>
       <c r="AD16" s="24">
         <f>'8_가정'!$F$91</f>
-        <v>5400</v>
+        <v>6945.99381</v>
       </c>
       <c r="AE16" s="24">
         <f>'8_가정'!$G$91</f>
-        <v>5700</v>
+        <v>7432.2133767</v>
       </c>
     </row>
     <row r="18">
@@ -31829,123 +31844,123 @@
       </c>
       <c r="C19" s="43">
         <f>C15*C16</f>
-        <v>25200</v>
+        <v>39690</v>
       </c>
       <c r="D19" s="43">
         <f>D15*D16</f>
-        <v>25200</v>
+        <v>39690</v>
       </c>
       <c r="E19" s="43">
         <f>E15*E16</f>
-        <v>25200</v>
+        <v>39690</v>
       </c>
       <c r="F19" s="43">
         <f>F15*F16</f>
-        <v>25200</v>
+        <v>39690</v>
       </c>
       <c r="G19" s="43">
         <f>G15*G16</f>
-        <v>25200</v>
+        <v>39690</v>
       </c>
       <c r="H19" s="43">
         <f>H15*H16</f>
-        <v>25200</v>
+        <v>39690</v>
       </c>
       <c r="I19" s="43">
         <f>I15*I16</f>
-        <v>25200</v>
+        <v>39690</v>
       </c>
       <c r="J19" s="43">
         <f>J15*J16</f>
-        <v>25200</v>
+        <v>39690</v>
       </c>
       <c r="K19" s="43">
         <f>K15*K16</f>
-        <v>25200</v>
+        <v>39690</v>
       </c>
       <c r="L19" s="43">
         <f>L15*L16</f>
-        <v>28800</v>
+        <v>45360</v>
       </c>
       <c r="M19" s="43">
         <f>M15*M16</f>
-        <v>28800</v>
+        <v>45360</v>
       </c>
       <c r="N19" s="43">
         <f>N15*N16</f>
-        <v>32400</v>
+        <v>51030</v>
       </c>
       <c r="O19" s="23">
         <f>SUM(C19:N19)</f>
-        <v>316800</v>
+        <v>498960</v>
       </c>
       <c r="P19" s="43">
         <f>P15*P16</f>
-        <v>46000</v>
+        <v>60669</v>
       </c>
       <c r="Q19" s="43">
         <f>Q15*Q16</f>
-        <v>50600</v>
+        <v>66735.9</v>
       </c>
       <c r="R19" s="43">
         <f>R15*R16</f>
-        <v>55200</v>
+        <v>72802.8</v>
       </c>
       <c r="S19" s="43">
         <f>S15*S16</f>
-        <v>59800</v>
+        <v>78869.7</v>
       </c>
       <c r="T19" s="43">
         <f>T15*T16</f>
-        <v>64400</v>
+        <v>84936.6</v>
       </c>
       <c r="U19" s="43">
         <f>U15*U16</f>
-        <v>69000</v>
+        <v>91003.5</v>
       </c>
       <c r="V19" s="43">
         <f>V15*V16</f>
-        <v>73600</v>
+        <v>97070.4</v>
       </c>
       <c r="W19" s="43">
         <f>W15*W16</f>
-        <v>78200</v>
+        <v>103137.3</v>
       </c>
       <c r="X19" s="43">
         <f>X15*X16</f>
-        <v>82800</v>
+        <v>109204.2</v>
       </c>
       <c r="Y19" s="43">
         <f>Y15*Y16</f>
-        <v>87400</v>
+        <v>115271.1</v>
       </c>
       <c r="Z19" s="43">
         <f>Z15*Z16</f>
-        <v>92000</v>
+        <v>121338</v>
       </c>
       <c r="AA19" s="43">
         <f>AA15*AA16</f>
-        <v>101200</v>
+        <v>133471.8</v>
       </c>
       <c r="AB19" s="23">
         <f>SUM(P19:AA19)</f>
-        <v>860200</v>
+        <v>1134510.3</v>
       </c>
       <c r="AC19" s="45">
         <f>AC15*AC16*12</f>
-        <v>3210000</v>
+        <v>4167596.286</v>
       </c>
       <c r="AD19" s="45">
         <f>AD15*AD16*12</f>
-        <v>6966000</v>
+        <v>8960332.0149</v>
       </c>
       <c r="AE19" s="45">
         <f>AE15*AE16*12</f>
-        <v>13338000</v>
+        <v>17391379.301478</v>
       </c>
       <c r="AF19" s="25">
         <f>O19+AB19+AC19+AD19+AE19</f>
-        <v>24691000</v>
+        <v>32152777.902378</v>
       </c>
     </row>
     <row r="20">
@@ -31960,124 +31975,124 @@
         </is>
       </c>
       <c r="C20" s="18">
-        <f>C19*'8_가정'!$C$92</f>
-        <v>5544</v>
+        <f>C19*'8_가정'!$C$93</f>
+        <v>8731.8</v>
       </c>
       <c r="D20" s="18">
-        <f>D19*'8_가정'!$C$92</f>
-        <v>5544</v>
+        <f>D19*'8_가정'!$C$93</f>
+        <v>8731.8</v>
       </c>
       <c r="E20" s="18">
-        <f>E19*'8_가정'!$C$92</f>
-        <v>5544</v>
+        <f>E19*'8_가정'!$C$93</f>
+        <v>8731.8</v>
       </c>
       <c r="F20" s="18">
-        <f>F19*'8_가정'!$C$92</f>
-        <v>5544</v>
+        <f>F19*'8_가정'!$C$93</f>
+        <v>8731.8</v>
       </c>
       <c r="G20" s="18">
-        <f>G19*'8_가정'!$C$92</f>
-        <v>5544</v>
+        <f>G19*'8_가정'!$C$93</f>
+        <v>8731.8</v>
       </c>
       <c r="H20" s="18">
-        <f>H19*'8_가정'!$C$92</f>
-        <v>5544</v>
+        <f>H19*'8_가정'!$C$93</f>
+        <v>8731.8</v>
       </c>
       <c r="I20" s="18">
-        <f>I19*'8_가정'!$C$92</f>
-        <v>5544</v>
+        <f>I19*'8_가정'!$C$93</f>
+        <v>8731.8</v>
       </c>
       <c r="J20" s="18">
-        <f>J19*'8_가정'!$C$92</f>
-        <v>5544</v>
+        <f>J19*'8_가정'!$C$93</f>
+        <v>8731.8</v>
       </c>
       <c r="K20" s="18">
-        <f>K19*'8_가정'!$C$92</f>
-        <v>5544</v>
+        <f>K19*'8_가정'!$C$93</f>
+        <v>8731.8</v>
       </c>
       <c r="L20" s="18">
-        <f>L19*'8_가정'!$C$92</f>
-        <v>6336</v>
+        <f>L19*'8_가정'!$C$93</f>
+        <v>9979.2</v>
       </c>
       <c r="M20" s="18">
-        <f>M19*'8_가정'!$C$92</f>
-        <v>6336</v>
+        <f>M19*'8_가정'!$C$93</f>
+        <v>9979.2</v>
       </c>
       <c r="N20" s="18">
-        <f>N19*'8_가정'!$C$92</f>
-        <v>7128</v>
+        <f>N19*'8_가정'!$C$93</f>
+        <v>11226.6</v>
       </c>
       <c r="O20" s="23">
         <f>SUM(C20:N20)</f>
-        <v>69696</v>
+        <v>109771.2</v>
       </c>
       <c r="P20" s="18">
-        <f>P19*'8_가정'!$C$92</f>
-        <v>10120</v>
+        <f>P19*'8_가정'!$C$93</f>
+        <v>13347.18</v>
       </c>
       <c r="Q20" s="18">
-        <f>Q19*'8_가정'!$C$92</f>
-        <v>11132</v>
+        <f>Q19*'8_가정'!$C$93</f>
+        <v>14681.898</v>
       </c>
       <c r="R20" s="18">
-        <f>R19*'8_가정'!$C$92</f>
-        <v>12144</v>
+        <f>R19*'8_가정'!$C$93</f>
+        <v>16016.616</v>
       </c>
       <c r="S20" s="18">
-        <f>S19*'8_가정'!$C$92</f>
-        <v>13156</v>
+        <f>S19*'8_가정'!$C$93</f>
+        <v>17351.334</v>
       </c>
       <c r="T20" s="18">
-        <f>T19*'8_가정'!$C$92</f>
-        <v>14168</v>
+        <f>T19*'8_가정'!$C$93</f>
+        <v>18686.052</v>
       </c>
       <c r="U20" s="18">
-        <f>U19*'8_가정'!$C$92</f>
-        <v>15180</v>
+        <f>U19*'8_가정'!$C$93</f>
+        <v>20020.77</v>
       </c>
       <c r="V20" s="18">
-        <f>V19*'8_가정'!$C$92</f>
-        <v>16192</v>
+        <f>V19*'8_가정'!$C$93</f>
+        <v>21355.488</v>
       </c>
       <c r="W20" s="18">
-        <f>W19*'8_가정'!$C$92</f>
-        <v>17204</v>
+        <f>W19*'8_가정'!$C$93</f>
+        <v>22690.206</v>
       </c>
       <c r="X20" s="18">
-        <f>X19*'8_가정'!$C$92</f>
-        <v>18216</v>
+        <f>X19*'8_가정'!$C$93</f>
+        <v>24024.924</v>
       </c>
       <c r="Y20" s="18">
-        <f>Y19*'8_가정'!$C$92</f>
-        <v>19228</v>
+        <f>Y19*'8_가정'!$C$93</f>
+        <v>25359.642</v>
       </c>
       <c r="Z20" s="18">
-        <f>Z19*'8_가정'!$C$92</f>
-        <v>20240</v>
+        <f>Z19*'8_가정'!$C$93</f>
+        <v>26694.36</v>
       </c>
       <c r="AA20" s="18">
-        <f>AA19*'8_가정'!$C$92</f>
-        <v>22264</v>
+        <f>AA19*'8_가정'!$C$93</f>
+        <v>29363.796</v>
       </c>
       <c r="AB20" s="23">
         <f>SUM(P20:AA20)</f>
-        <v>189244</v>
+        <v>249592.266</v>
       </c>
       <c r="AC20" s="24">
-        <f>AC19*'8_가정'!$C$92</f>
-        <v>706200</v>
+        <f>AC19*'8_가정'!$C$93</f>
+        <v>916871.18292</v>
       </c>
       <c r="AD20" s="24">
-        <f>AD19*'8_가정'!$C$92</f>
-        <v>1532520</v>
+        <f>AD19*'8_가정'!$C$93</f>
+        <v>1971273.043278</v>
       </c>
       <c r="AE20" s="24">
-        <f>AE19*'8_가정'!$C$92</f>
-        <v>2934360</v>
+        <f>AE19*'8_가정'!$C$93</f>
+        <v>3826103.44632516</v>
       </c>
       <c r="AF20" s="25">
         <f>O20+AB20+AC20+AD20+AE20</f>
-        <v>5432020</v>
+        <v>7073611.13852316</v>
       </c>
     </row>
     <row r="21">
@@ -32092,51 +32107,51 @@
         </is>
       </c>
       <c r="C21" s="18">
-        <f>C8*'8_가정'!$C$93</f>
+        <f>C8*'8_가정'!$C$94</f>
         <v>1011.68417406511</v>
       </c>
       <c r="D21" s="18">
-        <f>D8*'8_가정'!$C$93</f>
+        <f>D8*'8_가정'!$C$94</f>
         <v>1037.10790287867</v>
       </c>
       <c r="E21" s="18">
-        <f>E8*'8_가정'!$C$93</f>
+        <f>E8*'8_가정'!$C$94</f>
         <v>1062.53163169222</v>
       </c>
       <c r="F21" s="18">
-        <f>F8*'8_가정'!$C$93</f>
+        <f>F8*'8_가정'!$C$94</f>
         <v>1087.95536050578</v>
       </c>
       <c r="G21" s="18">
-        <f>G8*'8_가정'!$C$93</f>
+        <f>G8*'8_가정'!$C$94</f>
         <v>1113.37908931934</v>
       </c>
       <c r="H21" s="18">
-        <f>H8*'8_가정'!$C$93</f>
+        <f>H8*'8_가정'!$C$94</f>
         <v>1138.8028181329</v>
       </c>
       <c r="I21" s="18">
-        <f>I8*'8_가정'!$C$93</f>
+        <f>I8*'8_가정'!$C$94</f>
         <v>1420.89321361313</v>
       </c>
       <c r="J21" s="18">
-        <f>J8*'8_가정'!$C$93</f>
+        <f>J8*'8_가정'!$C$94</f>
         <v>1552.98360909335</v>
       </c>
       <c r="K21" s="18">
-        <f>K8*'8_가정'!$C$93</f>
+        <f>K8*'8_가정'!$C$94</f>
         <v>1685.07400457358</v>
       </c>
       <c r="L21" s="18">
-        <f>L8*'8_가정'!$C$93</f>
+        <f>L8*'8_가정'!$C$94</f>
         <v>1886.60884449825</v>
       </c>
       <c r="M21" s="18">
-        <f>M8*'8_가정'!$C$93</f>
+        <f>M8*'8_가정'!$C$94</f>
         <v>2207.24368442292</v>
       </c>
       <c r="N21" s="18">
-        <f>N8*'8_가정'!$C$93</f>
+        <f>N8*'8_가정'!$C$94</f>
         <v>2795.73566720473</v>
       </c>
       <c r="O21" s="23">
@@ -32144,51 +32159,51 @@
         <v>18000</v>
       </c>
       <c r="P21" s="18">
-        <f>P8*'8_가정'!$D$93</f>
+        <f>P8*'8_가정'!$D$94</f>
         <v>7150.15367455834</v>
       </c>
       <c r="Q21" s="18">
-        <f>Q8*'8_가정'!$D$93</f>
+        <f>Q8*'8_가정'!$D$94</f>
         <v>9923.59701187443</v>
       </c>
       <c r="R21" s="18">
-        <f>R8*'8_가정'!$D$93</f>
+        <f>R8*'8_가정'!$D$94</f>
         <v>12697.0403491905</v>
       </c>
       <c r="S21" s="18">
-        <f>S8*'8_가정'!$D$93</f>
+        <f>S8*'8_가정'!$D$94</f>
         <v>15428.1108051507</v>
       </c>
       <c r="T21" s="18">
-        <f>T8*'8_가정'!$D$93</f>
+        <f>T8*'8_가정'!$D$94</f>
         <v>18159.1812611108</v>
       </c>
       <c r="U21" s="18">
-        <f>U8*'8_가정'!$D$93</f>
+        <f>U8*'8_가정'!$D$94</f>
         <v>22390.251717071</v>
       </c>
       <c r="V21" s="18">
-        <f>V8*'8_가정'!$D$93</f>
+        <f>V8*'8_가정'!$D$94</f>
         <v>24943.5443952534</v>
       </c>
       <c r="W21" s="18">
-        <f>W8*'8_가정'!$D$93</f>
+        <f>W8*'8_가정'!$D$94</f>
         <v>27237.0331518672</v>
       </c>
       <c r="X21" s="18">
-        <f>X8*'8_가정'!$D$93</f>
+        <f>X8*'8_가정'!$D$94</f>
         <v>28030.5219084809</v>
       </c>
       <c r="Y21" s="18">
-        <f>Y8*'8_가정'!$D$93</f>
+        <f>Y8*'8_가정'!$D$94</f>
         <v>28030.5219084809</v>
       </c>
       <c r="Z21" s="18">
-        <f>Z8*'8_가정'!$D$93</f>
+        <f>Z8*'8_가정'!$D$94</f>
         <v>28030.5219084809</v>
       </c>
       <c r="AA21" s="18">
-        <f>AA8*'8_가정'!$D$93</f>
+        <f>AA8*'8_가정'!$D$94</f>
         <v>28030.5219084809</v>
       </c>
       <c r="AB21" s="23">
@@ -32196,15 +32211,15 @@
         <v>250051</v>
       </c>
       <c r="AC21" s="24">
-        <f>AC8*'8_가정'!$E$93</f>
+        <f>AC8*'8_가정'!$E$94</f>
         <v>924000</v>
       </c>
       <c r="AD21" s="24">
-        <f>AD8*'8_가정'!$F$93</f>
+        <f>AD8*'8_가정'!$F$94</f>
         <v>1820000</v>
       </c>
       <c r="AE21" s="24">
-        <f>AE8*'8_가정'!$G$93</f>
+        <f>AE8*'8_가정'!$G$94</f>
         <v>4680000</v>
       </c>
       <c r="AF21" s="25">
@@ -32224,51 +32239,51 @@
         </is>
       </c>
       <c r="C22" s="18">
-        <f>C8*'8_가정'!$C$94</f>
+        <f>C8*'8_가정'!$C$95</f>
         <v>809.347339252085</v>
       </c>
       <c r="D22" s="18">
-        <f>D8*'8_가정'!$C$94</f>
+        <f>D8*'8_가정'!$C$95</f>
         <v>829.686322302932</v>
       </c>
       <c r="E22" s="18">
-        <f>E8*'8_가정'!$C$94</f>
+        <f>E8*'8_가정'!$C$95</f>
         <v>850.02530535378</v>
       </c>
       <c r="F22" s="18">
-        <f>F8*'8_가정'!$C$94</f>
+        <f>F8*'8_가정'!$C$95</f>
         <v>870.364288404627</v>
       </c>
       <c r="G22" s="18">
-        <f>G8*'8_가정'!$C$94</f>
+        <f>G8*'8_가정'!$C$95</f>
         <v>890.703271455475</v>
       </c>
       <c r="H22" s="18">
-        <f>H8*'8_가정'!$C$94</f>
+        <f>H8*'8_가정'!$C$95</f>
         <v>911.042254506322</v>
       </c>
       <c r="I22" s="18">
-        <f>I8*'8_가정'!$C$94</f>
+        <f>I8*'8_가정'!$C$95</f>
         <v>1136.7145708905</v>
       </c>
       <c r="J22" s="18">
-        <f>J8*'8_가정'!$C$94</f>
+        <f>J8*'8_가정'!$C$95</f>
         <v>1242.38688727468</v>
       </c>
       <c r="K22" s="18">
-        <f>K8*'8_가정'!$C$94</f>
+        <f>K8*'8_가정'!$C$95</f>
         <v>1348.05920365886</v>
       </c>
       <c r="L22" s="18">
-        <f>L8*'8_가정'!$C$94</f>
+        <f>L8*'8_가정'!$C$95</f>
         <v>1509.2870755986</v>
       </c>
       <c r="M22" s="18">
-        <f>M8*'8_가정'!$C$94</f>
+        <f>M8*'8_가정'!$C$95</f>
         <v>1765.79494753834</v>
       </c>
       <c r="N22" s="18">
-        <f>N8*'8_가정'!$C$94</f>
+        <f>N8*'8_가정'!$C$95</f>
         <v>2236.58853376379</v>
       </c>
       <c r="O22" s="23">
@@ -32276,51 +32291,51 @@
         <v>14400</v>
       </c>
       <c r="P22" s="18">
-        <f>P8*'8_가정'!$D$94</f>
+        <f>P8*'8_가정'!$D$95</f>
         <v>5720.12293964667</v>
       </c>
       <c r="Q22" s="18">
-        <f>Q8*'8_가정'!$D$94</f>
+        <f>Q8*'8_가정'!$D$95</f>
         <v>7938.87760949954</v>
       </c>
       <c r="R22" s="18">
-        <f>R8*'8_가정'!$D$94</f>
+        <f>R8*'8_가정'!$D$95</f>
         <v>10157.6322793524</v>
       </c>
       <c r="S22" s="18">
-        <f>S8*'8_가정'!$D$94</f>
+        <f>S8*'8_가정'!$D$95</f>
         <v>12342.4886441205</v>
       </c>
       <c r="T22" s="18">
-        <f>T8*'8_가정'!$D$94</f>
+        <f>T8*'8_가정'!$D$95</f>
         <v>14527.3450088887</v>
       </c>
       <c r="U22" s="18">
-        <f>U8*'8_가정'!$D$94</f>
+        <f>U8*'8_가정'!$D$95</f>
         <v>17912.2013736568</v>
       </c>
       <c r="V22" s="18">
-        <f>V8*'8_가정'!$D$94</f>
+        <f>V8*'8_가정'!$D$95</f>
         <v>19954.8355162027</v>
       </c>
       <c r="W22" s="18">
-        <f>W8*'8_가정'!$D$94</f>
+        <f>W8*'8_가정'!$D$95</f>
         <v>21789.6265214937</v>
       </c>
       <c r="X22" s="18">
-        <f>X8*'8_가정'!$D$94</f>
+        <f>X8*'8_가정'!$D$95</f>
         <v>22424.4175267847</v>
       </c>
       <c r="Y22" s="18">
-        <f>Y8*'8_가정'!$D$94</f>
+        <f>Y8*'8_가정'!$D$95</f>
         <v>22424.4175267847</v>
       </c>
       <c r="Z22" s="18">
-        <f>Z8*'8_가정'!$D$94</f>
+        <f>Z8*'8_가정'!$D$95</f>
         <v>22424.4175267847</v>
       </c>
       <c r="AA22" s="18">
-        <f>AA8*'8_가정'!$D$94</f>
+        <f>AA8*'8_가정'!$D$95</f>
         <v>22424.4175267847</v>
       </c>
       <c r="AB22" s="23">
@@ -32328,15 +32343,15 @@
         <v>200040.8</v>
       </c>
       <c r="AC22" s="24">
-        <f>AC8*'8_가정'!$E$94</f>
+        <f>AC8*'8_가정'!$E$95</f>
         <v>726000</v>
       </c>
       <c r="AD22" s="24">
-        <f>AD8*'8_가정'!$F$94</f>
+        <f>AD8*'8_가정'!$F$95</f>
         <v>1540000</v>
       </c>
       <c r="AE22" s="24">
-        <f>AE8*'8_가정'!$G$94</f>
+        <f>AE8*'8_가정'!$G$95</f>
         <v>3432000</v>
       </c>
       <c r="AF22" s="25">
@@ -32356,51 +32371,51 @@
         </is>
       </c>
       <c r="C23" s="18">
-        <f>C8*'8_가정'!$C$95</f>
+        <f>C8*'8_가정'!$C$96</f>
         <v>1686.14029010851</v>
       </c>
       <c r="D23" s="18">
-        <f>D8*'8_가정'!$C$95</f>
+        <f>D8*'8_가정'!$C$96</f>
         <v>1728.51317146444</v>
       </c>
       <c r="E23" s="18">
-        <f>E8*'8_가정'!$C$95</f>
+        <f>E8*'8_가정'!$C$96</f>
         <v>1770.88605282037</v>
       </c>
       <c r="F23" s="18">
-        <f>F8*'8_가정'!$C$95</f>
+        <f>F8*'8_가정'!$C$96</f>
         <v>1813.25893417631</v>
       </c>
       <c r="G23" s="18">
-        <f>G8*'8_가정'!$C$95</f>
+        <f>G8*'8_가정'!$C$96</f>
         <v>1855.63181553224</v>
       </c>
       <c r="H23" s="18">
-        <f>H8*'8_가정'!$C$95</f>
+        <f>H8*'8_가정'!$C$96</f>
         <v>1898.00469688817</v>
       </c>
       <c r="I23" s="18">
-        <f>I8*'8_가정'!$C$95</f>
+        <f>I8*'8_가정'!$C$96</f>
         <v>2368.15535602188</v>
       </c>
       <c r="J23" s="18">
-        <f>J8*'8_가정'!$C$95</f>
+        <f>J8*'8_가정'!$C$96</f>
         <v>2588.30601515559</v>
       </c>
       <c r="K23" s="18">
-        <f>K8*'8_가정'!$C$95</f>
+        <f>K8*'8_가정'!$C$96</f>
         <v>2808.4566742893</v>
       </c>
       <c r="L23" s="18">
-        <f>L8*'8_가정'!$C$95</f>
+        <f>L8*'8_가정'!$C$96</f>
         <v>3144.34807416375</v>
       </c>
       <c r="M23" s="18">
-        <f>M8*'8_가정'!$C$95</f>
+        <f>M8*'8_가정'!$C$96</f>
         <v>3678.7394740382</v>
       </c>
       <c r="N23" s="18">
-        <f>N8*'8_가정'!$C$95</f>
+        <f>N8*'8_가정'!$C$96</f>
         <v>4659.55944534123</v>
       </c>
       <c r="O23" s="23">
@@ -32408,51 +32423,51 @@
         <v>30000</v>
       </c>
       <c r="P23" s="18">
-        <f>P8*'8_가정'!$D$95</f>
+        <f>P8*'8_가정'!$D$96</f>
         <v>10010.2151443817</v>
       </c>
       <c r="Q23" s="18">
-        <f>Q8*'8_가정'!$D$95</f>
+        <f>Q8*'8_가정'!$D$96</f>
         <v>13893.0358166242</v>
       </c>
       <c r="R23" s="18">
-        <f>R8*'8_가정'!$D$95</f>
+        <f>R8*'8_가정'!$D$96</f>
         <v>17775.8564888667</v>
       </c>
       <c r="S23" s="18">
-        <f>S8*'8_가정'!$D$95</f>
+        <f>S8*'8_가정'!$D$96</f>
         <v>21599.355127211</v>
       </c>
       <c r="T23" s="18">
-        <f>T8*'8_가정'!$D$95</f>
+        <f>T8*'8_가정'!$D$96</f>
         <v>25422.8537655552</v>
       </c>
       <c r="U23" s="18">
-        <f>U8*'8_가정'!$D$95</f>
+        <f>U8*'8_가정'!$D$96</f>
         <v>31346.3524038994</v>
       </c>
       <c r="V23" s="18">
-        <f>V8*'8_가정'!$D$95</f>
+        <f>V8*'8_가정'!$D$96</f>
         <v>34920.9621533548</v>
       </c>
       <c r="W23" s="18">
-        <f>W8*'8_가정'!$D$95</f>
+        <f>W8*'8_가정'!$D$96</f>
         <v>38131.846412614</v>
       </c>
       <c r="X23" s="18">
-        <f>X8*'8_가정'!$D$95</f>
+        <f>X8*'8_가정'!$D$96</f>
         <v>39242.7306718733</v>
       </c>
       <c r="Y23" s="18">
-        <f>Y8*'8_가정'!$D$95</f>
+        <f>Y8*'8_가정'!$D$96</f>
         <v>39242.7306718733</v>
       </c>
       <c r="Z23" s="18">
-        <f>Z8*'8_가정'!$D$95</f>
+        <f>Z8*'8_가정'!$D$96</f>
         <v>39242.7306718733</v>
       </c>
       <c r="AA23" s="18">
-        <f>AA8*'8_가정'!$D$95</f>
+        <f>AA8*'8_가정'!$D$96</f>
         <v>39242.7306718733</v>
       </c>
       <c r="AB23" s="23">
@@ -32460,15 +32475,15 @@
         <v>350071.4</v>
       </c>
       <c r="AC23" s="24">
-        <f>AC8*'8_가정'!$E$95</f>
+        <f>AC8*'8_가정'!$E$96</f>
         <v>1155000</v>
       </c>
       <c r="AD23" s="24">
-        <f>AD8*'8_가정'!$F$95</f>
+        <f>AD8*'8_가정'!$F$96</f>
         <v>2240000</v>
       </c>
       <c r="AE23" s="24">
-        <f>AE8*'8_가정'!$G$95</f>
+        <f>AE8*'8_가정'!$G$96</f>
         <v>5460000</v>
       </c>
       <c r="AF23" s="25">
@@ -32488,51 +32503,51 @@
         </is>
       </c>
       <c r="C24" s="18">
-        <f>C8*'8_가정'!$C$96</f>
+        <f>C8*'8_가정'!$C$97</f>
         <v>2360.59640615191</v>
       </c>
       <c r="D24" s="18">
-        <f>D8*'8_가정'!$C$96</f>
+        <f>D8*'8_가정'!$C$97</f>
         <v>2419.91844005022</v>
       </c>
       <c r="E24" s="18">
-        <f>E8*'8_가정'!$C$96</f>
+        <f>E8*'8_가정'!$C$97</f>
         <v>2479.24047394852</v>
       </c>
       <c r="F24" s="18">
-        <f>F8*'8_가정'!$C$96</f>
+        <f>F8*'8_가정'!$C$97</f>
         <v>2538.56250784683</v>
       </c>
       <c r="G24" s="18">
-        <f>G8*'8_가정'!$C$96</f>
+        <f>G8*'8_가정'!$C$97</f>
         <v>2597.88454174514</v>
       </c>
       <c r="H24" s="18">
-        <f>H8*'8_가정'!$C$96</f>
+        <f>H8*'8_가정'!$C$97</f>
         <v>2657.20657564344</v>
       </c>
       <c r="I24" s="18">
-        <f>I8*'8_가정'!$C$96</f>
+        <f>I8*'8_가정'!$C$97</f>
         <v>3315.41749843063</v>
       </c>
       <c r="J24" s="18">
-        <f>J8*'8_가정'!$C$96</f>
+        <f>J8*'8_가정'!$C$97</f>
         <v>3623.62842121783</v>
       </c>
       <c r="K24" s="18">
-        <f>K8*'8_가정'!$C$96</f>
+        <f>K8*'8_가정'!$C$97</f>
         <v>3931.83934400502</v>
       </c>
       <c r="L24" s="18">
-        <f>L8*'8_가정'!$C$96</f>
+        <f>L8*'8_가정'!$C$97</f>
         <v>4402.08730382925</v>
       </c>
       <c r="M24" s="18">
-        <f>M8*'8_가정'!$C$96</f>
+        <f>M8*'8_가정'!$C$97</f>
         <v>5150.23526365348</v>
       </c>
       <c r="N24" s="18">
-        <f>N8*'8_가정'!$C$96</f>
+        <f>N8*'8_가정'!$C$97</f>
         <v>6523.38322347772</v>
       </c>
       <c r="O24" s="23">
@@ -32540,51 +32555,51 @@
         <v>42000</v>
       </c>
       <c r="P24" s="18">
-        <f>P8*'8_가정'!$D$96</f>
+        <f>P8*'8_가정'!$D$97</f>
         <v>10010.2151443817</v>
       </c>
       <c r="Q24" s="18">
-        <f>Q8*'8_가정'!$D$96</f>
+        <f>Q8*'8_가정'!$D$97</f>
         <v>13893.0358166242</v>
       </c>
       <c r="R24" s="18">
-        <f>R8*'8_가정'!$D$96</f>
+        <f>R8*'8_가정'!$D$97</f>
         <v>17775.8564888667</v>
       </c>
       <c r="S24" s="18">
-        <f>S8*'8_가정'!$D$96</f>
+        <f>S8*'8_가정'!$D$97</f>
         <v>21599.355127211</v>
       </c>
       <c r="T24" s="18">
-        <f>T8*'8_가정'!$D$96</f>
+        <f>T8*'8_가정'!$D$97</f>
         <v>25422.8537655552</v>
       </c>
       <c r="U24" s="18">
-        <f>U8*'8_가정'!$D$96</f>
+        <f>U8*'8_가정'!$D$97</f>
         <v>31346.3524038994</v>
       </c>
       <c r="V24" s="18">
-        <f>V8*'8_가정'!$D$96</f>
+        <f>V8*'8_가정'!$D$97</f>
         <v>34920.9621533548</v>
       </c>
       <c r="W24" s="18">
-        <f>W8*'8_가정'!$D$96</f>
+        <f>W8*'8_가정'!$D$97</f>
         <v>38131.846412614</v>
       </c>
       <c r="X24" s="18">
-        <f>X8*'8_가정'!$D$96</f>
+        <f>X8*'8_가정'!$D$97</f>
         <v>39242.7306718733</v>
       </c>
       <c r="Y24" s="18">
-        <f>Y8*'8_가정'!$D$96</f>
+        <f>Y8*'8_가정'!$D$97</f>
         <v>39242.7306718733</v>
       </c>
       <c r="Z24" s="18">
-        <f>Z8*'8_가정'!$D$96</f>
+        <f>Z8*'8_가정'!$D$97</f>
         <v>39242.7306718733</v>
       </c>
       <c r="AA24" s="18">
-        <f>AA8*'8_가정'!$D$96</f>
+        <f>AA8*'8_가정'!$D$97</f>
         <v>39242.7306718733</v>
       </c>
       <c r="AB24" s="23">
@@ -32592,15 +32607,15 @@
         <v>350071.4</v>
       </c>
       <c r="AC24" s="24">
-        <f>AC8*'8_가정'!$E$96</f>
+        <f>AC8*'8_가정'!$E$97</f>
         <v>1056000</v>
       </c>
       <c r="AD24" s="24">
-        <f>AD8*'8_가정'!$F$96</f>
+        <f>AD8*'8_가정'!$F$97</f>
         <v>2030000</v>
       </c>
       <c r="AE24" s="24">
-        <f>AE8*'8_가정'!$G$96</f>
+        <f>AE8*'8_가정'!$G$97</f>
         <v>4836000</v>
       </c>
       <c r="AF24" s="25">
@@ -32620,51 +32635,51 @@
         </is>
       </c>
       <c r="C25" s="18">
-        <f>'8_가정'!$C$99/12</f>
+        <f>'8_가정'!$C$100/12</f>
         <v>3000</v>
       </c>
       <c r="D25" s="18">
-        <f>'8_가정'!$C$99/12</f>
+        <f>'8_가정'!$C$100/12</f>
         <v>3000</v>
       </c>
       <c r="E25" s="18">
-        <f>'8_가정'!$C$99/12</f>
+        <f>'8_가정'!$C$100/12</f>
         <v>3000</v>
       </c>
       <c r="F25" s="18">
-        <f>'8_가정'!$C$99/12</f>
+        <f>'8_가정'!$C$100/12</f>
         <v>3000</v>
       </c>
       <c r="G25" s="18">
-        <f>'8_가정'!$C$99/12</f>
+        <f>'8_가정'!$C$100/12</f>
         <v>3000</v>
       </c>
       <c r="H25" s="18">
-        <f>'8_가정'!$C$99/12</f>
+        <f>'8_가정'!$C$100/12</f>
         <v>3000</v>
       </c>
       <c r="I25" s="18">
-        <f>'8_가정'!$C$99/12</f>
+        <f>'8_가정'!$C$100/12</f>
         <v>3000</v>
       </c>
       <c r="J25" s="18">
-        <f>'8_가정'!$C$99/12</f>
+        <f>'8_가정'!$C$100/12</f>
         <v>3000</v>
       </c>
       <c r="K25" s="18">
-        <f>'8_가정'!$C$99/12</f>
+        <f>'8_가정'!$C$100/12</f>
         <v>3000</v>
       </c>
       <c r="L25" s="18">
-        <f>'8_가정'!$C$99/12</f>
+        <f>'8_가정'!$C$100/12</f>
         <v>3000</v>
       </c>
       <c r="M25" s="18">
-        <f>'8_가정'!$C$99/12</f>
+        <f>'8_가정'!$C$100/12</f>
         <v>3000</v>
       </c>
       <c r="N25" s="18">
-        <f>'8_가정'!$C$99/12</f>
+        <f>'8_가정'!$C$100/12</f>
         <v>3000</v>
       </c>
       <c r="O25" s="23">
@@ -32672,51 +32687,51 @@
         <v>36000</v>
       </c>
       <c r="P25" s="18">
-        <f>'8_가정'!$D$99/12</f>
+        <f>'8_가정'!$D$100/12</f>
         <v>12000</v>
       </c>
       <c r="Q25" s="18">
-        <f>'8_가정'!$D$99/12</f>
+        <f>'8_가정'!$D$100/12</f>
         <v>12000</v>
       </c>
       <c r="R25" s="18">
-        <f>'8_가정'!$D$99/12</f>
+        <f>'8_가정'!$D$100/12</f>
         <v>12000</v>
       </c>
       <c r="S25" s="18">
-        <f>'8_가정'!$D$99/12</f>
+        <f>'8_가정'!$D$100/12</f>
         <v>12000</v>
       </c>
       <c r="T25" s="18">
-        <f>'8_가정'!$D$99/12</f>
+        <f>'8_가정'!$D$100/12</f>
         <v>12000</v>
       </c>
       <c r="U25" s="18">
-        <f>'8_가정'!$D$99/12</f>
+        <f>'8_가정'!$D$100/12</f>
         <v>12000</v>
       </c>
       <c r="V25" s="18">
-        <f>'8_가정'!$D$99/12</f>
+        <f>'8_가정'!$D$100/12</f>
         <v>12000</v>
       </c>
       <c r="W25" s="18">
-        <f>'8_가정'!$D$99/12</f>
+        <f>'8_가정'!$D$100/12</f>
         <v>12000</v>
       </c>
       <c r="X25" s="18">
-        <f>'8_가정'!$D$99/12</f>
+        <f>'8_가정'!$D$100/12</f>
         <v>12000</v>
       </c>
       <c r="Y25" s="18">
-        <f>'8_가정'!$D$99/12</f>
+        <f>'8_가정'!$D$100/12</f>
         <v>12000</v>
       </c>
       <c r="Z25" s="18">
-        <f>'8_가정'!$D$99/12</f>
+        <f>'8_가정'!$D$100/12</f>
         <v>12000</v>
       </c>
       <c r="AA25" s="18">
-        <f>'8_가정'!$D$99/12</f>
+        <f>'8_가정'!$D$100/12</f>
         <v>12000</v>
       </c>
       <c r="AB25" s="23">
@@ -32724,15 +32739,15 @@
         <v>144000</v>
       </c>
       <c r="AC25" s="24">
-        <f>'8_가정'!$E$99</f>
+        <f>'8_가정'!$E$100</f>
         <v>300000</v>
       </c>
       <c r="AD25" s="24">
-        <f>'8_가정'!$F$99</f>
+        <f>'8_가정'!$F$100</f>
         <v>600000</v>
       </c>
       <c r="AE25" s="24">
-        <f>'8_가정'!$G$99</f>
+        <f>'8_가정'!$G$100</f>
         <v>1000000</v>
       </c>
       <c r="AF25" s="25">
@@ -32752,51 +32767,51 @@
         </is>
       </c>
       <c r="C26" s="18">
-        <f>'8_가정'!$C$100/12</f>
+        <f>'8_가정'!$C$101/12</f>
         <v>5000</v>
       </c>
       <c r="D26" s="18">
-        <f>'8_가정'!$C$100/12</f>
+        <f>'8_가정'!$C$101/12</f>
         <v>5000</v>
       </c>
       <c r="E26" s="18">
-        <f>'8_가정'!$C$100/12</f>
+        <f>'8_가정'!$C$101/12</f>
         <v>5000</v>
       </c>
       <c r="F26" s="18">
-        <f>'8_가정'!$C$100/12</f>
+        <f>'8_가정'!$C$101/12</f>
         <v>5000</v>
       </c>
       <c r="G26" s="18">
-        <f>'8_가정'!$C$100/12</f>
+        <f>'8_가정'!$C$101/12</f>
         <v>5000</v>
       </c>
       <c r="H26" s="18">
-        <f>'8_가정'!$C$100/12</f>
+        <f>'8_가정'!$C$101/12</f>
         <v>5000</v>
       </c>
       <c r="I26" s="18">
-        <f>'8_가정'!$C$100/12</f>
+        <f>'8_가정'!$C$101/12</f>
         <v>5000</v>
       </c>
       <c r="J26" s="18">
-        <f>'8_가정'!$C$100/12</f>
+        <f>'8_가정'!$C$101/12</f>
         <v>5000</v>
       </c>
       <c r="K26" s="18">
-        <f>'8_가정'!$C$100/12</f>
+        <f>'8_가정'!$C$101/12</f>
         <v>5000</v>
       </c>
       <c r="L26" s="18">
-        <f>'8_가정'!$C$100/12</f>
+        <f>'8_가정'!$C$101/12</f>
         <v>5000</v>
       </c>
       <c r="M26" s="18">
-        <f>'8_가정'!$C$100/12</f>
+        <f>'8_가정'!$C$101/12</f>
         <v>5000</v>
       </c>
       <c r="N26" s="18">
-        <f>'8_가정'!$C$100/12</f>
+        <f>'8_가정'!$C$101/12</f>
         <v>5000</v>
       </c>
       <c r="O26" s="23">
@@ -32804,51 +32819,51 @@
         <v>60000</v>
       </c>
       <c r="P26" s="18">
-        <f>'8_가정'!$D$100/12</f>
+        <f>'8_가정'!$D$101/12</f>
         <v>15000</v>
       </c>
       <c r="Q26" s="18">
-        <f>'8_가정'!$D$100/12</f>
+        <f>'8_가정'!$D$101/12</f>
         <v>15000</v>
       </c>
       <c r="R26" s="18">
-        <f>'8_가정'!$D$100/12</f>
+        <f>'8_가정'!$D$101/12</f>
         <v>15000</v>
       </c>
       <c r="S26" s="18">
-        <f>'8_가정'!$D$100/12</f>
+        <f>'8_가정'!$D$101/12</f>
         <v>15000</v>
       </c>
       <c r="T26" s="18">
-        <f>'8_가정'!$D$100/12</f>
+        <f>'8_가정'!$D$101/12</f>
         <v>15000</v>
       </c>
       <c r="U26" s="18">
-        <f>'8_가정'!$D$100/12</f>
+        <f>'8_가정'!$D$101/12</f>
         <v>15000</v>
       </c>
       <c r="V26" s="18">
-        <f>'8_가정'!$D$100/12</f>
+        <f>'8_가정'!$D$101/12</f>
         <v>15000</v>
       </c>
       <c r="W26" s="18">
-        <f>'8_가정'!$D$100/12</f>
+        <f>'8_가정'!$D$101/12</f>
         <v>15000</v>
       </c>
       <c r="X26" s="18">
-        <f>'8_가정'!$D$100/12</f>
+        <f>'8_가정'!$D$101/12</f>
         <v>15000</v>
       </c>
       <c r="Y26" s="18">
-        <f>'8_가정'!$D$100/12</f>
+        <f>'8_가정'!$D$101/12</f>
         <v>15000</v>
       </c>
       <c r="Z26" s="18">
-        <f>'8_가정'!$D$100/12</f>
+        <f>'8_가정'!$D$101/12</f>
         <v>15000</v>
       </c>
       <c r="AA26" s="18">
-        <f>'8_가정'!$D$100/12</f>
+        <f>'8_가정'!$D$101/12</f>
         <v>15000</v>
       </c>
       <c r="AB26" s="23">
@@ -32856,15 +32871,15 @@
         <v>180000</v>
       </c>
       <c r="AC26" s="24">
-        <f>'8_가정'!$E$100</f>
+        <f>'8_가정'!$E$101</f>
         <v>400000</v>
       </c>
       <c r="AD26" s="24">
-        <f>'8_가정'!$F$100</f>
+        <f>'8_가정'!$F$101</f>
         <v>800000</v>
       </c>
       <c r="AE26" s="24">
-        <f>'8_가정'!$G$100</f>
+        <f>'8_가정'!$G$101</f>
         <v>1400000</v>
       </c>
       <c r="AF26" s="25">
@@ -32884,51 +32899,51 @@
         </is>
       </c>
       <c r="C27" s="18">
-        <f>('8_가정'!$C$101+'8_가정'!$C$102)/12</f>
+        <f>('8_가정'!$C$102+'8_가정'!$C$103)/12</f>
         <v>1500</v>
       </c>
       <c r="D27" s="18">
-        <f>('8_가정'!$C$101+'8_가정'!$C$102)/12</f>
+        <f>('8_가정'!$C$102+'8_가정'!$C$103)/12</f>
         <v>1500</v>
       </c>
       <c r="E27" s="18">
-        <f>('8_가정'!$C$101+'8_가정'!$C$102)/12</f>
+        <f>('8_가정'!$C$102+'8_가정'!$C$103)/12</f>
         <v>1500</v>
       </c>
       <c r="F27" s="18">
-        <f>('8_가정'!$C$101+'8_가정'!$C$102)/12</f>
+        <f>('8_가정'!$C$102+'8_가정'!$C$103)/12</f>
         <v>1500</v>
       </c>
       <c r="G27" s="18">
-        <f>('8_가정'!$C$101+'8_가정'!$C$102)/12</f>
+        <f>('8_가정'!$C$102+'8_가정'!$C$103)/12</f>
         <v>1500</v>
       </c>
       <c r="H27" s="18">
-        <f>('8_가정'!$C$101+'8_가정'!$C$102)/12</f>
+        <f>('8_가정'!$C$102+'8_가정'!$C$103)/12</f>
         <v>1500</v>
       </c>
       <c r="I27" s="18">
-        <f>('8_가정'!$C$101+'8_가정'!$C$102)/12</f>
+        <f>('8_가정'!$C$102+'8_가정'!$C$103)/12</f>
         <v>1500</v>
       </c>
       <c r="J27" s="18">
-        <f>('8_가정'!$C$101+'8_가정'!$C$102)/12</f>
+        <f>('8_가정'!$C$102+'8_가정'!$C$103)/12</f>
         <v>1500</v>
       </c>
       <c r="K27" s="18">
-        <f>('8_가정'!$C$101+'8_가정'!$C$102)/12</f>
+        <f>('8_가정'!$C$102+'8_가정'!$C$103)/12</f>
         <v>1500</v>
       </c>
       <c r="L27" s="18">
-        <f>('8_가정'!$C$101+'8_가정'!$C$102)/12</f>
+        <f>('8_가정'!$C$102+'8_가정'!$C$103)/12</f>
         <v>1500</v>
       </c>
       <c r="M27" s="18">
-        <f>('8_가정'!$C$101+'8_가정'!$C$102)/12</f>
+        <f>('8_가정'!$C$102+'8_가정'!$C$103)/12</f>
         <v>1500</v>
       </c>
       <c r="N27" s="18">
-        <f>('8_가정'!$C$101+'8_가정'!$C$102)/12</f>
+        <f>('8_가정'!$C$102+'8_가정'!$C$103)/12</f>
         <v>1500</v>
       </c>
       <c r="O27" s="23">
@@ -32936,51 +32951,51 @@
         <v>18000</v>
       </c>
       <c r="P27" s="18">
-        <f>('8_가정'!$D$101+'8_가정'!$D$102)/12</f>
+        <f>('8_가정'!$D$102+'8_가정'!$D$103)/12</f>
         <v>36329.4166666667</v>
       </c>
       <c r="Q27" s="18">
-        <f>('8_가정'!$D$101+'8_가정'!$D$102)/12</f>
+        <f>('8_가정'!$D$102+'8_가정'!$D$103)/12</f>
         <v>36329.4166666667</v>
       </c>
       <c r="R27" s="18">
-        <f>('8_가정'!$D$101+'8_가정'!$D$102)/12</f>
+        <f>('8_가정'!$D$102+'8_가정'!$D$103)/12</f>
         <v>36329.4166666667</v>
       </c>
       <c r="S27" s="18">
-        <f>('8_가정'!$D$101+'8_가정'!$D$102)/12</f>
+        <f>('8_가정'!$D$102+'8_가정'!$D$103)/12</f>
         <v>36329.4166666667</v>
       </c>
       <c r="T27" s="18">
-        <f>('8_가정'!$D$101+'8_가정'!$D$102)/12</f>
+        <f>('8_가정'!$D$102+'8_가정'!$D$103)/12</f>
         <v>36329.4166666667</v>
       </c>
       <c r="U27" s="18">
-        <f>('8_가정'!$D$101+'8_가정'!$D$102)/12</f>
+        <f>('8_가정'!$D$102+'8_가정'!$D$103)/12</f>
         <v>36329.4166666667</v>
       </c>
       <c r="V27" s="18">
-        <f>('8_가정'!$D$101+'8_가정'!$D$102)/12</f>
+        <f>('8_가정'!$D$102+'8_가정'!$D$103)/12</f>
         <v>36329.4166666667</v>
       </c>
       <c r="W27" s="18">
-        <f>('8_가정'!$D$101+'8_가정'!$D$102)/12</f>
+        <f>('8_가정'!$D$102+'8_가정'!$D$103)/12</f>
         <v>36329.4166666667</v>
       </c>
       <c r="X27" s="18">
-        <f>('8_가정'!$D$101+'8_가정'!$D$102)/12</f>
+        <f>('8_가정'!$D$102+'8_가정'!$D$103)/12</f>
         <v>36329.4166666667</v>
       </c>
       <c r="Y27" s="18">
-        <f>('8_가정'!$D$101+'8_가정'!$D$102)/12</f>
+        <f>('8_가정'!$D$102+'8_가정'!$D$103)/12</f>
         <v>36329.4166666667</v>
       </c>
       <c r="Z27" s="18">
-        <f>('8_가정'!$D$101+'8_가정'!$D$102)/12</f>
+        <f>('8_가정'!$D$102+'8_가정'!$D$103)/12</f>
         <v>36329.4166666667</v>
       </c>
       <c r="AA27" s="18">
-        <f>('8_가정'!$D$101+'8_가정'!$D$102)/12</f>
+        <f>('8_가정'!$D$102+'8_가정'!$D$103)/12</f>
         <v>36329.4166666667</v>
       </c>
       <c r="AB27" s="23">
@@ -32988,15 +33003,15 @@
         <v>435953</v>
       </c>
       <c r="AC27" s="24">
-        <f>('8_가정'!$E$101+'8_가정'!$E$102)</f>
+        <f>('8_가정'!$E$102+'8_가정'!$E$103)</f>
         <v>485953</v>
       </c>
       <c r="AD27" s="24">
-        <f>('8_가정'!$F$101+'8_가정'!$F$102)</f>
+        <f>('8_가정'!$F$102+'8_가정'!$F$103)</f>
         <v>575953</v>
       </c>
       <c r="AE27" s="24">
-        <f>('8_가정'!$G$101+'8_가정'!$G$102)</f>
+        <f>('8_가정'!$G$102+'8_가정'!$G$103)</f>
         <v>695953</v>
       </c>
       <c r="AF27" s="25">
@@ -33016,51 +33031,51 @@
         </is>
       </c>
       <c r="C28" s="18">
-        <f>C8*'8_가정'!$C$97</f>
+        <f>C8*'8_가정'!$C$98</f>
         <v>269.782446417362</v>
       </c>
       <c r="D28" s="18">
-        <f>D8*'8_가정'!$C$97</f>
+        <f>D8*'8_가정'!$C$98</f>
         <v>276.562107434311</v>
       </c>
       <c r="E28" s="18">
-        <f>E8*'8_가정'!$C$97</f>
+        <f>E8*'8_가정'!$C$98</f>
         <v>283.34176845126</v>
       </c>
       <c r="F28" s="18">
-        <f>F8*'8_가정'!$C$97</f>
+        <f>F8*'8_가정'!$C$98</f>
         <v>290.121429468209</v>
       </c>
       <c r="G28" s="18">
-        <f>G8*'8_가정'!$C$97</f>
+        <f>G8*'8_가정'!$C$98</f>
         <v>296.901090485158</v>
       </c>
       <c r="H28" s="18">
-        <f>H8*'8_가정'!$C$97</f>
+        <f>H8*'8_가정'!$C$98</f>
         <v>303.680751502107</v>
       </c>
       <c r="I28" s="18">
-        <f>I8*'8_가정'!$C$97</f>
+        <f>I8*'8_가정'!$C$98</f>
         <v>378.904856963501</v>
       </c>
       <c r="J28" s="18">
-        <f>J8*'8_가정'!$C$97</f>
+        <f>J8*'8_가정'!$C$98</f>
         <v>414.128962424895</v>
       </c>
       <c r="K28" s="18">
-        <f>K8*'8_가정'!$C$97</f>
+        <f>K8*'8_가정'!$C$98</f>
         <v>449.353067886288</v>
       </c>
       <c r="L28" s="18">
-        <f>L8*'8_가정'!$C$97</f>
+        <f>L8*'8_가정'!$C$98</f>
         <v>503.0956918662</v>
       </c>
       <c r="M28" s="18">
-        <f>M8*'8_가정'!$C$97</f>
+        <f>M8*'8_가정'!$C$98</f>
         <v>588.598315846112</v>
       </c>
       <c r="N28" s="18">
-        <f>N8*'8_가정'!$C$97</f>
+        <f>N8*'8_가정'!$C$98</f>
         <v>745.529511254596</v>
       </c>
       <c r="O28" s="23">
@@ -33068,51 +33083,51 @@
         <v>4800</v>
       </c>
       <c r="P28" s="18">
-        <f>P8*'8_가정'!$D$97</f>
+        <f>P8*'8_가정'!$D$98</f>
         <v>1430.03073491167</v>
       </c>
       <c r="Q28" s="18">
-        <f>Q8*'8_가정'!$D$97</f>
+        <f>Q8*'8_가정'!$D$98</f>
         <v>1984.71940237489</v>
       </c>
       <c r="R28" s="18">
-        <f>R8*'8_가정'!$D$97</f>
+        <f>R8*'8_가정'!$D$98</f>
         <v>2539.40806983811</v>
       </c>
       <c r="S28" s="18">
-        <f>S8*'8_가정'!$D$97</f>
+        <f>S8*'8_가정'!$D$98</f>
         <v>3085.62216103014</v>
       </c>
       <c r="T28" s="18">
-        <f>T8*'8_가정'!$D$97</f>
+        <f>T8*'8_가정'!$D$98</f>
         <v>3631.83625222217</v>
       </c>
       <c r="U28" s="18">
-        <f>U8*'8_가정'!$D$97</f>
+        <f>U8*'8_가정'!$D$98</f>
         <v>4478.0503434142</v>
       </c>
       <c r="V28" s="18">
-        <f>V8*'8_가정'!$D$97</f>
+        <f>V8*'8_가정'!$D$98</f>
         <v>4988.70887905068</v>
       </c>
       <c r="W28" s="18">
-        <f>W8*'8_가정'!$D$97</f>
+        <f>W8*'8_가정'!$D$98</f>
         <v>5447.40663037343</v>
       </c>
       <c r="X28" s="18">
-        <f>X8*'8_가정'!$D$97</f>
+        <f>X8*'8_가정'!$D$98</f>
         <v>5606.10438169618</v>
       </c>
       <c r="Y28" s="18">
-        <f>Y8*'8_가정'!$D$97</f>
+        <f>Y8*'8_가정'!$D$98</f>
         <v>5606.10438169618</v>
       </c>
       <c r="Z28" s="18">
-        <f>Z8*'8_가정'!$D$97</f>
+        <f>Z8*'8_가정'!$D$98</f>
         <v>5606.10438169618</v>
       </c>
       <c r="AA28" s="18">
-        <f>AA8*'8_가정'!$D$97</f>
+        <f>AA8*'8_가정'!$D$98</f>
         <v>5606.10438169618</v>
       </c>
       <c r="AB28" s="23">
@@ -33120,15 +33135,15 @@
         <v>50010.2</v>
       </c>
       <c r="AC28" s="24">
-        <f>AC8*'8_가정'!$E$97</f>
+        <f>AC8*'8_가정'!$E$98</f>
         <v>165000</v>
       </c>
       <c r="AD28" s="24">
-        <f>AD8*'8_가정'!$F$97</f>
+        <f>AD8*'8_가정'!$F$98</f>
         <v>350000</v>
       </c>
       <c r="AE28" s="24">
-        <f>AE8*'8_가정'!$G$97</f>
+        <f>AE8*'8_가정'!$G$98</f>
         <v>780000</v>
       </c>
       <c r="AF28" s="25">
@@ -33148,51 +33163,51 @@
         </is>
       </c>
       <c r="C29" s="18">
-        <f>C8*'8_가정'!$C$98</f>
+        <f>C8*'8_가정'!$C$99</f>
         <v>1686.14029010851</v>
       </c>
       <c r="D29" s="18">
-        <f>D8*'8_가정'!$C$98</f>
+        <f>D8*'8_가정'!$C$99</f>
         <v>1728.51317146444</v>
       </c>
       <c r="E29" s="18">
-        <f>E8*'8_가정'!$C$98</f>
+        <f>E8*'8_가정'!$C$99</f>
         <v>1770.88605282037</v>
       </c>
       <c r="F29" s="18">
-        <f>F8*'8_가정'!$C$98</f>
+        <f>F8*'8_가정'!$C$99</f>
         <v>1813.25893417631</v>
       </c>
       <c r="G29" s="18">
-        <f>G8*'8_가정'!$C$98</f>
+        <f>G8*'8_가정'!$C$99</f>
         <v>1855.63181553224</v>
       </c>
       <c r="H29" s="18">
-        <f>H8*'8_가정'!$C$98</f>
+        <f>H8*'8_가정'!$C$99</f>
         <v>1898.00469688817</v>
       </c>
       <c r="I29" s="18">
-        <f>I8*'8_가정'!$C$98</f>
+        <f>I8*'8_가정'!$C$99</f>
         <v>2368.15535602188</v>
       </c>
       <c r="J29" s="18">
-        <f>J8*'8_가정'!$C$98</f>
+        <f>J8*'8_가정'!$C$99</f>
         <v>2588.30601515559</v>
       </c>
       <c r="K29" s="18">
-        <f>K8*'8_가정'!$C$98</f>
+        <f>K8*'8_가정'!$C$99</f>
         <v>2808.4566742893</v>
       </c>
       <c r="L29" s="18">
-        <f>L8*'8_가정'!$C$98</f>
+        <f>L8*'8_가정'!$C$99</f>
         <v>3144.34807416375</v>
       </c>
       <c r="M29" s="18">
-        <f>M8*'8_가정'!$C$98</f>
+        <f>M8*'8_가정'!$C$99</f>
         <v>3678.7394740382</v>
       </c>
       <c r="N29" s="18">
-        <f>N8*'8_가정'!$C$98</f>
+        <f>N8*'8_가정'!$C$99</f>
         <v>4659.55944534123</v>
       </c>
       <c r="O29" s="23">
@@ -33200,51 +33215,51 @@
         <v>30000</v>
       </c>
       <c r="P29" s="18">
-        <f>P8*'8_가정'!$D$98</f>
+        <f>P8*'8_가정'!$D$99</f>
         <v>8580.18440947</v>
       </c>
       <c r="Q29" s="18">
-        <f>Q8*'8_가정'!$D$98</f>
+        <f>Q8*'8_가정'!$D$99</f>
         <v>11908.3164142493</v>
       </c>
       <c r="R29" s="18">
-        <f>R8*'8_가정'!$D$98</f>
+        <f>R8*'8_가정'!$D$99</f>
         <v>15236.4484190286</v>
       </c>
       <c r="S29" s="18">
-        <f>S8*'8_가정'!$D$98</f>
+        <f>S8*'8_가정'!$D$99</f>
         <v>18513.7329661808</v>
       </c>
       <c r="T29" s="18">
-        <f>T8*'8_가정'!$D$98</f>
+        <f>T8*'8_가정'!$D$99</f>
         <v>21791.017513333</v>
       </c>
       <c r="U29" s="18">
-        <f>U8*'8_가정'!$D$98</f>
+        <f>U8*'8_가정'!$D$99</f>
         <v>26868.3020604852</v>
       </c>
       <c r="V29" s="18">
-        <f>V8*'8_가정'!$D$98</f>
+        <f>V8*'8_가정'!$D$99</f>
         <v>29932.2532743041</v>
       </c>
       <c r="W29" s="18">
-        <f>W8*'8_가정'!$D$98</f>
+        <f>W8*'8_가정'!$D$99</f>
         <v>32684.4397822406</v>
       </c>
       <c r="X29" s="18">
-        <f>X8*'8_가정'!$D$98</f>
+        <f>X8*'8_가정'!$D$99</f>
         <v>33636.6262901771</v>
       </c>
       <c r="Y29" s="18">
-        <f>Y8*'8_가정'!$D$98</f>
+        <f>Y8*'8_가정'!$D$99</f>
         <v>33636.6262901771</v>
       </c>
       <c r="Z29" s="18">
-        <f>Z8*'8_가정'!$D$98</f>
+        <f>Z8*'8_가정'!$D$99</f>
         <v>33636.6262901771</v>
       </c>
       <c r="AA29" s="18">
-        <f>AA8*'8_가정'!$D$98</f>
+        <f>AA8*'8_가정'!$D$99</f>
         <v>33636.6262901771</v>
       </c>
       <c r="AB29" s="23">
@@ -33252,15 +33267,15 @@
         <v>300061.2</v>
       </c>
       <c r="AC29" s="24">
-        <f>AC8*'8_가정'!$E$98</f>
+        <f>AC8*'8_가정'!$E$99</f>
         <v>858000</v>
       </c>
       <c r="AD29" s="24">
-        <f>AD8*'8_가정'!$F$98</f>
+        <f>AD8*'8_가정'!$F$99</f>
         <v>1540000</v>
       </c>
       <c r="AE29" s="24">
-        <f>AE8*'8_가정'!$G$98</f>
+        <f>AE8*'8_가정'!$G$99</f>
         <v>3744000</v>
       </c>
       <c r="AF29" s="25">
@@ -33276,123 +33291,123 @@
       </c>
       <c r="C30" s="26">
         <f>SUM(C19:C29)</f>
-        <v>48067.6909461035</v>
+        <v>65745.4909461035</v>
       </c>
       <c r="D30" s="26">
         <f>SUM(D19:D29)</f>
-        <v>48264.301115595</v>
+        <v>65942.101115595</v>
       </c>
       <c r="E30" s="26">
         <f>SUM(E19:E29)</f>
-        <v>48460.9112850865</v>
+        <v>66138.7112850865</v>
       </c>
       <c r="F30" s="26">
         <f>SUM(F19:F29)</f>
-        <v>48657.5214545781</v>
+        <v>66335.3214545781</v>
       </c>
       <c r="G30" s="26">
         <f>SUM(G19:G29)</f>
-        <v>48854.1316240696</v>
+        <v>66531.9316240696</v>
       </c>
       <c r="H30" s="26">
         <f>SUM(H19:H29)</f>
-        <v>49050.7417935611</v>
+        <v>66728.5417935611</v>
       </c>
       <c r="I30" s="26">
         <f>SUM(I19:I29)</f>
-        <v>51232.2408519415</v>
+        <v>68910.0408519415</v>
       </c>
       <c r="J30" s="26">
         <f>SUM(J19:J29)</f>
-        <v>52253.7399103219</v>
+        <v>69931.5399103219</v>
       </c>
       <c r="K30" s="26">
         <f>SUM(K19:K29)</f>
-        <v>53275.2389687024</v>
+        <v>70953.0389687024</v>
       </c>
       <c r="L30" s="26">
         <f>SUM(L19:L29)</f>
-        <v>59225.7750641198</v>
+        <v>79428.9750641198</v>
       </c>
       <c r="M30" s="26">
         <f>SUM(M19:M29)</f>
-        <v>61705.3511595373</v>
+        <v>81908.5511595373</v>
       </c>
       <c r="N30" s="26">
         <f>SUM(N19:N29)</f>
-        <v>70648.3558263833</v>
+        <v>93376.9558263833</v>
       </c>
       <c r="O30" s="27">
         <f>SUM(O19:O29)</f>
-        <v>639696</v>
+        <v>861931.2</v>
       </c>
       <c r="P30" s="26">
         <f>SUM(P19:P29)</f>
-        <v>162350.338714017</v>
+        <v>180246.518714017</v>
       </c>
       <c r="Q30" s="26">
         <f>SUM(Q19:Q29)</f>
-        <v>184602.998737913</v>
+        <v>204288.796737913</v>
       </c>
       <c r="R30" s="26">
         <f>SUM(R19:R29)</f>
-        <v>206855.65876181</v>
+        <v>228331.07476181</v>
       </c>
       <c r="S30" s="26">
         <f>SUM(S19:S29)</f>
-        <v>228854.081497571</v>
+        <v>252119.115497571</v>
       </c>
       <c r="T30" s="26">
         <f>SUM(T19:T29)</f>
-        <v>250852.504233332</v>
+        <v>275907.156233332</v>
       </c>
       <c r="U30" s="26">
         <f>SUM(U19:U29)</f>
-        <v>281850.926969093</v>
+        <v>308695.196969093</v>
       </c>
       <c r="V30" s="26">
         <f>SUM(V19:V29)</f>
-        <v>302782.683038187</v>
+        <v>331416.571038187</v>
       </c>
       <c r="W30" s="26">
         <f>SUM(W19:W29)</f>
-        <v>322155.61557787</v>
+        <v>352579.12157787</v>
       </c>
       <c r="X30" s="26">
         <f>SUM(X19:X29)</f>
-        <v>332528.548117552</v>
+        <v>364741.672117552</v>
       </c>
       <c r="Y30" s="26">
         <f>SUM(Y19:Y29)</f>
-        <v>338140.548117552</v>
+        <v>372143.290117552</v>
       </c>
       <c r="Z30" s="26">
         <f>SUM(Z19:Z29)</f>
-        <v>343752.548117552</v>
+        <v>379544.908117552</v>
       </c>
       <c r="AA30" s="26">
         <f>SUM(AA19:AA29)</f>
-        <v>354976.548117552</v>
+        <v>394348.144117552</v>
       </c>
       <c r="AB30" s="27">
         <f>SUM(AB19:AB29)</f>
-        <v>3309703</v>
+        <v>3644361.566</v>
       </c>
       <c r="AC30" s="28">
         <f>SUM(AC19:AC29)</f>
-        <v>9986153</v>
+        <v>11154420.46892</v>
       </c>
       <c r="AD30" s="28">
         <f>SUM(AD19:AD29)</f>
-        <v>19994473</v>
+        <v>22427558.058178</v>
       </c>
       <c r="AE30" s="28">
         <f>SUM(AE19:AE29)</f>
-        <v>42300313</v>
+        <v>47245435.7478032</v>
       </c>
       <c r="AF30" s="26">
         <f>SUM(AF19:AF29)</f>
-        <v>76230338</v>
+        <v>85333707.0409012</v>
       </c>
     </row>
     <row r="32">
@@ -33414,51 +33429,51 @@
         </is>
       </c>
       <c r="C33" s="18">
-        <f>'8_가정'!$C$108/12</f>
+        <f>'8_가정'!$C$109/12</f>
         <v>5416.66666666667</v>
       </c>
       <c r="D33" s="18">
-        <f>'8_가정'!$C$108/12</f>
+        <f>'8_가정'!$C$109/12</f>
         <v>5416.66666666667</v>
       </c>
       <c r="E33" s="18">
-        <f>'8_가정'!$C$108/12</f>
+        <f>'8_가정'!$C$109/12</f>
         <v>5416.66666666667</v>
       </c>
       <c r="F33" s="18">
-        <f>'8_가정'!$C$108/12</f>
+        <f>'8_가정'!$C$109/12</f>
         <v>5416.66666666667</v>
       </c>
       <c r="G33" s="18">
-        <f>'8_가정'!$C$108/12</f>
+        <f>'8_가정'!$C$109/12</f>
         <v>5416.66666666667</v>
       </c>
       <c r="H33" s="18">
-        <f>'8_가정'!$C$108/12</f>
+        <f>'8_가정'!$C$109/12</f>
         <v>5416.66666666667</v>
       </c>
       <c r="I33" s="18">
-        <f>'8_가정'!$C$108/12</f>
+        <f>'8_가정'!$C$109/12</f>
         <v>5416.66666666667</v>
       </c>
       <c r="J33" s="18">
-        <f>'8_가정'!$C$108/12</f>
+        <f>'8_가정'!$C$109/12</f>
         <v>5416.66666666667</v>
       </c>
       <c r="K33" s="18">
-        <f>'8_가정'!$C$108/12</f>
+        <f>'8_가정'!$C$109/12</f>
         <v>5416.66666666667</v>
       </c>
       <c r="L33" s="18">
-        <f>'8_가정'!$C$108/12</f>
+        <f>'8_가정'!$C$109/12</f>
         <v>5416.66666666667</v>
       </c>
       <c r="M33" s="18">
-        <f>'8_가정'!$C$108/12</f>
+        <f>'8_가정'!$C$109/12</f>
         <v>5416.66666666667</v>
       </c>
       <c r="N33" s="18">
-        <f>'8_가정'!$C$108/12</f>
+        <f>'8_가정'!$C$109/12</f>
         <v>5416.66666666667</v>
       </c>
       <c r="O33" s="23">
@@ -33466,51 +33481,51 @@
         <v>65000</v>
       </c>
       <c r="P33" s="18">
-        <f>'8_가정'!$D$108/12</f>
+        <f>'8_가정'!$D$109/12</f>
         <v>3333.33333333333</v>
       </c>
       <c r="Q33" s="18">
-        <f>'8_가정'!$D$108/12</f>
+        <f>'8_가정'!$D$109/12</f>
         <v>3333.33333333333</v>
       </c>
       <c r="R33" s="18">
-        <f>'8_가정'!$D$108/12</f>
+        <f>'8_가정'!$D$109/12</f>
         <v>3333.33333333333</v>
       </c>
       <c r="S33" s="18">
-        <f>'8_가정'!$D$108/12</f>
+        <f>'8_가정'!$D$109/12</f>
         <v>3333.33333333333</v>
       </c>
       <c r="T33" s="18">
-        <f>'8_가정'!$D$108/12</f>
+        <f>'8_가정'!$D$109/12</f>
         <v>3333.33333333333</v>
       </c>
       <c r="U33" s="18">
-        <f>'8_가정'!$D$108/12</f>
+        <f>'8_가정'!$D$109/12</f>
         <v>3333.33333333333</v>
       </c>
       <c r="V33" s="18">
-        <f>'8_가정'!$D$108/12</f>
+        <f>'8_가정'!$D$109/12</f>
         <v>3333.33333333333</v>
       </c>
       <c r="W33" s="18">
-        <f>'8_가정'!$D$108/12</f>
+        <f>'8_가정'!$D$109/12</f>
         <v>3333.33333333333</v>
       </c>
       <c r="X33" s="18">
-        <f>'8_가정'!$D$108/12</f>
+        <f>'8_가정'!$D$109/12</f>
         <v>3333.33333333333</v>
       </c>
       <c r="Y33" s="18">
-        <f>'8_가정'!$D$108/12</f>
+        <f>'8_가정'!$D$109/12</f>
         <v>3333.33333333333</v>
       </c>
       <c r="Z33" s="18">
-        <f>'8_가정'!$D$108/12</f>
+        <f>'8_가정'!$D$109/12</f>
         <v>3333.33333333333</v>
       </c>
       <c r="AA33" s="18">
-        <f>'8_가정'!$D$108/12</f>
+        <f>'8_가정'!$D$109/12</f>
         <v>3333.33333333333</v>
       </c>
       <c r="AB33" s="23">
@@ -33518,15 +33533,15 @@
         <v>40000</v>
       </c>
       <c r="AC33" s="24">
-        <f>'8_가정'!$E$108</f>
+        <f>'8_가정'!$E$109</f>
         <v>30000</v>
       </c>
       <c r="AD33" s="24">
-        <f>'8_가정'!$F$108</f>
+        <f>'8_가정'!$F$109</f>
         <v>0</v>
       </c>
       <c r="AE33" s="24">
-        <f>'8_가정'!$G$108</f>
+        <f>'8_가정'!$G$109</f>
         <v>0</v>
       </c>
       <c r="AF33" s="25">
@@ -33701,7 +33716,7 @@
       </c>
       <c r="B36" s="7" t="inlineStr"/>
       <c r="O36" s="48">
-        <f>AVERAGE('8_가정'!$C$106,O35)</f>
+        <f>AVERAGE('8_가정'!$C$107,O35)</f>
         <v>1199771.5</v>
       </c>
       <c r="AB36" s="44">
@@ -33729,23 +33744,23 @@
       </c>
       <c r="B37" s="7" t="inlineStr"/>
       <c r="O37" s="48">
-        <f>O36*'8_가정'!$C$107</f>
+        <f>O36*'8_가정'!$C$108</f>
         <v>57589.032</v>
       </c>
       <c r="AB37" s="48">
-        <f>AB36*'8_가정'!$D$107</f>
+        <f>AB36*'8_가정'!$D$108</f>
         <v>76800</v>
       </c>
       <c r="AC37" s="24">
-        <f>AC36*'8_가정'!$E$107</f>
+        <f>AC36*'8_가정'!$E$108</f>
         <v>192000</v>
       </c>
       <c r="AD37" s="24">
-        <f>AD36*'8_가정'!$F$107</f>
+        <f>AD36*'8_가정'!$F$108</f>
         <v>384000</v>
       </c>
       <c r="AE37" s="24">
-        <f>AE36*'8_가정'!$G$107</f>
+        <f>AE36*'8_가정'!$G$108</f>
         <v>528000</v>
       </c>
     </row>
@@ -33764,23 +33779,23 @@
       </c>
       <c r="O40" s="48">
         <f>'2_손익계산서'!O50</f>
-        <v>-62682.1427344632</v>
+        <v>-284917.342734463</v>
       </c>
       <c r="AB40" s="48">
         <f>'2_손익계산서'!AB50</f>
-        <v>624193.944</v>
+        <v>289535.378</v>
       </c>
       <c r="AC40" s="24">
         <f>'2_손익계산서'!AC50</f>
-        <v>2925930.16290429</v>
+        <v>1757662.69398429</v>
       </c>
       <c r="AD40" s="24">
         <f>'2_손익계산서'!AD50</f>
-        <v>7546515.51401019</v>
+        <v>5113430.45583219</v>
       </c>
       <c r="AE40" s="24">
         <f>'2_손익계산서'!AE50</f>
-        <v>20883992.5449323</v>
+        <v>15938869.7971292</v>
       </c>
     </row>
     <row r="41">
@@ -33790,20 +33805,20 @@
         </is>
       </c>
       <c r="O41" s="48">
-        <f>'8_가정'!$C$109</f>
+        <f>'8_가정'!$C$110</f>
         <v>3032082</v>
       </c>
       <c r="AB41" s="44">
         <f>O44</f>
-        <v>3094764.14273446</v>
+        <v>3316999.34273446</v>
       </c>
       <c r="AC41" s="45">
         <f>AB44</f>
-        <v>2470570.19873446</v>
+        <v>3027463.96473446</v>
       </c>
       <c r="AD41" s="45">
         <f>AC44</f>
-        <v>0</v>
+        <v>1269801.27075018</v>
       </c>
       <c r="AE41" s="45">
         <f>AD44</f>
@@ -33817,23 +33832,23 @@
         </is>
       </c>
       <c r="O42" s="48">
-        <f>MIN(O41,MAX(0,O40)*'8_가정'!$C$110)</f>
+        <f>MIN(O41,MAX(0,O40)*'8_가정'!$C$111)</f>
         <v>0</v>
       </c>
       <c r="AB42" s="48">
-        <f>MIN(AB41,MAX(0,AB40)*'8_가정'!$C$110)</f>
-        <v>624193.944</v>
+        <f>MIN(AB41,MAX(0,AB40)*'8_가정'!$C$111)</f>
+        <v>289535.378</v>
       </c>
       <c r="AC42" s="24">
-        <f>MIN(AC41,MAX(0,AC40)*'8_가정'!$C$110)</f>
-        <v>2470570.19873446</v>
+        <f>MIN(AC41,MAX(0,AC40)*'8_가정'!$C$111)</f>
+        <v>1757662.69398429</v>
       </c>
       <c r="AD42" s="24">
-        <f>MIN(AD41,MAX(0,AD40)*'8_가정'!$C$110)</f>
-        <v>0</v>
+        <f>MIN(AD41,MAX(0,AD40)*'8_가정'!$C$111)</f>
+        <v>1269801.27075018</v>
       </c>
       <c r="AE42" s="24">
-        <f>MIN(AE41,MAX(0,AE40)*'8_가정'!$C$110)</f>
+        <f>MIN(AE41,MAX(0,AE40)*'8_가정'!$C$111)</f>
         <v>0</v>
       </c>
     </row>
@@ -33845,7 +33860,7 @@
       </c>
       <c r="O43" s="44">
         <f>MAX(0,-O40)</f>
-        <v>62682.1427344632</v>
+        <v>284917.342734463</v>
       </c>
       <c r="AB43" s="44">
         <f>MAX(0,-AB40)</f>
@@ -33872,15 +33887,15 @@
       </c>
       <c r="O44" s="44">
         <f>O41-O42+O43</f>
-        <v>3094764.14273446</v>
+        <v>3316999.34273446</v>
       </c>
       <c r="AB44" s="44">
         <f>AB41-AB42+AB43</f>
-        <v>2470570.19873446</v>
+        <v>3027463.96473446</v>
       </c>
       <c r="AC44" s="45">
         <f>AC41-AC42+AC43</f>
-        <v>0</v>
+        <v>1269801.27075018</v>
       </c>
       <c r="AD44" s="45">
         <f>AD41-AD42+AD43</f>
@@ -33907,15 +33922,15 @@
       </c>
       <c r="AC45" s="45">
         <f>MAX(0,AC40)-AC42</f>
-        <v>455359.964169821</v>
+        <v>0</v>
       </c>
       <c r="AD45" s="45">
         <f>MAX(0,AD40)-AD42</f>
-        <v>7546515.51401019</v>
+        <v>3843629.18508201</v>
       </c>
       <c r="AE45" s="45">
         <f>MAX(0,AE40)-AE42</f>
-        <v>20883992.5449323</v>
+        <v>15938869.7971292</v>
       </c>
     </row>
     <row r="46">
@@ -33925,24 +33940,24 @@
         </is>
       </c>
       <c r="O46" s="48">
-        <f>MIN(O45,'8_가정'!$C$111)*'8_가정'!$C$112+MAX(0,MIN(O45,'8_가정'!$D$111)-'8_가정'!$C$111)*'8_가정'!$D$112+MAX(0,MIN(O45,'8_가정'!$E$111)-'8_가정'!$D$111)*'8_가정'!$E$112+MAX(0,O45-'8_가정'!$E$111)*'8_가정'!$F$112</f>
+        <f>MIN(O45,'8_가정'!$C$112)*'8_가정'!$C$113+MAX(0,MIN(O45,'8_가정'!$D$112)-'8_가정'!$C$112)*'8_가정'!$D$113+MAX(0,MIN(O45,'8_가정'!$E$112)-'8_가정'!$D$112)*'8_가정'!$E$113+MAX(0,O45-'8_가정'!$E$112)*'8_가정'!$F$113</f>
         <v>0</v>
       </c>
       <c r="AB46" s="48">
-        <f>MIN(AB45,'8_가정'!$C$111)*'8_가정'!$C$112+MAX(0,MIN(AB45,'8_가정'!$D$111)-'8_가정'!$C$111)*'8_가정'!$D$112+MAX(0,MIN(AB45,'8_가정'!$E$111)-'8_가정'!$D$111)*'8_가정'!$E$112+MAX(0,AB45-'8_가정'!$E$111)*'8_가정'!$F$112</f>
+        <f>MIN(AB45,'8_가정'!$C$112)*'8_가정'!$C$113+MAX(0,MIN(AB45,'8_가정'!$D$112)-'8_가정'!$C$112)*'8_가정'!$D$113+MAX(0,MIN(AB45,'8_가정'!$E$112)-'8_가정'!$D$112)*'8_가정'!$E$113+MAX(0,AB45-'8_가정'!$E$112)*'8_가정'!$F$113</f>
         <v>0</v>
       </c>
       <c r="AC46" s="24">
-        <f>MIN(AC45,'8_가정'!$C$111)*'8_가정'!$C$112+MAX(0,MIN(AC45,'8_가정'!$D$111)-'8_가정'!$C$111)*'8_가정'!$D$112+MAX(0,MIN(AC45,'8_가정'!$E$111)-'8_가정'!$D$111)*'8_가정'!$E$112+MAX(0,AC45-'8_가정'!$E$111)*'8_가정'!$F$112</f>
-        <v>71071.9928339643</v>
+        <f>MIN(AC45,'8_가정'!$C$112)*'8_가정'!$C$113+MAX(0,MIN(AC45,'8_가정'!$D$112)-'8_가정'!$C$112)*'8_가정'!$D$113+MAX(0,MIN(AC45,'8_가정'!$E$112)-'8_가정'!$D$112)*'8_가정'!$E$113+MAX(0,AC45-'8_가정'!$E$112)*'8_가정'!$F$113</f>
+        <v>0</v>
       </c>
       <c r="AD46" s="24">
-        <f>MIN(AD45,'8_가정'!$C$111)*'8_가정'!$C$112+MAX(0,MIN(AD45,'8_가정'!$D$111)-'8_가정'!$C$111)*'8_가정'!$D$112+MAX(0,MIN(AD45,'8_가정'!$E$111)-'8_가정'!$D$111)*'8_가정'!$E$112+MAX(0,AD45-'8_가정'!$E$111)*'8_가정'!$F$112</f>
-        <v>1489303.10280204</v>
+        <f>MIN(AD45,'8_가정'!$C$112)*'8_가정'!$C$113+MAX(0,MIN(AD45,'8_가정'!$D$112)-'8_가정'!$C$112)*'8_가정'!$D$113+MAX(0,MIN(AD45,'8_가정'!$E$112)-'8_가정'!$D$112)*'8_가정'!$E$113+MAX(0,AD45-'8_가정'!$E$112)*'8_가정'!$F$113</f>
+        <v>748725.837016403</v>
       </c>
       <c r="AE46" s="24">
-        <f>MIN(AE45,'8_가정'!$C$111)*'8_가정'!$C$112+MAX(0,MIN(AE45,'8_가정'!$D$111)-'8_가정'!$C$111)*'8_가정'!$D$112+MAX(0,MIN(AE45,'8_가정'!$E$111)-'8_가정'!$D$111)*'8_가정'!$E$112+MAX(0,AE45-'8_가정'!$E$111)*'8_가정'!$F$112</f>
-        <v>4174478.35988511</v>
+        <f>MIN(AE45,'8_가정'!$C$112)*'8_가정'!$C$113+MAX(0,MIN(AE45,'8_가정'!$D$112)-'8_가정'!$C$112)*'8_가정'!$D$113+MAX(0,MIN(AE45,'8_가정'!$E$112)-'8_가정'!$D$112)*'8_가정'!$E$113+MAX(0,AE45-'8_가정'!$E$112)*'8_가정'!$F$113</f>
+        <v>3167773.95942583</v>
       </c>
     </row>
     <row r="47">
@@ -33952,24 +33967,24 @@
         </is>
       </c>
       <c r="O47" s="48">
-        <f>O46*'8_가정'!$C$113</f>
+        <f>O46*'8_가정'!$C$114</f>
         <v>0</v>
       </c>
       <c r="AB47" s="48">
-        <f>AB46*'8_가정'!$C$113</f>
+        <f>AB46*'8_가정'!$C$114</f>
         <v>0</v>
       </c>
       <c r="AC47" s="24">
-        <f>AC46*'8_가정'!$C$113</f>
-        <v>7107.19928339643</v>
+        <f>AC46*'8_가정'!$C$114</f>
+        <v>0</v>
       </c>
       <c r="AD47" s="24">
-        <f>AD46*'8_가정'!$C$113</f>
-        <v>148930.310280204</v>
+        <f>AD46*'8_가정'!$C$114</f>
+        <v>74872.5837016403</v>
       </c>
       <c r="AE47" s="24">
-        <f>AE46*'8_가정'!$C$113</f>
-        <v>417447.835988511</v>
+        <f>AE46*'8_가정'!$C$114</f>
+        <v>316777.395942583</v>
       </c>
     </row>
     <row r="48">
@@ -33988,15 +34003,15 @@
       </c>
       <c r="AC48" s="34">
         <f>AC46+AC47</f>
-        <v>78179.1921173607</v>
+        <v>0</v>
       </c>
       <c r="AD48" s="34">
         <f>AD46+AD47</f>
-        <v>1638233.41308224</v>
+        <v>823598.420718043</v>
       </c>
       <c r="AE48" s="34">
         <f>AE46+AE47</f>
-        <v>4591926.19587363</v>
+        <v>3484551.35536842</v>
       </c>
     </row>
     <row r="49">
@@ -34111,19 +34126,19 @@
       </c>
       <c r="AC49" s="45">
         <f>AC48</f>
-        <v>78179.1921173607</v>
+        <v>0</v>
       </c>
       <c r="AD49" s="45">
         <f>AD48</f>
-        <v>1638233.41308224</v>
+        <v>823598.420718043</v>
       </c>
       <c r="AE49" s="45">
         <f>AE48</f>
-        <v>4591926.19587363</v>
+        <v>3484551.35536842</v>
       </c>
       <c r="AF49" s="25">
         <f>O49+AB49+AC49+AD49+AE49</f>
-        <v>6308338.80107323</v>
+        <v>4308149.77608646</v>
       </c>
     </row>
     <row r="51">
@@ -34140,23 +34155,23 @@
         </is>
       </c>
       <c r="O53" s="48">
-        <f>O8*'8_가정'!$C$114/365</f>
+        <f>O8*'8_가정'!$C$115/365</f>
         <v>197260.273972603</v>
       </c>
       <c r="AB53" s="48">
-        <f>AB8*'8_가정'!$C$114/365</f>
+        <f>AB8*'8_가정'!$C$115/365</f>
         <v>1644170.95890411</v>
       </c>
       <c r="AC53" s="24">
-        <f>AC8*'8_가정'!$C$114/365</f>
+        <f>AC8*'8_가정'!$C$115/365</f>
         <v>5424657.53424658</v>
       </c>
       <c r="AD53" s="24">
-        <f>AD8*'8_가정'!$C$114/365</f>
+        <f>AD8*'8_가정'!$C$115/365</f>
         <v>11506849.3150685</v>
       </c>
       <c r="AE53" s="24">
-        <f>AE8*'8_가정'!$C$114/365</f>
+        <f>AE8*'8_가정'!$C$115/365</f>
         <v>25643835.6164384</v>
       </c>
     </row>
@@ -34167,23 +34182,23 @@
         </is>
       </c>
       <c r="O54" s="48">
-        <f>'2_손익계산서'!O25*'8_가정'!$C$115/365</f>
+        <f>'2_손익계산서'!O25*'8_가정'!$C$116/365</f>
         <v>103626.922312515</v>
       </c>
       <c r="AB54" s="48">
-        <f>'2_손익계산서'!AB25*'8_가정'!$C$115/365</f>
+        <f>'2_손익계산서'!AB25*'8_가정'!$C$116/365</f>
         <v>991453.653041096</v>
       </c>
       <c r="AC54" s="24">
-        <f>'2_손익계산서'!AC25*'8_가정'!$C$115/365</f>
+        <f>'2_손익계산서'!AC25*'8_가정'!$C$116/365</f>
         <v>3275493.17870067</v>
       </c>
       <c r="AD54" s="24">
-        <f>'2_손익계산서'!AD25*'8_가정'!$C$115/365</f>
+        <f>'2_손익계산서'!AD25*'8_가정'!$C$116/365</f>
         <v>6916440.2442723</v>
       </c>
       <c r="AE54" s="24">
-        <f>'2_손익계산서'!AE25*'8_가정'!$C$115/365</f>
+        <f>'2_손익계산서'!AE25*'8_가정'!$C$116/365</f>
         <v>15170579.9104221</v>
       </c>
     </row>
@@ -34194,23 +34209,23 @@
         </is>
       </c>
       <c r="O55" s="48">
-        <f>'2_손익계산서'!O25*'8_가정'!$C$116/365</f>
+        <f>'2_손익계산서'!O25*'8_가정'!$C$117/365</f>
         <v>77720.1917343859</v>
       </c>
       <c r="AB55" s="48">
-        <f>'2_손익계산서'!AB25*'8_가정'!$C$116/365</f>
+        <f>'2_손익계산서'!AB25*'8_가정'!$C$117/365</f>
         <v>743590.239780822</v>
       </c>
       <c r="AC55" s="24">
-        <f>'2_손익계산서'!AC25*'8_가정'!$C$116/365</f>
+        <f>'2_손익계산서'!AC25*'8_가정'!$C$117/365</f>
         <v>2456619.8840255</v>
       </c>
       <c r="AD55" s="24">
-        <f>'2_손익계산서'!AD25*'8_가정'!$C$116/365</f>
+        <f>'2_손익계산서'!AD25*'8_가정'!$C$117/365</f>
         <v>5187330.18320422</v>
       </c>
       <c r="AE55" s="24">
-        <f>'2_손익계산서'!AE25*'8_가정'!$C$116/365</f>
+        <f>'2_손익계산서'!AE25*'8_가정'!$C$117/365</f>
         <v>11377934.9328166</v>
       </c>
     </row>
@@ -34248,7 +34263,7 @@
         </is>
       </c>
       <c r="O57" s="48">
-        <f>O56-('3_연간손익'!$C$7*'8_가정'!$C$114/365+'3_연간손익'!$C$9*('8_가정'!$C$115-'8_가정'!$C$116)/365)</f>
+        <f>O56-('3_연간손익'!$C$7*'8_가정'!$C$115/365+'3_연간손익'!$C$9*('8_가정'!$C$116-'8_가정'!$C$117)/365)</f>
         <v>66288.3716192245</v>
       </c>
       <c r="AB57" s="44">
@@ -34315,7 +34330,7 @@
     <outlinePr summaryBelow="1" summaryRight="1"/>
     <pageSetUpPr fitToPage="1"/>
   </sheetPr>
-  <dimension ref="A1:I128"/>
+  <dimension ref="A1:I129"/>
   <sheetFormatPr baseColWidth="8" defaultRowHeight="15"/>
   <cols>
     <col width="40" customWidth="1" min="1" max="1"/>
@@ -36466,637 +36481,651 @@
     <row r="91">
       <c r="A91" s="15" t="inlineStr">
         <is>
-          <t>1인당 월 급여(천원)</t>
+          <t>1인당 월 평균급여(천원)</t>
         </is>
       </c>
       <c r="B91" s="15" t="inlineStr">
         <is>
-          <t>급여만(퇴직·4대보험·복리 별도)</t>
+          <t>2026 = 급상여대장 2026-09 지급합계 평균, 2027~ = 전년 × (1+인상률)</t>
         </is>
       </c>
       <c r="C91" s="65" t="n">
-        <v>3600</v>
-      </c>
-      <c r="D91" s="65" t="n">
-        <v>4600</v>
-      </c>
-      <c r="E91" s="65" t="n">
-        <v>5000</v>
-      </c>
-      <c r="F91" s="65" t="n">
-        <v>5400</v>
-      </c>
-      <c r="G91" s="65" t="n">
-        <v>5700</v>
+        <v>5670</v>
+      </c>
+      <c r="D91" s="43">
+        <f>C91*(1+$C$92)</f>
+        <v>6066.9</v>
+      </c>
+      <c r="E91" s="43">
+        <f>D91*(1+$C$92)</f>
+        <v>6491.583</v>
+      </c>
+      <c r="F91" s="43">
+        <f>E91*(1+$C$92)</f>
+        <v>6945.99381</v>
+      </c>
+      <c r="G91" s="43">
+        <f>F91*(1+$C$92)</f>
+        <v>7432.2133767</v>
       </c>
       <c r="I91" s="86" t="inlineStr">
         <is>
-          <t>2025 판관비 4.27억/직원 6~7명 기준 환산 + 영업·해외·인허가 인력 영입(고연봉) 가정. 연 3~5% 상승 반영</t>
+          <t>급상여대장 2026-09: 7명, 지급합계 39,688,891원(대표 13,688,890원 포함, 대표 제외 평균 약 4,339천원). 연 상여 미포함, 공제 전 총액 기준</t>
         </is>
       </c>
     </row>
     <row r="92">
       <c r="A92" s="15" t="inlineStr">
         <is>
-          <t>퇴직급여·4대보험·복리후생 비율(급여 대비)</t>
-        </is>
-      </c>
-      <c r="C92" s="88" t="n">
-        <v>0.22</v>
+          <t>연간 급여 인상률(2027~)</t>
+        </is>
+      </c>
+      <c r="C92" s="91" t="n">
+        <v>0.07000000000000001</v>
       </c>
     </row>
     <row r="93">
       <c r="A93" s="15" t="inlineStr">
         <is>
-          <t>마케팅·광고선전비(매출 %)</t>
-        </is>
-      </c>
-      <c r="B93" s="15" t="inlineStr">
-        <is>
-          <t>전시회·해외 마케팅·샘플</t>
-        </is>
-      </c>
-      <c r="C93" s="91" t="n">
-        <v>0.015</v>
-      </c>
-      <c r="D93" s="91" t="n">
-        <v>0.025</v>
-      </c>
-      <c r="E93" s="91" t="n">
-        <v>0.028</v>
-      </c>
-      <c r="F93" s="91" t="n">
-        <v>0.026</v>
-      </c>
-      <c r="G93" s="91" t="n">
-        <v>0.03</v>
+          <t>퇴직급여·4대보험·복리후생 비율(급여 대비)</t>
+        </is>
+      </c>
+      <c r="C93" s="88" t="n">
+        <v>0.22</v>
       </c>
     </row>
     <row r="94">
       <c r="A94" s="15" t="inlineStr">
         <is>
-          <t>지급수수료(매출 %)</t>
+          <t>마케팅·광고선전비(매출 %)</t>
         </is>
       </c>
       <c r="B94" s="15" t="inlineStr">
         <is>
-          <t>총판 수수료·법무·회계·컨설팅·플랫폼</t>
+          <t>전시회·해외 마케팅·샘플</t>
         </is>
       </c>
       <c r="C94" s="91" t="n">
-        <v>0.012</v>
+        <v>0.015</v>
       </c>
       <c r="D94" s="91" t="n">
-        <v>0.02</v>
+        <v>0.025</v>
       </c>
       <c r="E94" s="91" t="n">
-        <v>0.022</v>
+        <v>0.028</v>
       </c>
       <c r="F94" s="91" t="n">
-        <v>0.022</v>
+        <v>0.026</v>
       </c>
       <c r="G94" s="91" t="n">
-        <v>0.022</v>
+        <v>0.03</v>
       </c>
     </row>
     <row r="95">
       <c r="A95" s="15" t="inlineStr">
         <is>
-          <t>판매물류·CS비(매출 %)</t>
+          <t>지급수수료(매출 %)</t>
         </is>
       </c>
       <c r="B95" s="15" t="inlineStr">
         <is>
-          <t>출고·설치·고객지원</t>
+          <t>총판 수수료·법무·회계·컨설팅·플랫폼</t>
         </is>
       </c>
       <c r="C95" s="91" t="n">
-        <v>0.025</v>
+        <v>0.012</v>
       </c>
       <c r="D95" s="91" t="n">
-        <v>0.035</v>
+        <v>0.02</v>
       </c>
       <c r="E95" s="91" t="n">
-        <v>0.035</v>
+        <v>0.022</v>
       </c>
       <c r="F95" s="91" t="n">
-        <v>0.032</v>
+        <v>0.022</v>
       </c>
       <c r="G95" s="91" t="n">
-        <v>0.035</v>
+        <v>0.022</v>
       </c>
     </row>
     <row r="96">
       <c r="A96" s="15" t="inlineStr">
         <is>
-          <t>연구개발비-경상(매출 %)</t>
+          <t>판매물류·CS비(매출 %)</t>
         </is>
       </c>
       <c r="B96" s="15" t="inlineStr">
         <is>
-          <t>인증(CE-MDR·FDA·KC·PMDA)·시험·외주</t>
+          <t>출고·설치·고객지원</t>
         </is>
       </c>
       <c r="C96" s="91" t="n">
-        <v>0.035</v>
+        <v>0.025</v>
       </c>
       <c r="D96" s="91" t="n">
         <v>0.035</v>
       </c>
       <c r="E96" s="91" t="n">
+        <v>0.035</v>
+      </c>
+      <c r="F96" s="91" t="n">
         <v>0.032</v>
       </c>
-      <c r="F96" s="91" t="n">
-        <v>0.029</v>
-      </c>
       <c r="G96" s="91" t="n">
-        <v>0.031</v>
-      </c>
-      <c r="I96" s="86" t="inlineStr">
-        <is>
-          <t>개발비 자본화(BS 개발비 19.8억)는 별도. 신규 자본화·상각 증가분은 미반영(보수적 가정은 상각에서 반영)</t>
-        </is>
+        <v>0.035</v>
       </c>
     </row>
     <row r="97">
       <c r="A97" s="15" t="inlineStr">
         <is>
-          <t>대손상각비(매출 %)</t>
-        </is>
-      </c>
-      <c r="B97" s="15" t="inlineStr"/>
+          <t>연구개발비-경상(매출 %)</t>
+        </is>
+      </c>
+      <c r="B97" s="15" t="inlineStr">
+        <is>
+          <t>인증(CE-MDR·FDA·KC·PMDA)·시험·외주</t>
+        </is>
+      </c>
       <c r="C97" s="91" t="n">
-        <v>0.004</v>
+        <v>0.035</v>
       </c>
       <c r="D97" s="91" t="n">
-        <v>0.005</v>
+        <v>0.035</v>
       </c>
       <c r="E97" s="91" t="n">
-        <v>0.005</v>
+        <v>0.032</v>
       </c>
       <c r="F97" s="91" t="n">
-        <v>0.005</v>
+        <v>0.029</v>
       </c>
       <c r="G97" s="91" t="n">
-        <v>0.005</v>
+        <v>0.031</v>
+      </c>
+      <c r="I97" s="86" t="inlineStr">
+        <is>
+          <t>개발비 자본화(BS 개발비 19.8억)는 별도. 신규 자본화·상각 증가분은 미반영(보수적 가정은 상각에서 반영)</t>
+        </is>
       </c>
     </row>
     <row r="98">
       <c r="A98" s="15" t="inlineStr">
         <is>
-          <t>기타 판관비(매출 %)</t>
-        </is>
-      </c>
-      <c r="B98" s="15" t="inlineStr">
-        <is>
-          <t>보험·세금과공과·소모품·복리 외</t>
-        </is>
-      </c>
+          <t>대손상각비(매출 %)</t>
+        </is>
+      </c>
+      <c r="B98" s="15" t="inlineStr"/>
       <c r="C98" s="91" t="n">
-        <v>0.025</v>
+        <v>0.004</v>
       </c>
       <c r="D98" s="91" t="n">
-        <v>0.03</v>
+        <v>0.005</v>
       </c>
       <c r="E98" s="91" t="n">
-        <v>0.026</v>
+        <v>0.005</v>
       </c>
       <c r="F98" s="91" t="n">
-        <v>0.022</v>
+        <v>0.005</v>
       </c>
       <c r="G98" s="91" t="n">
-        <v>0.024</v>
+        <v>0.005</v>
       </c>
     </row>
     <row r="99">
       <c r="A99" s="15" t="inlineStr">
         <is>
-          <t>임차·운영비(연, 천원)</t>
+          <t>기타 판관비(매출 %)</t>
         </is>
       </c>
       <c r="B99" s="15" t="inlineStr">
         <is>
-          <t>본사·해외 거점(일본·싱가포르·미국)</t>
-        </is>
-      </c>
-      <c r="C99" s="65" t="n">
-        <v>36000</v>
-      </c>
-      <c r="D99" s="65" t="n">
-        <v>144000</v>
-      </c>
-      <c r="E99" s="65" t="n">
-        <v>300000</v>
-      </c>
-      <c r="F99" s="65" t="n">
-        <v>600000</v>
-      </c>
-      <c r="G99" s="65" t="n">
-        <v>1000000</v>
+          <t>보험·세금과공과·소모품·복리 외</t>
+        </is>
+      </c>
+      <c r="C99" s="91" t="n">
+        <v>0.025</v>
+      </c>
+      <c r="D99" s="91" t="n">
+        <v>0.03</v>
+      </c>
+      <c r="E99" s="91" t="n">
+        <v>0.026</v>
+      </c>
+      <c r="F99" s="91" t="n">
+        <v>0.022</v>
+      </c>
+      <c r="G99" s="91" t="n">
+        <v>0.024</v>
       </c>
     </row>
     <row r="100">
       <c r="A100" s="15" t="inlineStr">
         <is>
-          <t>해외영업·출장비(연, 천원)</t>
-        </is>
-      </c>
-      <c r="B100" s="15" t="inlineStr"/>
+          <t>임차·운영비(연, 천원)</t>
+        </is>
+      </c>
+      <c r="B100" s="15" t="inlineStr">
+        <is>
+          <t>본사·해외 거점(일본·싱가포르·미국)</t>
+        </is>
+      </c>
       <c r="C100" s="65" t="n">
-        <v>60000</v>
+        <v>36000</v>
       </c>
       <c r="D100" s="65" t="n">
-        <v>180000</v>
+        <v>144000</v>
       </c>
       <c r="E100" s="65" t="n">
-        <v>400000</v>
+        <v>300000</v>
       </c>
       <c r="F100" s="65" t="n">
-        <v>800000</v>
+        <v>600000</v>
       </c>
       <c r="G100" s="65" t="n">
-        <v>1400000</v>
+        <v>1000000</v>
       </c>
     </row>
     <row r="101">
       <c r="A101" s="15" t="inlineStr">
         <is>
-          <t>감가상각비-유형(연, 천원)</t>
-        </is>
-      </c>
-      <c r="B101" s="15" t="inlineStr">
-        <is>
-          <t>설비·금형·사무기기</t>
-        </is>
-      </c>
+          <t>해외영업·출장비(연, 천원)</t>
+        </is>
+      </c>
+      <c r="B101" s="15" t="inlineStr"/>
       <c r="C101" s="65" t="n">
-        <v>18000</v>
+        <v>60000</v>
       </c>
       <c r="D101" s="65" t="n">
-        <v>40000</v>
+        <v>180000</v>
       </c>
       <c r="E101" s="65" t="n">
-        <v>90000</v>
+        <v>400000</v>
       </c>
       <c r="F101" s="65" t="n">
-        <v>180000</v>
+        <v>800000</v>
       </c>
       <c r="G101" s="65" t="n">
-        <v>300000</v>
+        <v>1400000</v>
       </c>
     </row>
     <row r="102">
       <c r="A102" s="15" t="inlineStr">
         <is>
+          <t>감가상각비-유형(연, 천원)</t>
+        </is>
+      </c>
+      <c r="B102" s="15" t="inlineStr">
+        <is>
+          <t>설비·금형·사무기기</t>
+        </is>
+      </c>
+      <c r="C102" s="65" t="n">
+        <v>18000</v>
+      </c>
+      <c r="D102" s="65" t="n">
+        <v>40000</v>
+      </c>
+      <c r="E102" s="65" t="n">
+        <v>90000</v>
+      </c>
+      <c r="F102" s="65" t="n">
+        <v>180000</v>
+      </c>
+      <c r="G102" s="65" t="n">
+        <v>300000</v>
+      </c>
+    </row>
+    <row r="103">
+      <c r="A103" s="15" t="inlineStr">
+        <is>
           <t>개발비 무형자산상각(연, 천원)</t>
         </is>
       </c>
-      <c r="B102" s="15" t="inlineStr">
+      <c r="B103" s="15" t="inlineStr">
         <is>
           <t>2025.12 개발비 잔액 19.8억을 5년 정액 상각, 2027-01 개시(신규 자본화는 미반영)</t>
         </is>
       </c>
-      <c r="C102" s="65" t="n">
-        <v>0</v>
-      </c>
-      <c r="D102" s="65" t="n">
+      <c r="C103" s="65" t="n">
+        <v>0</v>
+      </c>
+      <c r="D103" s="65" t="n">
         <v>395953</v>
       </c>
-      <c r="E102" s="65" t="n">
+      <c r="E103" s="65" t="n">
         <v>395953</v>
       </c>
-      <c r="F102" s="65" t="n">
+      <c r="F103" s="65" t="n">
         <v>395953</v>
       </c>
-      <c r="G102" s="65" t="n">
+      <c r="G103" s="65" t="n">
         <v>395953</v>
       </c>
-      <c r="I102" s="86" t="inlineStr">
+      <c r="I103" s="86" t="inlineStr">
         <is>
           <t>확인 필요: 2025 감사보고서상 상각 개시 시점·내용연수. 2025 판관비에 상각이 보이지 않아 상품화 시점(2027)부터 반영하는 보수적 가정</t>
         </is>
       </c>
     </row>
-    <row r="104">
-      <c r="A104" s="84" t="inlineStr">
+    <row r="105">
+      <c r="A105" s="84" t="inlineStr">
         <is>
           <t>6. 영업외손익 · 법인세</t>
         </is>
       </c>
-      <c r="B104" s="85" t="n"/>
-      <c r="C104" s="85" t="n"/>
-      <c r="D104" s="85" t="n"/>
-      <c r="E104" s="85" t="n"/>
-      <c r="F104" s="85" t="n"/>
-      <c r="G104" s="85" t="n"/>
-      <c r="H104" s="85" t="n"/>
-      <c r="I104" s="85" t="n"/>
-    </row>
-    <row r="105">
-      <c r="A105" s="22" t="inlineStr">
+      <c r="B105" s="85" t="n"/>
+      <c r="C105" s="85" t="n"/>
+      <c r="D105" s="85" t="n"/>
+      <c r="E105" s="85" t="n"/>
+      <c r="F105" s="85" t="n"/>
+      <c r="G105" s="85" t="n"/>
+      <c r="H105" s="85" t="n"/>
+      <c r="I105" s="85" t="n"/>
+    </row>
+    <row r="106">
+      <c r="A106" s="22" t="inlineStr">
         <is>
           <t>구분</t>
         </is>
       </c>
-      <c r="B105" s="22" t="inlineStr">
+      <c r="B106" s="22" t="inlineStr">
         <is>
           <t>설명</t>
         </is>
       </c>
-      <c r="C105" s="22" t="n">
+      <c r="C106" s="22" t="n">
         <v>2026</v>
       </c>
-      <c r="D105" s="22" t="n">
+      <c r="D106" s="22" t="n">
         <v>2027</v>
       </c>
-      <c r="E105" s="22" t="n">
+      <c r="E106" s="22" t="n">
         <v>2028</v>
       </c>
-      <c r="F105" s="22" t="n">
+      <c r="F106" s="22" t="n">
         <v>2029</v>
       </c>
-      <c r="G105" s="22" t="n">
+      <c r="G106" s="22" t="n">
         <v>2030</v>
       </c>
-      <c r="H105" s="22" t="inlineStr"/>
-      <c r="I105" s="22" t="inlineStr">
+      <c r="H106" s="22" t="inlineStr"/>
+      <c r="I106" s="22" t="inlineStr">
         <is>
           <t>근거 · 비고</t>
-        </is>
-      </c>
-    </row>
-    <row r="106">
-      <c r="A106" s="15" t="inlineStr">
-        <is>
-          <t>차입금 기초(2025.12, 천원)</t>
-        </is>
-      </c>
-      <c r="B106" s="15" t="inlineStr">
-        <is>
-          <t>단기 1,135,833 + 장기 63,710</t>
-        </is>
-      </c>
-      <c r="C106" s="55" t="n">
-        <v>1199543</v>
-      </c>
-      <c r="I106" s="86" t="inlineStr">
-        <is>
-          <t>투자사 양식 차입금 현황(2025감사보고서 주석 5). 현재 잔액·만기 확인 필요</t>
         </is>
       </c>
     </row>
     <row r="107">
       <c r="A107" s="15" t="inlineStr">
         <is>
-          <t>차입금 연 이자율</t>
+          <t>차입금 기초(2025.12, 천원)</t>
         </is>
       </c>
       <c r="B107" s="15" t="inlineStr">
         <is>
-          <t>2025 이자비용 0.50억/평균 차입금 ≈ 4.2% (우리 4.48~4.89%, 하나 5.00~5.58%)</t>
-        </is>
-      </c>
-      <c r="C107" s="91" t="n">
-        <v>0.048</v>
-      </c>
-      <c r="D107" s="91" t="n">
-        <v>0.048</v>
-      </c>
-      <c r="E107" s="91" t="n">
-        <v>0.048</v>
-      </c>
-      <c r="F107" s="91" t="n">
-        <v>0.048</v>
-      </c>
-      <c r="G107" s="91" t="n">
-        <v>0.048</v>
+          <t>단기 1,135,833 + 장기 63,710</t>
+        </is>
+      </c>
+      <c r="C107" s="55" t="n">
+        <v>1199543</v>
+      </c>
+      <c r="I107" s="86" t="inlineStr">
+        <is>
+          <t>투자사 양식 차입금 현황(2025감사보고서 주석 5). 현재 잔액·만기 확인 필요</t>
+        </is>
       </c>
     </row>
     <row r="108">
       <c r="A108" s="15" t="inlineStr">
         <is>
-          <t>정부보조금수익(천원)</t>
+          <t>차입금 연 이자율</t>
         </is>
       </c>
       <c r="B108" s="15" t="inlineStr">
         <is>
-          <t>2026: GDIN 지원금 3,500만원 포함</t>
-        </is>
-      </c>
-      <c r="C108" s="65" t="n">
-        <v>65000</v>
-      </c>
-      <c r="D108" s="65" t="n">
-        <v>40000</v>
-      </c>
-      <c r="E108" s="65" t="n">
-        <v>30000</v>
-      </c>
-      <c r="F108" s="65" t="n">
-        <v>0</v>
-      </c>
-      <c r="G108" s="65" t="n">
-        <v>0</v>
-      </c>
-      <c r="I108" s="86" t="inlineStr">
-        <is>
-          <t>2024 0.88억, 2025 0.31억 실적. 이후 보수적으로 체감, 2029~ 미반영</t>
-        </is>
+          <t>2025 이자비용 0.50억/평균 차입금 ≈ 4.2% (우리 4.48~4.89%, 하나 5.00~5.58%)</t>
+        </is>
+      </c>
+      <c r="C108" s="91" t="n">
+        <v>0.048</v>
+      </c>
+      <c r="D108" s="91" t="n">
+        <v>0.048</v>
+      </c>
+      <c r="E108" s="91" t="n">
+        <v>0.048</v>
+      </c>
+      <c r="F108" s="91" t="n">
+        <v>0.048</v>
+      </c>
+      <c r="G108" s="91" t="n">
+        <v>0.048</v>
       </c>
     </row>
     <row r="109">
       <c r="A109" s="15" t="inlineStr">
         <is>
-          <t>이월결손금 기초(천원)</t>
+          <t>정부보조금수익(천원)</t>
         </is>
       </c>
       <c r="B109" s="15" t="inlineStr">
         <is>
-          <t>자본총계 − 자본금 − 주식발행초과금 역산(2025.12)</t>
+          <t>2026: GDIN 지원금 3,500만원 포함</t>
         </is>
       </c>
       <c r="C109" s="65" t="n">
-        <v>3032082</v>
+        <v>65000</v>
+      </c>
+      <c r="D109" s="65" t="n">
+        <v>40000</v>
+      </c>
+      <c r="E109" s="65" t="n">
+        <v>30000</v>
+      </c>
+      <c r="F109" s="65" t="n">
+        <v>0</v>
+      </c>
+      <c r="G109" s="65" t="n">
+        <v>0</v>
       </c>
       <c r="I109" s="86" t="inlineStr">
         <is>
-          <t>계산: 12.375억 − 4.276억 − 38.420억 ≈ −30.3억. 세무상 결손금과 다를 수 있음(세무사 확인)</t>
+          <t>2024 0.88억, 2025 0.31억 실적. 이후 보수적으로 체감, 2029~ 미반영</t>
         </is>
       </c>
     </row>
     <row r="110">
       <c r="A110" s="15" t="inlineStr">
         <is>
-          <t>이월결손금 공제 한도(과세소득 대비)</t>
-        </is>
-      </c>
-      <c r="C110" s="88" t="n">
-        <v>1</v>
+          <t>이월결손금 기초(천원)</t>
+        </is>
+      </c>
+      <c r="B110" s="15" t="inlineStr">
+        <is>
+          <t>자본총계 − 자본금 − 주식발행초과금 역산(2025.12)</t>
+        </is>
+      </c>
+      <c r="C110" s="65" t="n">
+        <v>3032082</v>
       </c>
       <c r="I110" s="86" t="inlineStr">
         <is>
-          <t>중소기업 100% (일반법인 80%). 중소기업 졸업 시 한도 80% 적용 가능 — 보수적으로 보려면 80%로 변경</t>
+          <t>계산: 12.375억 − 4.276억 − 38.420억 ≈ −30.3억. 세무상 결손금과 다를 수 있음(세무사 확인)</t>
         </is>
       </c>
     </row>
     <row r="111">
       <c r="A111" s="15" t="inlineStr">
         <is>
-          <t>법인세율 구간(과세표준 상한, 천원)</t>
-        </is>
-      </c>
-      <c r="C111" s="55" t="n">
-        <v>200000</v>
-      </c>
-      <c r="D111" s="55" t="n">
-        <v>20000000</v>
-      </c>
-      <c r="E111" s="55" t="n">
-        <v>300000000</v>
+          <t>이월결손금 공제 한도(과세소득 대비)</t>
+        </is>
+      </c>
+      <c r="C111" s="88" t="n">
+        <v>1</v>
+      </c>
+      <c r="I111" s="86" t="inlineStr">
+        <is>
+          <t>중소기업 100% (일반법인 80%). 중소기업 졸업 시 한도 80% 적용 가능 — 보수적으로 보려면 80%로 변경</t>
+        </is>
       </c>
     </row>
     <row r="112">
       <c r="A112" s="15" t="inlineStr">
         <is>
-          <t>법인세율(구간별)</t>
-        </is>
-      </c>
-      <c r="C112" s="92" t="n">
-        <v>0.1</v>
-      </c>
-      <c r="D112" s="92" t="n">
-        <v>0.2</v>
-      </c>
-      <c r="E112" s="92" t="n">
-        <v>0.22</v>
-      </c>
-      <c r="F112" s="92" t="n">
-        <v>0.25</v>
-      </c>
-      <c r="I112" s="86" t="inlineStr">
-        <is>
-          <t>2026 귀속 10%/20%/22%/25% 가정(2025 세법개정 반영 여부 8_가정 하단 출처 메모 확인). 세액공제·최저한세 미반영</t>
-        </is>
+          <t>법인세율 구간(과세표준 상한, 천원)</t>
+        </is>
+      </c>
+      <c r="C112" s="55" t="n">
+        <v>200000</v>
+      </c>
+      <c r="D112" s="55" t="n">
+        <v>20000000</v>
+      </c>
+      <c r="E112" s="55" t="n">
+        <v>300000000</v>
       </c>
     </row>
     <row r="113">
       <c r="A113" s="15" t="inlineStr">
         <is>
-          <t>지방소득세율(법인세 대비)</t>
-        </is>
-      </c>
-      <c r="C113" s="67" t="n">
+          <t>법인세율(구간별)</t>
+        </is>
+      </c>
+      <c r="C113" s="92" t="n">
         <v>0.1</v>
+      </c>
+      <c r="D113" s="92" t="n">
+        <v>0.2</v>
+      </c>
+      <c r="E113" s="92" t="n">
+        <v>0.22</v>
+      </c>
+      <c r="F113" s="92" t="n">
+        <v>0.25</v>
+      </c>
+      <c r="I113" s="86" t="inlineStr">
+        <is>
+          <t>2026 귀속 10%/20%/22%/25% 가정(2025 세법개정 반영 여부 8_가정 하단 출처 메모 확인). 세액공제·최저한세 미반영</t>
+        </is>
       </c>
     </row>
     <row r="114">
       <c r="A114" s="15" t="inlineStr">
         <is>
-          <t>매출채권 회전일수(참고)</t>
-        </is>
-      </c>
-      <c r="C114" s="89" t="n">
-        <v>60</v>
-      </c>
-      <c r="I114" s="86" t="inlineStr">
-        <is>
-          <t>손익계산서 범위 밖의 참고 지표(운전자본 소요 추정)용. 2025 BS: 매출채권 2,304만원·선급금 8,557만원. 총판 공급 비중이 커지면 회전일수가 길어질 수 있음</t>
-        </is>
+          <t>지방소득세율(법인세 대비)</t>
+        </is>
+      </c>
+      <c r="C114" s="67" t="n">
+        <v>0.1</v>
       </c>
     </row>
     <row r="115">
       <c r="A115" s="15" t="inlineStr">
         <is>
-          <t>재고자산 회전일수(매출원가 기준, 참고)</t>
+          <t>매출채권 회전일수(참고)</t>
         </is>
       </c>
       <c r="C115" s="89" t="n">
         <v>60</v>
       </c>
+      <c r="I115" s="86" t="inlineStr">
+        <is>
+          <t>손익계산서 범위 밖의 참고 지표(운전자본 소요 추정)용. 2025 BS: 매출채권 2,304만원·선급금 8,557만원. 총판 공급 비중이 커지면 회전일수가 길어질 수 있음</t>
+        </is>
+      </c>
     </row>
     <row r="116">
       <c r="A116" s="15" t="inlineStr">
         <is>
+          <t>재고자산 회전일수(매출원가 기준, 참고)</t>
+        </is>
+      </c>
+      <c r="C116" s="89" t="n">
+        <v>60</v>
+      </c>
+    </row>
+    <row r="117">
+      <c r="A117" s="15" t="inlineStr">
+        <is>
           <t>매입채무 회전일수(매출원가 기준, 참고)</t>
         </is>
       </c>
-      <c r="C116" s="89" t="n">
+      <c r="C117" s="89" t="n">
         <v>45</v>
       </c>
     </row>
-    <row r="118">
-      <c r="A118" s="84" t="inlineStr">
+    <row r="119">
+      <c r="A119" s="84" t="inlineStr">
         <is>
           <t>7. 근거 구분 범례 · 출처 메모</t>
         </is>
       </c>
-      <c r="B118" s="85" t="n"/>
-      <c r="C118" s="85" t="n"/>
-      <c r="D118" s="85" t="n"/>
-      <c r="E118" s="85" t="n"/>
-      <c r="F118" s="85" t="n"/>
-      <c r="G118" s="85" t="n"/>
-      <c r="H118" s="85" t="n"/>
-      <c r="I118" s="85" t="n"/>
-    </row>
-    <row r="119">
-      <c r="A119" s="15" t="inlineStr">
-        <is>
-          <t>IR 근거 = IR 자료(2026-09-27판) 페이지 표기. 계약/등록/입찰/PoC 단계는 IR 표기에 입찰 자료(저장소)·회사연혁을 교차 반영.</t>
-        </is>
-      </c>
+      <c r="B119" s="85" t="n"/>
+      <c r="C119" s="85" t="n"/>
+      <c r="D119" s="85" t="n"/>
+      <c r="E119" s="85" t="n"/>
+      <c r="F119" s="85" t="n"/>
+      <c r="G119" s="85" t="n"/>
+      <c r="H119" s="85" t="n"/>
+      <c r="I119" s="85" t="n"/>
     </row>
     <row r="120">
       <c r="A120" s="15" t="inlineStr">
         <is>
-          <t>가정 = IR에 없는 시작월·램프·성장률·비용률. 모두 파란색 입력이며 투자사 질의 시 근거 설명이 필요한 항목.</t>
+          <t>IR 근거 = IR 자료(2026-09-27판) 페이지 표기. 계약/등록/입찰/PoC 단계는 IR 표기에 입찰 자료(저장소)·회사연혁을 교차 반영.</t>
         </is>
       </c>
     </row>
     <row r="121">
       <c r="A121" s="15" t="inlineStr">
         <is>
+          <t>가정 = IR에 없는 시작월·램프·성장률·비용률. 모두 파란색 입력이며 투자사 질의 시 근거 설명이 필요한 항목.</t>
+        </is>
+      </c>
+    </row>
+    <row r="122">
+      <c r="A122" s="15" t="inlineStr">
+        <is>
           <t>회사실적 = 투자사 양식 IS(2025 감사보고서 기준: 2024·2025). 2026 상반기 실적은 자료 없음 → 추정.</t>
         </is>
       </c>
     </row>
-    <row r="123">
-      <c r="A123" s="9" t="inlineStr">
+    <row r="124">
+      <c r="A124" s="9" t="inlineStr">
         <is>
           <t>외부 팩트 조사 요약(출처 URL 포함)</t>
-        </is>
-      </c>
-    </row>
-    <row r="124">
-      <c r="A124" s="69" t="inlineStr">
-        <is>
-          <t>환율: 2026-10-02 서울 종가 USD/KRW 1,350.60 · JPY 856.76/100엔 · EUR 1,520.64 (서울신문 2026/10/02, snmnews). 본 계획은 IR 고정환율 1,400원/달러 기준이며 SGD·JPY·EUR은 1,400 기준 교차환율을 사용(현물환 대비 USD 약 +3.7%).</t>
         </is>
       </c>
     </row>
     <row r="125">
       <c r="A125" s="69" t="inlineStr">
         <is>
-          <t>법인세: 2026 귀속 10/20/22/25%(+1%p, 2025-12-02 국회 통과·12-23 공포), 지방소득세 1.0/2.0/2.2/2.5%(국세청 nts.go.kr, 국회예산정책처 nabo.go.kr). 결손금 15년 이월, 중소기업은 소득의 100%까지 공제, 중소기업 졸업 유예 5년, 최저한세(중소) 7%.</t>
+          <t>환율: 2026-10-02 서울 종가 USD/KRW 1,350.60 · JPY 856.76/100엔 · EUR 1,520.64 (서울신문 2026/10/02, snmnews). 본 계획은 IR 고정환율 1,400원/달러 기준이며 SGD·JPY·EUR은 1,400 기준 교차환율을 사용(현물환 대비 USD 약 +3.7%).</t>
         </is>
       </c>
     </row>
     <row r="126">
       <c r="A126" s="69" t="inlineStr">
         <is>
-          <t>일본: 介護テクノロジー導入支援事業(2025년 통합) 보조율 3/4~4/5, 배설예측·검지 기기 1대당 상한 30만엔, TAIS 介護テクノロジー 선정이 보조금 신청 조건(techno-aids.or.jp). TAIS 등록 자체는 보험급여가 아님 → IR의 "TAIS 등록 완료"가 보조금 대상 선정을 뜻하는지 확인 필요. 시설 수(MHLW 2024): 특양 8,621 · 老健 4,214 · GH 14,341 · 유료노인홈 16,543.</t>
+          <t>법인세: 2026 귀속 10/20/22/25%(+1%p, 2025-12-02 국회 통과·12-23 공포), 지방소득세 1.0/2.0/2.2/2.5%(국세청 nts.go.kr, 국회예산정책처 nabo.go.kr). 결손금 15년 이월, 중소기업은 소득의 100%까지 공제, 중소기업 졸업 유예 5년, 최저한세(중소) 7%.</t>
         </is>
       </c>
     </row>
     <row r="127">
       <c r="A127" s="69" t="inlineStr">
         <is>
-          <t>한국: 기저귀센서는 2025-05 정규 복지용구 급여 편입(고시상 1개 제품), 재가 본인부담 15%(85% 지원)·연 한도 160만원, 성인용 기저귀 자체는 급여 품목이 아님(nhis.or.kr). 장기요양기관 29,734곳(시설 6,361·재가 23,373, 2025), 요양병원 약 1,300곳(감소 추세), 요양병원 간병비 건보 적용 2027~(보도).</t>
+          <t>일본: 介護テクノロジー導入支援事業(2025년 통합) 보조율 3/4~4/5, 배설예측·검지 기기 1대당 상한 30만엔, TAIS 介護テクノロジー 선정이 보조금 신청 조건(techno-aids.or.jp). TAIS 등록 자체는 보험급여가 아님 → IR의 "TAIS 등록 완료"가 보조금 대상 선정을 뜻하는지 확인 필요. 시설 수(MHLW 2024): 특양 8,621 · 老健 4,214 · GH 14,341 · 유료노인홈 16,543.</t>
         </is>
       </c>
     </row>
     <row r="128">
       <c r="A128" s="69" t="inlineStr">
+        <is>
+          <t>한국: 기저귀센서는 2025-05 정규 복지용구 급여 편입(고시상 1개 제품), 재가 본인부담 15%(85% 지원)·연 한도 160만원, 성인용 기저귀 자체는 급여 품목이 아님(nhis.or.kr). 장기요양기관 29,734곳(시설 6,361·재가 23,373, 2025), 요양병원 약 1,300곳(감소 추세), 요양병원 간병비 건보 적용 2027~(보도).</t>
+        </is>
+      </c>
+    </row>
+    <row r="129">
+      <c r="A129" s="69" t="inlineStr">
         <is>
           <t>동종 벤치마크: Essity FY2025 EBITA 마진 14.1%, Ontex FY2025 조정 EBITDA 마진 10.0% → 본 계획 S1의 2030 영업이익률은 약 14% 이내로 설정(상한 근거). 일부 공식 사이트 접근 제한으로 보도·2차 자료를 포함하므로 제출 전 재확인 권장.</t>
         </is>
@@ -37105,6 +37134,7 @@
   </sheetData>
   <pageMargins left="0.75" right="0.75" top="1" bottom="1" header="0.5" footer="0.5"/>
   <pageSetup orientation="landscape" fitToHeight="0" fitToWidth="1"/>
+  <legacyDrawing xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" r:id="anysvml"/>
 </worksheet>
 </file>
 
@@ -37234,19 +37264,19 @@
         </is>
       </c>
       <c r="C8" s="93" t="n">
-        <v>-0.700931107344632</v>
+        <v>-2.92328310734463</v>
       </c>
       <c r="D8" s="93" t="n">
-        <v>6.60993944</v>
+        <v>3.26335378</v>
       </c>
       <c r="E8" s="93" t="n">
-        <v>30.8793016290429</v>
+        <v>19.1966269398429</v>
       </c>
       <c r="F8" s="93" t="n">
-        <v>79.3051551401019</v>
+        <v>54.9743045583219</v>
       </c>
       <c r="G8" s="93" t="n">
-        <v>214.119925449323</v>
+        <v>164.668697971292</v>
       </c>
     </row>
     <row r="9">
@@ -37256,19 +37286,19 @@
         </is>
       </c>
       <c r="C9" s="94" t="n">
-        <v>-0.0584109256120527</v>
+        <v>-0.243606925612053</v>
       </c>
       <c r="D9" s="94" t="n">
-        <v>0.0660859128737737</v>
+        <v>0.0326268819160891</v>
       </c>
       <c r="E9" s="94" t="n">
-        <v>0.09357364130012991</v>
+        <v>0.0581715967874026</v>
       </c>
       <c r="F9" s="94" t="n">
-        <v>0.113293078771574</v>
+        <v>0.07853472079760269</v>
       </c>
       <c r="G9" s="94" t="n">
-        <v>0.137256362467515</v>
+        <v>0.105556857673905</v>
       </c>
     </row>
     <row r="10">
@@ -37278,19 +37308,19 @@
         </is>
       </c>
       <c r="C10" s="93" t="n">
-        <v>-0.626821427344632</v>
+        <v>-2.84917342734463</v>
       </c>
       <c r="D10" s="93" t="n">
-        <v>6.24193944</v>
+        <v>2.89535378</v>
       </c>
       <c r="E10" s="93" t="n">
-        <v>28.4775097078692</v>
+        <v>17.5766269398429</v>
       </c>
       <c r="F10" s="93" t="n">
-        <v>59.0828210092795</v>
+        <v>42.89832035114149</v>
       </c>
       <c r="G10" s="93" t="n">
-        <v>162.920663490587</v>
+        <v>124.543184417608</v>
       </c>
     </row>
     <row r="11">
@@ -37429,19 +37459,19 @@
         </is>
       </c>
       <c r="C19" s="93" t="n">
-        <v>-0.941584226437879</v>
+        <v>-2.87804937460938</v>
       </c>
       <c r="D19" s="93" t="n">
-        <v>-1.23988889758329</v>
+        <v>-3.41834516606513</v>
       </c>
       <c r="E19" s="93" t="n">
-        <v>9.38711946871755</v>
+        <v>1.41687759891742</v>
       </c>
       <c r="F19" s="93" t="n">
-        <v>13.2187182532477</v>
+        <v>-2.35437829103144</v>
       </c>
       <c r="G19" s="93" t="n">
-        <v>33.1598912347684</v>
+        <v>5.45283719214369</v>
       </c>
     </row>
     <row r="20">
@@ -37451,19 +37481,19 @@
         </is>
       </c>
       <c r="C20" s="94" t="n">
-        <v>-0.0947102531696752</v>
+        <v>-0.28949166442102</v>
       </c>
       <c r="D20" s="94" t="n">
-        <v>-0.0231881668445863</v>
+        <v>-0.0639292425293924</v>
       </c>
       <c r="E20" s="94" t="n">
-        <v>0.0484516053306718</v>
+        <v>0.00731321194466437</v>
       </c>
       <c r="F20" s="94" t="n">
-        <v>0.0396511064880436</v>
+        <v>-0.00706223572833091</v>
       </c>
       <c r="G20" s="94" t="n">
-        <v>0.0555785993348734</v>
+        <v>0.00913938623606486</v>
       </c>
     </row>
     <row r="21">
@@ -37473,19 +37503,19 @@
         </is>
       </c>
       <c r="C21" s="93" t="n">
-        <v>-0.867474546437879</v>
+        <v>-2.80393969460938</v>
       </c>
       <c r="D21" s="93" t="n">
-        <v>-1.60788889758329</v>
+        <v>-3.78634516606513</v>
       </c>
       <c r="E21" s="93" t="n">
-        <v>7.767119468717549</v>
+        <v>-0.203122401082581</v>
       </c>
       <c r="F21" s="93" t="n">
-        <v>9.37871825324768</v>
+        <v>-6.19437829103144</v>
       </c>
       <c r="G21" s="93" t="n">
-        <v>25.4093912219717</v>
+        <v>0.172837192143686</v>
       </c>
     </row>
     <row r="22">
@@ -37624,19 +37654,19 @@
         </is>
       </c>
       <c r="C30" s="93" t="n">
-        <v>-1.14827581351714</v>
+        <v>-2.83252934185578</v>
       </c>
       <c r="D30" s="93" t="n">
-        <v>-4.92136228848975</v>
+        <v>-6.5526427335011</v>
       </c>
       <c r="E30" s="93" t="n">
-        <v>-2.05908565359656</v>
+        <v>-8.12172093501316</v>
       </c>
       <c r="F30" s="93" t="n">
-        <v>-15.344760076104</v>
+        <v>-26.7672034641743</v>
       </c>
       <c r="G30" s="93" t="n">
-        <v>-31.4595648089956</v>
+        <v>-50.6570296309993</v>
       </c>
     </row>
     <row r="31">
@@ -37646,19 +37676,19 @@
         </is>
       </c>
       <c r="C31" s="94" t="n">
-        <v>-0.141310301117158</v>
+        <v>-0.348579643940094</v>
       </c>
       <c r="D31" s="94" t="n">
-        <v>-0.155414952304088</v>
+        <v>-0.206930235612734</v>
       </c>
       <c r="E31" s="94" t="n">
-        <v>-0.0168886153645679</v>
+        <v>-0.0666143347316385</v>
       </c>
       <c r="F31" s="94" t="n">
-        <v>-0.0904426832317751</v>
+        <v>-0.157767061322828</v>
       </c>
       <c r="G31" s="94" t="n">
-        <v>-0.129910919341742</v>
+        <v>-0.209186024359855</v>
       </c>
     </row>
     <row r="32">
@@ -37668,19 +37698,19 @@
         </is>
       </c>
       <c r="C32" s="93" t="n">
-        <v>-1.07416613351714</v>
+        <v>-2.75841966185578</v>
       </c>
       <c r="D32" s="93" t="n">
-        <v>-5.28936228848975</v>
+        <v>-6.920642733501101</v>
       </c>
       <c r="E32" s="93" t="n">
-        <v>-3.67908565359656</v>
+        <v>-9.741720935013161</v>
       </c>
       <c r="F32" s="93" t="n">
-        <v>-19.184760076104</v>
+        <v>-30.6072034641743</v>
       </c>
       <c r="G32" s="93" t="n">
-        <v>-36.7395648089956</v>
+        <v>-55.93702963099931</v>
       </c>
     </row>
     <row r="33">
@@ -37833,23 +37863,23 @@
       </c>
       <c r="C41" s="17">
         <f>'3_연간손익'!D13/100000</f>
-        <v>-0.700931107344632</v>
+        <v>-2.92328310734463</v>
       </c>
       <c r="D41" s="17">
         <f>'3_연간손익'!E13/100000</f>
-        <v>6.60993944</v>
+        <v>3.26335378</v>
       </c>
       <c r="E41" s="17">
         <f>'3_연간손익'!F13/100000</f>
-        <v>30.8793016290429</v>
+        <v>19.1966269398429</v>
       </c>
       <c r="F41" s="17">
         <f>'3_연간손익'!G13/100000</f>
-        <v>79.3051551401019</v>
+        <v>54.9743045583219</v>
       </c>
       <c r="G41" s="17">
         <f>'3_연간손익'!H13/100000</f>
-        <v>214.119925449323</v>
+        <v>164.668697971292</v>
       </c>
     </row>
     <row r="42">
@@ -37864,23 +37894,23 @@
       </c>
       <c r="C42" s="16">
         <f>'3_연간손익'!D14</f>
-        <v>-0.0584109256120527</v>
+        <v>-0.243606925612053</v>
       </c>
       <c r="D42" s="16">
         <f>'3_연간손익'!E14</f>
-        <v>0.0660859128737737</v>
+        <v>0.0326268819160891</v>
       </c>
       <c r="E42" s="16">
         <f>'3_연간손익'!F14</f>
-        <v>0.0935736413001299</v>
+        <v>0.0581715967874026</v>
       </c>
       <c r="F42" s="16">
         <f>'3_연간손익'!G14</f>
-        <v>0.113293078771574</v>
+        <v>0.0785347207976027</v>
       </c>
       <c r="G42" s="16">
         <f>'3_연간손익'!H14</f>
-        <v>0.137256362467515</v>
+        <v>0.105556857673905</v>
       </c>
     </row>
     <row r="43">
@@ -37895,23 +37925,23 @@
       </c>
       <c r="C43" s="17">
         <f>'3_연간손익'!D21/100000</f>
-        <v>-0.626821427344632</v>
+        <v>-2.84917342734463</v>
       </c>
       <c r="D43" s="17">
         <f>'3_연간손익'!E21/100000</f>
-        <v>6.24193944</v>
+        <v>2.89535378</v>
       </c>
       <c r="E43" s="17">
         <f>'3_연간손익'!F21/100000</f>
-        <v>28.4775097078692</v>
+        <v>17.5766269398429</v>
       </c>
       <c r="F43" s="17">
         <f>'3_연간손익'!G21/100000</f>
-        <v>59.0828210092795</v>
+        <v>42.8983203511415</v>
       </c>
       <c r="G43" s="17">
         <f>'3_연간손익'!H21/100000</f>
-        <v>162.920663490587</v>
+        <v>124.543184417608</v>
       </c>
     </row>
     <row r="44">

--- a/모닛_5개년_사업계획_손익계산서_2026-2030.xlsx
+++ b/모닛_5개년_사업계획_손익계산서_2026-2030.xlsx
@@ -91,6 +91,11 @@
     </font>
     <font>
       <name val="맑은 고딕"/>
+      <color rgb="00008000"/>
+      <sz val="9"/>
+    </font>
+    <font>
+      <name val="맑은 고딕"/>
       <b val="1"/>
       <color rgb="001F3864"/>
       <sz val="9"/>
@@ -118,7 +123,8 @@
     </font>
     <font>
       <name val="맑은 고딕"/>
-      <color rgb="00008000"/>
+      <i val="1"/>
+      <color rgb="00000000"/>
       <sz val="9"/>
     </font>
     <font>
@@ -136,12 +142,6 @@
       <name val="맑은 고딕"/>
       <b val="1"/>
       <color rgb="000000FF"/>
-      <sz val="9"/>
-    </font>
-    <font>
-      <name val="맑은 고딕"/>
-      <i val="1"/>
-      <color rgb="00000000"/>
       <sz val="9"/>
     </font>
     <font>
@@ -300,7 +300,7 @@
   <cellStyleXfs count="1">
     <xf numFmtId="0" fontId="0" fillId="0" borderId="0"/>
   </cellStyleXfs>
-  <cellXfs count="104">
+  <cellXfs count="109">
     <xf numFmtId="0" fontId="0" fillId="0" borderId="0" pivotButton="0" quotePrefix="0" xfId="0"/>
     <xf numFmtId="0" fontId="1" fillId="0" borderId="0" applyAlignment="1" pivotButton="0" quotePrefix="0" xfId="0">
       <alignment vertical="center"/>
@@ -308,7 +308,7 @@
     <xf numFmtId="0" fontId="2" fillId="0" borderId="0" applyAlignment="1" pivotButton="0" quotePrefix="0" xfId="0">
       <alignment vertical="center"/>
     </xf>
-    <xf numFmtId="0" fontId="12" fillId="0" borderId="0" applyAlignment="1" pivotButton="0" quotePrefix="0" xfId="0">
+    <xf numFmtId="0" fontId="13" fillId="0" borderId="0" applyAlignment="1" pivotButton="0" quotePrefix="0" xfId="0">
       <alignment vertical="center"/>
     </xf>
     <xf numFmtId="0" fontId="21" fillId="4" borderId="3" applyAlignment="1" pivotButton="0" quotePrefix="0" xfId="0">
@@ -316,13 +316,13 @@
     </xf>
     <xf numFmtId="0" fontId="0" fillId="0" borderId="6" pivotButton="0" quotePrefix="0" xfId="0"/>
     <xf numFmtId="0" fontId="0" fillId="0" borderId="7" pivotButton="0" quotePrefix="0" xfId="0"/>
-    <xf numFmtId="0" fontId="13" fillId="0" borderId="0" applyAlignment="1" pivotButton="0" quotePrefix="0" xfId="0">
+    <xf numFmtId="0" fontId="14" fillId="0" borderId="0" applyAlignment="1" pivotButton="0" quotePrefix="0" xfId="0">
       <alignment vertical="center"/>
     </xf>
     <xf numFmtId="1" fontId="6" fillId="0" borderId="0" applyAlignment="1" pivotButton="0" quotePrefix="0" xfId="0">
       <alignment vertical="center"/>
     </xf>
-    <xf numFmtId="0" fontId="9" fillId="0" borderId="0" applyAlignment="1" pivotButton="0" quotePrefix="0" xfId="0">
+    <xf numFmtId="0" fontId="10" fillId="0" borderId="0" applyAlignment="1" pivotButton="0" quotePrefix="0" xfId="0">
       <alignment vertical="center"/>
     </xf>
     <xf numFmtId="0" fontId="22" fillId="0" borderId="0" pivotButton="0" quotePrefix="0" xfId="0"/>
@@ -341,13 +341,13 @@
     <xf numFmtId="0" fontId="6" fillId="0" borderId="0" applyAlignment="1" pivotButton="0" quotePrefix="0" xfId="0">
       <alignment vertical="center"/>
     </xf>
-    <xf numFmtId="167" fontId="14" fillId="0" borderId="0" applyAlignment="1" pivotButton="0" quotePrefix="0" xfId="0">
+    <xf numFmtId="167" fontId="9" fillId="0" borderId="0" applyAlignment="1" pivotButton="0" quotePrefix="0" xfId="0">
       <alignment vertical="center"/>
     </xf>
-    <xf numFmtId="165" fontId="14" fillId="0" borderId="0" applyAlignment="1" pivotButton="0" quotePrefix="0" xfId="0">
+    <xf numFmtId="165" fontId="9" fillId="0" borderId="0" applyAlignment="1" pivotButton="0" quotePrefix="0" xfId="0">
       <alignment vertical="center"/>
     </xf>
-    <xf numFmtId="164" fontId="14" fillId="0" borderId="0" applyAlignment="1" pivotButton="0" quotePrefix="0" xfId="0">
+    <xf numFmtId="164" fontId="9" fillId="0" borderId="0" applyAlignment="1" pivotButton="0" quotePrefix="0" xfId="0">
       <alignment vertical="center"/>
     </xf>
     <xf numFmtId="165" fontId="5" fillId="0" borderId="1" applyAlignment="1" pivotButton="0" quotePrefix="0" xfId="0">
@@ -365,7 +365,7 @@
     <xf numFmtId="164" fontId="5" fillId="5" borderId="0" applyAlignment="1" pivotButton="0" quotePrefix="0" xfId="0">
       <alignment vertical="center"/>
     </xf>
-    <xf numFmtId="164" fontId="14" fillId="6" borderId="0" applyAlignment="1" pivotButton="0" quotePrefix="0" xfId="0">
+    <xf numFmtId="164" fontId="9" fillId="6" borderId="0" applyAlignment="1" pivotButton="0" quotePrefix="0" xfId="0">
       <alignment vertical="center"/>
     </xf>
     <xf numFmtId="164" fontId="5" fillId="0" borderId="0" applyAlignment="1" pivotButton="0" quotePrefix="0" xfId="0">
@@ -380,7 +380,7 @@
     <xf numFmtId="164" fontId="5" fillId="6" borderId="1" applyAlignment="1" pivotButton="0" quotePrefix="0" xfId="0">
       <alignment vertical="center"/>
     </xf>
-    <xf numFmtId="0" fontId="15" fillId="0" borderId="0" applyAlignment="1" pivotButton="0" quotePrefix="0" xfId="0">
+    <xf numFmtId="0" fontId="16" fillId="0" borderId="0" applyAlignment="1" pivotButton="0" quotePrefix="0" xfId="0">
       <alignment vertical="center"/>
     </xf>
     <xf numFmtId="167" fontId="2" fillId="5" borderId="0" applyAlignment="1" pivotButton="0" quotePrefix="0" xfId="0">
@@ -413,13 +413,13 @@
     <xf numFmtId="164" fontId="5" fillId="6" borderId="2" applyAlignment="1" pivotButton="0" quotePrefix="0" xfId="0">
       <alignment vertical="center"/>
     </xf>
-    <xf numFmtId="164" fontId="16" fillId="0" borderId="0" applyAlignment="1" pivotButton="0" quotePrefix="0" xfId="0">
+    <xf numFmtId="164" fontId="17" fillId="0" borderId="0" applyAlignment="1" pivotButton="0" quotePrefix="0" xfId="0">
       <alignment vertical="center"/>
     </xf>
-    <xf numFmtId="164" fontId="16" fillId="5" borderId="0" applyAlignment="1" pivotButton="0" quotePrefix="0" xfId="0">
+    <xf numFmtId="164" fontId="17" fillId="5" borderId="0" applyAlignment="1" pivotButton="0" quotePrefix="0" xfId="0">
       <alignment vertical="center"/>
     </xf>
-    <xf numFmtId="164" fontId="16" fillId="6" borderId="0" applyAlignment="1" pivotButton="0" quotePrefix="0" xfId="0">
+    <xf numFmtId="164" fontId="17" fillId="6" borderId="0" applyAlignment="1" pivotButton="0" quotePrefix="0" xfId="0">
       <alignment vertical="center"/>
     </xf>
     <xf numFmtId="164" fontId="6" fillId="0" borderId="0" applyAlignment="1" pivotButton="0" quotePrefix="0" xfId="0">
@@ -431,13 +431,13 @@
     <xf numFmtId="164" fontId="6" fillId="6" borderId="0" applyAlignment="1" pivotButton="0" quotePrefix="0" xfId="0">
       <alignment vertical="center"/>
     </xf>
-    <xf numFmtId="165" fontId="14" fillId="5" borderId="0" applyAlignment="1" pivotButton="0" quotePrefix="0" xfId="0">
+    <xf numFmtId="165" fontId="9" fillId="5" borderId="0" applyAlignment="1" pivotButton="0" quotePrefix="0" xfId="0">
       <alignment vertical="center"/>
     </xf>
-    <xf numFmtId="165" fontId="14" fillId="6" borderId="0" applyAlignment="1" pivotButton="0" quotePrefix="0" xfId="0">
+    <xf numFmtId="165" fontId="9" fillId="6" borderId="0" applyAlignment="1" pivotButton="0" quotePrefix="0" xfId="0">
       <alignment vertical="center"/>
     </xf>
-    <xf numFmtId="164" fontId="14" fillId="5" borderId="0" applyAlignment="1" pivotButton="0" quotePrefix="0" xfId="0">
+    <xf numFmtId="164" fontId="9" fillId="5" borderId="0" applyAlignment="1" pivotButton="0" quotePrefix="0" xfId="0">
       <alignment vertical="center"/>
     </xf>
     <xf numFmtId="167" fontId="6" fillId="5" borderId="0" applyAlignment="1" pivotButton="0" quotePrefix="0" xfId="0">
@@ -449,13 +449,13 @@
     <xf numFmtId="167" fontId="5" fillId="0" borderId="0" applyAlignment="1" pivotButton="0" quotePrefix="0" xfId="0">
       <alignment vertical="center"/>
     </xf>
-    <xf numFmtId="0" fontId="11" fillId="0" borderId="0" applyAlignment="1" pivotButton="0" quotePrefix="0" xfId="0">
+    <xf numFmtId="0" fontId="12" fillId="0" borderId="0" applyAlignment="1" pivotButton="0" quotePrefix="0" xfId="0">
       <alignment vertical="center"/>
     </xf>
-    <xf numFmtId="164" fontId="17" fillId="0" borderId="0" applyAlignment="1" pivotButton="0" quotePrefix="0" xfId="0">
+    <xf numFmtId="164" fontId="18" fillId="0" borderId="0" applyAlignment="1" pivotButton="0" quotePrefix="0" xfId="0">
       <alignment vertical="center"/>
     </xf>
-    <xf numFmtId="0" fontId="18" fillId="0" borderId="0" applyAlignment="1" pivotButton="0" quotePrefix="0" xfId="0">
+    <xf numFmtId="0" fontId="15" fillId="0" borderId="0" applyAlignment="1" pivotButton="0" quotePrefix="0" xfId="0">
       <alignment vertical="center"/>
     </xf>
     <xf numFmtId="164" fontId="7" fillId="0" borderId="0" applyAlignment="1" pivotButton="0" quotePrefix="0" xfId="0">
@@ -470,16 +470,16 @@
     <xf numFmtId="0" fontId="20" fillId="0" borderId="0" applyAlignment="1" pivotButton="0" quotePrefix="0" xfId="0">
       <alignment vertical="center"/>
     </xf>
-    <xf numFmtId="164" fontId="13" fillId="0" borderId="0" applyAlignment="1" pivotButton="0" quotePrefix="0" xfId="0">
+    <xf numFmtId="164" fontId="14" fillId="0" borderId="0" applyAlignment="1" pivotButton="0" quotePrefix="0" xfId="0">
       <alignment vertical="center"/>
     </xf>
-    <xf numFmtId="0" fontId="11" fillId="0" borderId="0" applyAlignment="1" pivotButton="0" quotePrefix="0" xfId="0">
+    <xf numFmtId="0" fontId="12" fillId="0" borderId="0" applyAlignment="1" pivotButton="0" quotePrefix="0" xfId="0">
       <alignment horizontal="right" vertical="center"/>
     </xf>
-    <xf numFmtId="1" fontId="11" fillId="0" borderId="0" applyAlignment="1" pivotButton="0" quotePrefix="0" xfId="0">
+    <xf numFmtId="1" fontId="12" fillId="0" borderId="0" applyAlignment="1" pivotButton="0" quotePrefix="0" xfId="0">
       <alignment horizontal="center" vertical="center"/>
     </xf>
-    <xf numFmtId="1" fontId="13" fillId="0" borderId="0" applyAlignment="1" pivotButton="0" quotePrefix="0" xfId="0">
+    <xf numFmtId="1" fontId="14" fillId="0" borderId="0" applyAlignment="1" pivotButton="0" quotePrefix="0" xfId="0">
       <alignment vertical="center"/>
     </xf>
     <xf numFmtId="0" fontId="6" fillId="0" borderId="0" applyAlignment="1" pivotButton="0" quotePrefix="0" xfId="0">
@@ -497,22 +497,22 @@
     <xf numFmtId="166" fontId="7" fillId="0" borderId="0" applyAlignment="1" pivotButton="0" quotePrefix="0" xfId="0">
       <alignment vertical="center"/>
     </xf>
-    <xf numFmtId="166" fontId="14" fillId="0" borderId="0" applyAlignment="1" pivotButton="0" quotePrefix="0" xfId="0">
+    <xf numFmtId="166" fontId="9" fillId="0" borderId="0" applyAlignment="1" pivotButton="0" quotePrefix="0" xfId="0">
       <alignment vertical="center"/>
     </xf>
-    <xf numFmtId="0" fontId="10" fillId="0" borderId="0" applyAlignment="1" pivotButton="0" quotePrefix="0" xfId="0">
+    <xf numFmtId="0" fontId="11" fillId="0" borderId="0" applyAlignment="1" pivotButton="0" quotePrefix="0" xfId="0">
       <alignment vertical="center"/>
     </xf>
     <xf numFmtId="169" fontId="6" fillId="0" borderId="0" applyAlignment="1" pivotButton="0" quotePrefix="0" xfId="0">
       <alignment vertical="center"/>
     </xf>
-    <xf numFmtId="1" fontId="14" fillId="0" borderId="0" applyAlignment="1" pivotButton="0" quotePrefix="0" xfId="0">
+    <xf numFmtId="1" fontId="9" fillId="0" borderId="0" applyAlignment="1" pivotButton="0" quotePrefix="0" xfId="0">
       <alignment vertical="center"/>
     </xf>
-    <xf numFmtId="167" fontId="11" fillId="0" borderId="0" applyAlignment="1" pivotButton="0" quotePrefix="0" xfId="0">
+    <xf numFmtId="167" fontId="12" fillId="0" borderId="0" applyAlignment="1" pivotButton="0" quotePrefix="0" xfId="0">
       <alignment vertical="center"/>
     </xf>
-    <xf numFmtId="0" fontId="14" fillId="0" borderId="0" applyAlignment="1" pivotButton="0" quotePrefix="0" xfId="0">
+    <xf numFmtId="0" fontId="9" fillId="0" borderId="0" applyAlignment="1" pivotButton="0" quotePrefix="0" xfId="0">
       <alignment vertical="center"/>
     </xf>
     <xf numFmtId="166" fontId="6" fillId="0" borderId="0" applyAlignment="1" pivotButton="0" quotePrefix="0" xfId="0">
@@ -524,10 +524,10 @@
     <xf numFmtId="0" fontId="6" fillId="0" borderId="0" applyAlignment="1" pivotButton="0" quotePrefix="0" xfId="0">
       <alignment vertical="top" wrapText="1"/>
     </xf>
-    <xf numFmtId="164" fontId="14" fillId="0" borderId="0" applyAlignment="1" pivotButton="0" quotePrefix="0" xfId="0">
+    <xf numFmtId="164" fontId="9" fillId="0" borderId="0" applyAlignment="1" pivotButton="0" quotePrefix="0" xfId="0">
       <alignment vertical="top"/>
     </xf>
-    <xf numFmtId="0" fontId="13" fillId="0" borderId="0" applyAlignment="1" pivotButton="0" quotePrefix="0" xfId="0">
+    <xf numFmtId="0" fontId="14" fillId="0" borderId="0" applyAlignment="1" pivotButton="0" quotePrefix="0" xfId="0">
       <alignment horizontal="right" vertical="top"/>
     </xf>
     <xf numFmtId="165" fontId="6" fillId="5" borderId="0" applyAlignment="1" pivotButton="0" quotePrefix="0" xfId="0">
@@ -537,6 +537,15 @@
       <alignment vertical="center"/>
     </xf>
     <xf numFmtId="165" fontId="6" fillId="6" borderId="0" applyAlignment="1" pivotButton="0" quotePrefix="0" xfId="0">
+      <alignment vertical="center"/>
+    </xf>
+    <xf numFmtId="164" fontId="15" fillId="0" borderId="0" applyAlignment="1" pivotButton="0" quotePrefix="0" xfId="0">
+      <alignment vertical="center"/>
+    </xf>
+    <xf numFmtId="164" fontId="15" fillId="5" borderId="0" applyAlignment="1" pivotButton="0" quotePrefix="0" xfId="0">
+      <alignment vertical="center"/>
+    </xf>
+    <xf numFmtId="164" fontId="15" fillId="6" borderId="0" applyAlignment="1" pivotButton="0" quotePrefix="0" xfId="0">
       <alignment vertical="center"/>
     </xf>
     <xf numFmtId="166" fontId="6" fillId="5" borderId="0" applyAlignment="1" pivotButton="0" quotePrefix="0" xfId="0">
@@ -567,6 +576,12 @@
     <xf numFmtId="167" fontId="7" fillId="4" borderId="0" applyAlignment="1" pivotButton="0" quotePrefix="0" xfId="0">
       <alignment vertical="center"/>
     </xf>
+    <xf numFmtId="0" fontId="6" fillId="3" borderId="0" applyAlignment="1" pivotButton="0" quotePrefix="0" xfId="0">
+      <alignment vertical="center" wrapText="1"/>
+    </xf>
+    <xf numFmtId="164" fontId="9" fillId="4" borderId="0" applyAlignment="1" pivotButton="0" quotePrefix="0" xfId="0">
+      <alignment vertical="center"/>
+    </xf>
     <xf numFmtId="167" fontId="7" fillId="0" borderId="0" applyAlignment="1" pivotButton="0" quotePrefix="0" xfId="0">
       <alignment vertical="center"/>
     </xf>
@@ -582,10 +597,10 @@
     <xf numFmtId="0" fontId="8" fillId="0" borderId="0" applyAlignment="1" pivotButton="0" quotePrefix="0" xfId="0">
       <alignment horizontal="center" vertical="center"/>
     </xf>
-    <xf numFmtId="0" fontId="10" fillId="0" borderId="0" applyAlignment="1" pivotButton="0" quotePrefix="0" xfId="0">
+    <xf numFmtId="0" fontId="11" fillId="0" borderId="0" applyAlignment="1" pivotButton="0" quotePrefix="0" xfId="0">
       <alignment vertical="center" wrapText="1"/>
     </xf>
-    <xf numFmtId="0" fontId="13" fillId="0" borderId="0" applyAlignment="1" pivotButton="0" quotePrefix="0" xfId="0">
+    <xf numFmtId="0" fontId="14" fillId="0" borderId="0" applyAlignment="1" pivotButton="0" quotePrefix="0" xfId="0">
       <alignment horizontal="right" vertical="center"/>
     </xf>
     <xf numFmtId="0" fontId="24" fillId="0" borderId="0" applyAlignment="1" pivotButton="0" quotePrefix="0" xfId="0">
@@ -1038,7 +1053,12 @@
   <commentList>
     <comment ref="C91" authorId="0" shapeId="0">
       <text>
-        <t>2026년 09월분 급상여대장(지급일 2026-09-25): 7명 지급합계 39,688,891원 ÷ 7 = 5,669,841원. 대표이사 포함, 기본급·연장·식대·상여 등 지급 항목 합계(공제 전). 연간 상여·성과급은 별도 반영 없음.</t>
+        <t>2026년 09월분 급상여대장(지급일 2026-09-25) 대표이사 지급합계 13,688,890원. 인상 없이 2026~2030 동일 적용.</t>
+      </text>
+    </comment>
+    <comment ref="C92" authorId="0" shapeId="0">
+      <text>
+        <t>2026년 09월분 급상여대장: 대표 제외 6명 지급합계 26,000,001원 ÷ 6 = 4,333,334원(약 4,339천원 가정치로 사용). 공제 전 총액 기준, 연 상여 미포함.</t>
       </text>
     </comment>
   </commentList>
@@ -1657,27 +1677,27 @@
       </c>
       <c r="D12" s="13">
         <f>'3_연간손익'!D13/100000</f>
-        <v>-2.92328310734463</v>
+        <v>-2.86316150734463</v>
       </c>
       <c r="E12" s="13">
         <f>'3_연간손익'!E13/100000</f>
-        <v>3.26335378</v>
+        <v>5.569748408</v>
       </c>
       <c r="F12" s="13">
         <f>'3_연간손익'!F13/100000</f>
-        <v>19.1966269398429</v>
+        <v>34.1354094148028</v>
       </c>
       <c r="G12" s="13">
         <f>'3_연간손익'!G13/100000</f>
-        <v>54.9743045583219</v>
+        <v>93.7766092908651</v>
       </c>
       <c r="H12" s="13">
         <f>'3_연간손익'!H13/100000</f>
-        <v>164.668697971292</v>
+        <v>250.42035249864</v>
       </c>
       <c r="I12" s="14">
         <f>IFERROR(('3_연간손익'!H13/'3_연간손익'!C13)^(1/5)-1,"n/a")</f>
-        <v>2.61167692074088</v>
+        <v>2.9275399218072</v>
       </c>
     </row>
     <row r="13">
@@ -1692,23 +1712,23 @@
       </c>
       <c r="D13" s="16">
         <f>'3_연간손익'!D14</f>
-        <v>-0.243606925612053</v>
+        <v>-0.238596792278719</v>
       </c>
       <c r="E13" s="16">
         <f>'3_연간손익'!E14</f>
-        <v>0.0326268819160891</v>
+        <v>0.0556861241106814</v>
       </c>
       <c r="F13" s="16">
         <f>'3_연간손익'!F14</f>
-        <v>0.0581715967874026</v>
+        <v>0.103440634590312</v>
       </c>
       <c r="G13" s="16">
         <f>'3_연간손익'!G14</f>
-        <v>0.0785347207976027</v>
+        <v>0.133966584701236</v>
       </c>
       <c r="H13" s="16">
         <f>'3_연간손익'!H14</f>
-        <v>0.105556857673905</v>
+        <v>0.160525866986308</v>
       </c>
     </row>
     <row r="14">
@@ -1723,27 +1743,27 @@
       </c>
       <c r="D14" s="17">
         <f>'3_연간손익'!D21/100000</f>
-        <v>-2.84917342734463</v>
+        <v>-0.489051827344633</v>
       </c>
       <c r="E14" s="17">
         <f>'3_연간손익'!E21/100000</f>
-        <v>2.89535378</v>
+        <v>5.201748408</v>
       </c>
       <c r="F14" s="17">
         <f>'3_연간손익'!F21/100000</f>
-        <v>17.5766269398429</v>
+        <v>31.215806495802</v>
       </c>
       <c r="G14" s="17">
         <f>'3_연간손익'!G21/100000</f>
-        <v>42.8983203511415</v>
+        <v>70.3705552468748</v>
       </c>
       <c r="H14" s="17">
         <f>'3_연간손익'!H21/100000</f>
-        <v>124.543184417608</v>
+        <v>190.436387193969</v>
       </c>
       <c r="I14" s="14">
         <f>IFERROR(('3_연간손익'!H21/'3_연간손익'!C21)^(1/5)-1,"n/a")</f>
-        <v>3.74693397338258</v>
+        <v>4.16772250041508</v>
       </c>
     </row>
     <row r="15">
@@ -1754,23 +1774,23 @@
       </c>
       <c r="D15" s="17">
         <f>'3_연간손익'!D23/100000</f>
-        <v>-2.74328310734463</v>
+        <v>-2.68316150734463</v>
       </c>
       <c r="E15" s="17">
         <f>'3_연간손익'!E23/100000</f>
-        <v>7.62288378</v>
+        <v>9.929278408</v>
       </c>
       <c r="F15" s="17">
         <f>'3_연간손익'!F23/100000</f>
-        <v>24.0561569398429</v>
+        <v>38.9949394148028</v>
       </c>
       <c r="G15" s="17">
         <f>'3_연간손익'!G23/100000</f>
-        <v>60.7338345583219</v>
+        <v>99.5361392908651</v>
       </c>
       <c r="H15" s="17">
         <f>'3_연간손익'!H23/100000</f>
-        <v>171.628227971292</v>
+        <v>257.37988249864</v>
       </c>
     </row>
     <row r="16">
@@ -2644,7 +2664,7 @@
         <f>'4_매출_거래처'!AZ32</f>
         <v>156000000</v>
       </c>
-      <c r="I7" s="97" t="inlineStr">
+      <c r="I7" s="102" t="inlineStr">
         <is>
           <t>2027은 IR p.25 표 합계에서 Sunway PoC(3.0억)를 제외한 값 ≈ IR 차트 10,005(차이 −2,960천원(약 −3백만원), 반올림 수준). 2026은 지정 거래처 + 기존 소액 조정, 2028~30은 삼성 채널 잔차로 일치</t>
         </is>
@@ -3336,7 +3356,7 @@
           <t>PoC</t>
         </is>
       </c>
-      <c r="D31" s="98" t="inlineStr">
+      <c r="D31" s="103" t="inlineStr">
         <is>
           <t>미정</t>
         </is>
@@ -3361,7 +3381,7 @@
           <t>진행 중</t>
         </is>
       </c>
-      <c r="D32" s="98" t="inlineStr">
+      <c r="D32" s="103" t="inlineStr">
         <is>
           <t>미정</t>
         </is>
@@ -3386,7 +3406,7 @@
           <t>진행 중</t>
         </is>
       </c>
-      <c r="D33" s="98" t="inlineStr">
+      <c r="D33" s="103" t="inlineStr">
         <is>
           <t>미정</t>
         </is>
@@ -3411,7 +3431,7 @@
           <t>진행 중</t>
         </is>
       </c>
-      <c r="D34" s="98" t="inlineStr">
+      <c r="D34" s="103" t="inlineStr">
         <is>
           <t>미정</t>
         </is>
@@ -3494,7 +3514,7 @@
         <f>IFERROR(C40/$D$35,0)</f>
         <v>0.525705588407733</v>
       </c>
-      <c r="E40" s="99" t="inlineStr">
+      <c r="E40" s="104" t="inlineStr">
         <is>
           <t>※ NHG는 IR에 "계약"이나 입찰자료상 LOA 미확인(★확인사항). NHG를 입찰 단계로 보면 "계약" 비중은 더 낮아집니다.</t>
         </is>
@@ -3570,7 +3590,7 @@
         <f>SUM(C40:C44)</f>
         <v>10302040</v>
       </c>
-      <c r="D45" s="100">
+      <c r="D45" s="105">
         <f>SUM(D40:D44)</f>
         <v>1</v>
       </c>
@@ -3633,7 +3653,7 @@
         <f>G6/'8_가정'!$C$11</f>
         <v>130000</v>
       </c>
-      <c r="H50" s="99" t="inlineStr">
+      <c r="H50" s="104" t="inlineStr">
         <is>
           <t>IR 매출 ÷ ARPU(120만원)</t>
         </is>
@@ -3665,7 +3685,7 @@
         <f>'3_연간손익'!H26</f>
         <v>106776.188196769</v>
       </c>
-      <c r="H51" s="99" t="inlineStr">
+      <c r="H51" s="104" t="inlineStr">
         <is>
           <t>구독형 매출 ÷ ARPU</t>
         </is>
@@ -3697,7 +3717,7 @@
         <f>G50/'8_가정'!$C$12</f>
         <v>866.666666666667</v>
       </c>
-      <c r="H52" s="99" t="inlineStr">
+      <c r="H52" s="104" t="inlineStr">
         <is>
           <t>시설+재가·유통 채널 혼합이므로 상한 지표</t>
         </is>
@@ -3729,7 +3749,7 @@
         <f>G50/'8_가정'!$C$13</f>
         <v>0.52</v>
       </c>
-      <c r="H53" s="99" t="inlineStr">
+      <c r="H53" s="104" t="inlineStr">
         <is>
           <t>SOM 25만 명(3년 목표)</t>
         </is>
@@ -3761,7 +3781,7 @@
         <f>IFERROR(SUMPRODUCT('4_매출_거래처'!$S$10:$S$25,'4_매출_거래처'!AZ10:AZ25)/G7,0)</f>
         <v>0.330987717970405</v>
       </c>
-      <c r="H54" s="99" t="inlineStr">
+      <c r="H54" s="104" t="inlineStr">
         <is>
           <t>나머지는 신규 파이프라인·삼성채널·기존 소액</t>
         </is>
@@ -3793,7 +3813,7 @@
         <f>IFERROR('4_매출_거래처'!AZ31/G7,0)</f>
         <v>0.1241404871578</v>
       </c>
-      <c r="H55" s="99" t="inlineStr">
+      <c r="H55" s="104" t="inlineStr">
         <is>
           <t>IR 총액과의 잔차</t>
         </is>
@@ -3814,7 +3834,7 @@
           <t>S1 매출 = IR 목표(2026±0.1%, 2027 −0.05% 이내, 2028~30 일치)</t>
         </is>
       </c>
-      <c r="D59" s="101" t="str">
+      <c r="D59" s="106" t="str">
         <f>IF(AND(ABS(C9)&lt;0.001,ABS(D9)&lt;0.0005,ABS(E9)&lt;0.0001,ABS(F9)&lt;0.0001,ABS(G9)&lt;0.0001),"OK","확인")</f>
         <v>OK</v>
       </c>
@@ -3825,7 +3845,7 @@
           <t>삼성 채널 잔차 ≥ 0</t>
         </is>
       </c>
-      <c r="D60" s="96" t="str">
+      <c r="D60" s="101" t="str">
         <f>IF(MIN('4_매출_거래처'!AX31:AZ31)&gt;=0,"OK","확인")</f>
         <v>OK</v>
       </c>
@@ -3836,7 +3856,7 @@
           <t>제품 믹스 프로파일 합계 100%</t>
         </is>
       </c>
-      <c r="D61" s="96" t="str">
+      <c r="D61" s="101" t="str">
         <f>'8_가정'!$C$87</f>
         <v>OK</v>
       </c>
@@ -3847,7 +3867,7 @@
           <t>기존 소액 조정 행 ≥ 0</t>
         </is>
       </c>
-      <c r="D62" s="96" t="str">
+      <c r="D62" s="101" t="str">
         <f>IF('4_매출_거래처'!M26&gt;=0,"OK","확인")</f>
         <v>OK</v>
       </c>
@@ -3899,11 +3919,11 @@
           <t>2028 매출 ÷ 2027-12 연환산(배)</t>
         </is>
       </c>
-      <c r="D68" s="102">
+      <c r="D68" s="107">
         <f>IFERROR(D67/D66,0)</f>
         <v>2.45268355061199</v>
       </c>
-      <c r="E68" s="99" t="inlineStr">
+      <c r="E68" s="104" t="inlineStr">
         <is>
           <t>※ 2028 신규 파이프라인·삼성 채널(약 1/3)이 포함되어 있어 12월 run-rate 대비 배수가 큼 → 투자사 질의 예상 지점</t>
         </is>
@@ -4152,7 +4172,7 @@
           <t>4_매출_거래처 · 2_손익계산서</t>
         </is>
       </c>
-      <c r="C5" s="103" t="inlineStr">
+      <c r="C5" s="108" t="inlineStr">
         <is>
           <t>2026년 1~9월 실적(월별) 및 2026 상반기 결산</t>
         </is>
@@ -4177,7 +4197,7 @@
           <t>6_거래처현황 · 4_매출_거래처</t>
         </is>
       </c>
-      <c r="C6" s="103" t="inlineStr">
+      <c r="C6" s="108" t="inlineStr">
         <is>
           <t>NHG(KTPH·TTSH·Woodlands) "계약" 표기</t>
         </is>
@@ -4202,7 +4222,7 @@
           <t>10_IR정합</t>
         </is>
       </c>
-      <c r="C7" s="103" t="inlineStr">
+      <c r="C7" s="108" t="inlineStr">
         <is>
           <t>IR p.25 2027 표의 통화·단위</t>
         </is>
@@ -4227,7 +4247,7 @@
           <t>10_IR정합</t>
         </is>
       </c>
-      <c r="C8" s="103" t="inlineStr">
+      <c r="C8" s="108" t="inlineStr">
         <is>
           <t>IR 차트(10,005) vs 표 합계(10,302,040)</t>
         </is>
@@ -4252,7 +4272,7 @@
           <t>4_매출_거래처</t>
         </is>
       </c>
-      <c r="C9" s="103" t="inlineStr">
+      <c r="C9" s="108" t="inlineStr">
         <is>
           <t>노인요양시설 "구독자 2만 명 = 1,980,000 USD"(IR p.10)</t>
         </is>
@@ -4277,7 +4297,7 @@
           <t>6_거래처현황</t>
         </is>
       </c>
-      <c r="C10" s="103" t="inlineStr">
+      <c r="C10" s="108" t="inlineStr">
         <is>
           <t>거래처명·국가 표기 확인</t>
         </is>
@@ -4302,7 +4322,7 @@
           <t>4_매출_거래처</t>
         </is>
       </c>
-      <c r="C11" s="103" t="inlineStr">
+      <c r="C11" s="108" t="inlineStr">
         <is>
           <t>거래처별 2025·2026 상반기 매출(투자사 양식 "거래처 현황" 시트)</t>
         </is>
@@ -4327,7 +4347,7 @@
           <t>7_비용인력 · 8_가정</t>
         </is>
       </c>
-      <c r="C12" s="103" t="inlineStr">
+      <c r="C12" s="108" t="inlineStr">
         <is>
           <t>개발비(자산 19.8억) 상각 시점·내용연수, 개발비 자본화 정책</t>
         </is>
@@ -4352,7 +4372,7 @@
           <t>8_가정</t>
         </is>
       </c>
-      <c r="C13" s="103" t="inlineStr">
+      <c r="C13" s="108" t="inlineStr">
         <is>
           <t>법인세율·이월결손금·중소기업 요건</t>
         </is>
@@ -4377,7 +4397,7 @@
           <t>7_비용인력 · 8_가정</t>
         </is>
       </c>
-      <c r="C14" s="103" t="inlineStr">
+      <c r="C14" s="108" t="inlineStr">
         <is>
           <t>인원 계획·급여·차입금·이자율</t>
         </is>
@@ -4402,7 +4422,7 @@
           <t>8_가정</t>
         </is>
       </c>
-      <c r="C15" s="103" t="inlineStr">
+      <c r="C15" s="108" t="inlineStr">
         <is>
           <t>Hansoms(Xiamen) 현물출자(최대 USD 448k 상당 제품 납품)</t>
         </is>
@@ -4427,7 +4447,7 @@
           <t>9_시나리오</t>
         </is>
       </c>
-      <c r="C16" s="103" t="inlineStr">
+      <c r="C16" s="108" t="inlineStr">
         <is>
           <t>스냅샷 갱신</t>
         </is>
@@ -4452,7 +4472,7 @@
           <t>6_거래처현황 · 4_매출_거래처</t>
         </is>
       </c>
-      <c r="C17" s="103" t="inlineStr">
+      <c r="C17" s="108" t="inlineStr">
         <is>
           <t>Vanguard Healthcare 단계</t>
         </is>
@@ -4477,7 +4497,7 @@
           <t>9_시나리오</t>
         </is>
       </c>
-      <c r="C18" s="103" t="inlineStr">
+      <c r="C18" s="108" t="inlineStr">
         <is>
           <t>S2·S3 비용 대응</t>
         </is>
@@ -4502,7 +4522,7 @@
           <t>10_IR정합</t>
         </is>
       </c>
-      <c r="C19" s="103" t="inlineStr">
+      <c r="C19" s="108" t="inlineStr">
         <is>
           <t>IR p.24 차트의 지역 구성 vs 모델 2028~30</t>
         </is>
@@ -4527,7 +4547,7 @@
           <t>2_손익계산서 · 7_비용인력</t>
         </is>
       </c>
-      <c r="C20" s="103" t="inlineStr">
+      <c r="C20" s="108" t="inlineStr">
         <is>
           <t>운전자본·자금 계획</t>
         </is>
@@ -4552,7 +4572,7 @@
           <t>1_요약 · 10_IR정합</t>
         </is>
       </c>
-      <c r="C21" s="103" t="inlineStr">
+      <c r="C21" s="108" t="inlineStr">
         <is>
           <t>2028~2030 신규 파이프라인·삼성 채널 비중</t>
         </is>
@@ -7184,123 +7204,123 @@
       </c>
       <c r="C30" s="18">
         <f>'7_비용인력'!C19</f>
-        <v>39690</v>
+        <v>39723</v>
       </c>
       <c r="D30" s="18">
         <f>'7_비용인력'!D19</f>
-        <v>39690</v>
+        <v>39723</v>
       </c>
       <c r="E30" s="18">
         <f>'7_비용인력'!E19</f>
-        <v>39690</v>
+        <v>39723</v>
       </c>
       <c r="F30" s="18">
         <f>'7_비용인력'!F19</f>
-        <v>39690</v>
+        <v>39723</v>
       </c>
       <c r="G30" s="18">
         <f>'7_비용인력'!G19</f>
-        <v>39690</v>
+        <v>39723</v>
       </c>
       <c r="H30" s="18">
         <f>'7_비용인력'!H19</f>
-        <v>39690</v>
+        <v>39723</v>
       </c>
       <c r="I30" s="18">
         <f>'7_비용인력'!I19</f>
-        <v>39690</v>
+        <v>39723</v>
       </c>
       <c r="J30" s="18">
         <f>'7_비용인력'!J19</f>
-        <v>39690</v>
+        <v>39723</v>
       </c>
       <c r="K30" s="18">
         <f>'7_비용인력'!K19</f>
-        <v>39690</v>
+        <v>39723</v>
       </c>
       <c r="L30" s="18">
         <f>'7_비용인력'!L19</f>
-        <v>45360</v>
+        <v>44062</v>
       </c>
       <c r="M30" s="18">
         <f>'7_비용인력'!M19</f>
-        <v>45360</v>
+        <v>44062</v>
       </c>
       <c r="N30" s="18">
         <f>'7_비용인력'!N19</f>
-        <v>51030</v>
+        <v>48401</v>
       </c>
       <c r="O30" s="35">
         <f>'7_비용인력'!O19</f>
-        <v>498960</v>
+        <v>494032</v>
       </c>
       <c r="P30" s="18">
         <f>'7_비용인력'!P19</f>
-        <v>60669</v>
+        <v>54562.38</v>
       </c>
       <c r="Q30" s="18">
         <f>'7_비용인력'!Q19</f>
-        <v>66735.9</v>
+        <v>58901.38</v>
       </c>
       <c r="R30" s="18">
         <f>'7_비용인력'!R19</f>
-        <v>72802.8</v>
+        <v>63240.38</v>
       </c>
       <c r="S30" s="18">
         <f>'7_비용인력'!S19</f>
-        <v>78869.7</v>
+        <v>67579.38</v>
       </c>
       <c r="T30" s="18">
         <f>'7_비용인력'!T19</f>
-        <v>84936.6</v>
+        <v>71918.38</v>
       </c>
       <c r="U30" s="18">
         <f>'7_비용인력'!U19</f>
-        <v>91003.5</v>
+        <v>76257.38</v>
       </c>
       <c r="V30" s="18">
         <f>'7_비용인력'!V19</f>
-        <v>97070.4</v>
+        <v>80596.38</v>
       </c>
       <c r="W30" s="18">
         <f>'7_비용인력'!W19</f>
-        <v>103137.3</v>
+        <v>84935.38</v>
       </c>
       <c r="X30" s="18">
         <f>'7_비용인력'!X19</f>
-        <v>109204.2</v>
+        <v>89274.38</v>
       </c>
       <c r="Y30" s="18">
         <f>'7_비용인력'!Y19</f>
-        <v>115271.1</v>
+        <v>93613.38</v>
       </c>
       <c r="Z30" s="18">
         <f>'7_비용인력'!Z19</f>
-        <v>121338</v>
+        <v>97952.38</v>
       </c>
       <c r="AA30" s="18">
         <f>'7_비용인력'!AA19</f>
-        <v>133471.8</v>
+        <v>106630.38</v>
       </c>
       <c r="AB30" s="35">
         <f>'7_비용인력'!AB19</f>
-        <v>1134510.3</v>
+        <v>945461.56</v>
       </c>
       <c r="AC30" s="24">
         <f>'7_비용인력'!AC19</f>
-        <v>4167596.286</v>
+        <v>2943105.9192</v>
       </c>
       <c r="AD30" s="24">
         <f>'7_비용인력'!AD19</f>
-        <v>8960332.0149</v>
+        <v>5779815.233544</v>
       </c>
       <c r="AE30" s="24">
         <f>'7_비용인력'!AE19</f>
-        <v>17391379.301478</v>
+        <v>10362555.1598921</v>
       </c>
       <c r="AF30" s="36">
         <f>'7_비용인력'!AF19</f>
-        <v>32152777.902378</v>
+        <v>20524969.8726361</v>
       </c>
     </row>
     <row r="31">
@@ -7311,123 +7331,123 @@
       </c>
       <c r="C31" s="18">
         <f>'7_비용인력'!C20</f>
-        <v>8731.8</v>
+        <v>8739.06</v>
       </c>
       <c r="D31" s="18">
         <f>'7_비용인력'!D20</f>
-        <v>8731.8</v>
+        <v>8739.06</v>
       </c>
       <c r="E31" s="18">
         <f>'7_비용인력'!E20</f>
-        <v>8731.8</v>
+        <v>8739.06</v>
       </c>
       <c r="F31" s="18">
         <f>'7_비용인력'!F20</f>
-        <v>8731.8</v>
+        <v>8739.06</v>
       </c>
       <c r="G31" s="18">
         <f>'7_비용인력'!G20</f>
-        <v>8731.8</v>
+        <v>8739.06</v>
       </c>
       <c r="H31" s="18">
         <f>'7_비용인력'!H20</f>
-        <v>8731.8</v>
+        <v>8739.06</v>
       </c>
       <c r="I31" s="18">
         <f>'7_비용인력'!I20</f>
-        <v>8731.8</v>
+        <v>8739.06</v>
       </c>
       <c r="J31" s="18">
         <f>'7_비용인력'!J20</f>
-        <v>8731.8</v>
+        <v>8739.06</v>
       </c>
       <c r="K31" s="18">
         <f>'7_비용인력'!K20</f>
-        <v>8731.8</v>
+        <v>8739.06</v>
       </c>
       <c r="L31" s="18">
         <f>'7_비용인력'!L20</f>
-        <v>9979.2</v>
+        <v>9693.64</v>
       </c>
       <c r="M31" s="18">
         <f>'7_비용인력'!M20</f>
-        <v>9979.2</v>
+        <v>9693.64</v>
       </c>
       <c r="N31" s="18">
         <f>'7_비용인력'!N20</f>
-        <v>11226.6</v>
+        <v>10648.22</v>
       </c>
       <c r="O31" s="35">
         <f>'7_비용인력'!O20</f>
-        <v>109771.2</v>
+        <v>108687.04</v>
       </c>
       <c r="P31" s="18">
         <f>'7_비용인력'!P20</f>
-        <v>13347.18</v>
+        <v>12003.7236</v>
       </c>
       <c r="Q31" s="18">
         <f>'7_비용인력'!Q20</f>
-        <v>14681.898</v>
+        <v>12958.3036</v>
       </c>
       <c r="R31" s="18">
         <f>'7_비용인력'!R20</f>
-        <v>16016.616</v>
+        <v>13912.8836</v>
       </c>
       <c r="S31" s="18">
         <f>'7_비용인력'!S20</f>
-        <v>17351.334</v>
+        <v>14867.4636</v>
       </c>
       <c r="T31" s="18">
         <f>'7_비용인력'!T20</f>
-        <v>18686.052</v>
+        <v>15822.0436</v>
       </c>
       <c r="U31" s="18">
         <f>'7_비용인력'!U20</f>
-        <v>20020.77</v>
+        <v>16776.6236</v>
       </c>
       <c r="V31" s="18">
         <f>'7_비용인력'!V20</f>
-        <v>21355.488</v>
+        <v>17731.2036</v>
       </c>
       <c r="W31" s="18">
         <f>'7_비용인력'!W20</f>
-        <v>22690.206</v>
+        <v>18685.7836</v>
       </c>
       <c r="X31" s="18">
         <f>'7_비용인력'!X20</f>
-        <v>24024.924</v>
+        <v>19640.3636</v>
       </c>
       <c r="Y31" s="18">
         <f>'7_비용인력'!Y20</f>
-        <v>25359.642</v>
+        <v>20594.9436</v>
       </c>
       <c r="Z31" s="18">
         <f>'7_비용인력'!Z20</f>
-        <v>26694.36</v>
+        <v>21549.5236</v>
       </c>
       <c r="AA31" s="18">
         <f>'7_비용인력'!AA20</f>
-        <v>29363.796</v>
+        <v>23458.6836</v>
       </c>
       <c r="AB31" s="35">
         <f>'7_비용인력'!AB20</f>
-        <v>249592.266</v>
+        <v>208001.5432</v>
       </c>
       <c r="AC31" s="24">
         <f>'7_비용인력'!AC20</f>
-        <v>916871.18292</v>
+        <v>647483.302224</v>
       </c>
       <c r="AD31" s="24">
         <f>'7_비용인력'!AD20</f>
-        <v>1971273.043278</v>
+        <v>1271559.35137968</v>
       </c>
       <c r="AE31" s="24">
         <f>'7_비용인력'!AE20</f>
-        <v>3826103.44632516</v>
+        <v>2279762.13517626</v>
       </c>
       <c r="AF31" s="36">
         <f>'7_비용인력'!AF20</f>
-        <v>7073611.13852316</v>
+        <v>4515493.37197994</v>
       </c>
     </row>
     <row r="32">
@@ -8581,123 +8601,123 @@
       </c>
       <c r="C41" s="26">
         <f>SUM(C30:C40)</f>
-        <v>65745.4909461035</v>
+        <v>65785.7509461035</v>
       </c>
       <c r="D41" s="26">
         <f>SUM(D30:D40)</f>
-        <v>65942.101115595</v>
+        <v>65982.361115595</v>
       </c>
       <c r="E41" s="26">
         <f>SUM(E30:E40)</f>
-        <v>66138.7112850865</v>
+        <v>66178.9712850866</v>
       </c>
       <c r="F41" s="26">
         <f>SUM(F30:F40)</f>
-        <v>66335.3214545781</v>
+        <v>66375.5814545781</v>
       </c>
       <c r="G41" s="26">
         <f>SUM(G30:G40)</f>
-        <v>66531.9316240696</v>
+        <v>66572.1916240696</v>
       </c>
       <c r="H41" s="26">
         <f>SUM(H30:H40)</f>
-        <v>66728.5417935611</v>
+        <v>66768.8017935611</v>
       </c>
       <c r="I41" s="26">
         <f>SUM(I30:I40)</f>
-        <v>68910.0408519415</v>
+        <v>68950.3008519415</v>
       </c>
       <c r="J41" s="26">
         <f>SUM(J30:J40)</f>
-        <v>69931.5399103219</v>
+        <v>69971.799910322</v>
       </c>
       <c r="K41" s="26">
         <f>SUM(K30:K40)</f>
-        <v>70953.0389687024</v>
+        <v>70993.2989687024</v>
       </c>
       <c r="L41" s="26">
         <f>SUM(L30:L40)</f>
-        <v>79428.9750641198</v>
+        <v>77845.4150641198</v>
       </c>
       <c r="M41" s="26">
         <f>SUM(M30:M40)</f>
-        <v>81908.5511595373</v>
+        <v>80324.9911595373</v>
       </c>
       <c r="N41" s="26">
         <f>SUM(N30:N40)</f>
-        <v>93376.9558263833</v>
+        <v>90169.5758263833</v>
       </c>
       <c r="O41" s="27">
         <f>SUM(O30:O40)</f>
-        <v>861931.2</v>
+        <v>855919.04</v>
       </c>
       <c r="P41" s="26">
         <f>SUM(P30:P40)</f>
-        <v>180246.518714017</v>
+        <v>172796.442314017</v>
       </c>
       <c r="Q41" s="26">
         <f>SUM(Q30:Q40)</f>
-        <v>204288.796737913</v>
+        <v>194730.682337913</v>
       </c>
       <c r="R41" s="26">
         <f>SUM(R30:R40)</f>
-        <v>228331.07476181</v>
+        <v>216664.92236181</v>
       </c>
       <c r="S41" s="26">
         <f>SUM(S30:S40)</f>
-        <v>252119.115497571</v>
+        <v>238344.925097571</v>
       </c>
       <c r="T41" s="26">
         <f>SUM(T30:T40)</f>
-        <v>275907.156233332</v>
+        <v>260024.927833332</v>
       </c>
       <c r="U41" s="26">
         <f>SUM(U30:U40)</f>
-        <v>308695.196969093</v>
+        <v>290704.930569093</v>
       </c>
       <c r="V41" s="26">
         <f>SUM(V30:V40)</f>
-        <v>331416.571038187</v>
+        <v>311318.266638187</v>
       </c>
       <c r="W41" s="26">
         <f>SUM(W30:W40)</f>
-        <v>352579.12157787</v>
+        <v>330372.77917787</v>
       </c>
       <c r="X41" s="26">
         <f>SUM(X30:X40)</f>
-        <v>364741.672117552</v>
+        <v>340427.291717552</v>
       </c>
       <c r="Y41" s="26">
         <f>SUM(Y30:Y40)</f>
-        <v>372143.290117552</v>
+        <v>345720.871717552</v>
       </c>
       <c r="Z41" s="26">
         <f>SUM(Z30:Z40)</f>
-        <v>379544.908117552</v>
+        <v>351014.451717552</v>
       </c>
       <c r="AA41" s="26">
         <f>SUM(AA30:AA40)</f>
-        <v>394348.144117552</v>
+        <v>361601.611717552</v>
       </c>
       <c r="AB41" s="27">
         <f>SUM(AB30:AB40)</f>
-        <v>3644361.566</v>
+        <v>3413722.1032</v>
       </c>
       <c r="AC41" s="28">
         <f>SUM(AC30:AC40)</f>
-        <v>11154420.46892</v>
+        <v>9660542.221424</v>
       </c>
       <c r="AD41" s="28">
         <f>SUM(AD30:AD40)</f>
-        <v>22427558.058178</v>
+        <v>18547327.5849237</v>
       </c>
       <c r="AE41" s="28">
         <f>SUM(AE30:AE40)</f>
-        <v>47245435.7478032</v>
+        <v>38670270.2950683</v>
       </c>
       <c r="AF41" s="26">
         <f>SUM(AF30:AF40)</f>
-        <v>85333707.0409012</v>
+        <v>71147781.244616</v>
       </c>
     </row>
     <row r="42">
@@ -8708,123 +8728,123 @@
       </c>
       <c r="C42" s="37">
         <f>C26-C41</f>
-        <v>-33654.3802476011</v>
+        <v>-33694.6402476011</v>
       </c>
       <c r="D42" s="37">
         <f>D26-D41</f>
-        <v>-33042.1768577706</v>
+        <v>-33082.4368577706</v>
       </c>
       <c r="E42" s="37">
         <f>E26-E41</f>
-        <v>-32429.9734679401</v>
+        <v>-32470.2334679401</v>
       </c>
       <c r="F42" s="37">
         <f>F26-F41</f>
-        <v>-31817.7700781096</v>
+        <v>-31858.0300781096</v>
       </c>
       <c r="G42" s="37">
         <f>G26-G41</f>
-        <v>-31205.5666882791</v>
+        <v>-31245.8266882791</v>
       </c>
       <c r="H42" s="37">
         <f>H26-H41</f>
-        <v>-30593.3632984486</v>
+        <v>-30633.6232984486</v>
       </c>
       <c r="I42" s="37">
         <f>I26-I41</f>
-        <v>-24222.6265752847</v>
+        <v>-24262.8865752847</v>
       </c>
       <c r="J42" s="37">
         <f>J26-J41</f>
-        <v>-21041.8898521209</v>
+        <v>-21082.1498521209</v>
       </c>
       <c r="K42" s="37">
         <f>K26-K41</f>
-        <v>-17861.1531289571</v>
+        <v>-17901.4131289571</v>
       </c>
       <c r="L42" s="37">
         <f>L26-L41</f>
-        <v>-19748.2793687562</v>
+        <v>-18164.7193687562</v>
       </c>
       <c r="M42" s="37">
         <f>M26-M41</f>
-        <v>-11934.2416085553</v>
+        <v>-10350.6816085553</v>
       </c>
       <c r="N42" s="37">
         <f>N26-N41</f>
-        <v>-4776.88956264011</v>
+        <v>-1569.50956264012</v>
       </c>
       <c r="O42" s="38">
         <f>O26-O41</f>
-        <v>-292328.310734463</v>
+        <v>-286316.150734463</v>
       </c>
       <c r="P42" s="37">
         <f>P26-P41</f>
-        <v>-66327.1753446328</v>
+        <v>-58877.0989446328</v>
       </c>
       <c r="Q42" s="37">
         <f>Q26-Q41</f>
-        <v>-46593.2407723496</v>
+        <v>-37035.1263723496</v>
       </c>
       <c r="R42" s="37">
         <f>R26-R41</f>
-        <v>-26859.3062000665</v>
+        <v>-15193.1538000665</v>
       </c>
       <c r="S42" s="37">
         <f>S26-S41</f>
-        <v>-7543.33772947823</v>
+        <v>6230.85267052177</v>
       </c>
       <c r="T42" s="37">
         <f>T26-T41</f>
-        <v>11772.63074111</v>
+        <v>27654.85914111</v>
       </c>
       <c r="U42" s="37">
         <f>U26-U41</f>
-        <v>49538.5992116982</v>
+        <v>67528.8656116983</v>
       </c>
       <c r="V42" s="37">
         <f>V26-V41</f>
-        <v>67100.9676822865</v>
+        <v>87199.2720822865</v>
       </c>
       <c r="W42" s="37">
         <f>W26-W41</f>
-        <v>82140.1596822866</v>
+        <v>104346.502082287</v>
       </c>
       <c r="X42" s="37">
         <f>X26-X41</f>
-        <v>78729.3516822865</v>
+        <v>103043.732082287</v>
       </c>
       <c r="Y42" s="37">
         <f>Y26-Y41</f>
-        <v>71327.7336822865</v>
+        <v>97750.1520822865</v>
       </c>
       <c r="Z42" s="37">
         <f>Z26-Z41</f>
-        <v>63926.1156822864</v>
+        <v>92456.5720822865</v>
       </c>
       <c r="AA42" s="37">
         <f>AA26-AA41</f>
-        <v>49122.8796822865</v>
+        <v>81869.4120822865</v>
       </c>
       <c r="AB42" s="38">
         <f>AB26-AB41</f>
-        <v>326335.378</v>
+        <v>556974.8408</v>
       </c>
       <c r="AC42" s="39">
         <f>AC26-AC41</f>
-        <v>1919662.69398429</v>
+        <v>3413540.94148028</v>
       </c>
       <c r="AD42" s="39">
         <f>AD26-AD41</f>
-        <v>5497430.45583219</v>
+        <v>9377660.92908651</v>
       </c>
       <c r="AE42" s="39">
         <f>AE26-AE41</f>
-        <v>16466869.7971292</v>
+        <v>25042035.249864</v>
       </c>
       <c r="AF42" s="37">
         <f>AF26-AF41</f>
-        <v>23917970.0142112</v>
+        <v>38103895.8104963</v>
       </c>
     </row>
     <row r="43">
@@ -8835,123 +8855,123 @@
       </c>
       <c r="C43" s="14">
         <f>IFERROR(C42/C14,0)</f>
-        <v>-0.498985470619341</v>
+        <v>-0.499582396038836</v>
       </c>
       <c r="D43" s="14">
         <f>IFERROR(D42/D14,0)</f>
-        <v>-0.477898829515085</v>
+        <v>-0.478481121867042</v>
       </c>
       <c r="E43" s="14">
         <f>IFERROR(E42/E14,0)</f>
-        <v>-0.457821289747737</v>
+        <v>-0.45838964929769</v>
       </c>
       <c r="F43" s="14">
         <f>IFERROR(F42/F14,0)</f>
-        <v>-0.43868210819768</v>
+        <v>-0.439237186119001</v>
       </c>
       <c r="G43" s="14">
         <f>IFERROR(G42/G14,0)</f>
-        <v>-0.420417003349996</v>
+        <v>-0.420959406207921</v>
       </c>
       <c r="H43" s="14">
         <f>IFERROR(H42/H14,0)</f>
-        <v>-0.402967434019094</v>
+        <v>-0.40349772775422</v>
       </c>
       <c r="I43" s="14">
         <f>IFERROR(I42/I14,0)</f>
-        <v>-0.255711967055814</v>
+        <v>-0.256136981401871</v>
       </c>
       <c r="J43" s="14">
         <f>IFERROR(J42/J14,0)</f>
-        <v>-0.203239973644075</v>
+        <v>-0.20362883801873</v>
       </c>
       <c r="K43" s="14">
         <f>IFERROR(K42/K14,0)</f>
-        <v>-0.15899438019172</v>
+        <v>-0.159352762077833</v>
       </c>
       <c r="L43" s="14">
         <f>IFERROR(L42/L14,0)</f>
-        <v>-0.157014100403056</v>
+        <v>-0.144423573188435</v>
       </c>
       <c r="M43" s="14">
         <f>IFERROR(M42/M14,0)</f>
-        <v>-0.0811027914097904</v>
+        <v>-0.0703412247700787</v>
       </c>
       <c r="N43" s="14">
         <f>IFERROR(N42/N14,0)</f>
-        <v>-0.0256295129329029</v>
+        <v>-0.00842091178925382</v>
       </c>
       <c r="O43" s="30">
         <f>IFERROR(O42/O14,0)</f>
-        <v>-0.243606925612053</v>
+        <v>-0.238596792278719</v>
       </c>
       <c r="P43" s="14">
         <f>IFERROR(P42/P14,0)</f>
-        <v>-0.231908216115124</v>
+        <v>-0.205859557795692</v>
       </c>
       <c r="Q43" s="14">
         <f>IFERROR(Q42/Q14,0)</f>
-        <v>-0.117379919591144</v>
+        <v>-0.0933006608592478</v>
       </c>
       <c r="R43" s="14">
         <f>IFERROR(R42/R14,0)</f>
-        <v>-0.0528849744928527</v>
+        <v>-0.0299147545062246</v>
       </c>
       <c r="S43" s="14">
         <f>IFERROR(S42/S14,0)</f>
-        <v>-0.0122233658818419</v>
+        <v>0.0100965904854041</v>
       </c>
       <c r="T43" s="14">
         <f>IFERROR(T42/T14,0)</f>
-        <v>0.0162075461605775</v>
+        <v>0.0380728331628238</v>
       </c>
       <c r="U43" s="14">
         <f>IFERROR(U42/U14,0)</f>
-        <v>0.0553126867862862</v>
+        <v>0.0753998508647987</v>
       </c>
       <c r="V43" s="14">
         <f>IFERROR(V42/V14,0)</f>
-        <v>0.0672528396716701</v>
+        <v>0.0873966332736578</v>
       </c>
       <c r="W43" s="14">
         <f>IFERROR(W42/W14,0)</f>
-        <v>0.0753938206341094</v>
+        <v>0.0957763107865636</v>
       </c>
       <c r="X43" s="14">
         <f>IFERROR(X42/X14,0)</f>
-        <v>0.0702175221169055</v>
+        <v>0.0919031515170519</v>
       </c>
       <c r="Y43" s="14">
         <f>IFERROR(Y42/Y14,0)</f>
-        <v>0.0636161305836278</v>
+        <v>0.0871818873025615</v>
       </c>
       <c r="Z43" s="14">
         <f>IFERROR(Z42/Z14,0)</f>
-        <v>0.0570147390503501</v>
+        <v>0.082460623088071</v>
       </c>
       <c r="AA43" s="14">
         <f>IFERROR(AA42/AA14,0)</f>
-        <v>0.0438119559837948</v>
+        <v>0.0730180946590903</v>
       </c>
       <c r="AB43" s="30">
         <f>IFERROR(AB42/AB14,0)</f>
-        <v>0.0326268819160891</v>
+        <v>0.0556861241106814</v>
       </c>
       <c r="AC43" s="31">
         <f>IFERROR(AC42/AC14,0)</f>
-        <v>0.0581715967874026</v>
+        <v>0.103440634590312</v>
       </c>
       <c r="AD43" s="31">
         <f>IFERROR(AD42/AD14,0)</f>
-        <v>0.0785347207976027</v>
+        <v>0.133966584701236</v>
       </c>
       <c r="AE43" s="31">
         <f>IFERROR(AE42/AE14,0)</f>
-        <v>0.105556857673905</v>
+        <v>0.160525866986308</v>
       </c>
       <c r="AF43" s="14">
         <f>IFERROR(AF42/AF14,0)</f>
-        <v>0.0885188358097193</v>
+        <v>0.141020015283735</v>
       </c>
     </row>
     <row r="44"/>
@@ -8970,55 +8990,55 @@
       </c>
       <c r="C46" s="25">
         <f>C47</f>
-        <v>5416.66666666667</v>
+        <v>24583.3333333333</v>
       </c>
       <c r="D46" s="25">
         <f>D47</f>
-        <v>5416.66666666667</v>
+        <v>24583.3333333333</v>
       </c>
       <c r="E46" s="25">
         <f>E47</f>
-        <v>5416.66666666667</v>
+        <v>24583.3333333333</v>
       </c>
       <c r="F46" s="25">
         <f>F47</f>
-        <v>5416.66666666667</v>
+        <v>24583.3333333333</v>
       </c>
       <c r="G46" s="25">
         <f>G47</f>
-        <v>5416.66666666667</v>
+        <v>24583.3333333333</v>
       </c>
       <c r="H46" s="25">
         <f>H47</f>
-        <v>5416.66666666667</v>
+        <v>24583.3333333333</v>
       </c>
       <c r="I46" s="25">
         <f>I47</f>
-        <v>5416.66666666667</v>
+        <v>24583.3333333333</v>
       </c>
       <c r="J46" s="25">
         <f>J47</f>
-        <v>5416.66666666667</v>
+        <v>24583.3333333333</v>
       </c>
       <c r="K46" s="25">
         <f>K47</f>
-        <v>5416.66666666667</v>
+        <v>24583.3333333333</v>
       </c>
       <c r="L46" s="25">
         <f>L47</f>
-        <v>5416.66666666667</v>
+        <v>24583.3333333333</v>
       </c>
       <c r="M46" s="25">
         <f>M47</f>
-        <v>5416.66666666667</v>
+        <v>24583.3333333333</v>
       </c>
       <c r="N46" s="25">
         <f>N47</f>
-        <v>5416.66666666667</v>
+        <v>24583.3333333333</v>
       </c>
       <c r="O46" s="23">
         <f>O47</f>
-        <v>65000</v>
+        <v>295000</v>
       </c>
       <c r="P46" s="25">
         <f>P47</f>
@@ -9086,7 +9106,7 @@
       </c>
       <c r="AF46" s="25">
         <f>AF47</f>
-        <v>135000</v>
+        <v>365000</v>
       </c>
     </row>
     <row r="47">
@@ -9097,55 +9117,55 @@
       </c>
       <c r="C47" s="40">
         <f>'7_비용인력'!C33</f>
-        <v>5416.66666666667</v>
+        <v>24583.3333333333</v>
       </c>
       <c r="D47" s="40">
         <f>'7_비용인력'!D33</f>
-        <v>5416.66666666667</v>
+        <v>24583.3333333333</v>
       </c>
       <c r="E47" s="40">
         <f>'7_비용인력'!E33</f>
-        <v>5416.66666666667</v>
+        <v>24583.3333333333</v>
       </c>
       <c r="F47" s="40">
         <f>'7_비용인력'!F33</f>
-        <v>5416.66666666667</v>
+        <v>24583.3333333333</v>
       </c>
       <c r="G47" s="40">
         <f>'7_비용인력'!G33</f>
-        <v>5416.66666666667</v>
+        <v>24583.3333333333</v>
       </c>
       <c r="H47" s="40">
         <f>'7_비용인력'!H33</f>
-        <v>5416.66666666667</v>
+        <v>24583.3333333333</v>
       </c>
       <c r="I47" s="40">
         <f>'7_비용인력'!I33</f>
-        <v>5416.66666666667</v>
+        <v>24583.3333333333</v>
       </c>
       <c r="J47" s="40">
         <f>'7_비용인력'!J33</f>
-        <v>5416.66666666667</v>
+        <v>24583.3333333333</v>
       </c>
       <c r="K47" s="40">
         <f>'7_비용인력'!K33</f>
-        <v>5416.66666666667</v>
+        <v>24583.3333333333</v>
       </c>
       <c r="L47" s="40">
         <f>'7_비용인력'!L33</f>
-        <v>5416.66666666667</v>
+        <v>24583.3333333333</v>
       </c>
       <c r="M47" s="40">
         <f>'7_비용인력'!M33</f>
-        <v>5416.66666666667</v>
+        <v>24583.3333333333</v>
       </c>
       <c r="N47" s="40">
         <f>'7_비용인력'!N33</f>
-        <v>5416.66666666667</v>
+        <v>24583.3333333333</v>
       </c>
       <c r="O47" s="41">
         <f>'7_비용인력'!O33</f>
-        <v>65000</v>
+        <v>295000</v>
       </c>
       <c r="P47" s="40">
         <f>'7_비용인력'!P33</f>
@@ -9213,7 +9233,7 @@
       </c>
       <c r="AF47" s="40">
         <f>'7_비용인력'!AF33</f>
-        <v>135000</v>
+        <v>365000</v>
       </c>
     </row>
     <row r="48">
@@ -9478,123 +9498,123 @@
       </c>
       <c r="C50" s="26">
         <f>C42+C46-C48</f>
-        <v>-33036.7995809344</v>
+        <v>-13910.3929142678</v>
       </c>
       <c r="D50" s="26">
         <f>D42+D46-D48</f>
-        <v>-32424.5961911039</v>
+        <v>-13298.1895244373</v>
       </c>
       <c r="E50" s="26">
         <f>E42+E46-E48</f>
-        <v>-31812.3928012734</v>
+        <v>-12685.9861346068</v>
       </c>
       <c r="F50" s="26">
         <f>F42+F46-F48</f>
-        <v>-31200.1894114429</v>
+        <v>-12073.7827447762</v>
       </c>
       <c r="G50" s="26">
         <f>G42+G46-G48</f>
-        <v>-30587.9860216124</v>
+        <v>-11461.5793549457</v>
       </c>
       <c r="H50" s="26">
         <f>H42+H46-H48</f>
-        <v>-29975.7826317819</v>
+        <v>-10849.3759651152</v>
       </c>
       <c r="I50" s="26">
         <f>I42+I46-I48</f>
-        <v>-23605.045908618</v>
+        <v>-4478.63924195137</v>
       </c>
       <c r="J50" s="26">
         <f>J42+J46-J48</f>
-        <v>-20424.3091854542</v>
+        <v>-1297.90251878757</v>
       </c>
       <c r="K50" s="26">
         <f>K42+K46-K48</f>
-        <v>-17243.5724622904</v>
+        <v>1882.83420437628</v>
       </c>
       <c r="L50" s="26">
         <f>L42+L46-L48</f>
-        <v>-19130.6987020895</v>
+        <v>1619.52796457717</v>
       </c>
       <c r="M50" s="26">
         <f>M42+M46-M48</f>
-        <v>-11316.6609418886</v>
+        <v>9433.56572477805</v>
       </c>
       <c r="N50" s="26">
         <f>N42+N46-N48</f>
-        <v>-4159.30889597344</v>
+        <v>18214.7377706932</v>
       </c>
       <c r="O50" s="27">
         <f>O42+O46-O48</f>
-        <v>-284917.342734463</v>
+        <v>-48905.1827344633</v>
       </c>
       <c r="P50" s="26">
         <f>P42+P46-P48</f>
-        <v>-69393.8420112995</v>
+        <v>-61943.7656112995</v>
       </c>
       <c r="Q50" s="26">
         <f>Q42+Q46-Q48</f>
-        <v>-49659.9074390163</v>
+        <v>-40101.7930390163</v>
       </c>
       <c r="R50" s="26">
         <f>R42+R46-R48</f>
-        <v>-29925.9728667332</v>
+        <v>-18259.8204667332</v>
       </c>
       <c r="S50" s="26">
         <f>S42+S46-S48</f>
-        <v>-10610.0043961449</v>
+        <v>3164.1860038551</v>
       </c>
       <c r="T50" s="26">
         <f>T42+T46-T48</f>
-        <v>8705.96407444329</v>
+        <v>24588.1924744433</v>
       </c>
       <c r="U50" s="26">
         <f>U42+U46-U48</f>
-        <v>46471.9325450316</v>
+        <v>64462.1989450316</v>
       </c>
       <c r="V50" s="26">
         <f>V42+V46-V48</f>
-        <v>64034.3010156198</v>
+        <v>84132.6054156198</v>
       </c>
       <c r="W50" s="26">
         <f>W42+W46-W48</f>
-        <v>79073.4930156199</v>
+        <v>101279.83541562</v>
       </c>
       <c r="X50" s="26">
         <f>X42+X46-X48</f>
-        <v>75662.6850156198</v>
+        <v>99977.0654156198</v>
       </c>
       <c r="Y50" s="26">
         <f>Y42+Y46-Y48</f>
-        <v>68261.0670156198</v>
+        <v>94683.4854156198</v>
       </c>
       <c r="Z50" s="26">
         <f>Z42+Z46-Z48</f>
-        <v>60859.4490156198</v>
+        <v>89389.9054156198</v>
       </c>
       <c r="AA50" s="26">
         <f>AA42+AA46-AA48</f>
-        <v>46056.2130156198</v>
+        <v>78802.7454156198</v>
       </c>
       <c r="AB50" s="27">
         <f>AB42+AB46-AB48</f>
-        <v>289535.378</v>
+        <v>520174.8408</v>
       </c>
       <c r="AC50" s="28">
         <f>AC42+AC46-AC48</f>
-        <v>1757662.69398429</v>
+        <v>3251540.94148028</v>
       </c>
       <c r="AD50" s="28">
         <f>AD42+AD46-AD48</f>
-        <v>5113430.45583219</v>
+        <v>8993660.92908651</v>
       </c>
       <c r="AE50" s="28">
         <f>AE42+AE46-AE48</f>
-        <v>15938869.7971292</v>
+        <v>24514035.249864</v>
       </c>
       <c r="AF50" s="26">
         <f>AF42+AF46-AF48</f>
-        <v>22814580.9822112</v>
+        <v>37230506.7784964</v>
       </c>
     </row>
     <row r="51">
@@ -9714,19 +9734,19 @@
       </c>
       <c r="AC51" s="24">
         <f>'7_비용인력'!AC49</f>
-        <v>0</v>
+        <v>129960.291900081</v>
       </c>
       <c r="AD51" s="24">
         <f>'7_비용인력'!AD49</f>
-        <v>823598.420718043</v>
+        <v>1956605.40439903</v>
       </c>
       <c r="AE51" s="24">
         <f>'7_비용인력'!AE49</f>
-        <v>3484551.35536842</v>
+        <v>5470396.53046709</v>
       </c>
       <c r="AF51" s="25">
         <f>O51+AB51+AC51+AD51+AE51</f>
-        <v>4308149.77608646</v>
+        <v>7556962.2267662</v>
       </c>
     </row>
     <row r="52">
@@ -9737,123 +9757,123 @@
       </c>
       <c r="C52" s="37">
         <f>C50-C51</f>
-        <v>-33036.7995809344</v>
+        <v>-13910.3929142678</v>
       </c>
       <c r="D52" s="37">
         <f>D50-D51</f>
-        <v>-32424.5961911039</v>
+        <v>-13298.1895244373</v>
       </c>
       <c r="E52" s="37">
         <f>E50-E51</f>
-        <v>-31812.3928012734</v>
+        <v>-12685.9861346068</v>
       </c>
       <c r="F52" s="37">
         <f>F50-F51</f>
-        <v>-31200.1894114429</v>
+        <v>-12073.7827447762</v>
       </c>
       <c r="G52" s="37">
         <f>G50-G51</f>
-        <v>-30587.9860216124</v>
+        <v>-11461.5793549457</v>
       </c>
       <c r="H52" s="37">
         <f>H50-H51</f>
-        <v>-29975.7826317819</v>
+        <v>-10849.3759651152</v>
       </c>
       <c r="I52" s="37">
         <f>I50-I51</f>
-        <v>-23605.045908618</v>
+        <v>-4478.63924195137</v>
       </c>
       <c r="J52" s="37">
         <f>J50-J51</f>
-        <v>-20424.3091854542</v>
+        <v>-1297.90251878757</v>
       </c>
       <c r="K52" s="37">
         <f>K50-K51</f>
-        <v>-17243.5724622904</v>
+        <v>1882.83420437628</v>
       </c>
       <c r="L52" s="37">
         <f>L50-L51</f>
-        <v>-19130.6987020895</v>
+        <v>1619.52796457717</v>
       </c>
       <c r="M52" s="37">
         <f>M50-M51</f>
-        <v>-11316.6609418886</v>
+        <v>9433.56572477805</v>
       </c>
       <c r="N52" s="37">
         <f>N50-N51</f>
-        <v>-4159.30889597344</v>
+        <v>18214.7377706932</v>
       </c>
       <c r="O52" s="38">
         <f>O50-O51</f>
-        <v>-284917.342734463</v>
+        <v>-48905.1827344633</v>
       </c>
       <c r="P52" s="37">
         <f>P50-P51</f>
-        <v>-69393.8420112995</v>
+        <v>-61943.7656112995</v>
       </c>
       <c r="Q52" s="37">
         <f>Q50-Q51</f>
-        <v>-49659.9074390163</v>
+        <v>-40101.7930390163</v>
       </c>
       <c r="R52" s="37">
         <f>R50-R51</f>
-        <v>-29925.9728667332</v>
+        <v>-18259.8204667332</v>
       </c>
       <c r="S52" s="37">
         <f>S50-S51</f>
-        <v>-10610.0043961449</v>
+        <v>3164.1860038551</v>
       </c>
       <c r="T52" s="37">
         <f>T50-T51</f>
-        <v>8705.96407444329</v>
+        <v>24588.1924744433</v>
       </c>
       <c r="U52" s="37">
         <f>U50-U51</f>
-        <v>46471.9325450316</v>
+        <v>64462.1989450316</v>
       </c>
       <c r="V52" s="37">
         <f>V50-V51</f>
-        <v>64034.3010156198</v>
+        <v>84132.6054156198</v>
       </c>
       <c r="W52" s="37">
         <f>W50-W51</f>
-        <v>79073.4930156199</v>
+        <v>101279.83541562</v>
       </c>
       <c r="X52" s="37">
         <f>X50-X51</f>
-        <v>75662.6850156198</v>
+        <v>99977.0654156198</v>
       </c>
       <c r="Y52" s="37">
         <f>Y50-Y51</f>
-        <v>68261.0670156198</v>
+        <v>94683.4854156198</v>
       </c>
       <c r="Z52" s="37">
         <f>Z50-Z51</f>
-        <v>60859.4490156198</v>
+        <v>89389.9054156198</v>
       </c>
       <c r="AA52" s="37">
         <f>AA50-AA51</f>
-        <v>46056.2130156198</v>
+        <v>78802.7454156198</v>
       </c>
       <c r="AB52" s="38">
         <f>AB50-AB51</f>
-        <v>289535.378</v>
+        <v>520174.8408</v>
       </c>
       <c r="AC52" s="39">
         <f>AC50-AC51</f>
-        <v>1757662.69398429</v>
+        <v>3121580.6495802</v>
       </c>
       <c r="AD52" s="39">
         <f>AD50-AD51</f>
-        <v>4289832.03511415</v>
+        <v>7037055.52468748</v>
       </c>
       <c r="AE52" s="39">
         <f>AE50-AE51</f>
-        <v>12454318.4417608</v>
+        <v>19043638.7193969</v>
       </c>
       <c r="AF52" s="37">
         <f>AF50-AF51</f>
-        <v>18506431.2061247</v>
+        <v>29673544.5517302</v>
       </c>
     </row>
     <row r="53">
@@ -9864,123 +9884,123 @@
       </c>
       <c r="C53" s="14">
         <f>IFERROR(C52/C14,0)</f>
-        <v>-0.489828749344581</v>
+        <v>-0.206246078631046</v>
       </c>
       <c r="D53" s="14">
         <f>IFERROR(D52/D14,0)</f>
-        <v>-0.468966576685571</v>
+        <v>-0.192335669521839</v>
       </c>
       <c r="E53" s="14">
         <f>IFERROR(E52/E14,0)</f>
-        <v>-0.44910276342467</v>
+        <v>-0.179090943124243</v>
       </c>
       <c r="F53" s="14">
         <f>IFERROR(F52/F14,0)</f>
-        <v>-0.430167319506631</v>
+        <v>-0.166465231705323</v>
       </c>
       <c r="G53" s="14">
         <f>IFERROR(G52/G14,0)</f>
-        <v>-0.412096647696772</v>
+        <v>-0.154416130115476</v>
       </c>
       <c r="H53" s="14">
         <f>IFERROR(H52/H14,0)</f>
-        <v>-0.394832829983614</v>
+        <v>-0.142905019978389</v>
       </c>
       <c r="I53" s="14">
         <f>IFERROR(I52/I14,0)</f>
-        <v>-0.249192328626095</v>
+        <v>-0.047279829325416</v>
       </c>
       <c r="J53" s="14">
         <f>IFERROR(J52/J14,0)</f>
-        <v>-0.197274868831791</v>
+        <v>-0.0125362158800758</v>
       </c>
       <c r="K53" s="14">
         <f>IFERROR(K52/K14,0)</f>
-        <v>-0.153496870898445</v>
+        <v>0.016760399240027</v>
       </c>
       <c r="L53" s="14">
         <f>IFERROR(L52/L14,0)</f>
-        <v>-0.152103856275337</v>
+        <v>0.0128765003617473</v>
       </c>
       <c r="M53" s="14">
         <f>IFERROR(M52/M14,0)</f>
-        <v>-0.0769058329745364</v>
+        <v>0.064108683092083</v>
       </c>
       <c r="N53" s="14">
         <f>IFERROR(N52/N14,0)</f>
-        <v>-0.0223159986730722</v>
+        <v>0.0977277894206548</v>
       </c>
       <c r="O53" s="30">
         <f>IFERROR(O52/O14,0)</f>
-        <v>-0.237431118945386</v>
+        <v>-0.0407543189453861</v>
       </c>
       <c r="P53" s="14">
         <f>IFERROR(P52/P14,0)</f>
-        <v>-0.242630596382203</v>
+        <v>-0.216581938062771</v>
       </c>
       <c r="Q53" s="14">
         <f>IFERROR(Q52/Q14,0)</f>
-        <v>-0.125105612862942</v>
+        <v>-0.101026354131045</v>
       </c>
       <c r="R53" s="14">
         <f>IFERROR(R52/R14,0)</f>
-        <v>-0.0589231270511026</v>
+        <v>-0.0359529070644745</v>
       </c>
       <c r="S53" s="14">
         <f>IFERROR(S52/S14,0)</f>
-        <v>-0.0171926500433915</v>
+        <v>0.00512730632385453</v>
       </c>
       <c r="T53" s="14">
         <f>IFERROR(T52/T14,0)</f>
-        <v>0.0119856230703084</v>
+        <v>0.0338509100725547</v>
       </c>
       <c r="U53" s="14">
         <f>IFERROR(U52/U14,0)</f>
-        <v>0.0518885775964724</v>
+        <v>0.0719757416749849</v>
       </c>
       <c r="V53" s="14">
         <f>IFERROR(V52/V14,0)</f>
-        <v>0.0641792321100576</v>
+        <v>0.0843230257120453</v>
       </c>
       <c r="W53" s="14">
         <f>IFERROR(W52/W14,0)</f>
-        <v>0.0725790255630313</v>
+        <v>0.0929615157154855</v>
       </c>
       <c r="X53" s="14">
         <f>IFERROR(X52/X14,0)</f>
-        <v>0.0674824083392533</v>
+        <v>0.0891680377393997</v>
       </c>
       <c r="Y53" s="14">
         <f>IFERROR(Y52/Y14,0)</f>
-        <v>0.0608810168059757</v>
+        <v>0.0844467735249093</v>
       </c>
       <c r="Z53" s="14">
         <f>IFERROR(Z52/Z14,0)</f>
-        <v>0.054279625272698</v>
+        <v>0.0797255093104189</v>
       </c>
       <c r="AA53" s="14">
         <f>IFERROR(AA52/AA14,0)</f>
-        <v>0.0410768422061427</v>
+        <v>0.0702829808814381</v>
       </c>
       <c r="AB53" s="30">
         <f>IFERROR(AB52/AB14,0)</f>
-        <v>0.0289476324829735</v>
+        <v>0.0520068746775658</v>
       </c>
       <c r="AC53" s="31">
         <f>IFERROR(AC52/AC14,0)</f>
-        <v>0.0532625058783117</v>
+        <v>0.0945933530175819</v>
       </c>
       <c r="AD53" s="31">
         <f>IFERROR(AD52/AD14,0)</f>
-        <v>0.061283314787345</v>
+        <v>0.100529364638393</v>
       </c>
       <c r="AE53" s="31">
         <f>IFERROR(AE52/AE14,0)</f>
-        <v>0.0798353746266715</v>
+        <v>0.122074607175621</v>
       </c>
       <c r="AF53" s="14">
         <f>IFERROR(AF52/AF14,0)</f>
-        <v>0.0684910861743484</v>
+        <v>0.109819839079417</v>
       </c>
     </row>
     <row r="54"/>
@@ -9999,123 +10019,123 @@
       </c>
       <c r="C56" s="43">
         <f>C42+C38</f>
-        <v>-32154.3802476011</v>
+        <v>-32194.6402476011</v>
       </c>
       <c r="D56" s="43">
         <f>D42+D38</f>
-        <v>-31542.1768577706</v>
+        <v>-31582.4368577706</v>
       </c>
       <c r="E56" s="43">
         <f>E42+E38</f>
-        <v>-30929.9734679401</v>
+        <v>-30970.2334679401</v>
       </c>
       <c r="F56" s="43">
         <f>F42+F38</f>
-        <v>-30317.7700781096</v>
+        <v>-30358.0300781096</v>
       </c>
       <c r="G56" s="43">
         <f>G42+G38</f>
-        <v>-29705.5666882791</v>
+        <v>-29745.8266882791</v>
       </c>
       <c r="H56" s="43">
         <f>H42+H38</f>
-        <v>-29093.3632984486</v>
+        <v>-29133.6232984486</v>
       </c>
       <c r="I56" s="43">
         <f>I42+I38</f>
-        <v>-22722.6265752847</v>
+        <v>-22762.8865752847</v>
       </c>
       <c r="J56" s="43">
         <f>J42+J38</f>
-        <v>-19541.8898521209</v>
+        <v>-19582.1498521209</v>
       </c>
       <c r="K56" s="43">
         <f>K42+K38</f>
-        <v>-16361.1531289571</v>
+        <v>-16401.4131289571</v>
       </c>
       <c r="L56" s="43">
         <f>L42+L38</f>
-        <v>-18248.2793687562</v>
+        <v>-16664.7193687562</v>
       </c>
       <c r="M56" s="43">
         <f>M42+M38</f>
-        <v>-10434.2416085553</v>
+        <v>-8850.68160855529</v>
       </c>
       <c r="N56" s="43">
         <f>N42+N38</f>
-        <v>-3276.88956264011</v>
+        <v>-69.5095626401162</v>
       </c>
       <c r="O56" s="44">
         <f>O42+O38</f>
-        <v>-274328.310734463</v>
+        <v>-268316.150734463</v>
       </c>
       <c r="P56" s="43">
         <f>P42+P38</f>
-        <v>-29997.7586779661</v>
+        <v>-22547.6822779661</v>
       </c>
       <c r="Q56" s="43">
         <f>Q42+Q38</f>
-        <v>-10263.824105683</v>
+        <v>-705.709705682959</v>
       </c>
       <c r="R56" s="43">
         <f>R42+R38</f>
-        <v>9470.11046660017</v>
+        <v>21136.2628666002</v>
       </c>
       <c r="S56" s="43">
         <f>S42+S38</f>
-        <v>28786.0789371884</v>
+        <v>42560.2693371884</v>
       </c>
       <c r="T56" s="43">
         <f>T42+T38</f>
-        <v>48102.0474077766</v>
+        <v>63984.2758077766</v>
       </c>
       <c r="U56" s="43">
         <f>U42+U38</f>
-        <v>85868.0158783649</v>
+        <v>103858.282278365</v>
       </c>
       <c r="V56" s="43">
         <f>V42+V38</f>
-        <v>103430.384348953</v>
+        <v>123528.688748953</v>
       </c>
       <c r="W56" s="43">
         <f>W42+W38</f>
-        <v>118469.576348953</v>
+        <v>140675.918748953</v>
       </c>
       <c r="X56" s="43">
         <f>X42+X38</f>
-        <v>115058.768348953</v>
+        <v>139373.148748953</v>
       </c>
       <c r="Y56" s="43">
         <f>Y42+Y38</f>
-        <v>107657.150348953</v>
+        <v>134079.568748953</v>
       </c>
       <c r="Z56" s="43">
         <f>Z42+Z38</f>
-        <v>100255.532348953</v>
+        <v>128785.988748953</v>
       </c>
       <c r="AA56" s="43">
         <f>AA42+AA38</f>
-        <v>85452.2963489531</v>
+        <v>118198.828748953</v>
       </c>
       <c r="AB56" s="44">
         <f>AB42+AB38</f>
-        <v>762288.378</v>
+        <v>992927.8408</v>
       </c>
       <c r="AC56" s="45">
         <f>AC42+AC38</f>
-        <v>2405615.69398429</v>
+        <v>3899493.94148028</v>
       </c>
       <c r="AD56" s="45">
         <f>AD42+AD38</f>
-        <v>6073383.45583219</v>
+        <v>9953613.92908651</v>
       </c>
       <c r="AE56" s="45">
         <f>AE42+AE38</f>
-        <v>17162822.7971292</v>
+        <v>25737988.249864</v>
       </c>
       <c r="AF56" s="43">
         <f>AF42+AF38</f>
-        <v>26129782.0142112</v>
+        <v>40315707.8104963</v>
       </c>
     </row>
     <row r="57">
@@ -10126,123 +10146,123 @@
       </c>
       <c r="C57" s="14">
         <f>IFERROR(C56/C14,0)</f>
-        <v>-0.476745328313278</v>
+        <v>-0.477342253732773</v>
       </c>
       <c r="D57" s="14">
         <f>IFERROR(D56/D14,0)</f>
-        <v>-0.456203883466032</v>
+        <v>-0.456786175817988</v>
       </c>
       <c r="E57" s="14">
         <f>IFERROR(E56/E14,0)</f>
-        <v>-0.436645449585533</v>
+        <v>-0.437213809135487</v>
       </c>
       <c r="F57" s="14">
         <f>IFERROR(F56/F14,0)</f>
-        <v>-0.418001112619387</v>
+        <v>-0.418556190540708</v>
       </c>
       <c r="G57" s="14">
         <f>IFERROR(G56/G14,0)</f>
-        <v>-0.400208253054753</v>
+        <v>-0.400750655912677</v>
       </c>
       <c r="H57" s="14">
         <f>IFERROR(H56/H14,0)</f>
-        <v>-0.383209843291588</v>
+        <v>-0.383740137026714</v>
       </c>
       <c r="I57" s="14">
         <f>IFERROR(I56/I14,0)</f>
-        <v>-0.239876857292157</v>
+        <v>-0.240301871638213</v>
       </c>
       <c r="J57" s="14">
         <f>IFERROR(J56/J14,0)</f>
-        <v>-0.188751733157663</v>
+        <v>-0.189140597532318</v>
       </c>
       <c r="K57" s="14">
         <f>IFERROR(K56/K14,0)</f>
-        <v>-0.145641850902839</v>
+        <v>-0.146000232788953</v>
       </c>
       <c r="L57" s="14">
         <f>IFERROR(L56/L14,0)</f>
-        <v>-0.145087939839559</v>
+        <v>-0.132497412624938</v>
       </c>
       <c r="M57" s="14">
         <f>IFERROR(M56/M14,0)</f>
-        <v>-0.0709090823242063</v>
+        <v>-0.0601475156844946</v>
       </c>
       <c r="N57" s="14">
         <f>IFERROR(N56/N14,0)</f>
-        <v>-0.0175815417802881</v>
+        <v>-0.000372940636639018</v>
       </c>
       <c r="O57" s="30">
         <f>IFERROR(O56/O14,0)</f>
-        <v>-0.228606925612053</v>
+        <v>-0.223596792278719</v>
       </c>
       <c r="P57" s="14">
         <f>IFERROR(P56/P14,0)</f>
-        <v>-0.10488501381692</v>
+        <v>-0.0788363554974883</v>
       </c>
       <c r="Q57" s="14">
         <f>IFERROR(Q56/Q14,0)</f>
-        <v>-0.025857116359626</v>
+        <v>-0.00177785762772943</v>
       </c>
       <c r="R57" s="14">
         <f>IFERROR(R56/R14,0)</f>
-        <v>0.0186462951328731</v>
+        <v>0.0416165151195012</v>
       </c>
       <c r="S57" s="14">
         <f>IFERROR(S56/S14,0)</f>
-        <v>0.046645502000767</v>
+        <v>0.068965458368013</v>
       </c>
       <c r="T57" s="14">
         <f>IFERROR(T56/T14,0)</f>
-        <v>0.0662227645565587</v>
+        <v>0.0880880515588049</v>
       </c>
       <c r="U57" s="14">
         <f>IFERROR(U56/U14,0)</f>
-        <v>0.0958765637870169</v>
+        <v>0.115963727865529</v>
       </c>
       <c r="V57" s="14">
         <f>IFERROR(V56/V14,0)</f>
-        <v>0.103664481989812</v>
+        <v>0.1238082755918</v>
       </c>
       <c r="W57" s="14">
         <f>IFERROR(W56/W14,0)</f>
-        <v>0.10873942812383</v>
+        <v>0.129121918276284</v>
       </c>
       <c r="X57" s="14">
         <f>IFERROR(X56/X14,0)</f>
-        <v>0.102619181266601</v>
+        <v>0.124304810666747</v>
       </c>
       <c r="Y57" s="14">
         <f>IFERROR(Y56/Y14,0)</f>
-        <v>0.0960177897333232</v>
+        <v>0.119583546452257</v>
       </c>
       <c r="Z57" s="14">
         <f>IFERROR(Z56/Z14,0)</f>
-        <v>0.0894163982000455</v>
+        <v>0.114862282237766</v>
       </c>
       <c r="AA57" s="14">
         <f>IFERROR(AA56/AA14,0)</f>
-        <v>0.0762136151334902</v>
+        <v>0.105419753808786</v>
       </c>
       <c r="AB57" s="30">
         <f>IFERROR(AB56/AB14,0)</f>
-        <v>0.0762132902887811</v>
+        <v>0.0992725324833734</v>
       </c>
       <c r="AC57" s="31">
         <f>IFERROR(AC56/AC14,0)</f>
-        <v>0.0728974452722511</v>
+        <v>0.11816648307516</v>
       </c>
       <c r="AD57" s="31">
         <f>IFERROR(AD56/AD14,0)</f>
-        <v>0.0867626207976027</v>
+        <v>0.142194484701236</v>
       </c>
       <c r="AE57" s="31">
         <f>IFERROR(AE56/AE14,0)</f>
-        <v>0.110018094853392</v>
+        <v>0.164987104165795</v>
       </c>
       <c r="AF57" s="14">
         <f>IFERROR(AF56/AF14,0)</f>
-        <v>0.0967046067239581</v>
+        <v>0.149205786197974</v>
       </c>
     </row>
     <row r="58">
@@ -10940,23 +10960,23 @@
       </c>
       <c r="D12" s="18">
         <f>'2_손익계산서'!O41</f>
-        <v>861931.2</v>
+        <v>855919.04</v>
       </c>
       <c r="E12" s="18">
         <f>'2_손익계산서'!AB41</f>
-        <v>3644361.566</v>
+        <v>3413722.1032</v>
       </c>
       <c r="F12" s="18">
         <f>'2_손익계산서'!AC41</f>
-        <v>11154420.46892</v>
+        <v>9660542.221424</v>
       </c>
       <c r="G12" s="18">
         <f>'2_손익계산서'!AD41</f>
-        <v>22427558.058178</v>
+        <v>18547327.5849237</v>
       </c>
       <c r="H12" s="18">
         <f>'2_손익계산서'!AE41</f>
-        <v>47245435.7478032</v>
+        <v>38670270.2950683</v>
       </c>
     </row>
     <row r="13">
@@ -10975,27 +10995,27 @@
       </c>
       <c r="D13" s="37">
         <f>D10-D12</f>
-        <v>-292328.310734463</v>
+        <v>-286316.150734463</v>
       </c>
       <c r="E13" s="37">
         <f>E10-E12</f>
-        <v>326335.378</v>
+        <v>556974.8408</v>
       </c>
       <c r="F13" s="37">
         <f>F10-F12</f>
-        <v>1919662.69398429</v>
+        <v>3413540.94148028</v>
       </c>
       <c r="G13" s="37">
         <f>G10-G12</f>
-        <v>5497430.45583219</v>
+        <v>9377660.92908651</v>
       </c>
       <c r="H13" s="37">
         <f>H10-H12</f>
-        <v>16466869.7971292</v>
+        <v>25042035.249864</v>
       </c>
       <c r="I13" s="14">
         <f>IFERROR((H13/C13)^(1/5)-1,"n/a")</f>
-        <v>2.61167692074088</v>
+        <v>2.9275399218072</v>
       </c>
     </row>
     <row r="14">
@@ -11014,23 +11034,23 @@
       </c>
       <c r="D14" s="14">
         <f>IFERROR(D13/D7,0)</f>
-        <v>-0.243606925612053</v>
+        <v>-0.238596792278719</v>
       </c>
       <c r="E14" s="14">
         <f>IFERROR(E13/E7,0)</f>
-        <v>0.0326268819160891</v>
+        <v>0.0556861241106814</v>
       </c>
       <c r="F14" s="14">
         <f>IFERROR(F13/F7,0)</f>
-        <v>0.0581715967874026</v>
+        <v>0.103440634590312</v>
       </c>
       <c r="G14" s="14">
         <f>IFERROR(G13/G7,0)</f>
-        <v>0.0785347207976027</v>
+        <v>0.133966584701236</v>
       </c>
       <c r="H14" s="14">
         <f>IFERROR(H13/H7,0)</f>
-        <v>0.105556857673905</v>
+        <v>0.160525866986308</v>
       </c>
     </row>
     <row r="15">
@@ -11047,7 +11067,7 @@
       </c>
       <c r="D15" s="18">
         <f>'2_손익계산서'!O46</f>
-        <v>65000</v>
+        <v>295000</v>
       </c>
       <c r="E15" s="18">
         <f>'2_손익계산서'!AB46</f>
@@ -11080,7 +11100,7 @@
       </c>
       <c r="D16" s="40">
         <f>'2_손익계산서'!O47</f>
-        <v>65000</v>
+        <v>295000</v>
       </c>
       <c r="E16" s="40">
         <f>'2_손익계산서'!AB47</f>
@@ -11181,23 +11201,23 @@
       </c>
       <c r="D19" s="25">
         <f>D13+D15-D17</f>
-        <v>-284917.342734463</v>
+        <v>-48905.1827344633</v>
       </c>
       <c r="E19" s="25">
         <f>E13+E15-E17</f>
-        <v>289535.378</v>
+        <v>520174.8408</v>
       </c>
       <c r="F19" s="25">
         <f>F13+F15-F17</f>
-        <v>1757662.69398429</v>
+        <v>3251540.94148028</v>
       </c>
       <c r="G19" s="25">
         <f>G13+G15-G17</f>
-        <v>5113430.45583219</v>
+        <v>8993660.92908651</v>
       </c>
       <c r="H19" s="25">
         <f>H13+H15-H17</f>
-        <v>15938869.7971292</v>
+        <v>24514035.249864</v>
       </c>
     </row>
     <row r="20">
@@ -11222,15 +11242,15 @@
       </c>
       <c r="F20" s="18">
         <f>'2_손익계산서'!AC51</f>
-        <v>0</v>
+        <v>129960.291900081</v>
       </c>
       <c r="G20" s="18">
         <f>'2_손익계산서'!AD51</f>
-        <v>823598.420718043</v>
+        <v>1956605.40439903</v>
       </c>
       <c r="H20" s="18">
         <f>'2_손익계산서'!AE51</f>
-        <v>3484551.35536842</v>
+        <v>5470396.53046709</v>
       </c>
     </row>
     <row r="21">
@@ -11249,27 +11269,27 @@
       </c>
       <c r="D21" s="37">
         <f>D19-D20</f>
-        <v>-284917.342734463</v>
+        <v>-48905.1827344633</v>
       </c>
       <c r="E21" s="37">
         <f>E19-E20</f>
-        <v>289535.378</v>
+        <v>520174.8408</v>
       </c>
       <c r="F21" s="37">
         <f>F19-F20</f>
-        <v>1757662.69398429</v>
+        <v>3121580.6495802</v>
       </c>
       <c r="G21" s="37">
         <f>G19-G20</f>
-        <v>4289832.03511415</v>
+        <v>7037055.52468748</v>
       </c>
       <c r="H21" s="37">
         <f>H19-H20</f>
-        <v>12454318.4417608</v>
+        <v>19043638.7193969</v>
       </c>
       <c r="I21" s="14">
         <f>IFERROR((H21/C21)^(1/5)-1,"n/a")</f>
-        <v>3.74693397338258</v>
+        <v>4.16772250041508</v>
       </c>
     </row>
     <row r="22">
@@ -11288,23 +11308,23 @@
       </c>
       <c r="D22" s="14">
         <f>IFERROR(D21/D7,0)</f>
-        <v>-0.237431118945386</v>
+        <v>-0.0407543189453861</v>
       </c>
       <c r="E22" s="14">
         <f>IFERROR(E21/E7,0)</f>
-        <v>0.0289476324829735</v>
+        <v>0.0520068746775658</v>
       </c>
       <c r="F22" s="14">
         <f>IFERROR(F21/F7,0)</f>
-        <v>0.0532625058783117</v>
+        <v>0.0945933530175819</v>
       </c>
       <c r="G22" s="14">
         <f>IFERROR(G21/G7,0)</f>
-        <v>0.061283314787345</v>
+        <v>0.100529364638393</v>
       </c>
       <c r="H22" s="14">
         <f>IFERROR(H21/H7,0)</f>
-        <v>0.0798353746266715</v>
+        <v>0.122074607175621</v>
       </c>
     </row>
     <row r="23">
@@ -11315,23 +11335,23 @@
       </c>
       <c r="D23" s="18">
         <f>'2_손익계산서'!O56</f>
-        <v>-274328.310734463</v>
+        <v>-268316.150734463</v>
       </c>
       <c r="E23" s="18">
         <f>'2_손익계산서'!AB56</f>
-        <v>762288.378</v>
+        <v>992927.8408</v>
       </c>
       <c r="F23" s="18">
         <f>'2_손익계산서'!AC56</f>
-        <v>2405615.69398429</v>
+        <v>3899493.94148028</v>
       </c>
       <c r="G23" s="18">
         <f>'2_손익계산서'!AD56</f>
-        <v>6073383.45583219</v>
+        <v>9953613.92908651</v>
       </c>
       <c r="H23" s="18">
         <f>'2_손익계산서'!AE56</f>
-        <v>17162822.7971292</v>
+        <v>25737988.249864</v>
       </c>
     </row>
     <row r="24">
@@ -31699,129 +31719,257 @@
     <row r="16">
       <c r="A16" s="15" t="inlineStr">
         <is>
-          <t>1인당 월 급여(천원)</t>
+          <t>기존 인력 1인당 월 평균급여(천원)</t>
         </is>
       </c>
       <c r="B16" s="7" t="inlineStr">
         <is>
-          <t>8_가정</t>
+          <t>급여대장 평균 × 인상률</t>
         </is>
       </c>
       <c r="C16" s="18">
-        <f>'8_가정'!$C$91</f>
-        <v>5670</v>
+        <f>'8_가정'!$C$92</f>
+        <v>4339</v>
       </c>
       <c r="D16" s="18">
-        <f>'8_가정'!$C$91</f>
-        <v>5670</v>
+        <f>'8_가정'!$C$92</f>
+        <v>4339</v>
       </c>
       <c r="E16" s="18">
-        <f>'8_가정'!$C$91</f>
-        <v>5670</v>
+        <f>'8_가정'!$C$92</f>
+        <v>4339</v>
       </c>
       <c r="F16" s="18">
-        <f>'8_가정'!$C$91</f>
-        <v>5670</v>
+        <f>'8_가정'!$C$92</f>
+        <v>4339</v>
       </c>
       <c r="G16" s="18">
-        <f>'8_가정'!$C$91</f>
-        <v>5670</v>
+        <f>'8_가정'!$C$92</f>
+        <v>4339</v>
       </c>
       <c r="H16" s="18">
-        <f>'8_가정'!$C$91</f>
-        <v>5670</v>
+        <f>'8_가정'!$C$92</f>
+        <v>4339</v>
       </c>
       <c r="I16" s="18">
-        <f>'8_가정'!$C$91</f>
-        <v>5670</v>
+        <f>'8_가정'!$C$92</f>
+        <v>4339</v>
       </c>
       <c r="J16" s="18">
-        <f>'8_가정'!$C$91</f>
-        <v>5670</v>
+        <f>'8_가정'!$C$92</f>
+        <v>4339</v>
       </c>
       <c r="K16" s="18">
-        <f>'8_가정'!$C$91</f>
-        <v>5670</v>
+        <f>'8_가정'!$C$92</f>
+        <v>4339</v>
       </c>
       <c r="L16" s="18">
-        <f>'8_가정'!$C$91</f>
-        <v>5670</v>
+        <f>'8_가정'!$C$92</f>
+        <v>4339</v>
       </c>
       <c r="M16" s="18">
-        <f>'8_가정'!$C$91</f>
-        <v>5670</v>
+        <f>'8_가정'!$C$92</f>
+        <v>4339</v>
       </c>
       <c r="N16" s="18">
-        <f>'8_가정'!$C$91</f>
-        <v>5670</v>
+        <f>'8_가정'!$C$92</f>
+        <v>4339</v>
       </c>
       <c r="O16" s="48">
-        <f>'8_가정'!$C$91</f>
-        <v>5670</v>
+        <f>'8_가정'!$C$92</f>
+        <v>4339</v>
       </c>
       <c r="P16" s="18">
-        <f>'8_가정'!$D$91</f>
-        <v>6066.9</v>
+        <f>'8_가정'!$D$92</f>
+        <v>4642.73</v>
       </c>
       <c r="Q16" s="18">
-        <f>'8_가정'!$D$91</f>
-        <v>6066.9</v>
+        <f>'8_가정'!$D$92</f>
+        <v>4642.73</v>
       </c>
       <c r="R16" s="18">
-        <f>'8_가정'!$D$91</f>
-        <v>6066.9</v>
+        <f>'8_가정'!$D$92</f>
+        <v>4642.73</v>
       </c>
       <c r="S16" s="18">
-        <f>'8_가정'!$D$91</f>
-        <v>6066.9</v>
+        <f>'8_가정'!$D$92</f>
+        <v>4642.73</v>
       </c>
       <c r="T16" s="18">
-        <f>'8_가정'!$D$91</f>
-        <v>6066.9</v>
+        <f>'8_가정'!$D$92</f>
+        <v>4642.73</v>
       </c>
       <c r="U16" s="18">
-        <f>'8_가정'!$D$91</f>
-        <v>6066.9</v>
+        <f>'8_가정'!$D$92</f>
+        <v>4642.73</v>
       </c>
       <c r="V16" s="18">
-        <f>'8_가정'!$D$91</f>
-        <v>6066.9</v>
+        <f>'8_가정'!$D$92</f>
+        <v>4642.73</v>
       </c>
       <c r="W16" s="18">
-        <f>'8_가정'!$D$91</f>
-        <v>6066.9</v>
+        <f>'8_가정'!$D$92</f>
+        <v>4642.73</v>
       </c>
       <c r="X16" s="18">
-        <f>'8_가정'!$D$91</f>
-        <v>6066.9</v>
+        <f>'8_가정'!$D$92</f>
+        <v>4642.73</v>
       </c>
       <c r="Y16" s="18">
-        <f>'8_가정'!$D$91</f>
-        <v>6066.9</v>
+        <f>'8_가정'!$D$92</f>
+        <v>4642.73</v>
       </c>
       <c r="Z16" s="18">
-        <f>'8_가정'!$D$91</f>
-        <v>6066.9</v>
+        <f>'8_가정'!$D$92</f>
+        <v>4642.73</v>
       </c>
       <c r="AA16" s="18">
-        <f>'8_가정'!$D$91</f>
-        <v>6066.9</v>
+        <f>'8_가정'!$D$92</f>
+        <v>4642.73</v>
       </c>
       <c r="AB16" s="48">
-        <f>'8_가정'!$D$91</f>
-        <v>6066.9</v>
+        <f>'8_가정'!$D$92</f>
+        <v>4642.73</v>
       </c>
       <c r="AC16" s="24">
-        <f>'8_가정'!$E$91</f>
-        <v>6491.583</v>
+        <f>'8_가정'!$E$92</f>
+        <v>4967.7211</v>
       </c>
       <c r="AD16" s="24">
-        <f>'8_가정'!$F$91</f>
-        <v>6945.99381</v>
+        <f>'8_가정'!$F$92</f>
+        <v>5315.461577</v>
       </c>
       <c r="AE16" s="24">
-        <f>'8_가정'!$G$91</f>
-        <v>7432.2133767</v>
+        <f>'8_가정'!$G$92</f>
+        <v>5687.54388739</v>
+      </c>
+    </row>
+    <row r="17">
+      <c r="A17" s="15" t="inlineStr">
+        <is>
+          <t>신규 채용 1인당 월 급여(천원)</t>
+        </is>
+      </c>
+      <c r="B17" s="7" t="inlineStr">
+        <is>
+          <t>고정(인상률 미적용)</t>
+        </is>
+      </c>
+      <c r="C17" s="18">
+        <f>'8_가정'!$C$94</f>
+        <v>4339</v>
+      </c>
+      <c r="D17" s="18">
+        <f>'8_가정'!$C$94</f>
+        <v>4339</v>
+      </c>
+      <c r="E17" s="18">
+        <f>'8_가정'!$C$94</f>
+        <v>4339</v>
+      </c>
+      <c r="F17" s="18">
+        <f>'8_가정'!$C$94</f>
+        <v>4339</v>
+      </c>
+      <c r="G17" s="18">
+        <f>'8_가정'!$C$94</f>
+        <v>4339</v>
+      </c>
+      <c r="H17" s="18">
+        <f>'8_가정'!$C$94</f>
+        <v>4339</v>
+      </c>
+      <c r="I17" s="18">
+        <f>'8_가정'!$C$94</f>
+        <v>4339</v>
+      </c>
+      <c r="J17" s="18">
+        <f>'8_가정'!$C$94</f>
+        <v>4339</v>
+      </c>
+      <c r="K17" s="18">
+        <f>'8_가정'!$C$94</f>
+        <v>4339</v>
+      </c>
+      <c r="L17" s="18">
+        <f>'8_가정'!$C$94</f>
+        <v>4339</v>
+      </c>
+      <c r="M17" s="18">
+        <f>'8_가정'!$C$94</f>
+        <v>4339</v>
+      </c>
+      <c r="N17" s="18">
+        <f>'8_가정'!$C$94</f>
+        <v>4339</v>
+      </c>
+      <c r="O17" s="48">
+        <f>'8_가정'!$C$94</f>
+        <v>4339</v>
+      </c>
+      <c r="P17" s="18">
+        <f>'8_가정'!$C$94</f>
+        <v>4339</v>
+      </c>
+      <c r="Q17" s="18">
+        <f>'8_가정'!$C$94</f>
+        <v>4339</v>
+      </c>
+      <c r="R17" s="18">
+        <f>'8_가정'!$C$94</f>
+        <v>4339</v>
+      </c>
+      <c r="S17" s="18">
+        <f>'8_가정'!$C$94</f>
+        <v>4339</v>
+      </c>
+      <c r="T17" s="18">
+        <f>'8_가정'!$C$94</f>
+        <v>4339</v>
+      </c>
+      <c r="U17" s="18">
+        <f>'8_가정'!$C$94</f>
+        <v>4339</v>
+      </c>
+      <c r="V17" s="18">
+        <f>'8_가정'!$C$94</f>
+        <v>4339</v>
+      </c>
+      <c r="W17" s="18">
+        <f>'8_가정'!$C$94</f>
+        <v>4339</v>
+      </c>
+      <c r="X17" s="18">
+        <f>'8_가정'!$C$94</f>
+        <v>4339</v>
+      </c>
+      <c r="Y17" s="18">
+        <f>'8_가정'!$C$94</f>
+        <v>4339</v>
+      </c>
+      <c r="Z17" s="18">
+        <f>'8_가정'!$C$94</f>
+        <v>4339</v>
+      </c>
+      <c r="AA17" s="18">
+        <f>'8_가정'!$C$94</f>
+        <v>4339</v>
+      </c>
+      <c r="AB17" s="48">
+        <f>'8_가정'!$C$94</f>
+        <v>4339</v>
+      </c>
+      <c r="AC17" s="24">
+        <f>'8_가정'!$C$94</f>
+        <v>4339</v>
+      </c>
+      <c r="AD17" s="24">
+        <f>'8_가정'!$C$94</f>
+        <v>4339</v>
+      </c>
+      <c r="AE17" s="24">
+        <f>'8_가정'!$C$94</f>
+        <v>4339</v>
       </c>
     </row>
     <row r="18">
@@ -31842,125 +31990,125 @@
           <t>인원 × 월급여</t>
         </is>
       </c>
-      <c r="C19" s="43">
-        <f>C15*C16</f>
-        <v>39690</v>
-      </c>
-      <c r="D19" s="43">
-        <f>D15*D16</f>
-        <v>39690</v>
-      </c>
-      <c r="E19" s="43">
-        <f>E15*E16</f>
-        <v>39690</v>
-      </c>
-      <c r="F19" s="43">
-        <f>F15*F16</f>
-        <v>39690</v>
-      </c>
-      <c r="G19" s="43">
-        <f>G15*G16</f>
-        <v>39690</v>
-      </c>
-      <c r="H19" s="43">
-        <f>H15*H16</f>
-        <v>39690</v>
-      </c>
-      <c r="I19" s="43">
-        <f>I15*I16</f>
-        <v>39690</v>
-      </c>
-      <c r="J19" s="43">
-        <f>J15*J16</f>
-        <v>39690</v>
-      </c>
-      <c r="K19" s="43">
-        <f>K15*K16</f>
-        <v>39690</v>
-      </c>
-      <c r="L19" s="43">
-        <f>L15*L16</f>
-        <v>45360</v>
-      </c>
-      <c r="M19" s="43">
-        <f>M15*M16</f>
-        <v>45360</v>
-      </c>
-      <c r="N19" s="43">
-        <f>N15*N16</f>
-        <v>51030</v>
+      <c r="C19" s="18">
+        <f>('8_가정'!$C$91+MIN(MAX(C15-1,0),'8_가정'!$C$95-1)*C16+MAX(0,C15-'8_가정'!$C$95)*C17)</f>
+        <v>39723</v>
+      </c>
+      <c r="D19" s="18">
+        <f>('8_가정'!$C$91+MIN(MAX(D15-1,0),'8_가정'!$C$95-1)*D16+MAX(0,D15-'8_가정'!$C$95)*D17)</f>
+        <v>39723</v>
+      </c>
+      <c r="E19" s="18">
+        <f>('8_가정'!$C$91+MIN(MAX(E15-1,0),'8_가정'!$C$95-1)*E16+MAX(0,E15-'8_가정'!$C$95)*E17)</f>
+        <v>39723</v>
+      </c>
+      <c r="F19" s="18">
+        <f>('8_가정'!$C$91+MIN(MAX(F15-1,0),'8_가정'!$C$95-1)*F16+MAX(0,F15-'8_가정'!$C$95)*F17)</f>
+        <v>39723</v>
+      </c>
+      <c r="G19" s="18">
+        <f>('8_가정'!$C$91+MIN(MAX(G15-1,0),'8_가정'!$C$95-1)*G16+MAX(0,G15-'8_가정'!$C$95)*G17)</f>
+        <v>39723</v>
+      </c>
+      <c r="H19" s="18">
+        <f>('8_가정'!$C$91+MIN(MAX(H15-1,0),'8_가정'!$C$95-1)*H16+MAX(0,H15-'8_가정'!$C$95)*H17)</f>
+        <v>39723</v>
+      </c>
+      <c r="I19" s="18">
+        <f>('8_가정'!$C$91+MIN(MAX(I15-1,0),'8_가정'!$C$95-1)*I16+MAX(0,I15-'8_가정'!$C$95)*I17)</f>
+        <v>39723</v>
+      </c>
+      <c r="J19" s="18">
+        <f>('8_가정'!$C$91+MIN(MAX(J15-1,0),'8_가정'!$C$95-1)*J16+MAX(0,J15-'8_가정'!$C$95)*J17)</f>
+        <v>39723</v>
+      </c>
+      <c r="K19" s="18">
+        <f>('8_가정'!$C$91+MIN(MAX(K15-1,0),'8_가정'!$C$95-1)*K16+MAX(0,K15-'8_가정'!$C$95)*K17)</f>
+        <v>39723</v>
+      </c>
+      <c r="L19" s="18">
+        <f>('8_가정'!$C$91+MIN(MAX(L15-1,0),'8_가정'!$C$95-1)*L16+MAX(0,L15-'8_가정'!$C$95)*L17)</f>
+        <v>44062</v>
+      </c>
+      <c r="M19" s="18">
+        <f>('8_가정'!$C$91+MIN(MAX(M15-1,0),'8_가정'!$C$95-1)*M16+MAX(0,M15-'8_가정'!$C$95)*M17)</f>
+        <v>44062</v>
+      </c>
+      <c r="N19" s="18">
+        <f>('8_가정'!$C$91+MIN(MAX(N15-1,0),'8_가정'!$C$95-1)*N16+MAX(0,N15-'8_가정'!$C$95)*N17)</f>
+        <v>48401</v>
       </c>
       <c r="O19" s="23">
         <f>SUM(C19:N19)</f>
-        <v>498960</v>
-      </c>
-      <c r="P19" s="43">
-        <f>P15*P16</f>
-        <v>60669</v>
-      </c>
-      <c r="Q19" s="43">
-        <f>Q15*Q16</f>
-        <v>66735.9</v>
-      </c>
-      <c r="R19" s="43">
-        <f>R15*R16</f>
-        <v>72802.8</v>
-      </c>
-      <c r="S19" s="43">
-        <f>S15*S16</f>
-        <v>78869.7</v>
-      </c>
-      <c r="T19" s="43">
-        <f>T15*T16</f>
-        <v>84936.6</v>
-      </c>
-      <c r="U19" s="43">
-        <f>U15*U16</f>
-        <v>91003.5</v>
-      </c>
-      <c r="V19" s="43">
-        <f>V15*V16</f>
-        <v>97070.4</v>
-      </c>
-      <c r="W19" s="43">
-        <f>W15*W16</f>
-        <v>103137.3</v>
-      </c>
-      <c r="X19" s="43">
-        <f>X15*X16</f>
-        <v>109204.2</v>
-      </c>
-      <c r="Y19" s="43">
-        <f>Y15*Y16</f>
-        <v>115271.1</v>
-      </c>
-      <c r="Z19" s="43">
-        <f>Z15*Z16</f>
-        <v>121338</v>
-      </c>
-      <c r="AA19" s="43">
-        <f>AA15*AA16</f>
-        <v>133471.8</v>
+        <v>494032</v>
+      </c>
+      <c r="P19" s="18">
+        <f>('8_가정'!$C$91+MIN(MAX(P15-1,0),'8_가정'!$C$95-1)*P16+MAX(0,P15-'8_가정'!$C$95)*P17)</f>
+        <v>54562.38</v>
+      </c>
+      <c r="Q19" s="18">
+        <f>('8_가정'!$C$91+MIN(MAX(Q15-1,0),'8_가정'!$C$95-1)*Q16+MAX(0,Q15-'8_가정'!$C$95)*Q17)</f>
+        <v>58901.38</v>
+      </c>
+      <c r="R19" s="18">
+        <f>('8_가정'!$C$91+MIN(MAX(R15-1,0),'8_가정'!$C$95-1)*R16+MAX(0,R15-'8_가정'!$C$95)*R17)</f>
+        <v>63240.38</v>
+      </c>
+      <c r="S19" s="18">
+        <f>('8_가정'!$C$91+MIN(MAX(S15-1,0),'8_가정'!$C$95-1)*S16+MAX(0,S15-'8_가정'!$C$95)*S17)</f>
+        <v>67579.38</v>
+      </c>
+      <c r="T19" s="18">
+        <f>('8_가정'!$C$91+MIN(MAX(T15-1,0),'8_가정'!$C$95-1)*T16+MAX(0,T15-'8_가정'!$C$95)*T17)</f>
+        <v>71918.38</v>
+      </c>
+      <c r="U19" s="18">
+        <f>('8_가정'!$C$91+MIN(MAX(U15-1,0),'8_가정'!$C$95-1)*U16+MAX(0,U15-'8_가정'!$C$95)*U17)</f>
+        <v>76257.38</v>
+      </c>
+      <c r="V19" s="18">
+        <f>('8_가정'!$C$91+MIN(MAX(V15-1,0),'8_가정'!$C$95-1)*V16+MAX(0,V15-'8_가정'!$C$95)*V17)</f>
+        <v>80596.38</v>
+      </c>
+      <c r="W19" s="18">
+        <f>('8_가정'!$C$91+MIN(MAX(W15-1,0),'8_가정'!$C$95-1)*W16+MAX(0,W15-'8_가정'!$C$95)*W17)</f>
+        <v>84935.38</v>
+      </c>
+      <c r="X19" s="18">
+        <f>('8_가정'!$C$91+MIN(MAX(X15-1,0),'8_가정'!$C$95-1)*X16+MAX(0,X15-'8_가정'!$C$95)*X17)</f>
+        <v>89274.38</v>
+      </c>
+      <c r="Y19" s="18">
+        <f>('8_가정'!$C$91+MIN(MAX(Y15-1,0),'8_가정'!$C$95-1)*Y16+MAX(0,Y15-'8_가정'!$C$95)*Y17)</f>
+        <v>93613.38</v>
+      </c>
+      <c r="Z19" s="18">
+        <f>('8_가정'!$C$91+MIN(MAX(Z15-1,0),'8_가정'!$C$95-1)*Z16+MAX(0,Z15-'8_가정'!$C$95)*Z17)</f>
+        <v>97952.38</v>
+      </c>
+      <c r="AA19" s="18">
+        <f>('8_가정'!$C$91+MIN(MAX(AA15-1,0),'8_가정'!$C$95-1)*AA16+MAX(0,AA15-'8_가정'!$C$95)*AA17)</f>
+        <v>106630.38</v>
       </c>
       <c r="AB19" s="23">
         <f>SUM(P19:AA19)</f>
-        <v>1134510.3</v>
-      </c>
-      <c r="AC19" s="45">
-        <f>AC15*AC16*12</f>
-        <v>4167596.286</v>
-      </c>
-      <c r="AD19" s="45">
-        <f>AD15*AD16*12</f>
-        <v>8960332.0149</v>
-      </c>
-      <c r="AE19" s="45">
-        <f>AE15*AE16*12</f>
-        <v>17391379.301478</v>
+        <v>945461.56</v>
+      </c>
+      <c r="AC19" s="24">
+        <f>('8_가정'!$C$91+MIN(MAX(AC15-1,0),'8_가정'!$C$95-1)*AC16+MAX(0,AC15-'8_가정'!$C$95)*AC17)*12</f>
+        <v>2943105.9192</v>
+      </c>
+      <c r="AD19" s="24">
+        <f>('8_가정'!$C$91+MIN(MAX(AD15-1,0),'8_가정'!$C$95-1)*AD16+MAX(0,AD15-'8_가정'!$C$95)*AD17)*12</f>
+        <v>5779815.233544</v>
+      </c>
+      <c r="AE19" s="24">
+        <f>('8_가정'!$C$91+MIN(MAX(AE15-1,0),'8_가정'!$C$95-1)*AE16+MAX(0,AE15-'8_가정'!$C$95)*AE17)*12</f>
+        <v>10362555.1598921</v>
       </c>
       <c r="AF19" s="25">
         <f>O19+AB19+AC19+AD19+AE19</f>
-        <v>32152777.902378</v>
+        <v>20524969.8726361</v>
       </c>
     </row>
     <row r="20">
@@ -31975,124 +32123,124 @@
         </is>
       </c>
       <c r="C20" s="18">
-        <f>C19*'8_가정'!$C$93</f>
-        <v>8731.8</v>
+        <f>C19*'8_가정'!$C$96</f>
+        <v>8739.06</v>
       </c>
       <c r="D20" s="18">
-        <f>D19*'8_가정'!$C$93</f>
-        <v>8731.8</v>
+        <f>D19*'8_가정'!$C$96</f>
+        <v>8739.06</v>
       </c>
       <c r="E20" s="18">
-        <f>E19*'8_가정'!$C$93</f>
-        <v>8731.8</v>
+        <f>E19*'8_가정'!$C$96</f>
+        <v>8739.06</v>
       </c>
       <c r="F20" s="18">
-        <f>F19*'8_가정'!$C$93</f>
-        <v>8731.8</v>
+        <f>F19*'8_가정'!$C$96</f>
+        <v>8739.06</v>
       </c>
       <c r="G20" s="18">
-        <f>G19*'8_가정'!$C$93</f>
-        <v>8731.8</v>
+        <f>G19*'8_가정'!$C$96</f>
+        <v>8739.06</v>
       </c>
       <c r="H20" s="18">
-        <f>H19*'8_가정'!$C$93</f>
-        <v>8731.8</v>
+        <f>H19*'8_가정'!$C$96</f>
+        <v>8739.06</v>
       </c>
       <c r="I20" s="18">
-        <f>I19*'8_가정'!$C$93</f>
-        <v>8731.8</v>
+        <f>I19*'8_가정'!$C$96</f>
+        <v>8739.06</v>
       </c>
       <c r="J20" s="18">
-        <f>J19*'8_가정'!$C$93</f>
-        <v>8731.8</v>
+        <f>J19*'8_가정'!$C$96</f>
+        <v>8739.06</v>
       </c>
       <c r="K20" s="18">
-        <f>K19*'8_가정'!$C$93</f>
-        <v>8731.8</v>
+        <f>K19*'8_가정'!$C$96</f>
+        <v>8739.06</v>
       </c>
       <c r="L20" s="18">
-        <f>L19*'8_가정'!$C$93</f>
-        <v>9979.2</v>
+        <f>L19*'8_가정'!$C$96</f>
+        <v>9693.64</v>
       </c>
       <c r="M20" s="18">
-        <f>M19*'8_가정'!$C$93</f>
-        <v>9979.2</v>
+        <f>M19*'8_가정'!$C$96</f>
+        <v>9693.64</v>
       </c>
       <c r="N20" s="18">
-        <f>N19*'8_가정'!$C$93</f>
-        <v>11226.6</v>
+        <f>N19*'8_가정'!$C$96</f>
+        <v>10648.22</v>
       </c>
       <c r="O20" s="23">
         <f>SUM(C20:N20)</f>
-        <v>109771.2</v>
+        <v>108687.04</v>
       </c>
       <c r="P20" s="18">
-        <f>P19*'8_가정'!$C$93</f>
-        <v>13347.18</v>
+        <f>P19*'8_가정'!$C$96</f>
+        <v>12003.7236</v>
       </c>
       <c r="Q20" s="18">
-        <f>Q19*'8_가정'!$C$93</f>
-        <v>14681.898</v>
+        <f>Q19*'8_가정'!$C$96</f>
+        <v>12958.3036</v>
       </c>
       <c r="R20" s="18">
-        <f>R19*'8_가정'!$C$93</f>
-        <v>16016.616</v>
+        <f>R19*'8_가정'!$C$96</f>
+        <v>13912.8836</v>
       </c>
       <c r="S20" s="18">
-        <f>S19*'8_가정'!$C$93</f>
-        <v>17351.334</v>
+        <f>S19*'8_가정'!$C$96</f>
+        <v>14867.4636</v>
       </c>
       <c r="T20" s="18">
-        <f>T19*'8_가정'!$C$93</f>
-        <v>18686.052</v>
+        <f>T19*'8_가정'!$C$96</f>
+        <v>15822.0436</v>
       </c>
       <c r="U20" s="18">
-        <f>U19*'8_가정'!$C$93</f>
-        <v>20020.77</v>
+        <f>U19*'8_가정'!$C$96</f>
+        <v>16776.6236</v>
       </c>
       <c r="V20" s="18">
-        <f>V19*'8_가정'!$C$93</f>
-        <v>21355.488</v>
+        <f>V19*'8_가정'!$C$96</f>
+        <v>17731.2036</v>
       </c>
       <c r="W20" s="18">
-        <f>W19*'8_가정'!$C$93</f>
-        <v>22690.206</v>
+        <f>W19*'8_가정'!$C$96</f>
+        <v>18685.7836</v>
       </c>
       <c r="X20" s="18">
-        <f>X19*'8_가정'!$C$93</f>
-        <v>24024.924</v>
+        <f>X19*'8_가정'!$C$96</f>
+        <v>19640.3636</v>
       </c>
       <c r="Y20" s="18">
-        <f>Y19*'8_가정'!$C$93</f>
-        <v>25359.642</v>
+        <f>Y19*'8_가정'!$C$96</f>
+        <v>20594.9436</v>
       </c>
       <c r="Z20" s="18">
-        <f>Z19*'8_가정'!$C$93</f>
-        <v>26694.36</v>
+        <f>Z19*'8_가정'!$C$96</f>
+        <v>21549.5236</v>
       </c>
       <c r="AA20" s="18">
-        <f>AA19*'8_가정'!$C$93</f>
-        <v>29363.796</v>
+        <f>AA19*'8_가정'!$C$96</f>
+        <v>23458.6836</v>
       </c>
       <c r="AB20" s="23">
         <f>SUM(P20:AA20)</f>
-        <v>249592.266</v>
+        <v>208001.5432</v>
       </c>
       <c r="AC20" s="24">
-        <f>AC19*'8_가정'!$C$93</f>
-        <v>916871.18292</v>
+        <f>AC19*'8_가정'!$C$96</f>
+        <v>647483.302224</v>
       </c>
       <c r="AD20" s="24">
-        <f>AD19*'8_가정'!$C$93</f>
-        <v>1971273.043278</v>
+        <f>AD19*'8_가정'!$C$96</f>
+        <v>1271559.35137968</v>
       </c>
       <c r="AE20" s="24">
-        <f>AE19*'8_가정'!$C$93</f>
-        <v>3826103.44632516</v>
+        <f>AE19*'8_가정'!$C$96</f>
+        <v>2279762.13517626</v>
       </c>
       <c r="AF20" s="25">
         <f>O20+AB20+AC20+AD20+AE20</f>
-        <v>7073611.13852316</v>
+        <v>4515493.37197994</v>
       </c>
     </row>
     <row r="21">
@@ -32107,51 +32255,51 @@
         </is>
       </c>
       <c r="C21" s="18">
-        <f>C8*'8_가정'!$C$94</f>
+        <f>C8*'8_가정'!$C$97</f>
         <v>1011.68417406511</v>
       </c>
       <c r="D21" s="18">
-        <f>D8*'8_가정'!$C$94</f>
+        <f>D8*'8_가정'!$C$97</f>
         <v>1037.10790287867</v>
       </c>
       <c r="E21" s="18">
-        <f>E8*'8_가정'!$C$94</f>
+        <f>E8*'8_가정'!$C$97</f>
         <v>1062.53163169222</v>
       </c>
       <c r="F21" s="18">
-        <f>F8*'8_가정'!$C$94</f>
+        <f>F8*'8_가정'!$C$97</f>
         <v>1087.95536050578</v>
       </c>
       <c r="G21" s="18">
-        <f>G8*'8_가정'!$C$94</f>
+        <f>G8*'8_가정'!$C$97</f>
         <v>1113.37908931934</v>
       </c>
       <c r="H21" s="18">
-        <f>H8*'8_가정'!$C$94</f>
+        <f>H8*'8_가정'!$C$97</f>
         <v>1138.8028181329</v>
       </c>
       <c r="I21" s="18">
-        <f>I8*'8_가정'!$C$94</f>
+        <f>I8*'8_가정'!$C$97</f>
         <v>1420.89321361313</v>
       </c>
       <c r="J21" s="18">
-        <f>J8*'8_가정'!$C$94</f>
+        <f>J8*'8_가정'!$C$97</f>
         <v>1552.98360909335</v>
       </c>
       <c r="K21" s="18">
-        <f>K8*'8_가정'!$C$94</f>
+        <f>K8*'8_가정'!$C$97</f>
         <v>1685.07400457358</v>
       </c>
       <c r="L21" s="18">
-        <f>L8*'8_가정'!$C$94</f>
+        <f>L8*'8_가정'!$C$97</f>
         <v>1886.60884449825</v>
       </c>
       <c r="M21" s="18">
-        <f>M8*'8_가정'!$C$94</f>
+        <f>M8*'8_가정'!$C$97</f>
         <v>2207.24368442292</v>
       </c>
       <c r="N21" s="18">
-        <f>N8*'8_가정'!$C$94</f>
+        <f>N8*'8_가정'!$C$97</f>
         <v>2795.73566720473</v>
       </c>
       <c r="O21" s="23">
@@ -32159,51 +32307,51 @@
         <v>18000</v>
       </c>
       <c r="P21" s="18">
-        <f>P8*'8_가정'!$D$94</f>
+        <f>P8*'8_가정'!$D$97</f>
         <v>7150.15367455834</v>
       </c>
       <c r="Q21" s="18">
-        <f>Q8*'8_가정'!$D$94</f>
+        <f>Q8*'8_가정'!$D$97</f>
         <v>9923.59701187443</v>
       </c>
       <c r="R21" s="18">
-        <f>R8*'8_가정'!$D$94</f>
+        <f>R8*'8_가정'!$D$97</f>
         <v>12697.0403491905</v>
       </c>
       <c r="S21" s="18">
-        <f>S8*'8_가정'!$D$94</f>
+        <f>S8*'8_가정'!$D$97</f>
         <v>15428.1108051507</v>
       </c>
       <c r="T21" s="18">
-        <f>T8*'8_가정'!$D$94</f>
+        <f>T8*'8_가정'!$D$97</f>
         <v>18159.1812611108</v>
       </c>
       <c r="U21" s="18">
-        <f>U8*'8_가정'!$D$94</f>
+        <f>U8*'8_가정'!$D$97</f>
         <v>22390.251717071</v>
       </c>
       <c r="V21" s="18">
-        <f>V8*'8_가정'!$D$94</f>
+        <f>V8*'8_가정'!$D$97</f>
         <v>24943.5443952534</v>
       </c>
       <c r="W21" s="18">
-        <f>W8*'8_가정'!$D$94</f>
+        <f>W8*'8_가정'!$D$97</f>
         <v>27237.0331518672</v>
       </c>
       <c r="X21" s="18">
-        <f>X8*'8_가정'!$D$94</f>
+        <f>X8*'8_가정'!$D$97</f>
         <v>28030.5219084809</v>
       </c>
       <c r="Y21" s="18">
-        <f>Y8*'8_가정'!$D$94</f>
+        <f>Y8*'8_가정'!$D$97</f>
         <v>28030.5219084809</v>
       </c>
       <c r="Z21" s="18">
-        <f>Z8*'8_가정'!$D$94</f>
+        <f>Z8*'8_가정'!$D$97</f>
         <v>28030.5219084809</v>
       </c>
       <c r="AA21" s="18">
-        <f>AA8*'8_가정'!$D$94</f>
+        <f>AA8*'8_가정'!$D$97</f>
         <v>28030.5219084809</v>
       </c>
       <c r="AB21" s="23">
@@ -32211,15 +32359,15 @@
         <v>250051</v>
       </c>
       <c r="AC21" s="24">
-        <f>AC8*'8_가정'!$E$94</f>
+        <f>AC8*'8_가정'!$E$97</f>
         <v>924000</v>
       </c>
       <c r="AD21" s="24">
-        <f>AD8*'8_가정'!$F$94</f>
+        <f>AD8*'8_가정'!$F$97</f>
         <v>1820000</v>
       </c>
       <c r="AE21" s="24">
-        <f>AE8*'8_가정'!$G$94</f>
+        <f>AE8*'8_가정'!$G$97</f>
         <v>4680000</v>
       </c>
       <c r="AF21" s="25">
@@ -32239,51 +32387,51 @@
         </is>
       </c>
       <c r="C22" s="18">
-        <f>C8*'8_가정'!$C$95</f>
+        <f>C8*'8_가정'!$C$98</f>
         <v>809.347339252085</v>
       </c>
       <c r="D22" s="18">
-        <f>D8*'8_가정'!$C$95</f>
+        <f>D8*'8_가정'!$C$98</f>
         <v>829.686322302932</v>
       </c>
       <c r="E22" s="18">
-        <f>E8*'8_가정'!$C$95</f>
+        <f>E8*'8_가정'!$C$98</f>
         <v>850.02530535378</v>
       </c>
       <c r="F22" s="18">
-        <f>F8*'8_가정'!$C$95</f>
+        <f>F8*'8_가정'!$C$98</f>
         <v>870.364288404627</v>
       </c>
       <c r="G22" s="18">
-        <f>G8*'8_가정'!$C$95</f>
+        <f>G8*'8_가정'!$C$98</f>
         <v>890.703271455475</v>
       </c>
       <c r="H22" s="18">
-        <f>H8*'8_가정'!$C$95</f>
+        <f>H8*'8_가정'!$C$98</f>
         <v>911.042254506322</v>
       </c>
       <c r="I22" s="18">
-        <f>I8*'8_가정'!$C$95</f>
+        <f>I8*'8_가정'!$C$98</f>
         <v>1136.7145708905</v>
       </c>
       <c r="J22" s="18">
-        <f>J8*'8_가정'!$C$95</f>
+        <f>J8*'8_가정'!$C$98</f>
         <v>1242.38688727468</v>
       </c>
       <c r="K22" s="18">
-        <f>K8*'8_가정'!$C$95</f>
+        <f>K8*'8_가정'!$C$98</f>
         <v>1348.05920365886</v>
       </c>
       <c r="L22" s="18">
-        <f>L8*'8_가정'!$C$95</f>
+        <f>L8*'8_가정'!$C$98</f>
         <v>1509.2870755986</v>
       </c>
       <c r="M22" s="18">
-        <f>M8*'8_가정'!$C$95</f>
+        <f>M8*'8_가정'!$C$98</f>
         <v>1765.79494753834</v>
       </c>
       <c r="N22" s="18">
-        <f>N8*'8_가정'!$C$95</f>
+        <f>N8*'8_가정'!$C$98</f>
         <v>2236.58853376379</v>
       </c>
       <c r="O22" s="23">
@@ -32291,51 +32439,51 @@
         <v>14400</v>
       </c>
       <c r="P22" s="18">
-        <f>P8*'8_가정'!$D$95</f>
+        <f>P8*'8_가정'!$D$98</f>
         <v>5720.12293964667</v>
       </c>
       <c r="Q22" s="18">
-        <f>Q8*'8_가정'!$D$95</f>
+        <f>Q8*'8_가정'!$D$98</f>
         <v>7938.87760949954</v>
       </c>
       <c r="R22" s="18">
-        <f>R8*'8_가정'!$D$95</f>
+        <f>R8*'8_가정'!$D$98</f>
         <v>10157.6322793524</v>
       </c>
       <c r="S22" s="18">
-        <f>S8*'8_가정'!$D$95</f>
+        <f>S8*'8_가정'!$D$98</f>
         <v>12342.4886441205</v>
       </c>
       <c r="T22" s="18">
-        <f>T8*'8_가정'!$D$95</f>
+        <f>T8*'8_가정'!$D$98</f>
         <v>14527.3450088887</v>
       </c>
       <c r="U22" s="18">
-        <f>U8*'8_가정'!$D$95</f>
+        <f>U8*'8_가정'!$D$98</f>
         <v>17912.2013736568</v>
       </c>
       <c r="V22" s="18">
-        <f>V8*'8_가정'!$D$95</f>
+        <f>V8*'8_가정'!$D$98</f>
         <v>19954.8355162027</v>
       </c>
       <c r="W22" s="18">
-        <f>W8*'8_가정'!$D$95</f>
+        <f>W8*'8_가정'!$D$98</f>
         <v>21789.6265214937</v>
       </c>
       <c r="X22" s="18">
-        <f>X8*'8_가정'!$D$95</f>
+        <f>X8*'8_가정'!$D$98</f>
         <v>22424.4175267847</v>
       </c>
       <c r="Y22" s="18">
-        <f>Y8*'8_가정'!$D$95</f>
+        <f>Y8*'8_가정'!$D$98</f>
         <v>22424.4175267847</v>
       </c>
       <c r="Z22" s="18">
-        <f>Z8*'8_가정'!$D$95</f>
+        <f>Z8*'8_가정'!$D$98</f>
         <v>22424.4175267847</v>
       </c>
       <c r="AA22" s="18">
-        <f>AA8*'8_가정'!$D$95</f>
+        <f>AA8*'8_가정'!$D$98</f>
         <v>22424.4175267847</v>
       </c>
       <c r="AB22" s="23">
@@ -32343,15 +32491,15 @@
         <v>200040.8</v>
       </c>
       <c r="AC22" s="24">
-        <f>AC8*'8_가정'!$E$95</f>
+        <f>AC8*'8_가정'!$E$98</f>
         <v>726000</v>
       </c>
       <c r="AD22" s="24">
-        <f>AD8*'8_가정'!$F$95</f>
+        <f>AD8*'8_가정'!$F$98</f>
         <v>1540000</v>
       </c>
       <c r="AE22" s="24">
-        <f>AE8*'8_가정'!$G$95</f>
+        <f>AE8*'8_가정'!$G$98</f>
         <v>3432000</v>
       </c>
       <c r="AF22" s="25">
@@ -32371,51 +32519,51 @@
         </is>
       </c>
       <c r="C23" s="18">
-        <f>C8*'8_가정'!$C$96</f>
+        <f>C8*'8_가정'!$C$99</f>
         <v>1686.14029010851</v>
       </c>
       <c r="D23" s="18">
-        <f>D8*'8_가정'!$C$96</f>
+        <f>D8*'8_가정'!$C$99</f>
         <v>1728.51317146444</v>
       </c>
       <c r="E23" s="18">
-        <f>E8*'8_가정'!$C$96</f>
+        <f>E8*'8_가정'!$C$99</f>
         <v>1770.88605282037</v>
       </c>
       <c r="F23" s="18">
-        <f>F8*'8_가정'!$C$96</f>
+        <f>F8*'8_가정'!$C$99</f>
         <v>1813.25893417631</v>
       </c>
       <c r="G23" s="18">
-        <f>G8*'8_가정'!$C$96</f>
+        <f>G8*'8_가정'!$C$99</f>
         <v>1855.63181553224</v>
       </c>
       <c r="H23" s="18">
-        <f>H8*'8_가정'!$C$96</f>
+        <f>H8*'8_가정'!$C$99</f>
         <v>1898.00469688817</v>
       </c>
       <c r="I23" s="18">
-        <f>I8*'8_가정'!$C$96</f>
+        <f>I8*'8_가정'!$C$99</f>
         <v>2368.15535602188</v>
       </c>
       <c r="J23" s="18">
-        <f>J8*'8_가정'!$C$96</f>
+        <f>J8*'8_가정'!$C$99</f>
         <v>2588.30601515559</v>
       </c>
       <c r="K23" s="18">
-        <f>K8*'8_가정'!$C$96</f>
+        <f>K8*'8_가정'!$C$99</f>
         <v>2808.4566742893</v>
       </c>
       <c r="L23" s="18">
-        <f>L8*'8_가정'!$C$96</f>
+        <f>L8*'8_가정'!$C$99</f>
         <v>3144.34807416375</v>
       </c>
       <c r="M23" s="18">
-        <f>M8*'8_가정'!$C$96</f>
+        <f>M8*'8_가정'!$C$99</f>
         <v>3678.7394740382</v>
       </c>
       <c r="N23" s="18">
-        <f>N8*'8_가정'!$C$96</f>
+        <f>N8*'8_가정'!$C$99</f>
         <v>4659.55944534123</v>
       </c>
       <c r="O23" s="23">
@@ -32423,51 +32571,51 @@
         <v>30000</v>
       </c>
       <c r="P23" s="18">
-        <f>P8*'8_가정'!$D$96</f>
+        <f>P8*'8_가정'!$D$99</f>
         <v>10010.2151443817</v>
       </c>
       <c r="Q23" s="18">
-        <f>Q8*'8_가정'!$D$96</f>
+        <f>Q8*'8_가정'!$D$99</f>
         <v>13893.0358166242</v>
       </c>
       <c r="R23" s="18">
-        <f>R8*'8_가정'!$D$96</f>
+        <f>R8*'8_가정'!$D$99</f>
         <v>17775.8564888667</v>
       </c>
       <c r="S23" s="18">
-        <f>S8*'8_가정'!$D$96</f>
+        <f>S8*'8_가정'!$D$99</f>
         <v>21599.355127211</v>
       </c>
       <c r="T23" s="18">
-        <f>T8*'8_가정'!$D$96</f>
+        <f>T8*'8_가정'!$D$99</f>
         <v>25422.8537655552</v>
       </c>
       <c r="U23" s="18">
-        <f>U8*'8_가정'!$D$96</f>
+        <f>U8*'8_가정'!$D$99</f>
         <v>31346.3524038994</v>
       </c>
       <c r="V23" s="18">
-        <f>V8*'8_가정'!$D$96</f>
+        <f>V8*'8_가정'!$D$99</f>
         <v>34920.9621533548</v>
       </c>
       <c r="W23" s="18">
-        <f>W8*'8_가정'!$D$96</f>
+        <f>W8*'8_가정'!$D$99</f>
         <v>38131.846412614</v>
       </c>
       <c r="X23" s="18">
-        <f>X8*'8_가정'!$D$96</f>
+        <f>X8*'8_가정'!$D$99</f>
         <v>39242.7306718733</v>
       </c>
       <c r="Y23" s="18">
-        <f>Y8*'8_가정'!$D$96</f>
+        <f>Y8*'8_가정'!$D$99</f>
         <v>39242.7306718733</v>
       </c>
       <c r="Z23" s="18">
-        <f>Z8*'8_가정'!$D$96</f>
+        <f>Z8*'8_가정'!$D$99</f>
         <v>39242.7306718733</v>
       </c>
       <c r="AA23" s="18">
-        <f>AA8*'8_가정'!$D$96</f>
+        <f>AA8*'8_가정'!$D$99</f>
         <v>39242.7306718733</v>
       </c>
       <c r="AB23" s="23">
@@ -32475,15 +32623,15 @@
         <v>350071.4</v>
       </c>
       <c r="AC23" s="24">
-        <f>AC8*'8_가정'!$E$96</f>
+        <f>AC8*'8_가정'!$E$99</f>
         <v>1155000</v>
       </c>
       <c r="AD23" s="24">
-        <f>AD8*'8_가정'!$F$96</f>
+        <f>AD8*'8_가정'!$F$99</f>
         <v>2240000</v>
       </c>
       <c r="AE23" s="24">
-        <f>AE8*'8_가정'!$G$96</f>
+        <f>AE8*'8_가정'!$G$99</f>
         <v>5460000</v>
       </c>
       <c r="AF23" s="25">
@@ -32503,51 +32651,51 @@
         </is>
       </c>
       <c r="C24" s="18">
-        <f>C8*'8_가정'!$C$97</f>
+        <f>C8*'8_가정'!$C$100</f>
         <v>2360.59640615191</v>
       </c>
       <c r="D24" s="18">
-        <f>D8*'8_가정'!$C$97</f>
+        <f>D8*'8_가정'!$C$100</f>
         <v>2419.91844005022</v>
       </c>
       <c r="E24" s="18">
-        <f>E8*'8_가정'!$C$97</f>
+        <f>E8*'8_가정'!$C$100</f>
         <v>2479.24047394852</v>
       </c>
       <c r="F24" s="18">
-        <f>F8*'8_가정'!$C$97</f>
+        <f>F8*'8_가정'!$C$100</f>
         <v>2538.56250784683</v>
       </c>
       <c r="G24" s="18">
-        <f>G8*'8_가정'!$C$97</f>
+        <f>G8*'8_가정'!$C$100</f>
         <v>2597.88454174514</v>
       </c>
       <c r="H24" s="18">
-        <f>H8*'8_가정'!$C$97</f>
+        <f>H8*'8_가정'!$C$100</f>
         <v>2657.20657564344</v>
       </c>
       <c r="I24" s="18">
-        <f>I8*'8_가정'!$C$97</f>
+        <f>I8*'8_가정'!$C$100</f>
         <v>3315.41749843063</v>
       </c>
       <c r="J24" s="18">
-        <f>J8*'8_가정'!$C$97</f>
+        <f>J8*'8_가정'!$C$100</f>
         <v>3623.62842121783</v>
       </c>
       <c r="K24" s="18">
-        <f>K8*'8_가정'!$C$97</f>
+        <f>K8*'8_가정'!$C$100</f>
         <v>3931.83934400502</v>
       </c>
       <c r="L24" s="18">
-        <f>L8*'8_가정'!$C$97</f>
+        <f>L8*'8_가정'!$C$100</f>
         <v>4402.08730382925</v>
       </c>
       <c r="M24" s="18">
-        <f>M8*'8_가정'!$C$97</f>
+        <f>M8*'8_가정'!$C$100</f>
         <v>5150.23526365348</v>
       </c>
       <c r="N24" s="18">
-        <f>N8*'8_가정'!$C$97</f>
+        <f>N8*'8_가정'!$C$100</f>
         <v>6523.38322347772</v>
       </c>
       <c r="O24" s="23">
@@ -32555,51 +32703,51 @@
         <v>42000</v>
       </c>
       <c r="P24" s="18">
-        <f>P8*'8_가정'!$D$97</f>
+        <f>P8*'8_가정'!$D$100</f>
         <v>10010.2151443817</v>
       </c>
       <c r="Q24" s="18">
-        <f>Q8*'8_가정'!$D$97</f>
+        <f>Q8*'8_가정'!$D$100</f>
         <v>13893.0358166242</v>
       </c>
       <c r="R24" s="18">
-        <f>R8*'8_가정'!$D$97</f>
+        <f>R8*'8_가정'!$D$100</f>
         <v>17775.8564888667</v>
       </c>
       <c r="S24" s="18">
-        <f>S8*'8_가정'!$D$97</f>
+        <f>S8*'8_가정'!$D$100</f>
         <v>21599.355127211</v>
       </c>
       <c r="T24" s="18">
-        <f>T8*'8_가정'!$D$97</f>
+        <f>T8*'8_가정'!$D$100</f>
         <v>25422.8537655552</v>
       </c>
       <c r="U24" s="18">
-        <f>U8*'8_가정'!$D$97</f>
+        <f>U8*'8_가정'!$D$100</f>
         <v>31346.3524038994</v>
       </c>
       <c r="V24" s="18">
-        <f>V8*'8_가정'!$D$97</f>
+        <f>V8*'8_가정'!$D$100</f>
         <v>34920.9621533548</v>
       </c>
       <c r="W24" s="18">
-        <f>W8*'8_가정'!$D$97</f>
+        <f>W8*'8_가정'!$D$100</f>
         <v>38131.846412614</v>
       </c>
       <c r="X24" s="18">
-        <f>X8*'8_가정'!$D$97</f>
+        <f>X8*'8_가정'!$D$100</f>
         <v>39242.7306718733</v>
       </c>
       <c r="Y24" s="18">
-        <f>Y8*'8_가정'!$D$97</f>
+        <f>Y8*'8_가정'!$D$100</f>
         <v>39242.7306718733</v>
       </c>
       <c r="Z24" s="18">
-        <f>Z8*'8_가정'!$D$97</f>
+        <f>Z8*'8_가정'!$D$100</f>
         <v>39242.7306718733</v>
       </c>
       <c r="AA24" s="18">
-        <f>AA8*'8_가정'!$D$97</f>
+        <f>AA8*'8_가정'!$D$100</f>
         <v>39242.7306718733</v>
       </c>
       <c r="AB24" s="23">
@@ -32607,15 +32755,15 @@
         <v>350071.4</v>
       </c>
       <c r="AC24" s="24">
-        <f>AC8*'8_가정'!$E$97</f>
+        <f>AC8*'8_가정'!$E$100</f>
         <v>1056000</v>
       </c>
       <c r="AD24" s="24">
-        <f>AD8*'8_가정'!$F$97</f>
+        <f>AD8*'8_가정'!$F$100</f>
         <v>2030000</v>
       </c>
       <c r="AE24" s="24">
-        <f>AE8*'8_가정'!$G$97</f>
+        <f>AE8*'8_가정'!$G$100</f>
         <v>4836000</v>
       </c>
       <c r="AF24" s="25">
@@ -32635,51 +32783,51 @@
         </is>
       </c>
       <c r="C25" s="18">
-        <f>'8_가정'!$C$100/12</f>
+        <f>'8_가정'!$C$103/12</f>
         <v>3000</v>
       </c>
       <c r="D25" s="18">
-        <f>'8_가정'!$C$100/12</f>
+        <f>'8_가정'!$C$103/12</f>
         <v>3000</v>
       </c>
       <c r="E25" s="18">
-        <f>'8_가정'!$C$100/12</f>
+        <f>'8_가정'!$C$103/12</f>
         <v>3000</v>
       </c>
       <c r="F25" s="18">
-        <f>'8_가정'!$C$100/12</f>
+        <f>'8_가정'!$C$103/12</f>
         <v>3000</v>
       </c>
       <c r="G25" s="18">
-        <f>'8_가정'!$C$100/12</f>
+        <f>'8_가정'!$C$103/12</f>
         <v>3000</v>
       </c>
       <c r="H25" s="18">
-        <f>'8_가정'!$C$100/12</f>
+        <f>'8_가정'!$C$103/12</f>
         <v>3000</v>
       </c>
       <c r="I25" s="18">
-        <f>'8_가정'!$C$100/12</f>
+        <f>'8_가정'!$C$103/12</f>
         <v>3000</v>
       </c>
       <c r="J25" s="18">
-        <f>'8_가정'!$C$100/12</f>
+        <f>'8_가정'!$C$103/12</f>
         <v>3000</v>
       </c>
       <c r="K25" s="18">
-        <f>'8_가정'!$C$100/12</f>
+        <f>'8_가정'!$C$103/12</f>
         <v>3000</v>
       </c>
       <c r="L25" s="18">
-        <f>'8_가정'!$C$100/12</f>
+        <f>'8_가정'!$C$103/12</f>
         <v>3000</v>
       </c>
       <c r="M25" s="18">
-        <f>'8_가정'!$C$100/12</f>
+        <f>'8_가정'!$C$103/12</f>
         <v>3000</v>
       </c>
       <c r="N25" s="18">
-        <f>'8_가정'!$C$100/12</f>
+        <f>'8_가정'!$C$103/12</f>
         <v>3000</v>
       </c>
       <c r="O25" s="23">
@@ -32687,51 +32835,51 @@
         <v>36000</v>
       </c>
       <c r="P25" s="18">
-        <f>'8_가정'!$D$100/12</f>
+        <f>'8_가정'!$D$103/12</f>
         <v>12000</v>
       </c>
       <c r="Q25" s="18">
-        <f>'8_가정'!$D$100/12</f>
+        <f>'8_가정'!$D$103/12</f>
         <v>12000</v>
       </c>
       <c r="R25" s="18">
-        <f>'8_가정'!$D$100/12</f>
+        <f>'8_가정'!$D$103/12</f>
         <v>12000</v>
       </c>
       <c r="S25" s="18">
-        <f>'8_가정'!$D$100/12</f>
+        <f>'8_가정'!$D$103/12</f>
         <v>12000</v>
       </c>
       <c r="T25" s="18">
-        <f>'8_가정'!$D$100/12</f>
+        <f>'8_가정'!$D$103/12</f>
         <v>12000</v>
       </c>
       <c r="U25" s="18">
-        <f>'8_가정'!$D$100/12</f>
+        <f>'8_가정'!$D$103/12</f>
         <v>12000</v>
       </c>
       <c r="V25" s="18">
-        <f>'8_가정'!$D$100/12</f>
+        <f>'8_가정'!$D$103/12</f>
         <v>12000</v>
       </c>
       <c r="W25" s="18">
-        <f>'8_가정'!$D$100/12</f>
+        <f>'8_가정'!$D$103/12</f>
         <v>12000</v>
       </c>
       <c r="X25" s="18">
-        <f>'8_가정'!$D$100/12</f>
+        <f>'8_가정'!$D$103/12</f>
         <v>12000</v>
       </c>
       <c r="Y25" s="18">
-        <f>'8_가정'!$D$100/12</f>
+        <f>'8_가정'!$D$103/12</f>
         <v>12000</v>
       </c>
       <c r="Z25" s="18">
-        <f>'8_가정'!$D$100/12</f>
+        <f>'8_가정'!$D$103/12</f>
         <v>12000</v>
       </c>
       <c r="AA25" s="18">
-        <f>'8_가정'!$D$100/12</f>
+        <f>'8_가정'!$D$103/12</f>
         <v>12000</v>
       </c>
       <c r="AB25" s="23">
@@ -32739,15 +32887,15 @@
         <v>144000</v>
       </c>
       <c r="AC25" s="24">
-        <f>'8_가정'!$E$100</f>
+        <f>'8_가정'!$E$103</f>
         <v>300000</v>
       </c>
       <c r="AD25" s="24">
-        <f>'8_가정'!$F$100</f>
+        <f>'8_가정'!$F$103</f>
         <v>600000</v>
       </c>
       <c r="AE25" s="24">
-        <f>'8_가정'!$G$100</f>
+        <f>'8_가정'!$G$103</f>
         <v>1000000</v>
       </c>
       <c r="AF25" s="25">
@@ -32767,51 +32915,51 @@
         </is>
       </c>
       <c r="C26" s="18">
-        <f>'8_가정'!$C$101/12</f>
+        <f>'8_가정'!$C$104/12</f>
         <v>5000</v>
       </c>
       <c r="D26" s="18">
-        <f>'8_가정'!$C$101/12</f>
+        <f>'8_가정'!$C$104/12</f>
         <v>5000</v>
       </c>
       <c r="E26" s="18">
-        <f>'8_가정'!$C$101/12</f>
+        <f>'8_가정'!$C$104/12</f>
         <v>5000</v>
       </c>
       <c r="F26" s="18">
-        <f>'8_가정'!$C$101/12</f>
+        <f>'8_가정'!$C$104/12</f>
         <v>5000</v>
       </c>
       <c r="G26" s="18">
-        <f>'8_가정'!$C$101/12</f>
+        <f>'8_가정'!$C$104/12</f>
         <v>5000</v>
       </c>
       <c r="H26" s="18">
-        <f>'8_가정'!$C$101/12</f>
+        <f>'8_가정'!$C$104/12</f>
         <v>5000</v>
       </c>
       <c r="I26" s="18">
-        <f>'8_가정'!$C$101/12</f>
+        <f>'8_가정'!$C$104/12</f>
         <v>5000</v>
       </c>
       <c r="J26" s="18">
-        <f>'8_가정'!$C$101/12</f>
+        <f>'8_가정'!$C$104/12</f>
         <v>5000</v>
       </c>
       <c r="K26" s="18">
-        <f>'8_가정'!$C$101/12</f>
+        <f>'8_가정'!$C$104/12</f>
         <v>5000</v>
       </c>
       <c r="L26" s="18">
-        <f>'8_가정'!$C$101/12</f>
+        <f>'8_가정'!$C$104/12</f>
         <v>5000</v>
       </c>
       <c r="M26" s="18">
-        <f>'8_가정'!$C$101/12</f>
+        <f>'8_가정'!$C$104/12</f>
         <v>5000</v>
       </c>
       <c r="N26" s="18">
-        <f>'8_가정'!$C$101/12</f>
+        <f>'8_가정'!$C$104/12</f>
         <v>5000</v>
       </c>
       <c r="O26" s="23">
@@ -32819,51 +32967,51 @@
         <v>60000</v>
       </c>
       <c r="P26" s="18">
-        <f>'8_가정'!$D$101/12</f>
+        <f>'8_가정'!$D$104/12</f>
         <v>15000</v>
       </c>
       <c r="Q26" s="18">
-        <f>'8_가정'!$D$101/12</f>
+        <f>'8_가정'!$D$104/12</f>
         <v>15000</v>
       </c>
       <c r="R26" s="18">
-        <f>'8_가정'!$D$101/12</f>
+        <f>'8_가정'!$D$104/12</f>
         <v>15000</v>
       </c>
       <c r="S26" s="18">
-        <f>'8_가정'!$D$101/12</f>
+        <f>'8_가정'!$D$104/12</f>
         <v>15000</v>
       </c>
       <c r="T26" s="18">
-        <f>'8_가정'!$D$101/12</f>
+        <f>'8_가정'!$D$104/12</f>
         <v>15000</v>
       </c>
       <c r="U26" s="18">
-        <f>'8_가정'!$D$101/12</f>
+        <f>'8_가정'!$D$104/12</f>
         <v>15000</v>
       </c>
       <c r="V26" s="18">
-        <f>'8_가정'!$D$101/12</f>
+        <f>'8_가정'!$D$104/12</f>
         <v>15000</v>
       </c>
       <c r="W26" s="18">
-        <f>'8_가정'!$D$101/12</f>
+        <f>'8_가정'!$D$104/12</f>
         <v>15000</v>
       </c>
       <c r="X26" s="18">
-        <f>'8_가정'!$D$101/12</f>
+        <f>'8_가정'!$D$104/12</f>
         <v>15000</v>
       </c>
       <c r="Y26" s="18">
-        <f>'8_가정'!$D$101/12</f>
+        <f>'8_가정'!$D$104/12</f>
         <v>15000</v>
       </c>
       <c r="Z26" s="18">
-        <f>'8_가정'!$D$101/12</f>
+        <f>'8_가정'!$D$104/12</f>
         <v>15000</v>
       </c>
       <c r="AA26" s="18">
-        <f>'8_가정'!$D$101/12</f>
+        <f>'8_가정'!$D$104/12</f>
         <v>15000</v>
       </c>
       <c r="AB26" s="23">
@@ -32871,15 +33019,15 @@
         <v>180000</v>
       </c>
       <c r="AC26" s="24">
-        <f>'8_가정'!$E$101</f>
+        <f>'8_가정'!$E$104</f>
         <v>400000</v>
       </c>
       <c r="AD26" s="24">
-        <f>'8_가정'!$F$101</f>
+        <f>'8_가정'!$F$104</f>
         <v>800000</v>
       </c>
       <c r="AE26" s="24">
-        <f>'8_가정'!$G$101</f>
+        <f>'8_가정'!$G$104</f>
         <v>1400000</v>
       </c>
       <c r="AF26" s="25">
@@ -32899,51 +33047,51 @@
         </is>
       </c>
       <c r="C27" s="18">
-        <f>('8_가정'!$C$102+'8_가정'!$C$103)/12</f>
+        <f>('8_가정'!$C$105+'8_가정'!$C$106)/12</f>
         <v>1500</v>
       </c>
       <c r="D27" s="18">
-        <f>('8_가정'!$C$102+'8_가정'!$C$103)/12</f>
+        <f>('8_가정'!$C$105+'8_가정'!$C$106)/12</f>
         <v>1500</v>
       </c>
       <c r="E27" s="18">
-        <f>('8_가정'!$C$102+'8_가정'!$C$103)/12</f>
+        <f>('8_가정'!$C$105+'8_가정'!$C$106)/12</f>
         <v>1500</v>
       </c>
       <c r="F27" s="18">
-        <f>('8_가정'!$C$102+'8_가정'!$C$103)/12</f>
+        <f>('8_가정'!$C$105+'8_가정'!$C$106)/12</f>
         <v>1500</v>
       </c>
       <c r="G27" s="18">
-        <f>('8_가정'!$C$102+'8_가정'!$C$103)/12</f>
+        <f>('8_가정'!$C$105+'8_가정'!$C$106)/12</f>
         <v>1500</v>
       </c>
       <c r="H27" s="18">
-        <f>('8_가정'!$C$102+'8_가정'!$C$103)/12</f>
+        <f>('8_가정'!$C$105+'8_가정'!$C$106)/12</f>
         <v>1500</v>
       </c>
       <c r="I27" s="18">
-        <f>('8_가정'!$C$102+'8_가정'!$C$103)/12</f>
+        <f>('8_가정'!$C$105+'8_가정'!$C$106)/12</f>
         <v>1500</v>
       </c>
       <c r="J27" s="18">
-        <f>('8_가정'!$C$102+'8_가정'!$C$103)/12</f>
+        <f>('8_가정'!$C$105+'8_가정'!$C$106)/12</f>
         <v>1500</v>
       </c>
       <c r="K27" s="18">
-        <f>('8_가정'!$C$102+'8_가정'!$C$103)/12</f>
+        <f>('8_가정'!$C$105+'8_가정'!$C$106)/12</f>
         <v>1500</v>
       </c>
       <c r="L27" s="18">
-        <f>('8_가정'!$C$102+'8_가정'!$C$103)/12</f>
+        <f>('8_가정'!$C$105+'8_가정'!$C$106)/12</f>
         <v>1500</v>
       </c>
       <c r="M27" s="18">
-        <f>('8_가정'!$C$102+'8_가정'!$C$103)/12</f>
+        <f>('8_가정'!$C$105+'8_가정'!$C$106)/12</f>
         <v>1500</v>
       </c>
       <c r="N27" s="18">
-        <f>('8_가정'!$C$102+'8_가정'!$C$103)/12</f>
+        <f>('8_가정'!$C$105+'8_가정'!$C$106)/12</f>
         <v>1500</v>
       </c>
       <c r="O27" s="23">
@@ -32951,51 +33099,51 @@
         <v>18000</v>
       </c>
       <c r="P27" s="18">
-        <f>('8_가정'!$D$102+'8_가정'!$D$103)/12</f>
+        <f>('8_가정'!$D$105+'8_가정'!$D$106)/12</f>
         <v>36329.4166666667</v>
       </c>
       <c r="Q27" s="18">
-        <f>('8_가정'!$D$102+'8_가정'!$D$103)/12</f>
+        <f>('8_가정'!$D$105+'8_가정'!$D$106)/12</f>
         <v>36329.4166666667</v>
       </c>
       <c r="R27" s="18">
-        <f>('8_가정'!$D$102+'8_가정'!$D$103)/12</f>
+        <f>('8_가정'!$D$105+'8_가정'!$D$106)/12</f>
         <v>36329.4166666667</v>
       </c>
       <c r="S27" s="18">
-        <f>('8_가정'!$D$102+'8_가정'!$D$103)/12</f>
+        <f>('8_가정'!$D$105+'8_가정'!$D$106)/12</f>
         <v>36329.4166666667</v>
       </c>
       <c r="T27" s="18">
-        <f>('8_가정'!$D$102+'8_가정'!$D$103)/12</f>
+        <f>('8_가정'!$D$105+'8_가정'!$D$106)/12</f>
         <v>36329.4166666667</v>
       </c>
       <c r="U27" s="18">
-        <f>('8_가정'!$D$102+'8_가정'!$D$103)/12</f>
+        <f>('8_가정'!$D$105+'8_가정'!$D$106)/12</f>
         <v>36329.4166666667</v>
       </c>
       <c r="V27" s="18">
-        <f>('8_가정'!$D$102+'8_가정'!$D$103)/12</f>
+        <f>('8_가정'!$D$105+'8_가정'!$D$106)/12</f>
         <v>36329.4166666667</v>
       </c>
       <c r="W27" s="18">
-        <f>('8_가정'!$D$102+'8_가정'!$D$103)/12</f>
+        <f>('8_가정'!$D$105+'8_가정'!$D$106)/12</f>
         <v>36329.4166666667</v>
       </c>
       <c r="X27" s="18">
-        <f>('8_가정'!$D$102+'8_가정'!$D$103)/12</f>
+        <f>('8_가정'!$D$105+'8_가정'!$D$106)/12</f>
         <v>36329.4166666667</v>
       </c>
       <c r="Y27" s="18">
-        <f>('8_가정'!$D$102+'8_가정'!$D$103)/12</f>
+        <f>('8_가정'!$D$105+'8_가정'!$D$106)/12</f>
         <v>36329.4166666667</v>
       </c>
       <c r="Z27" s="18">
-        <f>('8_가정'!$D$102+'8_가정'!$D$103)/12</f>
+        <f>('8_가정'!$D$105+'8_가정'!$D$106)/12</f>
         <v>36329.4166666667</v>
       </c>
       <c r="AA27" s="18">
-        <f>('8_가정'!$D$102+'8_가정'!$D$103)/12</f>
+        <f>('8_가정'!$D$105+'8_가정'!$D$106)/12</f>
         <v>36329.4166666667</v>
       </c>
       <c r="AB27" s="23">
@@ -33003,15 +33151,15 @@
         <v>435953</v>
       </c>
       <c r="AC27" s="24">
-        <f>('8_가정'!$E$102+'8_가정'!$E$103)</f>
+        <f>('8_가정'!$E$105+'8_가정'!$E$106)</f>
         <v>485953</v>
       </c>
       <c r="AD27" s="24">
-        <f>('8_가정'!$F$102+'8_가정'!$F$103)</f>
+        <f>('8_가정'!$F$105+'8_가정'!$F$106)</f>
         <v>575953</v>
       </c>
       <c r="AE27" s="24">
-        <f>('8_가정'!$G$102+'8_가정'!$G$103)</f>
+        <f>('8_가정'!$G$105+'8_가정'!$G$106)</f>
         <v>695953</v>
       </c>
       <c r="AF27" s="25">
@@ -33031,51 +33179,51 @@
         </is>
       </c>
       <c r="C28" s="18">
-        <f>C8*'8_가정'!$C$98</f>
+        <f>C8*'8_가정'!$C$101</f>
         <v>269.782446417362</v>
       </c>
       <c r="D28" s="18">
-        <f>D8*'8_가정'!$C$98</f>
+        <f>D8*'8_가정'!$C$101</f>
         <v>276.562107434311</v>
       </c>
       <c r="E28" s="18">
-        <f>E8*'8_가정'!$C$98</f>
+        <f>E8*'8_가정'!$C$101</f>
         <v>283.34176845126</v>
       </c>
       <c r="F28" s="18">
-        <f>F8*'8_가정'!$C$98</f>
+        <f>F8*'8_가정'!$C$101</f>
         <v>290.121429468209</v>
       </c>
       <c r="G28" s="18">
-        <f>G8*'8_가정'!$C$98</f>
+        <f>G8*'8_가정'!$C$101</f>
         <v>296.901090485158</v>
       </c>
       <c r="H28" s="18">
-        <f>H8*'8_가정'!$C$98</f>
+        <f>H8*'8_가정'!$C$101</f>
         <v>303.680751502107</v>
       </c>
       <c r="I28" s="18">
-        <f>I8*'8_가정'!$C$98</f>
+        <f>I8*'8_가정'!$C$101</f>
         <v>378.904856963501</v>
       </c>
       <c r="J28" s="18">
-        <f>J8*'8_가정'!$C$98</f>
+        <f>J8*'8_가정'!$C$101</f>
         <v>414.128962424895</v>
       </c>
       <c r="K28" s="18">
-        <f>K8*'8_가정'!$C$98</f>
+        <f>K8*'8_가정'!$C$101</f>
         <v>449.353067886288</v>
       </c>
       <c r="L28" s="18">
-        <f>L8*'8_가정'!$C$98</f>
+        <f>L8*'8_가정'!$C$101</f>
         <v>503.0956918662</v>
       </c>
       <c r="M28" s="18">
-        <f>M8*'8_가정'!$C$98</f>
+        <f>M8*'8_가정'!$C$101</f>
         <v>588.598315846112</v>
       </c>
       <c r="N28" s="18">
-        <f>N8*'8_가정'!$C$98</f>
+        <f>N8*'8_가정'!$C$101</f>
         <v>745.529511254596</v>
       </c>
       <c r="O28" s="23">
@@ -33083,51 +33231,51 @@
         <v>4800</v>
       </c>
       <c r="P28" s="18">
-        <f>P8*'8_가정'!$D$98</f>
+        <f>P8*'8_가정'!$D$101</f>
         <v>1430.03073491167</v>
       </c>
       <c r="Q28" s="18">
-        <f>Q8*'8_가정'!$D$98</f>
+        <f>Q8*'8_가정'!$D$101</f>
         <v>1984.71940237489</v>
       </c>
       <c r="R28" s="18">
-        <f>R8*'8_가정'!$D$98</f>
+        <f>R8*'8_가정'!$D$101</f>
         <v>2539.40806983811</v>
       </c>
       <c r="S28" s="18">
-        <f>S8*'8_가정'!$D$98</f>
+        <f>S8*'8_가정'!$D$101</f>
         <v>3085.62216103014</v>
       </c>
       <c r="T28" s="18">
-        <f>T8*'8_가정'!$D$98</f>
+        <f>T8*'8_가정'!$D$101</f>
         <v>3631.83625222217</v>
       </c>
       <c r="U28" s="18">
-        <f>U8*'8_가정'!$D$98</f>
+        <f>U8*'8_가정'!$D$101</f>
         <v>4478.0503434142</v>
       </c>
       <c r="V28" s="18">
-        <f>V8*'8_가정'!$D$98</f>
+        <f>V8*'8_가정'!$D$101</f>
         <v>4988.70887905068</v>
       </c>
       <c r="W28" s="18">
-        <f>W8*'8_가정'!$D$98</f>
+        <f>W8*'8_가정'!$D$101</f>
         <v>5447.40663037343</v>
       </c>
       <c r="X28" s="18">
-        <f>X8*'8_가정'!$D$98</f>
+        <f>X8*'8_가정'!$D$101</f>
         <v>5606.10438169618</v>
       </c>
       <c r="Y28" s="18">
-        <f>Y8*'8_가정'!$D$98</f>
+        <f>Y8*'8_가정'!$D$101</f>
         <v>5606.10438169618</v>
       </c>
       <c r="Z28" s="18">
-        <f>Z8*'8_가정'!$D$98</f>
+        <f>Z8*'8_가정'!$D$101</f>
         <v>5606.10438169618</v>
       </c>
       <c r="AA28" s="18">
-        <f>AA8*'8_가정'!$D$98</f>
+        <f>AA8*'8_가정'!$D$101</f>
         <v>5606.10438169618</v>
       </c>
       <c r="AB28" s="23">
@@ -33135,15 +33283,15 @@
         <v>50010.2</v>
       </c>
       <c r="AC28" s="24">
-        <f>AC8*'8_가정'!$E$98</f>
+        <f>AC8*'8_가정'!$E$101</f>
         <v>165000</v>
       </c>
       <c r="AD28" s="24">
-        <f>AD8*'8_가정'!$F$98</f>
+        <f>AD8*'8_가정'!$F$101</f>
         <v>350000</v>
       </c>
       <c r="AE28" s="24">
-        <f>AE8*'8_가정'!$G$98</f>
+        <f>AE8*'8_가정'!$G$101</f>
         <v>780000</v>
       </c>
       <c r="AF28" s="25">
@@ -33163,51 +33311,51 @@
         </is>
       </c>
       <c r="C29" s="18">
-        <f>C8*'8_가정'!$C$99</f>
+        <f>C8*'8_가정'!$C$102</f>
         <v>1686.14029010851</v>
       </c>
       <c r="D29" s="18">
-        <f>D8*'8_가정'!$C$99</f>
+        <f>D8*'8_가정'!$C$102</f>
         <v>1728.51317146444</v>
       </c>
       <c r="E29" s="18">
-        <f>E8*'8_가정'!$C$99</f>
+        <f>E8*'8_가정'!$C$102</f>
         <v>1770.88605282037</v>
       </c>
       <c r="F29" s="18">
-        <f>F8*'8_가정'!$C$99</f>
+        <f>F8*'8_가정'!$C$102</f>
         <v>1813.25893417631</v>
       </c>
       <c r="G29" s="18">
-        <f>G8*'8_가정'!$C$99</f>
+        <f>G8*'8_가정'!$C$102</f>
         <v>1855.63181553224</v>
       </c>
       <c r="H29" s="18">
-        <f>H8*'8_가정'!$C$99</f>
+        <f>H8*'8_가정'!$C$102</f>
         <v>1898.00469688817</v>
       </c>
       <c r="I29" s="18">
-        <f>I8*'8_가정'!$C$99</f>
+        <f>I8*'8_가정'!$C$102</f>
         <v>2368.15535602188</v>
       </c>
       <c r="J29" s="18">
-        <f>J8*'8_가정'!$C$99</f>
+        <f>J8*'8_가정'!$C$102</f>
         <v>2588.30601515559</v>
       </c>
       <c r="K29" s="18">
-        <f>K8*'8_가정'!$C$99</f>
+        <f>K8*'8_가정'!$C$102</f>
         <v>2808.4566742893</v>
       </c>
       <c r="L29" s="18">
-        <f>L8*'8_가정'!$C$99</f>
+        <f>L8*'8_가정'!$C$102</f>
         <v>3144.34807416375</v>
       </c>
       <c r="M29" s="18">
-        <f>M8*'8_가정'!$C$99</f>
+        <f>M8*'8_가정'!$C$102</f>
         <v>3678.7394740382</v>
       </c>
       <c r="N29" s="18">
-        <f>N8*'8_가정'!$C$99</f>
+        <f>N8*'8_가정'!$C$102</f>
         <v>4659.55944534123</v>
       </c>
       <c r="O29" s="23">
@@ -33215,51 +33363,51 @@
         <v>30000</v>
       </c>
       <c r="P29" s="18">
-        <f>P8*'8_가정'!$D$99</f>
+        <f>P8*'8_가정'!$D$102</f>
         <v>8580.18440947</v>
       </c>
       <c r="Q29" s="18">
-        <f>Q8*'8_가정'!$D$99</f>
+        <f>Q8*'8_가정'!$D$102</f>
         <v>11908.3164142493</v>
       </c>
       <c r="R29" s="18">
-        <f>R8*'8_가정'!$D$99</f>
+        <f>R8*'8_가정'!$D$102</f>
         <v>15236.4484190286</v>
       </c>
       <c r="S29" s="18">
-        <f>S8*'8_가정'!$D$99</f>
+        <f>S8*'8_가정'!$D$102</f>
         <v>18513.7329661808</v>
       </c>
       <c r="T29" s="18">
-        <f>T8*'8_가정'!$D$99</f>
+        <f>T8*'8_가정'!$D$102</f>
         <v>21791.017513333</v>
       </c>
       <c r="U29" s="18">
-        <f>U8*'8_가정'!$D$99</f>
+        <f>U8*'8_가정'!$D$102</f>
         <v>26868.3020604852</v>
       </c>
       <c r="V29" s="18">
-        <f>V8*'8_가정'!$D$99</f>
+        <f>V8*'8_가정'!$D$102</f>
         <v>29932.2532743041</v>
       </c>
       <c r="W29" s="18">
-        <f>W8*'8_가정'!$D$99</f>
+        <f>W8*'8_가정'!$D$102</f>
         <v>32684.4397822406</v>
       </c>
       <c r="X29" s="18">
-        <f>X8*'8_가정'!$D$99</f>
+        <f>X8*'8_가정'!$D$102</f>
         <v>33636.6262901771</v>
       </c>
       <c r="Y29" s="18">
-        <f>Y8*'8_가정'!$D$99</f>
+        <f>Y8*'8_가정'!$D$102</f>
         <v>33636.6262901771</v>
       </c>
       <c r="Z29" s="18">
-        <f>Z8*'8_가정'!$D$99</f>
+        <f>Z8*'8_가정'!$D$102</f>
         <v>33636.6262901771</v>
       </c>
       <c r="AA29" s="18">
-        <f>AA8*'8_가정'!$D$99</f>
+        <f>AA8*'8_가정'!$D$102</f>
         <v>33636.6262901771</v>
       </c>
       <c r="AB29" s="23">
@@ -33267,15 +33415,15 @@
         <v>300061.2</v>
       </c>
       <c r="AC29" s="24">
-        <f>AC8*'8_가정'!$E$99</f>
+        <f>AC8*'8_가정'!$E$102</f>
         <v>858000</v>
       </c>
       <c r="AD29" s="24">
-        <f>AD8*'8_가정'!$F$99</f>
+        <f>AD8*'8_가정'!$F$102</f>
         <v>1540000</v>
       </c>
       <c r="AE29" s="24">
-        <f>AE8*'8_가정'!$G$99</f>
+        <f>AE8*'8_가정'!$G$102</f>
         <v>3744000</v>
       </c>
       <c r="AF29" s="25">
@@ -33291,123 +33439,251 @@
       </c>
       <c r="C30" s="26">
         <f>SUM(C19:C29)</f>
-        <v>65745.4909461035</v>
+        <v>65785.7509461035</v>
       </c>
       <c r="D30" s="26">
         <f>SUM(D19:D29)</f>
-        <v>65942.101115595</v>
+        <v>65982.361115595</v>
       </c>
       <c r="E30" s="26">
         <f>SUM(E19:E29)</f>
-        <v>66138.7112850865</v>
+        <v>66178.9712850866</v>
       </c>
       <c r="F30" s="26">
         <f>SUM(F19:F29)</f>
-        <v>66335.3214545781</v>
+        <v>66375.5814545781</v>
       </c>
       <c r="G30" s="26">
         <f>SUM(G19:G29)</f>
-        <v>66531.9316240696</v>
+        <v>66572.1916240696</v>
       </c>
       <c r="H30" s="26">
         <f>SUM(H19:H29)</f>
-        <v>66728.5417935611</v>
+        <v>66768.8017935611</v>
       </c>
       <c r="I30" s="26">
         <f>SUM(I19:I29)</f>
-        <v>68910.0408519415</v>
+        <v>68950.3008519415</v>
       </c>
       <c r="J30" s="26">
         <f>SUM(J19:J29)</f>
-        <v>69931.5399103219</v>
+        <v>69971.799910322</v>
       </c>
       <c r="K30" s="26">
         <f>SUM(K19:K29)</f>
-        <v>70953.0389687024</v>
+        <v>70993.2989687024</v>
       </c>
       <c r="L30" s="26">
         <f>SUM(L19:L29)</f>
-        <v>79428.9750641198</v>
+        <v>77845.4150641198</v>
       </c>
       <c r="M30" s="26">
         <f>SUM(M19:M29)</f>
-        <v>81908.5511595373</v>
+        <v>80324.9911595373</v>
       </c>
       <c r="N30" s="26">
         <f>SUM(N19:N29)</f>
-        <v>93376.9558263833</v>
+        <v>90169.5758263833</v>
       </c>
       <c r="O30" s="27">
         <f>SUM(O19:O29)</f>
-        <v>861931.2</v>
+        <v>855919.04</v>
       </c>
       <c r="P30" s="26">
         <f>SUM(P19:P29)</f>
-        <v>180246.518714017</v>
+        <v>172796.442314017</v>
       </c>
       <c r="Q30" s="26">
         <f>SUM(Q19:Q29)</f>
-        <v>204288.796737913</v>
+        <v>194730.682337913</v>
       </c>
       <c r="R30" s="26">
         <f>SUM(R19:R29)</f>
-        <v>228331.07476181</v>
+        <v>216664.92236181</v>
       </c>
       <c r="S30" s="26">
         <f>SUM(S19:S29)</f>
-        <v>252119.115497571</v>
+        <v>238344.925097571</v>
       </c>
       <c r="T30" s="26">
         <f>SUM(T19:T29)</f>
-        <v>275907.156233332</v>
+        <v>260024.927833332</v>
       </c>
       <c r="U30" s="26">
         <f>SUM(U19:U29)</f>
-        <v>308695.196969093</v>
+        <v>290704.930569093</v>
       </c>
       <c r="V30" s="26">
         <f>SUM(V19:V29)</f>
-        <v>331416.571038187</v>
+        <v>311318.266638187</v>
       </c>
       <c r="W30" s="26">
         <f>SUM(W19:W29)</f>
-        <v>352579.12157787</v>
+        <v>330372.77917787</v>
       </c>
       <c r="X30" s="26">
         <f>SUM(X19:X29)</f>
-        <v>364741.672117552</v>
+        <v>340427.291717552</v>
       </c>
       <c r="Y30" s="26">
         <f>SUM(Y19:Y29)</f>
-        <v>372143.290117552</v>
+        <v>345720.871717552</v>
       </c>
       <c r="Z30" s="26">
         <f>SUM(Z19:Z29)</f>
-        <v>379544.908117552</v>
+        <v>351014.451717552</v>
       </c>
       <c r="AA30" s="26">
         <f>SUM(AA19:AA29)</f>
-        <v>394348.144117552</v>
+        <v>361601.611717552</v>
       </c>
       <c r="AB30" s="27">
         <f>SUM(AB19:AB29)</f>
-        <v>3644361.566</v>
+        <v>3413722.1032</v>
       </c>
       <c r="AC30" s="28">
         <f>SUM(AC19:AC29)</f>
-        <v>11154420.46892</v>
+        <v>9660542.221424</v>
       </c>
       <c r="AD30" s="28">
         <f>SUM(AD19:AD29)</f>
-        <v>22427558.058178</v>
+        <v>18547327.5849237</v>
       </c>
       <c r="AE30" s="28">
         <f>SUM(AE19:AE29)</f>
-        <v>47245435.7478032</v>
+        <v>38670270.2950683</v>
       </c>
       <c r="AF30" s="26">
         <f>SUM(AF19:AF29)</f>
-        <v>85333707.0409012</v>
+        <v>71147781.244616</v>
+      </c>
+    </row>
+    <row r="31">
+      <c r="A31" s="15" t="inlineStr">
+        <is>
+          <t>평균 월 급여(대표 포함 블렌드, 천원)</t>
+        </is>
+      </c>
+      <c r="B31" s="7" t="inlineStr">
+        <is>
+          <t>급여 ÷ 비용 산정 인원</t>
+        </is>
+      </c>
+      <c r="C31" s="82">
+        <f>IFERROR(C19/C15/1,0)</f>
+        <v>5674.71428571429</v>
+      </c>
+      <c r="D31" s="82">
+        <f>IFERROR(D19/D15/1,0)</f>
+        <v>5674.71428571429</v>
+      </c>
+      <c r="E31" s="82">
+        <f>IFERROR(E19/E15/1,0)</f>
+        <v>5674.71428571429</v>
+      </c>
+      <c r="F31" s="82">
+        <f>IFERROR(F19/F15/1,0)</f>
+        <v>5674.71428571429</v>
+      </c>
+      <c r="G31" s="82">
+        <f>IFERROR(G19/G15/1,0)</f>
+        <v>5674.71428571429</v>
+      </c>
+      <c r="H31" s="82">
+        <f>IFERROR(H19/H15/1,0)</f>
+        <v>5674.71428571429</v>
+      </c>
+      <c r="I31" s="82">
+        <f>IFERROR(I19/I15/1,0)</f>
+        <v>5674.71428571429</v>
+      </c>
+      <c r="J31" s="82">
+        <f>IFERROR(J19/J15/1,0)</f>
+        <v>5674.71428571429</v>
+      </c>
+      <c r="K31" s="82">
+        <f>IFERROR(K19/K15/1,0)</f>
+        <v>5674.71428571429</v>
+      </c>
+      <c r="L31" s="82">
+        <f>IFERROR(L19/L15/1,0)</f>
+        <v>5507.75</v>
+      </c>
+      <c r="M31" s="82">
+        <f>IFERROR(M19/M15/1,0)</f>
+        <v>5507.75</v>
+      </c>
+      <c r="N31" s="82">
+        <f>IFERROR(N19/N15/1,0)</f>
+        <v>5377.88888888889</v>
+      </c>
+      <c r="O31" s="83">
+        <f>IFERROR(O19/O15/12,0)</f>
+        <v>5614</v>
+      </c>
+      <c r="P31" s="82">
+        <f>IFERROR(P19/P15/1,0)</f>
+        <v>5456.238</v>
+      </c>
+      <c r="Q31" s="82">
+        <f>IFERROR(Q19/Q15/1,0)</f>
+        <v>5354.67090909091</v>
+      </c>
+      <c r="R31" s="82">
+        <f>IFERROR(R19/R15/1,0)</f>
+        <v>5270.03166666667</v>
+      </c>
+      <c r="S31" s="82">
+        <f>IFERROR(S19/S15/1,0)</f>
+        <v>5198.41384615385</v>
+      </c>
+      <c r="T31" s="82">
+        <f>IFERROR(T19/T15/1,0)</f>
+        <v>5137.02714285714</v>
+      </c>
+      <c r="U31" s="82">
+        <f>IFERROR(U19/U15/1,0)</f>
+        <v>5083.82533333333</v>
+      </c>
+      <c r="V31" s="82">
+        <f>IFERROR(V19/V15/1,0)</f>
+        <v>5037.27375</v>
+      </c>
+      <c r="W31" s="82">
+        <f>IFERROR(W19/W15/1,0)</f>
+        <v>4996.19882352941</v>
+      </c>
+      <c r="X31" s="82">
+        <f>IFERROR(X19/X15/1,0)</f>
+        <v>4959.68777777778</v>
+      </c>
+      <c r="Y31" s="82">
+        <f>IFERROR(Y19/Y15/1,0)</f>
+        <v>4927.02</v>
+      </c>
+      <c r="Z31" s="82">
+        <f>IFERROR(Z19/Z15/1,0)</f>
+        <v>4897.619</v>
+      </c>
+      <c r="AA31" s="82">
+        <f>IFERROR(AA19/AA15/1,0)</f>
+        <v>4846.83545454546</v>
+      </c>
+      <c r="AB31" s="83">
+        <f>IFERROR(AB19/AB15/12,0)</f>
+        <v>5055.944171123</v>
+      </c>
+      <c r="AC31" s="84">
+        <f>IFERROR(AC19/AC15/12,0)</f>
+        <v>4584.27713271028</v>
+      </c>
+      <c r="AD31" s="84">
+        <f>IFERROR(AD19/AD15/12,0)</f>
+        <v>4480.47692522791</v>
+      </c>
+      <c r="AE31" s="84">
+        <f>IFERROR(AE19/AE15/12,0)</f>
+        <v>4428.44237602226</v>
       </c>
     </row>
     <row r="32">
@@ -33429,103 +33705,103 @@
         </is>
       </c>
       <c r="C33" s="18">
-        <f>'8_가정'!$C$109/12</f>
-        <v>5416.66666666667</v>
+        <f>'8_가정'!$C$112/12</f>
+        <v>24583.3333333333</v>
       </c>
       <c r="D33" s="18">
-        <f>'8_가정'!$C$109/12</f>
-        <v>5416.66666666667</v>
+        <f>'8_가정'!$C$112/12</f>
+        <v>24583.3333333333</v>
       </c>
       <c r="E33" s="18">
-        <f>'8_가정'!$C$109/12</f>
-        <v>5416.66666666667</v>
+        <f>'8_가정'!$C$112/12</f>
+        <v>24583.3333333333</v>
       </c>
       <c r="F33" s="18">
-        <f>'8_가정'!$C$109/12</f>
-        <v>5416.66666666667</v>
+        <f>'8_가정'!$C$112/12</f>
+        <v>24583.3333333333</v>
       </c>
       <c r="G33" s="18">
-        <f>'8_가정'!$C$109/12</f>
-        <v>5416.66666666667</v>
+        <f>'8_가정'!$C$112/12</f>
+        <v>24583.3333333333</v>
       </c>
       <c r="H33" s="18">
-        <f>'8_가정'!$C$109/12</f>
-        <v>5416.66666666667</v>
+        <f>'8_가정'!$C$112/12</f>
+        <v>24583.3333333333</v>
       </c>
       <c r="I33" s="18">
-        <f>'8_가정'!$C$109/12</f>
-        <v>5416.66666666667</v>
+        <f>'8_가정'!$C$112/12</f>
+        <v>24583.3333333333</v>
       </c>
       <c r="J33" s="18">
-        <f>'8_가정'!$C$109/12</f>
-        <v>5416.66666666667</v>
+        <f>'8_가정'!$C$112/12</f>
+        <v>24583.3333333333</v>
       </c>
       <c r="K33" s="18">
-        <f>'8_가정'!$C$109/12</f>
-        <v>5416.66666666667</v>
+        <f>'8_가정'!$C$112/12</f>
+        <v>24583.3333333333</v>
       </c>
       <c r="L33" s="18">
-        <f>'8_가정'!$C$109/12</f>
-        <v>5416.66666666667</v>
+        <f>'8_가정'!$C$112/12</f>
+        <v>24583.3333333333</v>
       </c>
       <c r="M33" s="18">
-        <f>'8_가정'!$C$109/12</f>
-        <v>5416.66666666667</v>
+        <f>'8_가정'!$C$112/12</f>
+        <v>24583.3333333333</v>
       </c>
       <c r="N33" s="18">
-        <f>'8_가정'!$C$109/12</f>
-        <v>5416.66666666667</v>
+        <f>'8_가정'!$C$112/12</f>
+        <v>24583.3333333333</v>
       </c>
       <c r="O33" s="23">
         <f>SUM(C33:N33)</f>
-        <v>65000</v>
+        <v>295000</v>
       </c>
       <c r="P33" s="18">
-        <f>'8_가정'!$D$109/12</f>
+        <f>'8_가정'!$D$112/12</f>
         <v>3333.33333333333</v>
       </c>
       <c r="Q33" s="18">
-        <f>'8_가정'!$D$109/12</f>
+        <f>'8_가정'!$D$112/12</f>
         <v>3333.33333333333</v>
       </c>
       <c r="R33" s="18">
-        <f>'8_가정'!$D$109/12</f>
+        <f>'8_가정'!$D$112/12</f>
         <v>3333.33333333333</v>
       </c>
       <c r="S33" s="18">
-        <f>'8_가정'!$D$109/12</f>
+        <f>'8_가정'!$D$112/12</f>
         <v>3333.33333333333</v>
       </c>
       <c r="T33" s="18">
-        <f>'8_가정'!$D$109/12</f>
+        <f>'8_가정'!$D$112/12</f>
         <v>3333.33333333333</v>
       </c>
       <c r="U33" s="18">
-        <f>'8_가정'!$D$109/12</f>
+        <f>'8_가정'!$D$112/12</f>
         <v>3333.33333333333</v>
       </c>
       <c r="V33" s="18">
-        <f>'8_가정'!$D$109/12</f>
+        <f>'8_가정'!$D$112/12</f>
         <v>3333.33333333333</v>
       </c>
       <c r="W33" s="18">
-        <f>'8_가정'!$D$109/12</f>
+        <f>'8_가정'!$D$112/12</f>
         <v>3333.33333333333</v>
       </c>
       <c r="X33" s="18">
-        <f>'8_가정'!$D$109/12</f>
+        <f>'8_가정'!$D$112/12</f>
         <v>3333.33333333333</v>
       </c>
       <c r="Y33" s="18">
-        <f>'8_가정'!$D$109/12</f>
+        <f>'8_가정'!$D$112/12</f>
         <v>3333.33333333333</v>
       </c>
       <c r="Z33" s="18">
-        <f>'8_가정'!$D$109/12</f>
+        <f>'8_가정'!$D$112/12</f>
         <v>3333.33333333333</v>
       </c>
       <c r="AA33" s="18">
-        <f>'8_가정'!$D$109/12</f>
+        <f>'8_가정'!$D$112/12</f>
         <v>3333.33333333333</v>
       </c>
       <c r="AB33" s="23">
@@ -33533,20 +33809,20 @@
         <v>40000</v>
       </c>
       <c r="AC33" s="24">
-        <f>'8_가정'!$E$109</f>
+        <f>'8_가정'!$E$112</f>
         <v>30000</v>
       </c>
       <c r="AD33" s="24">
-        <f>'8_가정'!$F$109</f>
+        <f>'8_가정'!$F$112</f>
         <v>0</v>
       </c>
       <c r="AE33" s="24">
-        <f>'8_가정'!$G$109</f>
+        <f>'8_가정'!$G$112</f>
         <v>0</v>
       </c>
       <c r="AF33" s="25">
         <f>O33+AB33+AC33+AD33+AE33</f>
-        <v>135000</v>
+        <v>365000</v>
       </c>
     </row>
     <row r="34">
@@ -33716,7 +33992,7 @@
       </c>
       <c r="B36" s="7" t="inlineStr"/>
       <c r="O36" s="48">
-        <f>AVERAGE('8_가정'!$C$107,O35)</f>
+        <f>AVERAGE('8_가정'!$C$110,O35)</f>
         <v>1199771.5</v>
       </c>
       <c r="AB36" s="44">
@@ -33744,23 +34020,23 @@
       </c>
       <c r="B37" s="7" t="inlineStr"/>
       <c r="O37" s="48">
-        <f>O36*'8_가정'!$C$108</f>
+        <f>O36*'8_가정'!$C$111</f>
         <v>57589.032</v>
       </c>
       <c r="AB37" s="48">
-        <f>AB36*'8_가정'!$D$108</f>
+        <f>AB36*'8_가정'!$D$111</f>
         <v>76800</v>
       </c>
       <c r="AC37" s="24">
-        <f>AC36*'8_가정'!$E$108</f>
+        <f>AC36*'8_가정'!$E$111</f>
         <v>192000</v>
       </c>
       <c r="AD37" s="24">
-        <f>AD36*'8_가정'!$F$108</f>
+        <f>AD36*'8_가정'!$F$111</f>
         <v>384000</v>
       </c>
       <c r="AE37" s="24">
-        <f>AE36*'8_가정'!$G$108</f>
+        <f>AE36*'8_가정'!$G$111</f>
         <v>528000</v>
       </c>
     </row>
@@ -33779,23 +34055,23 @@
       </c>
       <c r="O40" s="48">
         <f>'2_손익계산서'!O50</f>
-        <v>-284917.342734463</v>
+        <v>-48905.1827344633</v>
       </c>
       <c r="AB40" s="48">
         <f>'2_손익계산서'!AB50</f>
-        <v>289535.378</v>
+        <v>520174.8408</v>
       </c>
       <c r="AC40" s="24">
         <f>'2_손익계산서'!AC50</f>
-        <v>1757662.69398429</v>
+        <v>3251540.94148028</v>
       </c>
       <c r="AD40" s="24">
         <f>'2_손익계산서'!AD50</f>
-        <v>5113430.45583219</v>
+        <v>8993660.92908651</v>
       </c>
       <c r="AE40" s="24">
         <f>'2_손익계산서'!AE50</f>
-        <v>15938869.7971292</v>
+        <v>24514035.249864</v>
       </c>
     </row>
     <row r="41">
@@ -33805,20 +34081,20 @@
         </is>
       </c>
       <c r="O41" s="48">
-        <f>'8_가정'!$C$110</f>
+        <f>'8_가정'!$C$116</f>
         <v>3032082</v>
       </c>
       <c r="AB41" s="44">
         <f>O44</f>
-        <v>3316999.34273446</v>
+        <v>3080987.18273446</v>
       </c>
       <c r="AC41" s="45">
         <f>AB44</f>
-        <v>3027463.96473446</v>
+        <v>2560812.34193446</v>
       </c>
       <c r="AD41" s="45">
         <f>AC44</f>
-        <v>1269801.27075018</v>
+        <v>0</v>
       </c>
       <c r="AE41" s="45">
         <f>AD44</f>
@@ -33832,23 +34108,23 @@
         </is>
       </c>
       <c r="O42" s="48">
-        <f>MIN(O41,MAX(0,O40)*'8_가정'!$C$111)</f>
+        <f>MIN(O41,MAX(0,O40)*'8_가정'!$C$117)</f>
         <v>0</v>
       </c>
       <c r="AB42" s="48">
-        <f>MIN(AB41,MAX(0,AB40)*'8_가정'!$C$111)</f>
-        <v>289535.378</v>
+        <f>MIN(AB41,MAX(0,AB40)*'8_가정'!$C$117)</f>
+        <v>520174.8408</v>
       </c>
       <c r="AC42" s="24">
-        <f>MIN(AC41,MAX(0,AC40)*'8_가정'!$C$111)</f>
-        <v>1757662.69398429</v>
+        <f>MIN(AC41,MAX(0,AC40)*'8_가정'!$C$117)</f>
+        <v>2560812.34193446</v>
       </c>
       <c r="AD42" s="24">
-        <f>MIN(AD41,MAX(0,AD40)*'8_가정'!$C$111)</f>
-        <v>1269801.27075018</v>
+        <f>MIN(AD41,MAX(0,AD40)*'8_가정'!$C$117)</f>
+        <v>0</v>
       </c>
       <c r="AE42" s="24">
-        <f>MIN(AE41,MAX(0,AE40)*'8_가정'!$C$111)</f>
+        <f>MIN(AE41,MAX(0,AE40)*'8_가정'!$C$117)</f>
         <v>0</v>
       </c>
     </row>
@@ -33860,7 +34136,7 @@
       </c>
       <c r="O43" s="44">
         <f>MAX(0,-O40)</f>
-        <v>284917.342734463</v>
+        <v>48905.1827344633</v>
       </c>
       <c r="AB43" s="44">
         <f>MAX(0,-AB40)</f>
@@ -33887,15 +34163,15 @@
       </c>
       <c r="O44" s="44">
         <f>O41-O42+O43</f>
-        <v>3316999.34273446</v>
+        <v>3080987.18273446</v>
       </c>
       <c r="AB44" s="44">
         <f>AB41-AB42+AB43</f>
-        <v>3027463.96473446</v>
+        <v>2560812.34193446</v>
       </c>
       <c r="AC44" s="45">
         <f>AC41-AC42+AC43</f>
-        <v>1269801.27075018</v>
+        <v>0</v>
       </c>
       <c r="AD44" s="45">
         <f>AD41-AD42+AD43</f>
@@ -33922,15 +34198,15 @@
       </c>
       <c r="AC45" s="45">
         <f>MAX(0,AC40)-AC42</f>
-        <v>0</v>
+        <v>690728.599545821</v>
       </c>
       <c r="AD45" s="45">
         <f>MAX(0,AD40)-AD42</f>
-        <v>3843629.18508201</v>
+        <v>8993660.92908651</v>
       </c>
       <c r="AE45" s="45">
         <f>MAX(0,AE40)-AE42</f>
-        <v>15938869.7971292</v>
+        <v>24514035.249864</v>
       </c>
     </row>
     <row r="46">
@@ -33940,24 +34216,24 @@
         </is>
       </c>
       <c r="O46" s="48">
-        <f>MIN(O45,'8_가정'!$C$112)*'8_가정'!$C$113+MAX(0,MIN(O45,'8_가정'!$D$112)-'8_가정'!$C$112)*'8_가정'!$D$113+MAX(0,MIN(O45,'8_가정'!$E$112)-'8_가정'!$D$112)*'8_가정'!$E$113+MAX(0,O45-'8_가정'!$E$112)*'8_가정'!$F$113</f>
+        <f>MIN(O45,'8_가정'!$C$118)*'8_가정'!$C$119+MAX(0,MIN(O45,'8_가정'!$D$118)-'8_가정'!$C$118)*'8_가정'!$D$119+MAX(0,MIN(O45,'8_가정'!$E$118)-'8_가정'!$D$118)*'8_가정'!$E$119+MAX(0,O45-'8_가정'!$E$118)*'8_가정'!$F$119</f>
         <v>0</v>
       </c>
       <c r="AB46" s="48">
-        <f>MIN(AB45,'8_가정'!$C$112)*'8_가정'!$C$113+MAX(0,MIN(AB45,'8_가정'!$D$112)-'8_가정'!$C$112)*'8_가정'!$D$113+MAX(0,MIN(AB45,'8_가정'!$E$112)-'8_가정'!$D$112)*'8_가정'!$E$113+MAX(0,AB45-'8_가정'!$E$112)*'8_가정'!$F$113</f>
+        <f>MIN(AB45,'8_가정'!$C$118)*'8_가정'!$C$119+MAX(0,MIN(AB45,'8_가정'!$D$118)-'8_가정'!$C$118)*'8_가정'!$D$119+MAX(0,MIN(AB45,'8_가정'!$E$118)-'8_가정'!$D$118)*'8_가정'!$E$119+MAX(0,AB45-'8_가정'!$E$118)*'8_가정'!$F$119</f>
         <v>0</v>
       </c>
       <c r="AC46" s="24">
-        <f>MIN(AC45,'8_가정'!$C$112)*'8_가정'!$C$113+MAX(0,MIN(AC45,'8_가정'!$D$112)-'8_가정'!$C$112)*'8_가정'!$D$113+MAX(0,MIN(AC45,'8_가정'!$E$112)-'8_가정'!$D$112)*'8_가정'!$E$113+MAX(0,AC45-'8_가정'!$E$112)*'8_가정'!$F$113</f>
-        <v>0</v>
+        <f>MIN(AC45,'8_가정'!$C$118)*'8_가정'!$C$119+MAX(0,MIN(AC45,'8_가정'!$D$118)-'8_가정'!$C$118)*'8_가정'!$D$119+MAX(0,MIN(AC45,'8_가정'!$E$118)-'8_가정'!$D$118)*'8_가정'!$E$119+MAX(0,AC45-'8_가정'!$E$118)*'8_가정'!$F$119</f>
+        <v>118145.719909164</v>
       </c>
       <c r="AD46" s="24">
-        <f>MIN(AD45,'8_가정'!$C$112)*'8_가정'!$C$113+MAX(0,MIN(AD45,'8_가정'!$D$112)-'8_가정'!$C$112)*'8_가정'!$D$113+MAX(0,MIN(AD45,'8_가정'!$E$112)-'8_가정'!$D$112)*'8_가정'!$E$113+MAX(0,AD45-'8_가정'!$E$112)*'8_가정'!$F$113</f>
-        <v>748725.837016403</v>
+        <f>MIN(AD45,'8_가정'!$C$118)*'8_가정'!$C$119+MAX(0,MIN(AD45,'8_가정'!$D$118)-'8_가정'!$C$118)*'8_가정'!$D$119+MAX(0,MIN(AD45,'8_가정'!$E$118)-'8_가정'!$D$118)*'8_가정'!$E$119+MAX(0,AD45-'8_가정'!$E$118)*'8_가정'!$F$119</f>
+        <v>1778732.1858173</v>
       </c>
       <c r="AE46" s="24">
-        <f>MIN(AE45,'8_가정'!$C$112)*'8_가정'!$C$113+MAX(0,MIN(AE45,'8_가정'!$D$112)-'8_가정'!$C$112)*'8_가정'!$D$113+MAX(0,MIN(AE45,'8_가정'!$E$112)-'8_가정'!$D$112)*'8_가정'!$E$113+MAX(0,AE45-'8_가정'!$E$112)*'8_가정'!$F$113</f>
-        <v>3167773.95942583</v>
+        <f>MIN(AE45,'8_가정'!$C$118)*'8_가정'!$C$119+MAX(0,MIN(AE45,'8_가정'!$D$118)-'8_가정'!$C$118)*'8_가정'!$D$119+MAX(0,MIN(AE45,'8_가정'!$E$118)-'8_가정'!$D$118)*'8_가정'!$E$119+MAX(0,AE45-'8_가정'!$E$118)*'8_가정'!$F$119</f>
+        <v>4973087.75497008</v>
       </c>
     </row>
     <row r="47">
@@ -33967,24 +34243,24 @@
         </is>
       </c>
       <c r="O47" s="48">
-        <f>O46*'8_가정'!$C$114</f>
+        <f>O46*'8_가정'!$C$120</f>
         <v>0</v>
       </c>
       <c r="AB47" s="48">
-        <f>AB46*'8_가정'!$C$114</f>
+        <f>AB46*'8_가정'!$C$120</f>
         <v>0</v>
       </c>
       <c r="AC47" s="24">
-        <f>AC46*'8_가정'!$C$114</f>
-        <v>0</v>
+        <f>AC46*'8_가정'!$C$120</f>
+        <v>11814.5719909164</v>
       </c>
       <c r="AD47" s="24">
-        <f>AD46*'8_가정'!$C$114</f>
-        <v>74872.5837016403</v>
+        <f>AD46*'8_가정'!$C$120</f>
+        <v>177873.21858173</v>
       </c>
       <c r="AE47" s="24">
-        <f>AE46*'8_가정'!$C$114</f>
-        <v>316777.395942583</v>
+        <f>AE46*'8_가정'!$C$120</f>
+        <v>497308.775497008</v>
       </c>
     </row>
     <row r="48">
@@ -34003,15 +34279,15 @@
       </c>
       <c r="AC48" s="34">
         <f>AC46+AC47</f>
-        <v>0</v>
+        <v>129960.291900081</v>
       </c>
       <c r="AD48" s="34">
         <f>AD46+AD47</f>
-        <v>823598.420718043</v>
+        <v>1956605.40439903</v>
       </c>
       <c r="AE48" s="34">
         <f>AE46+AE47</f>
-        <v>3484551.35536842</v>
+        <v>5470396.53046709</v>
       </c>
     </row>
     <row r="49">
@@ -34126,19 +34402,19 @@
       </c>
       <c r="AC49" s="45">
         <f>AC48</f>
-        <v>0</v>
+        <v>129960.291900081</v>
       </c>
       <c r="AD49" s="45">
         <f>AD48</f>
-        <v>823598.420718043</v>
+        <v>1956605.40439903</v>
       </c>
       <c r="AE49" s="45">
         <f>AE48</f>
-        <v>3484551.35536842</v>
+        <v>5470396.53046709</v>
       </c>
       <c r="AF49" s="25">
         <f>O49+AB49+AC49+AD49+AE49</f>
-        <v>4308149.77608646</v>
+        <v>7556962.2267662</v>
       </c>
     </row>
     <row r="51">
@@ -34155,23 +34431,23 @@
         </is>
       </c>
       <c r="O53" s="48">
-        <f>O8*'8_가정'!$C$115/365</f>
+        <f>O8*'8_가정'!$C$121/365</f>
         <v>197260.273972603</v>
       </c>
       <c r="AB53" s="48">
-        <f>AB8*'8_가정'!$C$115/365</f>
+        <f>AB8*'8_가정'!$C$121/365</f>
         <v>1644170.95890411</v>
       </c>
       <c r="AC53" s="24">
-        <f>AC8*'8_가정'!$C$115/365</f>
+        <f>AC8*'8_가정'!$C$121/365</f>
         <v>5424657.53424658</v>
       </c>
       <c r="AD53" s="24">
-        <f>AD8*'8_가정'!$C$115/365</f>
+        <f>AD8*'8_가정'!$C$121/365</f>
         <v>11506849.3150685</v>
       </c>
       <c r="AE53" s="24">
-        <f>AE8*'8_가정'!$C$115/365</f>
+        <f>AE8*'8_가정'!$C$121/365</f>
         <v>25643835.6164384</v>
       </c>
     </row>
@@ -34182,23 +34458,23 @@
         </is>
       </c>
       <c r="O54" s="48">
-        <f>'2_손익계산서'!O25*'8_가정'!$C$116/365</f>
+        <f>'2_손익계산서'!O25*'8_가정'!$C$122/365</f>
         <v>103626.922312515</v>
       </c>
       <c r="AB54" s="48">
-        <f>'2_손익계산서'!AB25*'8_가정'!$C$116/365</f>
+        <f>'2_손익계산서'!AB25*'8_가정'!$C$122/365</f>
         <v>991453.653041096</v>
       </c>
       <c r="AC54" s="24">
-        <f>'2_손익계산서'!AC25*'8_가정'!$C$116/365</f>
+        <f>'2_손익계산서'!AC25*'8_가정'!$C$122/365</f>
         <v>3275493.17870067</v>
       </c>
       <c r="AD54" s="24">
-        <f>'2_손익계산서'!AD25*'8_가정'!$C$116/365</f>
+        <f>'2_손익계산서'!AD25*'8_가정'!$C$122/365</f>
         <v>6916440.2442723</v>
       </c>
       <c r="AE54" s="24">
-        <f>'2_손익계산서'!AE25*'8_가정'!$C$116/365</f>
+        <f>'2_손익계산서'!AE25*'8_가정'!$C$122/365</f>
         <v>15170579.9104221</v>
       </c>
     </row>
@@ -34209,23 +34485,23 @@
         </is>
       </c>
       <c r="O55" s="48">
-        <f>'2_손익계산서'!O25*'8_가정'!$C$117/365</f>
+        <f>'2_손익계산서'!O25*'8_가정'!$C$123/365</f>
         <v>77720.1917343859</v>
       </c>
       <c r="AB55" s="48">
-        <f>'2_손익계산서'!AB25*'8_가정'!$C$117/365</f>
+        <f>'2_손익계산서'!AB25*'8_가정'!$C$123/365</f>
         <v>743590.239780822</v>
       </c>
       <c r="AC55" s="24">
-        <f>'2_손익계산서'!AC25*'8_가정'!$C$117/365</f>
+        <f>'2_손익계산서'!AC25*'8_가정'!$C$123/365</f>
         <v>2456619.8840255</v>
       </c>
       <c r="AD55" s="24">
-        <f>'2_손익계산서'!AD25*'8_가정'!$C$117/365</f>
+        <f>'2_손익계산서'!AD25*'8_가정'!$C$123/365</f>
         <v>5187330.18320422</v>
       </c>
       <c r="AE55" s="24">
-        <f>'2_손익계산서'!AE25*'8_가정'!$C$117/365</f>
+        <f>'2_손익계산서'!AE25*'8_가정'!$C$123/365</f>
         <v>11377934.9328166</v>
       </c>
     </row>
@@ -34263,7 +34539,7 @@
         </is>
       </c>
       <c r="O57" s="48">
-        <f>O56-('3_연간손익'!$C$7*'8_가정'!$C$115/365+'3_연간손익'!$C$9*('8_가정'!$C$116-'8_가정'!$C$117)/365)</f>
+        <f>O56-('3_연간손익'!$C$7*'8_가정'!$C$121/365+'3_연간손익'!$C$9*('8_가정'!$C$122-'8_가정'!$C$123)/365)</f>
         <v>66288.3716192245</v>
       </c>
       <c r="AB57" s="44">
@@ -34289,23 +34565,23 @@
           <t>차입금 기말 ÷ 순운전자본</t>
         </is>
       </c>
-      <c r="O58" s="82">
+      <c r="O58" s="85">
         <f>IFERROR(O35/O56,0)</f>
         <v>5.37713898349705</v>
       </c>
-      <c r="AB58" s="82">
+      <c r="AB58" s="85">
         <f>IFERROR(AB35/AB56,0)</f>
         <v>1.0570632486513</v>
       </c>
-      <c r="AC58" s="83">
+      <c r="AC58" s="86">
         <f>IFERROR(AC35/AC56,0)</f>
         <v>0.960994694253188</v>
       </c>
-      <c r="AD58" s="83">
+      <c r="AD58" s="86">
         <f>IFERROR(AD35/AD56,0)</f>
         <v>0.75551758023897</v>
       </c>
-      <c r="AE58" s="83">
+      <c r="AE58" s="86">
         <f>IFERROR(AE35/AE56,0)</f>
         <v>0.407657429075542</v>
       </c>
@@ -34330,7 +34606,7 @@
     <outlinePr summaryBelow="1" summaryRight="1"/>
     <pageSetUpPr fitToPage="1"/>
   </sheetPr>
-  <dimension ref="A1:I129"/>
+  <dimension ref="A1:I135"/>
   <sheetFormatPr baseColWidth="8" defaultRowHeight="15"/>
   <cols>
     <col width="40" customWidth="1" min="1" max="1"/>
@@ -34359,19 +34635,19 @@
       </c>
     </row>
     <row r="4">
-      <c r="A4" s="84" t="inlineStr">
+      <c r="A4" s="87" t="inlineStr">
         <is>
           <t>1. IR 목표 · 환율 · 이용자 지표</t>
         </is>
       </c>
-      <c r="B4" s="85" t="n"/>
-      <c r="C4" s="85" t="n"/>
-      <c r="D4" s="85" t="n"/>
-      <c r="E4" s="85" t="n"/>
-      <c r="F4" s="85" t="n"/>
-      <c r="G4" s="85" t="n"/>
-      <c r="H4" s="85" t="n"/>
-      <c r="I4" s="85" t="n"/>
+      <c r="B4" s="88" t="n"/>
+      <c r="C4" s="88" t="n"/>
+      <c r="D4" s="88" t="n"/>
+      <c r="E4" s="88" t="n"/>
+      <c r="F4" s="88" t="n"/>
+      <c r="G4" s="88" t="n"/>
+      <c r="H4" s="88" t="n"/>
+      <c r="I4" s="88" t="n"/>
     </row>
     <row r="5">
       <c r="A5" s="22" t="inlineStr">
@@ -34432,7 +34708,7 @@
       <c r="G6" s="65" t="n">
         <v>156000000</v>
       </c>
-      <c r="I6" s="86" t="inlineStr">
+      <c r="I6" s="89" t="inlineStr">
         <is>
           <t>IR 라벨 1,200 / 10,005 / 33,000 / 70,000 / 156,000을 백만원 단위로 해석. 2027 표(p.25) 합계는 10,302,040천원이며 차트(10,005)와의 차이 ≈ Sunway PoC 3.0억</t>
         </is>
@@ -34444,10 +34720,10 @@
           <t>USD/KRW</t>
         </is>
       </c>
-      <c r="C7" s="87" t="n">
+      <c r="C7" s="90" t="n">
         <v>1400</v>
       </c>
-      <c r="I7" s="86" t="inlineStr">
+      <c r="I7" s="89" t="inlineStr">
         <is>
           <t>IR p.35 고정 환율 1,400원/달러(2026-10-02 서울 종가 1,350.60). 참고용(계약 통화 환산 비교)</t>
         </is>
@@ -34459,10 +34735,10 @@
           <t>SGD/KRW</t>
         </is>
       </c>
-      <c r="C8" s="87" t="n">
+      <c r="C8" s="90" t="n">
         <v>1096</v>
       </c>
-      <c r="I8" s="86" t="inlineStr">
+      <c r="I8" s="89" t="inlineStr">
         <is>
           <t>1,400원/달러 기준 교차환율(USD/SGD 1.277). 현물 약 1,057~1,060</t>
         </is>
@@ -34474,10 +34750,10 @@
           <t>JPY 100엔/KRW</t>
         </is>
       </c>
-      <c r="C9" s="87" t="n">
+      <c r="C9" s="90" t="n">
         <v>888</v>
       </c>
-      <c r="I9" s="86" t="inlineStr">
+      <c r="I9" s="89" t="inlineStr">
         <is>
           <t>1,400원/달러 기준(USD/JPY 157.6). 현물 856.76(2026-10-02)</t>
         </is>
@@ -34489,10 +34765,10 @@
           <t>EUR/KRW</t>
         </is>
       </c>
-      <c r="C10" s="87" t="n">
+      <c r="C10" s="90" t="n">
         <v>1576</v>
       </c>
-      <c r="I10" s="86" t="inlineStr">
+      <c r="I10" s="89" t="inlineStr">
         <is>
           <t>1,400원/달러 기준(EUR/USD 1.126). 현물 1,520.64(2026-10-02)</t>
         </is>
@@ -34547,19 +34823,19 @@
       </c>
     </row>
     <row r="15">
-      <c r="A15" s="84" t="inlineStr">
+      <c r="A15" s="87" t="inlineStr">
         <is>
           <t>2. 시나리오 정의 — 단계별 확률 · 지연(개월)</t>
         </is>
       </c>
-      <c r="B15" s="85" t="n"/>
-      <c r="C15" s="85" t="n"/>
-      <c r="D15" s="85" t="n"/>
-      <c r="E15" s="85" t="n"/>
-      <c r="F15" s="85" t="n"/>
-      <c r="G15" s="85" t="n"/>
-      <c r="H15" s="85" t="n"/>
-      <c r="I15" s="85" t="n"/>
+      <c r="B15" s="88" t="n"/>
+      <c r="C15" s="88" t="n"/>
+      <c r="D15" s="88" t="n"/>
+      <c r="E15" s="88" t="n"/>
+      <c r="F15" s="88" t="n"/>
+      <c r="G15" s="88" t="n"/>
+      <c r="H15" s="88" t="n"/>
+      <c r="I15" s="88" t="n"/>
     </row>
     <row r="16">
       <c r="A16" s="22" t="inlineStr">
@@ -34614,25 +34890,25 @@
           <t>IR 단계 "계약" — 계약서/주문 확인</t>
         </is>
       </c>
-      <c r="C17" s="88" t="n">
+      <c r="C17" s="91" t="n">
         <v>1</v>
       </c>
-      <c r="D17" s="88" t="n">
+      <c r="D17" s="91" t="n">
         <v>0.9</v>
       </c>
-      <c r="E17" s="88" t="n">
+      <c r="E17" s="91" t="n">
         <v>0.75</v>
       </c>
-      <c r="F17" s="89" t="n">
-        <v>0</v>
-      </c>
-      <c r="G17" s="89" t="n">
+      <c r="F17" s="92" t="n">
+        <v>0</v>
+      </c>
+      <c r="G17" s="92" t="n">
         <v>2</v>
       </c>
-      <c r="H17" s="89" t="n">
+      <c r="H17" s="92" t="n">
         <v>4</v>
       </c>
-      <c r="I17" s="86" t="inlineStr">
+      <c r="I17" s="89" t="inlineStr">
         <is>
           <t>확률 = 해당 단계 거래처 매출의 반영률, 지연 = 매출 개시를 늦추는 개월 수(램프 전체를 평행 이동). 기존 거래(HeartKium·Intega)는 지연 미적용</t>
         </is>
@@ -34649,22 +34925,22 @@
           <t>제도 등록 완료(NHIS·TAIS), 매출 미개시</t>
         </is>
       </c>
-      <c r="C18" s="88" t="n">
+      <c r="C18" s="91" t="n">
         <v>1</v>
       </c>
-      <c r="D18" s="88" t="n">
+      <c r="D18" s="91" t="n">
         <v>0.5</v>
       </c>
-      <c r="E18" s="88" t="n">
+      <c r="E18" s="91" t="n">
         <v>0.3</v>
       </c>
-      <c r="F18" s="89" t="n">
-        <v>0</v>
-      </c>
-      <c r="G18" s="89" t="n">
+      <c r="F18" s="92" t="n">
+        <v>0</v>
+      </c>
+      <c r="G18" s="92" t="n">
         <v>3</v>
       </c>
-      <c r="H18" s="89" t="n">
+      <c r="H18" s="92" t="n">
         <v>6</v>
       </c>
     </row>
@@ -34679,22 +34955,22 @@
           <t>입찰 제안서 제출·LOA 대기(NHG)</t>
         </is>
       </c>
-      <c r="C19" s="88" t="n">
+      <c r="C19" s="91" t="n">
         <v>1</v>
       </c>
-      <c r="D19" s="88" t="n">
+      <c r="D19" s="91" t="n">
         <v>0.5</v>
       </c>
-      <c r="E19" s="88" t="n">
+      <c r="E19" s="91" t="n">
         <v>0.3</v>
       </c>
-      <c r="F19" s="89" t="n">
-        <v>0</v>
-      </c>
-      <c r="G19" s="89" t="n">
+      <c r="F19" s="92" t="n">
+        <v>0</v>
+      </c>
+      <c r="G19" s="92" t="n">
         <v>3</v>
       </c>
-      <c r="H19" s="89" t="n">
+      <c r="H19" s="92" t="n">
         <v>6</v>
       </c>
     </row>
@@ -34709,22 +34985,22 @@
           <t>IR 단계 "진행 중" — 협의 단계</t>
         </is>
       </c>
-      <c r="C20" s="88" t="n">
+      <c r="C20" s="91" t="n">
         <v>1</v>
       </c>
-      <c r="D20" s="88" t="n">
+      <c r="D20" s="91" t="n">
         <v>0.3</v>
       </c>
-      <c r="E20" s="88" t="n">
+      <c r="E20" s="91" t="n">
         <v>0.15</v>
       </c>
-      <c r="F20" s="89" t="n">
-        <v>0</v>
-      </c>
-      <c r="G20" s="89" t="n">
+      <c r="F20" s="92" t="n">
+        <v>0</v>
+      </c>
+      <c r="G20" s="92" t="n">
         <v>3</v>
       </c>
-      <c r="H20" s="89" t="n">
+      <c r="H20" s="92" t="n">
         <v>6</v>
       </c>
     </row>
@@ -34739,22 +35015,22 @@
           <t>IR 단계 "접촉" — 초기 접촉</t>
         </is>
       </c>
-      <c r="C21" s="88" t="n">
+      <c r="C21" s="91" t="n">
         <v>1</v>
       </c>
-      <c r="D21" s="88" t="n">
+      <c r="D21" s="91" t="n">
         <v>0.15</v>
       </c>
-      <c r="E21" s="88" t="n">
-        <v>0</v>
-      </c>
-      <c r="F21" s="89" t="n">
-        <v>0</v>
-      </c>
-      <c r="G21" s="89" t="n">
+      <c r="E21" s="91" t="n">
+        <v>0</v>
+      </c>
+      <c r="F21" s="92" t="n">
+        <v>0</v>
+      </c>
+      <c r="G21" s="92" t="n">
         <v>3</v>
       </c>
-      <c r="H21" s="89" t="n">
+      <c r="H21" s="92" t="n">
         <v>6</v>
       </c>
     </row>
@@ -34769,22 +35045,22 @@
           <t>PoC/R&amp;D 단계 — 모든 시나리오에서 매출 미반영(상방)</t>
         </is>
       </c>
-      <c r="C22" s="88" t="n">
-        <v>0</v>
-      </c>
-      <c r="D22" s="88" t="n">
-        <v>0</v>
-      </c>
-      <c r="E22" s="88" t="n">
-        <v>0</v>
-      </c>
-      <c r="F22" s="89" t="n">
-        <v>0</v>
-      </c>
-      <c r="G22" s="89" t="n">
-        <v>0</v>
-      </c>
-      <c r="H22" s="89" t="n">
+      <c r="C22" s="91" t="n">
+        <v>0</v>
+      </c>
+      <c r="D22" s="91" t="n">
+        <v>0</v>
+      </c>
+      <c r="E22" s="91" t="n">
+        <v>0</v>
+      </c>
+      <c r="F22" s="92" t="n">
+        <v>0</v>
+      </c>
+      <c r="G22" s="92" t="n">
+        <v>0</v>
+      </c>
+      <c r="H22" s="92" t="n">
         <v>0</v>
       </c>
     </row>
@@ -34799,22 +35075,22 @@
           <t>기존 소액 거래처·기타(2025 매출 기반)</t>
         </is>
       </c>
-      <c r="C23" s="88" t="n">
+      <c r="C23" s="91" t="n">
         <v>1</v>
       </c>
-      <c r="D23" s="88" t="n">
+      <c r="D23" s="91" t="n">
         <v>0.85</v>
       </c>
-      <c r="E23" s="88" t="n">
+      <c r="E23" s="91" t="n">
         <v>0.7</v>
       </c>
-      <c r="F23" s="89" t="n">
-        <v>0</v>
-      </c>
-      <c r="G23" s="89" t="n">
-        <v>0</v>
-      </c>
-      <c r="H23" s="89" t="n">
+      <c r="F23" s="92" t="n">
+        <v>0</v>
+      </c>
+      <c r="G23" s="92" t="n">
+        <v>0</v>
+      </c>
+      <c r="H23" s="92" t="n">
         <v>0</v>
       </c>
     </row>
@@ -34829,22 +35105,22 @@
           <t>신규 파이프라인 코호트(별도 달성률 적용)</t>
         </is>
       </c>
-      <c r="C24" s="88" t="n">
+      <c r="C24" s="91" t="n">
         <v>1</v>
       </c>
-      <c r="D24" s="88" t="n">
+      <c r="D24" s="91" t="n">
         <v>1</v>
       </c>
-      <c r="E24" s="88" t="n">
+      <c r="E24" s="91" t="n">
         <v>1</v>
       </c>
-      <c r="F24" s="89" t="n">
-        <v>0</v>
-      </c>
-      <c r="G24" s="89" t="n">
-        <v>0</v>
-      </c>
-      <c r="H24" s="89" t="n">
+      <c r="F24" s="92" t="n">
+        <v>0</v>
+      </c>
+      <c r="G24" s="92" t="n">
+        <v>0</v>
+      </c>
+      <c r="H24" s="92" t="n">
         <v>0</v>
       </c>
     </row>
@@ -34891,16 +35167,16 @@
           <t>지정 거래처 2028~30 성장률(양수)에 곱함</t>
         </is>
       </c>
-      <c r="C27" s="88" t="n">
+      <c r="C27" s="91" t="n">
         <v>1</v>
       </c>
-      <c r="D27" s="88" t="n">
+      <c r="D27" s="91" t="n">
         <v>0.7</v>
       </c>
-      <c r="E27" s="88" t="n">
+      <c r="E27" s="91" t="n">
         <v>0.4</v>
       </c>
-      <c r="G27" s="90">
+      <c r="G27" s="93">
         <f>INDEX(C27:E27,'1_요약'!$C$5)</f>
         <v>1</v>
       </c>
@@ -34916,16 +35192,16 @@
           <t>코호트·삼성채널 S1 매출 대비 반영률</t>
         </is>
       </c>
-      <c r="C28" s="88" t="n">
+      <c r="C28" s="91" t="n">
         <v>1</v>
       </c>
-      <c r="D28" s="88" t="n">
+      <c r="D28" s="91" t="n">
         <v>0.6</v>
       </c>
-      <c r="E28" s="88" t="n">
+      <c r="E28" s="91" t="n">
         <v>0.35</v>
       </c>
-      <c r="G28" s="90">
+      <c r="G28" s="93">
         <f>INDEX(C28:E28,'1_요약'!$C$5)</f>
         <v>1</v>
       </c>
@@ -34941,16 +35217,16 @@
           <t>코호트·삼성채널 S1 매출 대비 반영률</t>
         </is>
       </c>
-      <c r="C29" s="88" t="n">
+      <c r="C29" s="91" t="n">
         <v>1</v>
       </c>
-      <c r="D29" s="88" t="n">
+      <c r="D29" s="91" t="n">
         <v>0.45</v>
       </c>
-      <c r="E29" s="88" t="n">
+      <c r="E29" s="91" t="n">
         <v>0.2</v>
       </c>
-      <c r="G29" s="90">
+      <c r="G29" s="93">
         <f>INDEX(C29:E29,'1_요약'!$C$5)</f>
         <v>1</v>
       </c>
@@ -34966,16 +35242,16 @@
           <t>코호트·삼성채널 S1 매출 대비 반영률</t>
         </is>
       </c>
-      <c r="C30" s="88" t="n">
+      <c r="C30" s="91" t="n">
         <v>1</v>
       </c>
-      <c r="D30" s="88" t="n">
+      <c r="D30" s="91" t="n">
         <v>0.35</v>
       </c>
-      <c r="E30" s="88" t="n">
+      <c r="E30" s="91" t="n">
         <v>0.12</v>
       </c>
-      <c r="G30" s="90">
+      <c r="G30" s="93">
         <f>INDEX(C30:E30,'1_요약'!$C$5)</f>
         <v>1</v>
       </c>
@@ -34991,24 +35267,24 @@
           <t>인원 = S1 인원 × (1 − 탄력도 + 탄력도 × 매출달성률)</t>
         </is>
       </c>
-      <c r="C31" s="88" t="n">
+      <c r="C31" s="91" t="n">
         <v>0.75</v>
       </c>
     </row>
     <row r="33">
-      <c r="A33" s="84" t="inlineStr">
+      <c r="A33" s="87" t="inlineStr">
         <is>
           <t>3. 제품별 매출원가율(매출 대비)</t>
         </is>
       </c>
-      <c r="B33" s="85" t="n"/>
-      <c r="C33" s="85" t="n"/>
-      <c r="D33" s="85" t="n"/>
-      <c r="E33" s="85" t="n"/>
-      <c r="F33" s="85" t="n"/>
-      <c r="G33" s="85" t="n"/>
-      <c r="H33" s="85" t="n"/>
-      <c r="I33" s="85" t="n"/>
+      <c r="B33" s="88" t="n"/>
+      <c r="C33" s="88" t="n"/>
+      <c r="D33" s="88" t="n"/>
+      <c r="E33" s="88" t="n"/>
+      <c r="F33" s="88" t="n"/>
+      <c r="G33" s="88" t="n"/>
+      <c r="H33" s="88" t="n"/>
+      <c r="I33" s="88" t="n"/>
     </row>
     <row r="34">
       <c r="A34" s="22" t="inlineStr">
@@ -35054,22 +35330,22 @@
           <t>P1</t>
         </is>
       </c>
-      <c r="C35" s="91" t="n">
+      <c r="C35" s="94" t="n">
         <v>0.57</v>
       </c>
-      <c r="D35" s="91" t="n">
+      <c r="D35" s="94" t="n">
         <v>0.63</v>
       </c>
-      <c r="E35" s="91" t="n">
+      <c r="E35" s="94" t="n">
         <v>0.635</v>
       </c>
-      <c r="F35" s="91" t="n">
+      <c r="F35" s="94" t="n">
         <v>0.635</v>
       </c>
-      <c r="G35" s="91" t="n">
+      <c r="G35" s="94" t="n">
         <v>0.635</v>
       </c>
-      <c r="I35" s="86" t="inlineStr">
+      <c r="I35" s="89" t="inlineStr">
         <is>
           <t>2025 실적 GM 53%(매출총이익 4.53억/매출 8.54억). 소모품(기저귀) 비중 확대에 따라 2027~ 41% 내외로 보수적 설정. Hansoms 현물출자(최대 USD 448k 상당 제품 납품) 효과는 미반영</t>
         </is>
@@ -35086,19 +35362,19 @@
           <t>P2</t>
         </is>
       </c>
-      <c r="C36" s="91" t="n">
+      <c r="C36" s="94" t="n">
         <v>0.48</v>
       </c>
-      <c r="D36" s="91" t="n">
+      <c r="D36" s="94" t="n">
         <v>0.57</v>
       </c>
-      <c r="E36" s="91" t="n">
+      <c r="E36" s="94" t="n">
         <v>0.5600000000000001</v>
       </c>
-      <c r="F36" s="91" t="n">
+      <c r="F36" s="94" t="n">
         <v>0.55</v>
       </c>
-      <c r="G36" s="91" t="n">
+      <c r="G36" s="94" t="n">
         <v>0.54</v>
       </c>
     </row>
@@ -35113,19 +35389,19 @@
           <t>P3</t>
         </is>
       </c>
-      <c r="C37" s="91" t="n">
+      <c r="C37" s="94" t="n">
         <v>0.2</v>
       </c>
-      <c r="D37" s="91" t="n">
+      <c r="D37" s="94" t="n">
         <v>0.24</v>
       </c>
-      <c r="E37" s="91" t="n">
+      <c r="E37" s="94" t="n">
         <v>0.23</v>
       </c>
-      <c r="F37" s="91" t="n">
+      <c r="F37" s="94" t="n">
         <v>0.22</v>
       </c>
-      <c r="G37" s="91" t="n">
+      <c r="G37" s="94" t="n">
         <v>0.21</v>
       </c>
     </row>
@@ -35140,19 +35416,19 @@
           <t>P4</t>
         </is>
       </c>
-      <c r="C38" s="91" t="n">
+      <c r="C38" s="94" t="n">
         <v>0.6</v>
       </c>
-      <c r="D38" s="91" t="n">
+      <c r="D38" s="94" t="n">
         <v>0.6</v>
       </c>
-      <c r="E38" s="91" t="n">
+      <c r="E38" s="94" t="n">
         <v>0.58</v>
       </c>
-      <c r="F38" s="91" t="n">
+      <c r="F38" s="94" t="n">
         <v>0.5600000000000001</v>
       </c>
-      <c r="G38" s="91" t="n">
+      <c r="G38" s="94" t="n">
         <v>0.54</v>
       </c>
     </row>
@@ -35167,19 +35443,19 @@
           <t>P5</t>
         </is>
       </c>
-      <c r="C39" s="91" t="n">
+      <c r="C39" s="94" t="n">
         <v>0.6</v>
       </c>
-      <c r="D39" s="91" t="n">
+      <c r="D39" s="94" t="n">
         <v>0.58</v>
       </c>
-      <c r="E39" s="91" t="n">
+      <c r="E39" s="94" t="n">
         <v>0.57</v>
       </c>
-      <c r="F39" s="91" t="n">
+      <c r="F39" s="94" t="n">
         <v>0.55</v>
       </c>
-      <c r="G39" s="91" t="n">
+      <c r="G39" s="94" t="n">
         <v>0.53</v>
       </c>
     </row>
@@ -35194,19 +35470,19 @@
           <t>P6</t>
         </is>
       </c>
-      <c r="C40" s="91" t="n">
+      <c r="C40" s="94" t="n">
         <v>0.55</v>
       </c>
-      <c r="D40" s="91" t="n">
+      <c r="D40" s="94" t="n">
         <v>0.55</v>
       </c>
-      <c r="E40" s="91" t="n">
+      <c r="E40" s="94" t="n">
         <v>0.55</v>
       </c>
-      <c r="F40" s="91" t="n">
+      <c r="F40" s="94" t="n">
         <v>0.55</v>
       </c>
-      <c r="G40" s="91" t="n">
+      <c r="G40" s="94" t="n">
         <v>0.55</v>
       </c>
     </row>
@@ -35221,36 +35497,36 @@
           <t>전체 매출 대비</t>
         </is>
       </c>
-      <c r="C41" s="91" t="n">
+      <c r="C41" s="94" t="n">
         <v>0.015</v>
       </c>
-      <c r="D41" s="91" t="n">
+      <c r="D41" s="94" t="n">
         <v>0.025</v>
       </c>
-      <c r="E41" s="91" t="n">
+      <c r="E41" s="94" t="n">
         <v>0.03</v>
       </c>
-      <c r="F41" s="91" t="n">
+      <c r="F41" s="94" t="n">
         <v>0.035</v>
       </c>
-      <c r="G41" s="91" t="n">
+      <c r="G41" s="94" t="n">
         <v>0.035</v>
       </c>
     </row>
     <row r="43">
-      <c r="A43" s="84" t="inlineStr">
+      <c r="A43" s="87" t="inlineStr">
         <is>
           <t>4. 거래처 유형별 제품 믹스(매출 대비 %, 프로파일 × 제품 × 연도)</t>
         </is>
       </c>
-      <c r="B43" s="85" t="n"/>
-      <c r="C43" s="85" t="n"/>
-      <c r="D43" s="85" t="n"/>
-      <c r="E43" s="85" t="n"/>
-      <c r="F43" s="85" t="n"/>
-      <c r="G43" s="85" t="n"/>
-      <c r="H43" s="85" t="n"/>
-      <c r="I43" s="85" t="n"/>
+      <c r="B43" s="88" t="n"/>
+      <c r="C43" s="88" t="n"/>
+      <c r="D43" s="88" t="n"/>
+      <c r="E43" s="88" t="n"/>
+      <c r="F43" s="88" t="n"/>
+      <c r="G43" s="88" t="n"/>
+      <c r="H43" s="88" t="n"/>
+      <c r="I43" s="88" t="n"/>
     </row>
     <row r="44">
       <c r="A44" s="22" t="inlineStr">
@@ -36431,19 +36707,19 @@
       </c>
     </row>
     <row r="89">
-      <c r="A89" s="84" t="inlineStr">
+      <c r="A89" s="87" t="inlineStr">
         <is>
           <t>5. 판매비와관리비 가정</t>
         </is>
       </c>
-      <c r="B89" s="85" t="n"/>
-      <c r="C89" s="85" t="n"/>
-      <c r="D89" s="85" t="n"/>
-      <c r="E89" s="85" t="n"/>
-      <c r="F89" s="85" t="n"/>
-      <c r="G89" s="85" t="n"/>
-      <c r="H89" s="85" t="n"/>
-      <c r="I89" s="85" t="n"/>
+      <c r="B89" s="88" t="n"/>
+      <c r="C89" s="88" t="n"/>
+      <c r="D89" s="88" t="n"/>
+      <c r="E89" s="88" t="n"/>
+      <c r="F89" s="88" t="n"/>
+      <c r="G89" s="88" t="n"/>
+      <c r="H89" s="88" t="n"/>
+      <c r="I89" s="88" t="n"/>
     </row>
     <row r="90">
       <c r="A90" s="22" t="inlineStr">
@@ -36472,660 +36748,746 @@
         <v>2030</v>
       </c>
       <c r="H90" s="22" t="inlineStr"/>
-      <c r="I90" s="22" t="inlineStr">
-        <is>
-          <t>근거 · 비고</t>
+      <c r="I90" s="95" t="inlineStr">
+        <is>
+          <t>급상여대장 2026-09: 7명, 지급합계 39,688,891원(대표 13,688,890원 + 직원 6명 26,000,001원)</t>
         </is>
       </c>
     </row>
     <row r="91">
       <c r="A91" s="15" t="inlineStr">
         <is>
-          <t>1인당 월 평균급여(천원)</t>
+          <t>대표이사 월 급여(천원, 고정)</t>
         </is>
       </c>
       <c r="B91" s="15" t="inlineStr">
         <is>
-          <t>2026 = 급상여대장 2026-09 지급합계 평균, 2027~ = 전년 × (1+인상률)</t>
+          <t>2026-09 급상여대장 지급합계, 인상률 미적용(전 기간 동일)</t>
         </is>
       </c>
       <c r="C91" s="65" t="n">
-        <v>5670</v>
-      </c>
-      <c r="D91" s="43">
-        <f>C91*(1+$C$92)</f>
-        <v>6066.9</v>
-      </c>
-      <c r="E91" s="43">
-        <f>D91*(1+$C$92)</f>
-        <v>6491.583</v>
-      </c>
-      <c r="F91" s="43">
-        <f>E91*(1+$C$92)</f>
-        <v>6945.99381</v>
-      </c>
-      <c r="G91" s="43">
-        <f>F91*(1+$C$92)</f>
-        <v>7432.2133767</v>
-      </c>
-      <c r="I91" s="86" t="inlineStr">
-        <is>
-          <t>급상여대장 2026-09: 7명, 지급합계 39,688,891원(대표 13,688,890원 포함, 대표 제외 평균 약 4,339천원). 연 상여 미포함, 공제 전 총액 기준</t>
-        </is>
+        <v>13689</v>
       </c>
     </row>
     <row r="92">
       <c r="A92" s="15" t="inlineStr">
         <is>
-          <t>연간 급여 인상률(2027~)</t>
-        </is>
-      </c>
-      <c r="C92" s="91" t="n">
-        <v>0.07000000000000001</v>
+          <t>직원 1인당 월 급여(천원) — 기존 6명</t>
+        </is>
+      </c>
+      <c r="B92" s="15" t="inlineStr">
+        <is>
+          <t>2026 = 급상여대장 대표 제외 평균, 2027~ = 전년 × (1+인상률)</t>
+        </is>
+      </c>
+      <c r="C92" s="65" t="n">
+        <v>4339</v>
+      </c>
+      <c r="D92" s="43">
+        <f>C92*(1+$C$93)</f>
+        <v>4642.73</v>
+      </c>
+      <c r="E92" s="43">
+        <f>D92*(1+$C$93)</f>
+        <v>4967.7211</v>
+      </c>
+      <c r="F92" s="43">
+        <f>E92*(1+$C$93)</f>
+        <v>5315.461577</v>
+      </c>
+      <c r="G92" s="43">
+        <f>F92*(1+$C$93)</f>
+        <v>5687.54388739</v>
       </c>
     </row>
     <row r="93">
       <c r="A93" s="15" t="inlineStr">
         <is>
-          <t>퇴직급여·4대보험·복리후생 비율(급여 대비)</t>
-        </is>
-      </c>
-      <c r="C93" s="88" t="n">
-        <v>0.22</v>
+          <t>기존 직원 연간 급여 인상률(2027~)</t>
+        </is>
+      </c>
+      <c r="C93" s="94" t="n">
+        <v>0.07000000000000001</v>
       </c>
     </row>
     <row r="94">
       <c r="A94" s="15" t="inlineStr">
         <is>
-          <t>마케팅·광고선전비(매출 %)</t>
+          <t>신규 채용 1인당 월 급여(천원, 인상률 미적용)</t>
         </is>
       </c>
       <c r="B94" s="15" t="inlineStr">
         <is>
-          <t>전시회·해외 마케팅·샘플</t>
-        </is>
-      </c>
-      <c r="C94" s="91" t="n">
-        <v>0.015</v>
-      </c>
-      <c r="D94" s="91" t="n">
-        <v>0.025</v>
-      </c>
-      <c r="E94" s="91" t="n">
-        <v>0.028</v>
-      </c>
-      <c r="F94" s="91" t="n">
-        <v>0.026</v>
-      </c>
-      <c r="G94" s="91" t="n">
-        <v>0.03</v>
+          <t>추가 인력 급여 — 2026~2030 동일</t>
+        </is>
+      </c>
+      <c r="C94" s="65" t="n">
+        <v>4339</v>
       </c>
     </row>
     <row r="95">
       <c r="A95" s="15" t="inlineStr">
         <is>
-          <t>지급수수료(매출 %)</t>
-        </is>
-      </c>
-      <c r="B95" s="15" t="inlineStr">
-        <is>
-          <t>총판 수수료·법무·회계·컨설팅·플랫폼</t>
-        </is>
-      </c>
-      <c r="C95" s="91" t="n">
-        <v>0.012</v>
-      </c>
-      <c r="D95" s="91" t="n">
-        <v>0.02</v>
-      </c>
-      <c r="E95" s="91" t="n">
-        <v>0.022</v>
-      </c>
-      <c r="F95" s="91" t="n">
-        <v>0.022</v>
-      </c>
-      <c r="G95" s="91" t="n">
-        <v>0.022</v>
+          <t>기존 인력 수(대표 포함, 명)</t>
+        </is>
+      </c>
+      <c r="C95" s="65" t="n">
+        <v>7</v>
       </c>
     </row>
     <row r="96">
       <c r="A96" s="15" t="inlineStr">
         <is>
-          <t>판매물류·CS비(매출 %)</t>
-        </is>
-      </c>
-      <c r="B96" s="15" t="inlineStr">
-        <is>
-          <t>출고·설치·고객지원</t>
+          <t>퇴직급여·4대보험·복리후생 비율(급여 대비)</t>
         </is>
       </c>
       <c r="C96" s="91" t="n">
-        <v>0.025</v>
-      </c>
-      <c r="D96" s="91" t="n">
-        <v>0.035</v>
-      </c>
-      <c r="E96" s="91" t="n">
-        <v>0.035</v>
-      </c>
-      <c r="F96" s="91" t="n">
-        <v>0.032</v>
-      </c>
-      <c r="G96" s="91" t="n">
-        <v>0.035</v>
+        <v>0.22</v>
       </c>
     </row>
     <row r="97">
       <c r="A97" s="15" t="inlineStr">
         <is>
-          <t>연구개발비-경상(매출 %)</t>
+          <t>마케팅·광고선전비(매출 %)</t>
         </is>
       </c>
       <c r="B97" s="15" t="inlineStr">
         <is>
-          <t>인증(CE-MDR·FDA·KC·PMDA)·시험·외주</t>
-        </is>
-      </c>
-      <c r="C97" s="91" t="n">
-        <v>0.035</v>
-      </c>
-      <c r="D97" s="91" t="n">
-        <v>0.035</v>
-      </c>
-      <c r="E97" s="91" t="n">
-        <v>0.032</v>
-      </c>
-      <c r="F97" s="91" t="n">
-        <v>0.029</v>
-      </c>
-      <c r="G97" s="91" t="n">
-        <v>0.031</v>
-      </c>
-      <c r="I97" s="86" t="inlineStr">
-        <is>
-          <t>개발비 자본화(BS 개발비 19.8억)는 별도. 신규 자본화·상각 증가분은 미반영(보수적 가정은 상각에서 반영)</t>
-        </is>
+          <t>전시회·해외 마케팅·샘플</t>
+        </is>
+      </c>
+      <c r="C97" s="94" t="n">
+        <v>0.015</v>
+      </c>
+      <c r="D97" s="94" t="n">
+        <v>0.025</v>
+      </c>
+      <c r="E97" s="94" t="n">
+        <v>0.028</v>
+      </c>
+      <c r="F97" s="94" t="n">
+        <v>0.026</v>
+      </c>
+      <c r="G97" s="94" t="n">
+        <v>0.03</v>
       </c>
     </row>
     <row r="98">
       <c r="A98" s="15" t="inlineStr">
         <is>
-          <t>대손상각비(매출 %)</t>
-        </is>
-      </c>
-      <c r="B98" s="15" t="inlineStr"/>
-      <c r="C98" s="91" t="n">
-        <v>0.004</v>
-      </c>
-      <c r="D98" s="91" t="n">
-        <v>0.005</v>
-      </c>
-      <c r="E98" s="91" t="n">
-        <v>0.005</v>
-      </c>
-      <c r="F98" s="91" t="n">
-        <v>0.005</v>
-      </c>
-      <c r="G98" s="91" t="n">
-        <v>0.005</v>
+          <t>지급수수료(매출 %)</t>
+        </is>
+      </c>
+      <c r="B98" s="15" t="inlineStr">
+        <is>
+          <t>총판 수수료·법무·회계·컨설팅·플랫폼</t>
+        </is>
+      </c>
+      <c r="C98" s="94" t="n">
+        <v>0.012</v>
+      </c>
+      <c r="D98" s="94" t="n">
+        <v>0.02</v>
+      </c>
+      <c r="E98" s="94" t="n">
+        <v>0.022</v>
+      </c>
+      <c r="F98" s="94" t="n">
+        <v>0.022</v>
+      </c>
+      <c r="G98" s="94" t="n">
+        <v>0.022</v>
       </c>
     </row>
     <row r="99">
       <c r="A99" s="15" t="inlineStr">
         <is>
-          <t>기타 판관비(매출 %)</t>
+          <t>판매물류·CS비(매출 %)</t>
         </is>
       </c>
       <c r="B99" s="15" t="inlineStr">
         <is>
-          <t>보험·세금과공과·소모품·복리 외</t>
-        </is>
-      </c>
-      <c r="C99" s="91" t="n">
+          <t>출고·설치·고객지원</t>
+        </is>
+      </c>
+      <c r="C99" s="94" t="n">
         <v>0.025</v>
       </c>
-      <c r="D99" s="91" t="n">
-        <v>0.03</v>
-      </c>
-      <c r="E99" s="91" t="n">
-        <v>0.026</v>
-      </c>
-      <c r="F99" s="91" t="n">
-        <v>0.022</v>
-      </c>
-      <c r="G99" s="91" t="n">
-        <v>0.024</v>
+      <c r="D99" s="94" t="n">
+        <v>0.035</v>
+      </c>
+      <c r="E99" s="94" t="n">
+        <v>0.035</v>
+      </c>
+      <c r="F99" s="94" t="n">
+        <v>0.032</v>
+      </c>
+      <c r="G99" s="94" t="n">
+        <v>0.035</v>
       </c>
     </row>
     <row r="100">
       <c r="A100" s="15" t="inlineStr">
         <is>
-          <t>임차·운영비(연, 천원)</t>
+          <t>연구개발비-경상(매출 %)</t>
         </is>
       </c>
       <c r="B100" s="15" t="inlineStr">
         <is>
-          <t>본사·해외 거점(일본·싱가포르·미국)</t>
-        </is>
-      </c>
-      <c r="C100" s="65" t="n">
-        <v>36000</v>
-      </c>
-      <c r="D100" s="65" t="n">
-        <v>144000</v>
-      </c>
-      <c r="E100" s="65" t="n">
-        <v>300000</v>
-      </c>
-      <c r="F100" s="65" t="n">
-        <v>600000</v>
-      </c>
-      <c r="G100" s="65" t="n">
-        <v>1000000</v>
+          <t>인증(CE-MDR·FDA·KC·PMDA)·시험·외주</t>
+        </is>
+      </c>
+      <c r="C100" s="94" t="n">
+        <v>0.035</v>
+      </c>
+      <c r="D100" s="94" t="n">
+        <v>0.035</v>
+      </c>
+      <c r="E100" s="94" t="n">
+        <v>0.032</v>
+      </c>
+      <c r="F100" s="94" t="n">
+        <v>0.029</v>
+      </c>
+      <c r="G100" s="94" t="n">
+        <v>0.031</v>
+      </c>
+      <c r="I100" s="89" t="inlineStr">
+        <is>
+          <t>개발비 자본화(BS 개발비 19.8억)는 별도. 신규 자본화·상각 증가분은 미반영(보수적 가정은 상각에서 반영)</t>
+        </is>
       </c>
     </row>
     <row r="101">
       <c r="A101" s="15" t="inlineStr">
         <is>
-          <t>해외영업·출장비(연, 천원)</t>
+          <t>대손상각비(매출 %)</t>
         </is>
       </c>
       <c r="B101" s="15" t="inlineStr"/>
-      <c r="C101" s="65" t="n">
-        <v>60000</v>
-      </c>
-      <c r="D101" s="65" t="n">
-        <v>180000</v>
-      </c>
-      <c r="E101" s="65" t="n">
-        <v>400000</v>
-      </c>
-      <c r="F101" s="65" t="n">
-        <v>800000</v>
-      </c>
-      <c r="G101" s="65" t="n">
-        <v>1400000</v>
+      <c r="C101" s="94" t="n">
+        <v>0.004</v>
+      </c>
+      <c r="D101" s="94" t="n">
+        <v>0.005</v>
+      </c>
+      <c r="E101" s="94" t="n">
+        <v>0.005</v>
+      </c>
+      <c r="F101" s="94" t="n">
+        <v>0.005</v>
+      </c>
+      <c r="G101" s="94" t="n">
+        <v>0.005</v>
       </c>
     </row>
     <row r="102">
       <c r="A102" s="15" t="inlineStr">
         <is>
-          <t>감가상각비-유형(연, 천원)</t>
+          <t>기타 판관비(매출 %)</t>
         </is>
       </c>
       <c r="B102" s="15" t="inlineStr">
         <is>
-          <t>설비·금형·사무기기</t>
-        </is>
-      </c>
-      <c r="C102" s="65" t="n">
-        <v>18000</v>
-      </c>
-      <c r="D102" s="65" t="n">
-        <v>40000</v>
-      </c>
-      <c r="E102" s="65" t="n">
-        <v>90000</v>
-      </c>
-      <c r="F102" s="65" t="n">
-        <v>180000</v>
-      </c>
-      <c r="G102" s="65" t="n">
-        <v>300000</v>
+          <t>보험·세금과공과·소모품·복리 외</t>
+        </is>
+      </c>
+      <c r="C102" s="94" t="n">
+        <v>0.025</v>
+      </c>
+      <c r="D102" s="94" t="n">
+        <v>0.03</v>
+      </c>
+      <c r="E102" s="94" t="n">
+        <v>0.026</v>
+      </c>
+      <c r="F102" s="94" t="n">
+        <v>0.022</v>
+      </c>
+      <c r="G102" s="94" t="n">
+        <v>0.024</v>
       </c>
     </row>
     <row r="103">
       <c r="A103" s="15" t="inlineStr">
         <is>
+          <t>임차·운영비(연, 천원)</t>
+        </is>
+      </c>
+      <c r="B103" s="15" t="inlineStr">
+        <is>
+          <t>본사·해외 거점(일본·싱가포르·미국)</t>
+        </is>
+      </c>
+      <c r="C103" s="65" t="n">
+        <v>36000</v>
+      </c>
+      <c r="D103" s="65" t="n">
+        <v>144000</v>
+      </c>
+      <c r="E103" s="65" t="n">
+        <v>300000</v>
+      </c>
+      <c r="F103" s="65" t="n">
+        <v>600000</v>
+      </c>
+      <c r="G103" s="65" t="n">
+        <v>1000000</v>
+      </c>
+    </row>
+    <row r="104">
+      <c r="A104" s="15" t="inlineStr">
+        <is>
+          <t>해외영업·출장비(연, 천원)</t>
+        </is>
+      </c>
+      <c r="B104" s="15" t="inlineStr"/>
+      <c r="C104" s="65" t="n">
+        <v>60000</v>
+      </c>
+      <c r="D104" s="65" t="n">
+        <v>180000</v>
+      </c>
+      <c r="E104" s="65" t="n">
+        <v>400000</v>
+      </c>
+      <c r="F104" s="65" t="n">
+        <v>800000</v>
+      </c>
+      <c r="G104" s="65" t="n">
+        <v>1400000</v>
+      </c>
+    </row>
+    <row r="105">
+      <c r="A105" s="15" t="inlineStr">
+        <is>
+          <t>감가상각비-유형(연, 천원)</t>
+        </is>
+      </c>
+      <c r="B105" s="15" t="inlineStr">
+        <is>
+          <t>설비·금형·사무기기</t>
+        </is>
+      </c>
+      <c r="C105" s="65" t="n">
+        <v>18000</v>
+      </c>
+      <c r="D105" s="65" t="n">
+        <v>40000</v>
+      </c>
+      <c r="E105" s="65" t="n">
+        <v>90000</v>
+      </c>
+      <c r="F105" s="65" t="n">
+        <v>180000</v>
+      </c>
+      <c r="G105" s="65" t="n">
+        <v>300000</v>
+      </c>
+    </row>
+    <row r="106">
+      <c r="A106" s="15" t="inlineStr">
+        <is>
           <t>개발비 무형자산상각(연, 천원)</t>
         </is>
       </c>
-      <c r="B103" s="15" t="inlineStr">
+      <c r="B106" s="15" t="inlineStr">
         <is>
           <t>2025.12 개발비 잔액 19.8억을 5년 정액 상각, 2027-01 개시(신규 자본화는 미반영)</t>
         </is>
       </c>
-      <c r="C103" s="65" t="n">
-        <v>0</v>
-      </c>
-      <c r="D103" s="65" t="n">
+      <c r="C106" s="65" t="n">
+        <v>0</v>
+      </c>
+      <c r="D106" s="65" t="n">
         <v>395953</v>
       </c>
-      <c r="E103" s="65" t="n">
+      <c r="E106" s="65" t="n">
         <v>395953</v>
       </c>
-      <c r="F103" s="65" t="n">
+      <c r="F106" s="65" t="n">
         <v>395953</v>
       </c>
-      <c r="G103" s="65" t="n">
+      <c r="G106" s="65" t="n">
         <v>395953</v>
       </c>
-      <c r="I103" s="86" t="inlineStr">
+      <c r="I106" s="89" t="inlineStr">
         <is>
           <t>확인 필요: 2025 감사보고서상 상각 개시 시점·내용연수. 2025 판관비에 상각이 보이지 않아 상품화 시점(2027)부터 반영하는 보수적 가정</t>
         </is>
       </c>
     </row>
-    <row r="105">
-      <c r="A105" s="84" t="inlineStr">
+    <row r="108">
+      <c r="A108" s="87" t="inlineStr">
         <is>
           <t>6. 영업외손익 · 법인세</t>
         </is>
       </c>
-      <c r="B105" s="85" t="n"/>
-      <c r="C105" s="85" t="n"/>
-      <c r="D105" s="85" t="n"/>
-      <c r="E105" s="85" t="n"/>
-      <c r="F105" s="85" t="n"/>
-      <c r="G105" s="85" t="n"/>
-      <c r="H105" s="85" t="n"/>
-      <c r="I105" s="85" t="n"/>
-    </row>
-    <row r="106">
-      <c r="A106" s="22" t="inlineStr">
+      <c r="B108" s="88" t="n"/>
+      <c r="C108" s="88" t="n"/>
+      <c r="D108" s="88" t="n"/>
+      <c r="E108" s="88" t="n"/>
+      <c r="F108" s="88" t="n"/>
+      <c r="G108" s="88" t="n"/>
+      <c r="H108" s="88" t="n"/>
+      <c r="I108" s="88" t="n"/>
+    </row>
+    <row r="109">
+      <c r="A109" s="22" t="inlineStr">
         <is>
           <t>구분</t>
         </is>
       </c>
-      <c r="B106" s="22" t="inlineStr">
+      <c r="B109" s="22" t="inlineStr">
         <is>
           <t>설명</t>
         </is>
       </c>
-      <c r="C106" s="22" t="n">
+      <c r="C109" s="22" t="n">
         <v>2026</v>
       </c>
-      <c r="D106" s="22" t="n">
+      <c r="D109" s="22" t="n">
         <v>2027</v>
       </c>
-      <c r="E106" s="22" t="n">
+      <c r="E109" s="22" t="n">
         <v>2028</v>
       </c>
-      <c r="F106" s="22" t="n">
+      <c r="F109" s="22" t="n">
         <v>2029</v>
       </c>
-      <c r="G106" s="22" t="n">
+      <c r="G109" s="22" t="n">
         <v>2030</v>
       </c>
-      <c r="H106" s="22" t="inlineStr"/>
-      <c r="I106" s="22" t="inlineStr">
+      <c r="H109" s="22" t="inlineStr"/>
+      <c r="I109" s="22" t="inlineStr">
         <is>
           <t>근거 · 비고</t>
-        </is>
-      </c>
-    </row>
-    <row r="107">
-      <c r="A107" s="15" t="inlineStr">
-        <is>
-          <t>차입금 기초(2025.12, 천원)</t>
-        </is>
-      </c>
-      <c r="B107" s="15" t="inlineStr">
-        <is>
-          <t>단기 1,135,833 + 장기 63,710</t>
-        </is>
-      </c>
-      <c r="C107" s="55" t="n">
-        <v>1199543</v>
-      </c>
-      <c r="I107" s="86" t="inlineStr">
-        <is>
-          <t>투자사 양식 차입금 현황(2025감사보고서 주석 5). 현재 잔액·만기 확인 필요</t>
-        </is>
-      </c>
-    </row>
-    <row r="108">
-      <c r="A108" s="15" t="inlineStr">
-        <is>
-          <t>차입금 연 이자율</t>
-        </is>
-      </c>
-      <c r="B108" s="15" t="inlineStr">
-        <is>
-          <t>2025 이자비용 0.50억/평균 차입금 ≈ 4.2% (우리 4.48~4.89%, 하나 5.00~5.58%)</t>
-        </is>
-      </c>
-      <c r="C108" s="91" t="n">
-        <v>0.048</v>
-      </c>
-      <c r="D108" s="91" t="n">
-        <v>0.048</v>
-      </c>
-      <c r="E108" s="91" t="n">
-        <v>0.048</v>
-      </c>
-      <c r="F108" s="91" t="n">
-        <v>0.048</v>
-      </c>
-      <c r="G108" s="91" t="n">
-        <v>0.048</v>
-      </c>
-    </row>
-    <row r="109">
-      <c r="A109" s="15" t="inlineStr">
-        <is>
-          <t>정부보조금수익(천원)</t>
-        </is>
-      </c>
-      <c r="B109" s="15" t="inlineStr">
-        <is>
-          <t>2026: GDIN 지원금 3,500만원 포함</t>
-        </is>
-      </c>
-      <c r="C109" s="65" t="n">
-        <v>65000</v>
-      </c>
-      <c r="D109" s="65" t="n">
-        <v>40000</v>
-      </c>
-      <c r="E109" s="65" t="n">
-        <v>30000</v>
-      </c>
-      <c r="F109" s="65" t="n">
-        <v>0</v>
-      </c>
-      <c r="G109" s="65" t="n">
-        <v>0</v>
-      </c>
-      <c r="I109" s="86" t="inlineStr">
-        <is>
-          <t>2024 0.88억, 2025 0.31억 실적. 이후 보수적으로 체감, 2029~ 미반영</t>
         </is>
       </c>
     </row>
     <row r="110">
       <c r="A110" s="15" t="inlineStr">
         <is>
-          <t>이월결손금 기초(천원)</t>
+          <t>차입금 기초(2025.12, 천원)</t>
         </is>
       </c>
       <c r="B110" s="15" t="inlineStr">
         <is>
-          <t>자본총계 − 자본금 − 주식발행초과금 역산(2025.12)</t>
-        </is>
-      </c>
-      <c r="C110" s="65" t="n">
-        <v>3032082</v>
-      </c>
-      <c r="I110" s="86" t="inlineStr">
-        <is>
-          <t>계산: 12.375억 − 4.276억 − 38.420억 ≈ −30.3억. 세무상 결손금과 다를 수 있음(세무사 확인)</t>
+          <t>단기 1,135,833 + 장기 63,710</t>
+        </is>
+      </c>
+      <c r="C110" s="55" t="n">
+        <v>1199543</v>
+      </c>
+      <c r="I110" s="89" t="inlineStr">
+        <is>
+          <t>투자사 양식 차입금 현황(2025감사보고서 주석 5). 현재 잔액·만기 확인 필요</t>
         </is>
       </c>
     </row>
     <row r="111">
       <c r="A111" s="15" t="inlineStr">
         <is>
-          <t>이월결손금 공제 한도(과세소득 대비)</t>
-        </is>
-      </c>
-      <c r="C111" s="88" t="n">
-        <v>1</v>
-      </c>
-      <c r="I111" s="86" t="inlineStr">
-        <is>
-          <t>중소기업 100% (일반법인 80%). 중소기업 졸업 시 한도 80% 적용 가능 — 보수적으로 보려면 80%로 변경</t>
-        </is>
+          <t>차입금 연 이자율</t>
+        </is>
+      </c>
+      <c r="B111" s="15" t="inlineStr">
+        <is>
+          <t>2025 이자비용 0.50억/평균 차입금 ≈ 4.2% (우리 4.48~4.89%, 하나 5.00~5.58%)</t>
+        </is>
+      </c>
+      <c r="C111" s="94" t="n">
+        <v>0.048</v>
+      </c>
+      <c r="D111" s="94" t="n">
+        <v>0.048</v>
+      </c>
+      <c r="E111" s="94" t="n">
+        <v>0.048</v>
+      </c>
+      <c r="F111" s="94" t="n">
+        <v>0.048</v>
+      </c>
+      <c r="G111" s="94" t="n">
+        <v>0.048</v>
       </c>
     </row>
     <row r="112">
       <c r="A112" s="15" t="inlineStr">
         <is>
-          <t>법인세율 구간(과세표준 상한, 천원)</t>
-        </is>
-      </c>
-      <c r="C112" s="55" t="n">
-        <v>200000</v>
-      </c>
-      <c r="D112" s="55" t="n">
-        <v>20000000</v>
-      </c>
-      <c r="E112" s="55" t="n">
-        <v>300000000</v>
+          <t>정부보조금수익(천원) — 2026은 아래 R&amp;D 과제·GDIN 합산식</t>
+        </is>
+      </c>
+      <c r="B112" s="15" t="inlineStr">
+        <is>
+          <t>2027~ 입력(보수적 체감)</t>
+        </is>
+      </c>
+      <c r="C112" s="96">
+        <f>MIN('8_가정'!$C$113,'7_비용인력'!$O$24+'8_가정'!$C$115*('7_비용인력'!$O$19+'7_비용인력'!$O$20))+'8_가정'!$C$114</f>
+        <v>295000</v>
+      </c>
+      <c r="D112" s="65" t="n">
+        <v>40000</v>
+      </c>
+      <c r="E112" s="65" t="n">
+        <v>30000</v>
+      </c>
+      <c r="F112" s="65" t="n">
+        <v>0</v>
+      </c>
+      <c r="G112" s="65" t="n">
+        <v>0</v>
+      </c>
+      <c r="I112" s="89" t="inlineStr">
+        <is>
+          <t>2024 0.88억, 2025 0.31억 실적(영업외수익 처리 선례). 2029~ 미반영</t>
+        </is>
       </c>
     </row>
     <row r="113">
       <c r="A113" s="15" t="inlineStr">
         <is>
-          <t>법인세율(구간별)</t>
-        </is>
-      </c>
-      <c r="C113" s="92" t="n">
-        <v>0.1</v>
-      </c>
-      <c r="D113" s="92" t="n">
-        <v>0.2</v>
-      </c>
-      <c r="E113" s="92" t="n">
-        <v>0.22</v>
-      </c>
-      <c r="F113" s="92" t="n">
-        <v>0.25</v>
-      </c>
-      <c r="I113" s="86" t="inlineStr">
-        <is>
-          <t>2026 귀속 10%/20%/22%/25% 가정(2025 세법개정 반영 여부 8_가정 하단 출처 메모 확인). 세액공제·최저한세 미반영</t>
-        </is>
+          <t>정부과제(R&amp;D) 2026 수령 예상액(천원)</t>
+        </is>
+      </c>
+      <c r="B113" s="15" t="inlineStr">
+        <is>
+          <t>사용자 제공: 약 2.6억원</t>
+        </is>
+      </c>
+      <c r="C113" s="65" t="n">
+        <v>260000</v>
       </c>
     </row>
     <row r="114">
       <c r="A114" s="15" t="inlineStr">
         <is>
-          <t>지방소득세율(법인세 대비)</t>
-        </is>
-      </c>
-      <c r="C114" s="67" t="n">
-        <v>0.1</v>
-      </c>
-    </row>
-    <row r="115">
+          <t>GDIN 해외진출 지원금(천원)</t>
+        </is>
+      </c>
+      <c r="B114" s="15" t="inlineStr">
+        <is>
+          <t>회사연혁 2026-09 최종 선정 3,500만원</t>
+        </is>
+      </c>
+      <c r="C114" s="65" t="n">
+        <v>35000</v>
+      </c>
+    </row>
+    <row r="115" ht="60" customHeight="1">
       <c r="A115" s="15" t="inlineStr">
         <is>
-          <t>매출채권 회전일수(참고)</t>
-        </is>
-      </c>
-      <c r="C115" s="89" t="n">
-        <v>60</v>
-      </c>
-      <c r="I115" s="86" t="inlineStr">
-        <is>
-          <t>손익계산서 범위 밖의 참고 지표(운전자본 소요 추정)용. 2025 BS: 매출채권 2,304만원·선급금 8,557만원. 총판 공급 비중이 커지면 회전일수가 길어질 수 있음</t>
+          <t>R&amp;D 인력 인건비 비중(과제 대응 가능분)</t>
+        </is>
+      </c>
+      <c r="B115" s="15" t="inlineStr">
+        <is>
+          <t>급여·퇴직·복리 중 연구개발 인력 비중(가정)</t>
+        </is>
+      </c>
+      <c r="C115" s="91" t="n">
+        <v>0.4</v>
+      </c>
+      <c r="I115" s="89" t="inlineStr">
+        <is>
+          <t>영업외수익 인식 한도 = 과제 수행으로 해당 연도에 비용 처리된 R&amp;D 비용(경상 연구개발비 + 연구 인력 인건비). 자산화(개발비)된 지출에 대응하는 보조금은 자산 차감이며 영업외수익이 아님(일반기업회계기준 17장). 수령액 중 미사용분은 선수·이연수익. 회사는 과거 정부보조금수익을 영업외수익으로 처리(2024 0.88억·2025 0.31억). 회계 담당 확인 필요</t>
         </is>
       </c>
     </row>
     <row r="116">
       <c r="A116" s="15" t="inlineStr">
         <is>
-          <t>재고자산 회전일수(매출원가 기준, 참고)</t>
-        </is>
-      </c>
-      <c r="C116" s="89" t="n">
-        <v>60</v>
+          <t>이월결손금 기초(천원)</t>
+        </is>
+      </c>
+      <c r="B116" s="15" t="inlineStr">
+        <is>
+          <t>자본총계 − 자본금 − 주식발행초과금 역산(2025.12)</t>
+        </is>
+      </c>
+      <c r="C116" s="65" t="n">
+        <v>3032082</v>
+      </c>
+      <c r="I116" s="89" t="inlineStr">
+        <is>
+          <t>계산: 12.375억 − 4.276억 − 38.420억 ≈ −30.3억. 세무상 결손금과 다를 수 있음(세무사 확인)</t>
+        </is>
       </c>
     </row>
     <row r="117">
       <c r="A117" s="15" t="inlineStr">
         <is>
-          <t>매입채무 회전일수(매출원가 기준, 참고)</t>
-        </is>
-      </c>
-      <c r="C117" s="89" t="n">
-        <v>45</v>
+          <t>이월결손금 공제 한도(과세소득 대비)</t>
+        </is>
+      </c>
+      <c r="C117" s="91" t="n">
+        <v>1</v>
+      </c>
+      <c r="I117" s="89" t="inlineStr">
+        <is>
+          <t>중소기업 100% (일반법인 80%). 중소기업 졸업 시 한도 80% 적용 가능 — 보수적으로 보려면 80%로 변경</t>
+        </is>
+      </c>
+    </row>
+    <row r="118">
+      <c r="A118" s="15" t="inlineStr">
+        <is>
+          <t>법인세율 구간(과세표준 상한, 천원)</t>
+        </is>
+      </c>
+      <c r="C118" s="55" t="n">
+        <v>200000</v>
+      </c>
+      <c r="D118" s="55" t="n">
+        <v>20000000</v>
+      </c>
+      <c r="E118" s="55" t="n">
+        <v>300000000</v>
       </c>
     </row>
     <row r="119">
-      <c r="A119" s="84" t="inlineStr">
-        <is>
-          <t>7. 근거 구분 범례 · 출처 메모</t>
-        </is>
-      </c>
-      <c r="B119" s="85" t="n"/>
-      <c r="C119" s="85" t="n"/>
-      <c r="D119" s="85" t="n"/>
-      <c r="E119" s="85" t="n"/>
-      <c r="F119" s="85" t="n"/>
-      <c r="G119" s="85" t="n"/>
-      <c r="H119" s="85" t="n"/>
-      <c r="I119" s="85" t="n"/>
+      <c r="A119" s="15" t="inlineStr">
+        <is>
+          <t>법인세율(구간별)</t>
+        </is>
+      </c>
+      <c r="C119" s="97" t="n">
+        <v>0.1</v>
+      </c>
+      <c r="D119" s="97" t="n">
+        <v>0.2</v>
+      </c>
+      <c r="E119" s="97" t="n">
+        <v>0.22</v>
+      </c>
+      <c r="F119" s="97" t="n">
+        <v>0.25</v>
+      </c>
+      <c r="I119" s="89" t="inlineStr">
+        <is>
+          <t>2026 귀속 10%/20%/22%/25% 가정(2025 세법개정 반영 여부 8_가정 하단 출처 메모 확인). 세액공제·최저한세 미반영</t>
+        </is>
+      </c>
     </row>
     <row r="120">
       <c r="A120" s="15" t="inlineStr">
         <is>
-          <t>IR 근거 = IR 자료(2026-09-27판) 페이지 표기. 계약/등록/입찰/PoC 단계는 IR 표기에 입찰 자료(저장소)·회사연혁을 교차 반영.</t>
-        </is>
+          <t>지방소득세율(법인세 대비)</t>
+        </is>
+      </c>
+      <c r="C120" s="67" t="n">
+        <v>0.1</v>
       </c>
     </row>
     <row r="121">
       <c r="A121" s="15" t="inlineStr">
         <is>
-          <t>가정 = IR에 없는 시작월·램프·성장률·비용률. 모두 파란색 입력이며 투자사 질의 시 근거 설명이 필요한 항목.</t>
+          <t>매출채권 회전일수(참고)</t>
+        </is>
+      </c>
+      <c r="C121" s="92" t="n">
+        <v>60</v>
+      </c>
+      <c r="I121" s="89" t="inlineStr">
+        <is>
+          <t>손익계산서 범위 밖의 참고 지표(운전자본 소요 추정)용. 2025 BS: 매출채권 2,304만원·선급금 8,557만원. 총판 공급 비중이 커지면 회전일수가 길어질 수 있음</t>
         </is>
       </c>
     </row>
     <row r="122">
       <c r="A122" s="15" t="inlineStr">
         <is>
+          <t>재고자산 회전일수(매출원가 기준, 참고)</t>
+        </is>
+      </c>
+      <c r="C122" s="92" t="n">
+        <v>60</v>
+      </c>
+    </row>
+    <row r="123">
+      <c r="A123" s="15" t="inlineStr">
+        <is>
+          <t>매입채무 회전일수(매출원가 기준, 참고)</t>
+        </is>
+      </c>
+      <c r="C123" s="92" t="n">
+        <v>45</v>
+      </c>
+    </row>
+    <row r="125">
+      <c r="A125" s="87" t="inlineStr">
+        <is>
+          <t>7. 근거 구분 범례 · 출처 메모</t>
+        </is>
+      </c>
+      <c r="B125" s="88" t="n"/>
+      <c r="C125" s="88" t="n"/>
+      <c r="D125" s="88" t="n"/>
+      <c r="E125" s="88" t="n"/>
+      <c r="F125" s="88" t="n"/>
+      <c r="G125" s="88" t="n"/>
+      <c r="H125" s="88" t="n"/>
+      <c r="I125" s="88" t="n"/>
+    </row>
+    <row r="126">
+      <c r="A126" s="15" t="inlineStr">
+        <is>
+          <t>IR 근거 = IR 자료(2026-09-27판) 페이지 표기. 계약/등록/입찰/PoC 단계는 IR 표기에 입찰 자료(저장소)·회사연혁을 교차 반영.</t>
+        </is>
+      </c>
+    </row>
+    <row r="127">
+      <c r="A127" s="15" t="inlineStr">
+        <is>
+          <t>가정 = IR에 없는 시작월·램프·성장률·비용률. 모두 파란색 입력이며 투자사 질의 시 근거 설명이 필요한 항목.</t>
+        </is>
+      </c>
+    </row>
+    <row r="128">
+      <c r="A128" s="15" t="inlineStr">
+        <is>
           <t>회사실적 = 투자사 양식 IS(2025 감사보고서 기준: 2024·2025). 2026 상반기 실적은 자료 없음 → 추정.</t>
         </is>
       </c>
     </row>
-    <row r="124">
-      <c r="A124" s="9" t="inlineStr">
+    <row r="130">
+      <c r="A130" s="9" t="inlineStr">
         <is>
           <t>외부 팩트 조사 요약(출처 URL 포함)</t>
         </is>
       </c>
     </row>
-    <row r="125">
-      <c r="A125" s="69" t="inlineStr">
+    <row r="131">
+      <c r="A131" s="69" t="inlineStr">
         <is>
           <t>환율: 2026-10-02 서울 종가 USD/KRW 1,350.60 · JPY 856.76/100엔 · EUR 1,520.64 (서울신문 2026/10/02, snmnews). 본 계획은 IR 고정환율 1,400원/달러 기준이며 SGD·JPY·EUR은 1,400 기준 교차환율을 사용(현물환 대비 USD 약 +3.7%).</t>
         </is>
       </c>
     </row>
-    <row r="126">
-      <c r="A126" s="69" t="inlineStr">
+    <row r="132">
+      <c r="A132" s="69" t="inlineStr">
         <is>
           <t>법인세: 2026 귀속 10/20/22/25%(+1%p, 2025-12-02 국회 통과·12-23 공포), 지방소득세 1.0/2.0/2.2/2.5%(국세청 nts.go.kr, 국회예산정책처 nabo.go.kr). 결손금 15년 이월, 중소기업은 소득의 100%까지 공제, 중소기업 졸업 유예 5년, 최저한세(중소) 7%.</t>
         </is>
       </c>
     </row>
-    <row r="127">
-      <c r="A127" s="69" t="inlineStr">
+    <row r="133">
+      <c r="A133" s="69" t="inlineStr">
         <is>
           <t>일본: 介護テクノロジー導入支援事業(2025년 통합) 보조율 3/4~4/5, 배설예측·검지 기기 1대당 상한 30만엔, TAIS 介護テクノロジー 선정이 보조금 신청 조건(techno-aids.or.jp). TAIS 등록 자체는 보험급여가 아님 → IR의 "TAIS 등록 완료"가 보조금 대상 선정을 뜻하는지 확인 필요. 시설 수(MHLW 2024): 특양 8,621 · 老健 4,214 · GH 14,341 · 유료노인홈 16,543.</t>
         </is>
       </c>
     </row>
-    <row r="128">
-      <c r="A128" s="69" t="inlineStr">
+    <row r="134">
+      <c r="A134" s="69" t="inlineStr">
         <is>
           <t>한국: 기저귀센서는 2025-05 정규 복지용구 급여 편입(고시상 1개 제품), 재가 본인부담 15%(85% 지원)·연 한도 160만원, 성인용 기저귀 자체는 급여 품목이 아님(nhis.or.kr). 장기요양기관 29,734곳(시설 6,361·재가 23,373, 2025), 요양병원 약 1,300곳(감소 추세), 요양병원 간병비 건보 적용 2027~(보도).</t>
         </is>
       </c>
     </row>
-    <row r="129">
-      <c r="A129" s="69" t="inlineStr">
+    <row r="135">
+      <c r="A135" s="69" t="inlineStr">
         <is>
           <t>동종 벤치마크: Essity FY2025 EBITA 마진 14.1%, Ontex FY2025 조정 EBITDA 마진 10.0% → 본 계획 S1의 2030 영업이익률은 약 14% 이내로 설정(상한 근거). 일부 공식 사이트 접근 제한으로 보도·2차 자료를 포함하므로 제출 전 재확인 권장.</t>
         </is>
@@ -37215,19 +37577,19 @@
           <t>매출액</t>
         </is>
       </c>
-      <c r="C6" s="93" t="n">
+      <c r="C6" s="98" t="n">
         <v>12</v>
       </c>
-      <c r="D6" s="93" t="n">
+      <c r="D6" s="98" t="n">
         <v>100.0204</v>
       </c>
-      <c r="E6" s="93" t="n">
+      <c r="E6" s="98" t="n">
         <v>330</v>
       </c>
-      <c r="F6" s="93" t="n">
+      <c r="F6" s="98" t="n">
         <v>700</v>
       </c>
-      <c r="G6" s="93" t="n">
+      <c r="G6" s="98" t="n">
         <v>1560</v>
       </c>
       <c r="H6" s="14">
@@ -37241,19 +37603,19 @@
           <t>매출총이익</t>
         </is>
       </c>
-      <c r="C7" s="93" t="n">
+      <c r="C7" s="98" t="n">
         <v>5.69602889265537</v>
       </c>
-      <c r="D7" s="93" t="n">
+      <c r="D7" s="98" t="n">
         <v>39.70696944</v>
       </c>
-      <c r="E7" s="93" t="n">
+      <c r="E7" s="98" t="n">
         <v>130.740831629043</v>
       </c>
-      <c r="F7" s="93" t="n">
+      <c r="F7" s="98" t="n">
         <v>279.249885140102</v>
       </c>
-      <c r="G7" s="93" t="n">
+      <c r="G7" s="98" t="n">
         <v>637.123055449323</v>
       </c>
     </row>
@@ -37263,20 +37625,20 @@
           <t>영업이익</t>
         </is>
       </c>
-      <c r="C8" s="93" t="n">
-        <v>-2.92328310734463</v>
-      </c>
-      <c r="D8" s="93" t="n">
-        <v>3.26335378</v>
-      </c>
-      <c r="E8" s="93" t="n">
-        <v>19.1966269398429</v>
-      </c>
-      <c r="F8" s="93" t="n">
-        <v>54.9743045583219</v>
-      </c>
-      <c r="G8" s="93" t="n">
-        <v>164.668697971292</v>
+      <c r="C8" s="98" t="n">
+        <v>-2.86316150734463</v>
+      </c>
+      <c r="D8" s="98" t="n">
+        <v>5.569748408</v>
+      </c>
+      <c r="E8" s="98" t="n">
+        <v>34.1354094148028</v>
+      </c>
+      <c r="F8" s="98" t="n">
+        <v>93.7766092908651</v>
+      </c>
+      <c r="G8" s="98" t="n">
+        <v>250.42035249864</v>
       </c>
     </row>
     <row r="9">
@@ -37285,20 +37647,20 @@
           <t>영업이익률</t>
         </is>
       </c>
-      <c r="C9" s="94" t="n">
-        <v>-0.243606925612053</v>
-      </c>
-      <c r="D9" s="94" t="n">
-        <v>0.0326268819160891</v>
-      </c>
-      <c r="E9" s="94" t="n">
-        <v>0.0581715967874026</v>
-      </c>
-      <c r="F9" s="94" t="n">
-        <v>0.07853472079760269</v>
-      </c>
-      <c r="G9" s="94" t="n">
-        <v>0.105556857673905</v>
+      <c r="C9" s="99" t="n">
+        <v>-0.238596792278719</v>
+      </c>
+      <c r="D9" s="99" t="n">
+        <v>0.0556861241106814</v>
+      </c>
+      <c r="E9" s="99" t="n">
+        <v>0.103440634590312</v>
+      </c>
+      <c r="F9" s="99" t="n">
+        <v>0.133966584701236</v>
+      </c>
+      <c r="G9" s="99" t="n">
+        <v>0.160525866986308</v>
       </c>
     </row>
     <row r="10">
@@ -37307,20 +37669,20 @@
           <t>당기순이익</t>
         </is>
       </c>
-      <c r="C10" s="93" t="n">
-        <v>-2.84917342734463</v>
-      </c>
-      <c r="D10" s="93" t="n">
-        <v>2.89535378</v>
-      </c>
-      <c r="E10" s="93" t="n">
-        <v>17.5766269398429</v>
-      </c>
-      <c r="F10" s="93" t="n">
-        <v>42.89832035114149</v>
-      </c>
-      <c r="G10" s="93" t="n">
-        <v>124.543184417608</v>
+      <c r="C10" s="98" t="n">
+        <v>-0.489051827344633</v>
+      </c>
+      <c r="D10" s="98" t="n">
+        <v>5.201748408</v>
+      </c>
+      <c r="E10" s="98" t="n">
+        <v>31.215806495802</v>
+      </c>
+      <c r="F10" s="98" t="n">
+        <v>70.3705552468748</v>
+      </c>
+      <c r="G10" s="98" t="n">
+        <v>190.436387193969</v>
       </c>
     </row>
     <row r="11">
@@ -37329,19 +37691,19 @@
           <t>추정 유료 이용자(명)</t>
         </is>
       </c>
-      <c r="C11" s="95" t="n">
+      <c r="C11" s="100" t="n">
         <v>950</v>
       </c>
-      <c r="D11" s="95" t="n">
+      <c r="D11" s="100" t="n">
         <v>8012.73233333333</v>
       </c>
-      <c r="E11" s="95" t="n">
+      <c r="E11" s="100" t="n">
         <v>25314.3276219453</v>
       </c>
-      <c r="F11" s="95" t="n">
+      <c r="F11" s="100" t="n">
         <v>50824.2010157023</v>
       </c>
-      <c r="G11" s="95" t="n">
+      <c r="G11" s="100" t="n">
         <v>106776.188196769</v>
       </c>
     </row>
@@ -37351,19 +37713,19 @@
           <t>IR 대비 달성률</t>
         </is>
       </c>
-      <c r="C12" s="94" t="n">
+      <c r="C12" s="99" t="n">
         <v>1</v>
       </c>
-      <c r="D12" s="94" t="n">
+      <c r="D12" s="99" t="n">
         <v>0.999704147926037</v>
       </c>
-      <c r="E12" s="94" t="n">
+      <c r="E12" s="99" t="n">
         <v>1</v>
       </c>
-      <c r="F12" s="94" t="n">
+      <c r="F12" s="99" t="n">
         <v>1</v>
       </c>
-      <c r="G12" s="94" t="n">
+      <c r="G12" s="99" t="n">
         <v>1</v>
       </c>
     </row>
@@ -37410,19 +37772,19 @@
           <t>매출액</t>
         </is>
       </c>
-      <c r="C17" s="93" t="n">
+      <c r="C17" s="98" t="n">
         <v>9.941734869518431</v>
       </c>
-      <c r="D17" s="93" t="n">
+      <c r="D17" s="98" t="n">
         <v>53.4707597152194</v>
       </c>
-      <c r="E17" s="93" t="n">
+      <c r="E17" s="98" t="n">
         <v>193.742176438788</v>
       </c>
-      <c r="F17" s="93" t="n">
+      <c r="F17" s="98" t="n">
         <v>333.375772432319</v>
       </c>
-      <c r="G17" s="93" t="n">
+      <c r="G17" s="98" t="n">
         <v>596.630567009663</v>
       </c>
       <c r="H17" s="14">
@@ -37436,19 +37798,19 @@
           <t>매출총이익</t>
         </is>
       </c>
-      <c r="C18" s="93" t="n">
+      <c r="C18" s="98" t="n">
         <v>4.71942249350713</v>
       </c>
-      <c r="D18" s="93" t="n">
+      <c r="D18" s="98" t="n">
         <v>21.2115992788123</v>
       </c>
-      <c r="E18" s="93" t="n">
+      <c r="E18" s="98" t="n">
         <v>76.63788467946141</v>
       </c>
-      <c r="F18" s="93" t="n">
+      <c r="F18" s="98" t="n">
         <v>132.712604303856</v>
       </c>
-      <c r="G18" s="93" t="n">
+      <c r="G18" s="98" t="n">
         <v>242.996605322923</v>
       </c>
     </row>
@@ -37458,20 +37820,20 @@
           <t>영업이익</t>
         </is>
       </c>
-      <c r="C19" s="93" t="n">
-        <v>-2.87804937460938</v>
-      </c>
-      <c r="D19" s="93" t="n">
-        <v>-3.41834516606513</v>
-      </c>
-      <c r="E19" s="93" t="n">
-        <v>1.41687759891742</v>
-      </c>
-      <c r="F19" s="93" t="n">
-        <v>-2.35437829103144</v>
-      </c>
-      <c r="G19" s="93" t="n">
-        <v>5.45283719214369</v>
+      <c r="C19" s="98" t="n">
+        <v>-3.0017516392392</v>
+      </c>
+      <c r="D19" s="98" t="n">
+        <v>-2.48610320759547</v>
+      </c>
+      <c r="E19" s="98" t="n">
+        <v>10.9980502220071</v>
+      </c>
+      <c r="F19" s="98" t="n">
+        <v>21.6798139060112</v>
+      </c>
+      <c r="G19" s="98" t="n">
+        <v>52.3759218444459</v>
       </c>
     </row>
     <row r="20">
@@ -37480,20 +37842,20 @@
           <t>영업이익률</t>
         </is>
       </c>
-      <c r="C20" s="94" t="n">
-        <v>-0.28949166442102</v>
-      </c>
-      <c r="D20" s="94" t="n">
-        <v>-0.0639292425293924</v>
-      </c>
-      <c r="E20" s="94" t="n">
-        <v>0.00731321194466437</v>
-      </c>
-      <c r="F20" s="94" t="n">
-        <v>-0.00706223572833091</v>
-      </c>
-      <c r="G20" s="94" t="n">
-        <v>0.00913938623606486</v>
+      <c r="C20" s="99" t="n">
+        <v>-0.301934388578661</v>
+      </c>
+      <c r="D20" s="99" t="n">
+        <v>-0.0464946303519201</v>
+      </c>
+      <c r="E20" s="99" t="n">
+        <v>0.0567664223875481</v>
+      </c>
+      <c r="F20" s="99" t="n">
+        <v>0.06503116212625359</v>
+      </c>
+      <c r="G20" s="99" t="n">
+        <v>0.08778618585862299</v>
       </c>
     </row>
     <row r="21">
@@ -37502,20 +37864,20 @@
           <t>당기순이익</t>
         </is>
       </c>
-      <c r="C21" s="93" t="n">
-        <v>-2.80393969460938</v>
-      </c>
-      <c r="D21" s="93" t="n">
-        <v>-3.78634516606513</v>
-      </c>
-      <c r="E21" s="93" t="n">
-        <v>-0.203122401082581</v>
-      </c>
-      <c r="F21" s="93" t="n">
-        <v>-6.19437829103144</v>
-      </c>
-      <c r="G21" s="93" t="n">
-        <v>0.172837192143686</v>
+      <c r="C21" s="98" t="n">
+        <v>-0.7085080836531791</v>
+      </c>
+      <c r="D21" s="98" t="n">
+        <v>-2.85410320759547</v>
+      </c>
+      <c r="E21" s="98" t="n">
+        <v>9.378050222007131</v>
+      </c>
+      <c r="F21" s="98" t="n">
+        <v>17.8398139060112</v>
+      </c>
+      <c r="G21" s="98" t="n">
+        <v>38.4212438145785</v>
       </c>
     </row>
     <row r="22">
@@ -37524,19 +37886,19 @@
           <t>추정 유료 이용자(명)</t>
         </is>
       </c>
-      <c r="C22" s="95" t="n">
+      <c r="C22" s="100" t="n">
         <v>798.477905793203</v>
       </c>
-      <c r="D22" s="95" t="n">
+      <c r="D22" s="100" t="n">
         <v>4250.92186782991</v>
       </c>
-      <c r="E22" s="95" t="n">
+      <c r="E22" s="100" t="n">
         <v>14856.397714467</v>
       </c>
-      <c r="F22" s="95" t="n">
+      <c r="F22" s="100" t="n">
         <v>24346.4317211893</v>
       </c>
-      <c r="G22" s="95" t="n">
+      <c r="G22" s="100" t="n">
         <v>41227.8318993304</v>
       </c>
     </row>
@@ -37546,19 +37908,19 @@
           <t>IR 대비 달성률</t>
         </is>
       </c>
-      <c r="C23" s="94" t="n">
+      <c r="C23" s="99" t="n">
         <v>0.828477905793203</v>
       </c>
-      <c r="D23" s="94" t="n">
+      <c r="D23" s="99" t="n">
         <v>0.534440376963712</v>
       </c>
-      <c r="E23" s="94" t="n">
+      <c r="E23" s="99" t="n">
         <v>0.587097504359965</v>
       </c>
-      <c r="F23" s="94" t="n">
+      <c r="F23" s="99" t="n">
         <v>0.476251103474742</v>
       </c>
-      <c r="G23" s="94" t="n">
+      <c r="G23" s="99" t="n">
         <v>0.382455491672861</v>
       </c>
     </row>
@@ -37605,19 +37967,19 @@
           <t>매출액</t>
         </is>
       </c>
-      <c r="C28" s="93" t="n">
+      <c r="C28" s="98" t="n">
         <v>8.12591725047081</v>
       </c>
-      <c r="D28" s="93" t="n">
+      <c r="D28" s="98" t="n">
         <v>31.6659511554622</v>
       </c>
-      <c r="E28" s="93" t="n">
+      <c r="E28" s="98" t="n">
         <v>121.921519861036</v>
       </c>
-      <c r="F28" s="93" t="n">
+      <c r="F28" s="98" t="n">
         <v>169.662813262411</v>
       </c>
-      <c r="G28" s="93" t="n">
+      <c r="G28" s="98" t="n">
         <v>242.1625908615</v>
       </c>
       <c r="H28" s="14">
@@ -37631,19 +37993,19 @@
           <t>매출총이익</t>
         </is>
       </c>
-      <c r="C29" s="93" t="n">
+      <c r="C29" s="98" t="n">
         <v>3.86346715856121</v>
       </c>
-      <c r="D29" s="93" t="n">
+      <c r="D29" s="98" t="n">
         <v>12.5435352277311</v>
       </c>
-      <c r="E29" s="93" t="n">
+      <c r="E29" s="98" t="n">
         <v>48.1676516879981</v>
       </c>
-      <c r="F29" s="93" t="n">
+      <c r="F29" s="98" t="n">
         <v>67.38635189416171</v>
       </c>
-      <c r="G29" s="93" t="n">
+      <c r="G29" s="98" t="n">
         <v>98.2688073169506</v>
       </c>
     </row>
@@ -37653,20 +38015,20 @@
           <t>영업이익</t>
         </is>
       </c>
-      <c r="C30" s="93" t="n">
-        <v>-2.83252934185578</v>
-      </c>
-      <c r="D30" s="93" t="n">
-        <v>-6.5526427335011</v>
-      </c>
-      <c r="E30" s="93" t="n">
-        <v>-8.12172093501316</v>
-      </c>
-      <c r="F30" s="93" t="n">
-        <v>-26.7672034641743</v>
-      </c>
-      <c r="G30" s="93" t="n">
-        <v>-50.6570296309993</v>
+      <c r="C30" s="98" t="n">
+        <v>-3.11840245962451</v>
+      </c>
+      <c r="D30" s="98" t="n">
+        <v>-6.245432504077949</v>
+      </c>
+      <c r="E30" s="98" t="n">
+        <v>-1.29351714627082</v>
+      </c>
+      <c r="F30" s="98" t="n">
+        <v>-9.732215931278029</v>
+      </c>
+      <c r="G30" s="98" t="n">
+        <v>-18.9295182039728</v>
       </c>
     </row>
     <row r="31">
@@ -37675,20 +38037,20 @@
           <t>영업이익률</t>
         </is>
       </c>
-      <c r="C31" s="94" t="n">
-        <v>-0.348579643940094</v>
-      </c>
-      <c r="D31" s="94" t="n">
-        <v>-0.206930235612734</v>
-      </c>
-      <c r="E31" s="94" t="n">
-        <v>-0.0666143347316385</v>
-      </c>
-      <c r="F31" s="94" t="n">
-        <v>-0.157767061322828</v>
-      </c>
-      <c r="G31" s="94" t="n">
-        <v>-0.209186024359855</v>
+      <c r="C31" s="99" t="n">
+        <v>-0.383760056065527</v>
+      </c>
+      <c r="D31" s="99" t="n">
+        <v>-0.197228640738324</v>
+      </c>
+      <c r="E31" s="99" t="n">
+        <v>-0.010609424388288</v>
+      </c>
+      <c r="F31" s="99" t="n">
+        <v>-0.0573621039527713</v>
+      </c>
+      <c r="G31" s="99" t="n">
+        <v>-0.0781686309872657</v>
       </c>
     </row>
     <row r="32">
@@ -37697,20 +38059,20 @@
           <t>당기순이익</t>
         </is>
       </c>
-      <c r="C32" s="93" t="n">
-        <v>-2.75841966185578</v>
-      </c>
-      <c r="D32" s="93" t="n">
-        <v>-6.920642733501101</v>
-      </c>
-      <c r="E32" s="93" t="n">
-        <v>-9.741720935013161</v>
-      </c>
-      <c r="F32" s="93" t="n">
-        <v>-30.6072034641743</v>
-      </c>
-      <c r="G32" s="93" t="n">
-        <v>-55.93702963099931</v>
+      <c r="C32" s="98" t="n">
+        <v>-1.10018038900559</v>
+      </c>
+      <c r="D32" s="98" t="n">
+        <v>-6.61343250407795</v>
+      </c>
+      <c r="E32" s="98" t="n">
+        <v>-2.91351714627082</v>
+      </c>
+      <c r="F32" s="98" t="n">
+        <v>-13.572215931278</v>
+      </c>
+      <c r="G32" s="98" t="n">
+        <v>-24.2095182039728</v>
       </c>
     </row>
     <row r="33">
@@ -37719,19 +38081,19 @@
           <t>추정 유료 이용자(명)</t>
         </is>
       </c>
-      <c r="C33" s="95" t="n">
+      <c r="C33" s="100" t="n">
         <v>664.6597708725679</v>
       </c>
-      <c r="D33" s="95" t="n">
+      <c r="D33" s="100" t="n">
         <v>2498.13644389006</v>
       </c>
-      <c r="E33" s="95" t="n">
+      <c r="E33" s="100" t="n">
         <v>9359.57940320056</v>
       </c>
-      <c r="F33" s="95" t="n">
+      <c r="F33" s="100" t="n">
         <v>12484.9304710239</v>
       </c>
-      <c r="G33" s="95" t="n">
+      <c r="G33" s="100" t="n">
         <v>16957.0995423584</v>
       </c>
     </row>
@@ -37741,19 +38103,19 @@
           <t>IR 대비 달성률</t>
         </is>
       </c>
-      <c r="C34" s="94" t="n">
+      <c r="C34" s="99" t="n">
         <v>0.677159770872567</v>
       </c>
-      <c r="D34" s="94" t="n">
+      <c r="D34" s="99" t="n">
         <v>0.31650126092416</v>
       </c>
-      <c r="E34" s="94" t="n">
+      <c r="E34" s="99" t="n">
         <v>0.369459151094048</v>
       </c>
-      <c r="F34" s="94" t="n">
+      <c r="F34" s="99" t="n">
         <v>0.24237544751773</v>
       </c>
-      <c r="G34" s="94" t="n">
+      <c r="G34" s="99" t="n">
         <v>0.155232430039423</v>
       </c>
     </row>
@@ -37863,23 +38225,23 @@
       </c>
       <c r="C41" s="17">
         <f>'3_연간손익'!D13/100000</f>
-        <v>-2.92328310734463</v>
+        <v>-2.86316150734463</v>
       </c>
       <c r="D41" s="17">
         <f>'3_연간손익'!E13/100000</f>
-        <v>3.26335378</v>
+        <v>5.569748408</v>
       </c>
       <c r="E41" s="17">
         <f>'3_연간손익'!F13/100000</f>
-        <v>19.1966269398429</v>
+        <v>34.1354094148028</v>
       </c>
       <c r="F41" s="17">
         <f>'3_연간손익'!G13/100000</f>
-        <v>54.9743045583219</v>
+        <v>93.7766092908651</v>
       </c>
       <c r="G41" s="17">
         <f>'3_연간손익'!H13/100000</f>
-        <v>164.668697971292</v>
+        <v>250.42035249864</v>
       </c>
     </row>
     <row r="42">
@@ -37894,23 +38256,23 @@
       </c>
       <c r="C42" s="16">
         <f>'3_연간손익'!D14</f>
-        <v>-0.243606925612053</v>
+        <v>-0.238596792278719</v>
       </c>
       <c r="D42" s="16">
         <f>'3_연간손익'!E14</f>
-        <v>0.0326268819160891</v>
+        <v>0.0556861241106814</v>
       </c>
       <c r="E42" s="16">
         <f>'3_연간손익'!F14</f>
-        <v>0.0581715967874026</v>
+        <v>0.103440634590312</v>
       </c>
       <c r="F42" s="16">
         <f>'3_연간손익'!G14</f>
-        <v>0.0785347207976027</v>
+        <v>0.133966584701236</v>
       </c>
       <c r="G42" s="16">
         <f>'3_연간손익'!H14</f>
-        <v>0.105556857673905</v>
+        <v>0.160525866986308</v>
       </c>
     </row>
     <row r="43">
@@ -37925,23 +38287,23 @@
       </c>
       <c r="C43" s="17">
         <f>'3_연간손익'!D21/100000</f>
-        <v>-2.84917342734463</v>
+        <v>-0.489051827344633</v>
       </c>
       <c r="D43" s="17">
         <f>'3_연간손익'!E21/100000</f>
-        <v>2.89535378</v>
+        <v>5.201748408</v>
       </c>
       <c r="E43" s="17">
         <f>'3_연간손익'!F21/100000</f>
-        <v>17.5766269398429</v>
+        <v>31.215806495802</v>
       </c>
       <c r="F43" s="17">
         <f>'3_연간손익'!G21/100000</f>
-        <v>42.8983203511415</v>
+        <v>70.3705552468748</v>
       </c>
       <c r="G43" s="17">
         <f>'3_연간손익'!H21/100000</f>
-        <v>124.543184417608</v>
+        <v>190.436387193969</v>
       </c>
     </row>
     <row r="44">
@@ -38013,23 +38375,23 @@
           <t>점검: 라이브 매출 = 선택 시나리오 스냅샷</t>
         </is>
       </c>
-      <c r="C47" s="96" t="str">
+      <c r="C47" s="101" t="str">
         <f>IF(ISNUMBER(C6),IF(ABS(C39-CHOOSE('1_요약'!$C$5,C6,C17,C28))&lt;0.05,"OK","갱신 필요"),"스냅샷 없음")</f>
         <v>OK</v>
       </c>
-      <c r="D47" s="96" t="str">
+      <c r="D47" s="101" t="str">
         <f>IF(ISNUMBER(D6),IF(ABS(D39-CHOOSE('1_요약'!$C$5,D6,D17,D28))&lt;0.05,"OK","갱신 필요"),"스냅샷 없음")</f>
         <v>OK</v>
       </c>
-      <c r="E47" s="96" t="str">
+      <c r="E47" s="101" t="str">
         <f>IF(ISNUMBER(E6),IF(ABS(E39-CHOOSE('1_요약'!$C$5,E6,E17,E28))&lt;0.05,"OK","갱신 필요"),"스냅샷 없음")</f>
         <v>OK</v>
       </c>
-      <c r="F47" s="96" t="str">
+      <c r="F47" s="101" t="str">
         <f>IF(ISNUMBER(F6),IF(ABS(F39-CHOOSE('1_요약'!$C$5,F6,F17,F28))&lt;0.05,"OK","갱신 필요"),"스냅샷 없음")</f>
         <v>OK</v>
       </c>
-      <c r="G47" s="96" t="str">
+      <c r="G47" s="101" t="str">
         <f>IF(ISNUMBER(G6),IF(ABS(G39-CHOOSE('1_요약'!$C$5,G6,G17,G28))&lt;0.05,"OK","갱신 필요"),"스냅샷 없음")</f>
         <v>OK</v>
       </c>

--- a/모닛_5개년_사업계획_손익계산서_2026-2030.xlsx
+++ b/모닛_5개년_사업계획_손익계산서_2026-2030.xlsx
@@ -1747,23 +1747,23 @@
       </c>
       <c r="E14" s="17">
         <f>'3_연간손익'!E21/100000</f>
-        <v>5.201748408</v>
+        <v>7.801748408</v>
       </c>
       <c r="F14" s="17">
         <f>'3_연간손익'!F21/100000</f>
-        <v>31.215806495802</v>
+        <v>31.189806495802</v>
       </c>
       <c r="G14" s="17">
         <f>'3_연간손익'!G21/100000</f>
-        <v>70.3705552468748</v>
+        <v>71.1505552468748</v>
       </c>
       <c r="H14" s="17">
         <f>'3_연간손익'!H21/100000</f>
-        <v>190.436387193969</v>
+        <v>191.194387193969</v>
       </c>
       <c r="I14" s="14">
         <f>IFERROR(('3_연간손익'!H21/'3_연간손익'!C21)^(1/5)-1,"n/a")</f>
-        <v>4.16772250041508</v>
+        <v>4.17182981621665</v>
       </c>
     </row>
     <row r="15">
@@ -9042,71 +9042,71 @@
       </c>
       <c r="P46" s="25">
         <f>P47</f>
-        <v>3333.33333333333</v>
+        <v>25000</v>
       </c>
       <c r="Q46" s="25">
         <f>Q47</f>
-        <v>3333.33333333333</v>
+        <v>25000</v>
       </c>
       <c r="R46" s="25">
         <f>R47</f>
-        <v>3333.33333333333</v>
+        <v>25000</v>
       </c>
       <c r="S46" s="25">
         <f>S47</f>
-        <v>3333.33333333333</v>
+        <v>25000</v>
       </c>
       <c r="T46" s="25">
         <f>T47</f>
-        <v>3333.33333333333</v>
+        <v>25000</v>
       </c>
       <c r="U46" s="25">
         <f>U47</f>
-        <v>3333.33333333333</v>
+        <v>25000</v>
       </c>
       <c r="V46" s="25">
         <f>V47</f>
-        <v>3333.33333333333</v>
+        <v>25000</v>
       </c>
       <c r="W46" s="25">
         <f>W47</f>
-        <v>3333.33333333333</v>
+        <v>25000</v>
       </c>
       <c r="X46" s="25">
         <f>X47</f>
-        <v>3333.33333333333</v>
+        <v>25000</v>
       </c>
       <c r="Y46" s="25">
         <f>Y47</f>
-        <v>3333.33333333333</v>
+        <v>25000</v>
       </c>
       <c r="Z46" s="25">
         <f>Z47</f>
-        <v>3333.33333333333</v>
+        <v>25000</v>
       </c>
       <c r="AA46" s="25">
         <f>AA47</f>
-        <v>3333.33333333333</v>
+        <v>25000</v>
       </c>
       <c r="AB46" s="23">
         <f>AB47</f>
-        <v>40000</v>
+        <v>300000</v>
       </c>
       <c r="AC46" s="34">
         <f>AC47</f>
-        <v>30000</v>
+        <v>100000</v>
       </c>
       <c r="AD46" s="34">
         <f>AD47</f>
-        <v>0</v>
+        <v>100000</v>
       </c>
       <c r="AE46" s="34">
         <f>AE47</f>
-        <v>0</v>
+        <v>100000</v>
       </c>
       <c r="AF46" s="25">
         <f>AF47</f>
-        <v>365000</v>
+        <v>895000</v>
       </c>
     </row>
     <row r="47">
@@ -9169,71 +9169,71 @@
       </c>
       <c r="P47" s="40">
         <f>'7_비용인력'!P33</f>
-        <v>3333.33333333333</v>
+        <v>25000</v>
       </c>
       <c r="Q47" s="40">
         <f>'7_비용인력'!Q33</f>
-        <v>3333.33333333333</v>
+        <v>25000</v>
       </c>
       <c r="R47" s="40">
         <f>'7_비용인력'!R33</f>
-        <v>3333.33333333333</v>
+        <v>25000</v>
       </c>
       <c r="S47" s="40">
         <f>'7_비용인력'!S33</f>
-        <v>3333.33333333333</v>
+        <v>25000</v>
       </c>
       <c r="T47" s="40">
         <f>'7_비용인력'!T33</f>
-        <v>3333.33333333333</v>
+        <v>25000</v>
       </c>
       <c r="U47" s="40">
         <f>'7_비용인력'!U33</f>
-        <v>3333.33333333333</v>
+        <v>25000</v>
       </c>
       <c r="V47" s="40">
         <f>'7_비용인력'!V33</f>
-        <v>3333.33333333333</v>
+        <v>25000</v>
       </c>
       <c r="W47" s="40">
         <f>'7_비용인력'!W33</f>
-        <v>3333.33333333333</v>
+        <v>25000</v>
       </c>
       <c r="X47" s="40">
         <f>'7_비용인력'!X33</f>
-        <v>3333.33333333333</v>
+        <v>25000</v>
       </c>
       <c r="Y47" s="40">
         <f>'7_비용인력'!Y33</f>
-        <v>3333.33333333333</v>
+        <v>25000</v>
       </c>
       <c r="Z47" s="40">
         <f>'7_비용인력'!Z33</f>
-        <v>3333.33333333333</v>
+        <v>25000</v>
       </c>
       <c r="AA47" s="40">
         <f>'7_비용인력'!AA33</f>
-        <v>3333.33333333333</v>
+        <v>25000</v>
       </c>
       <c r="AB47" s="41">
         <f>'7_비용인력'!AB33</f>
-        <v>40000</v>
+        <v>300000</v>
       </c>
       <c r="AC47" s="42">
         <f>'7_비용인력'!AC33</f>
-        <v>30000</v>
+        <v>100000</v>
       </c>
       <c r="AD47" s="42">
         <f>'7_비용인력'!AD33</f>
-        <v>0</v>
+        <v>100000</v>
       </c>
       <c r="AE47" s="42">
         <f>'7_비용인력'!AE33</f>
-        <v>0</v>
+        <v>100000</v>
       </c>
       <c r="AF47" s="40">
         <f>'7_비용인력'!AF33</f>
-        <v>365000</v>
+        <v>895000</v>
       </c>
     </row>
     <row r="48">
@@ -9550,71 +9550,71 @@
       </c>
       <c r="P50" s="26">
         <f>P42+P46-P48</f>
-        <v>-61943.7656112995</v>
+        <v>-40277.0989446328</v>
       </c>
       <c r="Q50" s="26">
         <f>Q42+Q46-Q48</f>
-        <v>-40101.7930390163</v>
+        <v>-18435.1263723496</v>
       </c>
       <c r="R50" s="26">
         <f>R42+R46-R48</f>
-        <v>-18259.8204667332</v>
+        <v>3406.8461999335</v>
       </c>
       <c r="S50" s="26">
         <f>S42+S46-S48</f>
-        <v>3164.1860038551</v>
+        <v>24830.8526705218</v>
       </c>
       <c r="T50" s="26">
         <f>T42+T46-T48</f>
-        <v>24588.1924744433</v>
+        <v>46254.85914111</v>
       </c>
       <c r="U50" s="26">
         <f>U42+U46-U48</f>
-        <v>64462.1989450316</v>
+        <v>86128.8656116983</v>
       </c>
       <c r="V50" s="26">
         <f>V42+V46-V48</f>
-        <v>84132.6054156198</v>
+        <v>105799.272082286</v>
       </c>
       <c r="W50" s="26">
         <f>W42+W46-W48</f>
-        <v>101279.83541562</v>
+        <v>122946.502082287</v>
       </c>
       <c r="X50" s="26">
         <f>X42+X46-X48</f>
-        <v>99977.0654156198</v>
+        <v>121643.732082287</v>
       </c>
       <c r="Y50" s="26">
         <f>Y42+Y46-Y48</f>
-        <v>94683.4854156198</v>
+        <v>116350.152082286</v>
       </c>
       <c r="Z50" s="26">
         <f>Z42+Z46-Z48</f>
-        <v>89389.9054156198</v>
+        <v>111056.572082286</v>
       </c>
       <c r="AA50" s="26">
         <f>AA42+AA46-AA48</f>
-        <v>78802.7454156198</v>
+        <v>100469.412082287</v>
       </c>
       <c r="AB50" s="27">
         <f>AB42+AB46-AB48</f>
-        <v>520174.8408</v>
+        <v>780174.8408</v>
       </c>
       <c r="AC50" s="28">
         <f>AC42+AC46-AC48</f>
-        <v>3251540.94148028</v>
+        <v>3321540.94148028</v>
       </c>
       <c r="AD50" s="28">
         <f>AD42+AD46-AD48</f>
-        <v>8993660.92908651</v>
+        <v>9093660.92908651</v>
       </c>
       <c r="AE50" s="28">
         <f>AE42+AE46-AE48</f>
-        <v>24514035.249864</v>
+        <v>24614035.249864</v>
       </c>
       <c r="AF50" s="26">
         <f>AF42+AF46-AF48</f>
-        <v>37230506.7784964</v>
+        <v>37760506.7784964</v>
       </c>
     </row>
     <row r="51">
@@ -9734,19 +9734,19 @@
       </c>
       <c r="AC51" s="24">
         <f>'7_비용인력'!AC49</f>
-        <v>129960.291900081</v>
+        <v>202560.291900081</v>
       </c>
       <c r="AD51" s="24">
         <f>'7_비용인력'!AD49</f>
-        <v>1956605.40439903</v>
+        <v>1978605.40439903</v>
       </c>
       <c r="AE51" s="24">
         <f>'7_비용인력'!AE49</f>
-        <v>5470396.53046709</v>
+        <v>5494596.53046709</v>
       </c>
       <c r="AF51" s="25">
         <f>O51+AB51+AC51+AD51+AE51</f>
-        <v>7556962.2267662</v>
+        <v>7675762.2267662</v>
       </c>
     </row>
     <row r="52">
@@ -9809,71 +9809,71 @@
       </c>
       <c r="P52" s="37">
         <f>P50-P51</f>
-        <v>-61943.7656112995</v>
+        <v>-40277.0989446328</v>
       </c>
       <c r="Q52" s="37">
         <f>Q50-Q51</f>
-        <v>-40101.7930390163</v>
+        <v>-18435.1263723496</v>
       </c>
       <c r="R52" s="37">
         <f>R50-R51</f>
-        <v>-18259.8204667332</v>
+        <v>3406.8461999335</v>
       </c>
       <c r="S52" s="37">
         <f>S50-S51</f>
-        <v>3164.1860038551</v>
+        <v>24830.8526705218</v>
       </c>
       <c r="T52" s="37">
         <f>T50-T51</f>
-        <v>24588.1924744433</v>
+        <v>46254.85914111</v>
       </c>
       <c r="U52" s="37">
         <f>U50-U51</f>
-        <v>64462.1989450316</v>
+        <v>86128.8656116983</v>
       </c>
       <c r="V52" s="37">
         <f>V50-V51</f>
-        <v>84132.6054156198</v>
+        <v>105799.272082286</v>
       </c>
       <c r="W52" s="37">
         <f>W50-W51</f>
-        <v>101279.83541562</v>
+        <v>122946.502082287</v>
       </c>
       <c r="X52" s="37">
         <f>X50-X51</f>
-        <v>99977.0654156198</v>
+        <v>121643.732082287</v>
       </c>
       <c r="Y52" s="37">
         <f>Y50-Y51</f>
-        <v>94683.4854156198</v>
+        <v>116350.152082286</v>
       </c>
       <c r="Z52" s="37">
         <f>Z50-Z51</f>
-        <v>89389.9054156198</v>
+        <v>111056.572082286</v>
       </c>
       <c r="AA52" s="37">
         <f>AA50-AA51</f>
-        <v>78802.7454156198</v>
+        <v>100469.412082287</v>
       </c>
       <c r="AB52" s="38">
         <f>AB50-AB51</f>
-        <v>520174.8408</v>
+        <v>780174.8408</v>
       </c>
       <c r="AC52" s="39">
         <f>AC50-AC51</f>
-        <v>3121580.6495802</v>
+        <v>3118980.6495802</v>
       </c>
       <c r="AD52" s="39">
         <f>AD50-AD51</f>
-        <v>7037055.52468748</v>
+        <v>7115055.52468748</v>
       </c>
       <c r="AE52" s="39">
         <f>AE50-AE51</f>
-        <v>19043638.7193969</v>
+        <v>19119438.7193969</v>
       </c>
       <c r="AF52" s="37">
         <f>AF50-AF51</f>
-        <v>29673544.5517302</v>
+        <v>30084744.5517302</v>
       </c>
     </row>
     <row r="53">
@@ -9936,71 +9936,71 @@
       </c>
       <c r="P53" s="14">
         <f>IFERROR(P52/P14,0)</f>
-        <v>-0.216581938062771</v>
+        <v>-0.140825990523626</v>
       </c>
       <c r="Q53" s="14">
         <f>IFERROR(Q52/Q14,0)</f>
-        <v>-0.101026354131045</v>
+        <v>-0.0464426516672594</v>
       </c>
       <c r="R53" s="14">
         <f>IFERROR(R52/R14,0)</f>
-        <v>-0.0359529070644745</v>
+        <v>0.00670795340142141</v>
       </c>
       <c r="S53" s="14">
         <f>IFERROR(S52/S14,0)</f>
-        <v>0.00512730632385453</v>
+        <v>0.0402363792043676</v>
       </c>
       <c r="T53" s="14">
         <f>IFERROR(T52/T14,0)</f>
-        <v>0.0338509100725547</v>
+        <v>0.0636797145146736</v>
       </c>
       <c r="U53" s="14">
         <f>IFERROR(U52/U14,0)</f>
-        <v>0.0719757416749849</v>
+        <v>0.0961678174725823</v>
       </c>
       <c r="V53" s="14">
         <f>IFERROR(V52/V14,0)</f>
-        <v>0.0843230257120453</v>
+        <v>0.106038731310394</v>
       </c>
       <c r="W53" s="14">
         <f>IFERROR(W52/W14,0)</f>
-        <v>0.0929615157154855</v>
+        <v>0.112848654804624</v>
       </c>
       <c r="X53" s="14">
         <f>IFERROR(X52/X14,0)</f>
-        <v>0.0891680377393997</v>
+        <v>0.108492211168464</v>
       </c>
       <c r="Y53" s="14">
         <f>IFERROR(Y52/Y14,0)</f>
-        <v>0.0844467735249093</v>
+        <v>0.103770946953973</v>
       </c>
       <c r="Z53" s="14">
         <f>IFERROR(Z52/Z14,0)</f>
-        <v>0.0797255093104189</v>
+        <v>0.099049682739483</v>
       </c>
       <c r="AA53" s="14">
         <f>IFERROR(AA52/AA14,0)</f>
-        <v>0.0702829808814381</v>
+        <v>0.0896071543105022</v>
       </c>
       <c r="AB53" s="30">
         <f>IFERROR(AB52/AB14,0)</f>
-        <v>0.0520068746775658</v>
+        <v>0.0780015717593611</v>
       </c>
       <c r="AC53" s="31">
         <f>IFERROR(AC52/AC14,0)</f>
-        <v>0.0945933530175819</v>
+        <v>0.0945145651387941</v>
       </c>
       <c r="AD53" s="31">
         <f>IFERROR(AD52/AD14,0)</f>
-        <v>0.100529364638393</v>
+        <v>0.101643650352678</v>
       </c>
       <c r="AE53" s="31">
         <f>IFERROR(AE52/AE14,0)</f>
-        <v>0.122074607175621</v>
+        <v>0.122560504611519</v>
       </c>
       <c r="AF53" s="14">
         <f>IFERROR(AF52/AF14,0)</f>
-        <v>0.109819839079417</v>
+        <v>0.111341663266977</v>
       </c>
     </row>
     <row r="54"/>
@@ -11071,19 +11071,19 @@
       </c>
       <c r="E15" s="18">
         <f>'2_손익계산서'!AB46</f>
-        <v>40000</v>
+        <v>300000</v>
       </c>
       <c r="F15" s="18">
         <f>'2_손익계산서'!AC46</f>
-        <v>30000</v>
+        <v>100000</v>
       </c>
       <c r="G15" s="18">
         <f>'2_손익계산서'!AD46</f>
-        <v>0</v>
+        <v>100000</v>
       </c>
       <c r="H15" s="18">
         <f>'2_손익계산서'!AE46</f>
-        <v>0</v>
+        <v>100000</v>
       </c>
     </row>
     <row r="16">
@@ -11104,19 +11104,19 @@
       </c>
       <c r="E16" s="40">
         <f>'2_손익계산서'!AB47</f>
-        <v>40000</v>
+        <v>300000</v>
       </c>
       <c r="F16" s="40">
         <f>'2_손익계산서'!AC47</f>
-        <v>30000</v>
+        <v>100000</v>
       </c>
       <c r="G16" s="40">
         <f>'2_손익계산서'!AD47</f>
-        <v>0</v>
+        <v>100000</v>
       </c>
       <c r="H16" s="40">
         <f>'2_손익계산서'!AE47</f>
-        <v>0</v>
+        <v>100000</v>
       </c>
     </row>
     <row r="17">
@@ -11205,19 +11205,19 @@
       </c>
       <c r="E19" s="25">
         <f>E13+E15-E17</f>
-        <v>520174.8408</v>
+        <v>780174.8408</v>
       </c>
       <c r="F19" s="25">
         <f>F13+F15-F17</f>
-        <v>3251540.94148028</v>
+        <v>3321540.94148028</v>
       </c>
       <c r="G19" s="25">
         <f>G13+G15-G17</f>
-        <v>8993660.92908651</v>
+        <v>9093660.92908651</v>
       </c>
       <c r="H19" s="25">
         <f>H13+H15-H17</f>
-        <v>24514035.249864</v>
+        <v>24614035.249864</v>
       </c>
     </row>
     <row r="20">
@@ -11242,15 +11242,15 @@
       </c>
       <c r="F20" s="18">
         <f>'2_손익계산서'!AC51</f>
-        <v>129960.291900081</v>
+        <v>202560.291900081</v>
       </c>
       <c r="G20" s="18">
         <f>'2_손익계산서'!AD51</f>
-        <v>1956605.40439903</v>
+        <v>1978605.40439903</v>
       </c>
       <c r="H20" s="18">
         <f>'2_손익계산서'!AE51</f>
-        <v>5470396.53046709</v>
+        <v>5494596.53046709</v>
       </c>
     </row>
     <row r="21">
@@ -11273,23 +11273,23 @@
       </c>
       <c r="E21" s="37">
         <f>E19-E20</f>
-        <v>520174.8408</v>
+        <v>780174.8408</v>
       </c>
       <c r="F21" s="37">
         <f>F19-F20</f>
-        <v>3121580.6495802</v>
+        <v>3118980.6495802</v>
       </c>
       <c r="G21" s="37">
         <f>G19-G20</f>
-        <v>7037055.52468748</v>
+        <v>7115055.52468748</v>
       </c>
       <c r="H21" s="37">
         <f>H19-H20</f>
-        <v>19043638.7193969</v>
+        <v>19119438.7193969</v>
       </c>
       <c r="I21" s="14">
         <f>IFERROR((H21/C21)^(1/5)-1,"n/a")</f>
-        <v>4.16772250041508</v>
+        <v>4.17182981621665</v>
       </c>
     </row>
     <row r="22">
@@ -11312,19 +11312,19 @@
       </c>
       <c r="E22" s="14">
         <f>IFERROR(E21/E7,0)</f>
-        <v>0.0520068746775658</v>
+        <v>0.0780015717593611</v>
       </c>
       <c r="F22" s="14">
         <f>IFERROR(F21/F7,0)</f>
-        <v>0.0945933530175819</v>
+        <v>0.0945145651387941</v>
       </c>
       <c r="G22" s="14">
         <f>IFERROR(G21/G7,0)</f>
-        <v>0.100529364638393</v>
+        <v>0.101643650352678</v>
       </c>
       <c r="H22" s="14">
         <f>IFERROR(H21/H7,0)</f>
-        <v>0.122074607175621</v>
+        <v>0.122560504611519</v>
       </c>
     </row>
     <row r="23">
@@ -33758,71 +33758,71 @@
       </c>
       <c r="P33" s="18">
         <f>'8_가정'!$D$112/12</f>
-        <v>3333.33333333333</v>
+        <v>25000</v>
       </c>
       <c r="Q33" s="18">
         <f>'8_가정'!$D$112/12</f>
-        <v>3333.33333333333</v>
+        <v>25000</v>
       </c>
       <c r="R33" s="18">
         <f>'8_가정'!$D$112/12</f>
-        <v>3333.33333333333</v>
+        <v>25000</v>
       </c>
       <c r="S33" s="18">
         <f>'8_가정'!$D$112/12</f>
-        <v>3333.33333333333</v>
+        <v>25000</v>
       </c>
       <c r="T33" s="18">
         <f>'8_가정'!$D$112/12</f>
-        <v>3333.33333333333</v>
+        <v>25000</v>
       </c>
       <c r="U33" s="18">
         <f>'8_가정'!$D$112/12</f>
-        <v>3333.33333333333</v>
+        <v>25000</v>
       </c>
       <c r="V33" s="18">
         <f>'8_가정'!$D$112/12</f>
-        <v>3333.33333333333</v>
+        <v>25000</v>
       </c>
       <c r="W33" s="18">
         <f>'8_가정'!$D$112/12</f>
-        <v>3333.33333333333</v>
+        <v>25000</v>
       </c>
       <c r="X33" s="18">
         <f>'8_가정'!$D$112/12</f>
-        <v>3333.33333333333</v>
+        <v>25000</v>
       </c>
       <c r="Y33" s="18">
         <f>'8_가정'!$D$112/12</f>
-        <v>3333.33333333333</v>
+        <v>25000</v>
       </c>
       <c r="Z33" s="18">
         <f>'8_가정'!$D$112/12</f>
-        <v>3333.33333333333</v>
+        <v>25000</v>
       </c>
       <c r="AA33" s="18">
         <f>'8_가정'!$D$112/12</f>
-        <v>3333.33333333333</v>
+        <v>25000</v>
       </c>
       <c r="AB33" s="23">
         <f>SUM(P33:AA33)</f>
-        <v>40000</v>
+        <v>300000</v>
       </c>
       <c r="AC33" s="24">
         <f>'8_가정'!$E$112</f>
-        <v>30000</v>
+        <v>100000</v>
       </c>
       <c r="AD33" s="24">
         <f>'8_가정'!$F$112</f>
-        <v>0</v>
+        <v>100000</v>
       </c>
       <c r="AE33" s="24">
         <f>'8_가정'!$G$112</f>
-        <v>0</v>
+        <v>100000</v>
       </c>
       <c r="AF33" s="25">
         <f>O33+AB33+AC33+AD33+AE33</f>
-        <v>365000</v>
+        <v>895000</v>
       </c>
     </row>
     <row r="34">
@@ -34059,19 +34059,19 @@
       </c>
       <c r="AB40" s="48">
         <f>'2_손익계산서'!AB50</f>
-        <v>520174.8408</v>
+        <v>780174.8408</v>
       </c>
       <c r="AC40" s="24">
         <f>'2_손익계산서'!AC50</f>
-        <v>3251540.94148028</v>
+        <v>3321540.94148028</v>
       </c>
       <c r="AD40" s="24">
         <f>'2_손익계산서'!AD50</f>
-        <v>8993660.92908651</v>
+        <v>9093660.92908651</v>
       </c>
       <c r="AE40" s="24">
         <f>'2_손익계산서'!AE50</f>
-        <v>24514035.249864</v>
+        <v>24614035.249864</v>
       </c>
     </row>
     <row r="41">
@@ -34090,7 +34090,7 @@
       </c>
       <c r="AC41" s="45">
         <f>AB44</f>
-        <v>2560812.34193446</v>
+        <v>2300812.34193446</v>
       </c>
       <c r="AD41" s="45">
         <f>AC44</f>
@@ -34113,11 +34113,11 @@
       </c>
       <c r="AB42" s="48">
         <f>MIN(AB41,MAX(0,AB40)*'8_가정'!$C$117)</f>
-        <v>520174.8408</v>
+        <v>780174.8408</v>
       </c>
       <c r="AC42" s="24">
         <f>MIN(AC41,MAX(0,AC40)*'8_가정'!$C$117)</f>
-        <v>2560812.34193446</v>
+        <v>2300812.34193446</v>
       </c>
       <c r="AD42" s="24">
         <f>MIN(AD41,MAX(0,AD40)*'8_가정'!$C$117)</f>
@@ -34167,7 +34167,7 @@
       </c>
       <c r="AB44" s="44">
         <f>AB41-AB42+AB43</f>
-        <v>2560812.34193446</v>
+        <v>2300812.34193446</v>
       </c>
       <c r="AC44" s="45">
         <f>AC41-AC42+AC43</f>
@@ -34198,15 +34198,15 @@
       </c>
       <c r="AC45" s="45">
         <f>MAX(0,AC40)-AC42</f>
-        <v>690728.599545821</v>
+        <v>1020728.59954582</v>
       </c>
       <c r="AD45" s="45">
         <f>MAX(0,AD40)-AD42</f>
-        <v>8993660.92908651</v>
+        <v>9093660.92908651</v>
       </c>
       <c r="AE45" s="45">
         <f>MAX(0,AE40)-AE42</f>
-        <v>24514035.249864</v>
+        <v>24614035.249864</v>
       </c>
     </row>
     <row r="46">
@@ -34225,15 +34225,15 @@
       </c>
       <c r="AC46" s="24">
         <f>MIN(AC45,'8_가정'!$C$118)*'8_가정'!$C$119+MAX(0,MIN(AC45,'8_가정'!$D$118)-'8_가정'!$C$118)*'8_가정'!$D$119+MAX(0,MIN(AC45,'8_가정'!$E$118)-'8_가정'!$D$118)*'8_가정'!$E$119+MAX(0,AC45-'8_가정'!$E$118)*'8_가정'!$F$119</f>
-        <v>118145.719909164</v>
+        <v>184145.719909164</v>
       </c>
       <c r="AD46" s="24">
         <f>MIN(AD45,'8_가정'!$C$118)*'8_가정'!$C$119+MAX(0,MIN(AD45,'8_가정'!$D$118)-'8_가정'!$C$118)*'8_가정'!$D$119+MAX(0,MIN(AD45,'8_가정'!$E$118)-'8_가정'!$D$118)*'8_가정'!$E$119+MAX(0,AD45-'8_가정'!$E$118)*'8_가정'!$F$119</f>
-        <v>1778732.1858173</v>
+        <v>1798732.1858173</v>
       </c>
       <c r="AE46" s="24">
         <f>MIN(AE45,'8_가정'!$C$118)*'8_가정'!$C$119+MAX(0,MIN(AE45,'8_가정'!$D$118)-'8_가정'!$C$118)*'8_가정'!$D$119+MAX(0,MIN(AE45,'8_가정'!$E$118)-'8_가정'!$D$118)*'8_가정'!$E$119+MAX(0,AE45-'8_가정'!$E$118)*'8_가정'!$F$119</f>
-        <v>4973087.75497008</v>
+        <v>4995087.75497008</v>
       </c>
     </row>
     <row r="47">
@@ -34252,15 +34252,15 @@
       </c>
       <c r="AC47" s="24">
         <f>AC46*'8_가정'!$C$120</f>
-        <v>11814.5719909164</v>
+        <v>18414.5719909164</v>
       </c>
       <c r="AD47" s="24">
         <f>AD46*'8_가정'!$C$120</f>
-        <v>177873.21858173</v>
+        <v>179873.21858173</v>
       </c>
       <c r="AE47" s="24">
         <f>AE46*'8_가정'!$C$120</f>
-        <v>497308.775497008</v>
+        <v>499508.775497008</v>
       </c>
     </row>
     <row r="48">
@@ -34279,15 +34279,15 @@
       </c>
       <c r="AC48" s="34">
         <f>AC46+AC47</f>
-        <v>129960.291900081</v>
+        <v>202560.291900081</v>
       </c>
       <c r="AD48" s="34">
         <f>AD46+AD47</f>
-        <v>1956605.40439903</v>
+        <v>1978605.40439903</v>
       </c>
       <c r="AE48" s="34">
         <f>AE46+AE47</f>
-        <v>5470396.53046709</v>
+        <v>5494596.53046709</v>
       </c>
     </row>
     <row r="49">
@@ -34402,19 +34402,19 @@
       </c>
       <c r="AC49" s="45">
         <f>AC48</f>
-        <v>129960.291900081</v>
+        <v>202560.291900081</v>
       </c>
       <c r="AD49" s="45">
         <f>AD48</f>
-        <v>1956605.40439903</v>
+        <v>1978605.40439903</v>
       </c>
       <c r="AE49" s="45">
         <f>AE48</f>
-        <v>5470396.53046709</v>
+        <v>5494596.53046709</v>
       </c>
       <c r="AF49" s="25">
         <f>O49+AB49+AC49+AD49+AE49</f>
-        <v>7556962.2267662</v>
+        <v>7675762.2267662</v>
       </c>
     </row>
     <row r="51">
@@ -37220,7 +37220,7 @@
       </c>
       <c r="B112" s="15" t="inlineStr">
         <is>
-          <t>2027~ 입력(보수적 체감)</t>
+          <t>2027: 3억 예상, 2028~: 매년 1억(보수적)</t>
         </is>
       </c>
       <c r="C112" s="96">
@@ -37228,20 +37228,20 @@
         <v>295000</v>
       </c>
       <c r="D112" s="65" t="n">
-        <v>40000</v>
+        <v>300000</v>
       </c>
       <c r="E112" s="65" t="n">
-        <v>30000</v>
+        <v>100000</v>
       </c>
       <c r="F112" s="65" t="n">
-        <v>0</v>
+        <v>100000</v>
       </c>
       <c r="G112" s="65" t="n">
-        <v>0</v>
+        <v>100000</v>
       </c>
       <c r="I112" s="89" t="inlineStr">
         <is>
-          <t>2024 0.88억, 2025 0.31억 실적(영업외수익 처리 선례). 2029~ 미반영</t>
+          <t>2024 0.88억, 2025 0.31억 실적(영업외수익 처리 선례). 2027 3억(사용자 제공), 2028~ 연 1억 보수적 가정(과제 수행 비용 대응 한도 내 확인 필요)</t>
         </is>
       </c>
     </row>
@@ -37673,16 +37673,16 @@
         <v>-0.489051827344633</v>
       </c>
       <c r="D10" s="98" t="n">
-        <v>5.201748408</v>
+        <v>7.801748408</v>
       </c>
       <c r="E10" s="98" t="n">
-        <v>31.215806495802</v>
+        <v>31.189806495802</v>
       </c>
       <c r="F10" s="98" t="n">
-        <v>70.3705552468748</v>
+        <v>71.1505552468748</v>
       </c>
       <c r="G10" s="98" t="n">
-        <v>190.436387193969</v>
+        <v>191.194387193969</v>
       </c>
     </row>
     <row r="11">
@@ -37868,16 +37868,16 @@
         <v>-0.7085080836531791</v>
       </c>
       <c r="D21" s="98" t="n">
-        <v>-2.85410320759547</v>
+        <v>-0.254103207595469</v>
       </c>
       <c r="E21" s="98" t="n">
-        <v>9.378050222007131</v>
+        <v>10.0780502220071</v>
       </c>
       <c r="F21" s="98" t="n">
-        <v>17.8398139060112</v>
+        <v>18.8398139060112</v>
       </c>
       <c r="G21" s="98" t="n">
-        <v>38.4212438145785</v>
+        <v>38.2552438145785</v>
       </c>
     </row>
     <row r="22">
@@ -38063,16 +38063,16 @@
         <v>-1.10018038900559</v>
       </c>
       <c r="D32" s="98" t="n">
-        <v>-6.61343250407795</v>
+        <v>-4.01343250407795</v>
       </c>
       <c r="E32" s="98" t="n">
-        <v>-2.91351714627082</v>
+        <v>-2.21351714627082</v>
       </c>
       <c r="F32" s="98" t="n">
-        <v>-13.572215931278</v>
+        <v>-12.572215931278</v>
       </c>
       <c r="G32" s="98" t="n">
-        <v>-24.2095182039728</v>
+        <v>-23.2095182039728</v>
       </c>
     </row>
     <row r="33">
@@ -38291,19 +38291,19 @@
       </c>
       <c r="D43" s="17">
         <f>'3_연간손익'!E21/100000</f>
-        <v>5.201748408</v>
+        <v>7.801748408</v>
       </c>
       <c r="E43" s="17">
         <f>'3_연간손익'!F21/100000</f>
-        <v>31.215806495802</v>
+        <v>31.189806495802</v>
       </c>
       <c r="F43" s="17">
         <f>'3_연간손익'!G21/100000</f>
-        <v>70.3705552468748</v>
+        <v>71.1505552468748</v>
       </c>
       <c r="G43" s="17">
         <f>'3_연간손익'!H21/100000</f>
-        <v>190.436387193969</v>
+        <v>191.194387193969</v>
       </c>
     </row>
     <row r="44">

--- a/모닛_5개년_사업계획_손익계산서_2026-2030.xlsx
+++ b/모닛_5개년_사업계획_손익계산서_2026-2030.xlsx
@@ -596,10 +596,10 @@
     <xf numFmtId="165" fontId="6" fillId="6" borderId="0" applyAlignment="1" pivotButton="0" quotePrefix="0" xfId="0">
       <alignment vertical="center"/>
     </xf>
-    <xf numFmtId="166" fontId="6" fillId="5" borderId="0" applyAlignment="1" pivotButton="0" quotePrefix="0" xfId="0">
+    <xf numFmtId="169" fontId="6" fillId="5" borderId="0" applyAlignment="1" pivotButton="0" quotePrefix="0" xfId="0">
       <alignment vertical="center"/>
     </xf>
-    <xf numFmtId="166" fontId="6" fillId="6" borderId="0" applyAlignment="1" pivotButton="0" quotePrefix="0" xfId="0">
+    <xf numFmtId="169" fontId="6" fillId="6" borderId="0" applyAlignment="1" pivotButton="0" quotePrefix="0" xfId="0">
       <alignment vertical="center"/>
     </xf>
     <xf numFmtId="164" fontId="15" fillId="0" borderId="0" applyAlignment="1" pivotButton="0" quotePrefix="0" xfId="0">
@@ -1100,7 +1100,7 @@
     </comment>
     <comment ref="C85" authorId="0" shapeId="0">
       <text>
-        <t>2026년 09월분 급상여대장: 대표 제외 6명 지급합계 26,000,001원 ÷ 6 = 4,333,334원(약 4,339천원 가정치로 사용). 공제 전 총액 기준, 연 상여 미포함.</t>
+        <t>2026년 09월분 급상여대장: 대표 제외 6명 지급합계 26,000,001원 ÷ 6 ≈ 4,333,334원. 직원·신규 채용 1인당 월 급여는 4,339천원(회사 지정값)으로 적용. 공제 전 총액 기준, 연 상여 미포함.</t>
       </text>
     </comment>
   </commentList>
@@ -1446,7 +1446,7 @@
     <outlinePr summaryBelow="1" summaryRight="1"/>
     <pageSetUpPr fitToPage="1"/>
   </sheetPr>
-  <dimension ref="A1:I60"/>
+  <dimension ref="A1:I62"/>
   <sheetFormatPr baseColWidth="8" defaultRowHeight="15"/>
   <cols>
     <col width="34" customWidth="1" min="1" max="1"/>
@@ -1529,7 +1529,7 @@
       </c>
       <c r="I6" s="10" t="inlineStr">
         <is>
-          <t>★제출전_확인사항</t>
+          <t>6_거래처현황</t>
         </is>
       </c>
     </row>
@@ -1587,11 +1587,11 @@
       </c>
       <c r="D8" s="13">
         <f>'3_연간손익'!D7/100000</f>
-        <v>11.93317</v>
+        <v>12.01217</v>
       </c>
       <c r="E8" s="13">
         <f>'3_연간손익'!E7/100000</f>
-        <v>111.848</v>
+        <v>112.048</v>
       </c>
       <c r="F8" s="13">
         <f>'3_연간손익'!F7/100000</f>
@@ -1622,15 +1622,15 @@
       </c>
       <c r="D9" s="16">
         <f>'3_연간손익'!D8</f>
-        <v>0.397059897077665</v>
+        <v>0.40630871628238</v>
       </c>
       <c r="E9" s="16">
         <f>'3_연간손익'!E8</f>
-        <v>8.37286571799447</v>
+        <v>8.32787331514622</v>
       </c>
       <c r="F9" s="16">
         <f>'3_연간손익'!F8</f>
-        <v>1.95043273013375</v>
+        <v>1.94516635727545</v>
       </c>
       <c r="G9" s="16">
         <f>'3_연간손익'!G8</f>
@@ -1653,27 +1653,27 @@
       </c>
       <c r="D10" s="17">
         <f>'3_연간손익'!D10/100000</f>
-        <v>5.957275671</v>
+        <v>5.996159471</v>
       </c>
       <c r="E10" s="17">
         <f>'3_연간손익'!E10/100000</f>
-        <v>44.4544508</v>
+        <v>44.5318508</v>
       </c>
       <c r="F10" s="17">
         <f>'3_연간손익'!F10/100000</f>
-        <v>130.77002322</v>
+        <v>130.76001322</v>
       </c>
       <c r="G10" s="17">
         <f>'3_연간손익'!G10/100000</f>
-        <v>279.4089323776</v>
+        <v>279.3838943776</v>
       </c>
       <c r="H10" s="17">
         <f>'3_연간손익'!H10/100000</f>
-        <v>637.788779409696</v>
+        <v>637.740917985696</v>
       </c>
       <c r="I10" s="14">
         <f>IFERROR(('3_연간손익'!H10/'3_연간손익'!C10)^(1/5)-1,"n/a")</f>
-        <v>1.68925690761821</v>
+        <v>1.68921654455979</v>
       </c>
     </row>
     <row r="11">
@@ -1688,23 +1688,23 @@
       </c>
       <c r="D11" s="16">
         <f>'3_연간손익'!D11</f>
-        <v>0.499219877953637</v>
+        <v>0.499173710578522</v>
       </c>
       <c r="E11" s="16">
         <f>'3_연간손익'!E11</f>
-        <v>0.397454141334669</v>
+        <v>0.397435481222333</v>
       </c>
       <c r="F11" s="16">
         <f>'3_연간손익'!F11</f>
-        <v>0.396272797636364</v>
+        <v>0.39624246430303</v>
       </c>
       <c r="G11" s="16">
         <f>'3_연간손익'!G11</f>
-        <v>0.399155617682286</v>
+        <v>0.399119849110857</v>
       </c>
       <c r="H11" s="16">
         <f>'3_연간손익'!H11</f>
-        <v>0.408838961160062</v>
+        <v>0.408808280760062</v>
       </c>
     </row>
     <row r="12">
@@ -1719,27 +1719,27 @@
       </c>
       <c r="D12" s="13">
         <f>'3_연간손익'!D13/100000</f>
-        <v>0.189224991</v>
+        <v>0.219576791000001</v>
       </c>
       <c r="E12" s="13">
         <f>'3_연간손익'!E13/100000</f>
-        <v>11.6546401344</v>
+        <v>11.7020401344</v>
       </c>
       <c r="F12" s="13">
         <f>'3_연간손익'!F13/100000</f>
-        <v>37.334036193904</v>
+        <v>37.324026193904</v>
       </c>
       <c r="G12" s="13">
         <f>'3_연간손익'!G13/100000</f>
-        <v>96.3220719432602</v>
+        <v>96.2970339432603</v>
       </c>
       <c r="H12" s="13">
         <f>'3_연간손익'!H13/100000</f>
-        <v>255.56282577049</v>
+        <v>255.51496434649</v>
       </c>
       <c r="I12" s="14">
         <f>IFERROR(('3_연간손익'!H13/'3_연간손익'!C13)^(1/5)-1,"n/a")</f>
-        <v>2.94353972434384</v>
+        <v>2.94339200523261</v>
       </c>
     </row>
     <row r="13">
@@ -1754,23 +1754,23 @@
       </c>
       <c r="D13" s="16">
         <f>'3_연간손익'!D14</f>
-        <v>0.0158570598591992</v>
+        <v>0.0182795274292655</v>
       </c>
       <c r="E13" s="16">
         <f>'3_연간손익'!E14</f>
-        <v>0.104200702152922</v>
+        <v>0.104437742167642</v>
       </c>
       <c r="F13" s="16">
         <f>'3_연간손익'!F14</f>
-        <v>0.11313344301183</v>
+        <v>0.113103109678497</v>
       </c>
       <c r="G13" s="16">
         <f>'3_연간손익'!G14</f>
-        <v>0.137602959918943</v>
+        <v>0.137567191347515</v>
       </c>
       <c r="H13" s="16">
         <f>'3_연간손익'!H14</f>
-        <v>0.163822324211852</v>
+        <v>0.163791643811852</v>
       </c>
     </row>
     <row r="14">
@@ -1785,27 +1785,27 @@
       </c>
       <c r="D14" s="17">
         <f>'3_연간손익'!D21/100000</f>
-        <v>0.380995621</v>
+        <v>0.414112421000001</v>
       </c>
       <c r="E14" s="17">
         <f>'3_연간손익'!E21/100000</f>
-        <v>13.8866401344</v>
+        <v>13.9340401344</v>
       </c>
       <c r="F14" s="17">
         <f>'3_연간손익'!F21/100000</f>
-        <v>32.1546487650571</v>
+        <v>32.1291272690571</v>
       </c>
       <c r="G14" s="17">
         <f>'3_연간손익'!G21/100000</f>
-        <v>73.136016115743</v>
+        <v>73.116486475743</v>
       </c>
       <c r="H14" s="17">
         <f>'3_연간손익'!H21/100000</f>
-        <v>195.092381934031</v>
+        <v>195.056102974639</v>
       </c>
       <c r="I14" s="14">
         <f>IFERROR(('3_연간손익'!H21/'3_연간손익'!C21)^(1/5)-1,"n/a")</f>
-        <v>4.19274815470237</v>
+        <v>4.19255501388161</v>
       </c>
     </row>
     <row r="15">
@@ -1816,23 +1816,23 @@
       </c>
       <c r="D15" s="17">
         <f>'3_연간손익'!D23/100000</f>
-        <v>0.369224991</v>
+        <v>0.399576791000001</v>
       </c>
       <c r="E15" s="17">
         <f>'3_연간손익'!E23/100000</f>
-        <v>16.0141701344</v>
+        <v>16.0615701344</v>
       </c>
       <c r="F15" s="17">
         <f>'3_연간손익'!F23/100000</f>
-        <v>42.614720227184</v>
+        <v>42.604710227184</v>
       </c>
       <c r="G15" s="17">
         <f>'3_연간손익'!G23/100000</f>
-        <v>103.220873820825</v>
+        <v>103.195835820825</v>
       </c>
       <c r="H15" s="17">
         <f>'3_연간손익'!H23/100000</f>
-        <v>264.366765106547</v>
+        <v>264.318903682547</v>
       </c>
     </row>
     <row r="16">
@@ -1841,23 +1841,23 @@
           <t>인원(기말, 명)</t>
         </is>
       </c>
-      <c r="D16" s="18">
+      <c r="D16" s="17">
         <f>'3_연간손익'!D24</f>
         <v>7</v>
       </c>
-      <c r="E16" s="18">
+      <c r="E16" s="17">
         <f>'3_연간손익'!E24</f>
         <v>22</v>
       </c>
-      <c r="F16" s="18">
+      <c r="F16" s="17">
         <f>'3_연간손익'!F24</f>
         <v>85</v>
       </c>
-      <c r="G16" s="18">
+      <c r="G16" s="17">
         <f>'3_연간손익'!G24</f>
         <v>130</v>
       </c>
-      <c r="H16" s="18">
+      <c r="H16" s="17">
         <f>'3_연간손익'!H24</f>
         <v>260</v>
       </c>
@@ -1865,16 +1865,16 @@
     <row r="17">
       <c r="A17" s="15" t="inlineStr">
         <is>
-          <t>인당 매출(백만원)</t>
+          <t>인당 매출(백만원, 평균 인원 기준)</t>
         </is>
       </c>
       <c r="D17" s="17">
         <f>'3_연간손익'!D25</f>
-        <v>170.473857142857</v>
+        <v>171.602428571429</v>
       </c>
       <c r="E17" s="17">
         <f>'3_연간손익'!E25</f>
-        <v>798.914285714286</v>
+        <v>800.342857142857</v>
       </c>
       <c r="F17" s="17">
         <f>'3_연간손익'!F25</f>
@@ -1897,23 +1897,23 @@
       </c>
       <c r="D18" s="18">
         <f>'3_연간손익'!D26</f>
-        <v>928.102875</v>
+        <v>934.686208333333</v>
       </c>
       <c r="E18" s="18">
         <f>'3_연간손익'!E26</f>
-        <v>8795.97166666667</v>
+        <v>8812.63833333333</v>
       </c>
       <c r="F18" s="18">
         <f>'3_연간손익'!F26</f>
-        <v>25104.4494666667</v>
+        <v>25109.6494666667</v>
       </c>
       <c r="G18" s="18">
         <f>'3_연간손익'!G26</f>
-        <v>50397.0821066667</v>
+        <v>50410.3421066667</v>
       </c>
       <c r="H18" s="18">
         <f>'3_연간손익'!H26</f>
-        <v>105961.8822208</v>
+        <v>105986.1246208</v>
       </c>
     </row>
     <row r="19">
@@ -1951,11 +1951,11 @@
       </c>
       <c r="D20" s="16">
         <f>'3_연간손익'!D28</f>
-        <v>0.994430833333333</v>
+        <v>1.00101416666667</v>
       </c>
       <c r="E20" s="16">
         <f>'3_연간손익'!E28</f>
-        <v>1.11792103948026</v>
+        <v>1.11992003998001</v>
       </c>
       <c r="F20" s="16">
         <f>'3_연간손익'!F28</f>
@@ -2009,7 +2009,7 @@
       </c>
       <c r="D24" s="17">
         <f>'3_연간손익'!D46/100000</f>
-        <v>6.49167</v>
+        <v>6.57067</v>
       </c>
       <c r="E24" s="17">
         <f>'3_연간손익'!E46/100000</f>
@@ -2067,19 +2067,19 @@
       </c>
       <c r="E26" s="17">
         <f>'3_연간손익'!E48/100000</f>
-        <v>18.1</v>
+        <v>18.3</v>
       </c>
       <c r="F26" s="17">
         <f>'3_연간손익'!F48/100000</f>
-        <v>55.62</v>
+        <v>56.14</v>
       </c>
       <c r="G26" s="17">
         <f>'3_연간손익'!G48/100000</f>
-        <v>118.848</v>
+        <v>119.784</v>
       </c>
       <c r="H26" s="17">
         <f>'3_연간손익'!H48/100000</f>
-        <v>253.40672</v>
+        <v>254.792</v>
       </c>
     </row>
     <row r="27">
@@ -2179,15 +2179,15 @@
       </c>
       <c r="F30" s="17">
         <f>'3_연간손익'!F52/100000</f>
-        <v>46.41744</v>
+        <v>45.89744</v>
       </c>
       <c r="G30" s="17">
         <f>'3_연간손익'!G52/100000</f>
-        <v>101.478496</v>
+        <v>100.542496</v>
       </c>
       <c r="H30" s="17">
         <f>'3_연간손익'!H52/100000</f>
-        <v>231.10951488</v>
+        <v>229.72423488</v>
       </c>
     </row>
     <row r="31">
@@ -2198,11 +2198,11 @@
       </c>
       <c r="D31" s="19">
         <f>SUM(D24:D30)</f>
-        <v>11.93317</v>
+        <v>12.01217</v>
       </c>
       <c r="E31" s="19">
         <f>SUM(E24:E30)</f>
-        <v>111.848</v>
+        <v>112.048</v>
       </c>
       <c r="F31" s="19">
         <f>SUM(F24:F30)</f>
@@ -2256,23 +2256,23 @@
       </c>
       <c r="D35" s="16">
         <f>'3_연간손익'!D71</f>
-        <v>0.716796123745828</v>
+        <v>0.71865866034197</v>
       </c>
       <c r="E35" s="16">
         <f>'3_연간손익'!E71</f>
-        <v>0.509334096273514</v>
+        <v>0.510209910038555</v>
       </c>
       <c r="F35" s="16">
         <f>'3_연간손익'!F71</f>
-        <v>0.302458666666667</v>
+        <v>0.304034424242424</v>
       </c>
       <c r="G35" s="16">
         <f>'3_연간손익'!G71</f>
-        <v>0.204697805714286</v>
+        <v>0.206034948571429</v>
       </c>
       <c r="H35" s="16">
         <f>'3_연간손익'!H71</f>
-        <v>0.118977069948718</v>
+        <v>0.119865069948718</v>
       </c>
     </row>
     <row r="36">
@@ -2283,11 +2283,11 @@
       </c>
       <c r="D36" s="16">
         <f>'3_연간손익'!D72</f>
-        <v>0.283203876254172</v>
+        <v>0.28134133965803</v>
       </c>
       <c r="E36" s="16">
         <f>'3_연간손익'!E72</f>
-        <v>0.40125885129819</v>
+        <v>0.400542624589462</v>
       </c>
       <c r="F36" s="16">
         <f>'3_연간손익'!F72</f>
@@ -2314,19 +2314,19 @@
       </c>
       <c r="E37" s="16">
         <f>'3_연간손익'!E73</f>
-        <v>0.0894070524282955</v>
+        <v>0.0892474653719834</v>
       </c>
       <c r="F37" s="16">
         <f>'3_연간손익'!F73</f>
-        <v>0.358840727272727</v>
+        <v>0.35726496969697</v>
       </c>
       <c r="G37" s="16">
         <f>'3_연간손익'!G73</f>
-        <v>0.513540708571429</v>
+        <v>0.512203565714286</v>
       </c>
       <c r="H37" s="16">
         <f>'3_연간손익'!H73</f>
-        <v>0.699429176205128</v>
+        <v>0.698541176205128</v>
       </c>
     </row>
     <row r="38"/>
@@ -2368,23 +2368,23 @@
       </c>
       <c r="D41" s="17">
         <f>'3_연간손익'!D32/100000</f>
-        <v>7.3270742</v>
+        <v>7.3902742</v>
       </c>
       <c r="E41" s="17">
         <f>'3_연간손익'!E32/100000</f>
-        <v>78.85234</v>
+        <v>79.02234</v>
       </c>
       <c r="F41" s="17">
         <f>'3_연간손익'!F32/100000</f>
-        <v>222.7730648</v>
+        <v>222.8718648</v>
       </c>
       <c r="G41" s="17">
         <f>'3_연간손익'!G32/100000</f>
-        <v>438.5104544</v>
+        <v>438.7444544</v>
       </c>
       <c r="H41" s="17">
         <f>'3_연간손익'!H32/100000</f>
-        <v>906.9992596032</v>
+        <v>907.4009908032</v>
       </c>
     </row>
     <row r="42">
@@ -2395,23 +2395,23 @@
       </c>
       <c r="D42" s="17">
         <f>'3_연간손익'!D33/100000</f>
-        <v>2.4633851</v>
+        <v>2.4697051</v>
       </c>
       <c r="E42" s="17">
         <f>'3_연간손익'!E33/100000</f>
-        <v>14.85374</v>
+        <v>14.86374</v>
       </c>
       <c r="F42" s="17">
         <f>'3_연간손익'!F33/100000</f>
-        <v>40.6392488</v>
+        <v>40.6132488</v>
       </c>
       <c r="G42" s="17">
         <f>'3_연간손익'!G33/100000</f>
-        <v>85.15908288</v>
+        <v>85.10292288</v>
       </c>
       <c r="H42" s="17">
         <f>'3_연간손익'!H33/100000</f>
-        <v>181.3524710464</v>
+        <v>181.2693542464</v>
       </c>
     </row>
     <row r="43">
@@ -2422,23 +2422,23 @@
       </c>
       <c r="D43" s="17">
         <f>'3_연간손익'!D34/100000</f>
-        <v>1.3467752</v>
+        <v>1.3562552</v>
       </c>
       <c r="E43" s="17">
         <f>'3_연간손익'!E34/100000</f>
-        <v>11.84558</v>
+        <v>11.86558</v>
       </c>
       <c r="F43" s="17">
         <f>'3_연간손익'!F34/100000</f>
-        <v>37.84108</v>
+        <v>37.83068</v>
       </c>
       <c r="G43" s="17">
         <f>'3_연간손익'!G34/100000</f>
-        <v>81.095448</v>
+        <v>81.076728</v>
       </c>
       <c r="H43" s="17">
         <f>'3_연간손익'!H34/100000</f>
-        <v>183.190856</v>
+        <v>183.1631504</v>
       </c>
     </row>
     <row r="44">
@@ -2457,21 +2457,21 @@
       </c>
       <c r="F44" s="17">
         <f>'3_연간손익'!F35/100000</f>
-        <v>17.2254232</v>
+        <v>17.1838232</v>
       </c>
       <c r="G44" s="17">
         <f>'3_연간손익'!G35/100000</f>
-        <v>57.91768384</v>
+        <v>57.81472384</v>
       </c>
       <c r="H44" s="17">
         <f>'3_연간손익'!H35/100000</f>
-        <v>175.0686935552</v>
+        <v>174.8886071552</v>
       </c>
     </row>
     <row r="45">
       <c r="A45" s="15" t="inlineStr">
         <is>
-          <t>스마트 욕창 케어(2027 Q4 출시)</t>
+          <t>스마트 욕창 케어(2027 출시)</t>
         </is>
       </c>
       <c r="D45" s="17">
@@ -2484,15 +2484,15 @@
       </c>
       <c r="F45" s="17">
         <f>'3_연간손익'!F36/100000</f>
-        <v>4.0128344</v>
+        <v>4.0024344</v>
       </c>
       <c r="G45" s="17">
         <f>'3_연간손익'!G36/100000</f>
-        <v>22.45576096</v>
+        <v>22.41832096</v>
       </c>
       <c r="H45" s="17">
         <f>'3_연간손익'!H36/100000</f>
-        <v>81.7306894976</v>
+        <v>81.6475726976</v>
       </c>
     </row>
     <row r="46">
@@ -2511,15 +2511,15 @@
       </c>
       <c r="F46" s="17">
         <f>'3_연간손익'!F37/100000</f>
-        <v>7.5083488</v>
+        <v>7.4979488</v>
       </c>
       <c r="G46" s="17">
         <f>'3_연간손익'!G37/100000</f>
-        <v>14.86156992</v>
+        <v>14.84284992</v>
       </c>
       <c r="H46" s="17">
         <f>'3_연간손익'!H37/100000</f>
-        <v>31.6580302976</v>
+        <v>31.6303246976</v>
       </c>
     </row>
     <row r="47"/>
@@ -2565,19 +2565,19 @@
       </c>
       <c r="E50" s="17">
         <f>'3_연간손익'!E41/100000</f>
-        <v>24.51</v>
+        <v>24.71</v>
       </c>
       <c r="F50" s="17">
         <f>'3_연간손익'!F41/100000</f>
-        <v>41.754</v>
+        <v>42.274</v>
       </c>
       <c r="G50" s="17">
         <f>'3_연간손익'!G41/100000</f>
-        <v>58.0008</v>
+        <v>58.9368</v>
       </c>
       <c r="H50" s="17">
         <f>'3_연간손익'!H41/100000</f>
-        <v>73.409856</v>
+        <v>74.795136</v>
       </c>
     </row>
     <row r="51">
@@ -2588,7 +2588,7 @@
       </c>
       <c r="D51" s="17">
         <f>'3_연간손익'!D42/100000</f>
-        <v>9.58774</v>
+        <v>9.66674</v>
       </c>
       <c r="E51" s="17">
         <f>'3_연간손익'!E42/100000</f>
@@ -2596,15 +2596,15 @@
       </c>
       <c r="F51" s="17">
         <f>'3_연간손익'!F42/100000</f>
-        <v>288.246</v>
+        <v>287.726</v>
       </c>
       <c r="G51" s="17">
         <f>'3_연간손익'!G42/100000</f>
-        <v>641.9992</v>
+        <v>641.0632</v>
       </c>
       <c r="H51" s="17">
         <f>'3_연간손익'!H42/100000</f>
-        <v>1486.590144</v>
+        <v>1485.204864</v>
       </c>
     </row>
     <row r="52">
@@ -2615,11 +2615,11 @@
       </c>
       <c r="D52" s="19">
         <f>SUM(D50:D51)</f>
-        <v>11.93317</v>
+        <v>12.01217</v>
       </c>
       <c r="E52" s="19">
         <f>SUM(E50:E51)</f>
-        <v>111.848</v>
+        <v>112.048</v>
       </c>
       <c r="F52" s="19">
         <f>SUM(F50:F51)</f>
@@ -2674,7 +2674,15 @@
     <row r="60">
       <c r="A60" s="20" t="inlineStr">
         <is>
-          <t>• 파란색 = 입력값, 검정 = 수식(산출 시트), 초록 = 계산 시트 간 연동, 노란 배경 = 핵심 가정. 제출 전 "★제출전_확인사항" 시트의 항목을 반영하고 해당 시트는 삭제하세요.</t>
+          <t>• 파란색 = 입력값, 검정 = 수식(산출 시트), 초록 = 계산 시트 간 연동, 노란 배경 = 핵심 가정.</t>
+        </is>
+      </c>
+    </row>
+    <row r="61"/>
+    <row r="62">
+      <c r="A62" s="2" t="inlineStr">
+        <is>
+          <t>※ 억원 단위 소수 첫째 자리 반올림으로 항목 합계가 합계와 0.1억 차이날 수 있습니다.</t>
         </is>
       </c>
     </row>
@@ -2706,7 +2714,7 @@
     <outlinePr summaryBelow="1" summaryRight="1"/>
     <pageSetUpPr fitToPage="1"/>
   </sheetPr>
-  <dimension ref="A1:I101"/>
+  <dimension ref="A1:I103"/>
   <sheetFormatPr baseColWidth="8" defaultRowHeight="15"/>
   <cols>
     <col width="40" customWidth="1" min="1" max="1"/>
@@ -2795,16 +2803,16 @@
     <row r="7" ht="36" customHeight="1">
       <c r="A7" s="12" t="inlineStr">
         <is>
-          <t>S1 기준안(4_매출_거래처 A합계)</t>
+          <t>S1 경영계획(4_매출_거래처 A합계)</t>
         </is>
       </c>
       <c r="C7" s="18">
         <f>'4_매출_거래처'!AV46</f>
-        <v>1193317</v>
+        <v>1201217</v>
       </c>
       <c r="D7" s="18">
         <f>'4_매출_거래처'!AW46</f>
-        <v>11184800</v>
+        <v>11204800</v>
       </c>
       <c r="E7" s="18">
         <f>'4_매출_거래처'!AX46</f>
@@ -2820,7 +2828,7 @@
       </c>
       <c r="I7" s="116" t="inlineStr">
         <is>
-          <t>2026·2027은 거래처 매출표(사용자 입력) 합계이므로 IR 차트와 차이가 있습니다(2026 −0.6%, 2027 +11.8%). 2028~30은 삼성 글로벌 채널 잔차로 IR과 정확히 일치합니다.</t>
+          <t>2026·2027은 거래처 매출표 합계이므로 IR 차트와 차이가 있습니다(2026 +0.1%, 2027 +12.0%). 2028~30은 삼성 글로벌 채널 잔차로 IR과 정확히 일치합니다.</t>
         </is>
       </c>
     </row>
@@ -2832,11 +2840,11 @@
       </c>
       <c r="C8" s="44">
         <f>C7-C6</f>
-        <v>-6683</v>
+        <v>1217</v>
       </c>
       <c r="D8" s="44">
         <f>D7-D6</f>
-        <v>1179800</v>
+        <v>1199800</v>
       </c>
       <c r="E8" s="44">
         <f>E7-E6</f>
@@ -2859,11 +2867,11 @@
       </c>
       <c r="C9" s="70">
         <f>IFERROR(C8/C6,0)</f>
-        <v>-0.00556916666666667</v>
+        <v>0.00101416666666667</v>
       </c>
       <c r="D9" s="70">
         <f>IFERROR(D8/D6,0)</f>
-        <v>0.11792103948026</v>
+        <v>0.11992003998001</v>
       </c>
       <c r="E9" s="70">
         <f>IFERROR(E8/E6,0)</f>
@@ -2886,11 +2894,11 @@
       </c>
       <c r="C10" s="18">
         <f>'4_매출_거래처'!AV90</f>
-        <v>1193317</v>
+        <v>1201217</v>
       </c>
       <c r="D10" s="18">
         <f>'4_매출_거래처'!AW90</f>
-        <v>11184800</v>
+        <v>11204800</v>
       </c>
       <c r="E10" s="18">
         <f>'4_매출_거래처'!AX90</f>
@@ -2913,11 +2921,11 @@
       </c>
       <c r="C11" s="58">
         <f>IFERROR(C10/C6,0)</f>
-        <v>0.994430833333333</v>
+        <v>1.00101416666667</v>
       </c>
       <c r="D11" s="58">
         <f>IFERROR(D10/D6,0)</f>
-        <v>1.11792103948026</v>
+        <v>1.11992003998001</v>
       </c>
       <c r="E11" s="58">
         <f>IFERROR(E10/E6,0)</f>
@@ -2953,7 +2961,7 @@
       </c>
       <c r="C14" s="11" t="inlineStr">
         <is>
-          <t>IR 단계</t>
+          <t>단계(IR p.25 표기, 미표기 항목은 모델 단계)</t>
         </is>
       </c>
       <c r="D14" s="11" t="inlineStr">
@@ -3192,15 +3200,15 @@
       </c>
       <c r="E22" s="18">
         <f>'4_매출_거래처'!AW17</f>
-        <v>100000</v>
+        <v>120000</v>
       </c>
       <c r="F22" s="44">
         <f>E22-D22</f>
-        <v>10000</v>
+        <v>30000</v>
       </c>
       <c r="G22" s="18">
         <f>'4_매출_거래처'!AW61</f>
-        <v>100000</v>
+        <v>120000</v>
       </c>
     </row>
     <row r="23">
@@ -3216,7 +3224,7 @@
       </c>
       <c r="C23" s="15" t="inlineStr">
         <is>
-          <t>진행중</t>
+          <t>진행 중</t>
         </is>
       </c>
       <c r="E23" s="18">
@@ -3241,7 +3249,7 @@
       </c>
       <c r="C24" s="15" t="inlineStr">
         <is>
-          <t>진행중</t>
+          <t>진행 중</t>
         </is>
       </c>
       <c r="E24" s="18">
@@ -3291,7 +3299,7 @@
       </c>
       <c r="C26" s="15" t="inlineStr">
         <is>
-          <t>진행중</t>
+          <t>진행 중</t>
         </is>
       </c>
       <c r="D26" s="56" t="n">
@@ -3398,7 +3406,7 @@
       </c>
       <c r="C30" s="15" t="inlineStr">
         <is>
-          <t>등록완료</t>
+          <t>등록 완료</t>
         </is>
       </c>
       <c r="D30" s="56" t="n">
@@ -3519,7 +3527,7 @@
       </c>
       <c r="C34" s="15" t="inlineStr">
         <is>
-          <t>등록완료</t>
+          <t>등록 완료</t>
         </is>
       </c>
       <c r="D34" s="56" t="n">
@@ -3576,7 +3584,7 @@
       </c>
       <c r="C36" s="15" t="inlineStr">
         <is>
-          <t>진행중</t>
+          <t>진행 중</t>
         </is>
       </c>
       <c r="E36" s="18">
@@ -3601,7 +3609,7 @@
       </c>
       <c r="C37" s="15" t="inlineStr">
         <is>
-          <t>진행중</t>
+          <t>진행 중</t>
         </is>
       </c>
       <c r="E37" s="18">
@@ -3690,7 +3698,7 @@
       </c>
       <c r="C40" s="15" t="inlineStr">
         <is>
-          <t>진행중</t>
+          <t>진행 중</t>
         </is>
       </c>
       <c r="E40" s="18">
@@ -3747,7 +3755,7 @@
       </c>
       <c r="C42" s="15" t="inlineStr">
         <is>
-          <t>접촉</t>
+          <t>PoC / R&amp;D</t>
         </is>
       </c>
       <c r="D42" s="56" t="n">
@@ -3779,7 +3787,7 @@
       </c>
       <c r="C43" s="15" t="inlineStr">
         <is>
-          <t>입찰</t>
+          <t>계약</t>
         </is>
       </c>
       <c r="D43" s="56" t="n">
@@ -4029,11 +4037,11 @@
       </c>
       <c r="E52" s="26">
         <f>SUM(E15:E51)</f>
-        <v>11184800</v>
+        <v>11204800</v>
       </c>
       <c r="G52" s="26">
         <f>SUM(G15:G51)</f>
-        <v>11184800</v>
+        <v>11204800</v>
       </c>
       <c r="H52" s="116" t="inlineStr">
         <is>
@@ -4090,7 +4098,7 @@
       </c>
       <c r="E58" s="117" t="inlineStr">
         <is>
-          <t>※ NHG는 IR에 "계약"이나 입찰자료상 LOA 미확인(★확인사항).</t>
+          <t>※ NHG는 IR에 "계약"이나 입찰자료상 LOA 미확인(입찰 결과 확인 중).</t>
         </is>
       </c>
     </row>
@@ -4237,23 +4245,23 @@
       </c>
       <c r="C69" s="18">
         <f>'3_연간손익'!D26</f>
-        <v>928.102875</v>
+        <v>934.686208333333</v>
       </c>
       <c r="D69" s="18">
         <f>'3_연간손익'!E26</f>
-        <v>8795.97166666667</v>
+        <v>8812.63833333333</v>
       </c>
       <c r="E69" s="18">
         <f>'3_연간손익'!F26</f>
-        <v>25104.4494666667</v>
+        <v>25109.6494666667</v>
       </c>
       <c r="F69" s="18">
         <f>'3_연간손익'!G26</f>
-        <v>50397.0821066667</v>
+        <v>50410.3421066667</v>
       </c>
       <c r="G69" s="18">
         <f>'3_연간손익'!H26</f>
-        <v>105961.8822208</v>
+        <v>105986.1246208</v>
       </c>
       <c r="H69" s="117" t="inlineStr">
         <is>
@@ -4337,19 +4345,19 @@
       </c>
       <c r="D72" s="16">
         <f>IFERROR(SUM('4_매출_거래처'!AW10:AW40)/D7,0)</f>
-        <v>0.910592947571705</v>
+        <v>0.910752534628017</v>
       </c>
       <c r="E72" s="16">
         <f>IFERROR(SUM('4_매출_거래처'!AX10:AX40)/E7,0)</f>
-        <v>0.641159272727273</v>
+        <v>0.64273503030303</v>
       </c>
       <c r="F72" s="16">
         <f>IFERROR(SUM('4_매출_거래처'!AY10:AY40)/F7,0)</f>
-        <v>0.486459291428572</v>
+        <v>0.487796434285714</v>
       </c>
       <c r="G72" s="16">
         <f>IFERROR(SUM('4_매출_거래처'!AZ10:AZ40)/G7,0)</f>
-        <v>0.300570823794872</v>
+        <v>0.301458823794872</v>
       </c>
       <c r="H72" s="117" t="inlineStr">
         <is>
@@ -4369,19 +4377,19 @@
       </c>
       <c r="D73" s="16">
         <f>IFERROR('4_매출_거래처'!AW45/D7,0)</f>
-        <v>0.0107288462913955</v>
+        <v>0.010709695844638</v>
       </c>
       <c r="E73" s="16">
         <f>IFERROR('4_매출_거래처'!AX45/E7,0)</f>
-        <v>0.140658909090909</v>
+        <v>0.139083151515152</v>
       </c>
       <c r="F73" s="16">
         <f>IFERROR('4_매출_거래처'!AY45/F7,0)</f>
-        <v>0.14496928</v>
+        <v>0.143632137142857</v>
       </c>
       <c r="G73" s="16">
         <f>IFERROR('4_매출_거래처'!AZ45/G7,0)</f>
-        <v>0.148147124923077</v>
+        <v>0.147259124923077</v>
       </c>
       <c r="H73" s="117" t="inlineStr">
         <is>
@@ -4467,185 +4475,166 @@
     <row r="83">
       <c r="A83" s="15" t="inlineStr">
         <is>
+          <t>1_요약 매출·영업이익(억원) = 3_연간손익 (2026~2030)</t>
+        </is>
+      </c>
+      <c r="D83" s="115" t="str">
+        <f>IF(ABS('1_요약'!D8*100000-'3_연간손익'!D7)+ABS('1_요약'!D12*100000-'3_연간손익'!D13)+ABS('1_요약'!E8*100000-'3_연간손익'!E7)+ABS('1_요약'!E12*100000-'3_연간손익'!E13)+ABS('1_요약'!F8*100000-'3_연간손익'!F7)+ABS('1_요약'!F12*100000-'3_연간손익'!F13)+ABS('1_요약'!G8*100000-'3_연간손익'!G7)+ABS('1_요약'!G12*100000-'3_연간손익'!G13)+ABS('1_요약'!H8*100000-'3_연간손익'!H7)+ABS('1_요약'!H12*100000-'3_연간손익'!H13)&lt;1,"OK","확인")</f>
+        <v>OK</v>
+      </c>
+    </row>
+    <row r="84">
+      <c r="A84" s="15" t="inlineStr">
+        <is>
           <t>6_거래처현황 2027 합계 = 4번 시트 A합계</t>
         </is>
       </c>
-      <c r="D83" s="115" t="str">
+      <c r="D84" s="115" t="str">
         <f>IF(ABS('6_거래처현황'!$H$43)&lt;0.5,"OK","확인")</f>
         <v>OK</v>
       </c>
     </row>
-    <row r="84">
-      <c r="A84" s="15" t="inlineStr">
+    <row r="85">
+      <c r="A85" s="15" t="inlineStr">
         <is>
           <t>시나리오 격차: S2 = S1×80%, S3 = S1×60% (9_시나리오 점검)</t>
         </is>
       </c>
-      <c r="D84" s="115" t="str">
+      <c r="D85" s="115" t="str">
         <f>IF(COUNTIF('9_시나리오'!$C$43:$G$43,"OK")=5,"OK","확인")</f>
         <v>OK</v>
       </c>
     </row>
-    <row r="85">
-      <c r="A85" s="15" t="inlineStr">
+    <row r="86">
+      <c r="A86" s="15" t="inlineStr">
         <is>
           <t>제품 믹스 프로파일 합계 100%</t>
         </is>
       </c>
-      <c r="D85" s="115" t="str">
+      <c r="D86" s="115" t="str">
         <f>'8_가정'!$C$80</f>
         <v>OK</v>
       </c>
     </row>
-    <row r="86"/>
     <row r="87"/>
-    <row r="88">
-      <c r="A88" s="3" t="inlineStr">
+    <row r="88"/>
+    <row r="89">
+      <c r="A89" s="3" t="inlineStr">
         <is>
           <t>6. 성장 연속성 — 2027년 12월 run-rate 대비 2028년 매출(선택 시나리오)</t>
         </is>
       </c>
     </row>
-    <row r="89">
-      <c r="A89" s="15" t="inlineStr">
+    <row r="90">
+      <c r="A90" s="15" t="inlineStr">
         <is>
           <t>2027-12 월 매출(천원)</t>
         </is>
       </c>
-      <c r="D89" s="18">
+      <c r="D90" s="18">
         <f>'2_손익계산서'!AA14</f>
         <v>1172900</v>
       </c>
     </row>
-    <row r="90">
-      <c r="A90" s="15" t="inlineStr">
-        <is>
-          <t>2027-12 월 매출 연환산(천원)</t>
-        </is>
-      </c>
-      <c r="D90" s="44">
-        <f>D89*12</f>
-        <v>14074800</v>
-      </c>
-    </row>
     <row r="91">
       <c r="A91" s="15" t="inlineStr">
         <is>
+          <t>2027-12 월 매출 연환산(천원)</t>
+        </is>
+      </c>
+      <c r="D91" s="44">
+        <f>D90*12</f>
+        <v>14074800</v>
+      </c>
+    </row>
+    <row r="92">
+      <c r="A92" s="15" t="inlineStr">
+        <is>
           <t>2028 매출(천원)</t>
         </is>
       </c>
-      <c r="D91" s="18">
+      <c r="D92" s="18">
         <f>'2_손익계산서'!AC14</f>
         <v>33000000</v>
       </c>
     </row>
-    <row r="92">
-      <c r="A92" s="15" t="inlineStr">
-        <is>
-          <t>2028 매출 ÷ 2027-12 연환산(배)</t>
-        </is>
-      </c>
-      <c r="D92" s="119">
-        <f>IFERROR(D91/D90,0)</f>
-        <v>2.34461590928468</v>
-      </c>
-      <c r="E92" s="117" t="inlineStr">
-        <is>
-          <t>※ 2027 월별 입력은 분기·격월 발주가 많아 12월 단일 월 값이 대표성이 낮음 → 연환산 대비 배수는 참고용. 2028 신규 파이프라인·삼성 채널이 포함</t>
-        </is>
-      </c>
-    </row>
     <row r="93">
       <c r="A93" s="15" t="inlineStr">
         <is>
+          <t>2028 매출 ÷ 2027-12 연환산(배)</t>
+        </is>
+      </c>
+      <c r="D93" s="119">
+        <f>IFERROR(D92/D91,0)</f>
+        <v>2.34461590928468</v>
+      </c>
+      <c r="E93" s="117" t="inlineStr">
+        <is>
+          <t>※ 2027 월별 입력은 분기·격월 발주가 많아 12월 단일 월 값이 대표성이 낮음 → 연환산 대비 배수는 참고용. 2028 신규 파이프라인·삼성 채널이 포함</t>
+        </is>
+      </c>
+    </row>
+    <row r="94">
+      <c r="A94" s="15" t="inlineStr">
+        <is>
           <t>2028 평균 월 매출(천원)</t>
         </is>
       </c>
-      <c r="D93" s="44">
-        <f>D91/12</f>
+      <c r="D94" s="44">
+        <f>D92/12</f>
         <v>2750000</v>
       </c>
     </row>
-    <row r="94"/>
     <row r="95"/>
-    <row r="96">
-      <c r="A96" s="3" t="inlineStr">
+    <row r="96"/>
+    <row r="97">
+      <c r="A97" s="3" t="inlineStr">
         <is>
           <t>7. 계약 통화 → 원화 환산(참고, 모델 미반영) — IR 2027 표는 현지 통화 수치를 천원으로 표기한 것으로 보임</t>
         </is>
       </c>
     </row>
-    <row r="97">
-      <c r="A97" s="11" t="inlineStr">
+    <row r="98">
+      <c r="A98" s="11" t="inlineStr">
         <is>
           <t>거래처</t>
         </is>
       </c>
-      <c r="B97" s="11" t="inlineStr">
+      <c r="B98" s="11" t="inlineStr">
         <is>
           <t>계약 통화·금액</t>
         </is>
       </c>
-      <c r="C97" s="11" t="inlineStr">
+      <c r="C98" s="11" t="inlineStr">
         <is>
           <t>금액(현지통화)</t>
         </is>
       </c>
-      <c r="D97" s="11" t="inlineStr">
+      <c r="D98" s="11" t="inlineStr">
         <is>
           <t>환율(8_가정)</t>
         </is>
       </c>
-      <c r="E97" s="11" t="inlineStr">
+      <c r="E98" s="11" t="inlineStr">
         <is>
           <t>원화 환산(천원)</t>
         </is>
       </c>
-      <c r="F97" s="11" t="inlineStr">
+      <c r="F98" s="11" t="inlineStr">
         <is>
           <t>IR 표(천원)</t>
         </is>
       </c>
-      <c r="G97" s="11" t="inlineStr">
+      <c r="G98" s="11" t="inlineStr">
         <is>
           <t>상향 여지(천원)</t>
         </is>
-      </c>
-    </row>
-    <row r="98">
-      <c r="A98" s="15" t="inlineStr">
-        <is>
-          <t>NHG(KTPH·TTSH·WH) — RFP 초안 기준</t>
-        </is>
-      </c>
-      <c r="B98" s="64" t="inlineStr">
-        <is>
-          <t>SGD</t>
-        </is>
-      </c>
-      <c r="C98" s="56" t="n">
-        <v>180000</v>
-      </c>
-      <c r="D98" s="17">
-        <f>'8_가정'!$C$8</f>
-        <v>1096</v>
-      </c>
-      <c r="E98" s="44">
-        <f>C98*D98/1000</f>
-        <v>197280</v>
-      </c>
-      <c r="F98" s="56" t="n">
-        <v>180000</v>
-      </c>
-      <c r="G98" s="44">
-        <f>E98-F98</f>
-        <v>17280</v>
       </c>
     </row>
     <row r="99">
       <c r="A99" s="15" t="inlineStr">
         <is>
-          <t>IMH 욕창 R&amp;D(연)</t>
+          <t>NHG(KTPH·TTSH·WH) — RFP 초안 기준</t>
         </is>
       </c>
       <c r="B99" s="64" t="inlineStr">
@@ -4654,7 +4643,7 @@
         </is>
       </c>
       <c r="C99" s="56" t="n">
-        <v>120000</v>
+        <v>180000</v>
       </c>
       <c r="D99" s="17">
         <f>'8_가정'!$C$8</f>
@@ -4662,50 +4651,50 @@
       </c>
       <c r="E99" s="44">
         <f>C99*D99/1000</f>
-        <v>131520</v>
+        <v>197280</v>
       </c>
       <c r="F99" s="56" t="n">
-        <v>120000</v>
+        <v>180000</v>
       </c>
       <c r="G99" s="44">
         <f>E99-F99</f>
-        <v>11520</v>
+        <v>17280</v>
       </c>
     </row>
     <row r="100">
       <c r="A100" s="15" t="inlineStr">
         <is>
-          <t>Vanguard 입소자 300명 구독(연)</t>
+          <t>IMH 욕창 R&amp;D(연)</t>
         </is>
       </c>
       <c r="B100" s="64" t="inlineStr">
         <is>
-          <t>USD</t>
+          <t>SGD</t>
         </is>
       </c>
       <c r="C100" s="56" t="n">
-        <v>285840</v>
+        <v>120000</v>
       </c>
       <c r="D100" s="17">
-        <f>'8_가정'!$C$7</f>
-        <v>1400</v>
+        <f>'8_가정'!$C$8</f>
+        <v>1096</v>
       </c>
       <c r="E100" s="44">
         <f>C100*D100/1000</f>
-        <v>400176</v>
+        <v>131520</v>
       </c>
       <c r="F100" s="56" t="n">
-        <v>285840</v>
+        <v>120000</v>
       </c>
       <c r="G100" s="44">
         <f>E100-F100</f>
-        <v>114336</v>
+        <v>11520</v>
       </c>
     </row>
     <row r="101">
       <c r="A101" s="15" t="inlineStr">
         <is>
-          <t>Intega 첫 수출(2026-01)</t>
+          <t>Vanguard 입소자 300명 구독(연)</t>
         </is>
       </c>
       <c r="B101" s="64" t="inlineStr">
@@ -4714,7 +4703,7 @@
         </is>
       </c>
       <c r="C101" s="56" t="n">
-        <v>17440</v>
+        <v>285840</v>
       </c>
       <c r="D101" s="17">
         <f>'8_가정'!$C$7</f>
@@ -4722,7 +4711,44 @@
       </c>
       <c r="E101" s="44">
         <f>C101*D101/1000</f>
+        <v>400176</v>
+      </c>
+      <c r="F101" s="56" t="n">
+        <v>285840</v>
+      </c>
+      <c r="G101" s="44">
+        <f>E101-F101</f>
+        <v>114336</v>
+      </c>
+    </row>
+    <row r="102">
+      <c r="A102" s="15" t="inlineStr">
+        <is>
+          <t>Intega 첫 수출(2026-01)</t>
+        </is>
+      </c>
+      <c r="B102" s="64" t="inlineStr">
+        <is>
+          <t>USD</t>
+        </is>
+      </c>
+      <c r="C102" s="56" t="n">
+        <v>17440</v>
+      </c>
+      <c r="D102" s="17">
+        <f>'8_가정'!$C$7</f>
+        <v>1400</v>
+      </c>
+      <c r="E102" s="44">
+        <f>C102*D102/1000</f>
         <v>24416</v>
+      </c>
+    </row>
+    <row r="103">
+      <c r="A103" s="117" t="inlineStr">
+        <is>
+          <t>※ 환산은 IR 고정 환율(1,400원/달러 기준 교차환율, 8_가정). 거래처 매출표는 건별 적용 환율(SGD 약 1,050, EUR 약 1,304 등)로 환산되어 값이 다를 수 있음</t>
+        </is>
       </c>
     </row>
   </sheetData>
@@ -4805,7 +4831,7 @@
       </c>
       <c r="D5" s="80" t="inlineStr">
         <is>
-          <t>모든 시트(요약·손익계산서·연간손익·5번 제품지역·거래처현황·IR정합)의 매출은 4_매출_거래처(2026-10-09 사용자 수정 매출표) 한 곳에서 파생됩니다. 2026 합계 11.93억(IR 12.0억 대비 -0.6%), 2027 합계 111.85억(IR 차트 100.05억 대비 +11.8%). 2028~2030은 삼성 글로벌 채널 잔차로 IR 330억·700억·1,560억과 정확히 일치</t>
+          <t>모든 시트(요약·손익계산서·연간손익·5번 제품지역·거래처현황·IR정합)의 매출은 4_매출_거래처(2026-10-09 사용자 수정 매출표) 한 곳에서 파생됩니다. 2026 합계 12.01억(IR 12.0억 대비 +0.1%), 2027 합계 112.05억(IR 차트 100.05억 대비 +12.0%). 2028~2030은 삼성 글로벌 채널 잔차로 IR 330억·700억·1,560억과 정확히 일치</t>
         </is>
       </c>
       <c r="E5" s="80" t="inlineStr">
@@ -4835,7 +4861,7 @@
       </c>
       <c r="E6" s="80" t="inlineStr">
         <is>
-          <t>실제 발주 일정이 있으면 월별 입력 교체. 투자사 설명 시 "분기 발주 사이클"임을 명시</t>
+          <t>실제 발주 일정이 있으면 월별 입력 교체. 투자사 설명 시 "4개월 주기·분기 발주 사이클"임을 명시</t>
         </is>
       </c>
     </row>
@@ -4900,17 +4926,17 @@
       </c>
       <c r="C9" s="120" t="inlineStr">
         <is>
-          <t>매출표 입력값 중 확인이 필요한 항목</t>
+          <t>매출표 입력값 후속 확정 5건(2026-10-09 사용자 지시 반영)</t>
         </is>
       </c>
       <c r="D9" s="80" t="inlineStr">
         <is>
-          <t>(1) 피플앤피플: 비고 "2026-12 실증사업 3,500만원" vs 입력 2026-11 4,000천원·2027 분기 4,000천원, (2) 국내 B2B 기타 2026-11 −3,950천원(마이너스 입력), (3) Punnita 2026-12 2,000만원(대화 중 안내 USD 30,000 ≈ 4,200만원과 상이), (4) IMH SGD 45,000이 2026-10 47,250천원 단일 월로 입력(안내는 10·11월 분할), (5) NEUCA는 폴란드 총판으로 표기(IR p.25는 스페인)</t>
+          <t>(1) 피플앤피플: 입력 4,000천원 유지(비고도 4,000천원으로 정정), (2) 국내 B2B 기타 2026-11: −3,950 → +3,950천원, (3) Punnita: 12월 2,000만원 = USD 30,000 발주의 선금 50%, 잔금 50%(2,000만원)는 2027-01에 반영(수령월은 가정), (4) IMH: SGD 45,000을 2026-10·11월 50%씩(각 23,625천원), (5) NEUCA: 폴란드 총판으로 표기</t>
         </is>
       </c>
       <c r="E9" s="80" t="inlineStr">
         <is>
-          <t>해당 항목 확인 후 4_매출_거래처 A블록 입력값 교정(교정 시 모든 시트 자동 반영)</t>
+          <t>Punnita 잔금의 실제 수령·인식 월 확인(월이 다르면 4_매출_거래처 A블록 해당 셀만 이동). 매출 인식 시점(선금 수령 vs 납품)에 대한 회계 기준도 확인</t>
         </is>
       </c>
     </row>
@@ -4930,7 +4956,7 @@
       </c>
       <c r="D10" s="80" t="inlineStr">
         <is>
-          <t>매출 11.93억에서 영업이익 소폭 흑자가 되도록 (1) 연구 인력 인건비 40%를 개발비(무형자산)로 자본화(2025 판관비 4.27억이 급여 총액보다 낮은 구조와 일관), (2) 2026 마케팅 1.2%·해외 출장 0.45억·기타 판관비 2.0%로 가정. 정부과제 보조금은 비용 처리분(경상 연구개발비)만 영업외수익으로 인정(0.77억, GDIN 0.35억 포함)</t>
+          <t>매출 12.01억에서 영업이익 소폭 흑자가 되도록 (1) 연구 인력 인건비 40%를 개발비(무형자산)로 자본화(2025 판관비 4.27억이 급여 총액보다 낮은 구조와 일관), (2) 2026 마케팅 1.2%·해외 출장 0.45억·기타 판관비 2.0%로 가정. 정부과제 보조금은 비용 처리분(경상 연구개발비)만 영업외수익으로 인정(0.77억, GDIN 0.35억 포함)</t>
         </is>
       </c>
       <c r="E10" s="80" t="inlineStr">
@@ -5080,12 +5106,12 @@
       </c>
       <c r="D16" s="80" t="inlineStr">
         <is>
-          <t>GIV(Green Initiative Ventures) vs IR 지도 GISI Distribution(네덜란드), NEUCA 폴란드(매출표) vs 스페인(IR p.25), Armedion(독일 총판, IR 미표기 신규), Healthbeats는 호주·뉴질랜드 총판으로 통합 표기</t>
+          <t>GIV(Green Initiative Ventures) vs IR 지도 GISI Distribution(네덜란드), NEUCA는 폴란드 총판으로 표기(IR p.25의 스페인 표기는 슬라이드 정정 필요), Armedion(독일 총판, IR 미표기 신규), Healthbeats는 호주·뉴질랜드 총판으로 통합 표기</t>
         </is>
       </c>
       <c r="E16" s="80" t="inlineStr">
         <is>
-          <t>정확한 법인명·국가 확인</t>
+          <t>정확한 법인명 확인, IR 슬라이드의 NEUCA 국가 표기(스페인 → 폴란드) 정정</t>
         </is>
       </c>
     </row>
@@ -5230,7 +5256,7 @@
       </c>
       <c r="D22" s="80" t="inlineStr">
         <is>
-          <t>2030 S1 영업이익률은 약 16%로 동종 벤치마크(Essity FY2025 EBITA 14.1%, Ontex 조정 EBITDA 10.0%)보다 높음. 인당 매출 8억원(260명)과 고정비 비중 하락이 원인</t>
+          <t>2030 S1 영업이익률은 약 16%로 동종 벤치마크(Essity FY2025 EBITA 14.1%, Ontex 조정 EBITDA 10.0%)보다 높음. 인당 매출 8억원(평균 195명 기준; 기말 260명 기준 6억원)과 고정비 비중 하락이 원인</t>
         </is>
       </c>
       <c r="E22" s="80" t="inlineStr">
@@ -5352,7 +5378,7 @@
     <outlinePr summaryBelow="1" summaryRight="1"/>
     <pageSetUpPr fitToPage="1"/>
   </sheetPr>
-  <dimension ref="A1:AF71"/>
+  <dimension ref="A1:AF73"/>
   <sheetFormatPr baseColWidth="8" defaultRowHeight="15"/>
   <cols>
     <col width="38" customWidth="1" min="1" max="1"/>
@@ -5753,7 +5779,7 @@
       </c>
       <c r="M8" s="18">
         <f>'5_매출_제품지역'!M9</f>
-        <v>163898.5</v>
+        <v>170218.5</v>
       </c>
       <c r="N8" s="18">
         <f>'5_매출_제품지역'!N9</f>
@@ -5761,11 +5787,11 @@
       </c>
       <c r="O8" s="23">
         <f>SUM(C8:N8)</f>
-        <v>732707.42</v>
+        <v>739027.42</v>
       </c>
       <c r="P8" s="18">
         <f>'5_매출_제품지역'!O9</f>
-        <v>462952</v>
+        <v>479952</v>
       </c>
       <c r="Q8" s="18">
         <f>'5_매출_제품지역'!P9</f>
@@ -5813,23 +5839,23 @@
       </c>
       <c r="AB8" s="23">
         <f>SUM(P8:AA8)</f>
-        <v>7885234</v>
+        <v>7902234</v>
       </c>
       <c r="AC8" s="24">
         <f>'5_매출_제품지역'!AC9</f>
-        <v>22277306.48</v>
+        <v>22287186.48</v>
       </c>
       <c r="AD8" s="24">
         <f>'5_매출_제품지역'!AD9</f>
-        <v>43851045.44</v>
+        <v>43874445.44</v>
       </c>
       <c r="AE8" s="24">
         <f>'5_매출_제품지역'!AE9</f>
-        <v>90699925.96032</v>
+        <v>90740099.08032</v>
       </c>
       <c r="AF8" s="25">
         <f>O8+AB8+AC8+AD8+AE8</f>
-        <v>165446219.30032</v>
+        <v>165542992.42032</v>
       </c>
     </row>
     <row r="9">
@@ -5880,7 +5906,7 @@
       </c>
       <c r="M9" s="18">
         <f>'5_매출_제품지역'!M10</f>
-        <v>20535.6</v>
+        <v>21167.6</v>
       </c>
       <c r="N9" s="18">
         <f>'5_매출_제품지역'!N10</f>
@@ -5888,11 +5914,11 @@
       </c>
       <c r="O9" s="23">
         <f>SUM(C9:N9)</f>
-        <v>246338.51</v>
+        <v>246970.51</v>
       </c>
       <c r="P9" s="18">
         <f>'5_매출_제품지역'!O10</f>
-        <v>76322</v>
+        <v>77322</v>
       </c>
       <c r="Q9" s="18">
         <f>'5_매출_제품지역'!P10</f>
@@ -5940,23 +5966,23 @@
       </c>
       <c r="AB9" s="23">
         <f>SUM(P9:AA9)</f>
-        <v>1485374</v>
+        <v>1486374</v>
       </c>
       <c r="AC9" s="24">
         <f>'5_매출_제품지역'!AC10</f>
-        <v>4063924.88</v>
+        <v>4061324.88</v>
       </c>
       <c r="AD9" s="24">
         <f>'5_매출_제품지역'!AD10</f>
-        <v>8515908.288</v>
+        <v>8510292.288</v>
       </c>
       <c r="AE9" s="24">
         <f>'5_매출_제품지역'!AE10</f>
-        <v>18135247.10464</v>
+        <v>18126935.42464</v>
       </c>
       <c r="AF9" s="25">
         <f>O9+AB9+AC9+AD9+AE9</f>
-        <v>32446792.78264</v>
+        <v>32431897.10264</v>
       </c>
     </row>
     <row r="10">
@@ -6007,7 +6033,7 @@
       </c>
       <c r="M10" s="18">
         <f>'5_매출_제품지역'!M11</f>
-        <v>23960.9</v>
+        <v>24908.9</v>
       </c>
       <c r="N10" s="18">
         <f>'5_매출_제품지역'!N11</f>
@@ -6015,11 +6041,11 @@
       </c>
       <c r="O10" s="23">
         <f>SUM(C10:N10)</f>
-        <v>134677.52</v>
+        <v>135625.52</v>
       </c>
       <c r="P10" s="18">
         <f>'5_매출_제품지역'!O11</f>
-        <v>67099</v>
+        <v>69099</v>
       </c>
       <c r="Q10" s="18">
         <f>'5_매출_제품지역'!P11</f>
@@ -6067,23 +6093,23 @@
       </c>
       <c r="AB10" s="23">
         <f>SUM(P10:AA10)</f>
-        <v>1184558</v>
+        <v>1186558</v>
       </c>
       <c r="AC10" s="24">
         <f>'5_매출_제품지역'!AC11</f>
-        <v>3784108</v>
+        <v>3783068</v>
       </c>
       <c r="AD10" s="24">
         <f>'5_매출_제품지역'!AD11</f>
-        <v>8109544.8</v>
+        <v>8107672.8</v>
       </c>
       <c r="AE10" s="24">
         <f>'5_매출_제품지역'!AE11</f>
-        <v>18319085.6</v>
+        <v>18316315.04</v>
       </c>
       <c r="AF10" s="25">
         <f>O10+AB10+AC10+AD10+AE10</f>
-        <v>31531973.92</v>
+        <v>31529239.36</v>
       </c>
     </row>
     <row r="11">
@@ -6198,25 +6224,25 @@
       </c>
       <c r="AC11" s="24">
         <f>'5_매출_제품지역'!AC12</f>
-        <v>1722542.32</v>
+        <v>1718382.32</v>
       </c>
       <c r="AD11" s="24">
         <f>'5_매출_제품지역'!AD12</f>
-        <v>5791768.384</v>
+        <v>5781472.384</v>
       </c>
       <c r="AE11" s="24">
         <f>'5_매출_제품지역'!AE12</f>
-        <v>17506869.35552</v>
+        <v>17488860.71552</v>
       </c>
       <c r="AF11" s="25">
         <f>O11+AB11+AC11+AD11+AE11</f>
-        <v>25304814.05952</v>
+        <v>25272349.41952</v>
       </c>
     </row>
     <row r="12">
       <c r="A12" s="15" t="inlineStr">
         <is>
-          <t xml:space="preserve">  스마트 욕창 케어(2027 Q4 출시)</t>
+          <t xml:space="preserve">  스마트 욕창 케어(2027 출시)</t>
         </is>
       </c>
       <c r="C12" s="18">
@@ -6325,19 +6351,19 @@
       </c>
       <c r="AC12" s="24">
         <f>'5_매출_제품지역'!AC13</f>
-        <v>401283.44</v>
+        <v>400243.44</v>
       </c>
       <c r="AD12" s="24">
         <f>'5_매출_제품지역'!AD13</f>
-        <v>2245576.096</v>
+        <v>2241832.096</v>
       </c>
       <c r="AE12" s="24">
         <f>'5_매출_제품지역'!AE13</f>
-        <v>8173068.94976</v>
+        <v>8164757.26976</v>
       </c>
       <c r="AF12" s="25">
         <f>O12+AB12+AC12+AD12+AE12</f>
-        <v>10839928.48576</v>
+        <v>10826832.80576</v>
       </c>
     </row>
     <row r="13">
@@ -6384,11 +6410,11 @@
       </c>
       <c r="L13" s="18">
         <f>'5_매출_제품지역'!L14</f>
-        <v>47250</v>
+        <v>23625</v>
       </c>
       <c r="M13" s="18">
         <f>'5_매출_제품지역'!M14</f>
-        <v>4000</v>
+        <v>27625</v>
       </c>
       <c r="N13" s="18">
         <f>'5_매출_제품지역'!N14</f>
@@ -6452,19 +6478,19 @@
       </c>
       <c r="AC13" s="24">
         <f>'5_매출_제품지역'!AC14</f>
-        <v>750834.88</v>
+        <v>749794.88</v>
       </c>
       <c r="AD13" s="24">
         <f>'5_매출_제품지역'!AD14</f>
-        <v>1486156.992</v>
+        <v>1484284.992</v>
       </c>
       <c r="AE13" s="24">
         <f>'5_매출_제품지역'!AE14</f>
-        <v>3165803.02976</v>
+        <v>3163032.46976</v>
       </c>
       <c r="AF13" s="25">
         <f>O13+AB13+AC13+AD13+AE13</f>
-        <v>5808388.45176</v>
+        <v>5802705.89176</v>
       </c>
     </row>
     <row r="14">
@@ -6511,11 +6537,11 @@
       </c>
       <c r="L14" s="26">
         <f>SUM(L8:L13)</f>
-        <v>201950</v>
+        <v>178325</v>
       </c>
       <c r="M14" s="26">
         <f>SUM(M8:M13)</f>
-        <v>212395</v>
+        <v>243920</v>
       </c>
       <c r="N14" s="26">
         <f>SUM(N8:N13)</f>
@@ -6523,11 +6549,11 @@
       </c>
       <c r="O14" s="27">
         <f>SUM(O8:O13)</f>
-        <v>1193317</v>
+        <v>1201217</v>
       </c>
       <c r="P14" s="26">
         <f>SUM(P8:P13)</f>
-        <v>625900</v>
+        <v>645900</v>
       </c>
       <c r="Q14" s="26">
         <f>SUM(Q8:Q13)</f>
@@ -6575,7 +6601,7 @@
       </c>
       <c r="AB14" s="27">
         <f>SUM(AB8:AB13)</f>
-        <v>11184800</v>
+        <v>11204800</v>
       </c>
       <c r="AC14" s="28">
         <f>SUM(AC8:AC13)</f>
@@ -6591,7 +6617,7 @@
       </c>
       <c r="AF14" s="26">
         <f>SUM(AF8:AF13)</f>
-        <v>271378117</v>
+        <v>271406017</v>
       </c>
     </row>
     <row r="15">
@@ -6607,15 +6633,15 @@
       </c>
       <c r="O15" s="30">
         <f>IFERROR(O14/'3_연간손익'!$C$7-1,0)</f>
-        <v>0.397059897077665</v>
+        <v>0.40630871628238</v>
       </c>
       <c r="AB15" s="30">
         <f>IFERROR(AB14/O14-1,0)</f>
-        <v>8.37286571799447</v>
+        <v>8.32787331514622</v>
       </c>
       <c r="AC15" s="31">
         <f>IFERROR(AC14/AB14-1,0)</f>
-        <v>1.95043273013375</v>
+        <v>1.94516635727545</v>
       </c>
       <c r="AD15" s="31">
         <f>IFERROR(AD14/AC14-1,0)</f>
@@ -6698,7 +6724,7 @@
       </c>
       <c r="P17" s="18">
         <f>'5_매출_제품지역'!O18</f>
-        <v>185000</v>
+        <v>205000</v>
       </c>
       <c r="Q17" s="18">
         <f>'5_매출_제품지역'!P18</f>
@@ -6746,23 +6772,23 @@
       </c>
       <c r="AB17" s="23">
         <f>SUM(P17:AA17)</f>
-        <v>2451000</v>
+        <v>2471000</v>
       </c>
       <c r="AC17" s="24">
         <f>'5_매출_제품지역'!AC18</f>
-        <v>4175400</v>
+        <v>4227400</v>
       </c>
       <c r="AD17" s="24">
         <f>'5_매출_제품지역'!AD18</f>
-        <v>5800080</v>
+        <v>5893680</v>
       </c>
       <c r="AE17" s="24">
         <f>'5_매출_제품지역'!AE18</f>
-        <v>7340985.6</v>
+        <v>7479513.6</v>
       </c>
       <c r="AF17" s="25">
         <f>O17+AB17+AC17+AD17+AE17</f>
-        <v>20002008.6</v>
+        <v>20306136.6</v>
       </c>
     </row>
     <row r="18">
@@ -6814,11 +6840,11 @@
       </c>
       <c r="L18" s="18">
         <f>'5_매출_제품지역'!L19</f>
-        <v>193250</v>
+        <v>169625</v>
       </c>
       <c r="M18" s="18">
         <f>'5_매출_제품지역'!M19</f>
-        <v>183695</v>
+        <v>215220</v>
       </c>
       <c r="N18" s="18">
         <f>'5_매출_제품지역'!N19</f>
@@ -6826,7 +6852,7 @@
       </c>
       <c r="O18" s="23">
         <f>SUM(C18:N18)</f>
-        <v>958774</v>
+        <v>966674</v>
       </c>
       <c r="P18" s="18">
         <f>'5_매출_제품지역'!O19</f>
@@ -6882,19 +6908,19 @@
       </c>
       <c r="AC18" s="24">
         <f>'5_매출_제품지역'!AC19</f>
-        <v>28824600</v>
+        <v>28772600</v>
       </c>
       <c r="AD18" s="24">
         <f>'5_매출_제품지역'!AD19</f>
-        <v>64199920</v>
+        <v>64106320</v>
       </c>
       <c r="AE18" s="24">
         <f>'5_매출_제품지역'!AE19</f>
-        <v>148659014.4</v>
+        <v>148520486.4</v>
       </c>
       <c r="AF18" s="25">
         <f>O18+AB18+AC18+AD18+AE18</f>
-        <v>251376108.4</v>
+        <v>251099880.4</v>
       </c>
     </row>
     <row r="19">
@@ -6941,11 +6967,11 @@
       </c>
       <c r="L19" s="14">
         <f>IFERROR(L17/L14,0)</f>
-        <v>0.0430799702896757</v>
+        <v>0.0487873265105846</v>
       </c>
       <c r="M19" s="14">
         <f>IFERROR(M17/M14,0)</f>
-        <v>0.135125591468726</v>
+        <v>0.117661528369957</v>
       </c>
       <c r="N19" s="14">
         <f>IFERROR(N17/N14,0)</f>
@@ -6953,11 +6979,11 @@
       </c>
       <c r="O19" s="30">
         <f>IFERROR(O17/O14,0)</f>
-        <v>0.196547103577675</v>
+        <v>0.195254479415459</v>
       </c>
       <c r="P19" s="14">
         <f>IFERROR(P17/P14,0)</f>
-        <v>0.29557437290302</v>
+        <v>0.317386592351757</v>
       </c>
       <c r="Q19" s="14">
         <f>IFERROR(Q17/Q14,0)</f>
@@ -7005,23 +7031,23 @@
       </c>
       <c r="AB19" s="30">
         <f>IFERROR(AB17/AB14,0)</f>
-        <v>0.219136685501752</v>
+        <v>0.220530486934171</v>
       </c>
       <c r="AC19" s="31">
         <f>IFERROR(AC17/AC14,0)</f>
-        <v>0.126527272727273</v>
+        <v>0.12810303030303</v>
       </c>
       <c r="AD19" s="31">
         <f>IFERROR(AD17/AD14,0)</f>
-        <v>0.0828582857142857</v>
+        <v>0.0841954285714286</v>
       </c>
       <c r="AE19" s="31">
         <f>IFERROR(AE17/AE14,0)</f>
-        <v>0.0470576</v>
+        <v>0.0479456</v>
       </c>
       <c r="AF19" s="14">
         <f>IFERROR(AF17/AF14,0)</f>
-        <v>0.0737053113239783</v>
+        <v>0.0748182992567921</v>
       </c>
     </row>
     <row r="20">
@@ -7212,7 +7238,7 @@
       </c>
       <c r="M23" s="18">
         <f>M8*'8_가정'!$C$28</f>
-        <v>88505.19</v>
+        <v>91917.99</v>
       </c>
       <c r="N23" s="18">
         <f>N8*'8_가정'!$C$28</f>
@@ -7220,11 +7246,11 @@
       </c>
       <c r="O23" s="23">
         <f>SUM(C23:N23)</f>
-        <v>395662.0068</v>
+        <v>399074.8068</v>
       </c>
       <c r="P23" s="18">
         <f>P8*'8_가정'!$D$28</f>
-        <v>291659.76</v>
+        <v>302369.76</v>
       </c>
       <c r="Q23" s="18">
         <f>Q8*'8_가정'!$D$28</f>
@@ -7272,23 +7298,23 @@
       </c>
       <c r="AB23" s="23">
         <f>SUM(P23:AA23)</f>
-        <v>4967697.42</v>
+        <v>4978407.42</v>
       </c>
       <c r="AC23" s="24">
         <f>AC8*'8_가정'!$E$28</f>
-        <v>14146089.6148</v>
+        <v>14152363.4148</v>
       </c>
       <c r="AD23" s="24">
         <f>AD8*'8_가정'!$F$28</f>
-        <v>27845413.8544</v>
+        <v>27860272.8544</v>
       </c>
       <c r="AE23" s="24">
         <f>AE8*'8_가정'!$G$28</f>
-        <v>57594452.9848032</v>
+        <v>57619962.9160032</v>
       </c>
       <c r="AF23" s="25">
         <f>O23+AB23+AC23+AD23+AE23</f>
-        <v>104949315.880803</v>
+        <v>105010081.412003</v>
       </c>
     </row>
     <row r="24">
@@ -7344,7 +7370,7 @@
       </c>
       <c r="M24" s="18">
         <f>M9*'8_가정'!$C$29</f>
-        <v>9446.376</v>
+        <v>9737.096</v>
       </c>
       <c r="N24" s="18">
         <f>N9*'8_가정'!$C$29</f>
@@ -7352,11 +7378,11 @@
       </c>
       <c r="O24" s="23">
         <f>SUM(C24:N24)</f>
-        <v>113315.7146</v>
+        <v>113606.4346</v>
       </c>
       <c r="P24" s="18">
         <f>P9*'8_가정'!$D$29</f>
-        <v>43503.54</v>
+        <v>44073.54</v>
       </c>
       <c r="Q24" s="18">
         <f>Q9*'8_가정'!$D$29</f>
@@ -7404,23 +7430,23 @@
       </c>
       <c r="AB24" s="23">
         <f>SUM(P24:AA24)</f>
-        <v>846663.18</v>
+        <v>847233.18</v>
       </c>
       <c r="AC24" s="24">
         <f>AC9*'8_가정'!$E$29</f>
-        <v>2275797.9328</v>
+        <v>2274341.9328</v>
       </c>
       <c r="AD24" s="24">
         <f>AD9*'8_가정'!$F$29</f>
-        <v>4683749.5584</v>
+        <v>4680660.7584</v>
       </c>
       <c r="AE24" s="24">
         <f>AE9*'8_가정'!$G$29</f>
-        <v>9793033.4365056</v>
+        <v>9788545.1293056</v>
       </c>
       <c r="AF24" s="25">
         <f>O24+AB24+AC24+AD24+AE24</f>
-        <v>17712559.8223056</v>
+        <v>17704387.4351056</v>
       </c>
     </row>
     <row r="25">
@@ -7476,7 +7502,7 @@
       </c>
       <c r="M25" s="18">
         <f>M10*'8_가정'!$C$30</f>
-        <v>4792.18</v>
+        <v>4981.78</v>
       </c>
       <c r="N25" s="18">
         <f>N10*'8_가정'!$C$30</f>
@@ -7484,11 +7510,11 @@
       </c>
       <c r="O25" s="23">
         <f>SUM(C25:N25)</f>
-        <v>26935.504</v>
+        <v>27125.104</v>
       </c>
       <c r="P25" s="18">
         <f>P10*'8_가정'!$D$30</f>
-        <v>16103.76</v>
+        <v>16583.76</v>
       </c>
       <c r="Q25" s="18">
         <f>Q10*'8_가정'!$D$30</f>
@@ -7536,23 +7562,23 @@
       </c>
       <c r="AB25" s="23">
         <f>SUM(P25:AA25)</f>
-        <v>284293.92</v>
+        <v>284773.92</v>
       </c>
       <c r="AC25" s="24">
         <f>AC10*'8_가정'!$E$30</f>
-        <v>870344.84</v>
+        <v>870105.64</v>
       </c>
       <c r="AD25" s="24">
         <f>AD10*'8_가정'!$F$30</f>
-        <v>1784099.856</v>
+        <v>1783688.016</v>
       </c>
       <c r="AE25" s="24">
         <f>AE10*'8_가정'!$G$30</f>
-        <v>3847007.976</v>
+        <v>3846426.1584</v>
       </c>
       <c r="AF25" s="25">
         <f>O25+AB25+AC25+AD25+AE25</f>
-        <v>6812682.096</v>
+        <v>6812118.8384</v>
       </c>
     </row>
     <row r="26">
@@ -7672,25 +7698,25 @@
       </c>
       <c r="AC26" s="24">
         <f>AC11*'8_가정'!$E$31</f>
-        <v>999074.5456</v>
+        <v>996661.7456</v>
       </c>
       <c r="AD26" s="24">
         <f>AD11*'8_가정'!$F$31</f>
-        <v>3243390.29504</v>
+        <v>3237624.53504</v>
       </c>
       <c r="AE26" s="24">
         <f>AE11*'8_가정'!$G$31</f>
-        <v>9453709.4519808</v>
+        <v>9443984.7863808</v>
       </c>
       <c r="AF26" s="25">
         <f>O26+AB26+AC26+AD26+AE26</f>
-        <v>13866354.6926208</v>
+        <v>13848451.4670208</v>
       </c>
     </row>
     <row r="27">
       <c r="A27" s="15" t="inlineStr">
         <is>
-          <t xml:space="preserve">  스마트 욕창 케어(2027 Q4 출시) 원가</t>
+          <t xml:space="preserve">  스마트 욕창 케어(2027 출시) 원가</t>
         </is>
       </c>
       <c r="B27" s="29" t="inlineStr">
@@ -7804,19 +7830,19 @@
       </c>
       <c r="AC27" s="24">
         <f>AC12*'8_가정'!$E$32</f>
-        <v>228731.5608</v>
+        <v>228138.7608</v>
       </c>
       <c r="AD27" s="24">
         <f>AD12*'8_가정'!$F$32</f>
-        <v>1235066.8528</v>
+        <v>1233007.6528</v>
       </c>
       <c r="AE27" s="24">
         <f>AE12*'8_가정'!$G$32</f>
-        <v>4331726.5433728</v>
+        <v>4327321.3529728</v>
       </c>
       <c r="AF27" s="25">
         <f>O27+AB27+AC27+AD27+AE27</f>
-        <v>5807124.9569728</v>
+        <v>5800067.7665728</v>
       </c>
     </row>
     <row r="28">
@@ -7868,11 +7894,11 @@
       </c>
       <c r="L28" s="18">
         <f>L13*'8_가정'!$C$33</f>
-        <v>25987.5</v>
+        <v>12993.75</v>
       </c>
       <c r="M28" s="18">
         <f>M13*'8_가정'!$C$33</f>
-        <v>2200</v>
+        <v>15193.75</v>
       </c>
       <c r="N28" s="18">
         <f>N13*'8_가정'!$C$33</f>
@@ -7936,19 +7962,19 @@
       </c>
       <c r="AC28" s="24">
         <f>AC13*'8_가정'!$E$33</f>
-        <v>412959.184</v>
+        <v>412387.184</v>
       </c>
       <c r="AD28" s="24">
         <f>AD13*'8_가정'!$F$33</f>
-        <v>817386.3456</v>
+        <v>816356.7456</v>
       </c>
       <c r="AE28" s="24">
         <f>AE13*'8_가정'!$G$33</f>
-        <v>1741191.666368</v>
+        <v>1739667.858368</v>
       </c>
       <c r="AF28" s="25">
         <f>O28+AB28+AC28+AD28+AE28</f>
-        <v>3194613.648468</v>
+        <v>3191488.240468</v>
       </c>
     </row>
     <row r="29">
@@ -8000,11 +8026,11 @@
       </c>
       <c r="L29" s="18">
         <f>L14*'8_가정'!$C$34</f>
-        <v>3029.25</v>
+        <v>2674.875</v>
       </c>
       <c r="M29" s="18">
         <f>M14*'8_가정'!$C$34</f>
-        <v>3185.925</v>
+        <v>3658.8</v>
       </c>
       <c r="N29" s="18">
         <f>N14*'8_가정'!$C$34</f>
@@ -8012,11 +8038,11 @@
       </c>
       <c r="O29" s="23">
         <f>SUM(C29:N29)</f>
-        <v>17899.755</v>
+        <v>18018.255</v>
       </c>
       <c r="P29" s="18">
         <f>P14*'8_가정'!$D$34</f>
-        <v>15647.5</v>
+        <v>16147.5</v>
       </c>
       <c r="Q29" s="18">
         <f>Q14*'8_가정'!$D$34</f>
@@ -8064,7 +8090,7 @@
       </c>
       <c r="AB29" s="23">
         <f>SUM(P29:AA29)</f>
-        <v>279620</v>
+        <v>280120</v>
       </c>
       <c r="AC29" s="24">
         <f>AC14*'8_가정'!$E$34</f>
@@ -8080,7 +8106,7 @@
       </c>
       <c r="AF29" s="25">
         <f>O29+AB29+AC29+AD29+AE29</f>
-        <v>9197519.755</v>
+        <v>9198138.255</v>
       </c>
     </row>
     <row r="30">
@@ -8127,11 +8153,11 @@
       </c>
       <c r="L30" s="26">
         <f>SUM(L23:L29)</f>
-        <v>105185.75</v>
+        <v>91837.625</v>
       </c>
       <c r="M30" s="26">
         <f>SUM(M23:M29)</f>
-        <v>108129.671</v>
+        <v>125489.416</v>
       </c>
       <c r="N30" s="26">
         <f>SUM(N23:N29)</f>
@@ -8139,11 +8165,11 @@
       </c>
       <c r="O30" s="27">
         <f>SUM(O23:O29)</f>
-        <v>597589.4329</v>
+        <v>601601.0529</v>
       </c>
       <c r="P30" s="26">
         <f>SUM(P23:P29)</f>
-        <v>378363.76</v>
+        <v>390623.76</v>
       </c>
       <c r="Q30" s="26">
         <f>SUM(Q23:Q29)</f>
@@ -8191,23 +8217,23 @@
       </c>
       <c r="AB30" s="27">
         <f>SUM(AB23:AB29)</f>
-        <v>6739354.92</v>
+        <v>6751614.92</v>
       </c>
       <c r="AC30" s="28">
         <f>SUM(AC23:AC29)</f>
-        <v>19922997.678</v>
+        <v>19923998.678</v>
       </c>
       <c r="AD30" s="28">
         <f>SUM(AD23:AD29)</f>
-        <v>42059106.76224</v>
+        <v>42061610.56224</v>
       </c>
       <c r="AE30" s="28">
         <f>SUM(AE23:AE29)</f>
-        <v>92221122.0590304</v>
+        <v>92225908.2014304</v>
       </c>
       <c r="AF30" s="26">
         <f>SUM(AF23:AF29)</f>
-        <v>161540170.85217</v>
+        <v>161564733.41457</v>
       </c>
     </row>
     <row r="31">
@@ -8254,11 +8280,11 @@
       </c>
       <c r="L31" s="34">
         <f>L14-L30</f>
-        <v>96764.25</v>
+        <v>86487.375</v>
       </c>
       <c r="M31" s="34">
         <f>M14-M30</f>
-        <v>104265.329</v>
+        <v>118430.584</v>
       </c>
       <c r="N31" s="34">
         <f>N14-N30</f>
@@ -8266,11 +8292,11 @@
       </c>
       <c r="O31" s="23">
         <f>O14-O30</f>
-        <v>595727.5671</v>
+        <v>599615.9471</v>
       </c>
       <c r="P31" s="34">
         <f>P14-P30</f>
-        <v>247536.24</v>
+        <v>255276.24</v>
       </c>
       <c r="Q31" s="34">
         <f>Q14-Q30</f>
@@ -8318,23 +8344,23 @@
       </c>
       <c r="AB31" s="23">
         <f>AB14-AB30</f>
-        <v>4445445.08</v>
+        <v>4453185.08</v>
       </c>
       <c r="AC31" s="35">
         <f>AC14-AC30</f>
-        <v>13077002.322</v>
+        <v>13076001.322</v>
       </c>
       <c r="AD31" s="35">
         <f>AD14-AD30</f>
-        <v>27940893.23776</v>
+        <v>27938389.43776</v>
       </c>
       <c r="AE31" s="35">
         <f>AE14-AE30</f>
-        <v>63778877.9409696</v>
+        <v>63774091.7985696</v>
       </c>
       <c r="AF31" s="34">
         <f>AF14-AF30</f>
-        <v>109837946.14783</v>
+        <v>109841283.58543</v>
       </c>
     </row>
     <row r="32">
@@ -8381,11 +8407,11 @@
       </c>
       <c r="L32" s="14">
         <f>IFERROR(L31/L14,0)</f>
-        <v>0.479149541965833</v>
+        <v>0.48499859806533</v>
       </c>
       <c r="M32" s="14">
         <f>IFERROR(M31/M14,0)</f>
-        <v>0.490902935568163</v>
+        <v>0.485530436208593</v>
       </c>
       <c r="N32" s="14">
         <f>IFERROR(N31/N14,0)</f>
@@ -8393,11 +8419,11 @@
       </c>
       <c r="O32" s="30">
         <f>IFERROR(O31/O14,0)</f>
-        <v>0.499219877953637</v>
+        <v>0.499173710578522</v>
       </c>
       <c r="P32" s="14">
         <f>IFERROR(P31/P14,0)</f>
-        <v>0.395488480587953</v>
+        <v>0.395225638643753</v>
       </c>
       <c r="Q32" s="14">
         <f>IFERROR(Q31/Q14,0)</f>
@@ -8445,23 +8471,23 @@
       </c>
       <c r="AB32" s="30">
         <f>IFERROR(AB31/AB14,0)</f>
-        <v>0.397454141334669</v>
+        <v>0.397435481222333</v>
       </c>
       <c r="AC32" s="31">
         <f>IFERROR(AC31/AC14,0)</f>
-        <v>0.396272797636364</v>
+        <v>0.39624246430303</v>
       </c>
       <c r="AD32" s="31">
         <f>IFERROR(AD31/AD14,0)</f>
-        <v>0.399155617682286</v>
+        <v>0.399119849110857</v>
       </c>
       <c r="AE32" s="31">
         <f>IFERROR(AE31/AE14,0)</f>
-        <v>0.408838961160062</v>
+        <v>0.408808280760062</v>
       </c>
       <c r="AF32" s="14">
         <f>IFERROR(AF31/AF14,0)</f>
-        <v>0.404741352626563</v>
+        <v>0.404712042863182</v>
       </c>
     </row>
     <row r="33"/>
@@ -8478,6 +8504,11 @@
           <t xml:space="preserve">  급여</t>
         </is>
       </c>
+      <c r="B35" s="29" t="inlineStr">
+        <is>
+          <t>개발비 자본화(8_가정) 차감 후 — 7_비용인력 31·61행</t>
+        </is>
+      </c>
       <c r="C35" s="18">
         <f>'7_비용인력'!C19</f>
         <v>23833.8</v>
@@ -8605,6 +8636,11 @@
           <t xml:space="preserve">  퇴직급여·4대보험·복리후생</t>
         </is>
       </c>
+      <c r="B36" s="29" t="inlineStr">
+        <is>
+          <t>개발비 자본화(8_가정) 차감 후 — 7_비용인력 31·61행</t>
+        </is>
+      </c>
       <c r="C36" s="18">
         <f>'7_비용인력'!C20</f>
         <v>5243.436</v>
@@ -8770,11 +8806,11 @@
       </c>
       <c r="L37" s="18">
         <f>'7_비용인력'!L21</f>
-        <v>2423.4</v>
+        <v>2139.9</v>
       </c>
       <c r="M37" s="18">
         <f>'7_비용인력'!M21</f>
-        <v>2548.74</v>
+        <v>2927.04</v>
       </c>
       <c r="N37" s="18">
         <f>'7_비용인력'!N21</f>
@@ -8782,11 +8818,11 @@
       </c>
       <c r="O37" s="36">
         <f>'7_비용인력'!O21</f>
-        <v>14319.804</v>
+        <v>14414.604</v>
       </c>
       <c r="P37" s="18">
         <f>'7_비용인력'!P21</f>
-        <v>15647.5</v>
+        <v>16147.5</v>
       </c>
       <c r="Q37" s="18">
         <f>'7_비용인력'!Q21</f>
@@ -8834,7 +8870,7 @@
       </c>
       <c r="AB37" s="36">
         <f>'7_비용인력'!AB21</f>
-        <v>279620</v>
+        <v>280120</v>
       </c>
       <c r="AC37" s="24">
         <f>'7_비용인력'!AC21</f>
@@ -8850,7 +8886,7 @@
       </c>
       <c r="AF37" s="37">
         <f>'7_비용인력'!AF21</f>
-        <v>7717939.804</v>
+        <v>7718534.604</v>
       </c>
     </row>
     <row r="38">
@@ -8897,11 +8933,11 @@
       </c>
       <c r="L38" s="18">
         <f>'7_비용인력'!L22</f>
-        <v>2423.4</v>
+        <v>2139.9</v>
       </c>
       <c r="M38" s="18">
         <f>'7_비용인력'!M22</f>
-        <v>2548.74</v>
+        <v>2927.04</v>
       </c>
       <c r="N38" s="18">
         <f>'7_비용인력'!N22</f>
@@ -8909,11 +8945,11 @@
       </c>
       <c r="O38" s="36">
         <f>'7_비용인력'!O22</f>
-        <v>14319.804</v>
+        <v>14414.604</v>
       </c>
       <c r="P38" s="18">
         <f>'7_비용인력'!P22</f>
-        <v>12518</v>
+        <v>12918</v>
       </c>
       <c r="Q38" s="18">
         <f>'7_비용인력'!Q22</f>
@@ -8961,7 +8997,7 @@
       </c>
       <c r="AB38" s="36">
         <f>'7_비용인력'!AB22</f>
-        <v>223696</v>
+        <v>224096</v>
       </c>
       <c r="AC38" s="24">
         <f>'7_비용인력'!AC22</f>
@@ -8977,7 +9013,7 @@
       </c>
       <c r="AF38" s="37">
         <f>'7_비용인력'!AF22</f>
-        <v>5936015.804</v>
+        <v>5936510.604</v>
       </c>
     </row>
     <row r="39">
@@ -9024,11 +9060,11 @@
       </c>
       <c r="L39" s="18">
         <f>'7_비용인력'!L23</f>
-        <v>5048.75</v>
+        <v>4458.125</v>
       </c>
       <c r="M39" s="18">
         <f>'7_비용인력'!M23</f>
-        <v>5309.875</v>
+        <v>6098</v>
       </c>
       <c r="N39" s="18">
         <f>'7_비용인력'!N23</f>
@@ -9036,11 +9072,11 @@
       </c>
       <c r="O39" s="36">
         <f>'7_비용인력'!O23</f>
-        <v>29832.925</v>
+        <v>30030.425</v>
       </c>
       <c r="P39" s="18">
         <f>'7_비용인력'!P23</f>
-        <v>21906.5</v>
+        <v>22606.5</v>
       </c>
       <c r="Q39" s="18">
         <f>'7_비용인력'!Q23</f>
@@ -9088,7 +9124,7 @@
       </c>
       <c r="AB39" s="36">
         <f>'7_비용인력'!AB23</f>
-        <v>391468</v>
+        <v>392168</v>
       </c>
       <c r="AC39" s="24">
         <f>'7_비용인력'!AC23</f>
@@ -9104,7 +9140,7 @@
       </c>
       <c r="AF39" s="37">
         <f>'7_비용인력'!AF23</f>
-        <v>9276300.925</v>
+        <v>9277198.425</v>
       </c>
     </row>
     <row r="40">
@@ -9151,11 +9187,11 @@
       </c>
       <c r="L40" s="18">
         <f>'7_비용인력'!L24</f>
-        <v>7068.25</v>
+        <v>6241.375</v>
       </c>
       <c r="M40" s="18">
         <f>'7_비용인력'!M24</f>
-        <v>7433.825</v>
+        <v>8537.2</v>
       </c>
       <c r="N40" s="18">
         <f>'7_비용인력'!N24</f>
@@ -9163,11 +9199,11 @@
       </c>
       <c r="O40" s="36">
         <f>'7_비용인력'!O24</f>
-        <v>41766.095</v>
+        <v>42042.595</v>
       </c>
       <c r="P40" s="18">
         <f>'7_비용인력'!P24</f>
-        <v>21906.5</v>
+        <v>22606.5</v>
       </c>
       <c r="Q40" s="18">
         <f>'7_비용인력'!Q24</f>
@@ -9215,7 +9251,7 @@
       </c>
       <c r="AB40" s="36">
         <f>'7_비용인력'!AB24</f>
-        <v>391468</v>
+        <v>392168</v>
       </c>
       <c r="AC40" s="24">
         <f>'7_비용인력'!AC24</f>
@@ -9231,7 +9267,7 @@
       </c>
       <c r="AF40" s="37">
         <f>'7_비용인력'!AF24</f>
-        <v>8355234.095</v>
+        <v>8356210.595</v>
       </c>
     </row>
     <row r="41">
@@ -9659,11 +9695,11 @@
       </c>
       <c r="L44" s="18">
         <f>'7_비용인력'!L28</f>
-        <v>807.8</v>
+        <v>713.3</v>
       </c>
       <c r="M44" s="18">
         <f>'7_비용인력'!M28</f>
-        <v>849.58</v>
+        <v>975.68</v>
       </c>
       <c r="N44" s="18">
         <f>'7_비용인력'!N28</f>
@@ -9671,11 +9707,11 @@
       </c>
       <c r="O44" s="36">
         <f>'7_비용인력'!O28</f>
-        <v>4773.268</v>
+        <v>4804.868</v>
       </c>
       <c r="P44" s="18">
         <f>'7_비용인력'!P28</f>
-        <v>3129.5</v>
+        <v>3229.5</v>
       </c>
       <c r="Q44" s="18">
         <f>'7_비용인력'!Q28</f>
@@ -9723,7 +9759,7 @@
       </c>
       <c r="AB44" s="36">
         <f>'7_비용인력'!AB28</f>
-        <v>55924</v>
+        <v>56024</v>
       </c>
       <c r="AC44" s="24">
         <f>'7_비용인력'!AC28</f>
@@ -9739,7 +9775,7 @@
       </c>
       <c r="AF44" s="37">
         <f>'7_비용인력'!AF28</f>
-        <v>1355697.268</v>
+        <v>1355828.868</v>
       </c>
     </row>
     <row r="45">
@@ -9786,11 +9822,11 @@
       </c>
       <c r="L45" s="18">
         <f>'7_비용인력'!L29</f>
-        <v>4039</v>
+        <v>3566.5</v>
       </c>
       <c r="M45" s="18">
         <f>'7_비용인력'!M29</f>
-        <v>4247.9</v>
+        <v>4878.4</v>
       </c>
       <c r="N45" s="18">
         <f>'7_비용인력'!N29</f>
@@ -9798,11 +9834,11 @@
       </c>
       <c r="O45" s="36">
         <f>'7_비용인력'!O29</f>
-        <v>23866.34</v>
+        <v>24024.34</v>
       </c>
       <c r="P45" s="18">
         <f>'7_비용인력'!P29</f>
-        <v>18777</v>
+        <v>19377</v>
       </c>
       <c r="Q45" s="18">
         <f>'7_비용인력'!Q29</f>
@@ -9850,7 +9886,7 @@
       </c>
       <c r="AB45" s="36">
         <f>'7_비용인력'!AB29</f>
-        <v>335544</v>
+        <v>336144</v>
       </c>
       <c r="AC45" s="24">
         <f>'7_비용인력'!AC29</f>
@@ -9866,7 +9902,7 @@
       </c>
       <c r="AF45" s="37">
         <f>'7_비용인력'!AF29</f>
-        <v>6501410.34</v>
+        <v>6502168.34</v>
       </c>
     </row>
     <row r="46">
@@ -9913,11 +9949,11 @@
       </c>
       <c r="L46" s="26">
         <f>SUM(L35:L45)</f>
-        <v>59137.836</v>
+        <v>56586.336</v>
       </c>
       <c r="M46" s="26">
         <f>SUM(M35:M45)</f>
-        <v>60265.896</v>
+        <v>63670.596</v>
       </c>
       <c r="N46" s="26">
         <f>SUM(N35:N45)</f>
@@ -9925,11 +9961,11 @@
       </c>
       <c r="O46" s="27">
         <f>SUM(O35:O45)</f>
-        <v>576805.068</v>
+        <v>577658.268</v>
       </c>
       <c r="P46" s="26">
         <f>SUM(P35:P45)</f>
-        <v>201997.571546667</v>
+        <v>204997.571546667</v>
       </c>
       <c r="Q46" s="26">
         <f>SUM(Q35:Q45)</f>
@@ -9977,7 +10013,7 @@
       </c>
       <c r="AB46" s="27">
         <f>SUM(AB35:AB45)</f>
-        <v>3279981.06656</v>
+        <v>3282981.06656</v>
       </c>
       <c r="AC46" s="28">
         <f>SUM(AC35:AC45)</f>
@@ -9993,7 +10029,7 @@
       </c>
       <c r="AF46" s="26">
         <f>SUM(AF35:AF45)</f>
-        <v>69731666.2445242</v>
+        <v>69735519.4445242</v>
       </c>
     </row>
     <row r="47">
@@ -10040,11 +10076,11 @@
       </c>
       <c r="L47" s="38">
         <f>L31-L46</f>
-        <v>37626.414</v>
+        <v>29901.039</v>
       </c>
       <c r="M47" s="38">
         <f>M31-M46</f>
-        <v>43999.433</v>
+        <v>54759.988</v>
       </c>
       <c r="N47" s="38">
         <f>N31-N46</f>
@@ -10052,11 +10088,11 @@
       </c>
       <c r="O47" s="39">
         <f>O31-O46</f>
-        <v>18922.4991</v>
+        <v>21957.6791000001</v>
       </c>
       <c r="P47" s="38">
         <f>P31-P46</f>
-        <v>45538.6684533333</v>
+        <v>50278.6684533333</v>
       </c>
       <c r="Q47" s="38">
         <f>Q31-Q46</f>
@@ -10104,23 +10140,23 @@
       </c>
       <c r="AB47" s="39">
         <f>AB31-AB46</f>
-        <v>1165464.01344</v>
+        <v>1170204.01344</v>
       </c>
       <c r="AC47" s="40">
         <f>AC31-AC46</f>
-        <v>3733403.6193904</v>
+        <v>3732402.6193904</v>
       </c>
       <c r="AD47" s="40">
         <f>AD31-AD46</f>
-        <v>9632207.19432603</v>
+        <v>9629703.39432603</v>
       </c>
       <c r="AE47" s="40">
         <f>AE31-AE46</f>
-        <v>25556282.577049</v>
+        <v>25551496.434649</v>
       </c>
       <c r="AF47" s="38">
         <f>AF31-AF46</f>
-        <v>40106279.9033054</v>
+        <v>40105764.1409054</v>
       </c>
     </row>
     <row r="48">
@@ -10167,11 +10203,11 @@
       </c>
       <c r="L48" s="14">
         <f>IFERROR(L47/L14,0)</f>
-        <v>0.186315493934142</v>
+        <v>0.167677212953876</v>
       </c>
       <c r="M48" s="14">
         <f>IFERROR(M47/M14,0)</f>
-        <v>0.207158515972598</v>
+        <v>0.224499786815349</v>
       </c>
       <c r="N48" s="14">
         <f>IFERROR(N47/N14,0)</f>
@@ -10179,11 +10215,11 @@
       </c>
       <c r="O48" s="30">
         <f>IFERROR(O47/O14,0)</f>
-        <v>0.0158570598591992</v>
+        <v>0.0182795274292655</v>
       </c>
       <c r="P48" s="14">
         <f>IFERROR(P47/P14,0)</f>
-        <v>0.0727570993023379</v>
+        <v>0.077842806089694</v>
       </c>
       <c r="Q48" s="14">
         <f>IFERROR(Q47/Q14,0)</f>
@@ -10231,23 +10267,23 @@
       </c>
       <c r="AB48" s="30">
         <f>IFERROR(AB47/AB14,0)</f>
-        <v>0.104200702152922</v>
+        <v>0.104437742167642</v>
       </c>
       <c r="AC48" s="31">
         <f>IFERROR(AC47/AC14,0)</f>
-        <v>0.11313344301183</v>
+        <v>0.113103109678497</v>
       </c>
       <c r="AD48" s="31">
         <f>IFERROR(AD47/AD14,0)</f>
-        <v>0.137602959918943</v>
+        <v>0.137567191347515</v>
       </c>
       <c r="AE48" s="31">
         <f>IFERROR(AE47/AE14,0)</f>
-        <v>0.163822324211852</v>
+        <v>0.163791643811852</v>
       </c>
       <c r="AF48" s="14">
         <f>IFERROR(AF47/AF14,0)</f>
-        <v>0.147787450022381</v>
+        <v>0.1477703574306</v>
       </c>
     </row>
     <row r="49"/>
@@ -10266,55 +10302,55 @@
       </c>
       <c r="C51" s="25">
         <f>C52</f>
-        <v>6397.17458333333</v>
+        <v>6420.21625</v>
       </c>
       <c r="D51" s="25">
         <f>D52</f>
-        <v>6397.17458333333</v>
+        <v>6420.21625</v>
       </c>
       <c r="E51" s="25">
         <f>E52</f>
-        <v>6397.17458333333</v>
+        <v>6420.21625</v>
       </c>
       <c r="F51" s="25">
         <f>F52</f>
-        <v>6397.17458333333</v>
+        <v>6420.21625</v>
       </c>
       <c r="G51" s="25">
         <f>G52</f>
-        <v>6397.17458333333</v>
+        <v>6420.21625</v>
       </c>
       <c r="H51" s="25">
         <f>H52</f>
-        <v>6397.17458333333</v>
+        <v>6420.21625</v>
       </c>
       <c r="I51" s="25">
         <f>I52</f>
-        <v>6397.17458333333</v>
+        <v>6420.21625</v>
       </c>
       <c r="J51" s="25">
         <f>J52</f>
-        <v>6397.17458333333</v>
+        <v>6420.21625</v>
       </c>
       <c r="K51" s="25">
         <f>K52</f>
-        <v>6397.17458333333</v>
+        <v>6420.21625</v>
       </c>
       <c r="L51" s="25">
         <f>L52</f>
-        <v>6397.17458333333</v>
+        <v>6420.21625</v>
       </c>
       <c r="M51" s="25">
         <f>M52</f>
-        <v>6397.17458333333</v>
+        <v>6420.21625</v>
       </c>
       <c r="N51" s="25">
         <f>N52</f>
-        <v>6397.17458333333</v>
+        <v>6420.21625</v>
       </c>
       <c r="O51" s="23">
         <f>O52</f>
-        <v>76766.095</v>
+        <v>77042.595</v>
       </c>
       <c r="P51" s="25">
         <f>P52</f>
@@ -10382,7 +10418,7 @@
       </c>
       <c r="AF51" s="25">
         <f>AF52</f>
-        <v>676766.095</v>
+        <v>677042.595</v>
       </c>
     </row>
     <row r="52">
@@ -10393,55 +10429,55 @@
       </c>
       <c r="C52" s="41">
         <f>'7_비용인력'!C33</f>
-        <v>6397.17458333333</v>
+        <v>6420.21625</v>
       </c>
       <c r="D52" s="41">
         <f>'7_비용인력'!D33</f>
-        <v>6397.17458333333</v>
+        <v>6420.21625</v>
       </c>
       <c r="E52" s="41">
         <f>'7_비용인력'!E33</f>
-        <v>6397.17458333333</v>
+        <v>6420.21625</v>
       </c>
       <c r="F52" s="41">
         <f>'7_비용인력'!F33</f>
-        <v>6397.17458333333</v>
+        <v>6420.21625</v>
       </c>
       <c r="G52" s="41">
         <f>'7_비용인력'!G33</f>
-        <v>6397.17458333333</v>
+        <v>6420.21625</v>
       </c>
       <c r="H52" s="41">
         <f>'7_비용인력'!H33</f>
-        <v>6397.17458333333</v>
+        <v>6420.21625</v>
       </c>
       <c r="I52" s="41">
         <f>'7_비용인력'!I33</f>
-        <v>6397.17458333333</v>
+        <v>6420.21625</v>
       </c>
       <c r="J52" s="41">
         <f>'7_비용인력'!J33</f>
-        <v>6397.17458333333</v>
+        <v>6420.21625</v>
       </c>
       <c r="K52" s="41">
         <f>'7_비용인력'!K33</f>
-        <v>6397.17458333333</v>
+        <v>6420.21625</v>
       </c>
       <c r="L52" s="41">
         <f>'7_비용인력'!L33</f>
-        <v>6397.17458333333</v>
+        <v>6420.21625</v>
       </c>
       <c r="M52" s="41">
         <f>'7_비용인력'!M33</f>
-        <v>6397.17458333333</v>
+        <v>6420.21625</v>
       </c>
       <c r="N52" s="41">
         <f>'7_비용인력'!N33</f>
-        <v>6397.17458333333</v>
+        <v>6420.21625</v>
       </c>
       <c r="O52" s="42">
         <f>'7_비용인력'!O33</f>
-        <v>76766.095</v>
+        <v>77042.595</v>
       </c>
       <c r="P52" s="41">
         <f>'7_비용인력'!P33</f>
@@ -10509,7 +10545,7 @@
       </c>
       <c r="AF52" s="41">
         <f>'7_비용인력'!AF33</f>
-        <v>676766.095</v>
+        <v>677042.595</v>
       </c>
     </row>
     <row r="53">
@@ -10774,59 +10810,59 @@
       </c>
       <c r="C55" s="26">
         <f>C47+C51-C53</f>
-        <v>-17169.2060166667</v>
+        <v>-17146.16435</v>
       </c>
       <c r="D55" s="26">
         <f>D47+D51-D53</f>
-        <v>-21757.9140166667</v>
+        <v>-21734.87235</v>
       </c>
       <c r="E55" s="26">
         <f>E47+E51-E53</f>
-        <v>-14076.6762166667</v>
+        <v>-14053.63455</v>
       </c>
       <c r="F55" s="26">
         <f>F47+F51-F53</f>
-        <v>-31624.0604166667</v>
+        <v>-31601.01875</v>
       </c>
       <c r="G55" s="26">
         <f>G47+G51-G53</f>
-        <v>-27351.0816166667</v>
+        <v>-27328.03995</v>
       </c>
       <c r="H55" s="26">
         <f>H47+H51-H53</f>
-        <v>-16424.2260166667</v>
+        <v>-16401.18435</v>
       </c>
       <c r="I55" s="26">
         <f>I47+I51-I53</f>
-        <v>-30720.9138166667</v>
+        <v>-30697.87215</v>
       </c>
       <c r="J55" s="26">
         <f>J47+J51-J53</f>
-        <v>-32750.5770166667</v>
+        <v>-32727.53535</v>
       </c>
       <c r="K55" s="26">
         <f>K47+K51-K53</f>
-        <v>-19841.1480166667</v>
+        <v>-19818.10635</v>
       </c>
       <c r="L55" s="26">
         <f>L47+L51-L53</f>
-        <v>39224.5025833333</v>
+        <v>31522.16925</v>
       </c>
       <c r="M55" s="26">
         <f>M47+M51-M53</f>
-        <v>45597.5215833333</v>
+        <v>56381.11825</v>
       </c>
       <c r="N55" s="26">
         <f>N47+N51-N53</f>
-        <v>164993.341083333</v>
+        <v>165016.38275</v>
       </c>
       <c r="O55" s="27">
         <f>O47+O51-O53</f>
-        <v>38099.5621</v>
+        <v>41411.2421000001</v>
       </c>
       <c r="P55" s="26">
         <f>P47+P51-P53</f>
-        <v>64138.6684533333</v>
+        <v>68878.6684533333</v>
       </c>
       <c r="Q55" s="26">
         <f>Q47+Q51-Q53</f>
@@ -10874,23 +10910,23 @@
       </c>
       <c r="AB55" s="27">
         <f>AB47+AB51-AB53</f>
-        <v>1388664.01344</v>
+        <v>1393404.01344</v>
       </c>
       <c r="AC55" s="28">
         <f>AC47+AC51-AC53</f>
-        <v>3641403.6193904</v>
+        <v>3640402.6193904</v>
       </c>
       <c r="AD55" s="28">
         <f>AD47+AD51-AD53</f>
-        <v>9348207.19432603</v>
+        <v>9345703.39432603</v>
       </c>
       <c r="AE55" s="28">
         <f>AE47+AE51-AE53</f>
-        <v>25128282.577049</v>
+        <v>25123496.434649</v>
       </c>
       <c r="AF55" s="26">
         <f>AF47+AF51-AF53</f>
-        <v>39544656.9663054</v>
+        <v>39544417.7039054</v>
       </c>
     </row>
     <row r="56">
@@ -11010,19 +11046,19 @@
       </c>
       <c r="AC56" s="24">
         <f>'7_비용인력'!AC49</f>
-        <v>425938.742884688</v>
+        <v>427489.892484687</v>
       </c>
       <c r="AD56" s="24">
         <f>'7_비용인력'!AD49</f>
-        <v>2034605.58275173</v>
+        <v>2034054.74675173</v>
       </c>
       <c r="AE56" s="24">
         <f>'7_비용인력'!AE49</f>
-        <v>5619044.38364585</v>
+        <v>5617886.13718505</v>
       </c>
       <c r="AF56" s="25">
         <f>O56+AB56+AC56+AD56+AE56</f>
-        <v>8079588.70928227</v>
+        <v>8079430.77642147</v>
       </c>
     </row>
     <row r="57">
@@ -11033,59 +11069,59 @@
       </c>
       <c r="C57" s="38">
         <f>C55-C56</f>
-        <v>-17169.2060166667</v>
+        <v>-17146.16435</v>
       </c>
       <c r="D57" s="38">
         <f>D55-D56</f>
-        <v>-21757.9140166667</v>
+        <v>-21734.87235</v>
       </c>
       <c r="E57" s="38">
         <f>E55-E56</f>
-        <v>-14076.6762166667</v>
+        <v>-14053.63455</v>
       </c>
       <c r="F57" s="38">
         <f>F55-F56</f>
-        <v>-31624.0604166667</v>
+        <v>-31601.01875</v>
       </c>
       <c r="G57" s="38">
         <f>G55-G56</f>
-        <v>-27351.0816166667</v>
+        <v>-27328.03995</v>
       </c>
       <c r="H57" s="38">
         <f>H55-H56</f>
-        <v>-16424.2260166667</v>
+        <v>-16401.18435</v>
       </c>
       <c r="I57" s="38">
         <f>I55-I56</f>
-        <v>-30720.9138166667</v>
+        <v>-30697.87215</v>
       </c>
       <c r="J57" s="38">
         <f>J55-J56</f>
-        <v>-32750.5770166667</v>
+        <v>-32727.53535</v>
       </c>
       <c r="K57" s="38">
         <f>K55-K56</f>
-        <v>-19841.1480166667</v>
+        <v>-19818.10635</v>
       </c>
       <c r="L57" s="38">
         <f>L55-L56</f>
-        <v>39224.5025833333</v>
+        <v>31522.16925</v>
       </c>
       <c r="M57" s="38">
         <f>M55-M56</f>
-        <v>45597.5215833333</v>
+        <v>56381.11825</v>
       </c>
       <c r="N57" s="38">
         <f>N55-N56</f>
-        <v>164993.341083333</v>
+        <v>165016.38275</v>
       </c>
       <c r="O57" s="39">
         <f>O55-O56</f>
-        <v>38099.5621</v>
+        <v>41411.2421000001</v>
       </c>
       <c r="P57" s="38">
         <f>P55-P56</f>
-        <v>64138.6684533333</v>
+        <v>68878.6684533333</v>
       </c>
       <c r="Q57" s="38">
         <f>Q55-Q56</f>
@@ -11133,23 +11169,23 @@
       </c>
       <c r="AB57" s="39">
         <f>AB55-AB56</f>
-        <v>1388664.01344</v>
+        <v>1393404.01344</v>
       </c>
       <c r="AC57" s="40">
         <f>AC55-AC56</f>
-        <v>3215464.87650571</v>
+        <v>3212912.72690571</v>
       </c>
       <c r="AD57" s="40">
         <f>AD55-AD56</f>
-        <v>7313601.6115743</v>
+        <v>7311648.6475743</v>
       </c>
       <c r="AE57" s="40">
         <f>AE55-AE56</f>
-        <v>19509238.1934031</v>
+        <v>19505610.2974639</v>
       </c>
       <c r="AF57" s="38">
         <f>AF55-AF56</f>
-        <v>31465068.2570232</v>
+        <v>31464986.927484</v>
       </c>
     </row>
     <row r="58">
@@ -11160,59 +11196,59 @@
       </c>
       <c r="C58" s="14">
         <f>IFERROR(C57/C14,0)</f>
-        <v>-0.364782246938761</v>
+        <v>-0.364292696581469</v>
       </c>
       <c r="D58" s="14">
         <f>IFERROR(D57/D14,0)</f>
-        <v>-0.60204521352149</v>
+        <v>-0.601407646651909</v>
       </c>
       <c r="E58" s="14">
         <f>IFERROR(E57/E14,0)</f>
-        <v>-0.249347720563054</v>
+        <v>-0.248939571155277</v>
       </c>
       <c r="F58" s="14">
         <f>IFERROR(F57/F14,0)</f>
-        <v>-2.89200369608291</v>
+        <v>-2.88989654778235</v>
       </c>
       <c r="G58" s="14">
         <f>IFERROR(G57/G14,0)</f>
-        <v>-1.22557160983406</v>
+        <v>-1.22453913832504</v>
       </c>
       <c r="H58" s="14">
         <f>IFERROR(H57/H14,0)</f>
-        <v>-0.319208326369049</v>
+        <v>-0.318760506675995</v>
       </c>
       <c r="I58" s="14">
         <f>IFERROR(I57/I14,0)</f>
-        <v>-2.3074142869661</v>
+        <v>-2.30568365254619</v>
       </c>
       <c r="J58" s="14">
         <f>IFERROR(J57/J14,0)</f>
-        <v>-4.13204352973337</v>
+        <v>-4.12913643073429</v>
       </c>
       <c r="K58" s="14">
         <f>IFERROR(K57/K14,0)</f>
-        <v>-0.487150384656306</v>
+        <v>-0.486584653441037</v>
       </c>
       <c r="L58" s="14">
         <f>IFERROR(L57/L14,0)</f>
-        <v>0.194228782289345</v>
+        <v>0.17676808776111</v>
       </c>
       <c r="M58" s="14">
         <f>IFERROR(M57/M14,0)</f>
-        <v>0.214682650643063</v>
+        <v>0.231145942317153</v>
       </c>
       <c r="N58" s="14">
         <f>IFERROR(N57/N14,0)</f>
-        <v>0.334918694867282</v>
+        <v>0.334965466966549</v>
       </c>
       <c r="O58" s="30">
         <f>IFERROR(O57/O14,0)</f>
-        <v>0.0319274443421153</v>
+        <v>0.0344744056236301</v>
       </c>
       <c r="P58" s="14">
         <f>IFERROR(P57/P14,0)</f>
-        <v>0.102474306523939</v>
+        <v>0.106639833493317</v>
       </c>
       <c r="Q58" s="14">
         <f>IFERROR(Q57/Q14,0)</f>
@@ -11260,23 +11296,23 @@
       </c>
       <c r="AB58" s="30">
         <f>IFERROR(AB57/AB14,0)</f>
-        <v>0.124156356254917</v>
+        <v>0.124357776438669</v>
       </c>
       <c r="AC58" s="31">
         <f>IFERROR(AC57/AC14,0)</f>
-        <v>0.0974383295910822</v>
+        <v>0.0973609917244154</v>
       </c>
       <c r="AD58" s="31">
         <f>IFERROR(AD57/AD14,0)</f>
-        <v>0.10448002302249</v>
+        <v>0.104452123536776</v>
       </c>
       <c r="AE58" s="31">
         <f>IFERROR(AE57/AE14,0)</f>
-        <v>0.125059219188482</v>
+        <v>0.125035963445282</v>
       </c>
       <c r="AF58" s="14">
         <f>IFERROR(AF57/AF14,0)</f>
-        <v>0.115945488180328</v>
+        <v>0.115933269554167</v>
       </c>
     </row>
     <row r="59"/>
@@ -11331,11 +11367,11 @@
       </c>
       <c r="L61" s="44">
         <f>L47+L43</f>
-        <v>39126.414</v>
+        <v>31401.039</v>
       </c>
       <c r="M61" s="44">
         <f>M47+M43</f>
-        <v>45499.433</v>
+        <v>56259.988</v>
       </c>
       <c r="N61" s="44">
         <f>N47+N43</f>
@@ -11343,11 +11379,11 @@
       </c>
       <c r="O61" s="45">
         <f>O47+O43</f>
-        <v>36922.4991</v>
+        <v>39957.6791000001</v>
       </c>
       <c r="P61" s="44">
         <f>P47+P43</f>
-        <v>81868.08512</v>
+        <v>86608.08512</v>
       </c>
       <c r="Q61" s="44">
         <f>Q47+Q43</f>
@@ -11395,23 +11431,23 @@
       </c>
       <c r="AB61" s="45">
         <f>AB47+AB43</f>
-        <v>1601417.01344</v>
+        <v>1606157.01344</v>
       </c>
       <c r="AC61" s="46">
         <f>AC47+AC43</f>
-        <v>4261472.0227184</v>
+        <v>4260471.0227184</v>
       </c>
       <c r="AD61" s="46">
         <f>AD47+AD43</f>
-        <v>10322087.3820825</v>
+        <v>10319583.5820825</v>
       </c>
       <c r="AE61" s="46">
         <f>AE47+AE43</f>
-        <v>26436676.5106547</v>
+        <v>26431890.3682547</v>
       </c>
       <c r="AF61" s="44">
         <f>AF47+AF43</f>
-        <v>42658575.4279956</v>
+        <v>42658059.6655956</v>
       </c>
     </row>
     <row r="62">
@@ -11458,11 +11494,11 @@
       </c>
       <c r="L62" s="14">
         <f>IFERROR(L61/L14,0)</f>
-        <v>0.193743075018569</v>
+        <v>0.176088820972943</v>
       </c>
       <c r="M62" s="14">
         <f>IFERROR(M61/M14,0)</f>
-        <v>0.214220829115563</v>
+        <v>0.230649344047229</v>
       </c>
       <c r="N62" s="14">
         <f>IFERROR(N61/N14,0)</f>
@@ -11470,11 +11506,11 @@
       </c>
       <c r="O62" s="30">
         <f>IFERROR(O61/O14,0)</f>
-        <v>0.0309410651989371</v>
+        <v>0.0332643303416452</v>
       </c>
       <c r="P62" s="14">
         <f>IFERROR(P61/P14,0)</f>
-        <v>0.130800583351973</v>
+        <v>0.134089000030965</v>
       </c>
       <c r="Q62" s="14">
         <f>IFERROR(Q61/Q14,0)</f>
@@ -11522,23 +11558,23 @@
       </c>
       <c r="AB62" s="30">
         <f>IFERROR(AB61/AB14,0)</f>
-        <v>0.143177974880195</v>
+        <v>0.143345442438955</v>
       </c>
       <c r="AC62" s="31">
         <f>IFERROR(AC61/AC14,0)</f>
-        <v>0.129135515839952</v>
+        <v>0.129105182506618</v>
       </c>
       <c r="AD62" s="31">
         <f>IFERROR(AD61/AD14,0)</f>
-        <v>0.147458391172607</v>
+        <v>0.147422622601179</v>
       </c>
       <c r="AE62" s="31">
         <f>IFERROR(AE61/AE14,0)</f>
-        <v>0.169465875068299</v>
+        <v>0.169435194668299</v>
       </c>
       <c r="AF62" s="14">
         <f>IFERROR(AF61/AF14,0)</f>
-        <v>0.157192392295933</v>
+        <v>0.157174332894748</v>
       </c>
     </row>
     <row r="63">
@@ -11672,21 +11708,21 @@
     <row r="64">
       <c r="A64" s="15" t="inlineStr">
         <is>
-          <t>인당 매출(백만원, 연환산)</t>
+          <t>인당 매출(백만원, 평균 인원 기준)</t>
         </is>
       </c>
       <c r="B64" s="29" t="inlineStr">
         <is>
-          <t>매출 ÷ 평균 인원</t>
+          <t>연 매출 ÷ 평균 인원</t>
         </is>
       </c>
       <c r="O64" s="47">
         <f>IFERROR(O14/1000/'7_비용인력'!O15,0)</f>
-        <v>170.473857142857</v>
+        <v>171.602428571429</v>
       </c>
       <c r="AB64" s="47">
         <f>IFERROR(AB14/1000/'7_비용인력'!AB15,0)</f>
-        <v>798.914285714286</v>
+        <v>800.342857142857</v>
       </c>
       <c r="AC64" s="48">
         <f>IFERROR(AC14/1000/'7_비용인력'!AC15,0)</f>
@@ -11754,7 +11790,7 @@
       </c>
       <c r="M65" s="18">
         <f>'5_매출_제품지역'!M58</f>
-        <v>2083.95</v>
+        <v>2162.95</v>
       </c>
       <c r="N65" s="18">
         <f>'5_매출_제품지역'!N58</f>
@@ -11762,11 +11798,11 @@
       </c>
       <c r="O65" s="49">
         <f>'5_매출_제품지역'!AA58</f>
-        <v>928.102875</v>
+        <v>934.686208333333</v>
       </c>
       <c r="P65" s="18">
         <f>'5_매출_제품지역'!O58</f>
-        <v>6063.73</v>
+        <v>6263.73</v>
       </c>
       <c r="Q65" s="18">
         <f>'5_매출_제품지역'!P58</f>
@@ -11814,19 +11850,19 @@
       </c>
       <c r="AB65" s="49">
         <f>'5_매출_제품지역'!AB58</f>
-        <v>8795.97166666667</v>
+        <v>8812.63833333333</v>
       </c>
       <c r="AC65" s="24">
         <f>'5_매출_제품지역'!AC58</f>
-        <v>25104.4494666667</v>
+        <v>25109.6494666667</v>
       </c>
       <c r="AD65" s="24">
         <f>'5_매출_제품지역'!AD58</f>
-        <v>50397.0821066667</v>
+        <v>50410.3421066667</v>
       </c>
       <c r="AE65" s="24">
         <f>'5_매출_제품지역'!AE58</f>
-        <v>105961.8822208</v>
+        <v>105986.1246208</v>
       </c>
     </row>
     <row r="66">
@@ -11873,11 +11909,11 @@
       </c>
       <c r="O67" s="50">
         <f>IFERROR(O14/O66,0)</f>
-        <v>0.994430833333333</v>
+        <v>1.00101416666667</v>
       </c>
       <c r="AB67" s="50">
         <f>IFERROR(AB14/AB66,0)</f>
-        <v>1.11792103948026</v>
+        <v>1.11992003998001</v>
       </c>
       <c r="AC67" s="51">
         <f>IFERROR(AC14/AC66,0)</f>
@@ -11893,7 +11929,7 @@
       </c>
       <c r="AF67" s="52">
         <f>IFERROR(AF14/AF66,0)</f>
-        <v>1.00434158139191</v>
+        <v>1.00444483632797</v>
       </c>
     </row>
     <row r="68"/>
@@ -11915,6 +11951,20 @@
       <c r="A71" s="53" t="inlineStr">
         <is>
           <t>※ 매출원가는 제품별 원가율 + 운영성 원가, 판관비는 인원·변동비율·고정비로 산출(7_비용인력·8_가정).</t>
+        </is>
+      </c>
+    </row>
+    <row r="72">
+      <c r="A72" s="53" t="inlineStr">
+        <is>
+          <t>※ 천원 미만 단수 처리로 표시된 항목 합계와 소계·이익이 ±1천원 차이날 수 있습니다(내부 계산값은 정확히 일치).</t>
+        </is>
+      </c>
+    </row>
+    <row r="73">
+      <c r="A73" s="53" t="inlineStr">
+        <is>
+          <t>※ 신제품(P4·P5) 매출은 연 단위 제품 믹스로 배분되어, 출시 분기 이전 월에도 사전 예약·PoC 물량이 배분됩니다.</t>
         </is>
       </c>
     </row>
@@ -11931,7 +11981,7 @@
     <outlinePr summaryBelow="1" summaryRight="1"/>
     <pageSetUpPr fitToPage="1"/>
   </sheetPr>
-  <dimension ref="A1:I73"/>
+  <dimension ref="A1:I75"/>
   <sheetFormatPr baseColWidth="8" defaultRowHeight="15"/>
   <cols>
     <col width="40" customWidth="1" min="1" max="1"/>
@@ -12061,11 +12111,11 @@
       </c>
       <c r="D7" s="37">
         <f>'2_손익계산서'!O14</f>
-        <v>1193317</v>
+        <v>1201217</v>
       </c>
       <c r="E7" s="37">
         <f>'2_손익계산서'!AB14</f>
-        <v>11184800</v>
+        <v>11204800</v>
       </c>
       <c r="F7" s="37">
         <f>'2_손익계산서'!AC14</f>
@@ -12096,15 +12146,15 @@
       </c>
       <c r="D8" s="14">
         <f>IFERROR(D7/C7-1,0)</f>
-        <v>0.397059897077665</v>
+        <v>0.40630871628238</v>
       </c>
       <c r="E8" s="14">
         <f>IFERROR(E7/D7-1,0)</f>
-        <v>8.37286571799447</v>
+        <v>8.32787331514622</v>
       </c>
       <c r="F8" s="14">
         <f>IFERROR(F7/E7-1,0)</f>
-        <v>1.95043273013375</v>
+        <v>1.94516635727545</v>
       </c>
       <c r="G8" s="14">
         <f>IFERROR(G7/F7-1,0)</f>
@@ -12129,23 +12179,23 @@
       </c>
       <c r="D9" s="18">
         <f>'2_손익계산서'!O30</f>
-        <v>597589.4329</v>
+        <v>601601.0529</v>
       </c>
       <c r="E9" s="18">
         <f>'2_손익계산서'!AB30</f>
-        <v>6739354.92</v>
+        <v>6751614.92</v>
       </c>
       <c r="F9" s="18">
         <f>'2_손익계산서'!AC30</f>
-        <v>19922997.678</v>
+        <v>19923998.678</v>
       </c>
       <c r="G9" s="18">
         <f>'2_손익계산서'!AD30</f>
-        <v>42059106.76224</v>
+        <v>42061610.56224</v>
       </c>
       <c r="H9" s="18">
         <f>'2_손익계산서'!AE30</f>
-        <v>92221122.0590304</v>
+        <v>92225908.2014304</v>
       </c>
     </row>
     <row r="10">
@@ -12164,27 +12214,27 @@
       </c>
       <c r="D10" s="34">
         <f>D7-D9</f>
-        <v>595727.5671</v>
+        <v>599615.9471</v>
       </c>
       <c r="E10" s="34">
         <f>E7-E9</f>
-        <v>4445445.08</v>
+        <v>4453185.08</v>
       </c>
       <c r="F10" s="34">
         <f>F7-F9</f>
-        <v>13077002.322</v>
+        <v>13076001.322</v>
       </c>
       <c r="G10" s="34">
         <f>G7-G9</f>
-        <v>27940893.23776</v>
+        <v>27938389.43776</v>
       </c>
       <c r="H10" s="34">
         <f>H7-H9</f>
-        <v>63778877.9409696</v>
+        <v>63774091.7985696</v>
       </c>
       <c r="I10" s="14">
         <f>IFERROR((H10/C10)^(1/5)-1,"n/a")</f>
-        <v>1.68925690761821</v>
+        <v>1.68921654455979</v>
       </c>
     </row>
     <row r="11">
@@ -12203,23 +12253,23 @@
       </c>
       <c r="D11" s="14">
         <f>IFERROR(D10/D7,0)</f>
-        <v>0.499219877953637</v>
+        <v>0.499173710578522</v>
       </c>
       <c r="E11" s="14">
         <f>IFERROR(E10/E7,0)</f>
-        <v>0.397454141334669</v>
+        <v>0.397435481222333</v>
       </c>
       <c r="F11" s="14">
         <f>IFERROR(F10/F7,0)</f>
-        <v>0.396272797636364</v>
+        <v>0.39624246430303</v>
       </c>
       <c r="G11" s="14">
         <f>IFERROR(G10/G7,0)</f>
-        <v>0.399155617682286</v>
+        <v>0.399119849110857</v>
       </c>
       <c r="H11" s="14">
         <f>IFERROR(H10/H7,0)</f>
-        <v>0.408838961160062</v>
+        <v>0.408808280760062</v>
       </c>
     </row>
     <row r="12">
@@ -12236,11 +12286,11 @@
       </c>
       <c r="D12" s="18">
         <f>'2_손익계산서'!O46</f>
-        <v>576805.068</v>
+        <v>577658.268</v>
       </c>
       <c r="E12" s="18">
         <f>'2_손익계산서'!AB46</f>
-        <v>3279981.06656</v>
+        <v>3282981.06656</v>
       </c>
       <c r="F12" s="18">
         <f>'2_손익계산서'!AC46</f>
@@ -12271,27 +12321,27 @@
       </c>
       <c r="D13" s="38">
         <f>D10-D12</f>
-        <v>18922.4991</v>
+        <v>21957.6791000001</v>
       </c>
       <c r="E13" s="38">
         <f>E10-E12</f>
-        <v>1165464.01344</v>
+        <v>1170204.01344</v>
       </c>
       <c r="F13" s="38">
         <f>F10-F12</f>
-        <v>3733403.6193904</v>
+        <v>3732402.6193904</v>
       </c>
       <c r="G13" s="38">
         <f>G10-G12</f>
-        <v>9632207.19432603</v>
+        <v>9629703.39432603</v>
       </c>
       <c r="H13" s="38">
         <f>H10-H12</f>
-        <v>25556282.577049</v>
+        <v>25551496.434649</v>
       </c>
       <c r="I13" s="14">
         <f>IFERROR((H13/C13)^(1/5)-1,"n/a")</f>
-        <v>2.94353972434384</v>
+        <v>2.94339200523261</v>
       </c>
     </row>
     <row r="14">
@@ -12310,23 +12360,23 @@
       </c>
       <c r="D14" s="14">
         <f>IFERROR(D13/D7,0)</f>
-        <v>0.0158570598591992</v>
+        <v>0.0182795274292655</v>
       </c>
       <c r="E14" s="14">
         <f>IFERROR(E13/E7,0)</f>
-        <v>0.104200702152922</v>
+        <v>0.104437742167642</v>
       </c>
       <c r="F14" s="14">
         <f>IFERROR(F13/F7,0)</f>
-        <v>0.11313344301183</v>
+        <v>0.113103109678497</v>
       </c>
       <c r="G14" s="14">
         <f>IFERROR(G13/G7,0)</f>
-        <v>0.137602959918943</v>
+        <v>0.137567191347515</v>
       </c>
       <c r="H14" s="14">
         <f>IFERROR(H13/H7,0)</f>
-        <v>0.163822324211852</v>
+        <v>0.163791643811852</v>
       </c>
     </row>
     <row r="15">
@@ -12343,7 +12393,7 @@
       </c>
       <c r="D15" s="18">
         <f>'2_손익계산서'!O51</f>
-        <v>76766.095</v>
+        <v>77042.595</v>
       </c>
       <c r="E15" s="18">
         <f>'2_손익계산서'!AB51</f>
@@ -12376,7 +12426,7 @@
       </c>
       <c r="D16" s="41">
         <f>'2_손익계산서'!O52</f>
-        <v>76766.095</v>
+        <v>77042.595</v>
       </c>
       <c r="E16" s="41">
         <f>'2_손익계산서'!AB52</f>
@@ -12477,23 +12527,23 @@
       </c>
       <c r="D19" s="25">
         <f>D13+D15-D17</f>
-        <v>38099.5621</v>
+        <v>41411.2421000001</v>
       </c>
       <c r="E19" s="25">
         <f>E13+E15-E17</f>
-        <v>1388664.01344</v>
+        <v>1393404.01344</v>
       </c>
       <c r="F19" s="25">
         <f>F13+F15-F17</f>
-        <v>3641403.6193904</v>
+        <v>3640402.6193904</v>
       </c>
       <c r="G19" s="25">
         <f>G13+G15-G17</f>
-        <v>9348207.19432603</v>
+        <v>9345703.39432603</v>
       </c>
       <c r="H19" s="25">
         <f>H13+H15-H17</f>
-        <v>25128282.577049</v>
+        <v>25123496.434649</v>
       </c>
     </row>
     <row r="20">
@@ -12518,15 +12568,15 @@
       </c>
       <c r="F20" s="18">
         <f>'2_손익계산서'!AC56</f>
-        <v>425938.742884688</v>
+        <v>427489.892484687</v>
       </c>
       <c r="G20" s="18">
         <f>'2_손익계산서'!AD56</f>
-        <v>2034605.58275173</v>
+        <v>2034054.74675173</v>
       </c>
       <c r="H20" s="18">
         <f>'2_손익계산서'!AE56</f>
-        <v>5619044.38364585</v>
+        <v>5617886.13718505</v>
       </c>
     </row>
     <row r="21">
@@ -12545,27 +12595,27 @@
       </c>
       <c r="D21" s="38">
         <f>D19-D20</f>
-        <v>38099.5621</v>
+        <v>41411.2421000001</v>
       </c>
       <c r="E21" s="38">
         <f>E19-E20</f>
-        <v>1388664.01344</v>
+        <v>1393404.01344</v>
       </c>
       <c r="F21" s="38">
         <f>F19-F20</f>
-        <v>3215464.87650571</v>
+        <v>3212912.72690571</v>
       </c>
       <c r="G21" s="38">
         <f>G19-G20</f>
-        <v>7313601.6115743</v>
+        <v>7311648.6475743</v>
       </c>
       <c r="H21" s="38">
         <f>H19-H20</f>
-        <v>19509238.1934031</v>
+        <v>19505610.2974639</v>
       </c>
       <c r="I21" s="14">
         <f>IFERROR((H21/C21)^(1/5)-1,"n/a")</f>
-        <v>4.19274815470237</v>
+        <v>4.19255501388161</v>
       </c>
     </row>
     <row r="22">
@@ -12584,23 +12634,23 @@
       </c>
       <c r="D22" s="14">
         <f>IFERROR(D21/D7,0)</f>
-        <v>0.0319274443421153</v>
+        <v>0.0344744056236301</v>
       </c>
       <c r="E22" s="14">
         <f>IFERROR(E21/E7,0)</f>
-        <v>0.124156356254917</v>
+        <v>0.124357776438669</v>
       </c>
       <c r="F22" s="14">
         <f>IFERROR(F21/F7,0)</f>
-        <v>0.0974383295910822</v>
+        <v>0.0973609917244154</v>
       </c>
       <c r="G22" s="14">
         <f>IFERROR(G21/G7,0)</f>
-        <v>0.10448002302249</v>
+        <v>0.104452123536776</v>
       </c>
       <c r="H22" s="14">
         <f>IFERROR(H21/H7,0)</f>
-        <v>0.125059219188482</v>
+        <v>0.125035963445282</v>
       </c>
     </row>
     <row r="23">
@@ -12611,23 +12661,23 @@
       </c>
       <c r="D23" s="18">
         <f>'2_손익계산서'!O61</f>
-        <v>36922.4991</v>
+        <v>39957.6791000001</v>
       </c>
       <c r="E23" s="18">
         <f>'2_손익계산서'!AB61</f>
-        <v>1601417.01344</v>
+        <v>1606157.01344</v>
       </c>
       <c r="F23" s="18">
         <f>'2_손익계산서'!AC61</f>
-        <v>4261472.0227184</v>
+        <v>4260471.0227184</v>
       </c>
       <c r="G23" s="18">
         <f>'2_손익계산서'!AD61</f>
-        <v>10322087.3820825</v>
+        <v>10319583.5820825</v>
       </c>
       <c r="H23" s="18">
         <f>'2_손익계산서'!AE61</f>
-        <v>26436676.5106547</v>
+        <v>26431890.3682547</v>
       </c>
     </row>
     <row r="24">
@@ -12660,16 +12710,16 @@
     <row r="25">
       <c r="A25" s="15" t="inlineStr">
         <is>
-          <t>인당 매출(백만원)</t>
+          <t>인당 매출(백만원, 평균 인원 기준)</t>
         </is>
       </c>
       <c r="D25" s="17">
         <f>'2_손익계산서'!O64</f>
-        <v>170.473857142857</v>
+        <v>171.602428571429</v>
       </c>
       <c r="E25" s="17">
         <f>'2_손익계산서'!AB64</f>
-        <v>798.914285714286</v>
+        <v>800.342857142857</v>
       </c>
       <c r="F25" s="17">
         <f>'2_손익계산서'!AC64</f>
@@ -12692,23 +12742,23 @@
       </c>
       <c r="D26" s="18">
         <f>'2_손익계산서'!O65</f>
-        <v>928.102875</v>
+        <v>934.686208333333</v>
       </c>
       <c r="E26" s="18">
         <f>'2_손익계산서'!AB65</f>
-        <v>8795.97166666667</v>
+        <v>8812.63833333333</v>
       </c>
       <c r="F26" s="18">
         <f>'2_손익계산서'!AC65</f>
-        <v>25104.4494666667</v>
+        <v>25109.6494666667</v>
       </c>
       <c r="G26" s="18">
         <f>'2_손익계산서'!AD65</f>
-        <v>50397.0821066667</v>
+        <v>50410.3421066667</v>
       </c>
       <c r="H26" s="18">
         <f>'2_손익계산서'!AE65</f>
-        <v>105961.8822208</v>
+        <v>105986.1246208</v>
       </c>
     </row>
     <row r="27">
@@ -12746,11 +12796,11 @@
       </c>
       <c r="D28" s="58">
         <f>IFERROR(D7/D27,0)</f>
-        <v>0.994430833333333</v>
+        <v>1.00101416666667</v>
       </c>
       <c r="E28" s="58">
         <f>IFERROR(E7/E27,0)</f>
-        <v>1.11792103948026</v>
+        <v>1.11992003998001</v>
       </c>
       <c r="F28" s="58">
         <f>IFERROR(F7/F27,0)</f>
@@ -12834,23 +12884,23 @@
       </c>
       <c r="D32" s="18">
         <f>'5_매출_제품지역'!AA9</f>
-        <v>732707.42</v>
+        <v>739027.42</v>
       </c>
       <c r="E32" s="18">
         <f>'5_매출_제품지역'!AB9</f>
-        <v>7885234</v>
+        <v>7902234</v>
       </c>
       <c r="F32" s="18">
         <f>'5_매출_제품지역'!AC9</f>
-        <v>22277306.48</v>
+        <v>22287186.48</v>
       </c>
       <c r="G32" s="18">
         <f>'5_매출_제품지역'!AD9</f>
-        <v>43851045.44</v>
+        <v>43874445.44</v>
       </c>
       <c r="H32" s="18">
         <f>'5_매출_제품지역'!AE9</f>
-        <v>90699925.96032</v>
+        <v>90740099.08032</v>
       </c>
     </row>
     <row r="33">
@@ -12861,23 +12911,23 @@
       </c>
       <c r="D33" s="18">
         <f>'5_매출_제품지역'!AA10</f>
-        <v>246338.51</v>
+        <v>246970.51</v>
       </c>
       <c r="E33" s="18">
         <f>'5_매출_제품지역'!AB10</f>
-        <v>1485374</v>
+        <v>1486374</v>
       </c>
       <c r="F33" s="18">
         <f>'5_매출_제품지역'!AC10</f>
-        <v>4063924.88</v>
+        <v>4061324.88</v>
       </c>
       <c r="G33" s="18">
         <f>'5_매출_제품지역'!AD10</f>
-        <v>8515908.288</v>
+        <v>8510292.288</v>
       </c>
       <c r="H33" s="18">
         <f>'5_매출_제품지역'!AE10</f>
-        <v>18135247.10464</v>
+        <v>18126935.42464</v>
       </c>
     </row>
     <row r="34">
@@ -12888,23 +12938,23 @@
       </c>
       <c r="D34" s="18">
         <f>'5_매출_제품지역'!AA11</f>
-        <v>134677.52</v>
+        <v>135625.52</v>
       </c>
       <c r="E34" s="18">
         <f>'5_매출_제품지역'!AB11</f>
-        <v>1184558</v>
+        <v>1186558</v>
       </c>
       <c r="F34" s="18">
         <f>'5_매출_제품지역'!AC11</f>
-        <v>3784108</v>
+        <v>3783068</v>
       </c>
       <c r="G34" s="18">
         <f>'5_매출_제품지역'!AD11</f>
-        <v>8109544.8</v>
+        <v>8107672.8</v>
       </c>
       <c r="H34" s="18">
         <f>'5_매출_제품지역'!AE11</f>
-        <v>18319085.6</v>
+        <v>18316315.04</v>
       </c>
     </row>
     <row r="35">
@@ -12923,21 +12973,21 @@
       </c>
       <c r="F35" s="18">
         <f>'5_매출_제품지역'!AC12</f>
-        <v>1722542.32</v>
+        <v>1718382.32</v>
       </c>
       <c r="G35" s="18">
         <f>'5_매출_제품지역'!AD12</f>
-        <v>5791768.384</v>
+        <v>5781472.384</v>
       </c>
       <c r="H35" s="18">
         <f>'5_매출_제품지역'!AE12</f>
-        <v>17506869.35552</v>
+        <v>17488860.71552</v>
       </c>
     </row>
     <row r="36">
       <c r="A36" s="15" t="inlineStr">
         <is>
-          <t>스마트 욕창 케어(2027 Q4 출시)</t>
+          <t>스마트 욕창 케어(2027 출시)</t>
         </is>
       </c>
       <c r="D36" s="18">
@@ -12950,15 +13000,15 @@
       </c>
       <c r="F36" s="18">
         <f>'5_매출_제품지역'!AC13</f>
-        <v>401283.44</v>
+        <v>400243.44</v>
       </c>
       <c r="G36" s="18">
         <f>'5_매출_제품지역'!AD13</f>
-        <v>2245576.096</v>
+        <v>2241832.096</v>
       </c>
       <c r="H36" s="18">
         <f>'5_매출_제품지역'!AE13</f>
-        <v>8173068.94976</v>
+        <v>8164757.26976</v>
       </c>
     </row>
     <row r="37">
@@ -12977,15 +13027,15 @@
       </c>
       <c r="F37" s="18">
         <f>'5_매출_제품지역'!AC14</f>
-        <v>750834.88</v>
+        <v>749794.88</v>
       </c>
       <c r="G37" s="18">
         <f>'5_매출_제품지역'!AD14</f>
-        <v>1486156.992</v>
+        <v>1484284.992</v>
       </c>
       <c r="H37" s="18">
         <f>'5_매출_제품지역'!AE14</f>
-        <v>3165803.02976</v>
+        <v>3163032.46976</v>
       </c>
     </row>
     <row r="38">
@@ -12996,11 +13046,11 @@
       </c>
       <c r="D38" s="26">
         <f>SUM(D32:D37)</f>
-        <v>1193317</v>
+        <v>1201217</v>
       </c>
       <c r="E38" s="26">
         <f>SUM(E32:E37)</f>
-        <v>11184800</v>
+        <v>11204800</v>
       </c>
       <c r="F38" s="26">
         <f>SUM(F32:F37)</f>
@@ -13035,19 +13085,19 @@
       </c>
       <c r="E41" s="18">
         <f>'5_매출_제품지역'!AB18</f>
-        <v>2451000</v>
+        <v>2471000</v>
       </c>
       <c r="F41" s="18">
         <f>'5_매출_제품지역'!AC18</f>
-        <v>4175400</v>
+        <v>4227400</v>
       </c>
       <c r="G41" s="18">
         <f>'5_매출_제품지역'!AD18</f>
-        <v>5800080</v>
+        <v>5893680</v>
       </c>
       <c r="H41" s="18">
         <f>'5_매출_제품지역'!AE18</f>
-        <v>7340985.6</v>
+        <v>7479513.6</v>
       </c>
     </row>
     <row r="42">
@@ -13058,7 +13108,7 @@
       </c>
       <c r="D42" s="18">
         <f>'5_매출_제품지역'!AA19</f>
-        <v>958774</v>
+        <v>966674</v>
       </c>
       <c r="E42" s="18">
         <f>'5_매출_제품지역'!AB19</f>
@@ -13066,15 +13116,15 @@
       </c>
       <c r="F42" s="18">
         <f>'5_매출_제품지역'!AC19</f>
-        <v>28824600</v>
+        <v>28772600</v>
       </c>
       <c r="G42" s="18">
         <f>'5_매출_제품지역'!AD19</f>
-        <v>64199920</v>
+        <v>64106320</v>
       </c>
       <c r="H42" s="18">
         <f>'5_매출_제품지역'!AE19</f>
-        <v>148659014.4</v>
+        <v>148520486.4</v>
       </c>
     </row>
     <row r="43">
@@ -13085,11 +13135,11 @@
       </c>
       <c r="D43" s="26">
         <f>SUM(D41:D42)</f>
-        <v>1193317</v>
+        <v>1201217</v>
       </c>
       <c r="E43" s="26">
         <f>SUM(E41:E42)</f>
-        <v>11184800</v>
+        <v>11204800</v>
       </c>
       <c r="F43" s="26">
         <f>SUM(F41:F42)</f>
@@ -13120,7 +13170,7 @@
       </c>
       <c r="D46" s="18">
         <f>'5_매출_제품지역'!AA24</f>
-        <v>649167</v>
+        <v>657067</v>
       </c>
       <c r="E46" s="18">
         <f>'5_매출_제품지역'!AB24</f>
@@ -13178,19 +13228,19 @@
       </c>
       <c r="E48" s="18">
         <f>'5_매출_제품지역'!AB26</f>
-        <v>1810000</v>
+        <v>1830000</v>
       </c>
       <c r="F48" s="18">
         <f>'5_매출_제품지역'!AC26</f>
-        <v>5562000</v>
+        <v>5614000</v>
       </c>
       <c r="G48" s="18">
         <f>'5_매출_제품지역'!AD26</f>
-        <v>11884800</v>
+        <v>11978400</v>
       </c>
       <c r="H48" s="18">
         <f>'5_매출_제품지역'!AE26</f>
-        <v>25340672</v>
+        <v>25479200</v>
       </c>
     </row>
     <row r="49">
@@ -13290,15 +13340,15 @@
       </c>
       <c r="F52" s="18">
         <f>'5_매출_제품지역'!AC30</f>
-        <v>4641744</v>
+        <v>4589744</v>
       </c>
       <c r="G52" s="18">
         <f>'5_매출_제품지역'!AD30</f>
-        <v>10147849.6</v>
+        <v>10054249.6</v>
       </c>
       <c r="H52" s="18">
         <f>'5_매출_제품지역'!AE30</f>
-        <v>23110951.488</v>
+        <v>22972423.488</v>
       </c>
     </row>
     <row r="53">
@@ -13309,11 +13359,11 @@
       </c>
       <c r="D53" s="26">
         <f>SUM(D46:D52)</f>
-        <v>1193317</v>
+        <v>1201217</v>
       </c>
       <c r="E53" s="26">
         <f>SUM(E46:E52)</f>
-        <v>11184800</v>
+        <v>11204800</v>
       </c>
       <c r="F53" s="26">
         <f>SUM(F46:F52)</f>
@@ -13371,7 +13421,7 @@
       </c>
       <c r="D57" s="18">
         <f>'5_매출_제품지역'!AA36</f>
-        <v>6921</v>
+        <v>14821</v>
       </c>
       <c r="E57" s="18">
         <f>'5_매출_제품지역'!AB36</f>
@@ -13402,19 +13452,19 @@
       </c>
       <c r="E58" s="18">
         <f>'5_매출_제품지역'!AB37</f>
-        <v>4928000</v>
+        <v>4948000</v>
       </c>
       <c r="F58" s="18">
         <f>'5_매출_제품지역'!AC37</f>
-        <v>12388320</v>
+        <v>12440320</v>
       </c>
       <c r="G58" s="18">
         <f>'5_매출_제품지역'!AD37</f>
-        <v>22015784</v>
+        <v>22109384</v>
       </c>
       <c r="H58" s="18">
         <f>'5_매출_제품지역'!AE37</f>
-        <v>31724952</v>
+        <v>31863480</v>
       </c>
     </row>
     <row r="59">
@@ -13460,15 +13510,15 @@
       </c>
       <c r="F60" s="18">
         <f>'5_매출_제품지역'!AC39</f>
-        <v>8971344</v>
+        <v>8919344</v>
       </c>
       <c r="G60" s="18">
         <f>'5_매출_제품지역'!AD39</f>
-        <v>15776329.6</v>
+        <v>15682729.6</v>
       </c>
       <c r="H60" s="18">
         <f>'5_매출_제품지역'!AE39</f>
-        <v>29865127.488</v>
+        <v>29726599.488</v>
       </c>
     </row>
     <row r="61">
@@ -13560,11 +13610,11 @@
       </c>
       <c r="D64" s="26">
         <f>SUM(D56:D63)</f>
-        <v>1193317</v>
+        <v>1201217</v>
       </c>
       <c r="E64" s="26">
         <f>SUM(E56:E63)</f>
-        <v>11184800</v>
+        <v>11204800</v>
       </c>
       <c r="F64" s="26">
         <f>SUM(F56:F63)</f>
@@ -13595,23 +13645,23 @@
       </c>
       <c r="D67" s="18">
         <f>'5_매출_제품지역'!AA47</f>
-        <v>855365</v>
+        <v>863265</v>
       </c>
       <c r="E67" s="18">
         <f>'5_매출_제품지역'!AB47</f>
-        <v>5696800</v>
+        <v>5716800</v>
       </c>
       <c r="F67" s="18">
         <f>'5_매출_제품지역'!AC47</f>
-        <v>9981136</v>
+        <v>10033136</v>
       </c>
       <c r="G67" s="18">
         <f>'5_매출_제품지역'!AD47</f>
-        <v>14328846.4</v>
+        <v>14422446.4</v>
       </c>
       <c r="H67" s="18">
         <f>'5_매출_제품지역'!AE47</f>
-        <v>18560422.912</v>
+        <v>18698950.912</v>
       </c>
     </row>
     <row r="68">
@@ -13657,15 +13707,15 @@
       </c>
       <c r="F69" s="18">
         <f>'5_매출_제품지역'!AC49</f>
-        <v>11841744</v>
+        <v>11789744</v>
       </c>
       <c r="G69" s="18">
         <f>'5_매출_제품지역'!AD49</f>
-        <v>35947849.6</v>
+        <v>35854249.6</v>
       </c>
       <c r="H69" s="18">
         <f>'5_매출_제품지역'!AE49</f>
-        <v>109110951.488</v>
+        <v>108972423.488</v>
       </c>
     </row>
     <row r="70">
@@ -13676,11 +13726,11 @@
       </c>
       <c r="D70" s="26">
         <f>SUM(D67:D69)</f>
-        <v>1193317</v>
+        <v>1201217</v>
       </c>
       <c r="E70" s="26">
         <f>SUM(E67:E69)</f>
-        <v>11184800</v>
+        <v>11204800</v>
       </c>
       <c r="F70" s="26">
         <f>SUM(F67:F69)</f>
@@ -13703,23 +13753,23 @@
       </c>
       <c r="D71" s="14">
         <f>IFERROR(D67/D70,0)</f>
-        <v>0.716796123745828</v>
+        <v>0.71865866034197</v>
       </c>
       <c r="E71" s="14">
         <f>IFERROR(E67/E70,0)</f>
-        <v>0.509334096273514</v>
+        <v>0.510209910038555</v>
       </c>
       <c r="F71" s="14">
         <f>IFERROR(F67/F70,0)</f>
-        <v>0.302458666666667</v>
+        <v>0.304034424242424</v>
       </c>
       <c r="G71" s="14">
         <f>IFERROR(G67/G70,0)</f>
-        <v>0.204697805714286</v>
+        <v>0.206034948571429</v>
       </c>
       <c r="H71" s="14">
         <f>IFERROR(H67/H70,0)</f>
-        <v>0.118977069948718</v>
+        <v>0.119865069948718</v>
       </c>
     </row>
     <row r="72">
@@ -13730,11 +13780,11 @@
       </c>
       <c r="D72" s="14">
         <f>IFERROR(D68/D70,0)</f>
-        <v>0.283203876254172</v>
+        <v>0.28134133965803</v>
       </c>
       <c r="E72" s="14">
         <f>IFERROR(E68/E70,0)</f>
-        <v>0.40125885129819</v>
+        <v>0.400542624589462</v>
       </c>
       <c r="F72" s="14">
         <f>IFERROR(F68/F70,0)</f>
@@ -13761,19 +13811,27 @@
       </c>
       <c r="E73" s="14">
         <f>IFERROR(E69/E70,0)</f>
-        <v>0.0894070524282955</v>
+        <v>0.0892474653719834</v>
       </c>
       <c r="F73" s="14">
         <f>IFERROR(F69/F70,0)</f>
-        <v>0.358840727272727</v>
+        <v>0.35726496969697</v>
       </c>
       <c r="G73" s="14">
         <f>IFERROR(G69/G70,0)</f>
-        <v>0.513540708571429</v>
+        <v>0.512203565714286</v>
       </c>
       <c r="H73" s="14">
         <f>IFERROR(H69/H70,0)</f>
-        <v>0.699429176205128</v>
+        <v>0.698541176205128</v>
+      </c>
+    </row>
+    <row r="74"/>
+    <row r="75">
+      <c r="A75" s="2" t="inlineStr">
+        <is>
+          <t>※ 천원 미만 단수 처리로 항목 합계와 소계·이익이 ±1천원 차이날 수 있습니다(내부 계산값은 정확히 일치).</t>
+        </is>
       </c>
     </row>
   </sheetData>
@@ -13789,7 +13847,7 @@
     <outlinePr summaryBelow="1" summaryRight="1"/>
     <pageSetUpPr fitToPage="1"/>
   </sheetPr>
-  <dimension ref="A1:BA95"/>
+  <dimension ref="A1:BA96"/>
   <sheetFormatPr baseColWidth="8" defaultRowHeight="15"/>
   <cols>
     <col width="4" customWidth="1" min="1" max="1"/>
@@ -13797,7 +13855,16 @@
     <col width="11" customWidth="1" min="3" max="3"/>
     <col width="40" customWidth="1" min="4" max="4"/>
     <col width="8" customWidth="1" min="5" max="5"/>
-    <col hidden="1" outlineLevel="1" width="10" customWidth="1" min="6" max="22"/>
+    <col width="10" customWidth="1" min="6" max="6"/>
+    <col width="8" customWidth="1" min="7" max="7"/>
+    <col width="20" customWidth="1" min="8" max="8"/>
+    <col width="7" customWidth="1" min="9" max="9"/>
+    <col width="6" customWidth="1" min="10" max="10"/>
+    <col width="11" customWidth="1" min="11" max="11"/>
+    <col width="8" customWidth="1" min="12" max="12"/>
+    <col width="8" customWidth="1" min="13" max="13"/>
+    <col width="8" customWidth="1" min="14" max="14"/>
+    <col hidden="1" outlineLevel="1" width="1" customWidth="1" min="15" max="22"/>
     <col width="1" customWidth="1" min="23" max="23"/>
     <col outlineLevel="1" width="10.5" customWidth="1" min="24" max="47"/>
     <col width="10.5" customWidth="1" min="48" max="48"/>
@@ -13818,7 +13885,7 @@
     <row r="2">
       <c r="A2" s="2" t="inlineStr">
         <is>
-          <t>단위: 천원. A블록=기준안(S1, 입력) / B블록=선택 시나리오 적용(손익계산서·5번 시트 연동). 파란색 = 입력(2026-01~09 = 실적, 10~12월 = 예상).</t>
+          <t>단위: 천원. A블록=경영계획(S1, 입력) / B블록=선택 시나리오 적용(손익계산서·5번 시트 연동). 파란색 = 입력(2026-01~09 = 실적, 10~12월 = 예상).</t>
         </is>
       </c>
     </row>
@@ -14238,7 +14305,7 @@
     <row r="9">
       <c r="A9" s="3" t="inlineStr">
         <is>
-          <t>A. 기준안(S1) — 거래처별 매출 입력</t>
+          <t>A. 경영계획(S1) — 거래처별 매출 입력</t>
         </is>
       </c>
     </row>
@@ -14306,7 +14373,7 @@
       </c>
       <c r="V10" s="66" t="inlineStr">
         <is>
-          <t>2026-10-05 매출표(JCS) 2026 행5·2027 행5</t>
+          <t>거래처 매출표</t>
         </is>
       </c>
       <c r="X10" s="56" t="n">
@@ -14470,7 +14537,7 @@
       </c>
       <c r="V11" s="66" t="inlineStr">
         <is>
-          <t>2026-10-05 매출표(JCS)</t>
+          <t>거래처 매출표</t>
         </is>
       </c>
       <c r="X11" s="56" t="n">
@@ -14634,7 +14701,7 @@
       </c>
       <c r="V12" s="66" t="inlineStr">
         <is>
-          <t>2026-10-05 매출표(JCS)</t>
+          <t>거래처 매출표</t>
         </is>
       </c>
       <c r="X12" s="56" t="n">
@@ -14798,7 +14865,7 @@
       </c>
       <c r="V13" s="66" t="inlineStr">
         <is>
-          <t>2026-10-05 매출표(JCS)</t>
+          <t>거래처 매출표</t>
         </is>
       </c>
       <c r="X13" s="56" t="n">
@@ -14962,7 +15029,7 @@
       </c>
       <c r="V14" s="66" t="inlineStr">
         <is>
-          <t>2026-10-05 매출표(JCS)</t>
+          <t>거래처 매출표</t>
         </is>
       </c>
       <c r="X14" s="56" t="n">
@@ -15126,7 +15193,7 @@
       </c>
       <c r="V15" s="66" t="inlineStr">
         <is>
-          <t>2026-10-05 매출표(JCS) · IR p.12 APP 베이비 협업</t>
+          <t>거래처 매출표 · IR p.12 APP 베이비 협업</t>
         </is>
       </c>
       <c r="X15" s="56" t="n">
@@ -15290,7 +15357,7 @@
       </c>
       <c r="V16" s="66" t="inlineStr">
         <is>
-          <t>2026-10-05 매출표(JCS) · 2026 행11</t>
+          <t>거래처 매출표</t>
         </is>
       </c>
       <c r="X16" s="56" t="n">
@@ -15441,7 +15508,7 @@
       </c>
       <c r="K17" s="44">
         <f>AW17</f>
-        <v>100000</v>
+        <v>120000</v>
       </c>
       <c r="L17" s="65" t="n">
         <v>1.6</v>
@@ -15454,7 +15521,7 @@
       </c>
       <c r="V17" s="66" t="inlineStr">
         <is>
-          <t>2026-10-05 매출표(JCS) · 2026 행12</t>
+          <t>거래처 매출표 · USD 30,000 발주: 2026-12 선금 50%(2,000만원) + 잔금 50%(2,000만원)는 2027-01에 반영(잔금 수령월은 가정)</t>
         </is>
       </c>
       <c r="X17" s="56" t="n">
@@ -15494,7 +15561,7 @@
         <v>20000</v>
       </c>
       <c r="AJ17" s="56" t="n">
-        <v>0</v>
+        <v>20000</v>
       </c>
       <c r="AK17" s="56" t="n">
         <v>0</v>
@@ -15535,23 +15602,23 @@
       </c>
       <c r="AW17" s="23">
         <f>SUM(AJ17:AU17)</f>
-        <v>100000</v>
+        <v>120000</v>
       </c>
       <c r="AX17" s="46">
         <f>$K17*(1+$L17)</f>
-        <v>260000</v>
+        <v>312000</v>
       </c>
       <c r="AY17" s="46">
         <f>AX17*(1+$M17)</f>
-        <v>468000</v>
+        <v>561600</v>
       </c>
       <c r="AZ17" s="46">
         <f>AY17*(1+$N17)</f>
-        <v>692640</v>
+        <v>831168</v>
       </c>
       <c r="BA17" s="25">
         <f>SUM(AV17:AZ17)</f>
-        <v>1586522</v>
+        <v>1890650</v>
       </c>
     </row>
     <row r="18">
@@ -15585,7 +15652,7 @@
       </c>
       <c r="G18" s="15" t="inlineStr">
         <is>
-          <t>진행중</t>
+          <t>진행 중</t>
         </is>
       </c>
       <c r="H18" s="15" t="inlineStr">
@@ -15618,7 +15685,7 @@
       </c>
       <c r="V18" s="66" t="inlineStr">
         <is>
-          <t>2026-10-05 매출표(JCS) · 2027 신규</t>
+          <t>거래처 매출표 · 2027 신규</t>
         </is>
       </c>
       <c r="X18" s="56" t="n">
@@ -15749,7 +15816,7 @@
       </c>
       <c r="G19" s="15" t="inlineStr">
         <is>
-          <t>진행중</t>
+          <t>진행 중</t>
         </is>
       </c>
       <c r="H19" s="15" t="inlineStr">
@@ -15782,7 +15849,7 @@
       </c>
       <c r="V19" s="66" t="inlineStr">
         <is>
-          <t>2026-10-05 매출표(JCS) · 2027 신규</t>
+          <t>거래처 매출표 · 2027 신규</t>
         </is>
       </c>
       <c r="X19" s="56" t="n">
@@ -15946,7 +16013,7 @@
       </c>
       <c r="V20" s="66" t="inlineStr">
         <is>
-          <t>2026-10-05 매출표(JCS) · 요양시설 레퍼런스(IR p.10)</t>
+          <t>거래처 매출표 · 요양시설 레퍼런스(IR p.10)</t>
         </is>
       </c>
       <c r="X20" s="56" t="n">
@@ -16077,7 +16144,7 @@
       </c>
       <c r="G21" s="15" t="inlineStr">
         <is>
-          <t>진행중</t>
+          <t>진행 중</t>
         </is>
       </c>
       <c r="H21" s="15" t="inlineStr">
@@ -16110,7 +16177,7 @@
       </c>
       <c r="V21" s="66" t="inlineStr">
         <is>
-          <t>2026-10-05 매출표(JCS) · IR p.10 요양시설 기저귀 유통사 경유</t>
+          <t>거래처 매출표 · IR p.10 요양시설 기저귀 유통사 경유</t>
         </is>
       </c>
       <c r="X21" s="56" t="n">
@@ -16274,7 +16341,7 @@
       </c>
       <c r="V22" s="66" t="inlineStr">
         <is>
-          <t>2026-10-05 매출표(JCS) · 2026-12 실증사업 3,500만원</t>
+          <t>거래처 매출표 · 실증사업: 2026-11 4,000천원 + 2027 분기 4,000천원</t>
         </is>
       </c>
       <c r="X22" s="56" t="n">
@@ -16438,7 +16505,7 @@
       </c>
       <c r="V23" s="66" t="inlineStr">
         <is>
-          <t>2026-10-05 매출표(JCS) · 2027 표에 미표기</t>
+          <t>거래처 매출표 · 2027 표에 미표기</t>
         </is>
       </c>
       <c r="X23" s="56" t="n">
@@ -16602,7 +16669,7 @@
       </c>
       <c r="V24" s="66" t="inlineStr">
         <is>
-          <t>2026-10-05 매출표(JCS)</t>
+          <t>거래처 매출표</t>
         </is>
       </c>
       <c r="X24" s="56" t="n">
@@ -16733,7 +16800,7 @@
       </c>
       <c r="G25" s="15" t="inlineStr">
         <is>
-          <t>등록완료</t>
+          <t>등록 완료</t>
         </is>
       </c>
       <c r="H25" s="15" t="inlineStr">
@@ -16766,7 +16833,7 @@
       </c>
       <c r="V25" s="66" t="inlineStr">
         <is>
-          <t>2026-10-05 매출표(JCS) · IR p.9 NHIS 혁신 복지용구</t>
+          <t>거래처 매출표 · IR p.9 NHIS 혁신 복지용구</t>
         </is>
       </c>
       <c r="X25" s="56" t="n">
@@ -16930,7 +16997,7 @@
       </c>
       <c r="V26" s="66" t="inlineStr">
         <is>
-          <t>2026-10-05 매출표(JCS)</t>
+          <t>거래처 매출표 · 2026-11 3,950천원(예상)</t>
         </is>
       </c>
       <c r="X26" s="56" t="n">
@@ -16964,7 +17031,7 @@
         <v>0</v>
       </c>
       <c r="AH26" s="56" t="n">
-        <v>-3950</v>
+        <v>3950</v>
       </c>
       <c r="AI26" s="56" t="n">
         <v>0</v>
@@ -17007,7 +17074,7 @@
       </c>
       <c r="AV26" s="23">
         <f>SUM(X26:AI26)</f>
-        <v>-3079</v>
+        <v>4821</v>
       </c>
       <c r="AW26" s="23">
         <f>SUM(AJ26:AU26)</f>
@@ -17027,7 +17094,7 @@
       </c>
       <c r="BA26" s="25">
         <f>SUM(AV26:AZ26)</f>
-        <v>476921</v>
+        <v>484821</v>
       </c>
     </row>
     <row r="27">
@@ -17094,7 +17161,7 @@
       </c>
       <c r="V27" s="66" t="inlineStr">
         <is>
-          <t>2026-10-05 매출표(JCS) · IR p.11 APP 시니어 파트너십</t>
+          <t>거래처 매출표 · IR p.11 APP 시니어 파트너십</t>
         </is>
       </c>
       <c r="X27" s="56" t="n">
@@ -17258,7 +17325,7 @@
       </c>
       <c r="V28" s="66" t="inlineStr">
         <is>
-          <t>2026-10-05 매출표(JCS) · IR p.13</t>
+          <t>거래처 매출표 · IR p.13</t>
         </is>
       </c>
       <c r="X28" s="56" t="n">
@@ -17389,7 +17456,7 @@
       </c>
       <c r="G29" s="15" t="inlineStr">
         <is>
-          <t>등록완료</t>
+          <t>등록 완료</t>
         </is>
       </c>
       <c r="H29" s="15" t="inlineStr">
@@ -17422,7 +17489,7 @@
       </c>
       <c r="V29" s="66" t="inlineStr">
         <is>
-          <t>2026-10-05 매출표(JCS) · IR p.13</t>
+          <t>거래처 매출표 · IR p.13</t>
         </is>
       </c>
       <c r="X29" s="56" t="n">
@@ -17586,7 +17653,7 @@
       </c>
       <c r="V30" s="66" t="inlineStr">
         <is>
-          <t>2026-10-05 매출표(JCS) · 2026 행25</t>
+          <t>거래처 매출표</t>
         </is>
       </c>
       <c r="X30" s="56" t="n">
@@ -17717,7 +17784,7 @@
       </c>
       <c r="G31" s="15" t="inlineStr">
         <is>
-          <t>진행중</t>
+          <t>진행 중</t>
         </is>
       </c>
       <c r="H31" s="15" t="inlineStr">
@@ -17735,9 +17802,13 @@
           <t>N</t>
         </is>
       </c>
+      <c r="K31" s="44">
+        <f>AW31</f>
+        <v>60000</v>
+      </c>
       <c r="V31" s="66" t="inlineStr">
         <is>
-          <t>2026-10-09 거래처 매출표(사용자 수정본) · 인도 신규 디스트리뷰터(2026-12 초도, 2027 분기 발주), 2028~30 연간 입력값</t>
+          <t>거래처 매출표 · 인도 신규 디스트리뷰터(2026-12 초도, 2027 분기 단위 발주), 2028~30 연간 입력값</t>
         </is>
       </c>
       <c r="X31" s="56" t="n">
@@ -17865,7 +17936,7 @@
       </c>
       <c r="G32" s="15" t="inlineStr">
         <is>
-          <t>진행중</t>
+          <t>진행 중</t>
         </is>
       </c>
       <c r="H32" s="15" t="inlineStr">
@@ -17883,9 +17954,13 @@
           <t>N</t>
         </is>
       </c>
+      <c r="K32" s="44">
+        <f>AW32</f>
+        <v>80000</v>
+      </c>
       <c r="V32" s="66" t="inlineStr">
         <is>
-          <t>2026-10-09 거래처 매출표(사용자 수정본) · 인도 신규 디스트리뷰터(2027 분기 발주), 2028~30 연간 입력값</t>
+          <t>거래처 매출표 · 인도 신규 디스트리뷰터(2027 분기 단위 발주), 2028~30 연간 입력값</t>
         </is>
       </c>
       <c r="X32" s="56" t="n">
@@ -18046,7 +18121,7 @@
       </c>
       <c r="V33" s="66" t="inlineStr">
         <is>
-          <t>2026-10-05 매출표(JCS) · 2026-09 €24,000 포함(●) · IR p.23</t>
+          <t>거래처 매출표 · 2026-09 €24,000(매출표 환산 31,303천원) 포함 · IR p.23</t>
         </is>
       </c>
       <c r="X33" s="56" t="n">
@@ -18210,7 +18285,7 @@
       </c>
       <c r="V34" s="66" t="inlineStr">
         <is>
-          <t>2026-10-05 매출표(JCS) · 2027 행30 (IR p.25는 스페인 표기)</t>
+          <t>거래처 매출표 · 폴란드 총판</t>
         </is>
       </c>
       <c r="X34" s="56" t="n">
@@ -18341,7 +18416,7 @@
       </c>
       <c r="G35" s="15" t="inlineStr">
         <is>
-          <t>진행중</t>
+          <t>진행 중</t>
         </is>
       </c>
       <c r="H35" s="15" t="inlineStr">
@@ -18374,7 +18449,7 @@
       </c>
       <c r="V35" s="66" t="inlineStr">
         <is>
-          <t>2026-10-05 매출표(JCS) · 2027 행31</t>
+          <t>거래처 매출표</t>
         </is>
       </c>
       <c r="X35" s="56" t="n">
@@ -18538,7 +18613,7 @@
       </c>
       <c r="V36" s="66" t="inlineStr">
         <is>
-          <t>2026-10-05 매출표(JCS) · IR p.23</t>
+          <t>거래처 매출표 · IR p.23</t>
         </is>
       </c>
       <c r="X36" s="56" t="n">
@@ -18702,7 +18777,7 @@
       </c>
       <c r="V37" s="66" t="inlineStr">
         <is>
-          <t>2026-10-05 매출표(JCS) · IR p.31 PoC/R&amp;D → 상용 전환 가정</t>
+          <t>거래처 매출표 · IR p.31 PoC/R&amp;D → 상용 전환 가정</t>
         </is>
       </c>
       <c r="X37" s="56" t="n">
@@ -18866,7 +18941,7 @@
       </c>
       <c r="V38" s="66" t="inlineStr">
         <is>
-          <t>2026-10-05 매출표(JCS) · 2026-12 KTPH SGD 180,000, 2027 NHG 4억 · 입찰 단계(LOA 미확인)</t>
+          <t>거래처 매출표 · 2026-12 KTPH SGD 180,000, 2027 NHG 4억 · 입찰 단계(LOA 미확인)</t>
         </is>
       </c>
       <c r="X38" s="56" t="n">
@@ -19030,7 +19105,7 @@
       </c>
       <c r="V39" s="66" t="inlineStr">
         <is>
-          <t>2026-10-05 매출표(JCS) · SGD 45,000(10·11월) · IR p.20</t>
+          <t>거래처 매출표 · SGD 45,000을 2026-10·11월 50%씩 분할(각 23,625천원) · IR p.20</t>
         </is>
       </c>
       <c r="X39" s="56" t="n">
@@ -19061,10 +19136,10 @@
         <v>0</v>
       </c>
       <c r="AG39" s="56" t="n">
-        <v>47250</v>
+        <v>23625</v>
       </c>
       <c r="AH39" s="56" t="n">
-        <v>0</v>
+        <v>23625</v>
       </c>
       <c r="AI39" s="56" t="n">
         <v>0</v>
@@ -19194,7 +19269,7 @@
       </c>
       <c r="V40" s="66" t="inlineStr">
         <is>
-          <t>2026-10-05 매출표(JCS) · IR p.23</t>
+          <t>거래처 매출표 · IR p.23</t>
         </is>
       </c>
       <c r="X40" s="56" t="n">
@@ -19343,6 +19418,10 @@
           <t>N</t>
         </is>
       </c>
+      <c r="K41" s="44">
+        <f>AW41</f>
+        <v>0</v>
+      </c>
       <c r="V41" s="66" t="inlineStr">
         <is>
           <t>오사카 외 간사이·수도권 시설 확대, 介護テクノロジー導入支援 연계(가정)</t>
@@ -19491,9 +19570,13 @@
           <t>N</t>
         </is>
       </c>
+      <c r="K42" s="44">
+        <f>AW42</f>
+        <v>200000</v>
+      </c>
       <c r="V42" s="66" t="inlineStr">
         <is>
-          <t>IR p.29~32: PoC·구매절차 준비 중인 대형 그룹의 상용 전환(가정)</t>
+          <t>IR p.19·25·29~32: PoC·구매절차 준비 중인 대형 그룹의 상용 전환(가정)</t>
         </is>
       </c>
       <c r="X42" s="56" t="n">
@@ -19639,6 +19722,10 @@
           <t>N</t>
         </is>
       </c>
+      <c r="K43" s="44">
+        <f>AW43</f>
+        <v>480000</v>
+      </c>
       <c r="V43" s="66" t="inlineStr">
         <is>
           <t>IR p.24 로드맵 2027 EU PoC → 2028 확대(가정)</t>
@@ -19787,9 +19874,13 @@
           <t>N</t>
         </is>
       </c>
+      <c r="K44" s="44">
+        <f>AW44</f>
+        <v>200000</v>
+      </c>
       <c r="V44" s="66" t="inlineStr">
         <is>
-          <t>IR p.24 로드맵 2029 미국 의료 유통 채널 진입. FDA 등 인허가 일정은 별도 확인 필요</t>
+          <t>IR p.24 로드맵: 2029 미국 의료 유통 채널 본격 진입. 2027~28은 Shelter Device PoC·초기 공급 가정(미확정, 2027-03부터 월 2천만원), FDA 등 인허가 일정은 별도 확인 필요</t>
         </is>
       </c>
       <c r="X44" s="56" t="n">
@@ -19935,6 +20026,10 @@
           <t>S</t>
         </is>
       </c>
+      <c r="K45" s="44">
+        <f>AW45</f>
+        <v>120000</v>
+      </c>
       <c r="V45" s="66" t="inlineStr">
         <is>
           <t>IR p.23·24: 삼성 B2B 오퍼링 번들(2028 글로벌 확장, 273개국). IR 총액과의 차이를 채우는 잔여 — 가장 불확실한 항목</t>
@@ -20022,19 +20117,19 @@
       </c>
       <c r="AX45" s="68">
         <f>'8_가정'!$E$6-SUM(AX10:AX44)</f>
-        <v>4641744</v>
+        <v>4589744</v>
       </c>
       <c r="AY45" s="68">
         <f>'8_가정'!$F$6-SUM(AY10:AY44)</f>
-        <v>10147849.6</v>
+        <v>10054249.6</v>
       </c>
       <c r="AZ45" s="68">
         <f>'8_가정'!$G$6-SUM(AZ10:AZ44)</f>
-        <v>23110951.488</v>
+        <v>22972423.488</v>
       </c>
       <c r="BA45" s="25">
         <f>SUM(AV45:AZ45)</f>
-        <v>38020545.088</v>
+        <v>37736417.088</v>
       </c>
     </row>
     <row r="46">
@@ -20081,11 +20176,11 @@
       </c>
       <c r="AG46" s="26">
         <f>SUM(AG10:AG45)</f>
-        <v>201950</v>
+        <v>178325</v>
       </c>
       <c r="AH46" s="26">
         <f>SUM(AH10:AH45)</f>
-        <v>212395</v>
+        <v>243920</v>
       </c>
       <c r="AI46" s="26">
         <f>SUM(AI10:AI45)</f>
@@ -20093,7 +20188,7 @@
       </c>
       <c r="AJ46" s="26">
         <f>SUM(AJ10:AJ45)</f>
-        <v>625900</v>
+        <v>645900</v>
       </c>
       <c r="AK46" s="26">
         <f>SUM(AK10:AK45)</f>
@@ -20141,11 +20236,11 @@
       </c>
       <c r="AV46" s="27">
         <f>SUM(AV10:AV45)</f>
-        <v>1193317</v>
+        <v>1201217</v>
       </c>
       <c r="AW46" s="27">
         <f>SUM(AW10:AW45)</f>
-        <v>11184800</v>
+        <v>11204800</v>
       </c>
       <c r="AX46" s="28">
         <f>SUM(AX10:AX45)</f>
@@ -20161,7 +20256,7 @@
       </c>
       <c r="BA46" s="26">
         <f>SUM(BA10:BA45)</f>
-        <v>271378117</v>
+        <v>271406017</v>
       </c>
     </row>
     <row r="47">
@@ -20190,6 +20285,10 @@
         <f>'8_가정'!$G$6</f>
         <v>156000000</v>
       </c>
+      <c r="BA47" s="44">
+        <f>SUM(AV47:AZ47)</f>
+        <v>270205000</v>
+      </c>
     </row>
     <row r="48">
       <c r="D48" s="53" t="inlineStr">
@@ -20199,11 +20298,11 @@
       </c>
       <c r="AV48" s="44">
         <f>AV46-AV47</f>
-        <v>-6683</v>
+        <v>1217</v>
       </c>
       <c r="AW48" s="44">
         <f>AW46-AW47</f>
-        <v>1179800</v>
+        <v>1199800</v>
       </c>
       <c r="AX48" s="44">
         <f>AX46-AX47</f>
@@ -20217,6 +20316,10 @@
         <f>AZ46-AZ47</f>
         <v>0</v>
       </c>
+      <c r="BA48" s="44">
+        <f>BA46-BA47</f>
+        <v>1201017</v>
+      </c>
     </row>
     <row r="49">
       <c r="D49" s="53" t="inlineStr">
@@ -20226,11 +20329,11 @@
       </c>
       <c r="AV49" s="70">
         <f>IFERROR(AV48/AV47,0)</f>
-        <v>-0.00556916666666667</v>
+        <v>0.00101416666666667</v>
       </c>
       <c r="AW49" s="70">
         <f>IFERROR(AW48/AW47,0)</f>
-        <v>0.11792103948026</v>
+        <v>0.11992003998001</v>
       </c>
       <c r="AX49" s="70">
         <f>IFERROR(AX48/AX47,0)</f>
@@ -20243,6 +20346,10 @@
       <c r="AZ49" s="70">
         <f>IFERROR(AZ48/AZ47,0)</f>
         <v>0</v>
+      </c>
+      <c r="BA49" s="70">
+        <f>IFERROR(BA48/BA47,0)</f>
+        <v>0.00444483632797321</v>
       </c>
     </row>
     <row r="51">
@@ -21806,7 +21913,7 @@
       </c>
       <c r="AJ61" s="44">
         <f>AJ17*AJ$52</f>
-        <v>0</v>
+        <v>20000</v>
       </c>
       <c r="AK61" s="44">
         <f>AK17*AK$52</f>
@@ -21858,23 +21965,23 @@
       </c>
       <c r="AW61" s="23">
         <f>SUM(AJ61:AU61)</f>
-        <v>100000</v>
+        <v>120000</v>
       </c>
       <c r="AX61" s="46">
         <f>AX17*AX$52</f>
-        <v>260000</v>
+        <v>312000</v>
       </c>
       <c r="AY61" s="46">
         <f>AY17*AY$52</f>
-        <v>468000</v>
+        <v>561600</v>
       </c>
       <c r="AZ61" s="46">
         <f>AZ17*AZ$52</f>
-        <v>692640</v>
+        <v>831168</v>
       </c>
       <c r="BA61" s="25">
         <f>SUM(AV61:AZ61)</f>
-        <v>1586522</v>
+        <v>1890650</v>
       </c>
     </row>
     <row r="62">
@@ -21904,7 +22011,7 @@
       </c>
       <c r="G62" s="15" t="str">
         <f>G18</f>
-        <v>진행중</v>
+        <v>진행 중</v>
       </c>
       <c r="H62" s="15" t="str">
         <f>H18</f>
@@ -22066,7 +22173,7 @@
       </c>
       <c r="G63" s="15" t="str">
         <f>G19</f>
-        <v>진행중</v>
+        <v>진행 중</v>
       </c>
       <c r="H63" s="15" t="str">
         <f>H19</f>
@@ -22390,7 +22497,7 @@
       </c>
       <c r="G65" s="15" t="str">
         <f>G21</f>
-        <v>진행중</v>
+        <v>진행 중</v>
       </c>
       <c r="H65" s="15" t="str">
         <f>H21</f>
@@ -23038,7 +23145,7 @@
       </c>
       <c r="G69" s="15" t="str">
         <f>G25</f>
-        <v>등록완료</v>
+        <v>등록 완료</v>
       </c>
       <c r="H69" s="15" t="str">
         <f>H25</f>
@@ -23256,7 +23363,7 @@
       </c>
       <c r="AH70" s="44">
         <f>AH26*AH$52</f>
-        <v>-3950</v>
+        <v>3950</v>
       </c>
       <c r="AI70" s="44">
         <f>AI26*AI$52</f>
@@ -23312,7 +23419,7 @@
       </c>
       <c r="AV70" s="23">
         <f>SUM(X70:AI70)</f>
-        <v>-3079</v>
+        <v>4821</v>
       </c>
       <c r="AW70" s="23">
         <f>SUM(AJ70:AU70)</f>
@@ -23332,7 +23439,7 @@
       </c>
       <c r="BA70" s="25">
         <f>SUM(AV70:AZ70)</f>
-        <v>476921</v>
+        <v>484821</v>
       </c>
     </row>
     <row r="71">
@@ -23686,7 +23793,7 @@
       </c>
       <c r="G73" s="15" t="str">
         <f>G29</f>
-        <v>등록완료</v>
+        <v>등록 완료</v>
       </c>
       <c r="H73" s="15" t="str">
         <f>H29</f>
@@ -24010,7 +24117,7 @@
       </c>
       <c r="G75" s="15" t="str">
         <f>G31</f>
-        <v>진행중</v>
+        <v>진행 중</v>
       </c>
       <c r="H75" s="15" t="str">
         <f>H31</f>
@@ -24172,7 +24279,7 @@
       </c>
       <c r="G76" s="15" t="str">
         <f>G32</f>
-        <v>진행중</v>
+        <v>진행 중</v>
       </c>
       <c r="H76" s="15" t="str">
         <f>H32</f>
@@ -24658,7 +24765,7 @@
       </c>
       <c r="G79" s="15" t="str">
         <f>G35</f>
-        <v>진행중</v>
+        <v>진행 중</v>
       </c>
       <c r="H79" s="15" t="str">
         <f>H35</f>
@@ -25358,11 +25465,11 @@
       </c>
       <c r="AG83" s="44">
         <f>AG39*AG$52</f>
-        <v>47250</v>
+        <v>23625</v>
       </c>
       <c r="AH83" s="44">
         <f>AH39*AH$52</f>
-        <v>0</v>
+        <v>23625</v>
       </c>
       <c r="AI83" s="44">
         <f>AI39*AI$52</f>
@@ -26398,19 +26505,19 @@
       </c>
       <c r="AX89" s="46">
         <f>AX45*AX$52</f>
-        <v>4641744</v>
+        <v>4589744</v>
       </c>
       <c r="AY89" s="46">
         <f>AY45*AY$52</f>
-        <v>10147849.6</v>
+        <v>10054249.6</v>
       </c>
       <c r="AZ89" s="46">
         <f>AZ45*AZ$52</f>
-        <v>23110951.488</v>
+        <v>22972423.488</v>
       </c>
       <c r="BA89" s="25">
         <f>SUM(AV89:AZ89)</f>
-        <v>38020545.088</v>
+        <v>37736417.088</v>
       </c>
     </row>
     <row r="90">
@@ -26457,11 +26564,11 @@
       </c>
       <c r="AG90" s="26">
         <f>SUM(AG54:AG89)</f>
-        <v>201950</v>
+        <v>178325</v>
       </c>
       <c r="AH90" s="26">
         <f>SUM(AH54:AH89)</f>
-        <v>212395</v>
+        <v>243920</v>
       </c>
       <c r="AI90" s="26">
         <f>SUM(AI54:AI89)</f>
@@ -26469,7 +26576,7 @@
       </c>
       <c r="AJ90" s="26">
         <f>SUM(AJ54:AJ89)</f>
-        <v>625900</v>
+        <v>645900</v>
       </c>
       <c r="AK90" s="26">
         <f>SUM(AK54:AK89)</f>
@@ -26517,11 +26624,11 @@
       </c>
       <c r="AV90" s="27">
         <f>SUM(AV54:AV89)</f>
-        <v>1193317</v>
+        <v>1201217</v>
       </c>
       <c r="AW90" s="27">
         <f>SUM(AW54:AW89)</f>
-        <v>11184800</v>
+        <v>11204800</v>
       </c>
       <c r="AX90" s="28">
         <f>SUM(AX54:AX89)</f>
@@ -26537,7 +26644,7 @@
       </c>
       <c r="BA90" s="26">
         <f>SUM(BA54:BA89)</f>
-        <v>271378117</v>
+        <v>271406017</v>
       </c>
     </row>
     <row r="91">
@@ -26548,11 +26655,11 @@
       </c>
       <c r="AW91" s="58">
         <f>IFERROR(AW90/AV90-1,0)</f>
-        <v>8.37286571799447</v>
+        <v>8.32787331514622</v>
       </c>
       <c r="AX91" s="58">
         <f>IFERROR(AX90/AW90-1,0)</f>
-        <v>1.95043273013375</v>
+        <v>1.94516635727545</v>
       </c>
       <c r="AY91" s="58">
         <f>IFERROR(AY90/AX90-1,0)</f>
@@ -26566,7 +26673,7 @@
     <row r="93">
       <c r="A93" s="53" t="inlineStr">
         <is>
-          <t>※ 2026·2027 거래처 매출은 사용자 매출표(2026-10-09)의 입력값입니다. 2026-01~09는 실적, 10~12월은 예상 발주입니다. 2027 합계는 IR 차트(100.05억)와 다를 수 있으며 위 "차이" 행에 표시됩니다.</t>
+          <t>※ 2026·2027 거래처 매출은 거래처 매출표(2026-10-09)의 입력값입니다. 2026-01~09는 실적, 10~12월은 예상 발주입니다. 2027 합계는 IR 차트(100.05억)와 다를 수 있으며 위 "차이" 행에 표시됩니다.</t>
         </is>
       </c>
     </row>
@@ -26579,6 +26686,13 @@
     </row>
     <row r="95">
       <c r="A95" s="53" t="inlineStr">
+        <is>
+          <t>※ O~V열(근거·가정 메모)은 그룹으로 접혀 있습니다(열 머리글 위 + 클릭 시 펼쳐짐).</t>
+        </is>
+      </c>
+    </row>
+    <row r="96">
+      <c r="A96" s="53" t="inlineStr">
         <is>
           <t>※ 시나리오: B블록 = A블록 × 적용 계수(S1 100% · S2 80% · S3 60%). 2026은 1~9월 실적을 고정하고 10~12월에 계수를 역산 적용해 연간 달성률을 맞춥니다. S1에서 B블록 = A블록입니다.</t>
         </is>
@@ -26625,6 +26739,13 @@
         </is>
       </c>
     </row>
+    <row r="3">
+      <c r="A3" s="2" t="inlineStr">
+        <is>
+          <t>※ 천원 미만 단수 처리로 표시된 항목 합계가 ±1천원 차이날 수 있습니다(내부 계산값은 정확히 일치).</t>
+        </is>
+      </c>
+    </row>
     <row r="5">
       <c r="A5" s="21" t="inlineStr">
         <is>
@@ -27001,7 +27122,7 @@
       </c>
       <c r="M9" s="69">
         <f>SUMPRODUCT('4_매출_거래처'!AH$54:AH$89,$C$65:$C$100)</f>
-        <v>163898.5</v>
+        <v>170218.5</v>
       </c>
       <c r="N9" s="69">
         <f>SUMPRODUCT('4_매출_거래처'!AI$54:AI$89,$C$65:$C$100)</f>
@@ -27009,7 +27130,7 @@
       </c>
       <c r="O9" s="69">
         <f>SUMPRODUCT('4_매출_거래처'!AJ$54:AJ$89,$D$65:$D$100)</f>
-        <v>462952</v>
+        <v>479952</v>
       </c>
       <c r="P9" s="69">
         <f>SUMPRODUCT('4_매출_거래처'!AK$54:AK$89,$D$65:$D$100)</f>
@@ -27057,27 +27178,27 @@
       </c>
       <c r="AA9" s="23">
         <f>SUM(C9:N9)</f>
-        <v>732707.42</v>
+        <v>739027.42</v>
       </c>
       <c r="AB9" s="23">
         <f>SUM(O9:Z9)</f>
-        <v>7885234</v>
+        <v>7902234</v>
       </c>
       <c r="AC9" s="68">
         <f>SUMPRODUCT('4_매출_거래처'!AX$54:AX$89,$E$65:$E$100)</f>
-        <v>22277306.48</v>
+        <v>22287186.48</v>
       </c>
       <c r="AD9" s="68">
         <f>SUMPRODUCT('4_매출_거래처'!AY$54:AY$89,$F$65:$F$100)</f>
-        <v>43851045.44</v>
+        <v>43874445.44</v>
       </c>
       <c r="AE9" s="68">
         <f>SUMPRODUCT('4_매출_거래처'!AZ$54:AZ$89,$G$65:$G$100)</f>
-        <v>90699925.96032</v>
+        <v>90740099.08032</v>
       </c>
       <c r="AF9" s="25">
         <f>SUM(AA9:AE9)</f>
-        <v>165446219.30032</v>
+        <v>165542992.42032</v>
       </c>
     </row>
     <row r="10">
@@ -27133,7 +27254,7 @@
       </c>
       <c r="M10" s="69">
         <f>SUMPRODUCT('4_매출_거래처'!AH$54:AH$89,$H$65:$H$100)</f>
-        <v>20535.6</v>
+        <v>21167.6</v>
       </c>
       <c r="N10" s="69">
         <f>SUMPRODUCT('4_매출_거래처'!AI$54:AI$89,$H$65:$H$100)</f>
@@ -27141,7 +27262,7 @@
       </c>
       <c r="O10" s="69">
         <f>SUMPRODUCT('4_매출_거래처'!AJ$54:AJ$89,$I$65:$I$100)</f>
-        <v>76322</v>
+        <v>77322</v>
       </c>
       <c r="P10" s="69">
         <f>SUMPRODUCT('4_매출_거래처'!AK$54:AK$89,$I$65:$I$100)</f>
@@ -27189,27 +27310,27 @@
       </c>
       <c r="AA10" s="23">
         <f>SUM(C10:N10)</f>
-        <v>246338.51</v>
+        <v>246970.51</v>
       </c>
       <c r="AB10" s="23">
         <f>SUM(O10:Z10)</f>
-        <v>1485374</v>
+        <v>1486374</v>
       </c>
       <c r="AC10" s="68">
         <f>SUMPRODUCT('4_매출_거래처'!AX$54:AX$89,$J$65:$J$100)</f>
-        <v>4063924.88</v>
+        <v>4061324.88</v>
       </c>
       <c r="AD10" s="68">
         <f>SUMPRODUCT('4_매출_거래처'!AY$54:AY$89,$K$65:$K$100)</f>
-        <v>8515908.288</v>
+        <v>8510292.288</v>
       </c>
       <c r="AE10" s="68">
         <f>SUMPRODUCT('4_매출_거래처'!AZ$54:AZ$89,$L$65:$L$100)</f>
-        <v>18135247.10464</v>
+        <v>18126935.42464</v>
       </c>
       <c r="AF10" s="25">
         <f>SUM(AA10:AE10)</f>
-        <v>32446792.78264</v>
+        <v>32431897.10264</v>
       </c>
     </row>
     <row r="11">
@@ -27265,7 +27386,7 @@
       </c>
       <c r="M11" s="69">
         <f>SUMPRODUCT('4_매출_거래처'!AH$54:AH$89,$M$65:$M$100)</f>
-        <v>23960.9</v>
+        <v>24908.9</v>
       </c>
       <c r="N11" s="69">
         <f>SUMPRODUCT('4_매출_거래처'!AI$54:AI$89,$M$65:$M$100)</f>
@@ -27273,7 +27394,7 @@
       </c>
       <c r="O11" s="69">
         <f>SUMPRODUCT('4_매출_거래처'!AJ$54:AJ$89,$N$65:$N$100)</f>
-        <v>67099</v>
+        <v>69099</v>
       </c>
       <c r="P11" s="69">
         <f>SUMPRODUCT('4_매출_거래처'!AK$54:AK$89,$N$65:$N$100)</f>
@@ -27321,27 +27442,27 @@
       </c>
       <c r="AA11" s="23">
         <f>SUM(C11:N11)</f>
-        <v>134677.52</v>
+        <v>135625.52</v>
       </c>
       <c r="AB11" s="23">
         <f>SUM(O11:Z11)</f>
-        <v>1184558</v>
+        <v>1186558</v>
       </c>
       <c r="AC11" s="68">
         <f>SUMPRODUCT('4_매출_거래처'!AX$54:AX$89,$O$65:$O$100)</f>
-        <v>3784108</v>
+        <v>3783068</v>
       </c>
       <c r="AD11" s="68">
         <f>SUMPRODUCT('4_매출_거래처'!AY$54:AY$89,$P$65:$P$100)</f>
-        <v>8109544.8</v>
+        <v>8107672.8</v>
       </c>
       <c r="AE11" s="68">
         <f>SUMPRODUCT('4_매출_거래처'!AZ$54:AZ$89,$Q$65:$Q$100)</f>
-        <v>18319085.6</v>
+        <v>18316315.04</v>
       </c>
       <c r="AF11" s="25">
         <f>SUM(AA11:AE11)</f>
-        <v>31531973.92</v>
+        <v>31529239.36</v>
       </c>
     </row>
     <row r="12">
@@ -27461,25 +27582,25 @@
       </c>
       <c r="AC12" s="68">
         <f>SUMPRODUCT('4_매출_거래처'!AX$54:AX$89,$T$65:$T$100)</f>
-        <v>1722542.32</v>
+        <v>1718382.32</v>
       </c>
       <c r="AD12" s="68">
         <f>SUMPRODUCT('4_매출_거래처'!AY$54:AY$89,$U$65:$U$100)</f>
-        <v>5791768.384</v>
+        <v>5781472.384</v>
       </c>
       <c r="AE12" s="68">
         <f>SUMPRODUCT('4_매출_거래처'!AZ$54:AZ$89,$V$65:$V$100)</f>
-        <v>17506869.35552</v>
+        <v>17488860.71552</v>
       </c>
       <c r="AF12" s="25">
         <f>SUM(AA12:AE12)</f>
-        <v>25304814.05952</v>
+        <v>25272349.41952</v>
       </c>
     </row>
     <row r="13">
       <c r="A13" s="15" t="inlineStr">
         <is>
-          <t>스마트 욕창 케어(2027 Q4 출시)</t>
+          <t>스마트 욕창 케어(2027 출시)</t>
         </is>
       </c>
       <c r="B13" s="15" t="inlineStr">
@@ -27593,19 +27714,19 @@
       </c>
       <c r="AC13" s="68">
         <f>SUMPRODUCT('4_매출_거래처'!AX$54:AX$89,$Y$65:$Y$100)</f>
-        <v>401283.44</v>
+        <v>400243.44</v>
       </c>
       <c r="AD13" s="68">
         <f>SUMPRODUCT('4_매출_거래처'!AY$54:AY$89,$Z$65:$Z$100)</f>
-        <v>2245576.096</v>
+        <v>2241832.096</v>
       </c>
       <c r="AE13" s="68">
         <f>SUMPRODUCT('4_매출_거래처'!AZ$54:AZ$89,$AA$65:$AA$100)</f>
-        <v>8173068.94976</v>
+        <v>8164757.26976</v>
       </c>
       <c r="AF13" s="25">
         <f>SUM(AA13:AE13)</f>
-        <v>10839928.48576</v>
+        <v>10826832.80576</v>
       </c>
     </row>
     <row r="14">
@@ -27657,11 +27778,11 @@
       </c>
       <c r="L14" s="69">
         <f>SUMPRODUCT('4_매출_거래처'!AG$54:AG$89,$AB$65:$AB$100)</f>
-        <v>47250</v>
+        <v>23625</v>
       </c>
       <c r="M14" s="69">
         <f>SUMPRODUCT('4_매출_거래처'!AH$54:AH$89,$AB$65:$AB$100)</f>
-        <v>4000</v>
+        <v>27625</v>
       </c>
       <c r="N14" s="69">
         <f>SUMPRODUCT('4_매출_거래처'!AI$54:AI$89,$AB$65:$AB$100)</f>
@@ -27725,19 +27846,19 @@
       </c>
       <c r="AC14" s="68">
         <f>SUMPRODUCT('4_매출_거래처'!AX$54:AX$89,$AD$65:$AD$100)</f>
-        <v>750834.88</v>
+        <v>749794.88</v>
       </c>
       <c r="AD14" s="68">
         <f>SUMPRODUCT('4_매출_거래처'!AY$54:AY$89,$AE$65:$AE$100)</f>
-        <v>1486156.992</v>
+        <v>1484284.992</v>
       </c>
       <c r="AE14" s="68">
         <f>SUMPRODUCT('4_매출_거래처'!AZ$54:AZ$89,$AF$65:$AF$100)</f>
-        <v>3165803.02976</v>
+        <v>3163032.46976</v>
       </c>
       <c r="AF14" s="25">
         <f>SUM(AA14:AE14)</f>
-        <v>5808388.45176</v>
+        <v>5802705.89176</v>
       </c>
     </row>
     <row r="15">
@@ -27784,11 +27905,11 @@
       </c>
       <c r="L15" s="26">
         <f>SUM(L9:L14)</f>
-        <v>201950</v>
+        <v>178325</v>
       </c>
       <c r="M15" s="26">
         <f>SUM(M9:M14)</f>
-        <v>212395</v>
+        <v>243920</v>
       </c>
       <c r="N15" s="26">
         <f>SUM(N9:N14)</f>
@@ -27796,7 +27917,7 @@
       </c>
       <c r="O15" s="26">
         <f>SUM(O9:O14)</f>
-        <v>625900</v>
+        <v>645900</v>
       </c>
       <c r="P15" s="26">
         <f>SUM(P9:P14)</f>
@@ -27844,11 +27965,11 @@
       </c>
       <c r="AA15" s="27">
         <f>SUM(AA9:AA14)</f>
-        <v>1193317</v>
+        <v>1201217</v>
       </c>
       <c r="AB15" s="27">
         <f>SUM(AB9:AB14)</f>
-        <v>11184800</v>
+        <v>11204800</v>
       </c>
       <c r="AC15" s="28">
         <f>SUM(AC9:AC14)</f>
@@ -27864,7 +27985,7 @@
       </c>
       <c r="AF15" s="26">
         <f>SUM(AF9:AF14)</f>
-        <v>271378117</v>
+        <v>271406017</v>
       </c>
     </row>
     <row r="16">
@@ -28057,7 +28178,7 @@
       </c>
       <c r="O18" s="69">
         <f>SUMIF('4_매출_거래처'!$E$54:$E$89,$A18,'4_매출_거래처'!AJ$54:AJ$89)</f>
-        <v>185000</v>
+        <v>205000</v>
       </c>
       <c r="P18" s="69">
         <f>SUMIF('4_매출_거래처'!$E$54:$E$89,$A18,'4_매출_거래처'!AK$54:AK$89)</f>
@@ -28109,23 +28230,23 @@
       </c>
       <c r="AB18" s="23">
         <f>SUM(O18:Z18)</f>
-        <v>2451000</v>
+        <v>2471000</v>
       </c>
       <c r="AC18" s="68">
         <f>SUMIF('4_매출_거래처'!$E$54:$E$89,$A18,'4_매출_거래처'!AX$54:AX$89)</f>
-        <v>4175400</v>
+        <v>4227400</v>
       </c>
       <c r="AD18" s="68">
         <f>SUMIF('4_매출_거래처'!$E$54:$E$89,$A18,'4_매출_거래처'!AY$54:AY$89)</f>
-        <v>5800080</v>
+        <v>5893680</v>
       </c>
       <c r="AE18" s="68">
         <f>SUMIF('4_매출_거래처'!$E$54:$E$89,$A18,'4_매출_거래처'!AZ$54:AZ$89)</f>
-        <v>7340985.6</v>
+        <v>7479513.6</v>
       </c>
       <c r="AF18" s="25">
         <f>SUM(AA18:AE18)</f>
-        <v>20002008.6</v>
+        <v>20306136.6</v>
       </c>
     </row>
     <row r="19">
@@ -28172,11 +28293,11 @@
       </c>
       <c r="L19" s="69">
         <f>SUMIF('4_매출_거래처'!$E$54:$E$89,$A19,'4_매출_거래처'!AG$54:AG$89)</f>
-        <v>193250</v>
+        <v>169625</v>
       </c>
       <c r="M19" s="69">
         <f>SUMIF('4_매출_거래처'!$E$54:$E$89,$A19,'4_매출_거래처'!AH$54:AH$89)</f>
-        <v>183695</v>
+        <v>215220</v>
       </c>
       <c r="N19" s="69">
         <f>SUMIF('4_매출_거래처'!$E$54:$E$89,$A19,'4_매출_거래처'!AI$54:AI$89)</f>
@@ -28232,7 +28353,7 @@
       </c>
       <c r="AA19" s="23">
         <f>SUM(C19:N19)</f>
-        <v>958774</v>
+        <v>966674</v>
       </c>
       <c r="AB19" s="23">
         <f>SUM(O19:Z19)</f>
@@ -28240,19 +28361,19 @@
       </c>
       <c r="AC19" s="68">
         <f>SUMIF('4_매출_거래처'!$E$54:$E$89,$A19,'4_매출_거래처'!AX$54:AX$89)</f>
-        <v>28824600</v>
+        <v>28772600</v>
       </c>
       <c r="AD19" s="68">
         <f>SUMIF('4_매출_거래처'!$E$54:$E$89,$A19,'4_매출_거래처'!AY$54:AY$89)</f>
-        <v>64199920</v>
+        <v>64106320</v>
       </c>
       <c r="AE19" s="68">
         <f>SUMIF('4_매출_거래처'!$E$54:$E$89,$A19,'4_매출_거래처'!AZ$54:AZ$89)</f>
-        <v>148659014.4</v>
+        <v>148520486.4</v>
       </c>
       <c r="AF19" s="25">
         <f>SUM(AA19:AE19)</f>
-        <v>251376108.4</v>
+        <v>251099880.4</v>
       </c>
     </row>
     <row r="20">
@@ -28299,11 +28420,11 @@
       </c>
       <c r="L20" s="26">
         <f>SUM(L18:L19)</f>
-        <v>201950</v>
+        <v>178325</v>
       </c>
       <c r="M20" s="26">
         <f>SUM(M18:M19)</f>
-        <v>212395</v>
+        <v>243920</v>
       </c>
       <c r="N20" s="26">
         <f>SUM(N18:N19)</f>
@@ -28311,7 +28432,7 @@
       </c>
       <c r="O20" s="26">
         <f>SUM(O18:O19)</f>
-        <v>625900</v>
+        <v>645900</v>
       </c>
       <c r="P20" s="26">
         <f>SUM(P18:P19)</f>
@@ -28359,11 +28480,11 @@
       </c>
       <c r="AA20" s="27">
         <f>SUM(AA18:AA19)</f>
-        <v>1193317</v>
+        <v>1201217</v>
       </c>
       <c r="AB20" s="27">
         <f>SUM(AB18:AB19)</f>
-        <v>11184800</v>
+        <v>11204800</v>
       </c>
       <c r="AC20" s="28">
         <f>SUM(AC18:AC19)</f>
@@ -28379,7 +28500,7 @@
       </c>
       <c r="AF20" s="26">
         <f>SUM(AF18:AF19)</f>
-        <v>271378117</v>
+        <v>271406017</v>
       </c>
     </row>
     <row r="21">
@@ -28564,7 +28685,7 @@
       </c>
       <c r="M24" s="69">
         <f>SUMIF('4_매출_거래처'!$C$54:$C$89,$A24,'4_매출_거래처'!AH$54:AH$89)</f>
-        <v>168770</v>
+        <v>176670</v>
       </c>
       <c r="N24" s="69">
         <f>SUMIF('4_매출_거래처'!$C$54:$C$89,$A24,'4_매출_거래처'!AI$54:AI$89)</f>
@@ -28620,7 +28741,7 @@
       </c>
       <c r="AA24" s="23">
         <f>SUM(C24:N24)</f>
-        <v>649167</v>
+        <v>657067</v>
       </c>
       <c r="AB24" s="23">
         <f>SUM(O24:Z24)</f>
@@ -28640,7 +28761,7 @@
       </c>
       <c r="AF24" s="25">
         <f>SUM(AA24:AE24)</f>
-        <v>71490247.512</v>
+        <v>71498147.512</v>
       </c>
     </row>
     <row r="25">
@@ -28814,11 +28935,11 @@
       </c>
       <c r="L26" s="69">
         <f>SUMIF('4_매출_거래처'!$C$54:$C$89,$A26,'4_매출_거래처'!AG$54:AG$89)</f>
-        <v>47250</v>
+        <v>23625</v>
       </c>
       <c r="M26" s="69">
         <f>SUMIF('4_매출_거래처'!$C$54:$C$89,$A26,'4_매출_거래처'!AH$54:AH$89)</f>
-        <v>43625</v>
+        <v>67250</v>
       </c>
       <c r="N26" s="69">
         <f>SUMIF('4_매출_거래처'!$C$54:$C$89,$A26,'4_매출_거래처'!AI$54:AI$89)</f>
@@ -28826,7 +28947,7 @@
       </c>
       <c r="O26" s="69">
         <f>SUMIF('4_매출_거래처'!$C$54:$C$89,$A26,'4_매출_거래처'!AJ$54:AJ$89)</f>
-        <v>70000</v>
+        <v>90000</v>
       </c>
       <c r="P26" s="69">
         <f>SUMIF('4_매출_거래처'!$C$54:$C$89,$A26,'4_매출_거래처'!AK$54:AK$89)</f>
@@ -28878,23 +28999,23 @@
       </c>
       <c r="AB26" s="23">
         <f>SUM(O26:Z26)</f>
-        <v>1810000</v>
+        <v>1830000</v>
       </c>
       <c r="AC26" s="68">
         <f>SUMIF('4_매출_거래처'!$C$54:$C$89,$A26,'4_매출_거래처'!AX$54:AX$89)</f>
-        <v>5562000</v>
+        <v>5614000</v>
       </c>
       <c r="AD26" s="68">
         <f>SUMIF('4_매출_거래처'!$C$54:$C$89,$A26,'4_매출_거래처'!AY$54:AY$89)</f>
-        <v>11884800</v>
+        <v>11978400</v>
       </c>
       <c r="AE26" s="68">
         <f>SUMIF('4_매출_거래처'!$C$54:$C$89,$A26,'4_매출_거래처'!AZ$54:AZ$89)</f>
-        <v>25340672</v>
+        <v>25479200</v>
       </c>
       <c r="AF26" s="25">
         <f>SUM(AA26:AE26)</f>
-        <v>45001960</v>
+        <v>45306088</v>
       </c>
     </row>
     <row r="27">
@@ -29390,19 +29511,19 @@
       </c>
       <c r="AC30" s="68">
         <f>SUMIF('4_매출_거래처'!$C$54:$C$89,$A30,'4_매출_거래처'!AX$54:AX$89)</f>
-        <v>4641744</v>
+        <v>4589744</v>
       </c>
       <c r="AD30" s="68">
         <f>SUMIF('4_매출_거래처'!$C$54:$C$89,$A30,'4_매출_거래처'!AY$54:AY$89)</f>
-        <v>10147849.6</v>
+        <v>10054249.6</v>
       </c>
       <c r="AE30" s="68">
         <f>SUMIF('4_매출_거래처'!$C$54:$C$89,$A30,'4_매출_거래처'!AZ$54:AZ$89)</f>
-        <v>23110951.488</v>
+        <v>22972423.488</v>
       </c>
       <c r="AF30" s="25">
         <f>SUM(AA30:AE30)</f>
-        <v>38020545.088</v>
+        <v>37736417.088</v>
       </c>
     </row>
     <row r="31">
@@ -29449,11 +29570,11 @@
       </c>
       <c r="L31" s="26">
         <f>SUM(L24:L30)</f>
-        <v>201950</v>
+        <v>178325</v>
       </c>
       <c r="M31" s="26">
         <f>SUM(M24:M30)</f>
-        <v>212395</v>
+        <v>243920</v>
       </c>
       <c r="N31" s="26">
         <f>SUM(N24:N30)</f>
@@ -29461,7 +29582,7 @@
       </c>
       <c r="O31" s="26">
         <f>SUM(O24:O30)</f>
-        <v>625900</v>
+        <v>645900</v>
       </c>
       <c r="P31" s="26">
         <f>SUM(P24:P30)</f>
@@ -29509,11 +29630,11 @@
       </c>
       <c r="AA31" s="27">
         <f>SUM(AA24:AA30)</f>
-        <v>1193317</v>
+        <v>1201217</v>
       </c>
       <c r="AB31" s="27">
         <f>SUM(AB24:AB30)</f>
-        <v>11184800</v>
+        <v>11204800</v>
       </c>
       <c r="AC31" s="28">
         <f>SUM(AC24:AC30)</f>
@@ -29529,7 +29650,7 @@
       </c>
       <c r="AF31" s="26">
         <f>SUM(AF24:AF30)</f>
-        <v>271378117</v>
+        <v>271406017</v>
       </c>
     </row>
     <row r="32">
@@ -29841,7 +29962,7 @@
       </c>
       <c r="M36" s="69">
         <f>SUMIF('4_매출_거래처'!$F$54:$F$89,$A36,'4_매출_거래처'!AH$54:AH$89)</f>
-        <v>-3950</v>
+        <v>3950</v>
       </c>
       <c r="N36" s="69">
         <f>SUMIF('4_매출_거래처'!$F$54:$F$89,$A36,'4_매출_거래처'!AI$54:AI$89)</f>
@@ -29897,7 +30018,7 @@
       </c>
       <c r="AA36" s="23">
         <f>SUM(C36:N36)</f>
-        <v>6921</v>
+        <v>14821</v>
       </c>
       <c r="AB36" s="23">
         <f>SUM(O36:Z36)</f>
@@ -29917,7 +30038,7 @@
       </c>
       <c r="AF36" s="25">
         <f>SUM(AA36:AE36)</f>
-        <v>1798473</v>
+        <v>1806373</v>
       </c>
     </row>
     <row r="37">
@@ -29976,7 +30097,7 @@
       </c>
       <c r="O37" s="69">
         <f>SUMIF('4_매출_거래처'!$F$54:$F$89,$A37,'4_매출_거래처'!AJ$54:AJ$89)</f>
-        <v>268000</v>
+        <v>288000</v>
       </c>
       <c r="P37" s="69">
         <f>SUMIF('4_매출_거래처'!$F$54:$F$89,$A37,'4_매출_거래처'!AK$54:AK$89)</f>
@@ -30028,23 +30149,23 @@
       </c>
       <c r="AB37" s="23">
         <f>SUM(O37:Z37)</f>
-        <v>4928000</v>
+        <v>4948000</v>
       </c>
       <c r="AC37" s="68">
         <f>SUMIF('4_매출_거래처'!$F$54:$F$89,$A37,'4_매출_거래처'!AX$54:AX$89)</f>
-        <v>12388320</v>
+        <v>12440320</v>
       </c>
       <c r="AD37" s="68">
         <f>SUMIF('4_매출_거래처'!$F$54:$F$89,$A37,'4_매출_거래처'!AY$54:AY$89)</f>
-        <v>22015784</v>
+        <v>22109384</v>
       </c>
       <c r="AE37" s="68">
         <f>SUMIF('4_매출_거래처'!$F$54:$F$89,$A37,'4_매출_거래처'!AZ$54:AZ$89)</f>
-        <v>31724952</v>
+        <v>31863480</v>
       </c>
       <c r="AF37" s="25">
         <f>SUM(AA37:AE37)</f>
-        <v>71428199</v>
+        <v>71732327</v>
       </c>
     </row>
     <row r="38">
@@ -30286,19 +30407,19 @@
       </c>
       <c r="AC39" s="68">
         <f>SUMIF('4_매출_거래처'!$F$54:$F$89,$A39,'4_매출_거래처'!AX$54:AX$89)</f>
-        <v>8971344</v>
+        <v>8919344</v>
       </c>
       <c r="AD39" s="68">
         <f>SUMIF('4_매출_거래처'!$F$54:$F$89,$A39,'4_매출_거래처'!AY$54:AY$89)</f>
-        <v>15776329.6</v>
+        <v>15682729.6</v>
       </c>
       <c r="AE39" s="68">
         <f>SUMIF('4_매출_거래처'!$F$54:$F$89,$A39,'4_매출_거래처'!AZ$54:AZ$89)</f>
-        <v>29865127.488</v>
+        <v>29726599.488</v>
       </c>
       <c r="AF39" s="25">
         <f>SUM(AA39:AE39)</f>
-        <v>57732801.088</v>
+        <v>57448673.088</v>
       </c>
     </row>
     <row r="40">
@@ -30345,11 +30466,11 @@
       </c>
       <c r="L40" s="69">
         <f>SUMIF('4_매출_거래처'!$F$54:$F$89,$A40,'4_매출_거래처'!AG$54:AG$89)</f>
-        <v>47250</v>
+        <v>23625</v>
       </c>
       <c r="M40" s="69">
         <f>SUMIF('4_매출_거래처'!$F$54:$F$89,$A40,'4_매출_거래처'!AH$54:AH$89)</f>
-        <v>11900</v>
+        <v>35525</v>
       </c>
       <c r="N40" s="69">
         <f>SUMIF('4_매출_거래처'!$F$54:$F$89,$A40,'4_매출_거래처'!AI$54:AI$89)</f>
@@ -30726,11 +30847,11 @@
       </c>
       <c r="L43" s="26">
         <f>SUM(L35:L42)</f>
-        <v>201950</v>
+        <v>178325</v>
       </c>
       <c r="M43" s="26">
         <f>SUM(M35:M42)</f>
-        <v>212395</v>
+        <v>243920</v>
       </c>
       <c r="N43" s="26">
         <f>SUM(N35:N42)</f>
@@ -30738,7 +30859,7 @@
       </c>
       <c r="O43" s="26">
         <f>SUM(O35:O42)</f>
-        <v>625900</v>
+        <v>645900</v>
       </c>
       <c r="P43" s="26">
         <f>SUM(P35:P42)</f>
@@ -30786,11 +30907,11 @@
       </c>
       <c r="AA43" s="27">
         <f>SUM(AA35:AA42)</f>
-        <v>1193317</v>
+        <v>1201217</v>
       </c>
       <c r="AB43" s="27">
         <f>SUM(AB35:AB42)</f>
-        <v>11184800</v>
+        <v>11204800</v>
       </c>
       <c r="AC43" s="28">
         <f>SUM(AC35:AC42)</f>
@@ -30806,7 +30927,7 @@
       </c>
       <c r="AF43" s="26">
         <f>SUM(AF35:AF42)</f>
-        <v>271378117</v>
+        <v>271406017</v>
       </c>
     </row>
     <row r="44">
@@ -30987,11 +31108,11 @@
       </c>
       <c r="L47" s="69">
         <f>SUMIF('4_매출_거래처'!$H$54:$H$89,$A47,'4_매출_거래처'!AG$54:AG$89)</f>
-        <v>201950</v>
+        <v>178325</v>
       </c>
       <c r="M47" s="69">
         <f>SUMIF('4_매출_거래처'!$H$54:$H$89,$A47,'4_매출_거래처'!AH$54:AH$89)</f>
-        <v>190275</v>
+        <v>221800</v>
       </c>
       <c r="N47" s="69">
         <f>SUMIF('4_매출_거래처'!$H$54:$H$89,$A47,'4_매출_거래처'!AI$54:AI$89)</f>
@@ -30999,7 +31120,7 @@
       </c>
       <c r="O47" s="69">
         <f>SUMIF('4_매출_거래처'!$H$54:$H$89,$A47,'4_매출_거래처'!AJ$54:AJ$89)</f>
-        <v>367900</v>
+        <v>387900</v>
       </c>
       <c r="P47" s="69">
         <f>SUMIF('4_매출_거래처'!$H$54:$H$89,$A47,'4_매출_거래처'!AK$54:AK$89)</f>
@@ -31047,27 +31168,27 @@
       </c>
       <c r="AA47" s="23">
         <f>SUM(C47:N47)</f>
-        <v>855365</v>
+        <v>863265</v>
       </c>
       <c r="AB47" s="23">
         <f>SUM(O47:Z47)</f>
-        <v>5696800</v>
+        <v>5716800</v>
       </c>
       <c r="AC47" s="68">
         <f>SUMIF('4_매출_거래처'!$H$54:$H$89,$A47,'4_매출_거래처'!AX$54:AX$89)</f>
-        <v>9981136</v>
+        <v>10033136</v>
       </c>
       <c r="AD47" s="68">
         <f>SUMIF('4_매출_거래처'!$H$54:$H$89,$A47,'4_매출_거래처'!AY$54:AY$89)</f>
-        <v>14328846.4</v>
+        <v>14422446.4</v>
       </c>
       <c r="AE47" s="68">
         <f>SUMIF('4_매출_거래처'!$H$54:$H$89,$A47,'4_매출_거래처'!AZ$54:AZ$89)</f>
-        <v>18560422.912</v>
+        <v>18698950.912</v>
       </c>
       <c r="AF47" s="25">
         <f>SUM(AA47:AE47)</f>
-        <v>49422570.312</v>
+        <v>49734598.312</v>
       </c>
     </row>
     <row r="48">
@@ -31309,19 +31430,19 @@
       </c>
       <c r="AC49" s="68">
         <f>SUMIF('4_매출_거래처'!$H$54:$H$89,$A49,'4_매출_거래처'!AX$54:AX$89)</f>
-        <v>11841744</v>
+        <v>11789744</v>
       </c>
       <c r="AD49" s="68">
         <f>SUMIF('4_매출_거래처'!$H$54:$H$89,$A49,'4_매출_거래처'!AY$54:AY$89)</f>
-        <v>35947849.6</v>
+        <v>35854249.6</v>
       </c>
       <c r="AE49" s="68">
         <f>SUMIF('4_매출_거래처'!$H$54:$H$89,$A49,'4_매출_거래처'!AZ$54:AZ$89)</f>
-        <v>109110951.488</v>
+        <v>108972423.488</v>
       </c>
       <c r="AF49" s="25">
         <f>SUM(AA49:AE49)</f>
-        <v>157900545.088</v>
+        <v>157616417.088</v>
       </c>
     </row>
     <row r="50">
@@ -31368,11 +31489,11 @@
       </c>
       <c r="L50" s="26">
         <f>SUM(L47:L49)</f>
-        <v>201950</v>
+        <v>178325</v>
       </c>
       <c r="M50" s="26">
         <f>SUM(M47:M49)</f>
-        <v>212395</v>
+        <v>243920</v>
       </c>
       <c r="N50" s="26">
         <f>SUM(N47:N49)</f>
@@ -31380,7 +31501,7 @@
       </c>
       <c r="O50" s="26">
         <f>SUM(O47:O49)</f>
-        <v>625900</v>
+        <v>645900</v>
       </c>
       <c r="P50" s="26">
         <f>SUM(P47:P49)</f>
@@ -31428,11 +31549,11 @@
       </c>
       <c r="AA50" s="27">
         <f>SUM(AA47:AA49)</f>
-        <v>1193317</v>
+        <v>1201217</v>
       </c>
       <c r="AB50" s="27">
         <f>SUM(AB47:AB49)</f>
-        <v>11184800</v>
+        <v>11204800</v>
       </c>
       <c r="AC50" s="28">
         <f>SUM(AC47:AC49)</f>
@@ -31448,7 +31569,7 @@
       </c>
       <c r="AF50" s="26">
         <f>SUM(AF47:AF49)</f>
-        <v>271378117</v>
+        <v>271406017</v>
       </c>
     </row>
     <row r="51">
@@ -31626,7 +31747,7 @@
       </c>
       <c r="M52" s="75">
         <f>IFERROR(M47/M50,0)</f>
-        <v>0.89585442218508</v>
+        <v>0.909314529353887</v>
       </c>
       <c r="N52" s="75">
         <f>IFERROR(N47/N50,0)</f>
@@ -31634,7 +31755,7 @@
       </c>
       <c r="O52" s="75">
         <f>IFERROR(O47/O50,0)</f>
-        <v>0.587793577248762</v>
+        <v>0.600557361820715</v>
       </c>
       <c r="P52" s="75">
         <f>IFERROR(P47/P50,0)</f>
@@ -31682,27 +31803,27 @@
       </c>
       <c r="AA52" s="75">
         <f>IFERROR(AA47/AA50,0)</f>
-        <v>0.716796123745828</v>
+        <v>0.71865866034197</v>
       </c>
       <c r="AB52" s="75">
         <f>IFERROR(AB47/AB50,0)</f>
-        <v>0.509334096273514</v>
+        <v>0.510209910038555</v>
       </c>
       <c r="AC52" s="75">
         <f>IFERROR(AC47/AC50,0)</f>
-        <v>0.302458666666667</v>
+        <v>0.304034424242424</v>
       </c>
       <c r="AD52" s="75">
         <f>IFERROR(AD47/AD50,0)</f>
-        <v>0.204697805714286</v>
+        <v>0.206034948571429</v>
       </c>
       <c r="AE52" s="75">
         <f>IFERROR(AE47/AE50,0)</f>
-        <v>0.118977069948718</v>
+        <v>0.119865069948718</v>
       </c>
       <c r="AF52" s="75">
         <f>IFERROR(AF47/AF50,0)</f>
-        <v>0.18211700655289</v>
+        <v>0.183247957660423</v>
       </c>
     </row>
     <row r="53">
@@ -31753,7 +31874,7 @@
       </c>
       <c r="M53" s="75">
         <f>IFERROR(M48/M50,0)</f>
-        <v>0.10414557781492</v>
+        <v>0.0906854706461135</v>
       </c>
       <c r="N53" s="75">
         <f>IFERROR(N48/N50,0)</f>
@@ -31761,7 +31882,7 @@
       </c>
       <c r="O53" s="75">
         <f>IFERROR(O48/O50,0)</f>
-        <v>0.364275443361559</v>
+        <v>0.352995819786345</v>
       </c>
       <c r="P53" s="75">
         <f>IFERROR(P48/P50,0)</f>
@@ -31809,11 +31930,11 @@
       </c>
       <c r="AA53" s="75">
         <f>IFERROR(AA48/AA50,0)</f>
-        <v>0.283203876254172</v>
+        <v>0.28134133965803</v>
       </c>
       <c r="AB53" s="75">
         <f>IFERROR(AB48/AB50,0)</f>
-        <v>0.40125885129819</v>
+        <v>0.400542624589462</v>
       </c>
       <c r="AC53" s="75">
         <f>IFERROR(AC48/AC50,0)</f>
@@ -31829,7 +31950,7 @@
       </c>
       <c r="AF53" s="75">
         <f>IFERROR(AF48/AF50,0)</f>
-        <v>0.236035986645158</v>
+        <v>0.236011722614094</v>
       </c>
     </row>
     <row r="54">
@@ -31888,7 +32009,7 @@
       </c>
       <c r="O54" s="75">
         <f>IFERROR(O49/O50,0)</f>
-        <v>0.0479309793896789</v>
+        <v>0.0464468183929401</v>
       </c>
       <c r="P54" s="75">
         <f>IFERROR(P49/P50,0)</f>
@@ -31940,23 +32061,23 @@
       </c>
       <c r="AB54" s="75">
         <f>IFERROR(AB49/AB50,0)</f>
-        <v>0.0894070524282955</v>
+        <v>0.0892474653719834</v>
       </c>
       <c r="AC54" s="75">
         <f>IFERROR(AC49/AC50,0)</f>
-        <v>0.358840727272727</v>
+        <v>0.35726496969697</v>
       </c>
       <c r="AD54" s="75">
         <f>IFERROR(AD49/AD50,0)</f>
-        <v>0.513540708571429</v>
+        <v>0.512203565714286</v>
       </c>
       <c r="AE54" s="75">
         <f>IFERROR(AE49/AE50,0)</f>
-        <v>0.699429176205128</v>
+        <v>0.698541176205128</v>
       </c>
       <c r="AF54" s="75">
         <f>IFERROR(AF49/AF50,0)</f>
-        <v>0.581847006801952</v>
+        <v>0.580740319725484</v>
       </c>
     </row>
     <row r="56">
@@ -32014,7 +32135,7 @@
       </c>
       <c r="M57" s="44">
         <f>SUM(M9:M11)</f>
-        <v>208395</v>
+        <v>216295</v>
       </c>
       <c r="N57" s="44">
         <f>SUM(N9:N11)</f>
@@ -32022,7 +32143,7 @@
       </c>
       <c r="O57" s="44">
         <f>SUM(O9:O11)</f>
-        <v>606373</v>
+        <v>626373</v>
       </c>
       <c r="P57" s="44">
         <f>SUM(P9:P11)</f>
@@ -32070,27 +32191,27 @@
       </c>
       <c r="AA57" s="45">
         <f>SUM(AA9:AA11)</f>
-        <v>1113723.45</v>
+        <v>1121623.45</v>
       </c>
       <c r="AB57" s="45">
         <f>SUM(AB9:AB11)</f>
-        <v>10555166</v>
+        <v>10575166</v>
       </c>
       <c r="AC57" s="46">
         <f>SUM(AC9:AC11)</f>
-        <v>30125339.36</v>
+        <v>30131579.36</v>
       </c>
       <c r="AD57" s="46">
         <f>SUM(AD9:AD11)</f>
-        <v>60476498.528</v>
+        <v>60492410.528</v>
       </c>
       <c r="AE57" s="46">
         <f>SUM(AE9:AE11)</f>
-        <v>127154258.66496</v>
+        <v>127183349.54496</v>
       </c>
       <c r="AF57" s="44">
         <f>SUM(AF9:AF11)</f>
-        <v>229424986.00296</v>
+        <v>229504128.88296</v>
       </c>
     </row>
     <row r="58">
@@ -32141,7 +32262,7 @@
       </c>
       <c r="M58" s="69">
         <f>M57*12/'8_가정'!$C$11</f>
-        <v>2083.95</v>
+        <v>2162.95</v>
       </c>
       <c r="N58" s="69">
         <f>N57*12/'8_가정'!$C$11</f>
@@ -32149,7 +32270,7 @@
       </c>
       <c r="O58" s="69">
         <f>O57*12/'8_가정'!$C$11</f>
-        <v>6063.73</v>
+        <v>6263.73</v>
       </c>
       <c r="P58" s="69">
         <f>P57*12/'8_가정'!$C$11</f>
@@ -32197,23 +32318,23 @@
       </c>
       <c r="AA58" s="76">
         <f>AA57/'8_가정'!$C$11</f>
-        <v>928.102875</v>
+        <v>934.686208333333</v>
       </c>
       <c r="AB58" s="76">
         <f>AB57/'8_가정'!$C$11</f>
-        <v>8795.97166666667</v>
+        <v>8812.63833333333</v>
       </c>
       <c r="AC58" s="68">
         <f>AC57/'8_가정'!$C$11</f>
-        <v>25104.4494666667</v>
+        <v>25109.6494666667</v>
       </c>
       <c r="AD58" s="68">
         <f>AD57/'8_가정'!$C$11</f>
-        <v>50397.0821066667</v>
+        <v>50410.3421066667</v>
       </c>
       <c r="AE58" s="68">
         <f>AE57/'8_가정'!$C$11</f>
-        <v>105961.8822208</v>
+        <v>105986.1246208</v>
       </c>
     </row>
     <row r="62">
@@ -37185,7 +37306,7 @@
     <row r="2">
       <c r="A2" s="2" t="inlineStr">
         <is>
-          <t>출처: 거래처 매출표(2026-10-09 사용자 수정본) · IR 자료(2026-09-27판) · 입찰자료(KTPH-RFP-26-165-MJ) · 투자사 양식 회사연혁. 금액 미정 PoC는 매출에 반영하지 않고 신규 파이프라인 근거로만 표기.</t>
+          <t>출처: 거래처 매출표(2026-10-09) · IR 자료(2026-09-27판) · 입찰자료(KTPH-RFP-26-165-MJ) · 투자사 양식 회사연혁. 금액 미정 PoC는 매출에 반영하지 않고 신규 파이프라인 근거로만 표기.</t>
         </is>
       </c>
     </row>
@@ -37223,7 +37344,7 @@
       </c>
       <c r="G4" s="11" t="inlineStr">
         <is>
-          <t>IR 쪽</t>
+          <t>근거(IR 쪽·출처)</t>
         </is>
       </c>
       <c r="H4" s="11" t="inlineStr">
@@ -37238,7 +37359,7 @@
       </c>
       <c r="J4" s="11" t="inlineStr">
         <is>
-          <t>다음 마일스톤 · 확인 필요</t>
+          <t>다음 마일스톤</t>
         </is>
       </c>
     </row>
@@ -37289,7 +37410,7 @@
       </c>
       <c r="J5" s="80" t="inlineStr">
         <is>
-          <t>월별 실적 확정치 교체</t>
+          <t>월별 실적 마감 반영</t>
         </is>
       </c>
     </row>
@@ -37340,7 +37461,7 @@
       </c>
       <c r="J6" s="80" t="inlineStr">
         <is>
-          <t>월별 실적 확정치 교체</t>
+          <t>월별 실적 마감 반영</t>
         </is>
       </c>
     </row>
@@ -37419,7 +37540,7 @@
       </c>
       <c r="F8" s="80" t="inlineStr">
         <is>
-          <t>국내 기관·기업 대상 판매(베이비 B2B 2026-12 1,000만원 예상, 기타 B2B 2026-07~08 실적)</t>
+          <t>국내 기관·기업 대상 판매(베이비 B2B 2026-12 1,000만원 예상, 기타 B2B 2026-07~08 실적 + 2026-11 3,950천원 예상)</t>
         </is>
       </c>
       <c r="G8" s="79" t="inlineStr">
@@ -37436,11 +37557,7 @@
           <t>2026 실적·예상 + 2027 월별 입력</t>
         </is>
       </c>
-      <c r="J8" s="80" t="inlineStr">
-        <is>
-          <t>기타 B2B 2026-11 −3,950천원(마이너스 입력) 조정 근거 확인</t>
-        </is>
-      </c>
+      <c r="J8" s="80" t="inlineStr"/>
     </row>
     <row r="9" ht="36" customHeight="1">
       <c r="A9" s="79" t="inlineStr">
@@ -37489,7 +37606,7 @@
       </c>
       <c r="J9" s="80" t="inlineStr">
         <is>
-          <t>복지용구 매장 입점·실구매 개시 시점 확인</t>
+          <t>복지용구 매장 입점·실구매 개시</t>
         </is>
       </c>
     </row>
@@ -37521,7 +37638,7 @@
       </c>
       <c r="F10" s="80" t="inlineStr">
         <is>
-          <t>삼성노블카운티·KB골든라이프케어·화이트하우스 요양원·가톨릭대 성빈센트병원 등 프리미엄 요양. 2027 전국 1,000개 병원 도입 목표, 구독자 2만 명(중장기 목표)</t>
+          <t>KB골든라이프케어·화이트하우스 요양원·가톨릭대 성빈센트병원 등 프리미엄 요양(삼성노블카운티는 별도 직접 계약 행으로 집계). 2027 전국 1,000개 병원 도입 목표, 구독자 2만 명(중장기 목표)</t>
         </is>
       </c>
       <c r="G10" s="79" t="inlineStr">
@@ -37540,7 +37657,7 @@
       </c>
       <c r="J10" s="80" t="inlineStr">
         <is>
-          <t>유통사 계약 체결 여부·도입 시설 수</t>
+          <t>유통사 계약 체결·도입 시설 수 확대</t>
         </is>
       </c>
     </row>
@@ -37591,7 +37708,7 @@
       </c>
       <c r="J11" s="80" t="inlineStr">
         <is>
-          <t>계약·발주 근거 확인</t>
+          <t>정기 발주 개시</t>
         </is>
       </c>
     </row>
@@ -37623,7 +37740,7 @@
       </c>
       <c r="F12" s="80" t="inlineStr">
         <is>
-          <t>실증사업(매출표 비고: 2026-12 실증사업 3,500만원). 모델에는 2026-11 4,000천원 + 2027 분기 4,000천원 입력값을 그대로 반영</t>
+          <t>실증사업: 2026-11 4,000천원 + 2027 분기 4,000천원</t>
         </is>
       </c>
       <c r="G12" s="79" t="inlineStr">
@@ -37642,7 +37759,7 @@
       </c>
       <c r="J12" s="80" t="inlineStr">
         <is>
-          <t>★ 실증사업 3,500만원(비고) vs 입력 4,000천원 불일치 확인</t>
+          <t>실증사업 정산·후속 계약</t>
         </is>
       </c>
     </row>
@@ -37693,7 +37810,7 @@
       </c>
       <c r="J13" s="80" t="inlineStr">
         <is>
-          <t>출시일·초도 발주 확인</t>
+          <t>제품 출시·초도 발주</t>
         </is>
       </c>
     </row>
@@ -37744,7 +37861,7 @@
       </c>
       <c r="J14" s="80" t="inlineStr">
         <is>
-          <t>출시일·초도 발주 확인</t>
+          <t>제품 출시·초도 발주</t>
         </is>
       </c>
     </row>
@@ -37790,12 +37907,12 @@
       </c>
       <c r="I15" s="80" t="inlineStr">
         <is>
-          <t>2026 매출 없음, 2027 분기 발주(3·7·11월) 입력</t>
+          <t>2026 매출 없음, 2027 4개월 주기 발주(3·7·11월) 입력</t>
         </is>
       </c>
       <c r="J15" s="80" t="inlineStr">
         <is>
-          <t>시설별 발주 이력(2025·2026) 확인</t>
+          <t>오사카 시설 23곳 확대·4개월 주기 발주</t>
         </is>
       </c>
     </row>
@@ -37841,12 +37958,12 @@
       </c>
       <c r="I16" s="80" t="inlineStr">
         <is>
-          <t>2027 분기 발주(2·6·10월) 입력</t>
+          <t>2027 4개월 주기 발주(2·6·10월) 입력</t>
         </is>
       </c>
       <c r="J16" s="80" t="inlineStr">
         <is>
-          <t>등록일·실제 도입 경로(시설/재가) 확인</t>
+          <t>TAIS 채널 도입(시설·재가) 개시</t>
         </is>
       </c>
     </row>
@@ -37897,7 +38014,7 @@
       </c>
       <c r="J17" s="80" t="inlineStr">
         <is>
-          <t>계약·발주 근거 확인</t>
+          <t>발주 이행</t>
         </is>
       </c>
     </row>
@@ -37934,7 +38051,7 @@
       </c>
       <c r="G18" s="79" t="inlineStr">
         <is>
-          <t>사용자 입력(2026-10-09)</t>
+          <t>매출표(2026-10-09)</t>
         </is>
       </c>
       <c r="H18" s="81">
@@ -37948,7 +38065,7 @@
       </c>
       <c r="J18" s="80" t="inlineStr">
         <is>
-          <t>디스트리뷰터 계약·최소 발주량 확인</t>
+          <t>디스트리뷰터 계약 체결·초도 발주</t>
         </is>
       </c>
     </row>
@@ -37985,7 +38102,7 @@
       </c>
       <c r="G19" s="79" t="inlineStr">
         <is>
-          <t>사용자 입력(2026-10-09)</t>
+          <t>매출표(2026-10-09)</t>
         </is>
       </c>
       <c r="H19" s="81">
@@ -37999,7 +38116,7 @@
       </c>
       <c r="J19" s="80" t="inlineStr">
         <is>
-          <t>디스트리뷰터 계약·최소 발주량 확인</t>
+          <t>디스트리뷰터 계약 체결·초도 발주</t>
         </is>
       </c>
     </row>
@@ -38031,7 +38148,7 @@
       </c>
       <c r="F20" s="80" t="inlineStr">
         <is>
-          <t>싱가포르 총판. 2026-01 첫 수출(USD 17,440)</t>
+          <t>싱가포르 총판. 회사연혁: 2026-01 첫 수출(USD 17,440). 매출표 2026 실적은 1·3월 12,879·13,042천원, 11월 23,625천원(SGD 22,500) 예상</t>
         </is>
       </c>
       <c r="G20" s="79" t="inlineStr">
@@ -38050,7 +38167,7 @@
       </c>
       <c r="J20" s="80" t="inlineStr">
         <is>
-          <t>분기별 발주 계획 확인</t>
+          <t>4개월 주기 발주 이행</t>
         </is>
       </c>
     </row>
@@ -38101,7 +38218,7 @@
       </c>
       <c r="J21" s="80" t="inlineStr">
         <is>
-          <t>★ LOA 수령 여부·표현("계약") 정합</t>
+          <t>LOA 수령(입찰 결과) 후 병동별 납품·검수</t>
         </is>
       </c>
     </row>
@@ -38133,7 +38250,7 @@
       </c>
       <c r="F22" s="80" t="inlineStr">
         <is>
-          <t>스마트 욕창 케어 솔루션 R&amp;D 프로젝트(SGD 45,000, 2026-10 매출표 기준 47,250천원)</t>
+          <t>스마트 욕창 케어 솔루션 R&amp;D 프로젝트(SGD 45,000을 2026-10·11월 50%씩, 각 23,625천원)</t>
         </is>
       </c>
       <c r="G22" s="79" t="inlineStr">
@@ -38147,12 +38264,12 @@
       </c>
       <c r="I22" s="80" t="inlineStr">
         <is>
-          <t>2026-10 + 2027 입력</t>
+          <t>2026-10·11 + 2027 입력</t>
         </is>
       </c>
       <c r="J22" s="80" t="inlineStr">
         <is>
-          <t>계약 체결월·기간 확인</t>
+          <t>R&amp;D 프로젝트 수행·상용 전환 협의</t>
         </is>
       </c>
     </row>
@@ -38204,7 +38321,7 @@
       </c>
       <c r="J23" s="80" t="inlineStr">
         <is>
-          <t>계약서/PO·개시일 확인 후 매출표 반영</t>
+          <t>계약 개시 후 매출 반영</t>
         </is>
       </c>
     </row>
@@ -38256,7 +38373,7 @@
       </c>
       <c r="J24" s="80" t="inlineStr">
         <is>
-          <t>PoC 종료·상용 전환 조건</t>
+          <t>PoC 종료·상용 전환</t>
         </is>
       </c>
     </row>
@@ -38308,7 +38425,7 @@
       </c>
       <c r="J25" s="80" t="inlineStr">
         <is>
-          <t>PoC 일정·구매 절차</t>
+          <t>PoC 진행·구매 절차</t>
         </is>
       </c>
     </row>
@@ -38359,7 +38476,7 @@
       </c>
       <c r="J26" s="80" t="inlineStr">
         <is>
-          <t>PoC 결과·상용 계약</t>
+          <t>PoC 결과·상용 계약 협의</t>
         </is>
       </c>
     </row>
@@ -38411,7 +38528,7 @@
       </c>
       <c r="J27" s="80" t="inlineStr">
         <is>
-          <t>구매 절차 완료·발주 시점</t>
+          <t>구매 절차 완료·발주</t>
         </is>
       </c>
     </row>
@@ -38463,7 +38580,7 @@
       </c>
       <c r="J28" s="80" t="inlineStr">
         <is>
-          <t>논의 결과</t>
+          <t>사업 논의 진행</t>
         </is>
       </c>
     </row>
@@ -38515,7 +38632,7 @@
       </c>
       <c r="J29" s="80" t="inlineStr">
         <is>
-          <t>내용 확인</t>
+          <t>협의 진행</t>
         </is>
       </c>
     </row>
@@ -38547,7 +38664,7 @@
       </c>
       <c r="F30" s="80" t="inlineStr">
         <is>
-          <t>베이비 스마트 기저귀 총판. 2026-03·06 실적 + 12월 2,000만원 발주 예상</t>
+          <t>베이비 스마트 기저귀 총판. 2026-03·06 실적. USD 30,000 발주: 2026-12 선금 50%(2,000만원) + 잔금 50%(2,000만원)는 2027-01에 반영</t>
         </is>
       </c>
       <c r="G30" s="79" t="inlineStr">
@@ -38557,16 +38674,16 @@
       </c>
       <c r="H30" s="81">
         <f>'4_매출_거래처'!AW17</f>
-        <v>100000</v>
+        <v>120000</v>
       </c>
       <c r="I30" s="80" t="inlineStr">
         <is>
-          <t>2026 실적·예상 + 2027 분기 입력</t>
+          <t>2026 실적·예상 + 2027-01 잔금 + 2027 격월 입력</t>
         </is>
       </c>
       <c r="J30" s="80" t="inlineStr">
         <is>
-          <t>12월 발주 확정 여부(USD 30,000 안내 대비 2,000만원 입력) 확인</t>
+          <t>잔금 수령(2027-01 예정)</t>
         </is>
       </c>
     </row>
@@ -38617,7 +38734,7 @@
       </c>
       <c r="J31" s="80" t="inlineStr">
         <is>
-          <t>11월 발주 확정 여부 확인</t>
+          <t>11월 발주·2027 격월 발주</t>
         </is>
       </c>
     </row>
@@ -38668,7 +38785,7 @@
       </c>
       <c r="J32" s="80" t="inlineStr">
         <is>
-          <t>계약 상대·개시일 확인</t>
+          <t>계약 체결·초도 발주</t>
         </is>
       </c>
     </row>
@@ -38700,7 +38817,7 @@
       </c>
       <c r="F33" s="80" t="inlineStr">
         <is>
-          <t>유럽 총판(네덜란드·룩셈부르크·독일·폴란드). 2026-09 €24,000 반영</t>
+          <t>유럽 총판(네덜란드·룩셈부르크·독일·폴란드). 2026-09 €24,000(매출표 환산 31,303천원) 반영</t>
         </is>
       </c>
       <c r="G33" s="79" t="inlineStr">
@@ -38719,7 +38836,7 @@
       </c>
       <c r="J33" s="80" t="inlineStr">
         <is>
-          <t>★ 거래처명 표기 불일치 확인</t>
+          <t>4개월 주기 발주 이행</t>
         </is>
       </c>
     </row>
@@ -38751,7 +38868,7 @@
       </c>
       <c r="F34" s="80" t="inlineStr">
         <is>
-          <t>초기 접촉 단계(IR p.25는 스페인 표기)</t>
+          <t>폴란드 총판. 초기 접촉 단계</t>
         </is>
       </c>
       <c r="G34" s="79" t="inlineStr">
@@ -38770,7 +38887,7 @@
       </c>
       <c r="J34" s="80" t="inlineStr">
         <is>
-          <t>국가·법인 표기 확인</t>
+          <t>계약 체결·초도 발주</t>
         </is>
       </c>
     </row>
@@ -38802,7 +38919,7 @@
       </c>
       <c r="F35" s="80" t="inlineStr">
         <is>
-          <t>2026-12 5,000만원 발주 예상(매출표), 2027 분기 입력</t>
+          <t>2026-12 5,000만원 발주 예상(매출표), 2027 입력</t>
         </is>
       </c>
       <c r="G35" s="79" t="inlineStr">
@@ -38821,7 +38938,7 @@
       </c>
       <c r="J35" s="80" t="inlineStr">
         <is>
-          <t>계약·발주 근거 확인</t>
+          <t>발주 이행</t>
         </is>
       </c>
     </row>
@@ -38948,7 +39065,7 @@
       </c>
       <c r="F38" s="80" t="inlineStr">
         <is>
-          <t>금액 미정. 2029 미국 의료 유통 채널 진입의 출발점</t>
+          <t>금액 미정. 2029 미국 의료 유통 채널 진입의 출발점(PoC·초기 공급은 4_매출_거래처 미국 파이프라인 행의 2027~28 입력으로 가정 반영)</t>
         </is>
       </c>
       <c r="G38" s="79" t="inlineStr">
@@ -38968,7 +39085,7 @@
       </c>
       <c r="J38" s="80" t="inlineStr">
         <is>
-          <t>인허가(FDA 등) 일정</t>
+          <t>FDA 등 인허가 진행</t>
         </is>
       </c>
     </row>
@@ -39020,7 +39137,7 @@
       </c>
       <c r="J39" s="80" t="inlineStr">
         <is>
-          <t>계약 효력일·납품 일정</t>
+          <t>납품·검수 후 회차별 지분 발행</t>
         </is>
       </c>
     </row>
@@ -39032,7 +39149,7 @@
       </c>
       <c r="H40" s="26">
         <f>SUM(H5:H39)</f>
-        <v>10184800</v>
+        <v>10204800</v>
       </c>
     </row>
     <row r="41">
@@ -39054,7 +39171,7 @@
       </c>
       <c r="H42" s="85">
         <f>H40+H41</f>
-        <v>11184800</v>
+        <v>11204800</v>
       </c>
     </row>
     <row r="43">
@@ -39482,11 +39599,11 @@
       </c>
       <c r="L8" s="69">
         <f>'2_손익계산서'!L14</f>
-        <v>201950</v>
+        <v>178325</v>
       </c>
       <c r="M8" s="69">
         <f>'2_손익계산서'!M14</f>
-        <v>212395</v>
+        <v>243920</v>
       </c>
       <c r="N8" s="69">
         <f>'2_손익계산서'!N14</f>
@@ -39494,11 +39611,11 @@
       </c>
       <c r="O8" s="76">
         <f>'2_손익계산서'!O14</f>
-        <v>1193317</v>
+        <v>1201217</v>
       </c>
       <c r="P8" s="69">
         <f>'2_손익계산서'!P14</f>
-        <v>625900</v>
+        <v>645900</v>
       </c>
       <c r="Q8" s="69">
         <f>'2_손익계산서'!Q14</f>
@@ -39546,7 +39663,7 @@
       </c>
       <c r="AB8" s="76">
         <f>'2_손익계산서'!AB14</f>
-        <v>11184800</v>
+        <v>11204800</v>
       </c>
       <c r="AC8" s="68">
         <f>'2_손익계산서'!AC14</f>
@@ -39562,7 +39679,7 @@
       </c>
       <c r="AF8" s="69">
         <f>'2_손익계산서'!AF14</f>
-        <v>271378117</v>
+        <v>271406017</v>
       </c>
     </row>
     <row r="9">
@@ -39614,11 +39731,11 @@
       </c>
       <c r="L9" s="69">
         <f>'4_매출_거래처'!AG46</f>
-        <v>201950</v>
+        <v>178325</v>
       </c>
       <c r="M9" s="69">
         <f>'4_매출_거래처'!AH46</f>
-        <v>212395</v>
+        <v>243920</v>
       </c>
       <c r="N9" s="69">
         <f>'4_매출_거래처'!AI46</f>
@@ -39626,11 +39743,11 @@
       </c>
       <c r="O9" s="76">
         <f>'4_매출_거래처'!AV46</f>
-        <v>1193317</v>
+        <v>1201217</v>
       </c>
       <c r="P9" s="69">
         <f>'4_매출_거래처'!AJ46</f>
-        <v>625900</v>
+        <v>645900</v>
       </c>
       <c r="Q9" s="69">
         <f>'4_매출_거래처'!AK46</f>
@@ -39678,7 +39795,7 @@
       </c>
       <c r="AB9" s="76">
         <f>'4_매출_거래처'!AW46</f>
-        <v>11184800</v>
+        <v>11204800</v>
       </c>
       <c r="AC9" s="68">
         <f>'4_매출_거래처'!AX46</f>
@@ -39694,7 +39811,7 @@
       </c>
       <c r="AF9" s="69">
         <f>'4_매출_거래처'!BA46</f>
-        <v>271378117</v>
+        <v>271406017</v>
       </c>
     </row>
     <row r="10">
@@ -40325,7 +40442,7 @@
       </c>
       <c r="B16" s="7" t="inlineStr">
         <is>
-          <t>급여대장 평균 × 인상률</t>
+          <t>2026 회사 지정값, 2027~ × (1+인상률)</t>
         </is>
       </c>
       <c r="C16" s="69">
@@ -40588,7 +40705,7 @@
       </c>
       <c r="B19" s="7" t="inlineStr">
         <is>
-          <t>인원 × 월급여</t>
+          <t>급여 총액(61행) × (1−자본화율) — 자본화분은 31행</t>
         </is>
       </c>
       <c r="C19" s="44">
@@ -40720,7 +40837,7 @@
       </c>
       <c r="B20" s="7" t="inlineStr">
         <is>
-          <t>급여 × 비율</t>
+          <t>급여 총액 × 비율 × (1−자본화율)</t>
         </is>
       </c>
       <c r="C20" s="69">
@@ -40893,11 +41010,11 @@
       </c>
       <c r="L21" s="69">
         <f>L8*'8_가정'!$C$91</f>
-        <v>2423.4</v>
+        <v>2139.9</v>
       </c>
       <c r="M21" s="69">
         <f>M8*'8_가정'!$C$91</f>
-        <v>2548.74</v>
+        <v>2927.04</v>
       </c>
       <c r="N21" s="69">
         <f>N8*'8_가정'!$C$91</f>
@@ -40905,11 +41022,11 @@
       </c>
       <c r="O21" s="23">
         <f>SUM(C21:N21)</f>
-        <v>14319.804</v>
+        <v>14414.604</v>
       </c>
       <c r="P21" s="69">
         <f>P8*'8_가정'!$D$91</f>
-        <v>15647.5</v>
+        <v>16147.5</v>
       </c>
       <c r="Q21" s="69">
         <f>Q8*'8_가정'!$D$91</f>
@@ -40957,7 +41074,7 @@
       </c>
       <c r="AB21" s="23">
         <f>SUM(P21:AA21)</f>
-        <v>279620</v>
+        <v>280120</v>
       </c>
       <c r="AC21" s="68">
         <f>AC8*'8_가정'!$E$91</f>
@@ -40973,7 +41090,7 @@
       </c>
       <c r="AF21" s="25">
         <f>O21+AB21+AC21+AD21+AE21</f>
-        <v>7717939.804</v>
+        <v>7718534.604</v>
       </c>
     </row>
     <row r="22">
@@ -41025,11 +41142,11 @@
       </c>
       <c r="L22" s="69">
         <f>L8*'8_가정'!$C$92</f>
-        <v>2423.4</v>
+        <v>2139.9</v>
       </c>
       <c r="M22" s="69">
         <f>M8*'8_가정'!$C$92</f>
-        <v>2548.74</v>
+        <v>2927.04</v>
       </c>
       <c r="N22" s="69">
         <f>N8*'8_가정'!$C$92</f>
@@ -41037,11 +41154,11 @@
       </c>
       <c r="O22" s="23">
         <f>SUM(C22:N22)</f>
-        <v>14319.804</v>
+        <v>14414.604</v>
       </c>
       <c r="P22" s="69">
         <f>P8*'8_가정'!$D$92</f>
-        <v>12518</v>
+        <v>12918</v>
       </c>
       <c r="Q22" s="69">
         <f>Q8*'8_가정'!$D$92</f>
@@ -41089,7 +41206,7 @@
       </c>
       <c r="AB22" s="23">
         <f>SUM(P22:AA22)</f>
-        <v>223696</v>
+        <v>224096</v>
       </c>
       <c r="AC22" s="68">
         <f>AC8*'8_가정'!$E$92</f>
@@ -41105,7 +41222,7 @@
       </c>
       <c r="AF22" s="25">
         <f>O22+AB22+AC22+AD22+AE22</f>
-        <v>5936015.804</v>
+        <v>5936510.604</v>
       </c>
     </row>
     <row r="23">
@@ -41157,11 +41274,11 @@
       </c>
       <c r="L23" s="69">
         <f>L8*'8_가정'!$C$93</f>
-        <v>5048.75</v>
+        <v>4458.125</v>
       </c>
       <c r="M23" s="69">
         <f>M8*'8_가정'!$C$93</f>
-        <v>5309.875</v>
+        <v>6098</v>
       </c>
       <c r="N23" s="69">
         <f>N8*'8_가정'!$C$93</f>
@@ -41169,11 +41286,11 @@
       </c>
       <c r="O23" s="23">
         <f>SUM(C23:N23)</f>
-        <v>29832.925</v>
+        <v>30030.425</v>
       </c>
       <c r="P23" s="69">
         <f>P8*'8_가정'!$D$93</f>
-        <v>21906.5</v>
+        <v>22606.5</v>
       </c>
       <c r="Q23" s="69">
         <f>Q8*'8_가정'!$D$93</f>
@@ -41221,7 +41338,7 @@
       </c>
       <c r="AB23" s="23">
         <f>SUM(P23:AA23)</f>
-        <v>391468</v>
+        <v>392168</v>
       </c>
       <c r="AC23" s="68">
         <f>AC8*'8_가정'!$E$93</f>
@@ -41237,7 +41354,7 @@
       </c>
       <c r="AF23" s="25">
         <f>O23+AB23+AC23+AD23+AE23</f>
-        <v>9276300.925</v>
+        <v>9277198.425</v>
       </c>
     </row>
     <row r="24">
@@ -41289,11 +41406,11 @@
       </c>
       <c r="L24" s="69">
         <f>L8*'8_가정'!$C$94</f>
-        <v>7068.25</v>
+        <v>6241.375</v>
       </c>
       <c r="M24" s="69">
         <f>M8*'8_가정'!$C$94</f>
-        <v>7433.825</v>
+        <v>8537.2</v>
       </c>
       <c r="N24" s="69">
         <f>N8*'8_가정'!$C$94</f>
@@ -41301,11 +41418,11 @@
       </c>
       <c r="O24" s="23">
         <f>SUM(C24:N24)</f>
-        <v>41766.095</v>
+        <v>42042.595</v>
       </c>
       <c r="P24" s="69">
         <f>P8*'8_가정'!$D$94</f>
-        <v>21906.5</v>
+        <v>22606.5</v>
       </c>
       <c r="Q24" s="69">
         <f>Q8*'8_가정'!$D$94</f>
@@ -41353,7 +41470,7 @@
       </c>
       <c r="AB24" s="23">
         <f>SUM(P24:AA24)</f>
-        <v>391468</v>
+        <v>392168</v>
       </c>
       <c r="AC24" s="68">
         <f>AC8*'8_가정'!$E$94</f>
@@ -41369,7 +41486,7 @@
       </c>
       <c r="AF24" s="25">
         <f>O24+AB24+AC24+AD24+AE24</f>
-        <v>8355234.095</v>
+        <v>8356210.595</v>
       </c>
     </row>
     <row r="25">
@@ -41817,11 +41934,11 @@
       </c>
       <c r="L28" s="69">
         <f>L8*'8_가정'!$C$95</f>
-        <v>807.8</v>
+        <v>713.3</v>
       </c>
       <c r="M28" s="69">
         <f>M8*'8_가정'!$C$95</f>
-        <v>849.58</v>
+        <v>975.68</v>
       </c>
       <c r="N28" s="69">
         <f>N8*'8_가정'!$C$95</f>
@@ -41829,11 +41946,11 @@
       </c>
       <c r="O28" s="23">
         <f>SUM(C28:N28)</f>
-        <v>4773.268</v>
+        <v>4804.868</v>
       </c>
       <c r="P28" s="69">
         <f>P8*'8_가정'!$D$95</f>
-        <v>3129.5</v>
+        <v>3229.5</v>
       </c>
       <c r="Q28" s="69">
         <f>Q8*'8_가정'!$D$95</f>
@@ -41881,7 +41998,7 @@
       </c>
       <c r="AB28" s="23">
         <f>SUM(P28:AA28)</f>
-        <v>55924</v>
+        <v>56024</v>
       </c>
       <c r="AC28" s="68">
         <f>AC8*'8_가정'!$E$95</f>
@@ -41897,7 +42014,7 @@
       </c>
       <c r="AF28" s="25">
         <f>O28+AB28+AC28+AD28+AE28</f>
-        <v>1355697.268</v>
+        <v>1355828.868</v>
       </c>
     </row>
     <row r="29">
@@ -41949,11 +42066,11 @@
       </c>
       <c r="L29" s="69">
         <f>L8*'8_가정'!$C$96</f>
-        <v>4039</v>
+        <v>3566.5</v>
       </c>
       <c r="M29" s="69">
         <f>M8*'8_가정'!$C$96</f>
-        <v>4247.9</v>
+        <v>4878.4</v>
       </c>
       <c r="N29" s="69">
         <f>N8*'8_가정'!$C$96</f>
@@ -41961,11 +42078,11 @@
       </c>
       <c r="O29" s="23">
         <f>SUM(C29:N29)</f>
-        <v>23866.34</v>
+        <v>24024.34</v>
       </c>
       <c r="P29" s="69">
         <f>P8*'8_가정'!$D$96</f>
-        <v>18777</v>
+        <v>19377</v>
       </c>
       <c r="Q29" s="69">
         <f>Q8*'8_가정'!$D$96</f>
@@ -42013,7 +42130,7 @@
       </c>
       <c r="AB29" s="23">
         <f>SUM(P29:AA29)</f>
-        <v>335544</v>
+        <v>336144</v>
       </c>
       <c r="AC29" s="68">
         <f>AC8*'8_가정'!$E$96</f>
@@ -42029,7 +42146,7 @@
       </c>
       <c r="AF29" s="25">
         <f>O29+AB29+AC29+AD29+AE29</f>
-        <v>6501410.34</v>
+        <v>6502168.34</v>
       </c>
     </row>
     <row r="30">
@@ -42076,11 +42193,11 @@
       </c>
       <c r="L30" s="26">
         <f>SUM(L19:L29)</f>
-        <v>59137.836</v>
+        <v>56586.336</v>
       </c>
       <c r="M30" s="26">
         <f>SUM(M19:M29)</f>
-        <v>60265.896</v>
+        <v>63670.596</v>
       </c>
       <c r="N30" s="26">
         <f>SUM(N19:N29)</f>
@@ -42088,11 +42205,11 @@
       </c>
       <c r="O30" s="27">
         <f>SUM(O19:O29)</f>
-        <v>576805.068</v>
+        <v>577658.268</v>
       </c>
       <c r="P30" s="26">
         <f>SUM(P19:P29)</f>
-        <v>201997.571546667</v>
+        <v>204997.571546667</v>
       </c>
       <c r="Q30" s="26">
         <f>SUM(Q19:Q29)</f>
@@ -42140,7 +42257,7 @@
       </c>
       <c r="AB30" s="27">
         <f>SUM(AB19:AB29)</f>
-        <v>3279981.06656</v>
+        <v>3282981.06656</v>
       </c>
       <c r="AC30" s="28">
         <f>SUM(AC19:AC29)</f>
@@ -42156,7 +42273,7 @@
       </c>
       <c r="AF30" s="26">
         <f>SUM(AF19:AF29)</f>
-        <v>69731666.2445242</v>
+        <v>69735519.4445242</v>
       </c>
     </row>
     <row r="31">
@@ -42311,55 +42428,55 @@
       </c>
       <c r="C33" s="69">
         <f>'8_가정'!$C$106/12</f>
-        <v>6397.17458333333</v>
+        <v>6420.21625</v>
       </c>
       <c r="D33" s="69">
         <f>'8_가정'!$C$106/12</f>
-        <v>6397.17458333333</v>
+        <v>6420.21625</v>
       </c>
       <c r="E33" s="69">
         <f>'8_가정'!$C$106/12</f>
-        <v>6397.17458333333</v>
+        <v>6420.21625</v>
       </c>
       <c r="F33" s="69">
         <f>'8_가정'!$C$106/12</f>
-        <v>6397.17458333333</v>
+        <v>6420.21625</v>
       </c>
       <c r="G33" s="69">
         <f>'8_가정'!$C$106/12</f>
-        <v>6397.17458333333</v>
+        <v>6420.21625</v>
       </c>
       <c r="H33" s="69">
         <f>'8_가정'!$C$106/12</f>
-        <v>6397.17458333333</v>
+        <v>6420.21625</v>
       </c>
       <c r="I33" s="69">
         <f>'8_가정'!$C$106/12</f>
-        <v>6397.17458333333</v>
+        <v>6420.21625</v>
       </c>
       <c r="J33" s="69">
         <f>'8_가정'!$C$106/12</f>
-        <v>6397.17458333333</v>
+        <v>6420.21625</v>
       </c>
       <c r="K33" s="69">
         <f>'8_가정'!$C$106/12</f>
-        <v>6397.17458333333</v>
+        <v>6420.21625</v>
       </c>
       <c r="L33" s="69">
         <f>'8_가정'!$C$106/12</f>
-        <v>6397.17458333333</v>
+        <v>6420.21625</v>
       </c>
       <c r="M33" s="69">
         <f>'8_가정'!$C$106/12</f>
-        <v>6397.17458333333</v>
+        <v>6420.21625</v>
       </c>
       <c r="N33" s="69">
         <f>'8_가정'!$C$106/12</f>
-        <v>6397.17458333333</v>
+        <v>6420.21625</v>
       </c>
       <c r="O33" s="23">
         <f>SUM(C33:N33)</f>
-        <v>76766.095</v>
+        <v>77042.595</v>
       </c>
       <c r="P33" s="69">
         <f>'8_가정'!$D$106/12</f>
@@ -42427,7 +42544,7 @@
       </c>
       <c r="AF33" s="25">
         <f>O33+AB33+AC33+AD33+AE33</f>
-        <v>676766.095</v>
+        <v>677042.595</v>
       </c>
     </row>
     <row r="34">
@@ -42660,23 +42777,23 @@
       </c>
       <c r="O40" s="76">
         <f>'2_손익계산서'!O55</f>
-        <v>38099.5621</v>
+        <v>41411.2421000001</v>
       </c>
       <c r="AB40" s="76">
         <f>'2_손익계산서'!AB55</f>
-        <v>1388664.01344</v>
+        <v>1393404.01344</v>
       </c>
       <c r="AC40" s="68">
         <f>'2_손익계산서'!AC55</f>
-        <v>3641403.6193904</v>
+        <v>3640402.6193904</v>
       </c>
       <c r="AD40" s="68">
         <f>'2_손익계산서'!AD55</f>
-        <v>9348207.19432603</v>
+        <v>9345703.39432603</v>
       </c>
       <c r="AE40" s="68">
         <f>'2_손익계산서'!AE55</f>
-        <v>25128282.577049</v>
+        <v>25123496.434649</v>
       </c>
     </row>
     <row r="41">
@@ -42691,11 +42808,11 @@
       </c>
       <c r="AB41" s="45">
         <f>O44</f>
-        <v>2993982.4379</v>
+        <v>2990670.7579</v>
       </c>
       <c r="AC41" s="46">
         <f>AB44</f>
-        <v>1605318.42446</v>
+        <v>1597266.74446</v>
       </c>
       <c r="AD41" s="46">
         <f>AC44</f>
@@ -42714,15 +42831,15 @@
       </c>
       <c r="O42" s="76">
         <f>MIN(O41,MAX(0,O40)*'8_가정'!$C$111)</f>
-        <v>38099.5621</v>
+        <v>41411.2421000001</v>
       </c>
       <c r="AB42" s="76">
         <f>MIN(AB41,MAX(0,AB40)*'8_가정'!$C$111)</f>
-        <v>1388664.01344</v>
+        <v>1393404.01344</v>
       </c>
       <c r="AC42" s="68">
         <f>MIN(AC41,MAX(0,AC40)*'8_가정'!$C$111)</f>
-        <v>1605318.42446</v>
+        <v>1597266.74446</v>
       </c>
       <c r="AD42" s="68">
         <f>MIN(AD41,MAX(0,AD40)*'8_가정'!$C$111)</f>
@@ -42768,11 +42885,11 @@
       </c>
       <c r="O44" s="45">
         <f>O41-O42+O43</f>
-        <v>2993982.4379</v>
+        <v>2990670.7579</v>
       </c>
       <c r="AB44" s="45">
         <f>AB41-AB42+AB43</f>
-        <v>1605318.42446</v>
+        <v>1597266.74446</v>
       </c>
       <c r="AC44" s="46">
         <f>AC41-AC42+AC43</f>
@@ -42803,15 +42920,15 @@
       </c>
       <c r="AC45" s="46">
         <f>MAX(0,AC40)-AC42</f>
-        <v>2036085.1949304</v>
+        <v>2043135.8749304</v>
       </c>
       <c r="AD45" s="46">
         <f>MAX(0,AD40)-AD42</f>
-        <v>9348207.19432603</v>
+        <v>9345703.39432603</v>
       </c>
       <c r="AE45" s="46">
         <f>MAX(0,AE40)-AE42</f>
-        <v>25128282.577049</v>
+        <v>25123496.434649</v>
       </c>
     </row>
     <row r="46">
@@ -42830,15 +42947,15 @@
       </c>
       <c r="AC46" s="68">
         <f>MIN(AC45,'8_가정'!$C$112)*'8_가정'!$C$113+MAX(0,MIN(AC45,'8_가정'!$D$112)-'8_가정'!$C$112)*'8_가정'!$D$113+MAX(0,MIN(AC45,'8_가정'!$E$112)-'8_가정'!$D$112)*'8_가정'!$E$113+MAX(0,AC45-'8_가정'!$E$112)*'8_가정'!$F$113</f>
-        <v>387217.03898608</v>
+        <v>388627.174986079</v>
       </c>
       <c r="AD46" s="68">
         <f>MIN(AD45,'8_가정'!$C$112)*'8_가정'!$C$113+MAX(0,MIN(AD45,'8_가정'!$D$112)-'8_가정'!$C$112)*'8_가정'!$D$113+MAX(0,MIN(AD45,'8_가정'!$E$112)-'8_가정'!$D$112)*'8_가정'!$E$113+MAX(0,AD45-'8_가정'!$E$112)*'8_가정'!$F$113</f>
-        <v>1849641.43886521</v>
+        <v>1849140.67886521</v>
       </c>
       <c r="AE46" s="68">
         <f>MIN(AE45,'8_가정'!$C$112)*'8_가정'!$C$113+MAX(0,MIN(AE45,'8_가정'!$D$112)-'8_가정'!$C$112)*'8_가정'!$D$113+MAX(0,MIN(AE45,'8_가정'!$E$112)-'8_가정'!$D$112)*'8_가정'!$E$113+MAX(0,AE45-'8_가정'!$E$112)*'8_가정'!$F$113</f>
-        <v>5108222.16695077</v>
+        <v>5107169.21562277</v>
       </c>
     </row>
     <row r="47">
@@ -42857,15 +42974,15 @@
       </c>
       <c r="AC47" s="68">
         <f>AC46*'8_가정'!$C$114</f>
-        <v>38721.703898608</v>
+        <v>38862.7174986079</v>
       </c>
       <c r="AD47" s="68">
         <f>AD46*'8_가정'!$C$114</f>
-        <v>184964.143886521</v>
+        <v>184914.067886521</v>
       </c>
       <c r="AE47" s="68">
         <f>AE46*'8_가정'!$C$114</f>
-        <v>510822.216695077</v>
+        <v>510716.921562278</v>
       </c>
     </row>
     <row r="48">
@@ -42884,15 +43001,15 @@
       </c>
       <c r="AC48" s="35">
         <f>AC46+AC47</f>
-        <v>425938.742884688</v>
+        <v>427489.892484687</v>
       </c>
       <c r="AD48" s="35">
         <f>AD46+AD47</f>
-        <v>2034605.58275173</v>
+        <v>2034054.74675173</v>
       </c>
       <c r="AE48" s="35">
         <f>AE46+AE47</f>
-        <v>5619044.38364585</v>
+        <v>5617886.13718505</v>
       </c>
     </row>
     <row r="49">
@@ -43007,25 +43124,39 @@
       </c>
       <c r="AC49" s="46">
         <f>AC48</f>
-        <v>425938.742884688</v>
+        <v>427489.892484687</v>
       </c>
       <c r="AD49" s="46">
         <f>AD48</f>
-        <v>2034605.58275173</v>
+        <v>2034054.74675173</v>
       </c>
       <c r="AE49" s="46">
         <f>AE48</f>
-        <v>5619044.38364585</v>
+        <v>5617886.13718505</v>
       </c>
       <c r="AF49" s="25">
         <f>O49+AB49+AC49+AD49+AE49</f>
-        <v>8079588.70928227</v>
+        <v>8079430.77642147</v>
+      </c>
+    </row>
+    <row r="50">
+      <c r="A50" s="53" t="inlineStr">
+        <is>
+          <t>※ 법인세는 연간 세전이익 기준으로 산출하고(이월결손금 공제 후 누진세율 + 지방소득세) 월별로는 매출 비중으로 배분합니다. 세액공제·최저한세·이연법인세는 미반영.</t>
+        </is>
       </c>
     </row>
     <row r="51">
-      <c r="A51" s="53" t="inlineStr">
-        <is>
-          <t>※ 법인세는 연간 세전이익 기준으로 산출하고(이월결손금 공제 후 누진세율 + 지방소득세) 월별로는 매출 비중으로 배분합니다. 세액공제·최저한세·이연법인세는 미반영.</t>
+      <c r="A51" s="3" t="inlineStr">
+        <is>
+          <t>F. 참고: 운전자본 소요(손익 외 추정) — 차입금·증자 필요성 가늠용</t>
+        </is>
+      </c>
+    </row>
+    <row r="52">
+      <c r="A52" s="53" t="inlineStr">
+        <is>
+          <t>※ 운전자본은 손익계산서 범위 밖의 참고 추정입니다. 순운전자본 증가분은 영업이익·차입·증자로 조달하는 것으로 가정합니다(차입금 가정은 위 D절 참조).</t>
         </is>
       </c>
     </row>
@@ -43037,11 +43168,11 @@
       </c>
       <c r="O53" s="76">
         <f>O8*'8_가정'!$C$115/365</f>
-        <v>196161.698630137</v>
+        <v>197460.328767123</v>
       </c>
       <c r="AB53" s="76">
         <f>AB8*'8_가정'!$C$115/365</f>
-        <v>1838597.26027397</v>
+        <v>1841884.93150685</v>
       </c>
       <c r="AC53" s="68">
         <f>AC8*'8_가정'!$C$115/365</f>
@@ -43064,23 +43195,23 @@
       </c>
       <c r="O54" s="76">
         <f>'2_손익계산서'!O30*'8_가정'!$C$116/365</f>
-        <v>98233.8793808219</v>
+        <v>98893.3237643836</v>
       </c>
       <c r="AB54" s="76">
         <f>'2_손익계산서'!AB30*'8_가정'!$C$116/365</f>
-        <v>1107839.16493151</v>
+        <v>1109854.50739726</v>
       </c>
       <c r="AC54" s="68">
         <f>'2_손익계산서'!AC30*'8_가정'!$C$116/365</f>
-        <v>3275013.31693151</v>
+        <v>3275177.86487671</v>
       </c>
       <c r="AD54" s="68">
         <f>'2_손익계산서'!AD30*'8_가정'!$C$116/365</f>
-        <v>6913825.76913534</v>
+        <v>6914237.35269699</v>
       </c>
       <c r="AE54" s="68">
         <f>'2_손익계산서'!AE30*'8_가정'!$C$116/365</f>
-        <v>15159636.5028543</v>
+        <v>15160423.2659886</v>
       </c>
     </row>
     <row r="55">
@@ -43091,23 +43222,23 @@
       </c>
       <c r="O55" s="76">
         <f>'2_손익계산서'!O30*'8_가정'!$C$117/365</f>
-        <v>73675.4095356165</v>
+        <v>74169.9928232877</v>
       </c>
       <c r="AB55" s="76">
         <f>'2_손익계산서'!AB30*'8_가정'!$C$117/365</f>
-        <v>830879.37369863</v>
+        <v>832390.880547945</v>
       </c>
       <c r="AC55" s="68">
         <f>'2_손익계산서'!AC30*'8_가정'!$C$117/365</f>
-        <v>2456259.98769863</v>
+        <v>2456383.39865753</v>
       </c>
       <c r="AD55" s="68">
         <f>'2_손익계산서'!AD30*'8_가정'!$C$117/365</f>
-        <v>5185369.32685151</v>
+        <v>5185678.01452274</v>
       </c>
       <c r="AE55" s="68">
         <f>'2_손익계산서'!AE30*'8_가정'!$C$117/365</f>
-        <v>11369727.3771407</v>
+        <v>11370317.4494914</v>
       </c>
     </row>
     <row r="56">
@@ -43118,23 +43249,23 @@
       </c>
       <c r="O56" s="27">
         <f>O53+O54-O55</f>
-        <v>220720.168475342</v>
+        <v>222183.659708219</v>
       </c>
       <c r="AB56" s="27">
         <f>AB53+AB54-AB55</f>
-        <v>2115557.05150685</v>
+        <v>2119348.55835616</v>
       </c>
       <c r="AC56" s="28">
         <f>AC53+AC54-AC55</f>
-        <v>6243410.86347945</v>
+        <v>6243452.00046575</v>
       </c>
       <c r="AD56" s="28">
         <f>AD53+AD54-AD55</f>
-        <v>13235305.7573523</v>
+        <v>13235408.6532427</v>
       </c>
       <c r="AE56" s="28">
         <f>AE53+AE54-AE55</f>
-        <v>29433744.7421519</v>
+        <v>29433941.4329355</v>
       </c>
     </row>
     <row r="57">
@@ -43145,23 +43276,23 @@
       </c>
       <c r="O57" s="76">
         <f>O56-('3_연간손익'!$C$7*'8_가정'!$C$115/365+'3_연간손익'!$C$9*('8_가정'!$C$116-'8_가정'!$C$117)/365)</f>
-        <v>63841.5355438356</v>
+        <v>65305.0267767123</v>
       </c>
       <c r="AB57" s="45">
         <f>AB56-O56</f>
-        <v>1894836.88303151</v>
+        <v>1897164.89864795</v>
       </c>
       <c r="AC57" s="46">
         <f>AC56-AB56</f>
-        <v>4127853.8119726</v>
+        <v>4124103.44210959</v>
       </c>
       <c r="AD57" s="46">
         <f>AD56-AC56</f>
-        <v>6991894.89387288</v>
+        <v>6991956.65277699</v>
       </c>
       <c r="AE57" s="46">
         <f>AE56-AD56</f>
-        <v>16198438.9847996</v>
+        <v>16198532.7796928</v>
       </c>
     </row>
     <row r="58">
@@ -43172,29 +43303,29 @@
       </c>
       <c r="O58" s="94">
         <f>IFERROR(O35/O56,0)</f>
-        <v>5.43674829667438</v>
+        <v>5.40093723172933</v>
       </c>
       <c r="AB58" s="94">
         <f>IFERROR(AB35/AB56,0)</f>
-        <v>0.945377482765335</v>
+        <v>0.943686205893034</v>
       </c>
       <c r="AC58" s="95">
         <f>IFERROR(AC35/AC56,0)</f>
-        <v>0.961013159504963</v>
+        <v>0.961006827561485</v>
       </c>
       <c r="AD58" s="95">
         <f>IFERROR(AD35/AD56,0)</f>
-        <v>0.755554891087039</v>
+        <v>0.755549017185046</v>
       </c>
       <c r="AE58" s="95">
         <f>IFERROR(AE35/AE56,0)</f>
-        <v>0.407695320630231</v>
+        <v>0.407692596227444</v>
       </c>
     </row>
     <row r="59">
-      <c r="A59" s="53" t="inlineStr">
-        <is>
-          <t>※ 운전자본은 손익계산서 범위 밖의 참고 추정입니다. 순운전자본 증가분은 영업이익·차입·증자로 조달해야 하며, 차입금 가정(위 D절)이 이를 충분히 덮는지 점검하세요.</t>
+      <c r="A59" s="3" t="inlineStr">
+        <is>
+          <t>G. 급여 총액 · 평균 급여 (급여·개발비 자본화 산출 근거)</t>
         </is>
       </c>
     </row>
@@ -43590,7 +43721,7 @@
       </c>
       <c r="I7" s="101" t="inlineStr">
         <is>
-          <t>IR p.35 고정 환율 1,400원/달러(2026-10-02 서울 종가 1,350.60). 참고용(계약 통화 환산 비교)</t>
+          <t>IR p.35 고정 환율 1,400원/달러(2026-10-02 서울 종가 1,350.60). 참고용(계약 통화 환산 비교). 거래처 매출표는 건별 적용 환율(SGD 약 1,050·EUR 약 1,304 등)로 환산되어 본 환율과 다를 수 있음</t>
         </is>
       </c>
     </row>
@@ -43992,7 +44123,7 @@
       </c>
       <c r="I28" s="101" t="inlineStr">
         <is>
-          <t>2025 실적 GM 53%(매출총이익 4.53억/매출 8.54억). 소모품(기저귀) 비중 확대에 따라 2027~ 41% 내외로 보수적 설정. Hansoms 현물출자(최대 USD 448k 상당 제품 납품) 효과는 미반영</t>
+          <t>2025 실적 GM 53%(매출총이익 4.53억/매출 8.54억). 소모품(기저귀) 비중 확대에 따라 2027~ 매출총이익률 약 40%(제품별 원가율 + 운영성 원가)로 보수적 설정. Hansoms 현물출자(최대 USD 448k 상당 제품 납품) 효과는 미반영</t>
         </is>
       </c>
     </row>
@@ -44080,7 +44211,7 @@
     <row r="32">
       <c r="A32" s="15" t="inlineStr">
         <is>
-          <t>스마트 욕창 케어(2027 Q4 출시)</t>
+          <t>스마트 욕창 케어(2027 출시)</t>
         </is>
       </c>
       <c r="B32" s="15" t="inlineStr">
@@ -44322,7 +44453,7 @@
       </c>
       <c r="B42" s="15" t="inlineStr">
         <is>
-          <t>정액 구독형(시설·정부·기관) — 스마트 욕창 케어(2027 Q4 출시)</t>
+          <t>정액 구독형(시설·정부·기관) — 스마트 욕창 케어(2027 출시)</t>
         </is>
       </c>
       <c r="C42" s="65" t="n">
@@ -44484,7 +44615,7 @@
       </c>
       <c r="B48" s="15" t="inlineStr">
         <is>
-          <t>복지용구(기저귀센서 급여) — 센서·스티커 중심 — 스마트 욕창 케어(2027 Q4 출시)</t>
+          <t>복지용구(기저귀센서 급여) — 센서·스티커 중심 — 스마트 욕창 케어(2027 출시)</t>
         </is>
       </c>
       <c r="C48" s="65" t="n">
@@ -44646,7 +44777,7 @@
       </c>
       <c r="B54" s="15" t="inlineStr">
         <is>
-          <t>총판 공급형(소모품+센서) — 스마트 욕창 케어(2027 Q4 출시)</t>
+          <t>총판 공급형(소모품+센서) — 스마트 욕창 케어(2027 출시)</t>
         </is>
       </c>
       <c r="C54" s="65" t="n">
@@ -44808,7 +44939,7 @@
       </c>
       <c r="B60" s="15" t="inlineStr">
         <is>
-          <t>베이비 B2C 구독 — 스마트 욕창 케어(2027 Q4 출시)</t>
+          <t>베이비 B2C 구독 — 스마트 욕창 케어(2027 출시)</t>
         </is>
       </c>
       <c r="C60" s="65" t="n">
@@ -44970,7 +45101,7 @@
       </c>
       <c r="B66" s="15" t="inlineStr">
         <is>
-          <t>병원 하드웨어 프로젝트(NHG) — 스마트 욕창 케어(2027 Q4 출시)</t>
+          <t>병원 하드웨어 프로젝트(NHG) — 스마트 욕창 케어(2027 출시)</t>
         </is>
       </c>
       <c r="C66" s="65" t="n">
@@ -45132,7 +45263,7 @@
       </c>
       <c r="B72" s="15" t="inlineStr">
         <is>
-          <t>R&amp;D·PoC 용역 — 스마트 욕창 케어(2027 Q4 출시)</t>
+          <t>R&amp;D·PoC 용역 — 스마트 욕창 케어(2027 출시)</t>
         </is>
       </c>
       <c r="C72" s="65" t="n">
@@ -45294,7 +45425,7 @@
       </c>
       <c r="B78" s="15" t="inlineStr">
         <is>
-          <t>신규 파이프라인(신제품 비중 확대) — 스마트 욕창 케어(2027 Q4 출시)</t>
+          <t>신규 파이프라인(신제품 비중 확대) — 스마트 욕창 케어(2027 출시)</t>
         </is>
       </c>
       <c r="C78" s="65" t="n">
@@ -45422,7 +45553,7 @@
       </c>
       <c r="B85" s="15" t="inlineStr">
         <is>
-          <t>2026 = 급상여대장 대표 제외 평균, 2027~ = 전년 × (1+인상률)</t>
+          <t>2026 = 회사 지정값(급상여대장 2026-09 대표 제외 평균은 약 4,333), 2027~ = 전년 × (1+인상률)</t>
         </is>
       </c>
       <c r="C85" s="67" t="n">
@@ -45518,7 +45649,7 @@
       </c>
       <c r="I90" s="101" t="inlineStr">
         <is>
-          <t>2025 판관비 4.27억은 7명 급여 총액(약 5억 안팎)보다 낮아 연구 인력 인건비 일부가 개발비(자산 19.8억)로 자본화된 구조와 일관. 자산화 요건(기술적 실현가능성·판매 의도·미래 경제적 효익 등) 충족과 감사인 수용 여부 확인 필요. 자본화분은 2027-01부터 상각(개발비 상각 행)</t>
+          <t>2025 판관비 4.27억은 7명 급여 총액(약 5억 안팎)보다 낮아 연구 인력 인건비 일부가 개발비(자산 19.8억)로 자본화된 구조와 일관. 자산화 요건(기술적 실현가능성·판매 의도·미래 경제적 효익 등) 충족과 감사인 수용을 전제로 한 가정. 2025.12 개발비 잔액(19.8억)은 2027-01부터 상각하고, 2027~ 신규 자본화분은 다음 해부터 상각(개발비 상각 행 참조)</t>
         </is>
       </c>
     </row>
@@ -45631,7 +45762,7 @@
       </c>
       <c r="I94" s="101" t="inlineStr">
         <is>
-          <t>개발비 자본화(BS 개발비 19.8억)는 별도. 신규 자본화·상각 증가분은 미반영(보수적 가정은 상각에서 반영)</t>
+          <t>개발비 자본화(BS 개발비 19.8억)는 별도. 2027~ 신규 자본화분은 다음 해부터 5년 정액 상각으로 아래 상각 행에 가산</t>
         </is>
       </c>
     </row>
@@ -45770,7 +45901,7 @@
       </c>
       <c r="B100" s="15" t="inlineStr">
         <is>
-          <t>2025.12 개발비 잔액 19.8억을 5년 정액 상각, 2027-01 개시(신규 자본화는 미반영)</t>
+          <t>2025.12 개발비 잔액 19.8억을 5년 정액 상각, 2027-01 개시(2027~ 신규 자본화분은 다음 해부터 가산)</t>
         </is>
       </c>
       <c r="C100" s="67" t="n">
@@ -45780,20 +45911,20 @@
         <v>395953</v>
       </c>
       <c r="E100" s="109">
-        <f>395953+('7_비용인력'!$AB$31)/5</f>
+        <f>$D$100+('7_비용인력'!$AB$31)/5</f>
         <v>438068.403328</v>
       </c>
       <c r="F100" s="109">
-        <f>395953+('7_비용인력'!$AB$31+'7_비용인력'!$AC$31)/5</f>
+        <f>$D$100+('7_비용인력'!$AB$31+'7_비용인력'!$AC$31)/5</f>
         <v>509880.18775648</v>
       </c>
       <c r="G100" s="109">
-        <f>395953+('7_비용인력'!$AB$31+'7_비용인력'!$AC$31+'7_비용인력'!$AD$31)/5</f>
+        <f>$D$100+('7_비용인력'!$AB$31+'7_비용인력'!$AC$31+'7_비용인력'!$AD$31)/5</f>
         <v>580393.933605717</v>
       </c>
       <c r="I100" s="101" t="inlineStr">
         <is>
-          <t>2027~ 기존 개발비 잔액 상각(연 395,953천원) + 2027년 이후 신규 자본화분의 5년 정액 상각을 다음 해부터 가산. 2026 자본화분(약 2.3억)은 정부과제 대응 자산차감분과 상계되는 것으로 보아 별도 가산하지 않음(보수 여지)</t>
+          <t>2027~ 기존 개발비 잔액 상각(연 395,953천원) + 2027년 이후 신규 자본화분의 5년 정액 상각을 다음 해부터 가산(신규 자본화분은 선택 시나리오의 인원에 연동되어 S2·S3에서 소폭 감소). 2026 자본화분(약 2.3억)은 정부과제 대응 자산차감분과 상계되는 것으로 보아 별도 가산하지 않음(보수 여지)</t>
         </is>
       </c>
     </row>
@@ -45861,7 +45992,7 @@
       </c>
       <c r="I104" s="101" t="inlineStr">
         <is>
-          <t>투자사 양식 차입금 현황(2025감사보고서 주석 5). 현재 잔액·만기 확인 필요</t>
+          <t>투자사 양식 차입금 현황(2025감사보고서 주석 5). 잔액·만기는 변동될 수 있음</t>
         </is>
       </c>
     </row>
@@ -45905,7 +46036,7 @@
       </c>
       <c r="C106" s="109">
         <f>MIN('8_가정'!$C$107,'7_비용인력'!$O$24+MAX(0,'8_가정'!$C$109-'8_가정'!$C$90)*'7_비용인력'!$O$61*(1+'8_가정'!$C$89))+'8_가정'!$C$108</f>
-        <v>76766.095</v>
+        <v>77042.595</v>
       </c>
       <c r="D106" s="67" t="n">
         <v>300000</v>
@@ -45921,7 +46052,7 @@
       </c>
       <c r="I106" s="101" t="inlineStr">
         <is>
-          <t>2024 0.88억, 2025 0.31억 실적(영업외수익 처리 선례). 2027 3억(사용자 제공), 2028~ 연 1억 보수적 가정(과제 수행 비용 대응 한도 내 확인 필요)</t>
+          <t>2024 0.88억, 2025 0.31억 실적(영업외수익 처리 선례). 2027 3억(회사 추정), 2028~ 연 1억 보수적 가정(과제 수행 비용 대응 한도 내)</t>
         </is>
       </c>
     </row>
@@ -45933,7 +46064,7 @@
       </c>
       <c r="B107" s="15" t="inlineStr">
         <is>
-          <t>사용자 제공: 약 2.6억원</t>
+          <t>회사 추정: 약 2.6억원</t>
         </is>
       </c>
       <c r="C107" s="67" t="n">
@@ -45971,7 +46102,7 @@
       </c>
       <c r="I109" s="101" t="inlineStr">
         <is>
-          <t>영업외수익 인식 한도 = 과제 수행으로 해당 연도에 비용 처리된 R&amp;D 비용(경상 연구개발비 + 연구 인력 인건비). 자산화(개발비)된 지출에 대응하는 보조금은 자산 차감이며 영업외수익이 아님(일반기업회계기준 17장). 수령액 중 미사용분은 선수·이연수익. 회사는 과거 정부보조금수익을 영업외수익으로 처리(2024 0.88억·2025 0.31억). 회계 담당 확인 필요</t>
+          <t>영업외수익 인식 한도 = 과제 수행으로 해당 연도에 비용 처리된 R&amp;D 비용(경상 연구개발비 + 연구 인력 인건비). 자산화(개발비)된 지출에 대응하는 보조금은 자산 차감이며 영업외수익이 아님(일반기업회계기준 17장). 수령액 중 미사용분은 선수·이연수익. 회사는 과거 정부보조금수익을 영업외수익으로 처리(2024 0.88억·2025 0.31억). 회계처리는 회계 기준 해석에 따라 달라질 수 있음. 2026 금액은 경상 연구개발비(매출 %)에 연동되어 시나리오별로 변동</t>
         </is>
       </c>
     </row>
@@ -45991,7 +46122,7 @@
       </c>
       <c r="I110" s="101" t="inlineStr">
         <is>
-          <t>계산: 12.375억 − 4.276억 − 38.420억 ≈ −30.3억. 세무상 결손금과 다를 수 있음(세무사 확인)</t>
+          <t>계산: 12.375억 − 4.276억 − 38.420억 ≈ −30.3억. 세무상 결손금과 다를 수 있음</t>
         </is>
       </c>
     </row>
@@ -46113,14 +46244,14 @@
     <row r="120">
       <c r="A120" s="15" t="inlineStr">
         <is>
-          <t>IR 근거 = IR 자료(2026-09-27판) 페이지 표기. 계약/등록/입찰/PoC 단계는 IR 표기에 입찰 자료(저장소)·회사연혁을 교차 반영.</t>
+          <t>IR 근거 = IR 자료(2026-09-27판) 페이지 표기. 계약/등록/입찰/PoC 단계는 IR 표기에 입찰 자료·회사연혁을 교차 반영.</t>
         </is>
       </c>
     </row>
     <row r="121">
       <c r="A121" s="15" t="inlineStr">
         <is>
-          <t>가정 = IR에 없는 성장률·비용률·제품 믹스. 모두 파란색 입력이며 투자사 질의 시 근거 설명이 필요한 항목. 거래처 월별 매출은 사용자 매출표(2026-10-09) 입력값.</t>
+          <t>가정 = IR에 없는 성장률·비용률·제품 믹스. 모두 파란색 입력이며 근거는 각 행 비고 참조. 거래처 월별 매출은 거래처 매출표(2026-10-09) 입력값.</t>
         </is>
       </c>
     </row>
@@ -46134,7 +46265,7 @@
     <row r="124">
       <c r="A124" s="9" t="inlineStr">
         <is>
-          <t>외부 팩트 조사 요약(출처 URL 포함)</t>
+          <t>외부 팩트 조사 요약(출처 표기)</t>
         </is>
       </c>
     </row>
@@ -46155,7 +46286,7 @@
     <row r="127">
       <c r="A127" s="66" t="inlineStr">
         <is>
-          <t>일본: 介護テクノロジー導入支援事業(2025년 통합) 보조율 3/4~4/5, 배설예측·검지 기기 1대당 상한 30만엔, TAIS 介護テクノロジー 선정이 보조금 신청 조건(techno-aids.or.jp). TAIS 등록 자체는 보험급여가 아님 → IR의 "TAIS 등록 완료"가 보조금 대상 선정을 뜻하는지 확인 필요. 시설 수(MHLW 2024): 특양 8,621 · 老健 4,214 · GH 14,341 · 유료노인홈 16,543.</t>
+          <t>일본: 介護テクノロジー導入支援事業(2025년 통합) 보조율 3/4~4/5, 배설예측·검지 기기 1대당 상한 30만엔, TAIS 介護テクノロジー 선정이 보조금 신청 조건(techno-aids.or.jp). TAIS 등록 자체는 보험급여가 아니며 보조금 신청 조건인 TAIS 선정과는 구분됨. 시설 수(MHLW 2024): 특양 8,621 · 老健 4,214 · GH 14,341 · 유료노인홈 16,543.</t>
         </is>
       </c>
     </row>
@@ -46169,7 +46300,7 @@
     <row r="129">
       <c r="A129" s="66" t="inlineStr">
         <is>
-          <t>동종 벤치마크: Essity FY2025 EBITA 마진 14.1%, Ontex FY2025 조정 EBITDA 마진 10.0% → 본 계획 S1의 2030 영업이익률(약 16%)은 이들보다 높아 투자사 질의 지점(★제출전_확인사항 참조). 일부 공식 사이트 접근 제한으로 보도·2차 자료를 포함하므로 제출 전 재확인 권장.</t>
+          <t>동종 벤치마크: Essity FY2025 EBITA 마진 14.1%, Ontex FY2025 조정 EBITDA 마진 10.0% → 본 계획 S1의 2030 영업이익률(약 16%)은 이들보다 높음. 일부 수치는 보도·2차 자료 기반.</t>
         </is>
       </c>
     </row>
@@ -46187,7 +46318,7 @@
     <outlinePr summaryBelow="1" summaryRight="1"/>
     <pageSetUpPr fitToPage="1"/>
   </sheetPr>
-  <dimension ref="A1:H63"/>
+  <dimension ref="A1:H64"/>
   <sheetFormatPr baseColWidth="8" defaultRowHeight="15"/>
   <cols>
     <col width="34" customWidth="1" min="1" max="1"/>
@@ -46211,7 +46342,7 @@
     <row r="2">
       <c r="A2" s="2" t="inlineStr">
         <is>
-          <t>단위: 억원. S2·S3는 S1(경영계획) 매출의 80%·60%를 거래처 전체에 일률 적용한 완만한 시나리오입니다. 값은 시나리오별로 재계산한 스냅샷입니다. 입력을 바꾼 뒤에는 "라이브" 행과 비교해 일치 여부(점검 행)를 확인하세요.</t>
+          <t>단위: 억원. S2·S3는 S1(경영계획) 매출의 80%·60%를 거래처 전체에 일률 적용한 완만한 시나리오입니다. 값은 시나리오별로 재계산한 스냅샷입니다. 입력 변경 시 "점검" 행이 스냅샷 갱신 여부를 표시합니다.</t>
         </is>
       </c>
     </row>
@@ -46258,10 +46389,10 @@
         </is>
       </c>
       <c r="C6" s="111" t="n">
-        <v>11.93317</v>
+        <v>12.01217</v>
       </c>
       <c r="D6" s="111" t="n">
-        <v>111.848</v>
+        <v>112.048</v>
       </c>
       <c r="E6" s="111" t="n">
         <v>330</v>
@@ -46284,19 +46415,19 @@
         </is>
       </c>
       <c r="C7" s="111" t="n">
-        <v>5.957275671</v>
+        <v>5.996159470999999</v>
       </c>
       <c r="D7" s="111" t="n">
-        <v>44.4544508</v>
+        <v>44.5318508</v>
       </c>
       <c r="E7" s="111" t="n">
-        <v>130.77002322</v>
+        <v>130.76001322</v>
       </c>
       <c r="F7" s="111" t="n">
-        <v>279.4089323776</v>
+        <v>279.3838943776</v>
       </c>
       <c r="G7" s="111" t="n">
-        <v>637.788779409696</v>
+        <v>637.740917985696</v>
       </c>
     </row>
     <row r="8">
@@ -46306,19 +46437,19 @@
         </is>
       </c>
       <c r="C8" s="111" t="n">
-        <v>0.189224991</v>
+        <v>0.219576791000001</v>
       </c>
       <c r="D8" s="111" t="n">
-        <v>11.6546401344</v>
+        <v>11.7020401344</v>
       </c>
       <c r="E8" s="111" t="n">
-        <v>37.334036193904</v>
+        <v>37.324026193904</v>
       </c>
       <c r="F8" s="111" t="n">
-        <v>96.3220719432603</v>
+        <v>96.29703394326029</v>
       </c>
       <c r="G8" s="111" t="n">
-        <v>255.56282577049</v>
+        <v>255.51496434649</v>
       </c>
     </row>
     <row r="9">
@@ -46328,19 +46459,19 @@
         </is>
       </c>
       <c r="C9" s="112" t="n">
-        <v>0.0158570598591992</v>
+        <v>0.0182795274292655</v>
       </c>
       <c r="D9" s="112" t="n">
-        <v>0.104200702152922</v>
+        <v>0.104437742167642</v>
       </c>
       <c r="E9" s="112" t="n">
-        <v>0.11313344301183</v>
+        <v>0.113103109678497</v>
       </c>
       <c r="F9" s="112" t="n">
-        <v>0.137602959918943</v>
+        <v>0.137567191347515</v>
       </c>
       <c r="G9" s="112" t="n">
-        <v>0.163822324211852</v>
+        <v>0.163791643811852</v>
       </c>
     </row>
     <row r="10">
@@ -46350,19 +46481,19 @@
         </is>
       </c>
       <c r="C10" s="111" t="n">
-        <v>0.380995621</v>
+        <v>0.414112421000001</v>
       </c>
       <c r="D10" s="111" t="n">
-        <v>13.8866401344</v>
+        <v>13.9340401344</v>
       </c>
       <c r="E10" s="111" t="n">
-        <v>32.1546487650571</v>
+        <v>32.1291272690571</v>
       </c>
       <c r="F10" s="111" t="n">
-        <v>73.13601611574299</v>
+        <v>73.116486475743</v>
       </c>
       <c r="G10" s="111" t="n">
-        <v>195.092381934031</v>
+        <v>195.056102974639</v>
       </c>
     </row>
     <row r="11">
@@ -46372,19 +46503,19 @@
         </is>
       </c>
       <c r="C11" s="113" t="n">
-        <v>928.102875</v>
+        <v>934.686208333333</v>
       </c>
       <c r="D11" s="113" t="n">
-        <v>8795.97166666667</v>
+        <v>8812.638333333331</v>
       </c>
       <c r="E11" s="113" t="n">
-        <v>25104.4494666667</v>
+        <v>25109.6494666667</v>
       </c>
       <c r="F11" s="113" t="n">
-        <v>50397.0821066667</v>
+        <v>50410.3421066667</v>
       </c>
       <c r="G11" s="113" t="n">
-        <v>105961.8822208</v>
+        <v>105986.1246208</v>
       </c>
     </row>
     <row r="12">
@@ -46394,10 +46525,10 @@
         </is>
       </c>
       <c r="C12" s="112" t="n">
-        <v>0.994430833333333</v>
+        <v>1.00101416666667</v>
       </c>
       <c r="D12" s="112" t="n">
-        <v>1.11792103948026</v>
+        <v>1.11992003998001</v>
       </c>
       <c r="E12" s="112" t="n">
         <v>1</v>
@@ -46453,10 +46584,10 @@
         </is>
       </c>
       <c r="C17" s="111" t="n">
-        <v>9.546536</v>
+        <v>9.609736</v>
       </c>
       <c r="D17" s="111" t="n">
-        <v>89.47839999999999</v>
+        <v>89.6384</v>
       </c>
       <c r="E17" s="111" t="n">
         <v>264</v>
@@ -46479,19 +46610,19 @@
         </is>
       </c>
       <c r="C18" s="111" t="n">
-        <v>4.76010139525643</v>
+        <v>4.79125499837656</v>
       </c>
       <c r="D18" s="111" t="n">
-        <v>35.56356064</v>
+        <v>35.62548064</v>
       </c>
       <c r="E18" s="111" t="n">
-        <v>104.616018576</v>
+        <v>104.608010576</v>
       </c>
       <c r="F18" s="111" t="n">
-        <v>223.52714590208</v>
+        <v>223.50711550208</v>
       </c>
       <c r="G18" s="111" t="n">
-        <v>510.231023527757</v>
+        <v>510.192734388557</v>
       </c>
     </row>
     <row r="19">
@@ -46501,19 +46632,19 @@
         </is>
       </c>
       <c r="C19" s="111" t="n">
-        <v>-0.7501928127435751</v>
+        <v>-0.7258648096234399</v>
       </c>
       <c r="D19" s="111" t="n">
-        <v>7.18696858335999</v>
+        <v>7.22488858335999</v>
       </c>
       <c r="E19" s="111" t="n">
-        <v>25.589366266352</v>
+        <v>25.581358266352</v>
       </c>
       <c r="F19" s="111" t="n">
-        <v>69.36655218398819</v>
+        <v>69.34652178398829</v>
       </c>
       <c r="G19" s="111" t="n">
-        <v>191.778286452798</v>
+        <v>191.739997313598</v>
       </c>
     </row>
     <row r="20">
@@ -46523,19 +46654,19 @@
         </is>
       </c>
       <c r="C20" s="112" t="n">
-        <v>-0.0785827249531741</v>
+        <v>-0.0755343132863837</v>
       </c>
       <c r="D20" s="112" t="n">
-        <v>0.0803207096166224</v>
+        <v>0.08060037420748239</v>
       </c>
       <c r="E20" s="112" t="n">
-        <v>0.0969294176755757</v>
+        <v>0.0968990843422424</v>
       </c>
       <c r="F20" s="112" t="n">
-        <v>0.123868843185693</v>
+        <v>0.123833074614265</v>
       </c>
       <c r="G20" s="112" t="n">
-        <v>0.153668498760255</v>
+        <v>0.153637818360255</v>
       </c>
     </row>
     <row r="21">
@@ -46545,19 +46676,19 @@
         </is>
       </c>
       <c r="C21" s="111" t="n">
-        <v>-0.641954372743575</v>
+        <v>-0.61541436962344</v>
       </c>
       <c r="D21" s="111" t="n">
-        <v>9.418968583359989</v>
+        <v>9.456888583359989</v>
       </c>
       <c r="E21" s="111" t="n">
-        <v>24.2017429614189</v>
+        <v>24.1813155207325</v>
       </c>
       <c r="F21" s="111" t="n">
-        <v>52.1107107035108</v>
+        <v>52.0950869915108</v>
       </c>
       <c r="G21" s="111" t="n">
-        <v>146.468663433183</v>
+        <v>146.438797904607</v>
       </c>
     </row>
     <row r="22">
@@ -46567,19 +46698,19 @@
         </is>
       </c>
       <c r="C22" s="113" t="n">
-        <v>746.670258735537</v>
+        <v>751.900762406309</v>
       </c>
       <c r="D22" s="113" t="n">
-        <v>7036.77733333333</v>
+        <v>7050.11066666667</v>
       </c>
       <c r="E22" s="113" t="n">
-        <v>20083.5595733333</v>
+        <v>20087.7195733333</v>
       </c>
       <c r="F22" s="113" t="n">
-        <v>40317.6656853333</v>
+        <v>40328.2736853333</v>
       </c>
       <c r="G22" s="113" t="n">
-        <v>84769.50577664</v>
+        <v>84788.89969664</v>
       </c>
     </row>
     <row r="23">
@@ -46589,10 +46720,10 @@
         </is>
       </c>
       <c r="C23" s="112" t="n">
-        <v>0.795544666666667</v>
+        <v>0.800811333333333</v>
       </c>
       <c r="D23" s="112" t="n">
-        <v>0.894336831584208</v>
+        <v>0.895936031984008</v>
       </c>
       <c r="E23" s="112" t="n">
         <v>0.8</v>
@@ -46648,10 +46779,10 @@
         </is>
       </c>
       <c r="C28" s="111" t="n">
-        <v>7.159902</v>
+        <v>7.207301999999999</v>
       </c>
       <c r="D28" s="111" t="n">
-        <v>67.1088</v>
+        <v>67.22880000000001</v>
       </c>
       <c r="E28" s="111" t="n">
         <v>198</v>
@@ -46674,19 +46805,19 @@
         </is>
       </c>
       <c r="C29" s="111" t="n">
-        <v>3.56292711951285</v>
+        <v>3.58635052575312</v>
       </c>
       <c r="D29" s="111" t="n">
-        <v>26.67267048</v>
+        <v>26.71911048</v>
       </c>
       <c r="E29" s="111" t="n">
-        <v>78.462013932</v>
+        <v>78.45600793200001</v>
       </c>
       <c r="F29" s="111" t="n">
-        <v>167.64535942656</v>
+        <v>167.63033662656</v>
       </c>
       <c r="G29" s="111" t="n">
-        <v>382.673267645818</v>
+        <v>382.6445507914181</v>
       </c>
     </row>
     <row r="30">
@@ -46696,19 +46827,19 @@
         </is>
       </c>
       <c r="C30" s="111" t="n">
-        <v>-1.68961061648715</v>
+        <v>-1.67130641024688</v>
       </c>
       <c r="D30" s="111" t="n">
-        <v>2.72433652048</v>
+        <v>2.75277652048</v>
       </c>
       <c r="E30" s="111" t="n">
-        <v>13.844948313208</v>
+        <v>13.838942313208</v>
       </c>
       <c r="F30" s="111" t="n">
-        <v>42.4112843991242</v>
+        <v>42.39626159912429</v>
       </c>
       <c r="G30" s="111" t="n">
-        <v>127.993999109515</v>
+        <v>127.965282255115</v>
       </c>
     </row>
     <row r="31">
@@ -46718,19 +46849,19 @@
         </is>
       </c>
       <c r="C31" s="112" t="n">
-        <v>-0.23598236630713</v>
+        <v>-0.231890714479133</v>
       </c>
       <c r="D31" s="112" t="n">
-        <v>0.040595816353146</v>
+        <v>0.0409463878647247</v>
       </c>
       <c r="E31" s="112" t="n">
-        <v>0.0699239813798383</v>
+        <v>0.06989364804650509</v>
       </c>
       <c r="F31" s="112" t="n">
-        <v>0.100979248569343</v>
+        <v>0.100943479997915</v>
       </c>
       <c r="G31" s="112" t="n">
-        <v>0.136745725544354</v>
+        <v>0.136715045144354</v>
       </c>
     </row>
     <row r="32">
@@ -46740,19 +46871,19 @@
         </is>
       </c>
       <c r="C32" s="111" t="n">
-        <v>-1.66490436648715</v>
+        <v>-1.64494116024688</v>
       </c>
       <c r="D32" s="111" t="n">
-        <v>4.95633652048</v>
+        <v>4.984776520480001</v>
       </c>
       <c r="E32" s="111" t="n">
-        <v>12.924948313208</v>
+        <v>12.918942313208</v>
       </c>
       <c r="F32" s="111" t="n">
-        <v>34.18857852853269</v>
+        <v>34.1675333591599</v>
       </c>
       <c r="G32" s="111" t="n">
-        <v>96.7169193054218</v>
+        <v>96.69452015899</v>
       </c>
     </row>
     <row r="33">
@@ -46762,19 +46893,19 @@
         </is>
       </c>
       <c r="C33" s="113" t="n">
-        <v>565.237642471074</v>
+        <v>569.115316479284</v>
       </c>
       <c r="D33" s="113" t="n">
-        <v>5277.583</v>
+        <v>5287.583</v>
       </c>
       <c r="E33" s="113" t="n">
-        <v>15062.66968</v>
+        <v>15065.78968</v>
       </c>
       <c r="F33" s="113" t="n">
-        <v>30238.249264</v>
+        <v>30246.205264</v>
       </c>
       <c r="G33" s="113" t="n">
-        <v>63577.12933248</v>
+        <v>63591.67477248</v>
       </c>
     </row>
     <row r="34">
@@ -46784,10 +46915,10 @@
         </is>
       </c>
       <c r="C34" s="112" t="n">
-        <v>0.5966585</v>
+        <v>0.6006085</v>
       </c>
       <c r="D34" s="112" t="n">
-        <v>0.670752623688156</v>
+        <v>0.671952023988006</v>
       </c>
       <c r="E34" s="112" t="n">
         <v>0.6</v>
@@ -47010,11 +47141,11 @@
       </c>
       <c r="C48" s="17">
         <f>'3_연간손익'!D7/100000</f>
-        <v>11.93317</v>
+        <v>12.01217</v>
       </c>
       <c r="D48" s="17">
         <f>'3_연간손익'!E7/100000</f>
-        <v>111.848</v>
+        <v>112.048</v>
       </c>
       <c r="E48" s="17">
         <f>'3_연간손익'!F7/100000</f>
@@ -47041,23 +47172,23 @@
       </c>
       <c r="C49" s="17">
         <f>'3_연간손익'!D10/100000</f>
-        <v>5.957275671</v>
+        <v>5.996159471</v>
       </c>
       <c r="D49" s="17">
         <f>'3_연간손익'!E10/100000</f>
-        <v>44.4544508</v>
+        <v>44.5318508</v>
       </c>
       <c r="E49" s="17">
         <f>'3_연간손익'!F10/100000</f>
-        <v>130.77002322</v>
+        <v>130.76001322</v>
       </c>
       <c r="F49" s="17">
         <f>'3_연간손익'!G10/100000</f>
-        <v>279.4089323776</v>
+        <v>279.3838943776</v>
       </c>
       <c r="G49" s="17">
         <f>'3_연간손익'!H10/100000</f>
-        <v>637.788779409696</v>
+        <v>637.740917985696</v>
       </c>
     </row>
     <row r="50">
@@ -47072,23 +47203,23 @@
       </c>
       <c r="C50" s="17">
         <f>'3_연간손익'!D13/100000</f>
-        <v>0.189224991</v>
+        <v>0.219576791000001</v>
       </c>
       <c r="D50" s="17">
         <f>'3_연간손익'!E13/100000</f>
-        <v>11.6546401344</v>
+        <v>11.7020401344</v>
       </c>
       <c r="E50" s="17">
         <f>'3_연간손익'!F13/100000</f>
-        <v>37.334036193904</v>
+        <v>37.324026193904</v>
       </c>
       <c r="F50" s="17">
         <f>'3_연간손익'!G13/100000</f>
-        <v>96.3220719432602</v>
+        <v>96.2970339432603</v>
       </c>
       <c r="G50" s="17">
         <f>'3_연간손익'!H13/100000</f>
-        <v>255.56282577049</v>
+        <v>255.51496434649</v>
       </c>
     </row>
     <row r="51">
@@ -47103,23 +47234,23 @@
       </c>
       <c r="C51" s="16">
         <f>'3_연간손익'!D14</f>
-        <v>0.0158570598591992</v>
+        <v>0.0182795274292655</v>
       </c>
       <c r="D51" s="16">
         <f>'3_연간손익'!E14</f>
-        <v>0.104200702152922</v>
+        <v>0.104437742167642</v>
       </c>
       <c r="E51" s="16">
         <f>'3_연간손익'!F14</f>
-        <v>0.11313344301183</v>
+        <v>0.113103109678497</v>
       </c>
       <c r="F51" s="16">
         <f>'3_연간손익'!G14</f>
-        <v>0.137602959918943</v>
+        <v>0.137567191347515</v>
       </c>
       <c r="G51" s="16">
         <f>'3_연간손익'!H14</f>
-        <v>0.163822324211852</v>
+        <v>0.163791643811852</v>
       </c>
     </row>
     <row r="52">
@@ -47134,23 +47265,23 @@
       </c>
       <c r="C52" s="17">
         <f>'3_연간손익'!D21/100000</f>
-        <v>0.380995621</v>
+        <v>0.414112421000001</v>
       </c>
       <c r="D52" s="17">
         <f>'3_연간손익'!E21/100000</f>
-        <v>13.8866401344</v>
+        <v>13.9340401344</v>
       </c>
       <c r="E52" s="17">
         <f>'3_연간손익'!F21/100000</f>
-        <v>32.1546487650571</v>
+        <v>32.1291272690571</v>
       </c>
       <c r="F52" s="17">
         <f>'3_연간손익'!G21/100000</f>
-        <v>73.136016115743</v>
+        <v>73.116486475743</v>
       </c>
       <c r="G52" s="17">
         <f>'3_연간손익'!H21/100000</f>
-        <v>195.092381934031</v>
+        <v>195.056102974639</v>
       </c>
     </row>
     <row r="53">
@@ -47165,23 +47296,23 @@
       </c>
       <c r="C53" s="18">
         <f>'3_연간손익'!D26</f>
-        <v>928.102875</v>
+        <v>934.686208333333</v>
       </c>
       <c r="D53" s="18">
         <f>'3_연간손익'!E26</f>
-        <v>8795.97166666667</v>
+        <v>8812.63833333333</v>
       </c>
       <c r="E53" s="18">
         <f>'3_연간손익'!F26</f>
-        <v>25104.4494666667</v>
+        <v>25109.6494666667</v>
       </c>
       <c r="F53" s="18">
         <f>'3_연간손익'!G26</f>
-        <v>50397.0821066667</v>
+        <v>50410.3421066667</v>
       </c>
       <c r="G53" s="18">
         <f>'3_연간손익'!H26</f>
-        <v>105961.8822208</v>
+        <v>105986.1246208</v>
       </c>
     </row>
     <row r="54">
@@ -47196,11 +47327,11 @@
       </c>
       <c r="C54" s="16">
         <f>'3_연간손익'!D28</f>
-        <v>0.994430833333333</v>
+        <v>1.00101416666667</v>
       </c>
       <c r="D54" s="16">
         <f>'3_연간손익'!E28</f>
-        <v>1.11792103948026</v>
+        <v>1.11992003998001</v>
       </c>
       <c r="E54" s="16">
         <f>'3_연간손익'!F28</f>
@@ -47243,40 +47374,67 @@
         <v>OK</v>
       </c>
     </row>
-    <row r="57"/>
+    <row r="57">
+      <c r="A57" s="12" t="inlineStr">
+        <is>
+          <t>점검: 라이브 영업이익 = 선택 시나리오 스냅샷</t>
+        </is>
+      </c>
+      <c r="C57" s="115" t="str">
+        <f>IF(ISNUMBER(C8),IF(ABS(C50-CHOOSE('1_요약'!$C$5,C8,C19,C30))&lt;0.05,"OK","갱신 필요"),"스냅샷 없음")</f>
+        <v>OK</v>
+      </c>
+      <c r="D57" s="115" t="str">
+        <f>IF(ISNUMBER(D8),IF(ABS(D50-CHOOSE('1_요약'!$C$5,D8,D19,D30))&lt;0.05,"OK","갱신 필요"),"스냅샷 없음")</f>
+        <v>OK</v>
+      </c>
+      <c r="E57" s="115" t="str">
+        <f>IF(ISNUMBER(E8),IF(ABS(E50-CHOOSE('1_요약'!$C$5,E8,E19,E30))&lt;0.05,"OK","갱신 필요"),"스냅샷 없음")</f>
+        <v>OK</v>
+      </c>
+      <c r="F57" s="115" t="str">
+        <f>IF(ISNUMBER(F8),IF(ABS(F50-CHOOSE('1_요약'!$C$5,F8,F19,F30))&lt;0.05,"OK","갱신 필요"),"스냅샷 없음")</f>
+        <v>OK</v>
+      </c>
+      <c r="G57" s="115" t="str">
+        <f>IF(ISNUMBER(G8),IF(ABS(G50-CHOOSE('1_요약'!$C$5,G8,G19,G30))&lt;0.05,"OK","갱신 필요"),"스냅샷 없음")</f>
+        <v>OK</v>
+      </c>
+    </row>
     <row r="58"/>
-    <row r="59">
-      <c r="A59" s="3" t="inlineStr">
+    <row r="59"/>
+    <row r="60">
+      <c r="A60" s="3" t="inlineStr">
         <is>
           <t>시나리오 정의</t>
-        </is>
-      </c>
-    </row>
-    <row r="60">
-      <c r="A60" s="20" t="inlineStr">
-        <is>
-          <t>S1 경영계획(100%): 거래처 매출표(2026·2027 입력)와 IR 목표(2028~30, 삼성 글로벌 채널 = 잔차)를 그대로 반영.</t>
         </is>
       </c>
     </row>
     <row r="61">
       <c r="A61" s="20" t="inlineStr">
         <is>
-          <t>S2 기준(80%): 각 연도 매출 = S1의 80%. 모든 거래처·제품에 일률 적용(2026은 1~9월 실적 고정, 10~12월에 계수 역산 적용해 연간 80%).</t>
+          <t>S1 경영계획(100%): 거래처 매출표(2026·2027 입력)와 IR 목표(2028~30, 삼성 글로벌 채널 = 잔차)를 그대로 반영.</t>
         </is>
       </c>
     </row>
     <row r="62">
       <c r="A62" s="20" t="inlineStr">
         <is>
-          <t>S3 보수(60%): 각 연도 매출 = S1의 60%. 방식은 S2와 동일(2026은 1~9월 실적 고정 후 10~12월에 역산 적용).</t>
+          <t>S2 기준(80%): 각 연도 매출 = S1의 80%. 모든 거래처·제품에 일률 적용(2026은 1~9월 실적 고정, 10~12월에 계수 역산 적용해 연간 80%).</t>
         </is>
       </c>
     </row>
     <row r="63">
       <c r="A63" s="20" t="inlineStr">
         <is>
-          <t>인원은 2027년부터 매출 달성률에 75% 탄력적으로 연동(25%는 고정, 2026은 현 인력 7명 유지). 임차·출장·상각 등 고정비는 유지되어 규모 하락 시 이익률이 낮아집니다. 달성률은 8_가정 §2에서 조정 가능(S1 100%·S2 80%·S3 60%).</t>
+          <t>S3 보수(60%): 각 연도 매출 = S1의 60%. 방식은 S2와 동일(2026은 1~9월 실적 고정 후 10~12월에 역산 적용).</t>
+        </is>
+      </c>
+    </row>
+    <row r="64">
+      <c r="A64" s="20" t="inlineStr">
+        <is>
+          <t>인원은 2027년부터 매출 달성률에 75% 탄력적으로 연동(25%는 고정, 2026은 현 인력 7명 유지). 임차·출장·기존 개발비 상각 등 고정비는 유지되어(신규 자본화분 상각은 인원 연동으로 소폭 감소) 규모 하락 시 이익률이 낮아집니다. 달성률은 8_가정 §2에서 조정 가능(S1 100%·S2 80%·S3 60%).</t>
         </is>
       </c>
     </row>
